--- a/check2.xlsx
+++ b/check2.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL61"/>
+  <dimension ref="A1:AL64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1236,7 +1236,7 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>RBL Bank: RBI Approves Capital Increase
-Authorized capital rises from ₹1,000 Crore to ₹1,800 Crore (80 Crore new equity shares of ₹10 each)
+Authorized capital rises from ₹1,000 Crores to ₹1,800 Crores (80 Crores new equity shares of ₹10 each)
 MoA amendment cleared; paves the way for a preferential issue to Emirates NBD Bank
 Issue pending other regulatory approvals and conditions</t>
         </is>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>RBL Bank: RBI Approves Capital Increase Authorized capital rises from ₹1,000 Crore to ₹1,800 Crore (80 Crore new equity …</t>
+          <t>RBL Bank: RBI Approves Capital Increase Authorized capital rises from ₹1,000 Crores to ₹1,800 Crores (80 Crores new equi…</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -2133,6 +2133,310 @@
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
+        <is>
+          <t>الخاص مقفل</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>الخاص مقفل</t>
+        </is>
+      </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>['yara_saeed3', 'RotanaLive', 'RabehSaqer', 'JEDCalendar', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>7h</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Apr 10, 2026 · 12:02 AM UTC</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>46122.00138888889</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>38</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>الخاص مقفل</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>الخاص مقفل</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>The private is locked.</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE11" s="2" t="n">
+        <v>46122.16805555556</v>
+      </c>
+      <c r="AF11" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>The private is locked.</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK11" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>yara_saeed3, RotanaLive, RabehSaqer, JEDCalendar, EmiratesNBD_KSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2042390089641193859</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://x.com/Sadziz13/status/2042390089641193859</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://x.com/Sadziz13</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sadziz13</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>مَ. سعـد عبدالعزيز</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1711030291840577537/3X1cIUsy_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>@RotanaLive @RabehMedia @RabehSaqer @JEDCalendar @EmiratesNBD_KSA ليلة بانتظارك يا كبير المسرح ❤️🦅</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ليلة بانتظارك يا كبير المسرح ❤️🦅</t>
+        </is>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>['RotanaLive', 'RabehMedia', 'RabehSaqer', 'JEDCalendar', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>7h</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Apr 9, 2026 · 11:51 PM UTC</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>46121.99375</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>138</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>ليلة بانتظارك يا كبير المسرح ❤️🦅</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>https://x.com/Sadziz13/status/2042390089641193859</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>@RotanaLive @RabehMedia @RabehSaqer @JEDCalendar @EmiratesNBD_KSA ليلة بانتظارك يا كبير المسرح ❤️🦅</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>@RotanaLive @RabehMedia @RabehSaqer @JEDCalendar @EmiratesNBD_KSA ليلة بانتظارك يا كبير المسرح ❤️🦅</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>A night waiting for you, great one of the theater ❤️🦅</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE12" s="2" t="n">
+        <v>46122.16041666667</v>
+      </c>
+      <c r="AF12" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>A night waiting for you, great one of the theater ❤️🦅</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK12" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>RotanaLive, RabehMedia, RabehSaqer, JEDCalendar, EmiratesNBD_KSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2042389076863537661</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://x.com/yara_saeed3/status/2042389076863537661</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://x.com/yara_saeed3</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>yara_saeed3</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Yara.S.B</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1350213646945816589/3DACZ1Rf_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
         <is>
           <t>جمهور صقر الأغنية الخليجية في جدة غير 😉
 🔥🔥 SOLD OUT 
@@ -2145,63 +2449,65 @@
 @EmiratesNBD_KSA https://t.co/ushr2PgKVi</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>الخاص مقفل</t>
-        </is>
-      </c>
-      <c r="K11" t="b">
-        <v>0</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>['yara_saeed3', 'RotanaLive', 'RabehSaqer', 'JEDCalendar', 'EmiratesNBD_KSA']</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>عندي تذكرتين حفلة رابح صقر بجدة  B Center  
+التواصل خاص</t>
+        </is>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>['RotanaLive', 'RabehSaqer', 'JEDCalendar', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>7h</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Apr 10, 2026 · 12:02 AM UTC</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="n">
-        <v>46122.00138888889</v>
-      </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>38</v>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>الخاص مقفل</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>https://x.com/yourwishesst/status/2042392677023404378</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Apr 9, 2026 · 11:47 PM UTC</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>46121.99097222222</v>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>132</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>عندي تذكرتين حفلة رابح صقر بجدة  B Center  
+التواصل خاص</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>https://x.com/yara_saeed3/status/2042389076863537661</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
         <is>
           <t>جمهور صقر الأغنية الخليجية في جدة غير 😉
 🔥🔥 SOLD OUT 
@@ -2214,7 +2520,7 @@
 @EmiratesNBD_KSA https://t.co/ushr2PgKVi</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>جمهور صقر الأغنية الخليجية في جدة غير 😉
 🔥🔥 SOLD OUT 
@@ -2227,7 +2533,7 @@
 @EmiratesNBD_KSA https://t.co/ushr2PgKVi</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>The audience of the Gulf songbird in Jeddah is unique 😉  
 🔥🔥 SOLD OUT  
@@ -2240,314 +2546,6 @@
 @EmiratesNBD_KSA</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE11" s="2" t="n">
-        <v>46122.16805555556</v>
-      </c>
-      <c r="AF11" s="2" t="n">
-        <v>46122</v>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>The audience of the Gulf songbird in Jeddah is unique 😉 🔥🔥 SOLD OUT An exceptional night awaits you on April 10✨🦅 #Rabeh…</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK11" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>yara_saeed3, RotanaLive, RabehSaqer, JEDCalendar, EmiratesNBD_KSA</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2042390089641193859</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>https://x.com/Sadziz13/status/2042390089641193859</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>https://x.com/Sadziz13</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Sadziz13</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>مَ. سعـد عبدالعزيز</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1711030291840577537/3X1cIUsy_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>@RotanaLive @RabehMedia @RabehSaqer @JEDCalendar @EmiratesNBD_KSA ليلة بانتظارك يا كبير المسرح ❤️🦅</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>ليلة بانتظارك يا كبير المسرح ❤️🦅</t>
-        </is>
-      </c>
-      <c r="K12" t="b">
-        <v>0</v>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>['RotanaLive', 'RabehMedia', 'RabehSaqer', 'JEDCalendar', 'EmiratesNBD_KSA']</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>7h</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Apr 9, 2026 · 11:51 PM UTC</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="n">
-        <v>46121.99375</v>
-      </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>138</v>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>ليلة بانتظارك يا كبير المسرح ❤️🦅</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>https://x.com/Sadziz13/status/2042390089641193859</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>@RotanaLive @RabehMedia @RabehSaqer @JEDCalendar @EmiratesNBD_KSA ليلة بانتظارك يا كبير المسرح ❤️🦅</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>@RotanaLive @RabehMedia @RabehSaqer @JEDCalendar @EmiratesNBD_KSA ليلة بانتظارك يا كبير المسرح ❤️🦅</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>A night waiting for you, great of the theater ❤️🦅</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE12" s="2" t="n">
-        <v>46122.16041666667</v>
-      </c>
-      <c r="AF12" s="2" t="n">
-        <v>46122</v>
-      </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>A night waiting for you, great of the theater ❤️🦅</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK12" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>RotanaLive, RabehMedia, RabehSaqer, JEDCalendar, EmiratesNBD_KSA</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2042389076863537661</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>https://x.com/yara_saeed3/status/2042389076863537661</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>https://x.com/yara_saeed3</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>yara_saeed3</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Yara.S.B</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1350213646945816589/3DACZ1Rf_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>عندي تذكرتين حفلة رابح صقر بجدة  B Center  
-التواصل خاص</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>عندي تذكرتين حفلة رابح صقر بجدة  B Center  
-التواصل خاص</t>
-        </is>
-      </c>
-      <c r="K13" t="b">
-        <v>0</v>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>['RotanaLive', 'RabehSaqer', 'JEDCalendar', 'EmiratesNBD_KSA']</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>7h</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Apr 9, 2026 · 11:47 PM UTC</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="n">
-        <v>46121.99097222222</v>
-      </c>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>132</v>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>عندي تذكرتين حفلة رابح صقر بجدة  B Center  
-التواصل خاص</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>عندي تذكرتين حفلة رابح صقر بجدة  B Center  
-التواصل خاص</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>I have two tickets for Rabih Saqr's concert in Jeddah at B Center. Contact me privately.</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
           <t>Cust</t>
@@ -2576,7 +2574,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>I have two tickets for Rabih Saqr's concert in Jeddah at B Center.</t>
+          <t>The audience of the Gulf songbird in Jeddah is unique 😉 🔥🔥 SOLD OUT An exceptional night awaits you on April 10✨🦅 #Rabeh…</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -4465,10 +4463,8 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>✈️Moving to Dubai in 2026?
-The Metro, the holidays, the brunch culture, the delivery apps, it all hits different when you actually live here.
-🔥Read the full blog: https://t.co/AKgSHoKV0j
-#snxs #dubai #UAElife</t>
+          <t>🇦🇪The UAE's private sector dialogue is exactly what ecosystem resilience looks like in practice. 
+#UAE #EmiratesNBD #SNXS</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -4531,26 +4527,19 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>✈️Moving to Dubai in 2026?
-The Metro, the holidays, the brunch culture, the delivery apps, it all hits different when you actually live here.
-🔥Read the full blog: https://t.co/AKgSHoKV0j
-#snxs #dubai #UAElife</t>
+          <t>🇦🇪The UAE's private sector dialogue is exactly what ecosystem resilience looks like in practice. 
+#UAE #EmiratesNBD #SNXS</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>✈️Moving to Dubai in 2026?
-The Metro, the holidays, the brunch culture, the delivery apps, it all hits different when you actually live here.
-🔥Read the full blog: https://t.co/AKgSHoKV0j
-#snxs #dubai #UAElife</t>
+          <t>🇦🇪The UAE's private sector dialogue is exactly what ecosystem resilience looks like in practice. 
+#UAE #EmiratesNBD #SNXS</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Moving to Dubai in 2026? 
-The Metro, the holidays, the brunch culture, the delivery apps, it all feels different when you actually live here. 
-Read the full blog: https://t.co/AKgSHoKV0j 
-#snxs #dubai #UAElife</t>
+          <t>The UAE's private sector dialogue is exactly what ecosystem resilience looks like in practice.</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -4581,7 +4570,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>The Metro, the holidays, the brunch culture, the delivery apps, it all feels different when you actually live here. • Read the full blog: https://t.co/AKgSHoKV0j #snxs #dubai #UAElife</t>
+          <t>The UAE's private sector dialogue is exactly what ecosystem resilience looks like in practice.</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -5148,7 +5137,7 @@
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>Please provide the post you would like me to analyze.</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE29" s="2" t="n">
@@ -5272,7 +5261,7 @@
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>Please provide the post you would like me to analyze.</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE30" s="2" t="n">
@@ -6689,9 +6678,14 @@
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>🤯More than $10.8 Billion have been invested in Indian Financial Services companies in last 1 year alone!!!
-From Japan’s MUFG investing $4.4 billion in Shriram Finance to the UAE’s Emirates NBD putting $3 billion into RBL Bank
-So, here's why India's banking &amp; NBFC Sector is becoming a global destination for top investment banks &amp; funds👇</t>
+          <t>The world may be ahead in nuclear today
+But India has just made a move that could redefine its position tomorrow
+With the Prototype Fast Breeder Reactor (PFBR) at Kalpakkam achieving criticality, India has officially stepped into the second stage of its nuclear roadmap
+This isn’t just another reactor going live
+It’s the foundation for long-term energy independence
+While the gap with global leaders still exists, the direction has now changed
+The real question is… how fast can India build on this momentum?
+#SMCGlobal #Nuclear #Energy</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -6745,20 +6739,44 @@
 So, here's why India's banking &amp; NBFC Sector is becoming a global destination for top investment banks &amp; funds👇</t>
         </is>
       </c>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>https://x.com/smcglobal/status/2042141519180919080</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>The world may be ahead in nuclear today
+But India has just made a move that could redefine its position tomorrow
+With the Prototype Fast Breeder Reactor (PFBR) at Kalpakkam achieving criticality, India has officially stepped into the second stage of its nuclear roadmap
+This isn’t just another reactor going live
+It’s the foundation for long-term energy independence
+While the gap with global leaders still exists, the direction has now changed
+The real question is… how fast can India build on this momentum?
+#SMCGlobal #Nuclear #Energy</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>🤯More than $10.8 Billion have been invested in Indian Financial Services companies in last 1 year alone!!!
-From Japan’s MUFG investing $4.4 billion in Shriram Finance to the UAE’s Emirates NBD putting $3 billion into RBL Bank
-So, here's why India's banking &amp; NBFC Sector is becoming a global destination for top investment banks &amp; funds👇</t>
+          <t>The world may be ahead in nuclear today
+But India has just made a move that could redefine its position tomorrow
+With the Prototype Fast Breeder Reactor (PFBR) at Kalpakkam achieving criticality, India has officially stepped into the second stage of its nuclear roadmap
+This isn’t just another reactor going live
+It’s the foundation for long-term energy independence
+While the gap with global leaders still exists, the direction has now changed
+The real question is… how fast can India build on this momentum?
+#SMCGlobal #Nuclear #Energy</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>More than $10.8 billion has been invested in Indian financial services companies in the last year alone! 
-From Japan's MUFG investing $4.4 billion in Shriram Finance to the UAE's Emirates NBD putting $3 billion into RBL Bank. 
-So, here's why India's banking and NBFC sector is becoming a global destination for top investment banks and funds.</t>
+          <t>The world may be ahead in nuclear today
+But India has just made a move that could redefine its position tomorrow
+With the Prototype Fast Breeder Reactor (PFBR) at Kalpakkam achieving criticality, India has officially stepped into the second stage of its nuclear roadmap
+This isn’t just another reactor going live
+It’s the foundation for long-term energy independence
+While the gap with global leaders still exists, the direction has now changed
+The real question is… how fast can India build on this momentum?</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -6789,7 +6807,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>From Japan's MUFG investing $4.4 billion in Shriram Finance to the UAE's Emirates NBD putting $3 billion into RBL Bank. • More than $10.8 billion has been invested in Indian financial services companies in the last year alone! • So, here's why India's banking and NBFC sector is becoming a global destination for top investment banks and funds.</t>
+          <t>The world may be ahead in nuclear today But India has just made a move that could redefine its position tomorrow With th…</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
@@ -8541,42 +8559,202 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2042482710841528699</t>
+          <t>2042543802079154670</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2042482710841528699</t>
+          <t>https://x.com/yannoauh/status/2042543802079154670</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/yannoauh</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>yannoauh</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>yannoauh 🐣🕹️</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1907312478566207489/cIrGb9B7_bigger.jpg</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
+          <t>@EmiratesNBD_AE SMS 2 #UnitedAgainstFraud</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>SMS 2 &lt;a href="/search?f=tweets&amp;amp;q=%23UnitedAgainstFraud"&gt;#UnitedAgainstFraud&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K51" t="b">
+        <v>0</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>58m</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Apr 10, 2026 · 10:02 AM UTC</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="n">
+        <v>46122.41805555556</v>
+      </c>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23UnitedAgainstFraud']</t>
+        </is>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1</v>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>SMS 2 #UnitedAgainstFraud</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>https://x.com/yannoauh/status/2042543802079154670</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE SMS 2 #UnitedAgainstFraud</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE SMS 2 #UnitedAgainstFraud</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE SMS 2 #UnitedAgainstFraud</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE51" s="2" t="n">
+        <v>46122.58472222222</v>
+      </c>
+      <c r="AF51" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE SMS 2 #UnitedAgainstFraud</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK51" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL51" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2042482710841528699</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2042482710841528699</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
           <t>تسرنا زيارتكم لنا بفرعنا الجديد في سيليكون سنترال مول - دبي.
-نقدّم لكم خدمات مصرفية متكاملة مع ساعات عمل ممتدة عبر فترتين يومياً. نحن قريبين منكم في خدمتكم! https://t.co/loAWPzVN4u</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
+نقدّم لكم خدمات مصرفية متكاملة مع ساعات عمل ممتدة عبر فترتين يومياً. نحن قريبين منكم في خدمتكم! https://t.co/TrLnjtiJhq</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
         <is>
           <t>A message says “Get your full flight refund instantly.” What do you do?
 Do not fall for the traps. Stay alert to scams.
@@ -8585,48 +8763,48 @@
 &lt;a href="https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K51" t="b">
-        <v>0</v>
-      </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr">
+      <c r="K52" t="b">
+        <v>0</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
         <is>
           <t>1h</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>Apr 10, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
-      <c r="P51" s="2" t="n">
+      <c r="P52" s="2" t="n">
         <v>46122.25</v>
       </c>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr">
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr">
         <is>
           <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud', 'https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security']</t>
         </is>
       </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" t="n">
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" t="n">
         <v>39</v>
       </c>
-      <c r="W51" t="inlineStr">
+      <c r="W52" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>A message says “Get your full flight refund instantly.” What do you do?
 Do not fall for the traps. Stay alert to scams.
@@ -8635,196 +8813,40 @@
 emiratesislamic.ae/en/person…</t>
         </is>
       </c>
-      <c r="Y51" t="inlineStr">
+      <c r="Y52" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2042482710841528699</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t>تسرنا زيارتكم لنا بفرعنا الجديد في سيليكون سنترال مول - دبي.
-نقدّم لكم خدمات مصرفية متكاملة مع ساعات عمل ممتدة عبر فترتين يومياً. نحن قريبين منكم في خدمتكم! https://t.co/loAWPzVN4u</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
+نقدّم لكم خدمات مصرفية متكاملة مع ساعات عمل ممتدة عبر فترتين يومياً. نحن قريبين منكم في خدمتكم! https://t.co/TrLnjtiJhq</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
         <is>
           <t>تسرنا زيارتكم لنا بفرعنا الجديد في سيليكون سنترال مول - دبي.
-نقدّم لكم خدمات مصرفية متكاملة مع ساعات عمل ممتدة عبر فترتين يومياً. نحن قريبين منكم في خدمتكم! https://t.co/loAWPzVN4u</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
+نقدّم لكم خدمات مصرفية متكاملة مع ساعات عمل ممتدة عبر فترتين يومياً. نحن قريبين منكم في خدمتكم! https://t.co/TrLnjtiJhq</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
         <is>
           <t>We are pleased to welcome you to our new branch at Silicon Central Mall - Dubai. We offer you comprehensive banking services with extended hours across two daily shifts. We are close to you and at your service!</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
+      <c r="AC52" t="inlineStr">
         <is>
           <t>Bank</t>
         </is>
       </c>
-      <c r="AD51" t="inlineStr">
+      <c r="AD52" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="AE51" s="2" t="n">
+      <c r="AE52" s="2" t="n">
         <v>46122.41666666666</v>
-      </c>
-      <c r="AF51" s="2" t="n">
-        <v>46122</v>
-      </c>
-      <c r="AG51" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>We offer you comprehensive banking services with extended hours across two daily shifts. • We are pleased to welcome you to our new branch at Silicon Central Mall - Dubai. • We are close to you and at your service!</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK51" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL51" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2042436151131455658</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>https://x.com/Neli_Brown_/status/2042436151131455658</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>https://x.com/Neli_Brown_</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Neli_Brown_</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Cornelia Brown 🇦🇪</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2040254636754706432/0mffrtu0_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>I just opened my banking app to see this 👇 Proud of UAE!! 😍 @emiratesislamic https://t.co/rBbgDm1TZd</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>I just opened my banking app to see this 👇 Proud of UAE!! 😍 &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K52" t="b">
-        <v>0</v>
-      </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>4h</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>Apr 10, 2026 · 2:54 AM UTC</t>
-        </is>
-      </c>
-      <c r="P52" s="2" t="n">
-        <v>46122.12083333333</v>
-      </c>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>['https://x.com/emiratesislamic']</t>
-        </is>
-      </c>
-      <c r="S52" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" t="n">
-        <v>0</v>
-      </c>
-      <c r="U52" t="n">
-        <v>0</v>
-      </c>
-      <c r="V52" t="n">
-        <v>30</v>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>I just opened my banking app to see this 👇 Proud of UAE!! 😍 @emiratesislamic</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>https://x.com/Neli_Brown_/status/2042436151131455658</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>I just opened my banking app to see this 👇 Proud of UAE!! 😍 @emiratesislamic https://t.co/rBbgDm1TZd</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>I just opened my banking app to see this 👇 Proud of UAE!! 😍 @emiratesislamic https://t.co/rBbgDm1TZd</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>I just opened my banking app to see this 👇 Proud of UAE!! 😍 @emiratesislamic</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD52" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="AE52" s="2" t="n">
-        <v>46122.2875</v>
       </c>
       <c r="AF52" s="2" t="n">
         <v>46122</v>
@@ -8841,7 +8863,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>I just opened my banking app to see this 👇 Proud of UAE!!</t>
+          <t>We offer you comprehensive banking services with extended hours across two daily shifts. • We are pleased to welcome you to our new branch at Silicon Central Mall - Dubai. • We are close to you and at your service!</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
@@ -8864,41 +8886,198 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2042184588223746449</t>
+          <t>2042436151131455658</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://x.com/HHShkMohd/status/2042184588223746449</t>
+          <t>https://x.com/Neli_Brown_/status/2042436151131455658</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://x.com/HHShkMohd</t>
+          <t>https://x.com/Neli_Brown_</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>HHShkMohd</t>
+          <t>Neli_Brown_</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>HH Sheikh Mohammed</t>
+          <t>Cornelia Brown 🇦🇪</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1547632760927309837/9q-31iBH_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2040254636754706432/0mffrtu0_bigger.jpg</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>@HHShkMohd #فخورين_بالإمارات 🇦🇪 https://t.co/9zI7EZBTYM</t>
+          <t>I just opened my banking app to see this 👇 Proud of UAE!! 😍 @emiratesislamic https://t.co/rBbgDm1TZd</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
+        <is>
+          <t>I just opened my banking app to see this 👇 Proud of UAE!! 😍 &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K53" t="b">
+        <v>0</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Apr 10, 2026 · 2:54 AM UTC</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="n">
+        <v>46122.12083333333</v>
+      </c>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>30</v>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>I just opened my banking app to see this 👇 Proud of UAE!! 😍 @emiratesislamic</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>https://x.com/Neli_Brown_/status/2042436151131455658</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>I just opened my banking app to see this 👇 Proud of UAE!! 😍 @emiratesislamic https://t.co/rBbgDm1TZd</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>I just opened my banking app to see this 👇 Proud of UAE!! 😍 @emiratesislamic https://t.co/rBbgDm1TZd</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>I just opened my banking app to see this 👇 Proud of UAE!! 😍 @emiratesislamic</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AE53" s="2" t="n">
+        <v>46122.2875</v>
+      </c>
+      <c r="AF53" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>2. Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>I just opened my banking app to see this 👇 Proud of UAE!!</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AK53" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL53" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2042184588223746449</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://x.com/HHShkMohd/status/2042184588223746449</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://x.com/HHShkMohd</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>HHShkMohd</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>HH Sheikh Mohammed</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1547632760927309837/9q-31iBH_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>@HHShkMohd صدقت سموك..
+علم الإمارات رمز وحدتنا وقوتنا.. نرفعه شامخاً فخراً وولاءً https://t.co/Vt469sEQu3</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
         <is>
           <t>دخلت دولة الإمارات الأزمة الأخيرة متحدة .. وخرجت منها وهي أكثر اتحاداً والتفافاً وولاءً.. مواطنين ومقيمين .. صغاراً وكباراً .. عسكريين ومدنيين .. حكوميين واقتصاديين .. الجميع متحد تحت راية الدولة وعلمها ورمز وحدتها ..
 علم الإمارات رمز القوة والفخر  .. ندعو أبناء الإمارات والمقيمين على أرضها الطيبة أن يرفعوه فوق المنازل والمؤسسات والمباني.. 
@@ -8908,52 +9087,52 @@
 &lt;a href="/search?f=tweets&amp;amp;q=%23فخورين_بالإمارات"&gt;#فخورين_بالإمارات&lt;/a&gt; 🇦🇪</t>
         </is>
       </c>
-      <c r="K53" t="b">
+      <c r="K54" t="b">
         <v>1</v>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr">
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
         <is>
           <t>21h</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>Apr 9, 2026 · 10:15 AM UTC</t>
         </is>
       </c>
-      <c r="P53" s="2" t="n">
+      <c r="P54" s="2" t="n">
         <v>46121.42708333334</v>
       </c>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr">
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr">
         <is>
           <t>['https://x.com/search?f=tweets&amp;q=%23فخورين_بالإمارات']</t>
         </is>
       </c>
-      <c r="S53" t="n">
+      <c r="S54" t="n">
         <v>1402</v>
       </c>
-      <c r="T53" t="n">
+      <c r="T54" t="n">
         <v>8020</v>
       </c>
-      <c r="U53" t="n">
+      <c r="U54" t="n">
         <v>15913</v>
       </c>
-      <c r="V53" t="n">
+      <c r="V54" t="n">
         <v>873259</v>
       </c>
-      <c r="W53" t="inlineStr">
+      <c r="W54" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>دخلت دولة الإمارات الأزمة الأخيرة متحدة .. وخرجت منها وهي أكثر اتحاداً والتفافاً وولاءً.. مواطنين ومقيمين .. صغاراً وكباراً .. عسكريين ومدنيين .. حكوميين واقتصاديين .. الجميع متحد تحت راية الدولة وعلمها ورمز وحدتها ..
 علم الإمارات رمز القوة والفخر  .. ندعو أبناء الإمارات والمقيمين على أرضها الطيبة أن يرفعوه فوق المنازل والمؤسسات والمباني.. 
@@ -8963,186 +9142,40 @@
 #فخورين_بالإمارات 🇦🇪</t>
         </is>
       </c>
-      <c r="Y53" t="inlineStr">
+      <c r="Y54" t="inlineStr">
         <is>
           <t>https://x.com/HHShkMohd/status/2042184588223746449</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>@HHShkMohd #فخورين_بالإمارات 🇦🇪 https://t.co/9zI7EZBTYM</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>@HHShkMohd #فخورين_بالإمارات 🇦🇪 https://t.co/9zI7EZBTYM</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>Proud of the UAE</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>@HHShkMohd صدقت سموك..
+علم الإمارات رمز وحدتنا وقوتنا.. نرفعه شامخاً فخراً وولاءً https://t.co/Vt469sEQu3</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>@HHShkMohd صدقت سموك..
+علم الإمارات رمز وحدتنا وقوتنا.. نرفعه شامخاً فخراً وولاءً https://t.co/Vt469sEQu3</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>You are right, Your Highness.. The UAE flag is a symbol of our unity and strength.. We raise it high with pride and loyalty.</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="AD53" t="inlineStr">
+      <c r="AD54" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="AE53" s="2" t="n">
+      <c r="AE54" s="2" t="n">
         <v>46121.59375</v>
-      </c>
-      <c r="AF53" s="2" t="n">
-        <v>46121</v>
-      </c>
-      <c r="AG53" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>Proud of the UAE</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK53" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL53" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="n">
-        <v>52</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2042152553400385940</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2042152553400385940</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
-        </is>
-      </c>
-      <c r="K54" t="b">
-        <v>0</v>
-      </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>['aswanikumartst5']</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>23h</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>Apr 9, 2026 · 8:08 AM UTC</t>
-        </is>
-      </c>
-      <c r="P54" s="2" t="n">
-        <v>46121.33888888889</v>
-      </c>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V54" t="n">
-        <v>10</v>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr"/>
-      <c r="Z54" t="inlineStr"/>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>Dear customer, we will connect with you through private messaging to serve you better.</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD54" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE54" s="2" t="n">
-        <v>46121.50555555556</v>
       </c>
       <c r="AF54" s="2" t="n">
         <v>46121</v>
@@ -9159,7 +9192,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you through private messaging to serve you better.</t>
+          <t>The UAE flag is a symbol of our unity and strength.. • We raise it high with pride and loyalty. • You are right, Your Highness..</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
@@ -9172,7 +9205,7 @@
       </c>
       <c r="AL54" t="inlineStr">
         <is>
-          <t>aswanikumartst5</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9182,12 +9215,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2042120326721523923</t>
+          <t>2042152553400385940</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2042120326721523923</t>
+          <t>https://x.com/emiratesislamic/status/2042152553400385940</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9213,41 +9246,38 @@
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Investing doesn’t have to feel complicated.
-Understanding the different ways money can grow helps bring clarity and confidence over time.
-From long-term growth to steady income, each option plays a role in shaping your financial journey. https://t.co/VgSsKYMuov</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>To know more:
-&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
       <c r="K55" t="b">
         <v>0</v>
       </c>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>['aswanikumartst5']</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Apr 9</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Apr 9, 2026 · 6:00 AM UTC</t>
+          <t>Apr 9, 2026 · 8:08 AM UTC</t>
         </is>
       </c>
       <c r="P55" s="2" t="n">
-        <v>46121.25</v>
+        <v>46121.33888888889</v>
       </c>
       <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
-        </is>
-      </c>
+      <c r="R55" t="inlineStr"/>
       <c r="S55" t="n">
         <v>0</v>
       </c>
@@ -9258,7 +9288,7 @@
         <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
@@ -9267,37 +9297,24 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>To know more:
-emiratesislamic.ae/en/key-in…</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2042120326721523923</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>Investing doesn’t have to feel complicated.
-Understanding the different ways money can grow helps bring clarity and confidence over time.
-From long-term growth to steady income, each option plays a role in shaping your financial journey. https://t.co/VgSsKYMuov</t>
-        </is>
-      </c>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>Investing doesn’t have to feel complicated.
-Understanding the different ways money can grow helps bring clarity and confidence over time.
-From long-term growth to steady income, each option plays a role in shaping your financial journey. https://t.co/VgSsKYMuov</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>Investing doesn’t have to feel complicated. Understanding the different ways money can grow helps bring clarity and confidence over time. From long-term growth to steady income, each option plays a role in shaping your financial journey.</t>
+          <t>Dear customer, we will connect with you through private messaging to serve you better.</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Cust</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
@@ -9306,7 +9323,7 @@
         </is>
       </c>
       <c r="AE55" s="2" t="n">
-        <v>46121.41666666666</v>
+        <v>46121.50555555556</v>
       </c>
       <c r="AF55" s="2" t="n">
         <v>46121</v>
@@ -9323,7 +9340,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>From long-term growth to steady income, each option plays a role in shaping your financial journey. • Understanding the different ways money can grow helps bring clarity and confidence over time. • Investing doesn’t have to feel complicated.</t>
+          <t>Dear customer, we will connect with you through private messaging to serve you better.</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
@@ -9336,7 +9353,7 @@
       </c>
       <c r="AL55" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>aswanikumartst5</t>
         </is>
       </c>
     </row>
@@ -9346,12 +9363,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2042120323168956518</t>
+          <t>2042120326721523923</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2042120323168956518</t>
+          <t>https://x.com/emiratesislamic/status/2042120326721523923</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9379,14 +9396,13 @@
         <is>
           <t>Investing doesn’t have to feel complicated.
 Understanding the different ways money can grow helps bring clarity and confidence over time.
-From long-term growth to steady income, each option plays a role in shaping your financial journey.</t>
+From long-term growth to steady income, each option plays a role in shaping your financial journey. https://t.co/VgSsKYMuov</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Investing doesn’t have to feel complicated.
-Understanding the different ways money can grow helps bring clarity and confidence over time.
-From long-term growth to steady income, each option plays a role in shaping your financial journey.</t>
+          <t>To know more:
+&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K56" t="b">
@@ -9408,9 +9424,13 @@
         <v>46121.25</v>
       </c>
       <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+        </is>
+      </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
         <v>0</v>
@@ -9419,7 +9439,7 @@
         <v>0</v>
       </c>
       <c r="V56" t="n">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
@@ -9427,19 +9447,28 @@
         </is>
       </c>
       <c r="X56" t="inlineStr">
+        <is>
+          <t>To know more:
+emiratesislamic.ae/en/key-in…</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2042120326721523923</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
         <is>
           <t>Investing doesn’t have to feel complicated.
 Understanding the different ways money can grow helps bring clarity and confidence over time.
-From long-term growth to steady income, each option plays a role in shaping your financial journey.</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr"/>
-      <c r="Z56" t="inlineStr"/>
+From long-term growth to steady income, each option plays a role in shaping your financial journey. https://t.co/VgSsKYMuov</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>Investing doesn’t have to feel complicated.
 Understanding the different ways money can grow helps bring clarity and confidence over time.
-From long-term growth to steady income, each option plays a role in shaping your financial journey.</t>
+From long-term growth to steady income, each option plays a role in shaping your financial journey. https://t.co/VgSsKYMuov</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
@@ -9498,43 +9527,47 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2042145058133307907</t>
+          <t>2042120323168956518</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://x.com/aswanikumartst5/status/2042145058133307907</t>
+          <t>https://x.com/emiratesislamic/status/2042120323168956518</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://x.com/aswanikumartst5</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>aswanikumartst5</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>TS Aswani Kumar</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1412710891515092994/OVnKv5t7_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
-          <t>@emiratesislamic I have already cleared a personal loan and approached your Phone Banking &amp;amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp;amp; revert ASAP. Thank You.</t>
+          <t>Investing doesn’t have to feel complicated.
+Understanding the different ways money can grow helps bring clarity and confidence over time.
+From long-term growth to steady income, each option plays a role in shaping your financial journey.</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; I have already cleared a personal loan and approached your Phone Banking &amp;amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp;amp; revert ASAP. Thank You.</t>
+          <t>Investing doesn’t have to feel complicated.
+Understanding the different ways money can grow helps bring clarity and confidence over time.
+From long-term growth to steady income, each option plays a role in shaping your financial journey.</t>
         </is>
       </c>
       <c r="K57" t="b">
@@ -9544,23 +9577,19 @@
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>Apr 9</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Apr 9, 2026 · 7:38 AM UTC</t>
+          <t>Apr 9, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P57" s="2" t="n">
-        <v>46121.31805555556</v>
+        <v>46121.25</v>
       </c>
       <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>['https://x.com/emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="R57" t="inlineStr"/>
       <c r="S57" t="n">
         <v>1</v>
       </c>
@@ -9571,7 +9600,7 @@
         <v>0</v>
       </c>
       <c r="V57" t="n">
-        <v>9</v>
+        <v>108</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
@@ -9580,41 +9609,37 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>@emiratesislamic I have already cleared a personal loan and approached your Phone Banking &amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp; revert ASAP. Thank You.</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>https://x.com/aswanikumartst5/status/2042145058133307907</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>@emiratesislamic I have already cleared a personal loan and approached your Phone Banking &amp;amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp;amp; revert ASAP. Thank You.</t>
-        </is>
-      </c>
+          <t>Investing doesn’t have to feel complicated.
+Understanding the different ways money can grow helps bring clarity and confidence over time.
+From long-term growth to steady income, each option plays a role in shaping your financial journey.</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>@emiratesislamic I have already cleared a personal loan and approached your Phone Banking &amp;amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp;amp; revert ASAP. Thank You.</t>
+          <t>Investing doesn’t have to feel complicated.
+Understanding the different ways money can grow helps bring clarity and confidence over time.
+From long-term growth to steady income, each option plays a role in shaping your financial journey.</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>I have already cleared a personal loan and approached your Phone Banking and WhatsApp channel for the issuance of a NIL LIABILITY LETTER, but I have not received a concrete response. It is also not feasible to obtain it through your application. Can you please check and respond as soon as possible? Thank you.</t>
+          <t>Investing doesn’t have to feel complicated. Understanding the different ways money can grow helps bring clarity and confidence over time. From long-term growth to steady income, each option plays a role in shaping your financial journey.</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Cust</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE57" s="2" t="n">
-        <v>46121.48472222222</v>
+        <v>46121.41666666666</v>
       </c>
       <c r="AF57" s="2" t="n">
         <v>46121</v>
@@ -9631,7 +9656,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>I have already cleared a personal loan and approached your Phone Banking and WhatsApp channel for the issuance of a NIL LIABILITY LETTER, but I have not received a concrete response. • Can you please check and respond as soon as possible? • It is also not feasible to obtain it through your application.</t>
+          <t>From long-term growth to steady income, each option plays a role in shaping your financial journey. • Understanding the different ways money can grow helps bring clarity and confidence over time. • Investing doesn’t have to feel complicated.</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
@@ -9654,36 +9679,504 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2042482711168737317</t>
+          <t>2042513547683598491</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2042482711168737317</t>
+          <t>https://x.com/ZaibKang/status/2042513547683598491</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/ZaibKang</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>ZaibKang</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Jahan Zaib Akbar Kang</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2028644994790436864/h-Avrj3s_bigger.jpg</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE I applied for liv X digital account opening on 26th April almost 16 days passed my application is still in progress can you please check</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>I applied for liv X digital account opening on 26th April almost 16 days passed my application is still in progress can you please check</t>
+        </is>
+      </c>
+      <c r="K58" t="b">
+        <v>0</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>2h</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Apr 10, 2026 · 8:02 AM UTC</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="n">
+        <v>46122.33472222222</v>
+      </c>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" t="n">
+        <v>10</v>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>I applied for liv X digital account opening on 26th April almost 16 days passed my application is still in progress can you please check</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>https://x.com/ZaibKang/status/2042513547683598491</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE I applied for liv X digital account opening on 26th April almost 16 days passed my application is still in progress can you please check</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE I applied for liv X digital account opening on 26th April almost 16 days passed my application is still in progress can you please check</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>I applied for a liv X digital account opening on April 26th, and almost 16 days have passed. My application is still in progress; can you please check?</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AE58" s="2" t="n">
+        <v>46122.50138888889</v>
+      </c>
+      <c r="AF58" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>I applied for a liv X digital account opening on April 26th, and almost 16 days have passed. • My application is still in progress; can you please check?</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK58" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL58" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2042556913075069121</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://x.com/Zenap355057/status/2042556913075069121</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://x.com/Zenap355057</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Zenap355057</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Zenap</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2038629915940298752/N0SyjFf4_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE hi am trying to speak with your agent and no response, I have to clarify something</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; hi am trying to speak with your agent and no response, I have to clarify something</t>
+        </is>
+      </c>
+      <c r="K59" t="b">
+        <v>0</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>6m</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Apr 10, 2026 · 10:54 AM UTC</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="n">
+        <v>46122.45416666667</v>
+      </c>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" t="n">
+        <v>2</v>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE hi am trying to speak with your agent and no response, I have to clarify something</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>https://x.com/Zenap355057/status/2042556913075069121</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE hi am trying to speak with your agent and no response, I have to clarify something</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE hi am trying to speak with your agent and no response, I have to clarify something</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>Hi Emirates NBD, I am trying to speak with your agent and there is no response. I need to clarify something.</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AE59" s="2" t="n">
+        <v>46122.62083333333</v>
+      </c>
+      <c r="AF59" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Hi Emirates NBD, I am trying to speak with your agent and there is no response. • I need to clarify something.</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK59" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL59" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2042145058133307907</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://x.com/aswanikumartst5/status/2042145058133307907</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://x.com/aswanikumartst5</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>aswanikumartst5</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>TS Aswani Kumar</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1412710891515092994/OVnKv5t7_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>@emiratesislamic I have already cleared a personal loan and approached your Phone Banking &amp;amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp;amp; revert ASAP. Thank You.</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; I have already cleared a personal loan and approached your Phone Banking &amp;amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp;amp; revert ASAP. Thank You.</t>
+        </is>
+      </c>
+      <c r="K60" t="b">
+        <v>0</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>23h</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Apr 9, 2026 · 7:38 AM UTC</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="n">
+        <v>46121.31805555556</v>
+      </c>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="S60" t="n">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" t="n">
+        <v>9</v>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>@emiratesislamic I have already cleared a personal loan and approached your Phone Banking &amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp; revert ASAP. Thank You.</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>https://x.com/aswanikumartst5/status/2042145058133307907</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>@emiratesislamic I have already cleared a personal loan and approached your Phone Banking &amp;amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp;amp; revert ASAP. Thank You.</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>@emiratesislamic I have already cleared a personal loan and approached your Phone Banking &amp;amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp;amp; revert ASAP. Thank You.</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>I have already cleared a personal loan and approached your Phone Banking and WhatsApp channel for the issuance of a NIL LIABILITY LETTER, but I have not received a concrete response. It is also not feasible to obtain it through your application. Can you please check and respond as soon as possible? Thank you.</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AE60" s="2" t="n">
+        <v>46121.48472222222</v>
+      </c>
+      <c r="AF60" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>2. Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>I have already cleared a personal loan and approached your Phone Banking and WhatsApp channel for the issuance of a NIL LIABILITY LETTER, but I have not received a concrete response. • Can you please check and respond as soon as possible? • It is also not feasible to obtain it through your application.</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AK60" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL60" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2042482711168737317</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2042482711168737317</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
         <is>
           <t>تصلك رسالة تقول:
 "استرد قيمة رحلتك بالكامل فوراً"
@@ -9693,7 +10186,7 @@
 https://t.co/ltnxcRlBOA</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>تصلك رسالة تقول:
 &amp;#34;استرد قيمة رحلتك بالكامل فوراً&amp;#34;
@@ -9703,48 +10196,48 @@
 &lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K58" t="b">
-        <v>0</v>
-      </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr">
+      <c r="K61" t="b">
+        <v>0</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
         <is>
           <t>1h</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>Apr 10, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
-      <c r="P58" s="2" t="n">
+      <c r="P61" s="2" t="n">
         <v>46122.25</v>
       </c>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr">
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr">
         <is>
           <t>['https://x.com/search?f=tweets&amp;q=%23متحّدون_ضد_الاحتيال', 'https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security']</t>
         </is>
       </c>
-      <c r="S58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" t="n">
-        <v>0</v>
-      </c>
-      <c r="U58" t="n">
-        <v>0</v>
-      </c>
-      <c r="V58" t="n">
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" t="n">
         <v>60</v>
       </c>
-      <c r="W58" t="inlineStr">
+      <c r="W61" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>تصلك رسالة تقول:
 "استرد قيمة رحلتك بالكامل فوراً"
@@ -9754,12 +10247,12 @@
 emiratesislamic.ae/ar/person…</t>
         </is>
       </c>
-      <c r="Y58" t="inlineStr">
+      <c r="Y61" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2042482711168737317</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
+      <c r="Z61" t="inlineStr">
         <is>
           <t>تصلك رسالة تقول:
 "استرد قيمة رحلتك بالكامل فوراً"
@@ -9769,7 +10262,7 @@
 https://t.co/ltnxcRlBOA</t>
         </is>
       </c>
-      <c r="AA58" t="inlineStr">
+      <c r="AA61" t="inlineStr">
         <is>
           <t>تصلك رسالة تقول:
 "استرد قيمة رحلتك بالكامل فوراً"
@@ -9779,416 +10272,416 @@
 https://t.co/ltnxcRlBOA</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
+      <c r="AB61" t="inlineStr">
         <is>
           <t>You receive a message saying: "Get a full refund for your trip immediately." What do you do? 
 Don't fall into the trap. Beware of fraud. 
 #United_Against_Fraud with Emirates Islamic.</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
+      <c r="AC61" t="inlineStr">
         <is>
           <t>Bank</t>
         </is>
       </c>
-      <c r="AD58" t="inlineStr">
+      <c r="AD61" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="AE58" s="2" t="n">
+      <c r="AE61" s="2" t="n">
         <v>46122.41666666666</v>
       </c>
-      <c r="AF58" s="2" t="n">
+      <c r="AF61" s="2" t="n">
         <v>46122</v>
       </c>
-      <c r="AG58" t="inlineStr">
+      <c r="AG61" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="AH58" t="inlineStr">
+      <c r="AH61" t="inlineStr">
         <is>
           <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
-      <c r="AI58" t="inlineStr">
+      <c r="AI61" t="inlineStr">
         <is>
           <t>You receive a message saying: "Get a full refund for your trip immediately." What do you do? • #United_Against_Fraud with Emirates Islamic. • Don't fall into the trap.</t>
         </is>
       </c>
-      <c r="AJ58" t="inlineStr">
+      <c r="AJ61" t="inlineStr">
         <is>
           <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
-      <c r="AK58" t="n">
+      <c r="AK61" t="n">
         <v>2026</v>
       </c>
-      <c r="AL58" t="inlineStr">
+      <c r="AL61" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="1" t="n">
-        <v>57</v>
-      </c>
-      <c r="B59" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" t="inlineStr">
         <is>
           <t>2042343703474254316</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>https://x.com/great_harris/status/2042343703474254316</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>https://x.com/great_harris</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>great_harris</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>Who are you?</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1892265108597796864/sS4Q6Cfc_bigger.jpg</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr">
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
         <is>
           <t>@EmiratesNBD_KSA Hi, I received application update after updating now I am unable login. I tried to change password that also not working. Kindly assist.</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>&lt;a href="/EmiratesNBD_KSA" title="Emirates NBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; Hi, I received application update after updating now I am unable login. I tried to change password that also not working. Kindly assist.</t>
         </is>
       </c>
-      <c r="K59" t="b">
-        <v>0</v>
-      </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr">
+      <c r="K62" t="b">
+        <v>0</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
         <is>
           <t>11h</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>Apr 9, 2026 · 8:47 PM UTC</t>
         </is>
       </c>
-      <c r="P59" s="2" t="n">
+      <c r="P62" s="2" t="n">
         <v>46121.86597222222</v>
       </c>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr">
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr">
         <is>
           <t>['https://x.com/EmiratesNBD_KSA']</t>
         </is>
       </c>
-      <c r="S59" t="n">
+      <c r="S62" t="n">
         <v>1</v>
       </c>
-      <c r="T59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U59" t="n">
-        <v>0</v>
-      </c>
-      <c r="V59" t="n">
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" t="n">
         <v>14</v>
       </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr">
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
         <is>
           <t>@EmiratesNBD_KSA Hi, I received application update after updating now I am unable login. I tried to change password that also not working. Kindly assist.</t>
         </is>
       </c>
-      <c r="Y59" t="inlineStr">
+      <c r="Y62" t="inlineStr">
         <is>
           <t>https://x.com/great_harris/status/2042343703474254316</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
+      <c r="Z62" t="inlineStr">
         <is>
           <t>@EmiratesNBD_KSA Hi, I received application update after updating now I am unable login. I tried to change password that also not working. Kindly assist.</t>
         </is>
       </c>
-      <c r="AA59" t="inlineStr">
+      <c r="AA62" t="inlineStr">
         <is>
           <t>@EmiratesNBD_KSA Hi, I received application update after updating now I am unable login. I tried to change password that also not working. Kindly assist.</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
+      <c r="AB62" t="inlineStr">
         <is>
           <t>Hi, I received an application update and now I am unable to log in. I tried to change my password, but that is not working either. Kindly assist.</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
+      <c r="AC62" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="AD59" t="inlineStr">
+      <c r="AD62" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="AE59" s="2" t="n">
+      <c r="AE62" s="2" t="n">
         <v>46122.03263888889</v>
       </c>
-      <c r="AF59" s="2" t="n">
+      <c r="AF62" s="2" t="n">
         <v>46122</v>
       </c>
-      <c r="AG59" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH59" t="inlineStr">
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH62" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AI59" t="inlineStr">
+      <c r="AI62" t="inlineStr">
         <is>
           <t>Hi, I received an application update and now I am unable to log in. • I tried to change my password, but that is not working either.</t>
         </is>
       </c>
-      <c r="AJ59" t="inlineStr">
+      <c r="AJ62" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AK59" t="n">
+      <c r="AK62" t="n">
         <v>2026</v>
       </c>
-      <c r="AL59" t="inlineStr">
+      <c r="AL62" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="1" t="n">
-        <v>58</v>
-      </c>
-      <c r="B60" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" t="inlineStr">
         <is>
           <t>2042346115685618032</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>https://x.com/horatio_qu67318/status/2042346115685618032</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>https://x.com/horatio_qu67318</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>horatio_qu67318</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>Horatio Quintus</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1818333873941426177/n39rXfsp_bigger.png</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr">
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
         <is>
           <t>@EmiratesNBD_KSA 
 My card is not working and neither am I able to access online banking,  below error pops. 
 I tried calling the help center but no answer,  please support,  I need to book a ticket.  This is truly terrible service. https://t.co/YvBorzfyjo</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>&lt;a href="/EmiratesNBD_KSA" title="Emirates NBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; 
 My card is not working and neither am I able to access online banking,  below error pops. 
 I tried calling the help center but no answer,  please support,  I need to book a ticket.  This is truly terrible service.</t>
         </is>
       </c>
-      <c r="K60" t="b">
-        <v>0</v>
-      </c>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr">
+      <c r="K63" t="b">
+        <v>0</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
         <is>
           <t>10h</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>Apr 9, 2026 · 8:57 PM UTC</t>
         </is>
       </c>
-      <c r="P60" s="2" t="n">
+      <c r="P63" s="2" t="n">
         <v>46121.87291666667</v>
       </c>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr">
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr">
         <is>
           <t>['https://x.com/EmiratesNBD_KSA']</t>
         </is>
       </c>
-      <c r="S60" t="n">
+      <c r="S63" t="n">
         <v>1</v>
       </c>
-      <c r="T60" t="n">
-        <v>0</v>
-      </c>
-      <c r="U60" t="n">
-        <v>0</v>
-      </c>
-      <c r="V60" t="n">
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" t="n">
         <v>5</v>
       </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X60" t="inlineStr">
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
         <is>
           <t>@EmiratesNBD_KSA 
 My card is not working and neither am I able to access online banking,  below error pops. 
 I tried calling the help center but no answer,  please support,  I need to book a ticket.  This is truly terrible service.</t>
         </is>
       </c>
-      <c r="Y60" t="inlineStr">
+      <c r="Y63" t="inlineStr">
         <is>
           <t>https://x.com/horatio_qu67318/status/2042346115685618032</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
+      <c r="Z63" t="inlineStr">
         <is>
           <t>@EmiratesNBD_KSA 
 My card is not working and neither am I able to access online banking,  below error pops. 
 I tried calling the help center but no answer,  please support,  I need to book a ticket.  This is truly terrible service. https://t.co/YvBorzfyjo</t>
         </is>
       </c>
-      <c r="AA60" t="inlineStr">
+      <c r="AA63" t="inlineStr">
         <is>
           <t>@EmiratesNBD_KSA 
 My card is not working and neither am I able to access online banking,  below error pops. 
 I tried calling the help center but no answer,  please support,  I need to book a ticket.  This is truly terrible service. https://t.co/YvBorzfyjo</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
+      <c r="AB63" t="inlineStr">
         <is>
           <t>My card is not working and I am also unable to access online banking; the error below appears. I tried calling the help center but there was no answer. Please help, I need to book a ticket. This is truly terrible service.</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
+      <c r="AC63" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="AD60" t="inlineStr">
+      <c r="AD63" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="AE60" s="2" t="n">
+      <c r="AE63" s="2" t="n">
         <v>46122.03958333333</v>
       </c>
-      <c r="AF60" s="2" t="n">
+      <c r="AF63" s="2" t="n">
         <v>46122</v>
       </c>
-      <c r="AG60" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH60" t="inlineStr">
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH63" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AI60" t="inlineStr">
+      <c r="AI63" t="inlineStr">
         <is>
           <t>My card is not working and I am also unable to access online banking; the error below appears. • I tried calling the help center but there was no answer. • Please help, I need to book a ticket.</t>
         </is>
       </c>
-      <c r="AJ60" t="inlineStr">
+      <c r="AJ63" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AK60" t="n">
+      <c r="AK63" t="n">
         <v>2026</v>
       </c>
-      <c r="AL60" t="inlineStr">
+      <c r="AL63" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="1" t="n">
-        <v>59</v>
-      </c>
-      <c r="B61" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" t="inlineStr">
         <is>
           <t>2042461696749666379</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>https://x.com/jayesh8826/status/2042461696749666379</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>https://x.com/jayesh8826</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>jayesh8826</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>Jayesh Chavan</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr">
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
         <is>
           <t>"@RBLBankCares, RBL is currently transitioning into a foreign lender with Emirates NBD, yet your customer service feels like a local grocery shop. 📉🤡
 You are sending editable Excel sheets as 'Audit Proof' for a 431-day delay? This is a massive embarrassment for a scheduled commercial bank.
@@ -10198,7 +10691,7 @@
 @RBI @CNBCAwaaz #RBLBank #BankingEthics #AmateurHour #AuditFailure"</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>&amp;#34;&lt;a href="/RBLBankCares" title="RBL Bank Cares"&gt;@RBLBankCares&lt;/a&gt;, RBL is currently transitioning into a foreign lender with Emirates NBD, yet your customer service feels like a local grocery shop. 📉🤡
 You are sending editable Excel sheets as &amp;#39;Audit Proof&amp;#39; for a 431-day delay? This is a massive embarrassment for a scheduled commercial bank.
@@ -10208,48 +10701,48 @@
 &lt;a href="/RBI" title="ReserveBankOfIndia"&gt;@RBI&lt;/a&gt; &lt;a href="/CNBCAwaaz" title="CNBC Awaaz"&gt;@CNBCAwaaz&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23RBLBank"&gt;#RBLBank&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23BankingEthics"&gt;#BankingEthics&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23AmateurHour"&gt;#AmateurHour&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23AuditFailure"&gt;#AuditFailure&lt;/a&gt;&amp;#34;</t>
         </is>
       </c>
-      <c r="K61" t="b">
-        <v>0</v>
-      </c>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr">
+      <c r="K64" t="b">
+        <v>0</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
         <is>
           <t>2h</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>Apr 10, 2026 · 4:36 AM UTC</t>
         </is>
       </c>
-      <c r="P61" s="2" t="n">
+      <c r="P64" s="2" t="n">
         <v>46122.19166666667</v>
       </c>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr">
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr">
         <is>
           <t>['https://x.com/RBLBankCares', 'https://x.com/RBI', 'https://x.com/CNBCAwaaz', 'https://x.com/search?f=tweets&amp;q=%23RBLBank', 'https://x.com/search?f=tweets&amp;q=%23BankingEthics', 'https://x.com/search?f=tweets&amp;q=%23AmateurHour', 'https://x.com/search?f=tweets&amp;q=%23AuditFailure']</t>
         </is>
       </c>
-      <c r="S61" t="n">
+      <c r="S64" t="n">
         <v>1</v>
       </c>
-      <c r="T61" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" t="n">
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" t="n">
         <v>11</v>
       </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr">
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
         <is>
           <t>"@RBLBankCares, RBL is currently transitioning into a foreign lender with Emirates NBD, yet your customer service feels like a local grocery shop. 📉🤡
 You are sending editable Excel sheets as 'Audit Proof' for a 431-day delay? This is a massive embarrassment for a scheduled commercial bank.
@@ -10259,12 +10752,12 @@
 @RBI @CNBCAwaaz #RBLBank #BankingEthics #AmateurHour #AuditFailure"</t>
         </is>
       </c>
-      <c r="Y61" t="inlineStr">
+      <c r="Y64" t="inlineStr">
         <is>
           <t>https://x.com/jayesh8826/status/2042461696749666379</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
+      <c r="Z64" t="inlineStr">
         <is>
           <t>"@RBLBankCares, RBL is currently transitioning into a foreign lender with Emirates NBD, yet your customer service feels like a local grocery shop. 📉🤡
 You are sending editable Excel sheets as 'Audit Proof' for a 431-day delay? This is a massive embarrassment for a scheduled commercial bank.
@@ -10274,7 +10767,7 @@
 @RBI @CNBCAwaaz #RBLBank #BankingEthics #AmateurHour #AuditFailure"</t>
         </is>
       </c>
-      <c r="AA61" t="inlineStr">
+      <c r="AA64" t="inlineStr">
         <is>
           <t>"@RBLBankCares, RBL is currently transitioning into a foreign lender with Emirates NBD, yet your customer service feels like a local grocery shop. 📉🤡
 You are sending editable Excel sheets as 'Audit Proof' for a 431-day delay? This is a massive embarrassment for a scheduled commercial bank.
@@ -10284,54 +10777,55 @@
 @RBI @CNBCAwaaz #RBLBank #BankingEthics #AmateurHour #AuditFailure"</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>RBL is currently transitioning into a foreign lender with Emirates NBD, yet your customer service feels like a local grocery shop. 
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>@RBLBankCares, RBL is currently transitioning into a foreign lender with Emirates NBD, yet your customer service feels like a local grocery shop. 📉🤡
 You are sending editable Excel sheets as 'Audit Proof' for a 431-day delay? This is a massive embarrassment for a scheduled commercial bank.
-1️⃣ Is this the standard of 'Digital Banking' you are presenting to your new international promoters? 2️⃣ Why are you hiding behind spreadsheets that anyone can modify instead of providing an Authorized Outward Remittance Report? It’s time for some Professionalism &amp; Transparency. 
-I’ve informed the RBI Ombudsman that RBL prefers Excel over official banking records.</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
+1️⃣ Is this the standard of 'Digital Banking' you are presenting to your new international promoters? 2️⃣ Why are you hiding behind spreadsheets that anyone can modify instead of providing an Authorized Outward Remittance Report? It’s time for some Professionalism &amp; Transparency. 🏦🔍
+I’ve informed the RBI Ombudsman that RBL prefers Excel over official banking records.
+@RBI @CNBCAwaaz #RBLBank #BankingEthics #AmateurHour #AuditFailure</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="AD61" t="inlineStr">
+      <c r="AD64" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="AE61" s="2" t="n">
+      <c r="AE64" s="2" t="n">
         <v>46122.35833333333</v>
       </c>
-      <c r="AF61" s="2" t="n">
+      <c r="AF64" s="2" t="n">
         <v>46122</v>
       </c>
-      <c r="AG61" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH61" t="inlineStr">
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH64" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>RBL is currently transitioning into a foreign lender with Emirates NBD, yet your customer service feels like a local grocery shop. • You are sending editable Excel sheets as 'Audit Proof' for a 431-day delay? • 2️⃣ Why are you hiding behind spreadsheets that anyone can modify instead of providing an Authorized Outward Remittance Report?</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>@RBLBankCares, RBL is currently transitioning into a foreign lender with Emirates NBD, yet your customer service feels like a local grocery shop. • 📉🤡 You are sending editable Excel sheets as 'Audit Proof' for a 431-day delay? • 2️⃣ Why are you hiding behind spreadsheets that anyone can modify instead of providing an Authorized Outward Remittance Report?</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AK61" t="n">
+      <c r="AK64" t="n">
         <v>2026</v>
       </c>
-      <c r="AL61" t="inlineStr">
+      <c r="AL64" t="inlineStr">
         <is>
           <t>None</t>
         </is>

--- a/check2.xlsx
+++ b/check2.xlsx
@@ -778,14 +778,13 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>Corporate Action: Emirates NBD Acquisition of RBL Bank
-🔹 RBL Bank has officially received RBI approval for Emirates NBD Bank to launch an open offer to acquire a 26% stake in the company.
-🔹 The Open Offer Price is set at ₹280 per share, providing a specific valuation benchmark for the upcoming transaction.
-🔹 RBI Stipulations require RBL Bank to apply Wholly Owned Subsidiary (WOS) mode governance directions and amend its Articles of Association.
-🔹 Shareholder Approval via a special resolution will be necessary to implement these governance changes and move the deal forward.
-🔹 The Investment Agreement has been amended to reflect the Acquirer’s right to nominate non-independent directors to the board.
-🔹 Governance Shifts: The transition to WOS-style governance signals a tighter regulatory oversight and alignment with international banking standards.
-🔹 Market Impact: This move is expected to bolster RBL Bank's capital base and provide a strategic global partner in Emirates NBD.
-#RBLBank #EmiratesNBD #BankingNews #M&amp;A #RBI #StockMarketIndia #OpenOffer
+RBL Bank has officially received RBI approval for Emirates NBD Bank to launch an open offer to acquire a 26% stake in the company.
+The Open Offer Price is set at ₹280 per share, providing a specific valuation benchmark for the upcoming transaction.
+RBI Stipulations require RBL Bank to apply Wholly Owned Subsidiary (WOS) mode governance directions and amend its Articles of Association.
+Shareholder Approval via a special resolution will be necessary to implement these governance changes and move the deal forward.
+The Investment Agreement has been amended to reflect the Acquirer’s right to nominate non-independent directors to the board.
+Governance Shifts: The transition to WOS-style governance signals a tighter regulatory oversight and alignment with international banking standards.
+Market Impact: This move is expected to bolster RBL Bank's capital base and provide a strategic global partner in Emirates NBD.
 Disclaimer:
 All content provided is intended solely for educational and informational purposes and does not constitute financial advice. Investors are strongly encouraged to assess their individual risk tolerance, investment objectives, and overall financial situation before making any investment decisions. For personalized guidance, please consult a certified financial advisor. While every effort has been made to ensure accuracy, any inadvertent errors or omissions are regretted.</t>
         </is>
@@ -818,7 +817,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Corporate Action: Emirates NBD Acquisition of RBL Bank 🔹 RBL Bank has officially received RBI approval for Emirates NBD Bank to launch an open offer to acquire a 26% stake in the company. • 🔹 RBI Stipulations require RBL Bank to apply Wholly Owned Subsidiary (WOS) mode governance directions and amend its Articles of Association. • 🔹 Market Impact: This move is expected to bolster RBL Bank's capital base and provide a strategic global partner in Emirates NBD.</t>
+          <t>Corporate Action: Emirates NBD Acquisition of RBL Bank RBL Bank has officially received RBI approval for Emirates NBD Bank to launch an open offer to acquire a 26% stake in the company. • RBI Stipulations require RBL Bank to apply Wholly Owned Subsidiary (WOS) mode governance directions and amend its Articles of Association. • Market Impact: This move is expected to bolster RBL Bank's capital base and provide a strategic global partner in Emirates NBD.</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -1454,9 +1453,9 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>Rabeh Saqer addressed His Excellency Advisor Turki Al-Sheikh from "Jeddah Season" and, in collaboration with Rotana, presented an impressive concert that confirms "Jeddah is different" and promises "an album like no other."
-In a massive concert where tickets sold out before the event, "Jeddah Season" celebrated with the "Gulf Songbird," the great artist Rabeh Saqer, the tremendous success achieved by the "Songbird" as he soared with his voice, music, and creativity in front of his large audience that filled the "Abadi Al-Johar Arena" in Jeddah. Those who followed the live broadcast of the concert on Rotana channels also enjoyed Rabeh's artistic contributions on stage with his melodic, rhythmic, social, emotional, and patriotic songs, aligning with the season's slogan "Jeddah is different," as he indeed delivered something "different." This delighted everyone who watched the concert and ignited social media with clips captured by his fans, showcasing Rabeh singing with full musical and physical vigor throughout two singing sets, interspersed with a short break for the large accompanying band led by Maestro Hani Farhat.
-Mr. Salem Al-Hindi, Chairman and CEO of Rotana Music Group, was the first to welcome Rabeh Saqer upon his arrival at the concert venue and also the first to congratulate him on the success as he left the stage. However, between the beginning and the end, Rabeh Saqer crafted a success story for an artist armed with exceptional musical talent, a large, loyal, and loving audience. Before taking the stage, the eagle met with Mr. Salem in front of the Media Wall with media representatives. In response to a question about the message he sends from "Jeddah Season" to His Excellency Advisor Turki bin Abdul Mohsen Al-Sheikh, Chairman of the General Entertainment Authority, Rabeh conveyed a message of love, gratitude, and appreciation, saying: "His Excellency the Advisor is always with us in our hearts wherever we are in the Kingdom and outside it... not just in the Riyadh and Jeddah seasons." Rabeh also revealed that he is still working on his upcoming album produced by Rotana, which will include a group of prominent poets and composers as well as several talented individuals, emphasizing his commitment to musical diversity in these works to make his album, as usual, unique.
-On stage, Rabeh Saqer entertained his audience with a large number of his 30 songs that he rehearsed with his band, including: (Abarak Al-Saat, Sudfa, Afahemak, Enti Helwa, Taqdar Te'eed, Alf Min Yashhad, Khalna Kitha Helween, Kitha (Takhleen Al-Sahar), Al-Bashara, Al-Abaya Al-Raheefa, Al-Hikaya, Sadiqini, Gharam Atfal, Khalas, Wash Rayik Al-Laila, Awjah Al-Ma'na, Al-Rasas, La Tamnen, Yuhibunuh, Al-Dhahab Asli, Al-Waqi', Ya Dar, Ma Ad Tas'al, Sarra Al-Layl, Maghroura, Az'al Alayk). He concluded by bidding farewell to the audience of Jeddah and thanking those responsible for Jeddah Season and Rotana for their efforts in making this event a success.</t>
+In a grand concert where tickets sold out before the event, "Jeddah Season" celebrated with the "Saqer of Gulf Music," the great artist Rabeh Saqer, the tremendous success he achieved as he soared with his voice, music, and creativity in front of his large audience that filled the "Abadi Al-Johar Arena" in Jeddah, as well as those who followed the live broadcast of the concert through Rotana channels. Rabeh's artistic performance on stage harmonized with his melodic, rhythmic, social, emotional, and patriotic songs, aligning with the season's slogan "Jeddah is different," and he indeed delivered something "different," which delighted everyone who watched the concert and ignited social media with clips captured by his fans, showcasing Rabeh singing with full musical and physical vigor throughout two singing sets, interspersed with a short break for the large accompanying band led by Maestro Hani Farhat.
+Mr. Salem Al-Hindi, Chairman and CEO of Rotana Music Group, was the first to welcome Rabeh Saqer upon his arrival at the concert venue and also the first to congratulate him on the success as he left the stage. However, between the beginning and the end, Rabeh Saqer crafted a success story for an artist armed with exceptional musical talent, a large, loyal, and loving audience. Before taking the stage, Rabeh met with Mr. Salem in front of the Media Wall with media representatives, and in response to a question about the message he sends from "Jeddah Season" to His Excellency Advisor Turki bin Abdul Mohsen Al-Sheikh, Chairman of the General Entertainment Authority, Rabeh conveyed a message of love, gratitude, and appreciation, saying: "His Excellency the Advisor is always with us in our hearts wherever we are in the Kingdom and outside it... not just in the Riyadh and Jeddah seasons." Rabeh also revealed that he is still working on his upcoming album produced by Rotana, which will include a group of prominent poets and composers as well as several talented individuals, emphasizing his commitment to musical diversity in these works to make his album, as usual, unique.
+On stage, Rabeh Saqer entertained his audience with a large number of his 30 songs that he rehearsed with his band, including: (Abarak Al-Saat, Sudfa, Afahemak, Enti Helwa, Taqdar Te'eed, Alf Min Yashhad, Khalna Kitha Helween, Kitha (Takhleen Al-Sahar), Al-Bashara, Al-Abaya Al-Raheefa, Al-Hikaya, Sadiqini, Gharam Atfal, Khalas, Wash Rayik Al-Laila, Awjah Al-Ma'na, Al-Rasas, La Tamnin, Yuhibunuh, Al-Dhahab Asli, Al-Waqi', Ya Dar, Ma Ad Tas'al, Sarra Al-Layl, Maghroura, Az'al Alayk). He concluded by bidding farewell to the people of Jeddah and thanking those behind Jeddah Season and Rotana for their efforts in making this event a success.</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1487,7 +1486,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>He concluded by bidding farewell to the audience of Jeddah and thanking those responsible for Jeddah Season and Rotana for their efforts in making this event a success. • However, between the beginning and the end, Rabeh Saqer crafted a success story for an artist armed with exceptional musical talent, a large, loyal, and loving audience. • Salem in front of the Media Wall with media representatives.</t>
+          <t>However, between the beginning and the end, Rabeh Saqer crafted a success story for an artist armed with exceptional musical talent, a large, loyal, and loving audience. • He concluded by bidding farewell to the people of Jeddah and thanking those behind Jeddah Season and Rotana for their efforts in making this event a success. • Before taking the stage, Rabeh met with Mr.</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2464,9 +2463,9 @@
 - 2008 campus interview at Infosys with a salary of 25k
 - 2012 Emirates NBD in Dubai with a salary of 12k AED
 - 2013 IT Manager role in Dubai with a salary of 18k AED
-- 2015, married, earning around 23k AED in a Dubai-based startup
+- 2015, got married, earning around 23k AED in a Dubai-based startup
 - 2019 lost everything due to alimony and false cases that left me stuck here
-Moral: Don't marry, bro. 🥹</t>
+Moral: Don't get married, bro. 🥹</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2734,7 +2733,13 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>@KishSiff Try remarriage with a daughter of retired judge.</t>
+          <t>My career growth story 📈😀 
+- 2008 campus interview Infosys 25k salary
+- 2012 Emirates NBD Dubai 12k AED
+- 2013 IT Manager role in Dubai (18k AED)
+- 2015, married, ~23k AED in Dubai based startup
+- 2019 lost all as alimony &amp; fake cases stuck here
+Moral : Dont marry bro. 🥹</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2796,24 +2801,28 @@
 Moral : Dont marry bro. 🥹</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>https://x.com/KishSiff/status/2043299071918813643</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>@KishSiff Try remarriage with a daughter of retired judge.</t>
-        </is>
-      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>@KishSiff Try remarriage with a daughter of retired judge.</t>
+          <t>My career growth story 📈😀 
+- 2008 campus interview Infosys 25k salary
+- 2012 Emirates NBD Dubai 12k AED
+- 2013 IT Manager role in Dubai (18k AED)
+- 2015, married, ~23k AED in Dubai based startup
+- 2019 lost all as alimony &amp; fake cases stuck here
+Moral : Dont marry bro. 🥹</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Try remarriage with the daughter of a retired judge.</t>
+          <t>My career growth story 📈😀 
+- 2008 campus interview at Infosys with a salary of 25k
+- 2012 Emirates NBD in Dubai with a salary of 12k AED
+- 2013 IT Manager role in Dubai with a salary of 18k AED
+- 2015, got married, earning around 23k AED in a Dubai-based startup
+- 2019 lost everything due to alimony and false cases that left me stuck here
+Moral: Don't get married, bro. 🥹</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2844,7 +2853,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Try remarriage with the daughter of a retired judge.</t>
+          <t>My career growth story 📈😀 - 2008 campus interview at Infosys with a salary of 25k - 2012 Emirates NBD in Dubai with a sa…</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -3809,7 +3818,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Thursday is fun 🤩 Buy your coffee from Molten and get the second one free with #Emirates_NBD cards 💳 For details: https://t.co/e7pJxUCJeB https://t.co/zoLns3Ls04</t>
+          <t>Thursday is delicious 🤩 Buy your coffee from Molten and get the second one free with #Emirates_NBD cards 💳 For details: https://t.co/e7pJxUCJeB https://t.co/zoLns3Ls04</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3840,7 +3849,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Thursday is fun 🤩 Buy your coffee from Molten and get the second one free with #Emirates_NBD cards 💳 For details: https://t.co/e7pJxUCJeB https://t.co/zoLns3Ls04</t>
+          <t>Thursday is delicious 🤩 Buy your coffee from Molten and get the second one free with #Emirates_NBD cards 💳 For details: https://t.co/e7pJxUCJeB https://t.co/zoLns3Ls04</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3894,10 +3903,7 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Emirates NBD has launched a Business Support Package featuring temporary fee-relief measures to help SMEs manage their day-to-day operations over the coming months
-This initiative complements a broader set of measures introduced by the Government of Dubai and the Central Bank of the UAE
-This step reflects the UAE’s proactive and resilient economic approach where public and private sectors work hand in hand to support businesses, strengthen market confidence, and ensure continuity during evolving global conditions
-It also highlights a strong commitment to empowering SMEs, which remain a vital pillar of sustainable economic growth and innovation in the country 🇦🇪</t>
+          <t>مبادرة رائعة تدعم الشركات الناشئة والاستثماري</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3951,30 +3957,16 @@
           <t>مبادرة رائعة تدعم الشركات الناشئة والاستثماري</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>https://x.com/MuhammadBopxzr/status/2043204724711621075</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Emirates NBD has launched a Business Support Package featuring temporary fee-relief measures to help SMEs manage their day-to-day operations over the coming months
-This initiative complements a broader set of measures introduced by the Government of Dubai and the Central Bank of the UAE
-This step reflects the UAE’s proactive and resilient economic approach where public and private sectors work hand in hand to support businesses, strengthen market confidence, and ensure continuity during evolving global conditions
-It also highlights a strong commitment to empowering SMEs, which remain a vital pillar of sustainable economic growth and innovation in the country 🇦🇪</t>
-        </is>
-      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>Emirates NBD has launched a Business Support Package featuring temporary fee-relief measures to help SMEs manage their day-to-day operations over the coming months
-This initiative complements a broader set of measures introduced by the Government of Dubai and the Central Bank of the UAE
-This step reflects the UAE’s proactive and resilient economic approach where public and private sectors work hand in hand to support businesses, strengthen market confidence, and ensure continuity during evolving global conditions
-It also highlights a strong commitment to empowering SMEs, which remain a vital pillar of sustainable economic growth and innovation in the country 🇦🇪</t>
+          <t>مبادرة رائعة تدعم الشركات الناشئة والاستثماري</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Emirates NBD has launched a Business Support Package featuring temporary fee-relief measures to help SMEs manage their day-to-day operations over the coming months. This initiative complements a broader set of measures introduced by the Government of Dubai and the Central Bank of the UAE. This step reflects the UAE’s proactive and resilient economic approach where public and private sectors work hand in hand to support businesses, strengthen market confidence, and ensure continuity during evolving global conditions. It also highlights a strong commitment to empowering SMEs, which remain a vital pillar of sustainable economic growth and innovation in the country.</t>
+          <t>A wonderful initiative that supports startups and investment.</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -4005,7 +3997,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Emirates NBD has launched a Business Support Package featuring temporary fee-relief measures to help SMEs manage their day-to-day operations over the coming months. • It also highlights a strong commitment to empowering SMEs, which remain a vital pillar of sustainable economic growth and innovation in the country. • This initiative complements a broader set of measures introduced by the Government of Dubai and the Central Bank of the UAE.</t>
+          <t>A wonderful initiative that supports startups and investment.</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -4483,7 +4475,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Seeing your steps progress motivates you to keep going.
+          <t>Seeing your progress motivates you to keep going.
 💡Tip: Focus on what you have paid off, not just what remains.
 A small achievement gives you a greater drive to continue.</t>
         </is>
@@ -4516,7 +4508,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>💡Tip: Focus on what you have paid off, not just what remains. • Seeing your steps progress motivates you to keep going. • A small achievement gives you a greater drive to continue.</t>
+          <t>💡Tip: Focus on what you have paid off, not just what remains. • A small achievement gives you a greater drive to continue. • Seeing your progress motivates you to keep going.</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">

--- a/check2.xlsx
+++ b/check2.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL40"/>
+  <dimension ref="A1:AL41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -908,7 +908,7 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>Reducing uncertainty.
-Let our expert advisors in private banking at Emirates NBD provide you with investment strategies tailored specifically for you, aligned with your goals, acceptable risk profile, and long-term vision; to help you identify promising opportunities. Invest with confidence.</t>
+Let our expert advisors in private banking at Emirates NBD provide you with investment strategies tailored specifically for you, aligning with your goals, acceptable risk profile, and long-term vision; to help you identify promising opportunities. Invest with confidence.</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>A few clicks can change a child's future. Emirates NBD has made it easy for customers to donate to Dubai Cares through its app, contributing to supporting children's education around the world. #DubaiCares #ENBD #EducationForAll</t>
+          <t>A few clicks. A child’s future changed. Emirates NBD has made it so easy for its customers to donate to Dubai Cares through its app, helping support children’s education globally. #DubaiCares #ENBD #EducationForAll</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Emirates NBD has made it easy for customers to donate to Dubai Cares through its app, contributing to supporting children's education around the world. • A few clicks can change a child's future. • #DubaiCares #ENBD #EducationForAll</t>
+          <t>Emirates NBD has made it so easy for its customers to donate to Dubai Cares through its app, helping support children’s education globally. • A child’s future changed. • #DubaiCares #ENBD #EducationForAll</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1716,18 +1716,8 @@
 #EmiratesNBD #PrivateBanking #InvestmentAdvisory #InvestWithConfidence</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2043660471580942471</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Minimise uncertainty.
-Let our expert advisors at Emirates NBD Private Banking craft bespoke investment strategies designed to align with your goals, risk profile and long-term vision — helping you identify promising trends. Invest with confidence.
-#EmiratesNBD #PrivateBanking #InvestmentAdvisory #InvestWithConfidence</t>
-        </is>
-      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
           <t>Minimise uncertainty.
@@ -2528,7 +2518,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Hi @mohanstatsman - do you know when Surya Kumar Yadav last played an influential innings against a top-tier international team or a top 4 IPL team? It seems like it's been a long time.</t>
+          <t>Hi @mohanstatsman - do you have any idea when Surya Kumar Yadav last played an influential innings against a top-tier international team or a top 4 IPL team? It seems like it's been a long time.</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2559,7 +2549,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Hi @mohanstatsman - do you know when Surya Kumar Yadav last played an influential innings against a top-tier international team or a top 4 IPL team? • It seems like it's been a long time.</t>
+          <t>Hi @mohanstatsman - do you have any idea when Surya Kumar Yadav last played an influential innings against a top-tier international team or a top 4 IPL team? • It seems like it's been a long time.</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -4112,32 +4102,32 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2043618934671208880</t>
+          <t>2043569881270951992</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://x.com/Mohadsaleem89/status/2043618934671208880</t>
+          <t>https://x.com/emiratesislamic/status/2043569881270951992</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://x.com/Mohadsaleem89</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mohadsaleem89</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mohd Saleem</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1026443277493575680/Tn_rrbBC_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -4148,35 +4138,32 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>للاسف عندي معكم طلب خذ له اسبوع ولا احد يتواصل معاي والموظفين اللي كلموني من عندكم وسوو لي الطلب ما كانوا صادقين معاي والحين محد منهم يرد..</t>
+          <t>Big goals don’t wait for a certain age.
+The Emirates Islamic ALPHA Youth Account is designed for youth, helping parents introduce smart money habits early, through a secure, digital experience built for the next generation.</t>
         </is>
       </c>
       <c r="K23" t="b">
         <v>0</v>
       </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Apr 13, 2026 · 9:14 AM UTC</t>
+          <t>Apr 13, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P23" s="2" t="n">
-        <v>46125.38472222222</v>
+        <v>46125.25</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -4185,7 +4172,7 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>16</v>
+        <v>90</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -4194,12 +4181,13 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>للاسف عندي معكم طلب خذ له اسبوع ولا احد يتواصل معاي والموظفين اللي كلموني من عندكم وسوو لي الطلب ما كانوا صادقين معاي والحين محد منهم يرد..</t>
+          <t>Big goals don’t wait for a certain age.
+The Emirates Islamic ALPHA Youth Account is designed for youth, helping parents introduce smart money habits early, through a secure, digital experience built for the next generation.</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>https://x.com/Mohadsaleem89/status/2043618934671208880</t>
+          <t>https://x.com/emiratesislamic/status/2043569881270951992</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -4219,7 +4207,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Cust</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -4228,7 +4216,7 @@
         </is>
       </c>
       <c r="AE23" s="2" t="n">
-        <v>46125.55138888889</v>
+        <v>46125.41666666666</v>
       </c>
       <c r="AF23" s="2" t="n">
         <v>46125</v>
@@ -4258,7 +4246,7 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4268,12 +4256,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2043569881270951992</t>
+          <t>2043569875726053574</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043569881270951992</t>
+          <t>https://x.com/emiratesislamic/status/2043569875726053574</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4298,166 +4286,6 @@
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
-        <is>
-          <t>علمهم صغار!
-للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
-https://t.co/LETUDia8It</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Big goals don’t wait for a certain age.
-The Emirates Islamic ALPHA Youth Account is designed for youth, helping parents introduce smart money habits early, through a secure, digital experience built for the next generation.</t>
-        </is>
-      </c>
-      <c r="K24" t="b">
-        <v>0</v>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Apr 13, 2026 · 6:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="n">
-        <v>46125.25</v>
-      </c>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="n">
-        <v>1</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>90</v>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>Big goals don’t wait for a certain age.
-The Emirates Islamic ALPHA Youth Account is designed for youth, helping parents introduce smart money habits early, through a secure, digital experience built for the next generation.</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043569881270951992</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>علمهم صغار!
-للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
-https://t.co/LETUDia8It</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>علمهم صغار!
-للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
-https://t.co/LETUDia8It</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>Teach them young! For more information, please visit the following link:</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE24" s="2" t="n">
-        <v>46125.41666666666</v>
-      </c>
-      <c r="AF24" s="2" t="n">
-        <v>46125</v>
-      </c>
-      <c r="AG24" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>For more information, please visit the following link:</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK24" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL24" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2043569875726053574</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043569875726053574</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
         <is>
           <t>Would you click a delivery link from an unknown number?
 Do not fall for the traps. Stay alert to scams.
@@ -4466,7 +4294,7 @@
 https://t.co/y7eSpGNdfk</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Would you click a delivery link from an unknown number?
 Do not fall for the traps. Stay alert to scams.
@@ -4475,48 +4303,48 @@
 &lt;a href="https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K25" t="b">
-        <v>0</v>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
         <is>
           <t>22h</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>Apr 13, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
-      <c r="P25" s="2" t="n">
+      <c r="P24" s="2" t="n">
         <v>46125.25</v>
       </c>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr">
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
         <is>
           <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud', 'https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security']</t>
         </is>
       </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
         <v>62</v>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>Would you click a delivery link from an unknown number?
 Do not fall for the traps. Stay alert to scams.
@@ -4525,12 +4353,12 @@
 emiratesislamic.ae/en/person…</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2043569875726053574</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>Would you click a delivery link from an unknown number?
 Do not fall for the traps. Stay alert to scams.
@@ -4539,7 +4367,7 @@
 https://t.co/y7eSpGNdfk</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>Would you click a delivery link from an unknown number?
 Do not fall for the traps. Stay alert to scams.
@@ -4548,7 +4376,7 @@
 https://t.co/y7eSpGNdfk</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>Would you click a delivery link from an unknown number? 
 Do not fall for the traps. Stay alert to scams. 
@@ -4556,9 +4384,157 @@
 #TogetherAgainstFraud</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE24" s="2" t="n">
+        <v>46125.41666666666</v>
+      </c>
+      <c r="AF24" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>2. Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Would you click a delivery link from an unknown number? • #EIAgainstFraud with Emirates Islamic. • Do not fall for the traps.</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AK24" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2043657206629851210</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2043657206629851210</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>عزيزنا المتعامل لقد حاولنا التواصل معك برسالة خاصة و لم ننجح في ذلك بسبب قواعد عدم متباعة الصفحة يرجى مراسلتنا برسالة خاصة لنتمكن من مساعدتك بطريقة أسرع</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>عزيزنا المتعامل لقد حاولنا التواصل معك برسالة خاصة و لم ننجح في ذلك بسبب قواعد عدم متباعة الصفحة يرجى مراسلتنا برسالة خاصة لنتمكن من مساعدتك بطريقة أسرع</t>
+        </is>
+      </c>
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>['Mohadsaleem89']</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Apr 13, 2026 · 11:47 AM UTC</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="n">
+        <v>46125.49097222222</v>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>3</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>عزيزنا المتعامل لقد حاولنا التواصل معك برسالة خاصة و لم ننجح في ذلك بسبب قواعد عدم متباعة الصفحة يرجى مراسلتنا برسالة خاصة لنتمكن من مساعدتك بطريقة أسرع</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>عزيزنا المتعامل لقد حاولنا التواصل معك برسالة خاصة و لم ننجح في ذلك بسبب قواعد عدم متباعة الصفحة يرجى مراسلتنا برسالة خاصة لنتمكن من مساعدتك بطريقة أسرع</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>Dear valued customer, we tried to contact you with a private message but were unsuccessful due to the page's follow rules. Please send us a private message so we can assist you more quickly.</t>
+        </is>
+      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Cust</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -4567,7 +4543,7 @@
         </is>
       </c>
       <c r="AE25" s="2" t="n">
-        <v>46125.41666666666</v>
+        <v>46125.65763888889</v>
       </c>
       <c r="AF25" s="2" t="n">
         <v>46125</v>
@@ -4584,7 +4560,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Would you click a delivery link from an unknown number? • #EIAgainstFraud with Emirates Islamic. • Do not fall for the traps.</t>
+          <t>Dear valued customer, we tried to contact you with a private message but were unsuccessful due to the page's follow rules. • Please send us a private message so we can assist you more quickly.</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -4597,7 +4573,7 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Mohadsaleem89</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4583,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2043657206629851210</t>
+          <t>2043620884234096765</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043657206629851210</t>
+          <t>https://x.com/emiratesislamic/status/2043620884234096765</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4638,7 +4614,8 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>عزيزنا المتعامل لقد حاولنا التواصل معك برسالة خاصة و لم ننجح في ذلك بسبب قواعد عدم متباعة الصفحة يرجى مراسلتنا برسالة خاصة لنتمكن من مساعدتك بطريقة أسرع</t>
+          <t>@emiratesislamic 
+تحديث رقم الهاتف 00971505160117</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -4652,21 +4629,21 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>['Mohadsaleem89']</t>
+          <t>['Charbel96960993']</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Apr 13, 2026 · 11:47 AM UTC</t>
+          <t>Apr 13, 2026 · 9:22 AM UTC</t>
         </is>
       </c>
       <c r="P26" s="2" t="n">
-        <v>46125.49097222222</v>
+        <v>46125.39027777778</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
@@ -4680,7 +4657,7 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -4692,16 +4669,26 @@
           <t>عزيزنا المتعامل لقد حاولنا التواصل معك برسالة خاصة و لم ننجح في ذلك بسبب قواعد عدم متباعة الصفحة يرجى مراسلتنا برسالة خاصة لنتمكن من مساعدتك بطريقة أسرع</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2043620884234096765</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>@emiratesislamic 
+تحديث رقم الهاتف 00971505160117</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>عزيزنا المتعامل لقد حاولنا التواصل معك برسالة خاصة و لم ننجح في ذلك بسبب قواعد عدم متباعة الصفحة يرجى مراسلتنا برسالة خاصة لنتمكن من مساعدتك بطريقة أسرع</t>
+          <t>@emiratesislamic 
+تحديث رقم الهاتف 00971505160117</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Dear valued customer, we tried to contact you with a private message but were unsuccessful due to the page's follow rules. Please send us a private message so we can assist you more quickly.</t>
+          <t>Update phone number 00971505160117</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4715,7 +4702,7 @@
         </is>
       </c>
       <c r="AE26" s="2" t="n">
-        <v>46125.65763888889</v>
+        <v>46125.55694444444</v>
       </c>
       <c r="AF26" s="2" t="n">
         <v>46125</v>
@@ -4732,7 +4719,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Dear valued customer, we tried to contact you with a private message but were unsuccessful due to the page's follow rules. • Please send us a private message so we can assist you more quickly.</t>
+          <t>Update phone number 00971505160117</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -4745,7 +4732,7 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>Mohadsaleem89</t>
+          <t>Charbel96960993</t>
         </is>
       </c>
     </row>
@@ -4755,12 +4742,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2043620884234096765</t>
+          <t>2043620711407743228</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043620884234096765</t>
+          <t>https://x.com/emiratesislamic/status/2043620711407743228</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4786,13 +4773,12 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>@emiratesislamic 
-تحديث رقم الهاتف 00971505160117</t>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>عزيزنا المتعامل لقد حاولنا التواصل معك برسالة خاصة و لم ننجح في ذلك بسبب قواعد عدم متباعة الصفحة يرجى مراسلتنا برسالة خاصة لنتمكن من مساعدتك بطريقة أسرع</t>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل.</t>
         </is>
       </c>
       <c r="K27" t="b">
@@ -4838,29 +4824,19 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>عزيزنا المتعامل لقد حاولنا التواصل معك برسالة خاصة و لم ننجح في ذلك بسبب قواعد عدم متباعة الصفحة يرجى مراسلتنا برسالة خاصة لنتمكن من مساعدتك بطريقة أسرع</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043620884234096765</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>@emiratesislamic 
-تحديث رقم الهاتف 00971505160117</t>
-        </is>
-      </c>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل.</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>@emiratesislamic 
-تحديث رقم الهاتف 00971505160117</t>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل.</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Update phone number 00971505160117</t>
+          <t>Hello dear customer. Thank you for contacting us. To protect your privacy, we will communicate with you via private messages to assist you better.</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4891,7 +4867,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Update phone number 00971505160117</t>
+          <t>To protect your privacy, we will communicate with you via private messages to assist you better. • Thank you for contacting us.</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -4914,12 +4890,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2043620711407743228</t>
+          <t>2043579224183722461</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043620711407743228</t>
+          <t>https://x.com/emiratesislamic/status/2043579224183722461</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4945,12 +4921,12 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>@Charbel96960993 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل.</t>
+          <t>@altamashhkhann Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل.</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
       <c r="K28" t="b">
@@ -4959,21 +4935,21 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>['Charbel96960993']</t>
+          <t>['altamashhkhann']</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Apr 13, 2026 · 9:22 AM UTC</t>
+          <t>Apr 13, 2026 · 6:37 AM UTC</t>
         </is>
       </c>
       <c r="P28" s="2" t="n">
-        <v>46125.39027777778</v>
+        <v>46125.27569444444</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
@@ -4987,7 +4963,7 @@
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -4996,27 +4972,27 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل.</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043620711407743228</t>
+          <t>https://x.com/emiratesislamic/status/2043579224183722461</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>@Charbel96960993 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل.</t>
+          <t>@altamashhkhann Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>@Charbel96960993 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل.</t>
+          <t>@altamashhkhann Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Hello dear customer. Thank you for contacting us. To protect your privacy, we will communicate with you via private messages to assist you better.</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -5030,7 +5006,7 @@
         </is>
       </c>
       <c r="AE28" s="2" t="n">
-        <v>46125.55694444444</v>
+        <v>46125.44236111111</v>
       </c>
       <c r="AF28" s="2" t="n">
         <v>46125</v>
@@ -5047,7 +5023,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>To protect your privacy, we will communicate with you via private messages to assist you better. • Thank you for contacting us.</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -5060,7 +5036,7 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>Charbel96960993</t>
+          <t>altamashhkhann</t>
         </is>
       </c>
     </row>
@@ -5999,36 +5975,192 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2043640004929573308</t>
+          <t>2043618934671208880</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://x.com/PRAVEEN16408007/status/2043640004929573308</t>
+          <t>https://x.com/Mohadsaleem89/status/2043618934671208880</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://x.com/PRAVEEN16408007</t>
+          <t>https://x.com/Mohadsaleem89</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>PRAVEEN16408007</t>
+          <t>Mohadsaleem89</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PRAVEENKUMAR</t>
+          <t>Mohd Saleem</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1431981849258049549/Yx_k4ZQN_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1026443277493575680/Tn_rrbBC_bigger.jpg</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
+        <is>
+          <t>@emiratesislamic للاسف عندي معكم طلب خذ له اسبوع ولا احد يتواصل معاي والموظفين اللي كلموني من عندكم وسوو لي الطلب ما كانوا صادقين معاي والحين محد منهم يرد..</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>للاسف عندي معكم طلب خذ له اسبوع ولا احد يتواصل معاي والموظفين اللي كلموني من عندكم وسوو لي الطلب ما كانوا صادقين معاي والحين محد منهم يرد..</t>
+        </is>
+      </c>
+      <c r="K35" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Apr 13, 2026 · 9:14 AM UTC</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>46125.38472222222</v>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="n">
+        <v>2</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>16</v>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>للاسف عندي معكم طلب خذ له اسبوع ولا احد يتواصل معاي والموظفين اللي كلموني من عندكم وسوو لي الطلب ما كانوا صادقين معاي والحين محد منهم يرد..</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>https://x.com/Mohadsaleem89/status/2043618934671208880</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>@emiratesislamic للاسف عندي معكم طلب خذ له اسبوع ولا احد يتواصل معاي والموظفين اللي كلموني من عندكم وسوو لي الطلب ما كانوا صادقين معاي والحين محد منهم يرد..</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>@emiratesislamic للاسف عندي معكم طلب خذ له اسبوع ولا احد يتواصل معاي والموظفين اللي كلموني من عندكم وسوو لي الطلب ما كانوا صادقين معاي والحين محد منهم يرد..</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>Unfortunately, I have a request with you that has taken a week and no one has contacted me. The employees who spoke to me from your side and processed my request were not honest with me, and now none of them are responding.</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AE35" s="2" t="n">
+        <v>46125.55138888889</v>
+      </c>
+      <c r="AF35" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>2. Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Unfortunately, I have a request with you that has taken a week and no one has contacted me. • The employees who spoke to me from your side and processed my request were not honest with me, and now none of them are responding.</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AK35" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL35" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2043640004929573308</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://x.com/PRAVEEN16408007/status/2043640004929573308</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://x.com/PRAVEEN16408007</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>PRAVEEN16408007</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>PRAVEENKUMAR</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1431981849258049549/Yx_k4ZQN_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
         <is>
           <t>DND is active. Guidelines followed.
 Still receiving repeated RBL credit card calls.
@@ -6039,7 +6171,7 @@
 @RBI @RBLBankCares #DND https://t.co/rR7uHyB8XQ</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>DND is active. Guidelines followed.
 Still receiving repeated RBL credit card calls.
@@ -6050,48 +6182,48 @@
 &lt;a href="/RBI" title="ReserveBankOfIndia"&gt;@RBI&lt;/a&gt; &lt;a href="/RBLBankCares" title="RBL Bank Cares"&gt;@RBLBankCares&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23DND"&gt;#DND&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K35" t="b">
-        <v>0</v>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
+      <c r="K36" t="b">
+        <v>0</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
         <is>
           <t>17h</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>Apr 13, 2026 · 10:38 AM UTC</t>
         </is>
       </c>
-      <c r="P35" s="2" t="n">
+      <c r="P36" s="2" t="n">
         <v>46125.44305555556</v>
       </c>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr">
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
         <is>
           <t>['https://x.com/rblbank', 'https://x.com/EmiratesNBD_AE', 'https://x.com/RBI', 'https://x.com/RBLBankCares', 'https://x.com/search?f=tweets&amp;q=%23DND']</t>
         </is>
       </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
         <v>14</v>
       </c>
-      <c r="W35" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>DND is active. Guidelines followed.
 Still receiving repeated RBL credit card calls.
@@ -6102,12 +6234,12 @@
 @RBI @RBLBankCares #DND</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
+      <c r="Y36" t="inlineStr">
         <is>
           <t>https://x.com/PRAVEEN16408007/status/2043640004929573308</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>DND is active. Guidelines followed.
 Still receiving repeated RBL credit card calls.
@@ -6118,7 +6250,7 @@
 @RBI @RBLBankCares #DND https://t.co/rR7uHyB8XQ</t>
         </is>
       </c>
-      <c r="AA35" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>DND is active. Guidelines followed.
 Still receiving repeated RBL credit card calls.
@@ -6129,179 +6261,23 @@
 @RBI @RBLBankCares #DND https://t.co/rR7uHyB8XQ</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
+      <c r="AB36" t="inlineStr">
         <is>
           <t>DND is active. Guidelines followed. Still receiving repeated RBL credit card calls. @RBLBank, if these numbers are not yours, why are your products being promoted repeatedly? @EmiratesNBD_AE 1 year. 35+ calls. No permanent resolution. Case ID: 118684309 @RBI @RBLBankCares #DND</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
+      <c r="AC36" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="AD35" t="inlineStr">
+      <c r="AD36" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="AE35" s="2" t="n">
+      <c r="AE36" s="2" t="n">
         <v>46125.60972222222</v>
-      </c>
-      <c r="AF35" s="2" t="n">
-        <v>46125</v>
-      </c>
-      <c r="AG35" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Case ID: 118684309 @RBI @RBLBankCares #DND • Still receiving repeated RBL credit card calls. • @RBLBank, if these numbers are not yours, why are your products being promoted repeatedly?</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK35" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL35" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>34</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2043682357216149641</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>https://x.com/chin2to/status/2043682357216149641</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>https://x.com/chin2to</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>chin2to</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Chintn S. Padhya</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2006918638885060609/VLnYZV2k_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Finally thought I'll get an @EmiratesNBD_AE Skywards Credit Card, but applying for one is such a hassle. Changed my mind immediately after speaking to them for 2 months.</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Finally thought I&amp;#39;ll get an &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; Skywards Credit Card, but applying for one is such a hassle. Changed my mind immediately after speaking to them for 2 months.</t>
-        </is>
-      </c>
-      <c r="K36" t="b">
-        <v>0</v>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>14h</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>Apr 13, 2026 · 1:26 PM UTC</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="n">
-        <v>46125.55972222222</v>
-      </c>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="S36" t="n">
-        <v>1</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>326</v>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>Finally thought I'll get an @EmiratesNBD_AE Skywards Credit Card, but applying for one is such a hassle. Changed my mind immediately after speaking to them for 2 months.</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>https://x.com/chin2to/status/2043682357216149641</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>Finally thought I'll get an @EmiratesNBD_AE Skywards Credit Card, but applying for one is such a hassle. Changed my mind immediately after speaking to them for 2 months.</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>Finally thought I'll get an @EmiratesNBD_AE Skywards Credit Card, but applying for one is such a hassle. Changed my mind immediately after speaking to them for 2 months.</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>Finally thought I'd get an Emirates NBD Skywards Credit Card, but applying for one is such a hassle. I changed my mind immediately after speaking to them for 2 months.</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD36" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="AE36" s="2" t="n">
-        <v>46125.72638888889</v>
       </c>
       <c r="AF36" s="2" t="n">
         <v>46125</v>
@@ -6318,7 +6294,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Finally thought I'd get an Emirates NBD Skywards Credit Card, but applying for one is such a hassle. • I changed my mind immediately after speaking to them for 2 months.</t>
+          <t>Case ID: 118684309 @RBI @RBLBankCares #DND • Still receiving repeated RBL credit card calls. • @RBLBank, if these numbers are not yours, why are your products being promoted repeatedly?</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -6341,71 +6317,71 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2043560931511189651</t>
+          <t>2043682357216149641</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043560931511189651</t>
+          <t>https://x.com/chin2to/status/2043682357216149641</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/chin2to</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>chin2to</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Chintn S. Padhya</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2006918638885060609/VLnYZV2k_bigger.jpg</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>@emiratesislamic I have already cleared a personal loan and approached your Phone Banking &amp;amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp;amp; revert ASAP. Thank You.</t>
+          <t>Finally thought I'll get an @EmiratesNBD_AE Skywards Credit Card, but applying for one is such a hassle. Changed my mind immediately after speaking to them for 2 months.</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
+          <t>Finally thought I&amp;#39;ll get an &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; Skywards Credit Card, but applying for one is such a hassle. Changed my mind immediately after speaking to them for 2 months.</t>
         </is>
       </c>
       <c r="K37" t="b">
         <v>0</v>
       </c>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>['aswanikumartst5']</t>
-        </is>
-      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Apr 13, 2026 · 5:24 AM UTC</t>
+          <t>Apr 13, 2026 · 1:26 PM UTC</t>
         </is>
       </c>
       <c r="P37" s="2" t="n">
-        <v>46125.225</v>
+        <v>46125.55972222222</v>
       </c>
       <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -6414,36 +6390,36 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>2</v>
+        <v>326</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
+          <t>Finally thought I'll get an @EmiratesNBD_AE Skywards Credit Card, but applying for one is such a hassle. Changed my mind immediately after speaking to them for 2 months.</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043560931511189651</t>
+          <t>https://x.com/chin2to/status/2043682357216149641</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>@emiratesislamic I have already cleared a personal loan and approached your Phone Banking &amp;amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp;amp; revert ASAP. Thank You.</t>
+          <t>Finally thought I'll get an @EmiratesNBD_AE Skywards Credit Card, but applying for one is such a hassle. Changed my mind immediately after speaking to them for 2 months.</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>@emiratesislamic I have already cleared a personal loan and approached your Phone Banking &amp;amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp;amp; revert ASAP. Thank You.</t>
+          <t>Finally thought I'll get an @EmiratesNBD_AE Skywards Credit Card, but applying for one is such a hassle. Changed my mind immediately after speaking to them for 2 months.</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>I have already cleared a personal loan and approached your Phone Banking and WhatsApp channel for the issuance of a NIL LIABILITY LETTER, but I have not received a concrete response. It is also not feasible to obtain it through your application. Can you please check and respond as soon as possible? Thank you.</t>
+          <t>Finally thought I'd get an Emirates NBD Skywards Credit Card, but applying for one is such a hassle. I changed my mind immediately after speaking to them for 2 months.</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -6457,29 +6433,29 @@
         </is>
       </c>
       <c r="AE37" s="2" t="n">
-        <v>46125.39166666667</v>
+        <v>46125.72638888889</v>
       </c>
       <c r="AF37" s="2" t="n">
         <v>46125</v>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
+          <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>I have already cleared a personal loan and approached your Phone Banking and WhatsApp channel for the issuance of a NIL LIABILITY LETTER, but I have not received a concrete response. • Can you please check and respond as soon as possible? • It is also not feasible to obtain it through your application.</t>
+          <t>Finally thought I'd get an Emirates NBD Skywards Credit Card, but applying for one is such a hassle. • I changed my mind immediately after speaking to them for 2 months.</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>Emirates Islamic Bank (EIB)</t>
+          <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
       <c r="AK37" t="n">
@@ -6487,7 +6463,7 @@
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>aswanikumartst5</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6497,119 +6473,109 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2043544891095908768</t>
+          <t>2043560931511189651</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://x.com/mahmoudyusof/status/2043544891095908768</t>
+          <t>https://x.com/emiratesislamic/status/2043560931511189651</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://x.com/mahmoudyusof</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>mahmoudyusof</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>محمود يوسف</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1635733798569607188/RIMg1fWQ_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE 
-التحويلات بين حساباتي أنا الشخصية مش شغال على ال application في الأجازات وعشان أحل الموضوع طلبت card لكل حساب لكن اتأخرت جداً ودلوقت عندي emergency محتاج فيها فلوس بكلم خدمة العملاء بيقولي ميقدرش يعمل تحويل ولازم أنتظر لبكرة
-تجربة في غاية السوء مع البنك دة</t>
+          <t>@emiratesislamic I have already cleared a personal loan and approached your Phone Banking &amp;amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp;amp; revert ASAP. Thank You.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; 
-التحويلات بين حساباتي أنا الشخصية مش شغال على ال application في الأجازات وعشان أحل الموضوع طلبت card لكل حساب لكن اتأخرت جداً ودلوقت عندي emergency محتاج فيها فلوس بكلم خدمة العملاء بيقولي ميقدرش يعمل تحويل ولازم أنتظر لبكرة
-تجربة في غاية السوء مع البنك دة</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
         </is>
       </c>
       <c r="K38" t="b">
         <v>0</v>
       </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>['aswanikumartst5']</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Apr 13, 2026 · 4:20 AM UTC</t>
+          <t>Apr 13, 2026 · 5:24 AM UTC</t>
         </is>
       </c>
       <c r="P38" s="2" t="n">
-        <v>46125.18055555555</v>
+        <v>46125.225</v>
       </c>
       <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
         <v>2</v>
       </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>21</v>
-      </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE 
-التحويلات بين حساباتي أنا الشخصية مش شغال على ال application في الأجازات وعشان أحل الموضوع طلبت card لكل حساب لكن اتأخرت جداً ودلوقت عندي emergency محتاج فيها فلوس بكلم خدمة العملاء بيقولي ميقدرش يعمل تحويل ولازم أنتظر لبكرة
-تجربة في غاية السوء مع البنك دة</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>https://x.com/mahmoudyusof/status/2043544891095908768</t>
+          <t>https://x.com/emiratesislamic/status/2043560931511189651</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE 
-التحويلات بين حساباتي أنا الشخصية مش شغال على ال application في الأجازات وعشان أحل الموضوع طلبت card لكل حساب لكن اتأخرت جداً ودلوقت عندي emergency محتاج فيها فلوس بكلم خدمة العملاء بيقولي ميقدرش يعمل تحويل ولازم أنتظر لبكرة
-تجربة في غاية السوء مع البنك دة</t>
+          <t>@emiratesislamic I have already cleared a personal loan and approached your Phone Banking &amp;amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp;amp; revert ASAP. Thank You.</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE 
-التحويلات بين حساباتي أنا الشخصية مش شغال على ال application في الأجازات وعشان أحل الموضوع طلبت card لكل حساب لكن اتأخرت جداً ودلوقت عندي emergency محتاج فيها فلوس بكلم خدمة العملاء بيقولي ميقدرش يعمل تحويل ولازم أنتظر لبكرة
-تجربة في غاية السوء مع البنك دة</t>
+          <t>@emiratesislamic I have already cleared a personal loan and approached your Phone Banking &amp;amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp;amp; revert ASAP. Thank You.</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Transfers between my personal accounts are not working on the application during the holidays, and to resolve the issue, I requested a card for each account, but it has been delayed significantly. Now I have an emergency and need money. When I called customer service, they told me they can't make a transfer and I have to wait until tomorrow. This is an extremely bad experience with this bank.</t>
+          <t>I have already cleared a personal loan and approached your Phone Banking and WhatsApp channel for the issuance of a NIL LIABILITY LETTER, but I have not received a concrete response. It is also not feasible to obtain it through your application. Can you please check and respond as soon as possible? Thank you.</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -6623,29 +6589,29 @@
         </is>
       </c>
       <c r="AE38" s="2" t="n">
-        <v>46125.34722222222</v>
+        <v>46125.39166666667</v>
       </c>
       <c r="AF38" s="2" t="n">
         <v>46125</v>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
+          <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Transfers between my personal accounts are not working on the application during the holidays, and to resolve the issue, I requested a card for each account, but it has been delayed significantly. • When I called customer service, they told me they can't make a transfer and I have to wait until tomorrow. • Now I have an emergency and need money.</t>
+          <t>I have already cleared a personal loan and approached your Phone Banking and WhatsApp channel for the issuance of a NIL LIABILITY LETTER, but I have not received a concrete response. • Can you please check and respond as soon as possible? • It is also not feasible to obtain it through your application.</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank (ENBD)</t>
+          <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AK38" t="n">
@@ -6653,7 +6619,7 @@
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>aswanikumartst5</t>
         </is>
       </c>
     </row>
@@ -6663,43 +6629,47 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2043621947788099696</t>
+          <t>2043544891095908768</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://x.com/nee_red4life/status/2043621947788099696</t>
+          <t>https://x.com/mahmoudyusof/status/2043544891095908768</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://x.com/nee_red4life</t>
+          <t>https://x.com/mahmoudyusof</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>nee_red4life</t>
+          <t>mahmoudyusof</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Neeraj</t>
+          <t>محمود يوسف</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2042877600255885313/TxiQEZSG_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1635733798569607188/RIMg1fWQ_bigger.jpg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>I am unable to register on the ENBDX app because of this issue and the relationship manager is now asking me to visit the ATM to get it done. This is after falsely assuring me that the ENBDX app would be enabled as soon as I receive the card.</t>
+          <t>@EmiratesNBD_AE 
+التحويلات بين حساباتي أنا الشخصية مش شغال على ال application في الأجازات وعشان أحل الموضوع طلبت card لكل حساب لكن اتأخرت جداً ودلوقت عندي emergency محتاج فيها فلوس بكلم خدمة العملاء بيقولي ميقدرش يعمل تحويل ولازم أنتظر لبكرة
+تجربة في غاية السوء مع البنك دة</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; highly disappointed with your relationship manager who failed to provide me complete info at the time of account opening. My Emirates ID is not linked to my account despite assurance from him and all documentation being provided</t>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; 
+التحويلات بين حساباتي أنا الشخصية مش شغال على ال application في الأجازات وعشان أحل الموضوع طلبت card لكل حساب لكن اتأخرت جداً ودلوقت عندي emergency محتاج فيها فلوس بكلم خدمة العملاء بيقولي ميقدرش يعمل تحويل ولازم أنتظر لبكرة
+تجربة في غاية السوء مع البنك دة</t>
         </is>
       </c>
       <c r="K39" t="b">
@@ -6709,16 +6679,16 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Apr 13, 2026 · 9:26 AM UTC</t>
+          <t>Apr 13, 2026 · 4:20 AM UTC</t>
         </is>
       </c>
       <c r="P39" s="2" t="n">
-        <v>46125.39305555556</v>
+        <v>46125.18055555555</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
@@ -6727,7 +6697,7 @@
         </is>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T39" t="n">
         <v>0</v>
@@ -6736,7 +6706,7 @@
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
@@ -6745,27 +6715,33 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE highly disappointed with your relationship manager who failed to provide me complete info at the time of account opening. My Emirates ID is not linked to my account despite assurance from him and all documentation being provided</t>
+          <t>@EmiratesNBD_AE 
+التحويلات بين حساباتي أنا الشخصية مش شغال على ال application في الأجازات وعشان أحل الموضوع طلبت card لكل حساب لكن اتأخرت جداً ودلوقت عندي emergency محتاج فيها فلوس بكلم خدمة العملاء بيقولي ميقدرش يعمل تحويل ولازم أنتظر لبكرة
+تجربة في غاية السوء مع البنك دة</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>https://x.com/nee_red4life/status/2043621947788099696</t>
+          <t>https://x.com/mahmoudyusof/status/2043544891095908768</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>I am unable to register on the ENBDX app because of this issue and the relationship manager is now asking me to visit the ATM to get it done. This is after falsely assuring me that the ENBDX app would be enabled as soon as I receive the card.</t>
+          <t>@EmiratesNBD_AE 
+التحويلات بين حساباتي أنا الشخصية مش شغال على ال application في الأجازات وعشان أحل الموضوع طلبت card لكل حساب لكن اتأخرت جداً ودلوقت عندي emergency محتاج فيها فلوس بكلم خدمة العملاء بيقولي ميقدرش يعمل تحويل ولازم أنتظر لبكرة
+تجربة في غاية السوء مع البنك دة</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>I am unable to register on the ENBDX app because of this issue and the relationship manager is now asking me to visit the ATM to get it done. This is after falsely assuring me that the ENBDX app would be enabled as soon as I receive the card.</t>
+          <t>@EmiratesNBD_AE 
+التحويلات بين حساباتي أنا الشخصية مش شغال على ال application في الأجازات وعشان أحل الموضوع طلبت card لكل حساب لكن اتأخرت جداً ودلوقت عندي emergency محتاج فيها فلوس بكلم خدمة العملاء بيقولي ميقدرش يعمل تحويل ولازم أنتظر لبكرة
+تجربة في غاية السوء مع البنك دة</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>I am unable to register on the ENBDX app because of this issue, and the relationship manager is now asking me to visit the ATM to get it done. This is after falsely assuring me that the ENBDX app would be enabled as soon as I receive the card.</t>
+          <t>Transfers between my personal accounts are not working on the application during the holidays, and to resolve the issue, I requested a card for each account, but it has been delayed significantly. Now I have an emergency and need money. When I called customer service, they told me they can't make a transfer and I have to wait until tomorrow. This is an extremely bad experience with this bank.</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -6779,7 +6755,7 @@
         </is>
       </c>
       <c r="AE39" s="2" t="n">
-        <v>46125.55972222222</v>
+        <v>46125.34722222222</v>
       </c>
       <c r="AF39" s="2" t="n">
         <v>46125</v>
@@ -6796,7 +6772,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>I am unable to register on the ENBDX app because of this issue, and the relationship manager is now asking me to visit the ATM to get it done. • This is after falsely assuring me that the ENBDX app would be enabled as soon as I receive the card.</t>
+          <t>Transfers between my personal accounts are not working on the application during the holidays, and to resolve the issue, I requested a card for each account, but it has been delayed significantly. • When I called customer service, they told me they can't make a transfer and I have to wait until tomorrow. • Now I have an emergency and need money.</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
@@ -6819,54 +6795,50 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2043618605657661464</t>
+          <t>2043621947788099696</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://x.com/saran945/status/2043618605657661464</t>
+          <t>https://x.com/nee_red4life/status/2043621947788099696</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://x.com/saran945</t>
+          <t>https://x.com/nee_red4life</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>saran945</t>
+          <t>nee_red4life</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Saravanan</t>
+          <t>Neeraj</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2008105033943175168/704WYC21_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2042877600255885313/TxiQEZSG_bigger.jpg</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>this is for your information. . there a security issue (critical). .  unable to browse your website.  this is nothing to do with my previous request. Kindly take action.</t>
+          <t>I am unable to register on the ENBDX app because of this issue and the relationship manager is now asking me to visit the ATM to get it done. This is after falsely assuring me that the ENBDX app would be enabled as soon as I receive the card.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>this is for your information. . there a security issue (critical). .  unable to browse your website.  this is nothing to do with my previous request. Kindly take action.</t>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; highly disappointed with your relationship manager who failed to provide me complete info at the time of account opening. My Emirates ID is not linked to my account despite assurance from him and all documentation being provided</t>
         </is>
       </c>
       <c r="K40" t="b">
         <v>0</v>
       </c>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>18h</t>
@@ -6874,16 +6846,20 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Apr 13, 2026 · 9:13 AM UTC</t>
+          <t>Apr 13, 2026 · 9:26 AM UTC</t>
         </is>
       </c>
       <c r="P40" s="2" t="n">
-        <v>46125.38402777778</v>
+        <v>46125.39305555556</v>
       </c>
       <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -6892,7 +6868,7 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
@@ -6901,19 +6877,27 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>this is for your information. . there a security issue (critical). .  unable to browse your website.  this is nothing to do with my previous request. Kindly take action.</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
+          <t>@EmiratesNBD_AE highly disappointed with your relationship manager who failed to provide me complete info at the time of account opening. My Emirates ID is not linked to my account despite assurance from him and all documentation being provided</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>https://x.com/nee_red4life/status/2043621947788099696</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>I am unable to register on the ENBDX app because of this issue and the relationship manager is now asking me to visit the ATM to get it done. This is after falsely assuring me that the ENBDX app would be enabled as soon as I receive the card.</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>this is for your information. . there a security issue (critical). .  unable to browse your website.  this is nothing to do with my previous request. Kindly take action.</t>
+          <t>I am unable to register on the ENBDX app because of this issue and the relationship manager is now asking me to visit the ATM to get it done. This is after falsely assuring me that the ENBDX app would be enabled as soon as I receive the card.</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>This is for your information. There is a critical security issue. I am unable to browse your website. This has nothing to do with my previous request. Kindly take action.</t>
+          <t>I am unable to register on the ENBDX app because of this issue, and the relationship manager is now asking me to visit the ATM to get it done. This is after falsely assuring me that the ENBDX app would be enabled as soon as I receive the card.</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -6927,7 +6911,7 @@
         </is>
       </c>
       <c r="AE40" s="2" t="n">
-        <v>46125.55069444444</v>
+        <v>46125.55972222222</v>
       </c>
       <c r="AF40" s="2" t="n">
         <v>46125</v>
@@ -6944,7 +6928,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>There is a critical security issue. • This has nothing to do with my previous request. • I am unable to browse your website.</t>
+          <t>I am unable to register on the ENBDX app because of this issue, and the relationship manager is now asking me to visit the ATM to get it done. • This is after falsely assuring me that the ENBDX app would be enabled as soon as I receive the card.</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
@@ -6956,6 +6940,154 @@
         <v>2026</v>
       </c>
       <c r="AL40" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2043618605657661464</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://x.com/saran945/status/2043618605657661464</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://x.com/saran945</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>saran945</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Saravanan</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2008105033943175168/704WYC21_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>this is for your information. . there a security issue (critical). .  unable to browse your website.  this is nothing to do with my previous request. Kindly take action.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>this is for your information. . there a security issue (critical). .  unable to browse your website.  this is nothing to do with my previous request. Kindly take action.</t>
+        </is>
+      </c>
+      <c r="K41" t="b">
+        <v>0</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Apr 13, 2026 · 9:13 AM UTC</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="n">
+        <v>46125.38402777778</v>
+      </c>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="n">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>20</v>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>this is for your information. . there a security issue (critical). .  unable to browse your website.  this is nothing to do with my previous request. Kindly take action.</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>this is for your information. . there a security issue (critical). .  unable to browse your website.  this is nothing to do with my previous request. Kindly take action.</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>This is for your information. There is a critical security issue. I am unable to browse your website. This has nothing to do with my previous request. Kindly take action.</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AE41" s="2" t="n">
+        <v>46125.55069444444</v>
+      </c>
+      <c r="AF41" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>There is a critical security issue. • This has nothing to do with my previous request. • I am unable to browse your website.</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK41" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL41" t="inlineStr">
         <is>
           <t>EmiratesNBD_AE</t>
         </is>

--- a/check2.xlsx
+++ b/check2.xlsx
@@ -1416,7 +1416,7 @@
           <t>Dear all,  
 The only reason for the rises in the markets is the influx of strong liquidity (regardless of the mechanism) coinciding with company results, which is a period that the market never misses, neither in good times nor in bad.  
 Come back to me in two weeks, so we can talk about the "earthquake of logic."  
-Additionally, I am a girl. ☹️</t>
+On top of that, I am a girl. ☹️</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Come back to me in two weeks, so we can talk about the "earthquake of logic." Additionally, I am a girl.</t>
+          <t>Come back to me in two weeks, so we can talk about the "earthquake of logic." On top of that, I am a girl.</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1470,12 +1470,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2044077090039873867</t>
+          <t>2044078376982319373</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077090039873867</t>
+          <t>https://x.com/attas_2010/status/2044078376982319373</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>وحاليا بعد ماكان عندي قرض عقاري في بنك الرياض راح ارجعه مليون٦٠٠ ألف على ١٥ سنةصرت مديون للبنك الفرنسي مليونين ٣٠٠ ألف والصك مرهون عندهم وكل الي سوه سددو لبنك الرياض مليون ٧٠الف قيمة السداد المبكر فقط والفائض الي وعدني فيه سحب علي ومايرد</t>
+          <t>فوق ١٠ مرات ارفع شكاوي هذا الرد</t>
         </is>
       </c>
       <c r="K7" t="b">
@@ -1523,21 +1523,21 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 3:35 PM UTC</t>
+          <t>Apr 14, 2026 · 3:40 PM UTC</t>
         </is>
       </c>
       <c r="P7" s="2" t="n">
-        <v>46126.64930555555</v>
+        <v>46126.65277777778</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1546,7 +1546,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>101</v>
+        <v>39</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1555,12 +1555,12 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>وحاليا بعد ماكان عندي قرض عقاري في بنك الرياض راح ارجعه مليون٦٠٠ ألف على ١٥ سنةصرت مديون للبنك الفرنسي مليونين ٣٠٠ ألف والصك مرهون عندهم وكل الي سوه سددو لبنك الرياض مليون ٧٠الف قيمة السداد المبكر فقط والفائض الي وعدني فيه سحب علي ومايرد</t>
+          <t>فوق ١٠ مرات ارفع شكاوي هذا الرد</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077090039873867</t>
+          <t>https://x.com/attas_2010/status/2044078376982319373</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="AE7" s="2" t="n">
-        <v>46126.81597222222</v>
+        <v>46126.81944444445</v>
       </c>
       <c r="AF7" s="2" t="n">
         <v>46126</v>
@@ -2099,8 +2099,8 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Sheikh Khalid bin Mohammed bin Zayed Al Nahyan met with leaders of Chinese companies as part of strengthening the strategic partnership between the two countries. 
-The meetings focused on exploring new opportunities for economic and developmental cooperation to support the expansion of investments and enhance bilateral relations.</t>
+          <t>His Highness Sheikh Khalid bin Mohammed bin Zayed Al Nahyan met with leaders of Chinese companies as part of enhancing the strategic partnership between the two countries. 
+The meetings focused on exploring new opportunities for economic and developmental cooperation, supporting the expansion of investments and strengthening bilateral relations.</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Sheikh Khalid bin Mohammed bin Zayed Al Nahyan met with leaders of Chinese companies as part of strengthening the strategic partnership between the two countries. • The meetings focused on exploring new opportunities for economic and developmental cooperation to support the expansion of investments and enhance bilateral relations.</t>
+          <t>His Highness Sheikh Khalid bin Mohammed bin Zayed Al Nahyan met with leaders of Chinese companies as part of enhancing the strategic partnership between the two countries. • The meetings focused on exploring new opportunities for economic and developmental cooperation, supporting the expansion of investments and strengthening bilateral relations.</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Emirates NBD and Sobha Realty have partnered to provide integrated home financing solutions for off-plan projects in Dubai.</t>
+          <t>Emirates NBD and Sobha Realty partner to offer integrated home financing solutions for off-plan projects in Dubai.</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Emirates NBD and Sobha Realty have partnered to provide integrated home financing solutions for off-plan projects in Dubai.</t>
+          <t>Emirates NBD and Sobha Realty partner to offer integrated home financing solutions for off-plan projects in Dubai.</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Dear UAE government, what is the daily limit to deposit in the machine if I have 100k to deposit and the machine is slow? There are people behind me in line arguing about what to do, while no one questions those depositing black money. Why is that?</t>
+          <t>Dear UAE government, what is the daily limit to deposit in the machine if I have 100k to deposit and the machine is slow? There are people behind me in line arguing about what to do. Those depositing black money are not questioned; why is that?</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Dear UAE government, what is the daily limit to deposit in the machine if I have 100k to deposit and the machine is slow? • There are people behind me in line arguing about what to do, while no one questions those depositing black money.</t>
+          <t>Dear UAE government, what is the daily limit to deposit in the machine if I have 100k to deposit and the machine is slow? • There are people behind me in line arguing about what to do. • Those depositing black money are not questioned; why is that?</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Money grows better over time, with balance and the right diversification. Diversifying investments and thinking long-term help achieve greater stability. Small steps today can lead to stronger results in the future.</t>
+          <t>Money grows better with time, balance, and the right diversification. Diversifying investments and thinking long-term help achieve greater stability. Small steps today can lead to stronger results in the future.</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Diversifying investments and thinking long-term help achieve greater stability. • Small steps today can lead to stronger results in the future. • Money grows better over time, with balance and the right diversification.</t>
+          <t>Diversifying investments and thinking long-term help achieve greater stability. • Small steps today can lead to stronger results in the future. • Money grows better with time, balance, and the right diversification.</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Really struggling to get hold of @emiratesislamic. I’ve called the international line and emailed and really need to get in touch with someone. Please help.</t>
+          <t>Really struggling to get in touch with @emiratesislamic. I've called the international line and emailed, and I really need to reach someone. Please help.</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>I’ve called the international line and emailed and really need to get in touch with someone. • Really struggling to get hold of @emiratesislamic.</t>
+          <t>I've called the international line and emailed, and I really need to reach someone. • Really struggling to get in touch with @emiratesislamic.</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">

--- a/check2.xlsx
+++ b/check2.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL27"/>
+  <dimension ref="A1:AL31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,43 +625,43 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044612515498496366</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/DustshotW/status/2044612515498496366</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes</t>
+          <t>https://x.com/DustshotW</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LeaderOkkes</t>
+          <t>DustshotW</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN</t>
+          <t>justice gaming</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2035156091634380800/0oGW-_Z4_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2042550502014193664/yhlYRmG6_bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ÖKKEŞ ŞAHİN'S INTERNATIONAL RECIPE: POWER SOUP. YOU WILL BOIL ONE CARROT, ONE GREEN PEPPER, AND ONE RED ONION. YOU WILL EAT IT LIKE THIS FOR A WHILE. LATER, YOU CAN ADD MEAT, FISH, AND CHICKEN TO IT. @LeaderOkkes @RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X https://t.co/UBoi80xAg0</t>
+          <t>anyone.....olease ......</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>A MINHA SOPA DE PODER. MY POWER SOUP. I’M KING OF THE WORLD. &lt;a href="/LeaderOkkes" title="THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN"&gt;@LeaderOkkes&lt;/a&gt; &lt;a href="/airasia_indo" title="AirAsia Indonesia"&gt;@airasia_indo&lt;/a&gt; &lt;a href="/IAF_MCC" title="Indian Air Force"&gt;@IAF_MCC&lt;/a&gt; &lt;a href="/CebuPacificAir" title="Cebu Pacific Air"&gt;@CebuPacificAir&lt;/a&gt; &lt;a href="/airasia" title="AirAsia"&gt;@airasia&lt;/a&gt; &lt;a href="/usairforce" title="U.S. Air Force"&gt;@usairforce&lt;/a&gt; &lt;a href="/airtelindia" title="airtel India"&gt;@airtelindia&lt;/a&gt; &lt;a href="/British_Airways" title="British Airways"&gt;@British_Airways&lt;/a&gt; &lt;a href="/KenyaAirways" title="Official Kenya Airways"&gt;@KenyaAirways&lt;/a&gt; &lt;a href="/etihad" title="Etihad Airways"&gt;@etihad&lt;/a&gt; &lt;a href="/flysaa" title="SAA - South African Airways"&gt;@flysaa&lt;/a&gt; &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; &lt;a href="/emirates" title="Emirates"&gt;@emirates&lt;/a&gt; &lt;a href="/AmericanAir" title="americanair"&gt;@AmericanAir&lt;/a&gt; &lt;a href="/AirCanada" title="Air Canada"&gt;@AirCanada&lt;/a&gt; &lt;a href="/airserbia" title="Air Serbia"&gt;@airserbia&lt;/a&gt; &lt;a href="/SaudiAirlinesEn" title="Saudia"&gt;@SaudiAirlinesEn&lt;/a&gt; &lt;a href="/X" title="X"&gt;@X&lt;/a&gt;</t>
+          <t>s enbd</t>
         </is>
       </c>
       <c r="K2" t="b">
@@ -670,39 +670,35 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>['LeaderOkkes', 'RoyalFamily', 'MonarchieBe', 'koninklijkhuis', 'KensingtonRoyal', 'DefensieMin', 'FratellidItalia', 'GiorgiaMeloni', 'Pontifex', 'MarkJCarney', 'EmmanuelMacron', 'PrimeministerGR', 'netanyahu', 'LulaOficial', 'JMilei', 'Jaemyung_Lee', 'chrisluxonmp', 'ParmelinG', 'scotgov', 'SwissGov', 'lemondefr', 'TheEconomist', 'iaeaorg', 'wef', 'wto', 'IMFNews', 'WorldBankGroup', 'Davos', 'nikkei', 'NYSE', 'BentleyMotors', 'UniofOxford', 'LeaderOkkes']</t>
+          <t>['dorienotfish']</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>58m</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 7:22 PM UTC</t>
+          <t>Apr 16, 2026 · 3:03 AM UTC</t>
         </is>
       </c>
       <c r="P2" s="2" t="n">
-        <v>46126.80694444444</v>
+        <v>46128.12708333333</v>
       </c>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>['https://x.com/LeaderOkkes', 'https://x.com/airasia_indo', 'https://x.com/IAF_MCC', 'https://x.com/CebuPacificAir', 'https://x.com/airasia', 'https://x.com/usairforce', 'https://x.com/airtelindia', 'https://x.com/British_Airways', 'https://x.com/KenyaAirways', 'https://x.com/etihad', 'https://x.com/flysaa', 'https://x.com/EmiratesNBD_AE', 'https://x.com/emirates', 'https://x.com/AmericanAir', 'https://x.com/AirCanada', 'https://x.com/airserbia', 'https://x.com/SaudiAirlinesEn', 'https://x.com/X']</t>
-        </is>
-      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>94</v>
+        <v>14</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -711,27 +707,27 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>A MINHA SOPA DE PODER. MY POWER SOUP. I’M KING OF THE WORLD. @LeaderOkkes @airasia_indo @IAF_MCC @CebuPacificAir @airasia @usairforce @airtelindia @British_Airways @KenyaAirways @etihad @flysaa @EmiratesNBD_AE @emirates @AmericanAir @AirCanada @airserbia @SaudiAirlinesEn @X</t>
+          <t>s enbd</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/DustshotW/status/2044612515498496366</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>ÖKKEŞ ŞAHİN'S INTERNATIONAL RECIPE: POWER SOUP. YOU WILL BOIL ONE CARROT, ONE GREEN PEPPER, AND ONE RED ONION. YOU WILL EAT IT LIKE THIS FOR A WHILE. LATER, YOU CAN ADD MEAT, FISH, AND CHICKEN TO IT. @LeaderOkkes @RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X https://t.co/UBoi80xAg0</t>
+          <t>anyone.....olease ......</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>ÖKKEŞ ŞAHİN'S INTERNATIONAL RECIPE: POWER SOUP. YOU WILL BOIL ONE CARROT, ONE GREEN PEPPER, AND ONE RED ONION. YOU WILL EAT IT LIKE THIS FOR A WHILE. LATER, YOU CAN ADD MEAT, FISH, AND CHICKEN TO IT. @LeaderOkkes @RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X https://t.co/UBoi80xAg0</t>
+          <t>anyone.....olease ......</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Ökkeş Şahin's international recipe: power soup. You will boil one carrot, one green pepper, and one red onion. You will eat it like this for a while. Later, you can add meat, fish, and chicken to it.</t>
+          <t>anyone.....please ......</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -745,10 +741,10 @@
         </is>
       </c>
       <c r="AE2" s="2" t="n">
-        <v>46126.97361111111</v>
+        <v>46128.29375</v>
       </c>
       <c r="AF2" s="2" t="n">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
@@ -762,7 +758,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>You will boil one carrot, one green pepper, and one red onion. • Ökkeş Şahin's international recipe: power soup. • Later, you can add meat, fish, and chicken to it.</t>
+          <t>anyone.....please ......</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -775,7 +771,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>LeaderOkkes, RoyalFamily, MonarchieBe, koninklijkhuis, KensingtonRoyal, DefensieMin, FratellidItalia, GiorgiaMeloni, Pontifex, MarkJCarney, EmmanuelMacron, PrimeministerGR, netanyahu, LulaOficial, JMilei, Jaemyung_Lee, chrisluxonmp, ParmelinG, scotgov, SwissGov, lemondefr, TheEconomist, iaeaorg, wef, wto, IMFNews, WorldBankGroup, Davos, nikkei, NYSE, BentleyMotors, UniofOxford, LeaderOkkes</t>
+          <t>dorienotfish</t>
         </is>
       </c>
     </row>
@@ -785,47 +781,57 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2044132083443155222</t>
+          <t>2044611289733878057</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/metrixyo/status/2044132083443155222</t>
+          <t>https://x.com/BehindNums/status/2044611289733878057</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/metrixyo</t>
+          <t>https://x.com/BehindNums</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>metrixyo</t>
+          <t>BehindNums</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Metrix</t>
+          <t>BehindNums | Business &amp; Data</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1920369464379383808/skWlialk_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2025763865783345152/vXOr5RDQ_bigger.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>$QBTS 16% ⬆️ 
-$BE 21% ⬆️
-💵💵💵💵💵💵💵💵💵💵💵💵
-#qbts #quantum #dwave #Bloom #NASdaq #Nyse</t>
+          <t>Top 5 Companies by Revenue 
+By Revenue (annual)
+1️⃣ Walmart — ~$650B
+2️⃣ Amazon — ~$575B
+3️⃣ Saudi Aramco — ~$500B
+4️⃣ China State Grid — ~$480B
+5️⃣ Apple — ~$390B
+@BehindNums</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Pattern Day Trader (PDT) rule is soon going. No 25K USD limit for day trading : SEC
-&lt;a href="/search?f=tweets&amp;amp;q=%23WIO"&gt;#WIO&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23NASDAQ"&gt;#NASDAQ&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23ROBINHOOD"&gt;#ROBINHOOD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23ENBD"&gt;#ENBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23NYSE"&gt;#NYSE&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23IG"&gt;#IG&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23IBKR"&gt;#IBKR&lt;/a&gt;</t>
+          <t>Top 5 Richest Companies in the Middle East 
+1️⃣ Saudi Aramco — ~$1.5T+
+2️⃣ International Holding Co (UAE) — ~$240B+
+3️⃣ QNB (Qatar National Bank) — ~$150B+
+4️⃣ Al Rajhi Bank (Saudi) — ~$100B+
+5️⃣ Emirates NBD (UAE) — ~$80B+
+Oil wealth meets financial power.
+&lt;a href="/BehindNums" title="BehindNums | Business &amp;amp; Data"&gt;@BehindNums&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K3" t="b">
@@ -835,21 +841,21 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>1h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 7:14 PM UTC</t>
+          <t>Apr 16, 2026 · 2:58 AM UTC</t>
         </is>
       </c>
       <c r="P3" s="2" t="n">
-        <v>46126.80138888889</v>
+        <v>46128.12361111111</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23WIO', 'https://x.com/search?f=tweets&amp;q=%23NASDAQ', 'https://x.com/search?f=tweets&amp;q=%23ROBINHOOD', 'https://x.com/search?f=tweets&amp;q=%23ENBD', 'https://x.com/search?f=tweets&amp;q=%23NYSE', 'https://x.com/search?f=tweets&amp;q=%23IG', 'https://x.com/search?f=tweets&amp;q=%23IBKR']</t>
+          <t>['https://x.com/BehindNums']</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -862,7 +868,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>154</v>
+        <v>6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -871,37 +877,55 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Pattern Day Trader (PDT) rule is soon going. No 25K USD limit for day trading : SEC
-#WIO #NASDAQ #ROBINHOOD #ENBD #NYSE #IG #IBKR</t>
+          <t>Top 5 Richest Companies in the Middle East 
+1️⃣ Saudi Aramco — ~$1.5T+
+2️⃣ International Holding Co (UAE) — ~$240B+
+3️⃣ QNB (Qatar National Bank) — ~$150B+
+4️⃣ Al Rajhi Bank (Saudi) — ~$100B+
+5️⃣ Emirates NBD (UAE) — ~$80B+
+Oil wealth meets financial power.
+@BehindNums</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>https://x.com/metrixyo/status/2044132083443155222</t>
+          <t>https://x.com/BehindNums/status/2044611289733878057</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>$QBTS 16% ⬆️ 
-$BE 21% ⬆️
-💵💵💵💵💵💵💵💵💵💵💵💵
-#qbts #quantum #dwave #Bloom #NASdaq #Nyse</t>
+          <t>Top 5 Companies by Revenue 
+By Revenue (annual)
+1️⃣ Walmart — ~$650B
+2️⃣ Amazon — ~$575B
+3️⃣ Saudi Aramco — ~$500B
+4️⃣ China State Grid — ~$480B
+5️⃣ Apple — ~$390B
+@BehindNums</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>$QBTS 16% ⬆️ 
-$BE 21% ⬆️
-💵💵💵💵💵💵💵💵💵💵💵💵
-#qbts #quantum #dwave #Bloom #NASdaq #Nyse</t>
+          <t>Top 5 Companies by Revenue 
+By Revenue (annual)
+1️⃣ Walmart — ~$650B
+2️⃣ Amazon — ~$575B
+3️⃣ Saudi Aramco — ~$500B
+4️⃣ China State Grid — ~$480B
+5️⃣ Apple — ~$390B
+@BehindNums</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>$QBTS 16% up  
-$BE 21% up  
-💵💵💵💵💵💵💵💵💵💵💵💵  
-#qbts #quantum #dwave #Bloom #NASDAQ #NYSE</t>
+          <t>Top 5 Companies by Revenue
+By Revenue (annual)
+1️⃣ Walmart — ~$650B
+2️⃣ Amazon — ~$575B
+3️⃣ Saudi Aramco — ~$500B
+4️⃣ China State Grid — ~$480B
+5️⃣ Apple — ~$390B
+@BehindNums</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -915,10 +939,10 @@
         </is>
       </c>
       <c r="AE3" s="2" t="n">
-        <v>46126.96805555555</v>
+        <v>46128.29027777778</v>
       </c>
       <c r="AF3" s="2" t="n">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
@@ -932,7 +956,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>$QBTS 16% up $BE 21% up 💵💵💵💵💵💵💵💵💵💵💵💵 #qbts #quantum #dwave #Bloom #NASDAQ #NYSE</t>
+          <t>Top 5 Companies by Revenue By Revenue (annual) 1️⃣ Walmart — ~$650B 2️⃣ Amazon — ~$575B 3️⃣ Saudi Aramco — ~$500B 4️⃣ China State Grid — ~$480B 5️⃣ Apple — ~$390B @BehindNums</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -955,49 +979,44 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2044090446926823921</t>
+          <t>2044582261102956879</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/AlAjlansambrfi/status/2044090446926823921</t>
+          <t>https://x.com/zaydaklabhoqx/status/2044582261102956879</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/AlAjlansambrfi</t>
+          <t>https://x.com/zaydaklabhoqx</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AlAjlansambrfi</t>
+          <t>zaydaklabhoqx</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>طموح العجلان</t>
+          <t>زيد أكلب</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2034995732173004803/dk7uz4Ir_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2035350140782002176/Clcsao6J_bigger.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>جمهور جدة غير ومع الصقر غير🦅
-#رابح_صقر_في_جدة
-#موسم_جدة
-#روتانا_لايف
-@RabehSaqer 
-@JEDCalendar 
-@EmiratesNBD_KSA https://t.co/3mI6SdN1pE</t>
+          <t>🚨 JUST IN: 🇦🇪 EMIRATES NBD ELIMINATES ATM WITHDRAWAL &amp;amp; DEBIT CARD FEES ACROSS THE UAE &amp;amp; GCC UNTIL MARCH 31, 2026! 💳🔥
+#UAE #EmiratesNBD #Banking #Finance #ATM #NoFees #GCC #MoneySmart https://t.co/aI9H5crVgx</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>رائع، الجوهرة تتألق في جدة! 🦅</t>
+          <t>ماذا عن مجانيّة سحب النقود؟ مبروك لعملاء Emirates NBD في الإمارات ودول الخليج</t>
         </is>
       </c>
       <c r="K4" t="b">
@@ -1006,21 +1025,21 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>['RotanaLive', 'RabehSaqer', 'JEDCalendar', 'EmiratesNBD_KSA']</t>
+          <t>['CryptoNewsHntrs']</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>2h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 4:28 PM UTC</t>
+          <t>Apr 16, 2026 · 1:02 AM UTC</t>
         </is>
       </c>
       <c r="P4" s="2" t="n">
-        <v>46126.68611111111</v>
+        <v>46128.04305555556</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
@@ -1031,10 +1050,10 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -1043,39 +1062,29 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>رائع، الجوهرة تتألق في جدة! 🦅</t>
+          <t>ماذا عن مجانيّة سحب النقود؟ مبروك لعملاء Emirates NBD في الإمارات ودول الخليج</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>https://x.com/AlAjlansambrfi/status/2044090446926823921</t>
+          <t>https://x.com/zaydaklabhoqx/status/2044582261102956879</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>جمهور جدة غير ومع الصقر غير🦅
-#رابح_صقر_في_جدة
-#موسم_جدة
-#روتانا_لايف
-@RabehSaqer 
-@JEDCalendar 
-@EmiratesNBD_KSA https://t.co/3mI6SdN1pE</t>
+          <t>🚨 JUST IN: 🇦🇪 EMIRATES NBD ELIMINATES ATM WITHDRAWAL &amp;amp; DEBIT CARD FEES ACROSS THE UAE &amp;amp; GCC UNTIL MARCH 31, 2026! 💳🔥
+#UAE #EmiratesNBD #Banking #Finance #ATM #NoFees #GCC #MoneySmart https://t.co/aI9H5crVgx</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>جمهور جدة غير ومع الصقر غير🦅
-#رابح_صقر_في_جدة
-#موسم_جدة
-#روتانا_لايف
-@RabehSaqer 
-@JEDCalendar 
-@EmiratesNBD_KSA https://t.co/3mI6SdN1pE</t>
+          <t>🚨 JUST IN: 🇦🇪 EMIRATES NBD ELIMINATES ATM WITHDRAWAL &amp;amp; DEBIT CARD FEES ACROSS THE UAE &amp;amp; GCC UNTIL MARCH 31, 2026! 💳🔥
+#UAE #EmiratesNBD #Banking #Finance #ATM #NoFees #GCC #MoneySmart https://t.co/aI9H5crVgx</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>The audience in Jeddah is different, and with the falcon, it's different.</t>
+          <t>JUST IN: EMIRATES NBD ELIMINATES ATM WITHDRAWAL &amp; DEBIT CARD FEES ACROSS THE UAE &amp; GCC UNTIL MARCH 31, 2026!</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1085,14 +1094,14 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE4" s="2" t="n">
-        <v>46126.85277777778</v>
+        <v>46128.20972222222</v>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
@@ -1106,7 +1115,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>The audience in Jeddah is different, and with the falcon, it's different.</t>
+          <t>JUST IN: EMIRATES NBD ELIMINATES ATM WITHDRAWAL &amp; DEBIT CARD FEES ACROSS THE UAE &amp; GCC UNTIL MARCH 31, 2026!</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1119,7 +1128,7 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>RotanaLive, RabehSaqer, JEDCalendar, EmiratesNBD_KSA</t>
+          <t>CryptoNewsHntrs</t>
         </is>
       </c>
     </row>
@@ -1129,69 +1138,75 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2044082383205609853</t>
+          <t>2044433219693466085</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/SunnyLusty/status/2044082383205609853</t>
+          <t>https://x.com/STFU1346/status/2044433219693466085</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/SunnyLusty</t>
+          <t>https://x.com/STFU1346</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SunnyLusty</t>
+          <t>STFU1346</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>आदियोगी</t>
+          <t>BraveFart🏴󠁧󠁢󠁳󠁣󠁴󠁿</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1799284544987615232/-AKwVwdx_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1691103462870650880/Mk3r6EQC_bigger.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Is there any updates or changes regarding Installment deferment for the personal loan due to current geopolitical circumstances,</t>
+          <t>🚨 Mark Clattenburg on Lisandro Martínez’s red card:
+“I was surprised that such an experienced referee considered this a red card offence. It was clearly a 50/50 challenge for the ball. 
+I think the referee’s seniority within the VAR group may have made others hesitant to overturn his on-field decision.
+In my opinion, this was a clear mistake. When we talk about ‘clear and obvious errors’, most referees would not have sent him off for that challenge.”</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; Is there any updates or changes regarding Installment deferment for the personal loan due to current geopolitical circumstances,</t>
+          <t>PepsiCo: Noted for regional arrangements in the Middle East and Asia. 
+Emirates NBD for the United Arab Emirates.
+Saudi Telecom Co.
+So, what&amp;#39;s your point?</t>
         </is>
       </c>
       <c r="K5" t="b">
         <v>0</v>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>['STFU1346', 'Cle_Etc', 'JeetyJeeterson', 'Brockutd']</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>12h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 3:56 PM UTC</t>
+          <t>Apr 15, 2026 · 3:10 PM UTC</t>
         </is>
       </c>
       <c r="P5" s="2" t="n">
-        <v>46126.66388888889</v>
+        <v>46127.63194444445</v>
       </c>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
         <v>1</v>
       </c>
@@ -1202,7 +1217,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1211,27 +1226,39 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Is there any updates or changes regarding Installment deferment for the personal loan due to current geopolitical circumstances,</t>
+          <t>PepsiCo: Noted for regional arrangements in the Middle East and Asia. 
+Emirates NBD for the United Arab Emirates.
+Saudi Telecom Co.
+So, what's your point?</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>https://x.com/SunnyLusty/status/2044082383205609853</t>
+          <t>https://x.com/STFU1346/status/2044433219693466085</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Is there any updates or changes regarding Installment deferment for the personal loan due to current geopolitical circumstances,</t>
+          <t>🚨 Mark Clattenburg on Lisandro Martínez’s red card:
+“I was surprised that such an experienced referee considered this a red card offence. It was clearly a 50/50 challenge for the ball. 
+I think the referee’s seniority within the VAR group may have made others hesitant to overturn his on-field decision.
+In my opinion, this was a clear mistake. When we talk about ‘clear and obvious errors’, most referees would not have sent him off for that challenge.”</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Is there any updates or changes regarding Installment deferment for the personal loan due to current geopolitical circumstances,</t>
+          <t>🚨 Mark Clattenburg on Lisandro Martínez’s red card:
+“I was surprised that such an experienced referee considered this a red card offence. It was clearly a 50/50 challenge for the ball. 
+I think the referee’s seniority within the VAR group may have made others hesitant to overturn his on-field decision.
+In my opinion, this was a clear mistake. When we talk about ‘clear and obvious errors’, most referees would not have sent him off for that challenge.”</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Is there any updates or changes regarding installment deferment for the personal loan due to current geopolitical circumstances?</t>
+          <t>Mark Clattenburg on Lisandro Martínez’s red card:
+“I was surprised that such an experienced referee considered this a red card offence. It was clearly a 50/50 challenge for the ball.
+I think the referee’s seniority within the VAR group may have made others hesitant to overturn his on-field decision.
+In my opinion, this was a clear mistake. When we talk about ‘clear and obvious errors’, most referees would not have sent him off for that challenge.”</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1245,10 +1272,10 @@
         </is>
       </c>
       <c r="AE5" s="2" t="n">
-        <v>46126.83055555556</v>
+        <v>46127.79861111111</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
@@ -1262,7 +1289,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Is there any updates or changes regarding installment deferment for the personal loan due to current geopolitical circumstances?</t>
+          <t>Mark Clattenburg on Lisandro Martínez’s red card: “I was surprised that such an experienced referee considered this a red card offence. • I think the referee’s seniority within the VAR group may have made others hesitant to overturn his on-field decision. • When we talk about ‘clear and obvious errors’, most referees would not have sent him off for that challenge.”</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1275,7 +1302,7 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>STFU1346, Cle_Etc, JeetyJeeterson, Brockutd</t>
         </is>
       </c>
     </row>
@@ -1285,78 +1312,70 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2044082310447018168</t>
+          <t>2044430548727128554</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/ChirinAsadi/status/2044082310447018168</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2044430548727128554</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/ChirinAsadi</t>
+          <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ChirinAsadi</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chirin Al Asadi</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2035029628335923200/lkGmKuGp_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2042294543308242946/ScvMjarh_bigger.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>أعزائي ..
-السبب الوحيد للارتفاعات في الاسواق 
-هو دخول سيولة قوية ( بغض النظر عن الآلية) 
-تتزامن مع نتائج الشركات
-وهي الفترة التي لا يفوتها السوق أبداً
-لا في سراء ولا في ضراء 
-عُدْ إلي بعد أسبوعين،
-حتى نتحدث عن " زلزال المنطق "
-أضف الى ذلك .. أنا بِنْت ☹️</t>
+          <t>We are together against Fraud. @UAEBF #FightFraud #UAEBF #togetheragainstfraud #UnitedAgainstFraud https://t.co/CqApZaCAFO</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>اعتقد بنك دبي الامارات الوطني ENBD استفاد من اللخبطة التي حصلت في مارس
-بينما كان دبي الاسلامي DIB محافظاً في الانتقاء</t>
+          <t>Manage your wealth with expertise you can trust. Contact us today &lt;a href="https://www.emiratesnbd.com/en/priority-banking/wealth-management-solutions"&gt;emiratesnbd.com/en/priority-…&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23WealthManagement"&gt;#WealthManagement&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K6" t="b">
         <v>0</v>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>['alnuaimi_bader']</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 3:56 PM UTC</t>
+          <t>Apr 15, 2026 · 3:00 PM UTC</t>
         </is>
       </c>
       <c r="P6" s="2" t="n">
-        <v>46126.66388888889</v>
+        <v>46127.625</v>
       </c>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesnbd.com/en/priority-banking/wealth-management-solutions', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23WealthManagement']</t>
+        </is>
+      </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
@@ -1364,10 +1383,10 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V6" t="n">
-        <v>90</v>
+        <v>1284</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1376,52 +1395,33 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>اعتقد بنك دبي الامارات الوطني ENBD استفاد من اللخبطة التي حصلت في مارس
-بينما كان دبي الاسلامي DIB محافظاً في الانتقاء</t>
+          <t>Manage your wealth with expertise you can trust. Contact us today emiratesnbd.com/en/priority-…
+#EmiratesNBD #WealthManagement</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>https://x.com/ChirinAsadi/status/2044082310447018168</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2044430548727128554</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>أعزائي ..
-السبب الوحيد للارتفاعات في الاسواق 
-هو دخول سيولة قوية ( بغض النظر عن الآلية) 
-تتزامن مع نتائج الشركات
-وهي الفترة التي لا يفوتها السوق أبداً
-لا في سراء ولا في ضراء 
-عُدْ إلي بعد أسبوعين،
-حتى نتحدث عن " زلزال المنطق "
-أضف الى ذلك .. أنا بِنْت ☹️</t>
+          <t>We are together against Fraud. @UAEBF #FightFraud #UAEBF #togetheragainstfraud #UnitedAgainstFraud https://t.co/CqApZaCAFO</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>أعزائي ..
-السبب الوحيد للارتفاعات في الاسواق 
-هو دخول سيولة قوية ( بغض النظر عن الآلية) 
-تتزامن مع نتائج الشركات
-وهي الفترة التي لا يفوتها السوق أبداً
-لا في سراء ولا في ضراء 
-عُدْ إلي بعد أسبوعين،
-حتى نتحدث عن " زلزال المنطق "
-أضف الى ذلك .. أنا بِنْت ☹️</t>
+          <t>We are together against Fraud. @UAEBF #FightFraud #UAEBF #togetheragainstfraud #UnitedAgainstFraud https://t.co/CqApZaCAFO</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Dear all,  
-The only reason for the rises in the markets is the influx of strong liquidity (regardless of the mechanism) coinciding with company results, which is a period that the market never misses, neither in good times nor in bad.  
-Come back to me in two weeks, so we can talk about the "earthquake of logic."  
-On top of that, I am a girl. ☹️</t>
+          <t>We are together against Fraud.</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Cust</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -1430,10 +1430,10 @@
         </is>
       </c>
       <c r="AE6" s="2" t="n">
-        <v>46126.83055555556</v>
+        <v>46127.79166666666</v>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Come back to me in two weeks, so we can talk about the "earthquake of logic." On top of that, I am a girl.</t>
+          <t>We are together against Fraud.</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>alnuaimi_bader</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1470,72 +1470,79 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2044078376982319373</t>
+          <t>2044410083262734349</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044078376982319373</t>
+          <t>https://x.com/ibmag_magazine/status/2044410083262734349</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010</t>
+          <t>https://x.com/ibmag_magazine</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>attas_2010</t>
+          <t>ibmag_magazine</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>محمد</t>
+          <t>International Business Magazine</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1581396792075247620/ZCrbkCda_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1017739481749655553/2mtvJ3Sb_bigger.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>سؤال:
-ماهو افضل بنك يشتري مديونية ؟!
-قرض عقاري + قرض شخصي .
-@alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE</t>
+          <t>To find the trending news on Corporate, Technology, Banking and Finance for #April14, check the links below:
+https://t.co/wCnnEeLf7A
+https://t.co/5jczPIqAT3
+https://t.co/X0IupL4wiw
+https://t.co/amPUbrkpdI
+#Intlbm #telecoms #Investment #MiddleEast #Banking #Finance #Innovation</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>فوق ١٠ مرات ارفع شكاوي هذا الرد</t>
+          <t>To find the trending news on Real estate, finance, and Technology for April 15, check the news links and the video link below:
+&lt;a href="https://tinyurl.com/4f7v9hen"&gt;tinyurl.com/4f7v9hen&lt;/a&gt;
+&lt;a href="https://tinyurl.com/2s3e7u9d"&gt;tinyurl.com/2s3e7u9d&lt;/a&gt;
+&lt;a href="https://tinyurl.com/mt35nuky"&gt;tinyurl.com/mt35nuky&lt;/a&gt;
+&lt;a href="https://tinyurl.com/55cdu3ep"&gt;tinyurl.com/55cdu3ep&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23INTLBM"&gt;#INTLBM&lt;/a&gt;  &lt;a href="/search?f=tweets&amp;amp;q=%23Sohar"&gt;#Sohar&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EToro"&gt;#EToro&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Sobha"&gt;#Sobha&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Headlines"&gt;#Headlines&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K7" t="b">
         <v>0</v>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>['attas_2010', 'KhalidSaeedR', 'amsh75', 'alrajhibank', 'BSF_sa', 'alinma', 'BankAlbilad', 'snbalahli', 'GulfIntlBank', 'EmiratesNBD_AE', 'BankAlJazira', 'RiyadBank', 'alawwalsab', 'SAIBLIVE']</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 3:40 PM UTC</t>
+          <t>Apr 15, 2026 · 1:38 PM UTC</t>
         </is>
       </c>
       <c r="P7" s="2" t="n">
-        <v>46126.65277777778</v>
+        <v>46127.56805555556</v>
       </c>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>['https://tinyurl.com/4f7v9hen', 'https://tinyurl.com/2s3e7u9d', 'https://tinyurl.com/mt35nuky', 'https://tinyurl.com/55cdu3ep', 'https://x.com/search?f=tweets&amp;q=%23INTLBM', 'https://x.com/search?f=tweets&amp;q=%23Sohar', 'https://x.com/search?f=tweets&amp;q=%23EToro', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23Sobha', 'https://x.com/search?f=tweets&amp;q=%23Headlines']</t>
+        </is>
+      </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
@@ -1543,10 +1550,10 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1555,35 +1562,42 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>فوق ١٠ مرات ارفع شكاوي هذا الرد</t>
+          <t>To find the trending news on Real estate, finance, and Technology for April 15, check the news links and the video link below:
+tinyurl.com/4f7v9hen
+tinyurl.com/2s3e7u9d
+tinyurl.com/mt35nuky
+tinyurl.com/55cdu3ep
+#INTLBM  #Sohar #EToro #EmiratesNBD #Sobha #Headlines</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044078376982319373</t>
+          <t>https://x.com/ibmag_magazine/status/2044410083262734349</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>سؤال:
-ماهو افضل بنك يشتري مديونية ؟!
-قرض عقاري + قرض شخصي .
-@alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE</t>
+          <t>To find the trending news on Corporate, Technology, Banking and Finance for #April14, check the links below:
+https://t.co/wCnnEeLf7A
+https://t.co/5jczPIqAT3
+https://t.co/X0IupL4wiw
+https://t.co/amPUbrkpdI
+#Intlbm #telecoms #Investment #MiddleEast #Banking #Finance #Innovation</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>سؤال:
-ماهو افضل بنك يشتري مديونية ؟!
-قرض عقاري + قرض شخصي .
-@alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE</t>
+          <t>To find the trending news on Corporate, Technology, Banking and Finance for #April14, check the links below:
+https://t.co/wCnnEeLf7A
+https://t.co/5jczPIqAT3
+https://t.co/X0IupL4wiw
+https://t.co/amPUbrkpdI
+#Intlbm #telecoms #Investment #MiddleEast #Banking #Finance #Innovation</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Question:
-What is the best bank to buy a debt?! 
-Mortgage loan + personal loan.</t>
+          <t>To find the trending news on Corporate, Technology, Banking, and Finance for April 14, check the links below:</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1597,10 +1611,10 @@
         </is>
       </c>
       <c r="AE7" s="2" t="n">
-        <v>46126.81944444445</v>
+        <v>46127.73472222222</v>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
@@ -1614,7 +1628,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Question: What is the best bank to buy a debt?! • Mortgage loan + personal loan.</t>
+          <t>To find the trending news on Corporate, Technology, Banking, and Finance for April 14, check the links below:</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1627,7 +1641,7 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>attas_2010, KhalidSaeedR, amsh75, alrajhibank, BSF_sa, alinma, BankAlbilad, snbalahli, GulfIntlBank, EmiratesNBD_AE, BankAlJazira, RiyadBank, alawwalsab, SAIBLIVE</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1637,73 +1651,75 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2044075725334954107</t>
+          <t>2044390258528395378</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044075725334954107</t>
+          <t>https://x.com/Gulf_const/status/2044390258528395378</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010</t>
+          <t>https://x.com/Gulf_const</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>attas_2010</t>
+          <t>Gulf_const</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>محمد</t>
+          <t>Gulf Construction</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1581396792075247620/ZCrbkCda_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/3497523518/ff8c5dd3c169b9bb1240a76dd5f61a37_bigger.jpeg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>عميلنا العزيز ، نود التوضيح بأن منصات التواصل الاجتماعي مخصصة للاستفسارات العامة فقط.
-ولضمان خصوصيتكم وحماية بياناتكم، نرجو عدم مشاركة أي معلومات شخصية أو مصرفية (مثل رقم الهوية، رقم الحساب، كلمة المرور، رقم الجوال أو الأرقام السرية) عبر هذه المنصات.
-يرجى استخدام البريد الإلكتروني أو القنوات الرسمية للبنك لمعالجة الطلبات بأمان وسرية تامة.</t>
+          <t>Mered, the award-winning developer based in UAE, has announced that main piling operations are now progressing at Riviera Residences, a waterfront residential tower in Abu Dhabi, Al Reem Island.
+Read more on https://t.co/xGW6cvJ1Nc
+#GCnews #developer #UAE #residences https://t.co/bFrmFMn6HS</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>والله من خلال تجربتي مع البنك السعودي الفرنسي لا انصح ابدا بشراء مديونية منه اتفقت مع الموظف على اعادة تمويل وكنت في بنك الرياض علي قرض شخصي وعقاري اتفقت مع الموظف بعد ماشاف راتبي والعقار المرهون لبنك الرياض قيمته ٣ مليون  قدروه عمارة ٢٥ شقة المهم موظف البنك الفرنسي</t>
+          <t>Emirates NBD has announced a strategic partnership with Sobha Realty to provide integrated home financing solutions for buyers of the premium luxury developer’s off-plan residential developments across Dubai.
+Read more on &lt;a href="https://gulfconstructiononline.com/ArticleTA/414024"&gt;gulfconstructiononline.com/A…&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23GCnews"&gt;#GCnews&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23emirates"&gt;#emirates&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23MENA"&gt;#MENA&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K8" t="b">
         <v>0</v>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>['KhalidSaeedR', 'amsh75', 'alrajhibank', 'BSF_sa', 'alinma', 'BankAlbilad', 'snbalahli', 'GulfIntlBank', 'EmiratesNBD_AE', 'BankAlJazira', 'RiyadBank', 'alawwalsab', 'SAIBLIVE']</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 3:30 PM UTC</t>
+          <t>Apr 15, 2026 · 12:19 PM UTC</t>
         </is>
       </c>
       <c r="P8" s="2" t="n">
-        <v>46126.64583333334</v>
+        <v>46127.51319444444</v>
       </c>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>['https://gulfconstructiononline.com/ArticleTA/414024', 'https://x.com/search?f=tweets&amp;q=%23GCnews', 'https://x.com/search?f=tweets&amp;q=%23emirates', 'https://x.com/search?f=tweets&amp;q=%23MENA']</t>
+        </is>
+      </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1712,7 +1728,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>135</v>
+        <v>22</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1721,31 +1737,33 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>والله من خلال تجربتي مع البنك السعودي الفرنسي لا انصح ابدا بشراء مديونية منه اتفقت مع الموظف على اعادة تمويل وكنت في بنك الرياض علي قرض شخصي وعقاري اتفقت مع الموظف بعد ماشاف راتبي والعقار المرهون لبنك الرياض قيمته ٣ مليون  قدروه عمارة ٢٥ شقة المهم موظف البنك الفرنسي</t>
+          <t>Emirates NBD has announced a strategic partnership with Sobha Realty to provide integrated home financing solutions for buyers of the premium luxury developer’s off-plan residential developments across Dubai.
+Read more on gulfconstructiononline.com/A…
+#GCnews #emirates #MENA</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044075725334954107</t>
+          <t>https://x.com/Gulf_const/status/2044390258528395378</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>عميلنا العزيز ، نود التوضيح بأن منصات التواصل الاجتماعي مخصصة للاستفسارات العامة فقط.
-ولضمان خصوصيتكم وحماية بياناتكم، نرجو عدم مشاركة أي معلومات شخصية أو مصرفية (مثل رقم الهوية، رقم الحساب، كلمة المرور، رقم الجوال أو الأرقام السرية) عبر هذه المنصات.
-يرجى استخدام البريد الإلكتروني أو القنوات الرسمية للبنك لمعالجة الطلبات بأمان وسرية تامة.</t>
+          <t>Mered, the award-winning developer based in UAE, has announced that main piling operations are now progressing at Riviera Residences, a waterfront residential tower in Abu Dhabi, Al Reem Island.
+Read more on https://t.co/xGW6cvJ1Nc
+#GCnews #developer #UAE #residences https://t.co/bFrmFMn6HS</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>عميلنا العزيز ، نود التوضيح بأن منصات التواصل الاجتماعي مخصصة للاستفسارات العامة فقط.
-ولضمان خصوصيتكم وحماية بياناتكم، نرجو عدم مشاركة أي معلومات شخصية أو مصرفية (مثل رقم الهوية، رقم الحساب، كلمة المرور، رقم الجوال أو الأرقام السرية) عبر هذه المنصات.
-يرجى استخدام البريد الإلكتروني أو القنوات الرسمية للبنك لمعالجة الطلبات بأمان وسرية تامة.</t>
+          <t>Mered, the award-winning developer based in UAE, has announced that main piling operations are now progressing at Riviera Residences, a waterfront residential tower in Abu Dhabi, Al Reem Island.
+Read more on https://t.co/xGW6cvJ1Nc
+#GCnews #developer #UAE #residences https://t.co/bFrmFMn6HS</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Dear valued customer, we would like to clarify that social media platforms are intended for general inquiries only. To ensure your privacy and protect your data, please do not share any personal or banking information (such as ID number, account number, password, mobile number, or PINs) through these platforms. Please use email or the bank's official channels to process requests securely and confidentially.</t>
+          <t>Mered, the award-winning developer based in the UAE, has announced that main piling operations are now progressing at Riviera Residences, a waterfront residential tower in Abu Dhabi, Al Reem Island.</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1759,10 +1777,10 @@
         </is>
       </c>
       <c r="AE8" s="2" t="n">
-        <v>46126.8125</v>
+        <v>46127.67986111111</v>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
@@ -1776,7 +1794,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>To ensure your privacy and protect your data, please do not share any personal or banking information (such as ID number, account number, password, mobile number, or PINs) through these platforms. • Dear valued customer, we would like to clarify that social media platforms are intended for general inquiries only. • Please use email or the bank's official channels to process requests securely and confidentially.</t>
+          <t>Mered, the award-winning developer based in the UAE, has announced that main piling operations are now progressing at Riviera Residences, a waterfront residential tower in Abu Dhabi, Al Reem Island.</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1789,7 +1807,7 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>KhalidSaeedR, amsh75, alrajhibank, BSF_sa, alinma, BankAlbilad, snbalahli, GulfIntlBank, EmiratesNBD_AE, BankAlJazira, RiyadBank, alawwalsab, SAIBLIVE</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1799,47 +1817,49 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2044047297034760542</t>
+          <t>2044377290952364098</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://x.com/biztoday_intl/status/2044047297034760542</t>
+          <t>https://x.com/khir_llnas/status/2044377290952364098</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://x.com/biztoday_intl</t>
+          <t>https://x.com/khir_llnas</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>biztoday_intl</t>
+          <t>khir_llnas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Biz Today Intl</t>
+          <t>خير للناس للتنمية</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/948095006644097024/ns0iZtDe_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1823295456106930177/7M4AerkA_bigger.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE and @SobhaRealtyDXB partner to offer integrated home financing solutions for off-plan projects in #Dubai .
-#EmiratesNBD #SobhaRealty #UAE #Dubairealestate #realestate
-https://t.co/ukweMYki3P</t>
+          <t>شكرا Emirates NBD بنك الإمارات دبي الوطني
+على دعمكم الإنساني في نجاح أنشطة المؤسسة لدعم الأسر المحتاجة..
+#متبرعين_خير_للناس
+#مؤسسة_خير_للناس https://t.co/5PUxmmX1mn</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; and &lt;a href="/SobhaRealtyDXB" title="Sobha Realty"&gt;@SobhaRealtyDXB&lt;/a&gt; partner to offer integrated home financing solutions for off-plan projects in &lt;a href="/search?f=tweets&amp;amp;q=%23Dubai"&gt;#Dubai&lt;/a&gt; .
-&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SobhaRealty"&gt;#SobhaRealty&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Dubairealestate"&gt;#Dubairealestate&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23realestate"&gt;#realestate&lt;/a&gt;
-&lt;a href="https://www.biztoday.news/2026/04/14/emirates-nbd-and-sobha-realty-partner-to-offer-integrated-home-financing-solutions-for-off-plan-projects-in-dubai/"&gt;biztoday.news/2026/04/14/emi…&lt;/a&gt;</t>
+          <t>شكرا Emirates NBD بنك الإمارات دبي الوطني
+على دعمكم الإنساني في نجاح أنشطة المؤسسة لدعم الأسر المحتاجة..
+&lt;a href="/search?f=tweets&amp;amp;q=%23متبرعين_خير_للناس"&gt;#متبرعين_خير_للناس&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23مؤسسة_خير_للناس"&gt;#مؤسسة_خير_للناس&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K9" t="b">
@@ -1849,34 +1869,34 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 1:37 PM UTC</t>
+          <t>Apr 15, 2026 · 11:28 AM UTC</t>
         </is>
       </c>
       <c r="P9" s="2" t="n">
-        <v>46126.56736111111</v>
+        <v>46127.47777777778</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>['https://x.com/EmiratesNBD_AE', 'https://x.com/SobhaRealtyDXB', 'https://x.com/search?f=tweets&amp;q=%23Dubai', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23SobhaRealty', 'https://x.com/search?f=tweets&amp;q=%23UAE', 'https://x.com/search?f=tweets&amp;q=%23Dubairealestate', 'https://x.com/search?f=tweets&amp;q=%23realestate', 'https://www.biztoday.news/2026/04/14/emirates-nbd-and-sobha-realty-partner-to-offer-integrated-home-financing-solutions-for-off-plan-projects-in-dubai/']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23متبرعين_خير_للناس', 'https://x.com/search?f=tweets&amp;q=%23مؤسسة_خير_للناس']</t>
         </is>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1885,33 +1905,36 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE and @SobhaRealtyDXB partner to offer integrated home financing solutions for off-plan projects in #Dubai .
-#EmiratesNBD #SobhaRealty #UAE #Dubairealestate #realestate
-biztoday.news/2026/04/14/emi…</t>
+          <t>شكرا Emirates NBD بنك الإمارات دبي الوطني
+على دعمكم الإنساني في نجاح أنشطة المؤسسة لدعم الأسر المحتاجة..
+#متبرعين_خير_للناس
+#مؤسسة_خير_للناس</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>https://x.com/biztoday_intl/status/2044047297034760542</t>
+          <t>https://x.com/khir_llnas/status/2044377290952364098</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE and @SobhaRealtyDXB partner to offer integrated home financing solutions for off-plan projects in #Dubai .
-#EmiratesNBD #SobhaRealty #UAE #Dubairealestate #realestate
-https://t.co/ukweMYki3P</t>
+          <t>شكرا Emirates NBD بنك الإمارات دبي الوطني
+على دعمكم الإنساني في نجاح أنشطة المؤسسة لدعم الأسر المحتاجة..
+#متبرعين_خير_للناس
+#مؤسسة_خير_للناس https://t.co/5PUxmmX1mn</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE and @SobhaRealtyDXB partner to offer integrated home financing solutions for off-plan projects in #Dubai .
-#EmiratesNBD #SobhaRealty #UAE #Dubairealestate #realestate
-https://t.co/ukweMYki3P</t>
+          <t>شكرا Emirates NBD بنك الإمارات دبي الوطني
+على دعمكم الإنساني في نجاح أنشطة المؤسسة لدعم الأسر المحتاجة..
+#متبرعين_خير_للناس
+#مؤسسة_خير_للناس https://t.co/5PUxmmX1mn</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Emirates NBD and Sobha Realty partner to offer integrated home financing solutions for off-plan projects in Dubai.</t>
+          <t>Thank you Emirates NBD for your humanitarian support in the success of the organization's activities to support needy families.</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1925,10 +1948,10 @@
         </is>
       </c>
       <c r="AE9" s="2" t="n">
-        <v>46126.73402777778</v>
+        <v>46127.64444444444</v>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
@@ -1942,7 +1965,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Emirates NBD and Sobha Realty partner to offer integrated home financing solutions for off-plan projects in Dubai.</t>
+          <t>Thank you Emirates NBD for your humanitarian support in the success of the organization's activities to support needy families.</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1965,84 +1988,69 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2044043515546800261</t>
+          <t>2044363346460172688</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://x.com/Net_eqtisad/status/2044043515546800261</t>
+          <t>https://x.com/Sems3499/status/2044363346460172688</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://x.com/Net_eqtisad</t>
+          <t>https://x.com/Sems3499</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Net_eqtisad</t>
+          <t>Sems3499</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>الشبكة الاقتصادية</t>
+          <t>Sem</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1892643729745317888/Zh1HkNvX_bigger.jpg</t>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>التقى سمو الشيخ خالد بن محمد بن زايد آل نهيان قادة شركات صينية، في إطار تعزيز الشراكة الاستراتيجية بين البلدين.
-📌 ركزت اللقاءات على استكشاف فرص جديدة للتعاون الاقتصادي والتنموي، بما يدعم توسيع الاستثمارات وتعزيز العلاقات الثنائية.
-#الإمارات #الصين #الاستثمار #الاقتصاد #الشبكة_الاقتصادية</t>
+          <t>@nurkanaydogan Enbd bankalarında çalışanlar için 1. Şık olduğunu düşünüyorum (:</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>القيمة السوقية لأكبر 10 شركات عامة في الإمارات تبلغ 692.3 مليار دولار في 2026، تتصدرها &amp;#34;الشركة العالمية القابضة&amp;#34; مستحوذة وحدها على نحو 34% من إجمالي القيمة السوقية.
-&lt;a href="/ihc__official" title="IHC"&gt;@ihc__official&lt;/a&gt;
-&lt;a href="/TAQAGroup" title="TAQA"&gt;@TAQAGroup&lt;/a&gt;
-&lt;a href="/ADNOCGas" title="ADNOC Gas"&gt;@ADNOCGas&lt;/a&gt;
-&lt;a href="/FABConnects" title="FAB Connects"&gt;@FABConnects&lt;/a&gt;
-&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;
-&lt;a href="/eAndUAE" title="e&amp;amp; UAE"&gt;@eAndUAE&lt;/a&gt;
-&lt;a href="/DEWAOfficial" title="DEWA | Official Page"&gt;@DEWAOfficial&lt;/a&gt;
-&lt;a href="/emaardubai" title="Emaar Dubai"&gt;@emaardubai&lt;/a&gt;
-&lt;a href="/OfficialADCB" title="ADCB بنك أبوظبي التجاري"&gt;@OfficialADCB&lt;/a&gt;
-&lt;a href="/adhuae" title="Moon"&gt;@adhuae&lt;/a&gt;
-&lt;a href="/ADX_AE" title="سوق أبوظبي للأوراق المالية"&gt;@ADX_AE&lt;/a&gt;
-&lt;a href="/DFMalerts" title="Dubai Financial Market"&gt;@DFMalerts&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات"&gt;#الإمارات&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23أدنوك"&gt;#أدنوك&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الطاقة"&gt;#الطاقة&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23IHC"&gt;#IHC&lt;/a&gt;  &lt;a href="/search?f=tweets&amp;amp;q=%23الشبكة_الاقتصادية"&gt;#الشبكة_الاقتصادية&lt;/a&gt;</t>
+          <t>Enbd bankalarında çalışanlar için 1. Şık olduğunu düşünüyorum (:</t>
         </is>
       </c>
       <c r="K10" t="b">
         <v>0</v>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>['nurkanaydogan']</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 1:22 PM UTC</t>
+          <t>Apr 15, 2026 · 10:32 AM UTC</t>
         </is>
       </c>
       <c r="P10" s="2" t="n">
-        <v>46126.55694444444</v>
+        <v>46127.43888888889</v>
       </c>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>['https://x.com/ihc__official', 'https://x.com/TAQAGroup', 'https://x.com/ADNOCGas', 'https://x.com/FABConnects', 'https://x.com/EmiratesNBD_AE', 'https://x.com/eAndUAE', 'https://x.com/DEWAOfficial', 'https://x.com/emaardubai', 'https://x.com/OfficialADCB', 'https://x.com/adhuae', 'https://x.com/ADX_AE', 'https://x.com/DFMalerts', 'https://x.com/search?f=tweets&amp;q=%23الإمارات', 'https://x.com/search?f=tweets&amp;q=%23أدنوك', 'https://x.com/search?f=tweets&amp;q=%23الطاقة', 'https://x.com/search?f=tweets&amp;q=%23IHC', 'https://x.com/search?f=tweets&amp;q=%23الشبكة_الاقتصادية']</t>
-        </is>
-      </c>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
         <v>0</v>
       </c>
@@ -2050,10 +2058,10 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -2062,45 +2070,27 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>القيمة السوقية لأكبر 10 شركات عامة في الإمارات تبلغ 692.3 مليار دولار في 2026، تتصدرها "الشركة العالمية القابضة" مستحوذة وحدها على نحو 34% من إجمالي القيمة السوقية.
-@ihc__official
-@TAQAGroup
-@ADNOCGas
-@FABConnects
-@EmiratesNBD_AE
-@eAndUAE
-@DEWAOfficial
-@emaardubai
-@OfficialADCB
-@adhuae
-@ADX_AE
-@DFMalerts
-#الإمارات #أدنوك #الطاقة #IHC  #الشبكة_الاقتصادية</t>
+          <t>Enbd bankalarında çalışanlar için 1. Şık olduğunu düşünüyorum (:</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>https://x.com/Net_eqtisad/status/2044043515546800261</t>
+          <t>https://x.com/Sems3499/status/2044363346460172688</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>التقى سمو الشيخ خالد بن محمد بن زايد آل نهيان قادة شركات صينية، في إطار تعزيز الشراكة الاستراتيجية بين البلدين.
-📌 ركزت اللقاءات على استكشاف فرص جديدة للتعاون الاقتصادي والتنموي، بما يدعم توسيع الاستثمارات وتعزيز العلاقات الثنائية.
-#الإمارات #الصين #الاستثمار #الاقتصاد #الشبكة_الاقتصادية</t>
+          <t>@nurkanaydogan Enbd bankalarında çalışanlar için 1. Şık olduğunu düşünüyorum (:</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>التقى سمو الشيخ خالد بن محمد بن زايد آل نهيان قادة شركات صينية، في إطار تعزيز الشراكة الاستراتيجية بين البلدين.
-📌 ركزت اللقاءات على استكشاف فرص جديدة للتعاون الاقتصادي والتنموي، بما يدعم توسيع الاستثمارات وتعزيز العلاقات الثنائية.
-#الإمارات #الصين #الاستثمار #الاقتصاد #الشبكة_الاقتصادية</t>
+          <t>@nurkanaydogan Enbd bankalarında çalışanlar için 1. Şık olduğunu düşünüyorum (:</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>His Highness Sheikh Khalid bin Mohammed bin Zayed Al Nahyan met with leaders of Chinese companies as part of enhancing the strategic partnership between the two countries. 
-The meetings focused on exploring new opportunities for economic and developmental cooperation, supporting the expansion of investments and strengthening bilateral relations.</t>
+          <t>I think it's stylish for employees working at Enbd banks.</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -2110,14 +2100,14 @@
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE10" s="2" t="n">
-        <v>46126.72361111111</v>
+        <v>46127.60555555556</v>
       </c>
       <c r="AF10" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
@@ -2131,7 +2121,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>His Highness Sheikh Khalid bin Mohammed bin Zayed Al Nahyan met with leaders of Chinese companies as part of enhancing the strategic partnership between the two countries. • The meetings focused on exploring new opportunities for economic and developmental cooperation, supporting the expansion of investments and strengthening bilateral relations.</t>
+          <t>I think it's stylish for employees working at Enbd banks.</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -2144,7 +2134,7 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>nurkanaydogan</t>
         </is>
       </c>
     </row>
@@ -2154,43 +2144,46 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2044025847523487886</t>
+          <t>2044351837869105398</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2044025847523487886</t>
+          <t>https://x.com/titledeednews/status/2044351837869105398</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide</t>
+          <t>https://x.com/titledeednews</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>dcgguide</t>
+          <t>titledeednews</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>DUBAI CITY GUIDE from Cyber Gear</t>
+          <t>The Title Deed</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1780203891230945280/ODQLZiT__bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2032863974820294659/y_r3-sNy_bigger.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Emirates NBD And Sobha Realty Partner To Offer Integrated Home Financing Solutions For Off-Plan Projects In Dubai https://t.co/fVBST6NQ7A</t>
+          <t>Al Habtoor Group is committing over AED 5 billion to a new commercial tower in Dubai. Another strong indicator of sustained demand for Grade A office space and long-term market confidence.
+#DubaiRealEstate #CommercialRealEstate #InvestInDubai #DubaiBrokers #RealEstateNews https://t.co/kHUr6Xe7wr</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Emirates NBD And Sobha Realty Partner To Offer Integrated Home Financing Solutions For Off-Plan Projects In Dubai &lt;a href="https://dubaipropertyguide.io/emirates-nbd-and-sobha-realty-partner-to-offer-integrated-home-financing-solutions-for-off-plan-projects-in-dubai-2/"&gt;dubaipropertyguide.io/emirat…&lt;/a&gt;</t>
+          <t>Sobha Realty is making off-plan investing in Dubai more accessible.
+In partnership with Emirates NBD, Sobha Realty introduces flexible financing solutions, giving investors easier access to high-potential opportunities.
+&lt;a href="/search?f=tweets&amp;amp;q=%23DubaiInvestors"&gt;#DubaiInvestors&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23OffPlanDubai"&gt;#OffPlanDubai&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23RealEstateInvesting"&gt;#RealEstateInvesting&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Dubai"&gt;#Dubai&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K11" t="b">
@@ -2200,34 +2193,34 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 12:11 PM UTC</t>
+          <t>Apr 15, 2026 · 9:47 AM UTC</t>
         </is>
       </c>
       <c r="P11" s="2" t="n">
-        <v>46126.50763888889</v>
+        <v>46127.40763888889</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>['https://dubaipropertyguide.io/emirates-nbd-and-sobha-realty-partner-to-offer-integrated-home-financing-solutions-for-off-plan-projects-in-dubai-2/']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23DubaiInvestors', 'https://x.com/search?f=tweets&amp;q=%23OffPlanDubai', 'https://x.com/search?f=tweets&amp;q=%23RealEstateInvesting', 'https://x.com/search?f=tweets&amp;q=%23Dubai']</t>
         </is>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -2236,27 +2229,31 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Emirates NBD And Sobha Realty Partner To Offer Integrated Home Financing Solutions For Off-Plan Projects In Dubai dubaipropertyguide.io/emirat…</t>
+          <t>Sobha Realty is making off-plan investing in Dubai more accessible.
+In partnership with Emirates NBD, Sobha Realty introduces flexible financing solutions, giving investors easier access to high-potential opportunities.
+#DubaiInvestors #OffPlanDubai #RealEstateInvesting #Dubai</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2044025847523487886</t>
+          <t>https://x.com/titledeednews/status/2044351837869105398</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>Emirates NBD And Sobha Realty Partner To Offer Integrated Home Financing Solutions For Off-Plan Projects In Dubai https://t.co/fVBST6NQ7A</t>
+          <t>Al Habtoor Group is committing over AED 5 billion to a new commercial tower in Dubai. Another strong indicator of sustained demand for Grade A office space and long-term market confidence.
+#DubaiRealEstate #CommercialRealEstate #InvestInDubai #DubaiBrokers #RealEstateNews https://t.co/kHUr6Xe7wr</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Emirates NBD And Sobha Realty Partner To Offer Integrated Home Financing Solutions For Off-Plan Projects In Dubai https://t.co/fVBST6NQ7A</t>
+          <t>Al Habtoor Group is committing over AED 5 billion to a new commercial tower in Dubai. Another strong indicator of sustained demand for Grade A office space and long-term market confidence.
+#DubaiRealEstate #CommercialRealEstate #InvestInDubai #DubaiBrokers #RealEstateNews https://t.co/kHUr6Xe7wr</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Emirates NBD and Sobha Realty partner to offer integrated home financing solutions for off-plan projects in Dubai.</t>
+          <t>Al Habtoor Group is committing over AED 5 billion to a new commercial tower in Dubai. This is another strong indicator of sustained demand for Grade A office space and long-term market confidence.</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2266,14 +2263,14 @@
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE11" s="2" t="n">
-        <v>46126.67430555556</v>
+        <v>46127.57430555556</v>
       </c>
       <c r="AF11" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
@@ -2287,7 +2284,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Emirates NBD and Sobha Realty partner to offer integrated home financing solutions for off-plan projects in Dubai.</t>
+          <t>This is another strong indicator of sustained demand for Grade A office space and long-term market confidence. • Al Habtoor Group is committing over AED 5 billion to a new commercial tower in Dubai.</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -2310,47 +2307,43 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2044022292972482932</t>
+          <t>2044283005183857003</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://x.com/OneVilleNews/status/2044022292972482932</t>
+          <t>https://x.com/Eisa_Shj/status/2044283005183857003</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://x.com/OneVilleNews</t>
+          <t>https://x.com/Eisa_Shj</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>OneVilleNews</t>
+          <t>Eisa_Shj</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>One Ville News</t>
+          <t>عـيـســى الأمـيــري</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1662461555869470723/h7J9k2pB_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2042552022017413120/xLRIeU1C_bigger.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>“Ya Biladi”… A Song That Feels Like Home, Bringing the UAE’s Spirit to Life 
-#YaBiladi #UAE #Dubai #Song #HussainAlJassmi @7sainaljassmi #محمد_بن_زايد #الامارات_العربية_المتحدة 
-https://t.co/TqZCzfMs1b via @onevillenews https://t.co/lrW3u4M1bq</t>
+          <t>ماعرف ليش اغلب الناس لين الحين تفتح عندهم و هم من اكثر البنوك في تعقيد الامور الحمدالله على نعمه ENBD الصراحة🦦</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Emirates NBD and Sobha Realty partner to offer integrated home financing solutions for off-plan projects in Dubai 
-&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SobhaRealty"&gt;#SobhaRealty&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Dubai"&gt;#Dubai&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Business"&gt;#Business&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Partnership"&gt;#Partnership&lt;/a&gt; &lt;a href="/SobhaRealtyDXB" title="Sobha Realty"&gt;@SobhaRealtyDXB&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23OneVilleNews"&gt;#OneVilleNews&lt;/a&gt;
-&lt;a href="https://onevillenews.com/2026/04/14/emirates-nbd-and-sobha-realty-partner-to-offer-integrated-home-financing-solutions-for-off-plan-projects-in-dubai/"&gt;onevillenews.com/2026/04/14/…&lt;/a&gt; via &lt;a href="/OneVilleNews" title="One Ville News"&gt;@onevillenews&lt;/a&gt;</t>
+          <t>ماعرف ليش اغلب الناس لين الحين تفتح عندهم و هم من اكثر البنوك في تعقيد الامور الحمدالله على نعمه ENBD الصراحة🦦</t>
         </is>
       </c>
       <c r="K12" t="b">
@@ -2360,23 +2353,19 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 11:57 AM UTC</t>
+          <t>Apr 15, 2026 · 5:13 AM UTC</t>
         </is>
       </c>
       <c r="P12" s="2" t="n">
-        <v>46126.49791666667</v>
+        <v>46127.21736111111</v>
       </c>
       <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23SobhaRealty', 'https://x.com/search?f=tweets&amp;q=%23Dubai', 'https://x.com/search?f=tweets&amp;q=%23UAE', 'https://x.com/search?f=tweets&amp;q=%23Business', 'https://x.com/search?f=tweets&amp;q=%23Partnership', 'https://x.com/SobhaRealtyDXB', 'https://x.com/search?f=tweets&amp;q=%23OneVilleNews', 'https://onevillenews.com/2026/04/14/emirates-nbd-and-sobha-realty-partner-to-offer-integrated-home-financing-solutions-for-off-plan-projects-in-dubai/', 'https://x.com/OneVilleNews']</t>
-        </is>
-      </c>
+      <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
         <v>0</v>
       </c>
@@ -2387,7 +2376,7 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -2396,33 +2385,27 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Emirates NBD and Sobha Realty partner to offer integrated home financing solutions for off-plan projects in Dubai 
-#EmiratesNBD #SobhaRealty #Dubai #UAE #Business #Partnership @SobhaRealtyDXB #OneVilleNews
-onevillenews.com/2026/04/14/… via @onevillenews</t>
+          <t>ماعرف ليش اغلب الناس لين الحين تفتح عندهم و هم من اكثر البنوك في تعقيد الامور الحمدالله على نعمه ENBD الصراحة🦦</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>https://x.com/OneVilleNews/status/2044022292972482932</t>
+          <t>https://x.com/Eisa_Shj/status/2044283005183857003</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>“Ya Biladi”… A Song That Feels Like Home, Bringing the UAE’s Spirit to Life 
-#YaBiladi #UAE #Dubai #Song #HussainAlJassmi @7sainaljassmi #محمد_بن_زايد #الامارات_العربية_المتحدة 
-https://t.co/TqZCzfMs1b via @onevillenews https://t.co/lrW3u4M1bq</t>
+          <t>ماعرف ليش اغلب الناس لين الحين تفتح عندهم و هم من اكثر البنوك في تعقيد الامور الحمدالله على نعمه ENBD الصراحة🦦</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>“Ya Biladi”… A Song That Feels Like Home, Bringing the UAE’s Spirit to Life 
-#YaBiladi #UAE #Dubai #Song #HussainAlJassmi @7sainaljassmi #محمد_بن_زايد #الامارات_العربية_المتحدة 
-https://t.co/TqZCzfMs1b via @onevillenews https://t.co/lrW3u4M1bq</t>
+          <t>ماعرف ليش اغلب الناس لين الحين تفتح عندهم و هم من اكثر البنوك في تعقيد الامور الحمدالله على نعمه ENBD الصراحة🦦</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>"Ya Biladi"... A Song That Feels Like Home, Bringing the UAE’s Spirit to Life</t>
+          <t>I don't know why most people still open accounts with them, as they are one of the banks that complicate matters the most. Thank God for the blessing of ENBD, honestly.</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2432,14 +2415,14 @@
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE12" s="2" t="n">
-        <v>46126.66458333333</v>
+        <v>46127.38402777778</v>
       </c>
       <c r="AF12" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
@@ -2453,7 +2436,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>A Song That Feels Like Home, Bringing the UAE’s Spirit to Life</t>
+          <t>I don't know why most people still open accounts with them, as they are one of the banks that complicate matters the most. • Thank God for the blessing of ENBD, honestly.</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2476,69 +2459,69 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2044003893114232972</t>
+          <t>2044447495619547616</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://x.com/nabilal_rawi/status/2044003893114232972</t>
+          <t>https://x.com/gold_hadas/status/2044447495619547616</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://x.com/nabilal_rawi</t>
+          <t>https://x.com/gold_hadas</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>nabilal_rawi</t>
+          <t>gold_hadas</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nabil Smarter</t>
+          <t>Nicholas MOLODYKO, writer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1920220852898967552/0V_1IXmc_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2026237940993552385/baDKDoMV_bigger.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>While regional tensions are driving higher volatility and risk premiums, the #banking sector in the GCC remains fundamentally sound, with Saudi and UAE institutions still offering upside even under adverse scenarios, according to CI Capital https://t.co/BjQ424Gns3</t>
+          <t>Emirates Islamic launches AED1m campaign for SME customers  https://t.co/7gX7HHRcOh</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Emirates NBD and ADCB demonstrate the UAE&amp;#39;s institutional strength. Free zones and global market access create a financial anchor for entrepreneurs navigating regional volatility.</t>
+          <t>Emirates Islamic launches AED1m campaign for SME customers  &lt;a href="https://www.arabianbusiness.com/finance/emirates-islamic-launches-aed1m-campaign-for-sme-customers"&gt;arabianbusiness.com/finance/…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K13" t="b">
         <v>0</v>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>['Zawya']</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 10:44 AM UTC</t>
+          <t>Apr 15, 2026 · 4:07 PM UTC</t>
         </is>
       </c>
       <c r="P13" s="2" t="n">
-        <v>46126.44722222222</v>
+        <v>46127.67152777778</v>
       </c>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>['https://www.arabianbusiness.com/finance/emirates-islamic-launches-aed1m-campaign-for-sme-customers']</t>
+        </is>
+      </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
@@ -2549,36 +2532,36 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Emirates NBD and ADCB demonstrate the UAE's institutional strength. Free zones and global market access create a financial anchor for entrepreneurs navigating regional volatility.</t>
+          <t>Emirates Islamic launches AED1m campaign for SME customers  arabianbusiness.com/finance/…</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>https://x.com/nabilal_rawi/status/2044003893114232972</t>
+          <t>https://x.com/gold_hadas/status/2044447495619547616</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>While regional tensions are driving higher volatility and risk premiums, the #banking sector in the GCC remains fundamentally sound, with Saudi and UAE institutions still offering upside even under adverse scenarios, according to CI Capital https://t.co/BjQ424Gns3</t>
+          <t>Emirates Islamic launches AED1m campaign for SME customers  https://t.co/7gX7HHRcOh</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>While regional tensions are driving higher volatility and risk premiums, the #banking sector in the GCC remains fundamentally sound, with Saudi and UAE institutions still offering upside even under adverse scenarios, according to CI Capital https://t.co/BjQ424Gns3</t>
+          <t>Emirates Islamic launches AED1m campaign for SME customers  https://t.co/7gX7HHRcOh</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>While regional tensions are driving higher volatility and risk premiums, the banking sector in the GCC remains fundamentally sound, with Saudi and UAE institutions still offering upside even under adverse scenarios, according to CI Capital.</t>
+          <t>Emirates Islamic launches a AED1 million campaign for SME customers.</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2588,33 +2571,33 @@
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE13" s="2" t="n">
-        <v>46126.61388888889</v>
+        <v>46127.83819444444</v>
       </c>
       <c r="AF13" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
+          <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>While regional tensions are driving higher volatility and risk premiums, the banking sector in the GCC remains fundament…</t>
+          <t>Emirates Islamic launches a AED1 million campaign for SME customers.</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank (ENBD)</t>
+          <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AK13" t="n">
@@ -2622,7 +2605,7 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>Zawya</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2632,47 +2615,47 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2043984421192077650</t>
+          <t>2044341445717610661</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2043984421192077650</t>
+          <t>https://x.com/EntAlArabiya/status/2044341445717610661</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals</t>
+          <t>https://x.com/EntAlArabiya</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ENBDdeals</t>
+          <t>EntAlArabiya</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Emirates NBD Deals</t>
+          <t>Entrepreneur العربية</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1763624422294814720/EmRI1Aqu_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1514308412343033862/Cl9tt_tx_bigger.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Travel more, earn more miles ✈️
-Earn bonus Skywards Miles on Emirates Holidays bookings when you pay with your Emirates NBD card. Offer valid until 30 April 2026. T&amp;amp;Cs apply.
-https://t.co/HWEZythYdM https://t.co/z5yAeQRQdC</t>
+          <t>الإمارات الإسلامي @emiratesislamic  يعزز قطاع الأعمال بحملة للشركات الصغيرة
+#الإمارات #دبي #بنوك #شركات #مشاريع_صغيرة #تمويل #اقتصاد #استثمار #نمو #entalarabiya
+https://t.co/XNTvseOsQ0</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Travel more, earn more miles ✈️
-Earn bonus Skywards Miles on Emirates Holidays bookings when you pay with your Emirates NBD card. Offer valid until 30 April 2026. T&amp;amp;Cs apply.
-&lt;a href="https://www.emiratesnbd.com/en/promotions/emirates-holidays-skywards-bonus-miles"&gt;emiratesnbd.com/en/promotion…&lt;/a&gt;</t>
+          <t>الإمارات الإسلامي &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt;  يعزز قطاع الأعمال بحملة للشركات الصغيرة
+&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات"&gt;#الإمارات&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23دبي"&gt;#دبي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23بنوك"&gt;#بنوك&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23شركات"&gt;#شركات&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23مشاريع_صغيرة"&gt;#مشاريع_صغيرة&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23تمويل"&gt;#تمويل&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23اقتصاد"&gt;#اقتصاد&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23استثمار"&gt;#استثمار&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23نمو"&gt;#نمو&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23entalarabiya"&gt;#entalarabiya&lt;/a&gt;
+&lt;a href="https://entrepreneuralarabiya.com/2026/04/15/77826/%d8%a7%d9%84%d8%a5%d9%85%d8%a7%d8%b1%d8%a7%d8%aa-%d8%a7%d9%84%d8%a5%d8%b3%d9%84%d8%a7%d9%85%d9%8a-%d9%8a%d8%af%d8%b9%d9%85-%d8%a7%d9%84%d8%b4%d8%b1%d9%83%d8%a7%d8%aa-%d8%a7%d9%84%d8%b5%d8%ba%d9%8a/"&gt;entrepreneuralarabiya.com/20…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K14" t="b">
@@ -2682,74 +2665,74 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 9:27 AM UTC</t>
+          <t>Apr 15, 2026 · 9:05 AM UTC</t>
         </is>
       </c>
       <c r="P14" s="2" t="n">
-        <v>46126.39375</v>
+        <v>46127.37847222222</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
-          <t>['https://www.emiratesnbd.com/en/promotions/emirates-holidays-skywards-bonus-miles']</t>
+          <t>['https://x.com/emiratesislamic', 'https://x.com/search?f=tweets&amp;q=%23الإمارات', 'https://x.com/search?f=tweets&amp;q=%23دبي', 'https://x.com/search?f=tweets&amp;q=%23بنوك', 'https://x.com/search?f=tweets&amp;q=%23شركات', 'https://x.com/search?f=tweets&amp;q=%23مشاريع_صغيرة', 'https://x.com/search?f=tweets&amp;q=%23تمويل', 'https://x.com/search?f=tweets&amp;q=%23اقتصاد', 'https://x.com/search?f=tweets&amp;q=%23استثمار', 'https://x.com/search?f=tweets&amp;q=%23نمو', 'https://x.com/search?f=tweets&amp;q=%23entalarabiya', 'https://entrepreneuralarabiya.com/2026/04/15/77826/%d8%a7%d9%84%d8%a5%d9%85%d8%a7%d8%b1%d8%a7%d8%aa-%d8%a7%d9%84%d8%a5%d8%b3%d9%84%d8%a7%d9%85%d9%8a-%d9%8a%d8%af%d8%b9%d9%85-%d8%a7%d9%84%d8%b4%d8%b1%d9%83%d8%a7%d8%aa-%d8%a7%d9%84%d8%b5%d8%ba%d9%8a/']</t>
         </is>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V14" t="n">
-        <v>149</v>
+        <v>80</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Travel more, earn more miles ✈️
-Earn bonus Skywards Miles on Emirates Holidays bookings when you pay with your Emirates NBD card. Offer valid until 30 April 2026. T&amp;Cs apply.
-emiratesnbd.com/en/promotion…</t>
+          <t>الإمارات الإسلامي @emiratesislamic  يعزز قطاع الأعمال بحملة للشركات الصغيرة
+#الإمارات #دبي #بنوك #شركات #مشاريع_صغيرة #تمويل #اقتصاد #استثمار #نمو #entalarabiya
+entrepreneuralarabiya.com/20…</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2043984421192077650</t>
+          <t>https://x.com/EntAlArabiya/status/2044341445717610661</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>Travel more, earn more miles ✈️
-Earn bonus Skywards Miles on Emirates Holidays bookings when you pay with your Emirates NBD card. Offer valid until 30 April 2026. T&amp;amp;Cs apply.
-https://t.co/HWEZythYdM https://t.co/z5yAeQRQdC</t>
+          <t>الإمارات الإسلامي @emiratesislamic  يعزز قطاع الأعمال بحملة للشركات الصغيرة
+#الإمارات #دبي #بنوك #شركات #مشاريع_صغيرة #تمويل #اقتصاد #استثمار #نمو #entalarabiya
+https://t.co/XNTvseOsQ0</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Travel more, earn more miles ✈️
-Earn bonus Skywards Miles on Emirates Holidays bookings when you pay with your Emirates NBD card. Offer valid until 30 April 2026. T&amp;amp;Cs apply.
-https://t.co/HWEZythYdM https://t.co/z5yAeQRQdC</t>
+          <t>الإمارات الإسلامي @emiratesislamic  يعزز قطاع الأعمال بحملة للشركات الصغيرة
+#الإمارات #دبي #بنوك #شركات #مشاريع_صغيرة #تمويل #اقتصاد #استثمار #نمو #entalarabiya
+https://t.co/XNTvseOsQ0</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Travel more, earn more miles ✈️ Earn bonus Skywards Miles on Emirates Holidays bookings when you pay with your Emirates NBD card. Offer valid until 30 April 2026. Terms and conditions apply.</t>
+          <t>Emirates Islamic @emiratesislamic strengthens the business sector with a campaign for small companies.</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Cust</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -2758,29 +2741,29 @@
         </is>
       </c>
       <c r="AE14" s="2" t="n">
-        <v>46126.56041666667</v>
+        <v>46127.54513888889</v>
       </c>
       <c r="AF14" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
+          <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Travel more, earn more miles ✈️ Earn bonus Skywards Miles on Emirates Holidays bookings when you pay with your Emirates NBD card. • Offer valid until 30 April 2026. • Terms and conditions apply.</t>
+          <t>Emirates Islamic @emiratesislamic strengthens the business sector with a campaign for small companies.</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank (ENBD)</t>
+          <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AK14" t="n">
@@ -2798,75 +2781,69 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2043855961165623417</t>
+          <t>2044340590037655768</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://x.com/FirasAlin3va/status/2043855961165623417</t>
+          <t>https://x.com/dcgguide/status/2044340590037655768</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://x.com/FirasAlin3va</t>
+          <t>https://x.com/dcgguide</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FirasAlin3va</t>
+          <t>dcgguide</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>فراس علي</t>
+          <t>DUBAI CITY GUIDE from Cyber Gear</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2036473244753207299/AACRtj0p_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1780203891230945280/ODQLZiT__bigger.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>ليلة استثنائية حلق فيها صقر الغناء في #موسم_جدة 🦅
-والجمهور ولعها حماس من أول لحظة لآخرها 🔥
-#رابح_صقر
-#روتانا_لايف
-@RabehSaqer 
-@JEDCalendar 
-@EmiratesNBD_KSA https://t.co/2PHoXVNSf7</t>
+          <t>Emirates Islamic Drives SME Growth And Engagement Through AED 1 Million Business Banking Campaign https://t.co/lYSRNGGq3N</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>أداء ساحر لطيور الغناء في موسم جدة!</t>
+          <t>Emirates Islamic Drives SME Growth And Engagement Through AED 1 Million Business Banking Campaign &lt;a href="https://blog.dubaicityguide.com/site/emirates-islamic-drives-sme-growth-and-engagement-through-aed-1-million-business-banking-campaign/"&gt;blog.dubaicityguide.com/site…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K15" t="b">
         <v>0</v>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>['RotanaLive', 'RabehSaqer', 'JEDCalendar', 'EmiratesNBD_KSA']</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Apr 14</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 12:56 AM UTC</t>
+          <t>Apr 15, 2026 · 9:02 AM UTC</t>
         </is>
       </c>
       <c r="P15" s="2" t="n">
-        <v>46126.03888888889</v>
+        <v>46127.37638888889</v>
       </c>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>['https://blog.dubaicityguide.com/site/emirates-islamic-drives-sme-growth-and-engagement-through-aed-1-million-business-banking-campaign/']</t>
+        </is>
+      </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
@@ -2874,51 +2851,39 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>أداء ساحر لطيور الغناء في موسم جدة!</t>
+          <t>Emirates Islamic Drives SME Growth And Engagement Through AED 1 Million Business Banking Campaign blog.dubaicityguide.com/site…</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>https://x.com/FirasAlin3va/status/2043855961165623417</t>
+          <t>https://x.com/dcgguide/status/2044340590037655768</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>ليلة استثنائية حلق فيها صقر الغناء في #موسم_جدة 🦅
-والجمهور ولعها حماس من أول لحظة لآخرها 🔥
-#رابح_صقر
-#روتانا_لايف
-@RabehSaqer 
-@JEDCalendar 
-@EmiratesNBD_KSA https://t.co/2PHoXVNSf7</t>
+          <t>Emirates Islamic Drives SME Growth And Engagement Through AED 1 Million Business Banking Campaign https://t.co/lYSRNGGq3N</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>ليلة استثنائية حلق فيها صقر الغناء في #موسم_جدة 🦅
-والجمهور ولعها حماس من أول لحظة لآخرها 🔥
-#رابح_صقر
-#روتانا_لايف
-@RabehSaqer 
-@JEDCalendar 
-@EmiratesNBD_KSA https://t.co/2PHoXVNSf7</t>
+          <t>Emirates Islamic Drives SME Growth And Engagement Through AED 1 Million Business Banking Campaign https://t.co/lYSRNGGq3N</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>An exceptional night where the singing falcon soared in #Jeddah_Season 🦅 and the audience was excited from the very first moment to the last 🔥</t>
+          <t>Emirates Islamic Drives SME Growth And Engagement Through AED 1 Million Business Banking Campaign</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2928,33 +2893,33 @@
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE15" s="2" t="n">
-        <v>46126.20555555556</v>
+        <v>46127.54305555556</v>
       </c>
       <c r="AF15" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
+          <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>An exceptional night where the singing falcon soared in #Jeddah_Season 🦅 and the audience was excited from the very first moment to the last 🔥</t>
+          <t>Emirates Islamic Drives SME Growth And Engagement Through AED 1 Million Business Banking Campaign</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank (ENBD)</t>
+          <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AK15" t="n">
@@ -2962,7 +2927,7 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>RotanaLive, RabehSaqer, JEDCalendar, EmiratesNBD_KSA</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2972,45 +2937,49 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2044143965486948528</t>
+          <t>2044312732879728677</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://x.com/GidwaniHero/status/2044143965486948528</t>
+          <t>https://x.com/EntMagazineME/status/2044312732879728677</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://x.com/GidwaniHero</t>
+          <t>https://x.com/EntMagazineME</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>GidwaniHero</t>
+          <t>EntMagazineME</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hero Gidwani</t>
+          <t>Entrepreneur Middle East</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1924556859526283267/UcvezR38_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1514494189895049219/SrZOixX4_bigger.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>@HHShkMohd @ENBDdeals @FABConnects @MashreqTweets @emiratesislamic 
-Dear uae government what is daily lime to deposit in machine if I have 100k to deposit and machine is slow and behind me standing In Q Are arguing what to do who deposit black money no one question them why</t>
+          <t>@emiratesislamic has announced the launch of a new Business Banking campaign aimed at supporting 3SME customers and strengthening #business resilience across the #UAE.
+Running until June 30, 2026, the campaign allows businesses to participate by increasing and maintaining their average balances in their Business Banking Accounts.
+The initiative offers a total prize pool of AED1 million and will reward 55 winners over three months, providing multiple opportunities for customers to win cash prizes while encouraging sustainable growth.
+🔗Read more HERE: https://t.co/j0Wq0RjPdm</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>&lt;a href="/HHShkMohd" title="HH Sheikh Mohammed"&gt;@HHShkMohd&lt;/a&gt; &lt;a href="/ENBDdeals" title="Emirates NBD Deals"&gt;@ENBDdeals&lt;/a&gt; &lt;a href="/FABConnects" title="FAB Connects"&gt;@FABConnects&lt;/a&gt; &lt;a href="/MashreqTweets" title="Mashreq"&gt;@MashreqTweets&lt;/a&gt; &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; 
-Dear uae government what is daily lime to deposit in machine if I have 100k to deposit and machine is slow and behind me standing In Q Are arguing what to do who deposit black money no one question them why</t>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; has announced the launch of a new Business Banking campaign aimed at supporting 3SME customers and strengthening &lt;a href="/search?f=tweets&amp;amp;q=%23business"&gt;#business&lt;/a&gt; resilience across the &lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt;.
+Running until June 30, 2026, the campaign allows businesses to participate by increasing and maintaining their average balances in their Business Banking Accounts.
+The initiative offers a total prize pool of AED1 million and will reward 55 winners over three months, providing multiple opportunities for customers to win cash prizes while encouraging sustainable growth.
+🔗Read more HERE: &lt;a href="https://mena.entrepreneur.com/business-news/emirates-islamic-launches-business-banking-campaign-with-aed1-million-prize-pool-to-support-uae-smes"&gt;mena.entrepreneur.com/busine…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K16" t="b">
@@ -3020,34 +2989,34 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>6h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 8:01 PM UTC</t>
+          <t>Apr 15, 2026 · 7:11 AM UTC</t>
         </is>
       </c>
       <c r="P16" s="2" t="n">
-        <v>46126.83402777778</v>
+        <v>46127.29930555556</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
-          <t>['https://x.com/HHShkMohd', 'https://x.com/ENBDdeals', 'https://x.com/FABConnects', 'https://x.com/MashreqTweets', 'https://x.com/emiratesislamic']</t>
+          <t>['https://x.com/emiratesislamic', 'https://x.com/search?f=tweets&amp;q=%23business', 'https://x.com/search?f=tweets&amp;q=%23UAE', 'https://mena.entrepreneur.com/business-news/emirates-islamic-launches-business-banking-campaign-with-aed1-million-prize-pool-to-support-uae-smes']</t>
         </is>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V16" t="n">
-        <v>3</v>
+        <v>105</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -3056,30 +3025,39 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>@HHShkMohd @ENBDdeals @FABConnects @MashreqTweets @emiratesislamic 
-Dear uae government what is daily lime to deposit in machine if I have 100k to deposit and machine is slow and behind me standing In Q Are arguing what to do who deposit black money no one question them why</t>
+          <t>@emiratesislamic has announced the launch of a new Business Banking campaign aimed at supporting 3SME customers and strengthening #business resilience across the #UAE.
+Running until June 30, 2026, the campaign allows businesses to participate by increasing and maintaining their average balances in their Business Banking Accounts.
+The initiative offers a total prize pool of AED1 million and will reward 55 winners over three months, providing multiple opportunities for customers to win cash prizes while encouraging sustainable growth.
+🔗Read more HERE: mena.entrepreneur.com/busine…</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>https://x.com/GidwaniHero/status/2044143965486948528</t>
+          <t>https://x.com/EntMagazineME/status/2044312732879728677</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>@HHShkMohd @ENBDdeals @FABConnects @MashreqTweets @emiratesislamic 
-Dear uae government what is daily lime to deposit in machine if I have 100k to deposit and machine is slow and behind me standing In Q Are arguing what to do who deposit black money no one question them why</t>
+          <t>@emiratesislamic has announced the launch of a new Business Banking campaign aimed at supporting 3SME customers and strengthening #business resilience across the #UAE.
+Running until June 30, 2026, the campaign allows businesses to participate by increasing and maintaining their average balances in their Business Banking Accounts.
+The initiative offers a total prize pool of AED1 million and will reward 55 winners over three months, providing multiple opportunities for customers to win cash prizes while encouraging sustainable growth.
+🔗Read more HERE: https://t.co/j0Wq0RjPdm</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>@HHShkMohd @ENBDdeals @FABConnects @MashreqTweets @emiratesislamic 
-Dear uae government what is daily lime to deposit in machine if I have 100k to deposit and machine is slow and behind me standing In Q Are arguing what to do who deposit black money no one question them why</t>
+          <t>@emiratesislamic has announced the launch of a new Business Banking campaign aimed at supporting 3SME customers and strengthening #business resilience across the #UAE.
+Running until June 30, 2026, the campaign allows businesses to participate by increasing and maintaining their average balances in their Business Banking Accounts.
+The initiative offers a total prize pool of AED1 million and will reward 55 winners over three months, providing multiple opportunities for customers to win cash prizes while encouraging sustainable growth.
+🔗Read more HERE: https://t.co/j0Wq0RjPdm</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Dear UAE government, what is the daily limit to deposit in the machine if I have 100k to deposit and the machine is slow? There are people behind me in line arguing about what to do. Those depositing black money are not questioned; why is that?</t>
+          <t>Emirates Islamic has announced the launch of a new Business Banking campaign aimed at supporting SME customers and strengthening business resilience across the UAE. 
+Running until June 30, 2026, the campaign allows businesses to participate by increasing and maintaining their average balances in their Business Banking Accounts. 
+The initiative offers a total prize pool of AED 1 million and will reward 55 winners over three months, providing multiple opportunities for customers to win cash prizes while encouraging sustainable growth. 
+Read more HERE: https://t.co/j0Wq0RjPdm</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -3089,11 +3067,11 @@
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE16" s="2" t="n">
-        <v>46127.00069444445</v>
+        <v>46127.46597222222</v>
       </c>
       <c r="AF16" s="2" t="n">
         <v>46127</v>
@@ -3110,7 +3088,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Dear UAE government, what is the daily limit to deposit in the machine if I have 100k to deposit and the machine is slow? • There are people behind me in line arguing about what to do. • Those depositing black money are not questioned; why is that?</t>
+          <t>Running until June 30, 2026, the campaign allows businesses to participate by increasing and maintaining their average balances in their Business Banking Accounts. • Emirates Islamic has announced the launch of a new Business Banking campaign aimed at supporting SME customers and strengthening business resilience across the UAE. • Read more HERE: https://t.co/j0Wq0RjPdm</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -3133,12 +3111,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2043932263390310621</t>
+          <t>2044294659795513346</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043932263390310621</t>
+          <t>https://x.com/emiratesislamic/status/2044294659795513346</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3164,16 +3142,18 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>How do you usually pay for your expenses?
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
-https://t.co/XvyZgR87nM</t>
+          <t>من “يوماً ما” إلى يوم الانتقال!
+التمويل السكني من الإمارات الإسلامي يجعل حلم امتلاك منزلك حقيقة، مع المرونة والوضوح في كل خطوة من رحلتك.
+استمتع بحلول تمويلية مصممة خصيصاً لك، ودعم متكامل طوال الطريق، لتصبح تجربة امتلاك المنزل سلسة وميسرة.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>How do you usually pay for your expenses?
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
+          <t>From “one day” to move-in day.
+Emirates Islamic Home Finance helps turn home ownership into reality, with the flexibility and clarity you need at every step.
+With tailored finance solutions and guided support throughout,
+Your home journey starts here.
+&lt;a href="https://www.emiratesislamic.ae/en/Personal-Banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=home_finance"&gt;emiratesislamic.ae/en/Person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K17" t="b">
@@ -3183,21 +3163,21 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 6:00 AM UTC</t>
+          <t>Apr 15, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P17" s="2" t="n">
-        <v>46126.25</v>
+        <v>46127.25</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+          <t>['https://www.emiratesislamic.ae/en/Personal-Banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=home_finance']</t>
         </is>
       </c>
       <c r="S17" t="n">
@@ -3210,7 +3190,7 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -3219,33 +3199,37 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>How do you usually pay for your expenses?
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
-emiratesislamic.ae/en/key-in…</t>
+          <t>From “one day” to move-in day.
+Emirates Islamic Home Finance helps turn home ownership into reality, with the flexibility and clarity you need at every step.
+With tailored finance solutions and guided support throughout,
+Your home journey starts here.
+emiratesislamic.ae/en/Person…</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043932263390310621</t>
+          <t>https://x.com/emiratesislamic/status/2044294659795513346</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>How do you usually pay for your expenses?
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
-https://t.co/XvyZgR87nM</t>
+          <t>من “يوماً ما” إلى يوم الانتقال!
+التمويل السكني من الإمارات الإسلامي يجعل حلم امتلاك منزلك حقيقة، مع المرونة والوضوح في كل خطوة من رحلتك.
+استمتع بحلول تمويلية مصممة خصيصاً لك، ودعم متكامل طوال الطريق، لتصبح تجربة امتلاك المنزل سلسة وميسرة.</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>How do you usually pay for your expenses?
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
-https://t.co/XvyZgR87nM</t>
+          <t>من “يوماً ما” إلى يوم الانتقال!
+التمويل السكني من الإمارات الإسلامي يجعل حلم امتلاك منزلك حقيقة، مع المرونة والوضوح في كل خطوة من رحلتك.
+استمتع بحلول تمويلية مصممة خصيصاً لك، ودعم متكامل طوال الطريق، لتصبح تجربة امتلاك المنزل سلسة وميسرة.</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>How do you usually pay for your expenses?</t>
+          <t>From "one day" to moving day! 
+Emirates Islamic home financing makes your dream of owning a home a reality, with flexibility and clarity at every step of your journey. 
+Enjoy financing solutions tailored just for you, with comprehensive support along the way, making the homeownership experience smooth and accessible.</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -3255,14 +3239,14 @@
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE17" s="2" t="n">
-        <v>46126.41666666666</v>
+        <v>46127.41666666666</v>
       </c>
       <c r="AF17" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
@@ -3276,7 +3260,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>How do you usually pay for your expenses?</t>
+          <t>Emirates Islamic home financing makes your dream of owning a home a reality, with flexibility and clarity at every step of your journey. • Enjoy financing solutions tailored just for you, with comprehensive support along the way, making the homeownership experience smooth and accessible. • From "one day" to moving day!</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -3299,12 +3283,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2043917165502316982</t>
+          <t>2044471342880170391</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043917165502316982</t>
+          <t>https://x.com/emiratesislamic/status/2044471342880170391</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3330,18 +3314,18 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>نظرتك الأسبوعية… لحياة أكثر وعياً واتزاناً مالياً.
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-Your Weekly Perspective. A step toward a more mindful financial week.
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic https://t.co/48pYcSntb5</t>
+          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية قيمتها تصل إلى 1,000,000 درهم. كل زيادة بقيمة 100,000 درهم في حسابك المصرفي للأعمال تمنحك فرصة واحدة للدخول في السحب.
+اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟ https://t.co/zGFXn2y3iT</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>نظرتك الأسبوعية… لحياة أكثر وعياً واتزاناً مالياً.
-&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
-Your Weekly Perspective. A step toward a more mindful financial week.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;</t>
+          <t>الجائزة النقدية الكبرى: 250,000 درهم (فائز واحد) 
+الجائزة النقدية الثانية: 100,000 درهم (فائزان اثنان)
+الجوائز النقدية الشهرية: تصل إلى 25 ألف درهم (52 فائز)
+يسري العرض لغاية 30 يونيو 2026.
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=bb_offer"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K18" t="b">
@@ -3351,21 +3335,21 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 5:00 AM UTC</t>
+          <t>Apr 15, 2026 · 5:42 PM UTC</t>
         </is>
       </c>
       <c r="P18" s="2" t="n">
-        <v>46126.20833333334</v>
+        <v>46127.7375</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic']</t>
+          <t>['https://www.emiratesislamic.ae/ar/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=bb_offer']</t>
         </is>
       </c>
       <c r="S18" t="n">
@@ -3378,7 +3362,7 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>56</v>
+        <v>147</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -3387,36 +3371,35 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>نظرتك الأسبوعية… لحياة أكثر وعياً واتزاناً مالياً.
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-Your Weekly Perspective. A step toward a more mindful financial week.
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic</t>
+          <t>الجائزة النقدية الكبرى: 250,000 درهم (فائز واحد) 
+الجائزة النقدية الثانية: 100,000 درهم (فائزان اثنان)
+الجوائز النقدية الشهرية: تصل إلى 25 ألف درهم (52 فائز)
+يسري العرض لغاية 30 يونيو 2026.
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/offers…</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043917165502316982</t>
+          <t>https://x.com/emiratesislamic/status/2044471342880170391</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>نظرتك الأسبوعية… لحياة أكثر وعياً واتزاناً مالياً.
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-Your Weekly Perspective. A step toward a more mindful financial week.
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic https://t.co/48pYcSntb5</t>
+          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية قيمتها تصل إلى 1,000,000 درهم. كل زيادة بقيمة 100,000 درهم في حسابك المصرفي للأعمال تمنحك فرصة واحدة للدخول في السحب.
+اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟ https://t.co/zGFXn2y3iT</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>نظرتك الأسبوعية… لحياة أكثر وعياً واتزاناً مالياً.
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-Your Weekly Perspective. A step toward a more mindful financial week.
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic https://t.co/48pYcSntb5</t>
+          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية قيمتها تصل إلى 1,000,000 درهم. كل زيادة بقيمة 100,000 درهم في حسابك المصرفي للأعمال تمنحك فرصة واحدة للدخول في السحب.
+اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟ https://t.co/zGFXn2y3iT</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Your weekly perspective… for a more conscious and financially balanced life.</t>
+          <t>Get a chance to win a share of cash prizes worth up to 1,000,000 dirhams. Every increase of 100,000 dirhams in your business bank account gives you one entry into the draw.
+Make your company one of the 55 winning companies. Will you be among them?</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3426,14 +3409,14 @@
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE18" s="2" t="n">
-        <v>46126.375</v>
+        <v>46127.90416666667</v>
       </c>
       <c r="AF18" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
@@ -3447,7 +3430,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Your weekly perspective… for a more conscious and financially balanced life.</t>
+          <t>Get a chance to win a share of cash prizes worth up to 1,000,000 dirhams. • Every increase of 100,000 dirhams in your business bank account gives you one entry into the draw. • Make your company one of the 55 winning companies.</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -3470,12 +3453,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2044023053797953761</t>
+          <t>2044471339784810653</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044023053797953761</t>
+          <t>https://x.com/emiratesislamic/status/2044471339784810653</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3501,49 +3484,48 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Dear Zahara,we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.
+⭐️Shariah-compliant offering https://t.co/lsN56x6Joc</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Dear Zahara,we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
+          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية قيمتها تصل إلى 1,000,000 درهم. كل زيادة بقيمة 100,000 درهم في حسابك المصرفي للأعمال تمنحك فرصة واحدة للدخول في السحب.
+اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟</t>
         </is>
       </c>
       <c r="K19" t="b">
         <v>0</v>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>['ZaharaMMalik']</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 12:00 PM UTC</t>
+          <t>Apr 15, 2026 · 5:42 PM UTC</t>
         </is>
       </c>
       <c r="P19" s="2" t="n">
-        <v>46126.5</v>
+        <v>46127.7375</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" t="n">
-        <v>65</v>
+        <v>147</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -3552,36 +3534,51 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Dear Zahara,we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
+          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية قيمتها تصل إلى 1,000,000 درهم. كل زيادة بقيمة 100,000 درهم في حسابك المصرفي للأعمال تمنحك فرصة واحدة للدخول في السحب.
+اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044471339784810653</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.
+⭐️Shariah-compliant offering https://t.co/lsN56x6Joc</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Dear Zahara,we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.
+⭐️Shariah-compliant offering https://t.co/lsN56x6Joc</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Dear Zahara, we have tried to reach you through direct message, but unfortunately, we were not successful because you are not following our page. Please DM us back so we can assist you better.</t>
+          <t>Invest in gold and silver easily and digitally with the EI + Mobile Banking App. 
+Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly. 
+Shariah-compliant offering.</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Cust</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE19" s="2" t="n">
-        <v>46126.66666666666</v>
+        <v>46127.90416666667</v>
       </c>
       <c r="AF19" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
@@ -3595,7 +3592,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Dear Zahara, we have tried to reach you through direct message, but unfortunately, we were not successful because you are not following our page. • Please DM us back so we can assist you better.</t>
+          <t>Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly. • Invest in gold and silver easily and digitally with the EI + Mobile Banking App. • Shariah-compliant offering.</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -3608,7 +3605,7 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>ZaharaMMalik</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3618,12 +3615,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2043955058459467807</t>
+          <t>2044471329382900119</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043955058459467807</t>
+          <t>https://x.com/emiratesislamic/status/2044471329382900119</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3649,38 +3646,44 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes! Every AED 100,000 increase in your Business Banking account earns you one entry into the draw.
+55 businesses will be winners. Will you be one of them?
+Grand cash prize: AED 250,000 (1 winner) https://t.co/PtTMEJsQ5k</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
+          <t>Second cash prize: AED 100,000 each (2 winners)
+Monthly cash prizes: up to AED 25,000 (52 winners)
+Valid until 30 June 2026.
+Terms and conditions apply.
+&lt;a href="https://www.emiratesislamic.ae/en/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=bb_offer"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K20" t="b">
         <v>0</v>
       </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>['aswanikumartst5']</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 7:30 AM UTC</t>
+          <t>Apr 15, 2026 · 5:42 PM UTC</t>
         </is>
       </c>
       <c r="P20" s="2" t="n">
-        <v>46126.3125</v>
+        <v>46127.7375</v>
       </c>
       <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=bb_offer']</t>
+        </is>
+      </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
@@ -3691,7 +3694,7 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -3700,36 +3703,54 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
+          <t>Second cash prize: AED 100,000 each (2 winners)
+Monthly cash prizes: up to AED 25,000 (52 winners)
+Valid until 30 June 2026.
+Terms and conditions apply.
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044471329382900119</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes! Every AED 100,000 increase in your Business Banking account earns you one entry into the draw.
+55 businesses will be winners. Will you be one of them?
+Grand cash prize: AED 250,000 (1 winner) https://t.co/PtTMEJsQ5k</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes! Every AED 100,000 increase in your Business Banking account earns you one entry into the draw.
+55 businesses will be winners. Will you be one of them?
+Grand cash prize: AED 250,000 (1 winner) https://t.co/PtTMEJsQ5k</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you through private messaging to serve you better.</t>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes! Every AED 100,000 increase in your Business Banking account earns you one entry into the draw. 
+55 businesses will be winners. Will you be one of them? 
+Grand cash prize: AED 250,000 (1 winner)</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Cust</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE20" s="2" t="n">
-        <v>46126.47916666666</v>
+        <v>46127.90416666667</v>
       </c>
       <c r="AF20" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
@@ -3743,7 +3764,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you through private messaging to serve you better.</t>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes! • Every AED 100,000 increase in your Business Banking account earns you one entry into the draw. • Grand cash prize: AED 250,000 (1 winner)</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3756,7 +3777,7 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>aswanikumartst5</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3766,12 +3787,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2043932266456367150</t>
+          <t>2044471327159996698</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043932266456367150</t>
+          <t>https://x.com/emiratesislamic/status/2044471327159996698</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3797,14 +3818,16 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>To know more:
-https://t.co/XvyZgR87nM</t>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes! Every AED 100,000 increase in your Business Banking account earns you one entry into the draw.
+55 businesses will be winners. Will you be one of them?
+Grand cash prize: AED 250,000 (1 winner)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>To know more:
-&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes! Every AED 100,000 increase in your Business Banking account earns you one entry into the draw.
+55 businesses will be winners. Will you be one of them?
+Grand cash prize: AED 250,000 (1 winner)</t>
         </is>
       </c>
       <c r="K21" t="b">
@@ -3814,25 +3837,21 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 6:00 AM UTC</t>
+          <t>Apr 15, 2026 · 5:42 PM UTC</t>
         </is>
       </c>
       <c r="P21" s="2" t="n">
-        <v>46126.25</v>
+        <v>46127.7375</v>
       </c>
       <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
-        </is>
-      </c>
+      <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
@@ -3841,7 +3860,7 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -3850,30 +3869,25 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>To know more:
-emiratesislamic.ae/en/key-in…</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932266456367150</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>To know more:
-https://t.co/XvyZgR87nM</t>
-        </is>
-      </c>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes! Every AED 100,000 increase in your Business Banking account earns you one entry into the draw.
+55 businesses will be winners. Will you be one of them?
+Grand cash prize: AED 250,000 (1 winner)</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>To know more:
-https://t.co/XvyZgR87nM</t>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes! Every AED 100,000 increase in your Business Banking account earns you one entry into the draw.
+55 businesses will be winners. Will you be one of them?
+Grand cash prize: AED 250,000 (1 winner)</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>To know more: https://t.co/XvyZgR87nM</t>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes! Every AED 100,000 increase in your Business Banking account earns you one entry into the draw. 
+55 businesses will be winners. Will you be one of them? 
+Grand cash prize: AED 250,000 (1 winner)</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3883,14 +3897,14 @@
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE21" s="2" t="n">
-        <v>46126.41666666666</v>
+        <v>46127.90416666667</v>
       </c>
       <c r="AF21" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
@@ -3904,7 +3918,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>To know more: https://t.co/XvyZgR87nM</t>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes! • Every AED 100,000 increase in your Business Banking account earns you one entry into the draw. • Grand cash prize: AED 250,000 (1 winner)</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3927,12 +3941,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2043932263725854816</t>
+          <t>2044322414310367621</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043932263725854816</t>
+          <t>https://x.com/emiratesislamic/status/2044322414310367621</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3958,18 +3972,18 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>ينمو المال بشكل أفضل مع الوقت، والتوازن، والتنوّع المناسب.
-تنويع الاستثمارات والتفكير على المدى الطويل يساعدان على تحقيق استقرار أكبر.
-خطوات صغيرة اليوم قد تصنع نتائج أقوى في المستقبل.
-للمزيد: 
-https://t.co/mgtIcQsyLZ https://t.co/Eh7yupmtiG</t>
+          <t>⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
+⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
+Terms and conditions apply.
+https://t.co/w5RtLlrqm8</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Money grows best when given time, balance, and the right mix.
-Spreading investments and thinking long term can help create steadier progress along the way.
-Small steps today can support stronger outcomes tomorrow.</t>
+          <t>⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
+⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
+Terms and conditions apply.
+&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=psb_wealth"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K22" t="b">
@@ -3984,16 +3998,20 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 6:00 AM UTC</t>
+          <t>Apr 15, 2026 · 7:50 AM UTC</t>
         </is>
       </c>
       <c r="P22" s="2" t="n">
-        <v>46126.25</v>
+        <v>46127.32638888889</v>
       </c>
       <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=psb_wealth']</t>
+        </is>
+      </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -4002,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>85</v>
+        <v>142</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -4011,37 +4029,36 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Money grows best when given time, balance, and the right mix.
-Spreading investments and thinking long term can help create steadier progress along the way.
-Small steps today can support stronger outcomes tomorrow.</t>
+          <t>⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
+⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
+Terms and conditions apply.
+emiratesislamic.ae/en/person…</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043932263725854816</t>
+          <t>https://x.com/emiratesislamic/status/2044322414310367621</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>ينمو المال بشكل أفضل مع الوقت، والتوازن، والتنوّع المناسب.
-تنويع الاستثمارات والتفكير على المدى الطويل يساعدان على تحقيق استقرار أكبر.
-خطوات صغيرة اليوم قد تصنع نتائج أقوى في المستقبل.
-للمزيد: 
-https://t.co/mgtIcQsyLZ https://t.co/Eh7yupmtiG</t>
+          <t>⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
+⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
+Terms and conditions apply.
+https://t.co/w5RtLlrqm8</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>ينمو المال بشكل أفضل مع الوقت، والتوازن، والتنوّع المناسب.
-تنويع الاستثمارات والتفكير على المدى الطويل يساعدان على تحقيق استقرار أكبر.
-خطوات صغيرة اليوم قد تصنع نتائج أقوى في المستقبل.
-للمزيد: 
-https://t.co/mgtIcQsyLZ https://t.co/Eh7yupmtiG</t>
+          <t>⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
+⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
+Terms and conditions apply.
+https://t.co/w5RtLlrqm8</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Money grows better with time, balance, and the right diversification. Diversifying investments and thinking long-term help achieve greater stability. Small steps today can lead to stronger results in the future.</t>
+          <t>Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards Certified silver bars compliant with UAE Good Delivery (UAE GD) standards Terms and conditions apply.</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -4055,10 +4072,10 @@
         </is>
       </c>
       <c r="AE22" s="2" t="n">
-        <v>46126.41666666666</v>
+        <v>46127.49305555555</v>
       </c>
       <c r="AF22" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
@@ -4072,7 +4089,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Diversifying investments and thinking long-term help achieve greater stability. • Small steps today can lead to stronger results in the future. • Money grows better with time, balance, and the right diversification.</t>
+          <t>Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards Certified s…</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -4095,12 +4112,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2043932263449006494</t>
+          <t>2044322412007735394</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043932263449006494</t>
+          <t>https://x.com/emiratesislamic/status/2044322412007735394</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4126,16 +4143,16 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>كيف تدفع نفقاتك عادةً؟
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-https://t.co/mgtIcQsyLZ</t>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.
+⭐️Shariah-compliant offering</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>كيف تدفع نفقاتك عادةً؟
-&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.
+⭐️Shariah-compliant offering</t>
         </is>
       </c>
       <c r="K23" t="b">
@@ -4150,29 +4167,25 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 6:00 AM UTC</t>
+          <t>Apr 15, 2026 · 7:50 AM UTC</t>
         </is>
       </c>
       <c r="P23" s="2" t="n">
-        <v>46126.25</v>
+        <v>46127.32638888889</v>
       </c>
       <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
-        </is>
-      </c>
+      <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" t="n">
-        <v>73</v>
+        <v>204</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -4181,33 +4194,25 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>كيف تدفع نفقاتك عادةً؟
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-emiratesislamic.ae/ar/key-in…</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263449006494</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>كيف تدفع نفقاتك عادةً؟
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-https://t.co/mgtIcQsyLZ</t>
-        </is>
-      </c>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.
+⭐️Shariah-compliant offering</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>كيف تدفع نفقاتك عادةً؟
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-https://t.co/mgtIcQsyLZ</t>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.
+⭐️Shariah-compliant offering</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>How do you usually pay your expenses?</t>
+          <t>Invest in gold and silver easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.
+⭐️Shariah-compliant offering</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -4217,14 +4222,14 @@
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE23" s="2" t="n">
-        <v>46126.41666666666</v>
+        <v>46127.49305555555</v>
       </c>
       <c r="AF23" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
@@ -4238,7 +4243,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>How do you usually pay your expenses?</t>
+          <t>Invest in gold and silver easily and digitally with the EI + Mobile Banking App ⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly. • ⭐️Shariah-compliant offering</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -4261,12 +4266,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2043932263386157239</t>
+          <t>2044322403761697193</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043932263386157239</t>
+          <t>https://x.com/emiratesislamic/status/2044322403761697193</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4292,20 +4297,18 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ينمو المال بشكل أفضل مع الوقت، والتوازن، والتنوّع المناسب.
-تنويع الاستثمارات والتفكير على المدى الطويل يساعدان على تحقيق استقرار أكبر.
-خطوات صغيرة اليوم قد تصنع نتائج أقوى في المستقبل.
-للمزيد: 
-emiratesislamic.ae/ar/key-in…</t>
+          <t>⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
+⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/person…</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>ينمو المال بشكل أفضل مع الوقت، والتوازن، والتنوّع المناسب.
-تنويع الاستثمارات والتفكير على المدى الطويل يساعدان على تحقيق استقرار أكبر.
-خطوات صغيرة اليوم قد تصنع نتائج أقوى في المستقبل.
-للمزيد: 
-&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
+          <t>⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
+⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organiic-twitter&amp;amp;utm_medium=socal&amp;amp;utm_campaign=psb_wealth"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K24" t="b">
@@ -4320,16 +4323,16 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 6:00 AM UTC</t>
+          <t>Apr 15, 2026 · 7:50 AM UTC</t>
         </is>
       </c>
       <c r="P24" s="2" t="n">
-        <v>46126.25</v>
+        <v>46127.32638888889</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+          <t>['https://www.emiratesislamic.ae/ar/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organiic-twitter&amp;utm_medium=socal&amp;utm_campaign=psb_wealth']</t>
         </is>
       </c>
       <c r="S24" t="n">
@@ -4342,7 +4345,7 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>52</v>
+        <v>115</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -4351,27 +4354,27 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>ينمو المال بشكل أفضل مع الوقت، والتوازن، والتنوّع المناسب.
-تنويع الاستثمارات والتفكير على المدى الطويل يساعدان على تحقيق استقرار أكبر.
-خطوات صغيرة اليوم قد تصنع نتائج أقوى في المستقبل.
-للمزيد: 
-emiratesislamic.ae/ar/key-in…</t>
+          <t>⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
+⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/person…</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>ينمو المال بشكل أفضل مع الوقت، والتوازن، والتنوّع المناسب.
-تنويع الاستثمارات والتفكير على المدى الطويل يساعدان على تحقيق استقرار أكبر.
-خطوات صغيرة اليوم قد تصنع نتائج أقوى في المستقبل.
-للمزيد: 
-emiratesislamic.ae/ar/key-in…</t>
+          <t>⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
+⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/person…</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Money grows better with time, balance, and the right diversification. Diversifying investments and thinking long-term help achieve greater stability. Small steps today can lead to stronger results in the future.</t>
+          <t>Certified gold bars that comply with the standards of the London Bullion Market Association and Dubai Good Delivery.
+Certified silver bars that meet the UAE Good Delivery standards.
+Terms and conditions apply.</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -4385,10 +4388,10 @@
         </is>
       </c>
       <c r="AE24" s="2" t="n">
-        <v>46126.41666666666</v>
+        <v>46127.49305555555</v>
       </c>
       <c r="AF24" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
@@ -4402,7 +4405,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Diversifying investments and thinking long-term help achieve greater stability. • Small steps today can lead to stronger results in the future. • Money grows better with time, balance, and the right diversification.</t>
+          <t>Certified gold bars that comply with the standards of the London Bullion Market Association and Dubai Good Delivery. • Certified silver bars that meet the UAE Good Delivery standards. • Terms and conditions apply.</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -4425,43 +4428,49 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2044011613422834071</t>
+          <t>2044322401052250291</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://x.com/ZaharaMMalik/status/2044011613422834071</t>
+          <t>https://x.com/emiratesislamic/status/2044322401052250291</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://x.com/ZaharaMMalik</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ZaharaMMalik</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Zahara Sadiq</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1123139785072304129/0KaXZD52_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Really struggling to get hold of @emiratesislamic I’ve called the international line and emailed and really need to get hold of someone. Please help 😭</t>
+          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
+EI + للخدمات المصرفية عبر الهاتف المتحرك
+⭐️ادخل إلى منصة "الثروات" في تطبيق + EI  للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.
+⭐️منتج متوافق مع أحكام الشريعة الإسلامية https://t.co/CZe51naJfQ</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Really struggling to get hold of &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; I’ve called the international line and emailed and really need to get hold of someone. Please help 😭</t>
+          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
+EI + للخدمات المصرفية عبر الهاتف المتحرك
+⭐️ادخل إلى منصة &amp;#34;الثروات&amp;#34; في تطبيق + EI  للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.
+⭐️منتج متوافق مع أحكام الشريعة الإسلامية</t>
         </is>
       </c>
       <c r="K25" t="b">
@@ -4471,23 +4480,19 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 11:15 AM UTC</t>
+          <t>Apr 15, 2026 · 7:50 AM UTC</t>
         </is>
       </c>
       <c r="P25" s="2" t="n">
-        <v>46126.46875</v>
+        <v>46127.32638888889</v>
       </c>
       <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>['https://x.com/emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
         <v>1</v>
       </c>
@@ -4498,7 +4503,7 @@
         <v>1</v>
       </c>
       <c r="V25" t="n">
-        <v>93</v>
+        <v>201</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -4507,44 +4512,55 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Really struggling to get hold of @emiratesislamic I’ve called the international line and emailed and really need to get hold of someone. Please help 😭</t>
+          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
+EI + للخدمات المصرفية عبر الهاتف المتحرك
+⭐️ادخل إلى منصة "الثروات" في تطبيق + EI  للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.
+⭐️منتج متوافق مع أحكام الشريعة الإسلامية</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>https://x.com/ZaharaMMalik/status/2044011613422834071</t>
+          <t>https://x.com/emiratesislamic/status/2044322401052250291</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>Really struggling to get hold of @emiratesislamic I’ve called the international line and emailed and really need to get hold of someone. Please help 😭</t>
+          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
+EI + للخدمات المصرفية عبر الهاتف المتحرك
+⭐️ادخل إلى منصة "الثروات" في تطبيق + EI  للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.
+⭐️منتج متوافق مع أحكام الشريعة الإسلامية https://t.co/CZe51naJfQ</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>Really struggling to get hold of @emiratesislamic I’ve called the international line and emailed and really need to get hold of someone. Please help 😭</t>
+          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
+EI + للخدمات المصرفية عبر الهاتف المتحرك
+⭐️ادخل إلى منصة "الثروات" في تطبيق + EI  للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.
+⭐️منتج متوافق مع أحكام الشريعة الإسلامية https://t.co/CZe51naJfQ</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Really struggling to get in touch with @emiratesislamic. I've called the international line and emailed, and I really need to reach someone. Please help.</t>
+          <t>Invest in gold and silver digitally and easily on the EI+ mobile banking app.
+⭐️Access the "Wealth" platform in the EI+ mobile banking app and start investing with utmost ease and security. 
+⭐️A product compliant with Islamic law.</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Cust</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE25" s="2" t="n">
-        <v>46126.63541666666</v>
+        <v>46127.49305555555</v>
       </c>
       <c r="AF25" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
@@ -4558,7 +4574,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>I've called the international line and emailed, and I really need to reach someone. • Really struggling to get in touch with @emiratesislamic.</t>
+          <t>⭐️Access the "Wealth" platform in the EI+ mobile banking app and start investing with utmost ease and security. • Invest in gold and silver digitally and easily on the EI+ mobile banking app. • ⭐️A product compliant with Islamic law.</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -4581,69 +4597,71 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2043951228640747823</t>
+          <t>2044294656716836969</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://x.com/aswanikumartst5/status/2043951228640747823</t>
+          <t>https://x.com/emiratesislamic/status/2044294656716836969</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://x.com/aswanikumartst5</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>aswanikumartst5</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>TS Aswani Kumar</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1412710891515092994/OVnKv5t7_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>@emiratesislamic I have already cleared a personal loan and approached your Phone Banking &amp;amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp;amp; revert ASAP. Thank You.</t>
+          <t>ابدأ رحلتك نحو منزل أحلامك اليوم.
+emiratesislamic.ae/ar/Person…</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>How many days more you require to issue a NIL LIABILITY LETTER...?</t>
+          <t>ابدأ رحلتك نحو منزل أحلامك اليوم.
+&lt;a href="https://www.emiratesislamic.ae/ar/Personal-Banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=home_finance"&gt;emiratesislamic.ae/ar/Person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K26" t="b">
         <v>0</v>
       </c>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 7:15 AM UTC</t>
+          <t>Apr 15, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P26" s="2" t="n">
-        <v>46126.30208333334</v>
+        <v>46127.25</v>
       </c>
       <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/Personal-Banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=home_finance']</t>
+        </is>
+      </c>
       <c r="S26" t="n">
         <v>1</v>
       </c>
@@ -4654,7 +4672,7 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>5</v>
+        <v>127</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -4663,44 +4681,38 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>How many days more you require to issue a NIL LIABILITY LETTER...?</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>https://x.com/aswanikumartst5/status/2043951228640747823</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>@emiratesislamic I have already cleared a personal loan and approached your Phone Banking &amp;amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp;amp; revert ASAP. Thank You.</t>
-        </is>
-      </c>
+          <t>ابدأ رحلتك نحو منزل أحلامك اليوم.
+emiratesislamic.ae/ar/Person…</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>@emiratesislamic I have already cleared a personal loan and approached your Phone Banking &amp;amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp;amp; revert ASAP. Thank You.</t>
+          <t>ابدأ رحلتك نحو منزل أحلامك اليوم.
+emiratesislamic.ae/ar/Person…</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>I have already cleared a personal loan and approached your Phone Banking and WhatsApp channel for the issuance of a NIL LIABILITY LETTER, but I have not received a concrete response. It is also not feasible to obtain it through your application. Can you please check and respond as soon as possible? Thank you.</t>
+          <t>Start your journey towards your dream home today.</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Cust</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE26" s="2" t="n">
-        <v>46126.46875</v>
+        <v>46127.41666666666</v>
       </c>
       <c r="AF26" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
@@ -4714,7 +4726,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>I have already cleared a personal loan and approached your Phone Banking and WhatsApp channel for the issuance of a NIL LIABILITY LETTER, but I have not received a concrete response. • Can you please check and respond as soon as possible? • It is also not feasible to obtain it through your application.</t>
+          <t>Start your journey towards your dream home today.</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -4727,7 +4739,7 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4737,68 +4749,66 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2044076340891009154</t>
+          <t>2044294653097156714</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044076340891009154</t>
+          <t>https://x.com/emiratesislamic/status/2044294653097156714</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>attas_2010</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>محمد</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1581396792075247620/ZCrbkCda_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>موظف البنك الفرنسي قال نعطيك اعادة تمويل ويطلع لك فائض بالشخصي٧٥٠٠٠ وفعلا تحولت لي والعقاري قال يفيض لك٢٥٥٠٠٠ وسحب علي وماعاد يرد وحتى اليوم فوق ١٠ مرات احاول ارفع شكوى من التطبيق مايقبلون الشكوى 
-اصلا</t>
+          <t>من “يوماً ما” إلى يوم الانتقال!
+التمويل السكني من الإمارات الإسلامي يجعل حلم امتلاك منزلك حقيقة، مع المرونة والوضوح في كل خطوة من رحلتك.
+استمتع بحلول تمويلية مصممة خصيصاً لك، ودعم متكامل طوال الطريق، لتصبح تجربة امتلاك المنزل سلسة وميسرة.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>موظف البنك الفرنسي قال نعطيك اعادة تمويل ويطلع لك فائض بالشخصي٧٥٠٠٠ وفعلا تحولت لي والعقاري قال يفيض لك٢٥٥٠٠٠ وسحب علي وماعاد يرد وحتى اليوم فوق ١٠ مرات احاول ارفع شكوى من التطبيق مايقبلون الشكوى 
-اصلا</t>
+          <t>من “يوماً ما” إلى يوم الانتقال!
+التمويل السكني من الإمارات الإسلامي يجعل حلم امتلاك منزلك حقيقة، مع المرونة والوضوح في كل خطوة من رحلتك.
+استمتع بحلول تمويلية مصممة خصيصاً لك، ودعم متكامل طوال الطريق، لتصبح تجربة امتلاك المنزل سلسة وميسرة.</t>
         </is>
       </c>
       <c r="K27" t="b">
         <v>0</v>
       </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>['attas_2010', 'KhalidSaeedR', 'amsh75', 'alrajhibank', 'BSF_sa', 'alinma', 'BankAlbilad', 'snbalahli', 'GulfIntlBank', 'EmiratesNBD_AE', 'BankAlJazira', 'RiyadBank', 'alawwalsab', 'SAIBLIVE']</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 3:32 PM UTC</t>
+          <t>Apr 15, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P27" s="2" t="n">
-        <v>46126.64722222222</v>
+        <v>46127.25</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
@@ -4812,66 +4822,70 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>76</v>
+        <v>194</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>موظف البنك الفرنسي قال نعطيك اعادة تمويل ويطلع لك فائض بالشخصي٧٥٠٠٠ وفعلا تحولت لي والعقاري قال يفيض لك٢٥٥٠٠٠ وسحب علي وماعاد يرد وحتى اليوم فوق ١٠ مرات احاول ارفع شكوى من التطبيق مايقبلون الشكوى 
-اصلا</t>
+          <t>من “يوماً ما” إلى يوم الانتقال!
+التمويل السكني من الإمارات الإسلامي يجعل حلم امتلاك منزلك حقيقة، مع المرونة والوضوح في كل خطوة من رحلتك.
+استمتع بحلول تمويلية مصممة خصيصاً لك، ودعم متكامل طوال الطريق، لتصبح تجربة امتلاك المنزل سلسة وميسرة.</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>موظف البنك الفرنسي قال نعطيك اعادة تمويل ويطلع لك فائض بالشخصي٧٥٠٠٠ وفعلا تحولت لي والعقاري قال يفيض لك٢٥٥٠٠٠ وسحب علي وماعاد يرد وحتى اليوم فوق ١٠ مرات احاول ارفع شكوى من التطبيق مايقبلون الشكوى 
-اصلا</t>
+          <t>من “يوماً ما” إلى يوم الانتقال!
+التمويل السكني من الإمارات الإسلامي يجعل حلم امتلاك منزلك حقيقة، مع المرونة والوضوح في كل خطوة من رحلتك.
+استمتع بحلول تمويلية مصممة خصيصاً لك، ودعم متكامل طوال الطريق، لتصبح تجربة امتلاك المنزل سلسة وميسرة.</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>The French bank employee said they would give you refinancing and you would have a surplus of 75,000 in personal loans, and indeed it was transferred to me, and the real estate loan said it would give you a surplus of 255,000. They stopped responding to me, and even today I have tried to file a complaint through the app more than 10 times, but they do not accept the complaint at all.</t>
+          <t>From "one day" to moving day! 
+Emirates Islamic home financing makes your dream of owning a home a reality, with flexibility and clarity at every step of your journey. 
+Enjoy financing solutions tailored just for you, with comprehensive support along the way, making the homeownership experience smooth and accessible.</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Cust</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE27" s="2" t="n">
-        <v>46126.81388888889</v>
+        <v>46127.41666666666</v>
       </c>
       <c r="AF27" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
+          <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>They stopped responding to me, and even today I have tried to file a complaint through the app more than 10 times, but they do not accept the complaint at all.</t>
+          <t>Emirates Islamic home financing makes your dream of owning a home a reality, with flexibility and clarity at every step of your journey. • Enjoy financing solutions tailored just for you, with comprehensive support along the way, making the homeownership experience smooth and accessible. • From "one day" to moving day!</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank (ENBD)</t>
+          <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AK27" t="n">
@@ -4879,7 +4893,672 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>attas_2010, KhalidSaeedR, amsh75, alrajhibank, BSF_sa, alinma, BankAlbilad, snbalahli, GulfIntlBank, EmiratesNBD_AE, BankAlJazira, RiyadBank, alawwalsab, SAIBLIVE</t>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2044356621351149946</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://x.com/HarshGada76429/status/2044356621351149946</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://x.com/HarshGada76429</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>HarshGada76429</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Harsh Gada</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>@RBLBankCares
+@rblbank
+I have been a loyal customer for last 3yrs using your world safari credit card I have achieved the milestone but missed the redemption date by 7 days 
+Request you to send me new redemption link for 10000rs voucher or I will have to end the relationship now</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>I haven&amp;#39;t got the resolution yet 
+On technical terms you are denying me the voucher
+What about last 3 years of harassment where you guys were denying for voucher which i have earned by reaching milestone?
+&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;   be careful with tie up with
+RBL Bank</t>
+        </is>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>['HarshGada76429', 'RBLBankCares', 'rblbank']</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Apr 15, 2026 · 10:06 AM UTC</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="n">
+        <v>46127.42083333333</v>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="S28" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>8</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>I haven't got the resolution yet 
+On technical terms you are denying me the voucher
+What about last 3 years of harassment where you guys were denying for voucher which i have earned by reaching milestone?
+@EmiratesNBD_AE   be careful with tie up with
+RBL Bank</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>https://x.com/HarshGada76429/status/2044356621351149946</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>@RBLBankCares
+@rblbank
+I have been a loyal customer for last 3yrs using your world safari credit card I have achieved the milestone but missed the redemption date by 7 days 
+Request you to send me new redemption link for 10000rs voucher or I will have to end the relationship now</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>@RBLBankCares
+@rblbank
+I have been a loyal customer for last 3yrs using your world safari credit card I have achieved the milestone but missed the redemption date by 7 days 
+Request you to send me new redemption link for 10000rs voucher or I will have to end the relationship now</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>I have been a loyal customer for the last 3 years using your World Safari credit card. I have achieved the milestone but missed the redemption date by 7 days. I request you to send me a new redemption link for a 10,000 INR voucher, or I will have to end the relationship now.</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AE28" s="2" t="n">
+        <v>46127.5875</v>
+      </c>
+      <c r="AF28" s="2" t="n">
+        <v>46127</v>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>I request you to send me a new redemption link for a 10,000 INR voucher, or I will have to end the relationship now. • I have been a loyal customer for the last 3 years using your World Safari credit card. • I have achieved the milestone but missed the redemption date by 7 days.</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK28" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>HarshGada76429, RBLBankCares, rblbank</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2044369434362753181</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://x.com/iRonyForChange/status/2044369434362753181</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://x.com/iRonyForChange</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>iRonyForChange</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Preetam Chakraborty</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2032194835424423936/eNr4L0LS_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE 
+You kept pushing to take the Share Credit Card,finally I applied and then you rejected citing “internal policies” despite having higher eligibility than required.
+Now your agents are calling and saying it’s a miss &amp;amp; to resubmit documents.
+Are you serious?</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; 
+You kept pushing to take the Share Credit Card,finally I applied and then you rejected citing “internal policies” despite having higher eligibility than required.
+Now your agents are calling and saying it’s a miss &amp;amp; to resubmit documents.
+Are you serious?</t>
+        </is>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Apr 15, 2026 · 10:57 AM UTC</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="n">
+        <v>46127.45625</v>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="S29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>2</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE 
+You kept pushing to take the Share Credit Card,finally I applied and then you rejected citing “internal policies” despite having higher eligibility than required.
+Now your agents are calling and saying it’s a miss &amp; to resubmit documents.
+Are you serious?</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>https://x.com/iRonyForChange/status/2044369434362753181</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE 
+You kept pushing to take the Share Credit Card,finally I applied and then you rejected citing “internal policies” despite having higher eligibility than required.
+Now your agents are calling and saying it’s a miss &amp;amp; to resubmit documents.
+Are you serious?</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE 
+You kept pushing to take the Share Credit Card,finally I applied and then you rejected citing “internal policies” despite having higher eligibility than required.
+Now your agents are calling and saying it’s a miss &amp;amp; to resubmit documents.
+Are you serious?</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>You kept pushing me to take the Share Credit Card, and I finally applied, but you rejected it citing "internal policies" despite having higher eligibility than required. Now your agents are calling and saying it's a mistake and to resubmit documents. Are you serious?</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AE29" s="2" t="n">
+        <v>46127.62291666667</v>
+      </c>
+      <c r="AF29" s="2" t="n">
+        <v>46127</v>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>You kept pushing me to take the Share Credit Card, and I finally applied, but you rejected it citing "internal policies" despite having higher eligibility than required. • Now your agents are calling and saying it's a mistake and to resubmit documents.</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK29" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2044307778140025041</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://x.com/metakixakbar/status/2044307778140025041</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://x.com/metakixakbar</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>metakixakbar</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Akbar Syed</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1478686329114267649/s_YERTLm_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>@ENBDdeals
+Took a Takaful policy from ENBD back in 2012. 15 year policy. Was supposed to mature in 2027. Policy was issued from Aman insurances. ENBD was distributor. Being told now to contact Aman insurance directly. Aman is as good as closed. ENBD is not taking responsibility.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>&lt;a href="/ENBDdeals" title="Emirates NBD Deals"&gt;@ENBDdeals&lt;/a&gt;
+Took a Takaful policy from ENBD back in 2012. 15 year policy. Was supposed to mature in 2027. Policy was issued from Aman insurances. ENBD was distributor. Being told now to contact Aman insurance directly. Aman is as good as closed. ENBD is not taking responsibility.</t>
+        </is>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Apr 15, 2026 · 6:52 AM UTC</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="n">
+        <v>46127.28611111111</v>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>['https://x.com/ENBDdeals']</t>
+        </is>
+      </c>
+      <c r="S30" t="n">
+        <v>2</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>10</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>@ENBDdeals
+Took a Takaful policy from ENBD back in 2012. 15 year policy. Was supposed to mature in 2027. Policy was issued from Aman insurances. ENBD was distributor. Being told now to contact Aman insurance directly. Aman is as good as closed. ENBD is not taking responsibility.</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>https://x.com/metakixakbar/status/2044307778140025041</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>@ENBDdeals
+Took a Takaful policy from ENBD back in 2012. 15 year policy. Was supposed to mature in 2027. Policy was issued from Aman insurances. ENBD was distributor. Being told now to contact Aman insurance directly. Aman is as good as closed. ENBD is not taking responsibility.</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>@ENBDdeals
+Took a Takaful policy from ENBD back in 2012. 15 year policy. Was supposed to mature in 2027. Policy was issued from Aman insurances. ENBD was distributor. Being told now to contact Aman insurance directly. Aman is as good as closed. ENBD is not taking responsibility.</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>I took a Takaful policy from ENBD back in 2012. It is a 15-year policy that was supposed to mature in 2027. The policy was issued by Aman Insurance, with ENBD as the distributor. I am now being told to contact Aman Insurance directly, but Aman is practically closed. ENBD is not taking responsibility.</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AE30" s="2" t="n">
+        <v>46127.45277777778</v>
+      </c>
+      <c r="AF30" s="2" t="n">
+        <v>46127</v>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>I took a Takaful policy from ENBD back in 2012. • It is a 15-year policy that was supposed to mature in 2027. • I am now being told to contact Aman Insurance directly, but Aman is practically closed.</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK30" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2044301025142513927</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://x.com/oras_2030/status/2044301025142513927</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://x.com/oras_2030</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>oras_2030</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>oras2030</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2043694467731886080/mS-jeUsJ_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA اسوء تجربة من البنك في خدمة العملاء ولا ادارة التحصيل الي اسلوبه زي الزفت تخيلو طلبت خطاب عدم مومانعه  من شراء المديونية لك وشو يسوي البنك يتصل على البنك الثاني ويتاكد متى تتغير النسبه ويتاخر الطلب لي ثلاث ايام وانا اتصل على ادارة التحصيل وخدمه العملاء اخر شي</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>هل تنصح اخ علي@ انقل راتبي عندهم عشان قرض شخصي لان نسبتهم اقل من البنوك الاخرى؟</t>
+        </is>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>['AliAhmedk66633', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Apr 15, 2026 · 6:25 AM UTC</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>46127.26736111111</v>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>20</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>هل تنصح اخ علي@ انقل راتبي عندهم عشان قرض شخصي لان نسبتهم اقل من البنوك الاخرى؟</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>https://x.com/oras_2030/status/2044301025142513927</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA اسوء تجربة من البنك في خدمة العملاء ولا ادارة التحصيل الي اسلوبه زي الزفت تخيلو طلبت خطاب عدم مومانعه  من شراء المديونية لك وشو يسوي البنك يتصل على البنك الثاني ويتاكد متى تتغير النسبه ويتاخر الطلب لي ثلاث ايام وانا اتصل على ادارة التحصيل وخدمه العملاء اخر شي</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA اسوء تجربة من البنك في خدمة العملاء ولا ادارة التحصيل الي اسلوبه زي الزفت تخيلو طلبت خطاب عدم مومانعه  من شراء المديونية لك وشو يسوي البنك يتصل على البنك الثاني ويتاكد متى تتغير النسبه ويتاخر الطلب لي ثلاث ايام وانا اتصل على ادارة التحصيل وخدمه العملاء اخر شي</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>The worst experience with the bank in customer service and the collection management is terrible. Imagine I requested a letter of no objection to purchase the debt, and what does the bank do? It calls the other bank to confirm when the rate changes, and the request is delayed for three days while I keep calling the collection management and customer service.</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AE31" s="2" t="n">
+        <v>46127.43402777778</v>
+      </c>
+      <c r="AF31" s="2" t="n">
+        <v>46127</v>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>It calls the other bank to confirm when the rate changes, and the request is delayed for three days while I keep calling the collection management and customer service. • The worst experience with the bank in customer service and the collection management is terrible. • Imagine I requested a letter of no objection to purchase the debt, and what does the bank do?</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK31" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>AliAhmedk66633, EmiratesNBD_KSA</t>
         </is>
       </c>
     </row>

--- a/check2.xlsx
+++ b/check2.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL51"/>
+  <dimension ref="A1:AL52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1084,7 +1084,7 @@
 2. Comment A LOT with the tags #iFoodNoBBB26 and #BBB26 responding to this tweet.
 The @ with THE MOST COMMENTS on this post is the winner!
 Let's go? It's on! Tomorrow we will have the champion.
-Check the rules in the bio.
+Check the regulations in the bio.
 Valid comments until 04/16/2026 at 6:30 PM.</t>
         </is>
       </c>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>You can own your dream car, whether new or used. We can finance it for you with the car leasing financing from Emirates NBD Bank.</t>
+          <t>You can own the car of your dreams, whether new or used. We can finance it for you with the car leasing financing from Emirates NBD Bank.</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>We can finance it for you with the car leasing financing from Emirates NBD Bank. • You can own your dream car, whether new or used.</t>
+          <t>We can finance it for you with the car leasing financing from Emirates NBD Bank. • You can own the car of your dreams, whether new or used.</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Not all types of interest are the same — some are simple. Can you name this type? Share your answer with us.</t>
+          <t>Not all types of interest are the same — some are simple. Can you name this type? Share your answer.</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Not all types of interest are the same — some are simple. • Share your answer with us.</t>
+          <t>Not all types of interest are the same — some are simple.</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -2151,9 +2151,9 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>استثمر في الأسهم و الصكوك و السندات و المعادن الثمينة (الذهب و الفضة)، كل ذلك من خلال تطبيق ENBD X.
-فرص استثمارية لا حصر لها، ابدأ الاستثمار اليوم
-https://t.co/6sm1UoslrI https://t.co/XdDf9aQ6x7</t>
+          <t>Not all interests work the same way — some are simple.
+Can you name this type? Comment your answer.
+#ENBDRiddleOfTheWeek #MoneyBasics #LearnFinance https://t.co/05i14Flw98</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -2218,21 +2218,21 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>استثمر في الأسهم و الصكوك و السندات و المعادن الثمينة (الذهب و الفضة)، كل ذلك من خلال تطبيق ENBD X.
-فرص استثمارية لا حصر لها، ابدأ الاستثمار اليوم
-https://t.co/6sm1UoslrI https://t.co/XdDf9aQ6x7</t>
+          <t>Not all interests work the same way — some are simple.
+Can you name this type? Comment your answer.
+#ENBDRiddleOfTheWeek #MoneyBasics #LearnFinance https://t.co/05i14Flw98</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>استثمر في الأسهم و الصكوك و السندات و المعادن الثمينة (الذهب و الفضة)، كل ذلك من خلال تطبيق ENBD X.
-فرص استثمارية لا حصر لها، ابدأ الاستثمار اليوم
-https://t.co/6sm1UoslrI https://t.co/XdDf9aQ6x7</t>
+          <t>Not all interests work the same way — some are simple.
+Can you name this type? Comment your answer.
+#ENBDRiddleOfTheWeek #MoneyBasics #LearnFinance https://t.co/05i14Flw98</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Invest in stocks, sukuk, bonds, and precious metals (gold and silver), all through the ENBD X app. Endless investment opportunities, start investing today.</t>
+          <t>Not all interests work the same way — some are simple. Can you name this type? Comment your answer.</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE11" s="2" t="n">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Invest in stocks, sukuk, bonds, and precious metals (gold and silver), all through the ENBD X app. • Endless investment opportunities, start investing today.</t>
+          <t>Not all interests work the same way — some are simple.</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2044734491336282349</t>
+          <t>2044733124177743954</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://x.com/masryeng/status/2044734491336282349</t>
+          <t>https://x.com/masryeng/status/2044733124177743954</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2317,15 +2317,14 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Not all interests work the same way — some are simple.
-Can you name this type? Comment your answer.
-#ENBDRiddleOfTheWeek #MoneyBasics #LearnFinance https://t.co/05i14Flw98</t>
+          <t>Manage your wealth with expertise you can trust. Contact us today https://t.co/XmTzVbwpLQ
+#EmiratesNBD #WealthManagement https://t.co/1RVFBUcixf</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>نزلتوا غرامه غير مستحقه علي بطاقة فيزا الائتمانية ورفعت ايميل بالمشكلة ولا تن الرد 
-لا انصح بالتعامل معهم</t>
+          <t>عندي بطاقه ائتمانية ونزلتوا عليها مبلغ غرامه غير مستحقه ورفعت لكم ايميل ولا ردتوا علي الايميل 
+لا انصح بالتعامل معاهم</t>
         </is>
       </c>
       <c r="K12" t="b">
@@ -2344,16 +2343,16 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Apr 16, 2026 · 11:07 AM UTC</t>
+          <t>Apr 16, 2026 · 11:02 AM UTC</t>
         </is>
       </c>
       <c r="P12" s="2" t="n">
-        <v>46128.46319444444</v>
+        <v>46128.45972222222</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -2362,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -2371,32 +2370,30 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>نزلتوا غرامه غير مستحقه علي بطاقة فيزا الائتمانية ورفعت ايميل بالمشكلة ولا تن الرد 
-لا انصح بالتعامل معهم</t>
+          <t>عندي بطاقه ائتمانية ونزلتوا عليها مبلغ غرامه غير مستحقه ورفعت لكم ايميل ولا ردتوا علي الايميل 
+لا انصح بالتعامل معاهم</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>https://x.com/masryeng/status/2044734491336282349</t>
+          <t>https://x.com/masryeng/status/2044733124177743954</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>Not all interests work the same way — some are simple.
-Can you name this type? Comment your answer.
-#ENBDRiddleOfTheWeek #MoneyBasics #LearnFinance https://t.co/05i14Flw98</t>
+          <t>Manage your wealth with expertise you can trust. Contact us today https://t.co/XmTzVbwpLQ
+#EmiratesNBD #WealthManagement https://t.co/1RVFBUcixf</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Not all interests work the same way — some are simple.
-Can you name this type? Comment your answer.
-#ENBDRiddleOfTheWeek #MoneyBasics #LearnFinance https://t.co/05i14Flw98</t>
+          <t>Manage your wealth with expertise you can trust. Contact us today https://t.co/XmTzVbwpLQ
+#EmiratesNBD #WealthManagement https://t.co/1RVFBUcixf</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Not all interests work the same way — some are simple. Can you name this type? Comment your answer.</t>
+          <t>Manage your wealth with expertise you can trust. Contact us today.</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2410,7 +2407,7 @@
         </is>
       </c>
       <c r="AE12" s="2" t="n">
-        <v>46128.62986111111</v>
+        <v>46128.62638888889</v>
       </c>
       <c r="AF12" s="2" t="n">
         <v>46128</v>
@@ -2427,7 +2424,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Not all interests work the same way — some are simple.</t>
+          <t>Manage your wealth with expertise you can trust.</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2450,56 +2447,50 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2044733124177743954</t>
+          <t>2044730856070144064</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://x.com/masryeng/status/2044733124177743954</t>
+          <t>https://x.com/dar_global/status/2044730856070144064</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://x.com/masryeng</t>
+          <t>https://x.com/dar_global</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>masryeng</t>
+          <t>dar_global</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El-Sayed El-Masry</t>
+          <t>DarGlobal</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1768318685356130304/iD9SmaJ3_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1904290533372985344/OQZ0hS5Q_bigger.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Manage your wealth with expertise you can trust. Contact us today https://t.co/XmTzVbwpLQ
-#EmiratesNBD #WealthManagement https://t.co/1RVFBUcixf</t>
+          <t>Emirates NBD successfully executes USD 250 Million Syndicated Term Loan facility for Darglobal, Accelerating Global Growth and Expansion https://t.co/EnXMEkr31m https://t.co/CkhOYQYv3e</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>عندي بطاقه ائتمانية ونزلتوا عليها مبلغ غرامه غير مستحقه ورفعت لكم ايميل ولا ردتوا علي الايميل 
-لا انصح بالتعامل معاهم</t>
+          <t>Emirates NBD successfully executes USD 250 Million Syndicated Term Loan facility for Darglobal, Accelerating Global Growth and Expansion &lt;a href="https://darglobal.co.uk/press/emirates-nbd-usd-250m-syndicated-loan-dar-global-expansion-uae"&gt;darglobal.co.uk/press/emirat…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K13" t="b">
         <v>0</v>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>15h</t>
@@ -2507,25 +2498,29 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Apr 16, 2026 · 11:02 AM UTC</t>
+          <t>Apr 16, 2026 · 10:53 AM UTC</t>
         </is>
       </c>
       <c r="P13" s="2" t="n">
-        <v>46128.45972222222</v>
+        <v>46128.45347222222</v>
       </c>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>['https://darglobal.co.uk/press/emirates-nbd-usd-250m-syndicated-loan-dar-global-expansion-uae']</t>
+        </is>
+      </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -2534,30 +2529,27 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>عندي بطاقه ائتمانية ونزلتوا عليها مبلغ غرامه غير مستحقه ورفعت لكم ايميل ولا ردتوا علي الايميل 
-لا انصح بالتعامل معاهم</t>
+          <t>Emirates NBD successfully executes USD 250 Million Syndicated Term Loan facility for Darglobal, Accelerating Global Growth and Expansion darglobal.co.uk/press/emirat…</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>https://x.com/masryeng/status/2044733124177743954</t>
+          <t>https://x.com/dar_global/status/2044730856070144064</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>Manage your wealth with expertise you can trust. Contact us today https://t.co/XmTzVbwpLQ
-#EmiratesNBD #WealthManagement https://t.co/1RVFBUcixf</t>
+          <t>Emirates NBD successfully executes USD 250 Million Syndicated Term Loan facility for Darglobal, Accelerating Global Growth and Expansion https://t.co/EnXMEkr31m https://t.co/CkhOYQYv3e</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Manage your wealth with expertise you can trust. Contact us today https://t.co/XmTzVbwpLQ
-#EmiratesNBD #WealthManagement https://t.co/1RVFBUcixf</t>
+          <t>Emirates NBD successfully executes USD 250 Million Syndicated Term Loan facility for Darglobal, Accelerating Global Growth and Expansion https://t.co/EnXMEkr31m https://t.co/CkhOYQYv3e</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Manage your wealth with expertise you can trust. Contact us today.</t>
+          <t>Emirates NBD successfully executes a USD 250 million syndicated term loan facility for Darglobal, accelerating global growth and expansion.</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2567,11 +2559,11 @@
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE13" s="2" t="n">
-        <v>46128.62638888889</v>
+        <v>46128.62013888889</v>
       </c>
       <c r="AF13" s="2" t="n">
         <v>46128</v>
@@ -2588,7 +2580,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Manage your wealth with expertise you can trust.</t>
+          <t>Emirates NBD successfully executes a USD 250 million syndicated term loan facility for Darglobal, accelerating global growth and expansion.</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2601,7 +2593,7 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2611,192 +2603,36 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2044730856070144064</t>
+          <t>2044728681705390440</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://x.com/dar_global/status/2044730856070144064</t>
+          <t>https://x.com/AyshaMoham64638/status/2044728681705390440</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://x.com/dar_global</t>
+          <t>https://x.com/AyshaMoham64638</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>dar_global</t>
+          <t>AyshaMoham64638</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>DarGlobal</t>
+          <t>Aysha Mohammad</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1904290533372985344/OQZ0hS5Q_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1676392392138579982/dZRAYQV-_bigger.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
-        <is>
-          <t>Emirates NBD successfully executes USD 250 Million Syndicated Term Loan facility for Darglobal, Accelerating Global Growth and Expansion https://t.co/EnXMEkr31m https://t.co/CkhOYQYv3e</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Emirates NBD successfully executes USD 250 Million Syndicated Term Loan facility for Darglobal, Accelerating Global Growth and Expansion &lt;a href="https://darglobal.co.uk/press/emirates-nbd-usd-250m-syndicated-loan-dar-global-expansion-uae"&gt;darglobal.co.uk/press/emirat…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K14" t="b">
-        <v>0</v>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Apr 16, 2026 · 10:53 AM UTC</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="n">
-        <v>46128.45347222222</v>
-      </c>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>['https://darglobal.co.uk/press/emirates-nbd-usd-250m-syndicated-loan-dar-global-expansion-uae']</t>
-        </is>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>82</v>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>Emirates NBD successfully executes USD 250 Million Syndicated Term Loan facility for Darglobal, Accelerating Global Growth and Expansion darglobal.co.uk/press/emirat…</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>https://x.com/dar_global/status/2044730856070144064</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Emirates NBD successfully executes USD 250 Million Syndicated Term Loan facility for Darglobal, Accelerating Global Growth and Expansion https://t.co/EnXMEkr31m https://t.co/CkhOYQYv3e</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Emirates NBD successfully executes USD 250 Million Syndicated Term Loan facility for Darglobal, Accelerating Global Growth and Expansion https://t.co/EnXMEkr31m https://t.co/CkhOYQYv3e</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Emirates NBD successfully executes a USD 250 million syndicated term loan facility for Darglobal, accelerating global growth and expansion.</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="AE14" s="2" t="n">
-        <v>46128.62013888889</v>
-      </c>
-      <c r="AF14" s="2" t="n">
-        <v>46128</v>
-      </c>
-      <c r="AG14" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Emirates NBD successfully executes a USD 250 million syndicated term loan facility for Darglobal, accelerating global growth and expansion.</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK14" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2044728681705390440</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>https://x.com/AyshaMoham64638/status/2044728681705390440</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>https://x.com/AyshaMoham64638</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AyshaMoham64638</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Aysha Mohammad</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1676392392138579982/dZRAYQV-_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
         <is>
           <t>Three messages say your Emirates ID or residence visa needs to be renewed. 
 Two are genuine and one is a trap designed to steal your data. Can you spot the fake message? 
@@ -2809,63 +2645,63 @@
  #متحدون_ضد_الاحتيال</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>SMS2 .</t>
         </is>
       </c>
-      <c r="K15" t="b">
-        <v>0</v>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>15h</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>Apr 16, 2026 · 10:44 AM UTC</t>
         </is>
       </c>
-      <c r="P15" s="2" t="n">
+      <c r="P14" s="2" t="n">
         <v>46128.44722222222</v>
       </c>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="inlineStr">
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SMS2 .</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>https://x.com/AyshaMoham64638/status/2044728681705390440</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>Three messages say your Emirates ID or residence visa needs to be renewed. 
 Two are genuine and one is a trap designed to steal your data. Can you spot the fake message? 
@@ -2878,7 +2714,7 @@
  #متحدون_ضد_الاحتيال</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>Three messages say your Emirates ID or residence visa needs to be renewed. 
 Two are genuine and one is a trap designed to steal your data. Can you spot the fake message? 
@@ -2891,7 +2727,7 @@
  #متحدون_ضد_الاحتيال</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>Three messages say your Emirates ID or residence visa needs to be renewed. 
 Two are genuine and one is a trap designed to steal your data. Can you spot the fake message? 
@@ -2899,6 +2735,162 @@
 #UnitedAgainstFraud</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE14" s="2" t="n">
+        <v>46128.61388888889</v>
+      </c>
+      <c r="AF14" s="2" t="n">
+        <v>46128</v>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Share your answer in the comments, put your scam detection skills to the test and stand the chance to win AED 2,000. • Three messages say your Emirates ID or residence visa needs to be renewed. • Two are genuine and one is a trap designed to steal your data.</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK14" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2044728654954111007</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://x.com/AyshaMoham64638/status/2044728654954111007</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://x.com/AyshaMoham64638</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AyshaMoham64638</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Aysha Mohammad</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1676392392138579982/dZRAYQV-_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE SMS2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>SMS2</t>
+        </is>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Apr 16, 2026 · 10:44 AM UTC</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="n">
+        <v>46128.44722222222</v>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>2</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>SMS2</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>https://x.com/AyshaMoham64638/status/2044728654954111007</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE SMS2</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE SMS2</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE SMS2</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr">
         <is>
           <t>Cust</t>
@@ -2927,7 +2919,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Share your answer in the comments, put your scam detection skills to the test and stand the chance to win AED 2,000. • Three messages say your Emirates ID or residence visa needs to be renewed. • Two are genuine and one is a trap designed to steal your data.</t>
+          <t>@EmiratesNBD_AE SMS2</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -2950,192 +2942,36 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2044728654954111007</t>
+          <t>2044721846457655694</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://x.com/AyshaMoham64638/status/2044728654954111007</t>
+          <t>https://x.com/FintechGate1/status/2044721846457655694</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://x.com/AyshaMoham64638</t>
+          <t>https://x.com/FintechGate1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AyshaMoham64638</t>
+          <t>FintechGate1</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aysha Mohammad</t>
+          <t>FinTech Gate-بوابة التكنولوجيا المالية</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1676392392138579982/dZRAYQV-_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1630704388531470336/_2WZb_12_bigger.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE SMS2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>SMS2</t>
-        </is>
-      </c>
-      <c r="K16" t="b">
-        <v>0</v>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Apr 16, 2026 · 10:44 AM UTC</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="n">
-        <v>46128.44722222222</v>
-      </c>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>2</v>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>SMS2</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>https://x.com/AyshaMoham64638/status/2044728654954111007</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE SMS2</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE SMS2</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE SMS2</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE16" s="2" t="n">
-        <v>46128.61388888889</v>
-      </c>
-      <c r="AF16" s="2" t="n">
-        <v>46128</v>
-      </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE SMS2</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK16" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>EmiratesNBD_AE</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2044721846457655694</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>https://x.com/FintechGate1/status/2044721846457655694</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>https://x.com/FintechGate1</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>FintechGate1</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>FinTech Gate-بوابة التكنولوجيا المالية</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1630704388531470336/_2WZb_12_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
         <is>
           <t>«الإمارات دبي الوطني» ينفذ تسهيلات قرض مشترك بقيمة 250 مليون دولار لصالح «دار جلوبال»
 https://t.co/t5ea8OOIgX | التفاصيل 
@@ -3145,7 +2981,7 @@
 #الإمارات_دبي_الوطني #دار_جلوبال https://t.co/o7GYOB2HP9</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>«الإمارات دبي الوطني» ينفذ تسهيلات قرض مشترك بقيمة 250 مليون دولار لصالح «دار جلوبال»
 &lt;a href="https://fintechgate.net/8hpf"&gt;fintechgate.net/8hpf&lt;/a&gt; | التفاصيل 
@@ -3155,48 +2991,48 @@
 &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_دبي_الوطني"&gt;#الإمارات_دبي_الوطني&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23دار_جلوبال"&gt;#دار_جلوبال&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K17" t="b">
-        <v>0</v>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
         <is>
           <t>16h</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>Apr 16, 2026 · 10:17 AM UTC</t>
         </is>
       </c>
-      <c r="P17" s="2" t="n">
+      <c r="P16" s="2" t="n">
         <v>46128.42847222222</v>
       </c>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr">
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
         <is>
           <t>['https://fintechgate.net/8hpf', 'https://x.com/EmiratesNBD_AE', 'https://x.com/dar_global', 'https://x.com/search?f=tweets&amp;q=%23fintech_gate', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_دبي_الوطني', 'https://x.com/search?f=tweets&amp;q=%23دار_جلوبال']</t>
         </is>
       </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
         <v>1</v>
       </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
         <v>63</v>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>«الإمارات دبي الوطني» ينفذ تسهيلات قرض مشترك بقيمة 250 مليون دولار لصالح «دار جلوبال»
 fintechgate.net/8hpf | التفاصيل 
@@ -3206,12 +3042,12 @@
 #الإمارات_دبي_الوطني #دار_جلوبال</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>https://x.com/FintechGate1/status/2044721846457655694</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>«الإمارات دبي الوطني» ينفذ تسهيلات قرض مشترك بقيمة 250 مليون دولار لصالح «دار جلوبال»
 https://t.co/t5ea8OOIgX | التفاصيل 
@@ -3221,7 +3057,7 @@
 #الإمارات_دبي_الوطني #دار_جلوبال https://t.co/o7GYOB2HP9</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>«الإمارات دبي الوطني» ينفذ تسهيلات قرض مشترك بقيمة 250 مليون دولار لصالح «دار جلوبال»
 https://t.co/t5ea8OOIgX | التفاصيل 
@@ -3231,9 +3067,175 @@
 #الإمارات_دبي_الوطني #دار_جلوبال https://t.co/o7GYOB2HP9</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>Emirates NBD is implementing a syndicated loan facility worth $250 million for Dar Global.</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE16" s="2" t="n">
+        <v>46128.59513888889</v>
+      </c>
+      <c r="AF16" s="2" t="n">
+        <v>46128</v>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Emirates NBD is implementing a syndicated loan facility worth $250 million for Dar Global.</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK16" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2044715070912188821</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://x.com/GCCBusinessNews/status/2044715070912188821</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://x.com/GCCBusinessNews</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>GCCBusinessNews</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>GCC Business News</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1253796411872862212/h2Q8-9rJ_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Dubai Holding Real Estate and Emirates NBD have signed an MoU to introduce integrated mortgage financing for off-plan developments in Dubai.
+https://t.co/7Rqdx9rNls
+#SaudiArabia #DigitalTransformation #DGA #GovTech #Innovation  #GCCBusinessNews @dubaiholding  @EmiratesNBD_AE https://t.co/SdUcJuRdBY</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Dubai Holding Real Estate and Emirates NBD have signed an MoU to introduce integrated mortgage financing for off-plan developments in Dubai.
+&lt;a href="https://www.gccbusinessnews.com/dubai-holding-emirates-nbd-mortgage-deal/"&gt;gccbusinessnews.com/dubai-ho…&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23SaudiArabia"&gt;#SaudiArabia&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23DigitalTransformation"&gt;#DigitalTransformation&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23DGA"&gt;#DGA&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23GovTech"&gt;#GovTech&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Innovation"&gt;#Innovation&lt;/a&gt;  &lt;a href="/search?f=tweets&amp;amp;q=%23GCCBusinessNews"&gt;#GCCBusinessNews&lt;/a&gt; &lt;a href="/dubaiholding" title="Dubai Holding"&gt;@dubaiholding&lt;/a&gt;  &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Apr 16, 2026 · 9:50 AM UTC</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="n">
+        <v>46128.40972222222</v>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>['https://www.gccbusinessnews.com/dubai-holding-emirates-nbd-mortgage-deal/', 'https://x.com/search?f=tweets&amp;q=%23SaudiArabia', 'https://x.com/search?f=tweets&amp;q=%23DigitalTransformation', 'https://x.com/search?f=tweets&amp;q=%23DGA', 'https://x.com/search?f=tweets&amp;q=%23GovTech', 'https://x.com/search?f=tweets&amp;q=%23Innovation', 'https://x.com/search?f=tweets&amp;q=%23GCCBusinessNews', 'https://x.com/dubaiholding', 'https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>24</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Dubai Holding Real Estate and Emirates NBD have signed an MoU to introduce integrated mortgage financing for off-plan developments in Dubai.
+gccbusinessnews.com/dubai-ho…
+#SaudiArabia #DigitalTransformation #DGA #GovTech #Innovation  #GCCBusinessNews @dubaiholding  @EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>https://x.com/GCCBusinessNews/status/2044715070912188821</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Dubai Holding Real Estate and Emirates NBD have signed an MoU to introduce integrated mortgage financing for off-plan developments in Dubai.
+https://t.co/7Rqdx9rNls
+#SaudiArabia #DigitalTransformation #DGA #GovTech #Innovation  #GCCBusinessNews @dubaiholding  @EmiratesNBD_AE https://t.co/SdUcJuRdBY</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Dubai Holding Real Estate and Emirates NBD have signed an MoU to introduce integrated mortgage financing for off-plan developments in Dubai.
+https://t.co/7Rqdx9rNls
+#SaudiArabia #DigitalTransformation #DGA #GovTech #Innovation  #GCCBusinessNews @dubaiholding  @EmiratesNBD_AE https://t.co/SdUcJuRdBY</t>
+        </is>
+      </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Emirates NBD implements a syndicated loan facility worth $250 million for Dar Global.</t>
+          <t>Dubai Holding Real Estate and Emirates NBD have signed a Memorandum of Understanding to introduce integrated mortgage financing for off-plan developments in Dubai.</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -3247,7 +3249,7 @@
         </is>
       </c>
       <c r="AE17" s="2" t="n">
-        <v>46128.59513888889</v>
+        <v>46128.57638888889</v>
       </c>
       <c r="AF17" s="2" t="n">
         <v>46128</v>
@@ -3264,7 +3266,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Emirates NBD implements a syndicated loan facility worth $250 million for Dar Global.</t>
+          <t>Dubai Holding Real Estate and Emirates NBD have signed a Memorandum of Understanding to introduce integrated mortgage financing for off-plan developments in Dubai.</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -3287,208 +3289,42 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2044715070912188821</t>
+          <t>2044709886311985369</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://x.com/GCCBusinessNews/status/2044715070912188821</t>
+          <t>https://x.com/OMFIF/status/2044709886311985369</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://x.com/GCCBusinessNews</t>
+          <t>https://x.com/OMFIF</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>GCCBusinessNews</t>
+          <t>OMFIF</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>GCC Business News</t>
+          <t>OMFIF</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1253796411872862212/h2Q8-9rJ_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1171002953228046337/H7K26AQF_bigger.png</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Dubai Holding Real Estate and Emirates NBD have signed an MoU to introduce integrated mortgage financing for off-plan developments in Dubai.
-https://t.co/7Rqdx9rNls
-#SaudiArabia #DigitalTransformation #DGA #GovTech #Innovation  #GCCBusinessNews @dubaiholding  @EmiratesNBD_AE https://t.co/SdUcJuRdBY</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Dubai Holding Real Estate and Emirates NBD have signed an MoU to introduce integrated mortgage financing for off-plan developments in Dubai.
-&lt;a href="https://www.gccbusinessnews.com/dubai-holding-emirates-nbd-mortgage-deal/"&gt;gccbusinessnews.com/dubai-ho…&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23SaudiArabia"&gt;#SaudiArabia&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23DigitalTransformation"&gt;#DigitalTransformation&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23DGA"&gt;#DGA&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23GovTech"&gt;#GovTech&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Innovation"&gt;#Innovation&lt;/a&gt;  &lt;a href="/search?f=tweets&amp;amp;q=%23GCCBusinessNews"&gt;#GCCBusinessNews&lt;/a&gt; &lt;a href="/dubaiholding" title="Dubai Holding"&gt;@dubaiholding&lt;/a&gt;  &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>16h</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Apr 16, 2026 · 9:50 AM UTC</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="n">
-        <v>46128.40972222222</v>
-      </c>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>['https://www.gccbusinessnews.com/dubai-holding-emirates-nbd-mortgage-deal/', 'https://x.com/search?f=tweets&amp;q=%23SaudiArabia', 'https://x.com/search?f=tweets&amp;q=%23DigitalTransformation', 'https://x.com/search?f=tweets&amp;q=%23DGA', 'https://x.com/search?f=tweets&amp;q=%23GovTech', 'https://x.com/search?f=tweets&amp;q=%23Innovation', 'https://x.com/search?f=tweets&amp;q=%23GCCBusinessNews', 'https://x.com/dubaiholding', 'https://x.com/EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>24</v>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>Dubai Holding Real Estate and Emirates NBD have signed an MoU to introduce integrated mortgage financing for off-plan developments in Dubai.
-gccbusinessnews.com/dubai-ho…
-#SaudiArabia #DigitalTransformation #DGA #GovTech #Innovation  #GCCBusinessNews @dubaiholding  @EmiratesNBD_AE</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>https://x.com/GCCBusinessNews/status/2044715070912188821</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Dubai Holding Real Estate and Emirates NBD have signed an MoU to introduce integrated mortgage financing for off-plan developments in Dubai.
-https://t.co/7Rqdx9rNls
-#SaudiArabia #DigitalTransformation #DGA #GovTech #Innovation  #GCCBusinessNews @dubaiholding  @EmiratesNBD_AE https://t.co/SdUcJuRdBY</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Dubai Holding Real Estate and Emirates NBD have signed an MoU to introduce integrated mortgage financing for off-plan developments in Dubai.
-https://t.co/7Rqdx9rNls
-#SaudiArabia #DigitalTransformation #DGA #GovTech #Innovation  #GCCBusinessNews @dubaiholding  @EmiratesNBD_AE https://t.co/SdUcJuRdBY</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Dubai Holding Real Estate and Emirates NBD have signed a Memorandum of Understanding to introduce integrated mortgage financing for off-plan developments in Dubai.</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="AE18" s="2" t="n">
-        <v>46128.57638888889</v>
-      </c>
-      <c r="AF18" s="2" t="n">
-        <v>46128</v>
-      </c>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Dubai Holding Real Estate and Emirates NBD have signed a Memorandum of Understanding to introduce integrated mortgage financing for off-plan developments in Dubai.</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK18" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2044709886311985369</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>https://x.com/OMFIF/status/2044709886311985369</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>https://x.com/OMFIF</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>OMFIF</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>OMFIF</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1171002953228046337/H7K26AQF_bigger.png</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
           <t>In 1989 #ViktorOrbán launched himself into the centre of Hungarian politics with an anti-Russia, pro-liberal speech. However, political support for Orbán has dwindled in the last few years, and this year’s election saw challenger #PéterMagyar win.
 https://t.co/awg2X83gbi https://t.co/myWYSUumtU</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Last year, on OMFIF’s &lt;a href="/search?f=tweets&amp;amp;q=%23GenderBalanceIndex"&gt;#GenderBalanceIndex&lt;/a&gt;, the least‑scoring commercial banks were:
 &lt;a href="/HDFC_Bank" title="HDFC Bank"&gt;@HDFC_Bank&lt;/a&gt; 
@@ -3499,48 +3335,48 @@
 Want to see how commercial banks performed over the last 5 years? Explore it here: &lt;a href="https://app.powerbi.com/view?r=eyJrIjoiZGYwZThkNWItYjdjMC00NTNmLWE0OTctYjA4ZTZhYTUzYjYxIiwidCI6ImNkZTEwNjE3LTZlNzMtNGIxYS1iYjY4LWQzOTViNDgzNjk4YiJ9"&gt;app.powerbi.com/view?r=eyJrI…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K19" t="b">
-        <v>0</v>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
         <is>
           <t>17h</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>Apr 16, 2026 · 9:30 AM UTC</t>
         </is>
       </c>
-      <c r="P19" s="2" t="n">
+      <c r="P18" s="2" t="n">
         <v>46128.39583333334</v>
       </c>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr">
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
         <is>
           <t>['https://x.com/search?f=tweets&amp;q=%23GenderBalanceIndex', 'https://x.com/HDFC_Bank', 'https://x.com/EmiratesNBD_AE', 'https://x.com/Bancolombia', 'https://x.com/mizuhobank', 'https://x.com/Bradesco', 'https://app.powerbi.com/view?r=eyJrIjoiZGYwZThkNWItYjdjMC00NTNmLWE0OTctYjA4ZTZhYTUzYjYxIiwidCI6ImNkZTEwNjE3LTZlNzMtNGIxYS1iYjY4LWQzOTViNDgzNjk4YiJ9']</t>
         </is>
       </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
         <v>1</v>
       </c>
-      <c r="V19" t="n">
+      <c r="V18" t="n">
         <v>168</v>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>Last year, on OMFIF’s #GenderBalanceIndex, the least‑scoring commercial banks were:
 @HDFC_Bank 
@@ -3551,26 +3387,185 @@
 Want to see how commercial banks performed over the last 5 years? Explore it here: app.powerbi.com/view?r=eyJrI…</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>https://x.com/OMFIF/status/2044709886311985369</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>In 1989 #ViktorOrbán launched himself into the centre of Hungarian politics with an anti-Russia, pro-liberal speech. However, political support for Orbán has dwindled in the last few years, and this year’s election saw challenger #PéterMagyar win.
 https://t.co/awg2X83gbi https://t.co/myWYSUumtU</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>In 1989 #ViktorOrbán launched himself into the centre of Hungarian politics with an anti-Russia, pro-liberal speech. However, political support for Orbán has dwindled in the last few years, and this year’s election saw challenger #PéterMagyar win.
 https://t.co/awg2X83gbi https://t.co/myWYSUumtU</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>In 1989, Viktor Orbán launched himself into the center of Hungarian politics with an anti-Russia, pro-liberal speech. However, political support for Orbán has dwindled in the last few years, and this year’s election saw challenger Péter Magyar win.</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE18" s="2" t="n">
+        <v>46128.5625</v>
+      </c>
+      <c r="AF18" s="2" t="n">
+        <v>46128</v>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>In 1989, Viktor Orbán launched himself into the center of Hungarian politics with an anti-Russia, pro-liberal speech. • However, political support for Orbán has dwindled in the last few years, and this year’s election saw challenger Péter Magyar win.</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK18" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2044694547498696848</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://x.com/msa3474/status/2044694547498696848</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://x.com/msa3474</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>msa3474</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>AHMARI</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1943001907854802944/sB6fjZIf_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>سافر لوجهتك، وقسط دفعاتها مع 0% هامش ربح ✈️
+على طيران الإمارات باستخدام بطاقات #بنك_الإمارات_دبي_الوطني الائتمانية</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>الرسائل الخاصه مقفله لديكم</t>
+        </is>
+      </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Apr 16, 2026 · 8:29 AM UTC</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="n">
+        <v>46128.35347222222</v>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>11</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>الرسائل الخاصه مقفله لديكم</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>https://x.com/msa3474/status/2044694547498696848</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>سافر لوجهتك، وقسط دفعاتها مع 0% هامش ربح ✈️
+على طيران الإمارات باستخدام بطاقات #بنك_الإمارات_دبي_الوطني الائتمانية</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>سافر لوجهتك، وقسط دفعاتها مع 0% هامش ربح ✈️
+على طيران الإمارات باستخدام بطاقات #بنك_الإمارات_دبي_الوطني الائتمانية</t>
+        </is>
+      </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>In 1989, Viktor Orbán launched himself into the center of Hungarian politics with an anti-Russia, pro-liberal speech. However, political support for Orbán has dwindled in the last few years, and this year’s election saw challenger Péter Magyar win.</t>
+          <t>Travel to your destination and pay in installments with 0% profit margin ✈️ on Emirates Airlines using #Emirates_NBD credit cards.</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3580,11 +3575,11 @@
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE19" s="2" t="n">
-        <v>46128.5625</v>
+        <v>46128.52013888889</v>
       </c>
       <c r="AF19" s="2" t="n">
         <v>46128</v>
@@ -3601,7 +3596,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>In 1989, Viktor Orbán launched himself into the center of Hungarian politics with an anti-Russia, pro-liberal speech. • However, political support for Orbán has dwindled in the last few years, and this year’s election saw challenger Péter Magyar win.</t>
+          <t>Travel to your destination and pay in installments with 0% profit margin ✈️ on Emirates Airlines using #Emirates_NBD credit cards.</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -3614,7 +3609,7 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>EmiratesNBD_KSA</t>
         </is>
       </c>
     </row>
@@ -3624,12 +3619,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2044694547498696848</t>
+          <t>2044694249686323218</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://x.com/msa3474/status/2044694547498696848</t>
+          <t>https://x.com/msa3474/status/2044694249686323218</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3655,13 +3650,12 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>سافر لوجهتك، وقسط دفعاتها مع 0% هامش ربح ✈️
-على طيران الإمارات باستخدام بطاقات #بنك_الإمارات_دبي_الوطني الائتمانية</t>
+          <t>@EmiratesNBD_KSA الرجاء إرسال رسالة خاصة لكي ارد عليكم</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>الرسائل الخاصه مقفله لديكم</t>
+          <t>الرجاء إرسال رسالة خاصة لكي ارد عليكم</t>
         </is>
       </c>
       <c r="K20" t="b">
@@ -3680,16 +3674,16 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Apr 16, 2026 · 8:29 AM UTC</t>
+          <t>Apr 16, 2026 · 8:27 AM UTC</t>
         </is>
       </c>
       <c r="P20" s="2" t="n">
-        <v>46128.35347222222</v>
+        <v>46128.35208333333</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -3698,7 +3692,7 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -3707,29 +3701,27 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>الرسائل الخاصه مقفله لديكم</t>
+          <t>الرجاء إرسال رسالة خاصة لكي ارد عليكم</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>https://x.com/msa3474/status/2044694547498696848</t>
+          <t>https://x.com/msa3474/status/2044694249686323218</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>سافر لوجهتك، وقسط دفعاتها مع 0% هامش ربح ✈️
-على طيران الإمارات باستخدام بطاقات #بنك_الإمارات_دبي_الوطني الائتمانية</t>
+          <t>@EmiratesNBD_KSA الرجاء إرسال رسالة خاصة لكي ارد عليكم</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>سافر لوجهتك، وقسط دفعاتها مع 0% هامش ربح ✈️
-على طيران الإمارات باستخدام بطاقات #بنك_الإمارات_دبي_الوطني الائتمانية</t>
+          <t>@EmiratesNBD_KSA الرجاء إرسال رسالة خاصة لكي ارد عليكم</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Travel to your destination and pay in installments with 0% profit margin ✈️ on Emirates Airlines using #Emirates_NBD credit cards.</t>
+          <t>@EmiratesNBD_KSA please send a private message so I can respond to you.</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3739,11 +3731,11 @@
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE20" s="2" t="n">
-        <v>46128.52013888889</v>
+        <v>46128.51875</v>
       </c>
       <c r="AF20" s="2" t="n">
         <v>46128</v>
@@ -3760,7 +3752,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Travel to your destination and pay in installments with 0% profit margin ✈️ on Emirates Airlines using #Emirates_NBD credit cards.</t>
+          <t>@EmiratesNBD_KSA please send a private message so I can respond to you.</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3783,54 +3775,51 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2044694249686323218</t>
+          <t>2044683879332589921</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://x.com/msa3474/status/2044694249686323218</t>
+          <t>https://x.com/gulf_news/status/2044683879332589921</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://x.com/msa3474</t>
+          <t>https://x.com/gulf_news</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>msa3474</t>
+          <t>gulf_news</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AHMARI</t>
+          <t>Gulf News</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1943001907854802944/sB6fjZIf_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2044041782519050242/muvl0wJC_bigger.jpg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA الرجاء إرسال رسالة خاصة لكي ارد عليكم</t>
+          <t>The Golden Elixir https://t.co/LGgbrnkX3c</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>الرجاء إرسال رسالة خاصة لكي ارد عليكم</t>
+          <t>Dubai opens earlier mortgage access for off-plan buyers as Dubai Holding Real Estate and Emirates NBD integrate financing at booking to boost homeownership.
+&lt;a href="https://mrf.lu/vYwK"&gt;mrf.lu/vYwK&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K21" t="b">
         <v>0</v>
       </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_KSA']</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>18h</t>
@@ -3838,25 +3827,29 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Apr 16, 2026 · 8:27 AM UTC</t>
+          <t>Apr 16, 2026 · 7:46 AM UTC</t>
         </is>
       </c>
       <c r="P21" s="2" t="n">
-        <v>46128.35208333333</v>
+        <v>46128.32361111111</v>
       </c>
       <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>['https://mrf.lu/vYwK']</t>
+        </is>
+      </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="V21" t="n">
-        <v>4</v>
+        <v>18983</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -3865,27 +3858,28 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>الرجاء إرسال رسالة خاصة لكي ارد عليكم</t>
+          <t>Dubai opens earlier mortgage access for off-plan buyers as Dubai Holding Real Estate and Emirates NBD integrate financing at booking to boost homeownership.
+mrf.lu/vYwK</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>https://x.com/msa3474/status/2044694249686323218</t>
+          <t>https://x.com/gulf_news/status/2044683879332589921</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA الرجاء إرسال رسالة خاصة لكي ارد عليكم</t>
+          <t>The Golden Elixir https://t.co/LGgbrnkX3c</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA الرجاء إرسال رسالة خاصة لكي ارد عليكم</t>
+          <t>The Golden Elixir https://t.co/LGgbrnkX3c</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA please send a private message so I can respond to you.</t>
+          <t>The Golden Elixir</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3899,7 +3893,7 @@
         </is>
       </c>
       <c r="AE21" s="2" t="n">
-        <v>46128.51875</v>
+        <v>46128.49027777778</v>
       </c>
       <c r="AF21" s="2" t="n">
         <v>46128</v>
@@ -3916,7 +3910,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA please send a private message so I can respond to you.</t>
+          <t>The Golden Elixir</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3929,7 +3923,7 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>EmiratesNBD_KSA</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3939,194 +3933,36 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2044683879332589921</t>
+          <t>2044676629453213871</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://x.com/gulf_news/status/2044683879332589921</t>
+          <t>https://x.com/proptglobal/status/2044676629453213871</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://x.com/gulf_news</t>
+          <t>https://x.com/proptglobal</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>gulf_news</t>
+          <t>proptglobal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gulf News</t>
+          <t>PROPT</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2044041782519050242/muvl0wJC_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1983901439580614656/g7YCwC90_bigger.jpg</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
-        <is>
-          <t>Best Foods High in Fiber https://t.co/j3Qv2TBkZl</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Dubai opens earlier mortgage access for off-plan buyers as Dubai Holding Real Estate and Emirates NBD integrate financing at booking to boost homeownership.
-&lt;a href="https://mrf.lu/vYwK"&gt;mrf.lu/vYwK&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K22" t="b">
-        <v>0</v>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>18h</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Apr 16, 2026 · 7:46 AM UTC</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="n">
-        <v>46128.32361111111</v>
-      </c>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>['https://mrf.lu/vYwK']</t>
-        </is>
-      </c>
-      <c r="S22" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" t="n">
-        <v>17</v>
-      </c>
-      <c r="U22" t="n">
-        <v>81</v>
-      </c>
-      <c r="V22" t="n">
-        <v>18983</v>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>Dubai opens earlier mortgage access for off-plan buyers as Dubai Holding Real Estate and Emirates NBD integrate financing at booking to boost homeownership.
-mrf.lu/vYwK</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>https://x.com/gulf_news/status/2044683879332589921</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>Best Foods High in Fiber https://t.co/j3Qv2TBkZl</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>Best Foods High in Fiber https://t.co/j3Qv2TBkZl</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>Best Foods High in Fiber</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE22" s="2" t="n">
-        <v>46128.49027777778</v>
-      </c>
-      <c r="AF22" s="2" t="n">
-        <v>46128</v>
-      </c>
-      <c r="AG22" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Best Foods High in Fiber</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK22" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2044676629453213871</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>https://x.com/proptglobal/status/2044676629453213871</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>https://x.com/proptglobal</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>proptglobal</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>PROPT</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1983901439580614656/g7YCwC90_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
         <is>
           <t>Dubai Holding Real Estate and Emirates NBD just teamed up to revolutionize off-plan mortgage financing🤝
 🔗Download the Propt!
@@ -4135,7 +3971,7 @@
 #HomeBuying #EmiratesNBD https://t.co/dSn1Zqufyh</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Dubai Holding Real Estate and Emirates NBD just teamed up to revolutionize off-plan mortgage financing🤝
 🔗Download the Propt!
@@ -4144,48 +3980,48 @@
 &lt;a href="/search?f=tweets&amp;amp;q=%23HomeBuying"&gt;#HomeBuying&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K23" t="b">
-        <v>0</v>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
         <is>
           <t>19h</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>Apr 16, 2026 · 7:17 AM UTC</t>
         </is>
       </c>
-      <c r="P23" s="2" t="n">
+      <c r="P22" s="2" t="n">
         <v>46128.30347222222</v>
       </c>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr">
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
         <is>
           <t>['https://apps.apple.com/pk/app/propt-real-estate-news/id6756180631', 'https://play.google.com/store/apps/details?id=com.propt.ProptGlobal', 'https://x.com/search?f=tweets&amp;q=%23HomeBuying', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBD']</t>
         </is>
       </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
         <v>1</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V22" t="n">
         <v>11</v>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>Dubai Holding Real Estate and Emirates NBD just teamed up to revolutionize off-plan mortgage financing🤝
 🔗Download the Propt!
@@ -4194,12 +4030,12 @@
 #HomeBuying #EmiratesNBD</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>https://x.com/proptglobal/status/2044676629453213871</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>Dubai Holding Real Estate and Emirates NBD just teamed up to revolutionize off-plan mortgage financing🤝
 🔗Download the Propt!
@@ -4208,7 +4044,7 @@
 #HomeBuying #EmiratesNBD https://t.co/dSn1Zqufyh</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>Dubai Holding Real Estate and Emirates NBD just teamed up to revolutionize off-plan mortgage financing🤝
 🔗Download the Propt!
@@ -4217,18 +4053,184 @@
 #HomeBuying #EmiratesNBD https://t.co/dSn1Zqufyh</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>Dubai Holding Real Estate and Emirates NBD just teamed up to revolutionize off-plan mortgage financing. 
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>Dubai Holding Real Estate and Emirates NBD have just partnered to revolutionize off-plan mortgage financing. 
 Download the Propt! 
 Appstore: https://t.co/sq8ARTKsof 
 Playstore: https://t.co/Ju874t2DvN 
 #HomeBuying #EmiratesNBD</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AE22" s="2" t="n">
+        <v>46128.47013888889</v>
+      </c>
+      <c r="AF22" s="2" t="n">
+        <v>46128</v>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Appstore: https://t.co/sq8ARTKsof Playstore: https://t.co/Ju874t2DvN #HomeBuying #EmiratesNBD • Dubai Holding Real Estate and Emirates NBD have just partnered to revolutionize off-plan mortgage financing.</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK22" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2044675073445871906</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2044675073445871906</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2042294543308242946/ScvMjarh_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>We at Emirates NBD are on a mission to make financial wellness truly inclusive. On our recent visit to a women accommodation camp in the UAE, we introduced them to everything finance, from budgeting to saving. Interactive sessions, quizzes, prizes, an evening well spent.
+Catch the action here.
+https://t.co/UAuXxgtnH8</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>We at Emirates NBD are on a mission to make financial wellness truly inclusive. On our recent visit to a women accommodation camp in the UAE, we introduced them to everything finance, from budgeting to saving. Interactive sessions, quizzes, prizes, an evening well spent.
+Catch the action here.
+&lt;a href="https://www.emiratesnbd.com/en/financial-wellbeing"&gt;emiratesnbd.com/en/financial…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Apr 16, 2026 · 7:11 AM UTC</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>46128.29930555556</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesnbd.com/en/financial-wellbeing']</t>
+        </is>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3</v>
+      </c>
+      <c r="V23" t="n">
+        <v>430</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>We at Emirates NBD are on a mission to make financial wellness truly inclusive. On our recent visit to a women accommodation camp in the UAE, we introduced them to everything finance, from budgeting to saving. Interactive sessions, quizzes, prizes, an evening well spent.
+Catch the action here.
+emiratesnbd.com/en/financial…</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2044675073445871906</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>We at Emirates NBD are on a mission to make financial wellness truly inclusive. On our recent visit to a women accommodation camp in the UAE, we introduced them to everything finance, from budgeting to saving. Interactive sessions, quizzes, prizes, an evening well spent.
+Catch the action here.
+https://t.co/UAuXxgtnH8</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>We at Emirates NBD are on a mission to make financial wellness truly inclusive. On our recent visit to a women accommodation camp in the UAE, we introduced them to everything finance, from budgeting to saving. Interactive sessions, quizzes, prizes, an evening well spent.
+Catch the action here.
+https://t.co/UAuXxgtnH8</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>We at Emirates NBD are on a mission to make financial wellness truly inclusive. On our recent visit to a women's accommodation camp in the UAE, we introduced them to everything finance, from budgeting to saving. Interactive sessions, quizzes, prizes, an evening well spent. Catch the action here.</t>
+        </is>
+      </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Cust</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -4237,7 +4239,7 @@
         </is>
       </c>
       <c r="AE23" s="2" t="n">
-        <v>46128.47013888889</v>
+        <v>46128.46597222222</v>
       </c>
       <c r="AF23" s="2" t="n">
         <v>46128</v>
@@ -4254,7 +4256,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Appstore: https://t.co/sq8ARTKsof Playstore: https://t.co/Ju874t2DvN #HomeBuying #EmiratesNBD • Dubai Holding Real Estate and Emirates NBD just teamed up to revolutionize off-plan mortgage financing.</t>
+          <t>On our recent visit to a women's accommodation camp in the UAE, we introduced them to everything finance, from budgeting to saving. • We at Emirates NBD are on a mission to make financial wellness truly inclusive. • Interactive sessions, quizzes, prizes, an evening well spent.</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -4277,202 +4279,36 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2044675073445871906</t>
+          <t>2044662520884179409</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2044675073445871906</t>
+          <t>https://x.com/talent_folder/status/2044662520884179409</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/talent_folder</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>talent_folder</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>Talentfolder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2042294543308242946/ScvMjarh_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1785222859268218880/QKe4zDoG_bigger.jpg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
-        <is>
-          <t>We at Emirates NBD are on a mission to make financial wellness truly inclusive. On our recent visit to a women accommodation camp in the UAE, we introduced them to everything finance, from budgeting to saving. Interactive sessions, quizzes, prizes, an evening well spent.
-Catch the action here.
-https://t.co/UAuXxgtnH8</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>We at Emirates NBD are on a mission to make financial wellness truly inclusive. On our recent visit to a women accommodation camp in the UAE, we introduced them to everything finance, from budgeting to saving. Interactive sessions, quizzes, prizes, an evening well spent.
-Catch the action here.
-&lt;a href="https://www.emiratesnbd.com/en/financial-wellbeing"&gt;emiratesnbd.com/en/financial…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K24" t="b">
-        <v>0</v>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>19h</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Apr 16, 2026 · 7:11 AM UTC</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="n">
-        <v>46128.29930555556</v>
-      </c>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesnbd.com/en/financial-wellbeing']</t>
-        </is>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>3</v>
-      </c>
-      <c r="V24" t="n">
-        <v>430</v>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>We at Emirates NBD are on a mission to make financial wellness truly inclusive. On our recent visit to a women accommodation camp in the UAE, we introduced them to everything finance, from budgeting to saving. Interactive sessions, quizzes, prizes, an evening well spent.
-Catch the action here.
-emiratesnbd.com/en/financial…</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2044675073445871906</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>We at Emirates NBD are on a mission to make financial wellness truly inclusive. On our recent visit to a women accommodation camp in the UAE, we introduced them to everything finance, from budgeting to saving. Interactive sessions, quizzes, prizes, an evening well spent.
-Catch the action here.
-https://t.co/UAuXxgtnH8</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>We at Emirates NBD are on a mission to make financial wellness truly inclusive. On our recent visit to a women accommodation camp in the UAE, we introduced them to everything finance, from budgeting to saving. Interactive sessions, quizzes, prizes, an evening well spent.
-Catch the action here.
-https://t.co/UAuXxgtnH8</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>We at Emirates NBD are on a mission to make financial wellness truly inclusive. On our recent visit to a women's accommodation camp in the UAE, we introduced them to everything finance, from budgeting to saving. Interactive sessions, quizzes, prizes, an evening well spent. Catch the action here.</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="AE24" s="2" t="n">
-        <v>46128.46597222222</v>
-      </c>
-      <c r="AF24" s="2" t="n">
-        <v>46128</v>
-      </c>
-      <c r="AG24" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>On our recent visit to a women's accommodation camp in the UAE, we introduced them to everything finance, from budgeting to saving. • We at Emirates NBD are on a mission to make financial wellness truly inclusive. • Interactive sessions, quizzes, prizes, an evening well spent.</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK24" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL24" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2044662520884179409</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>https://x.com/talent_folder/status/2044662520884179409</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>https://x.com/talent_folder</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>talent_folder</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Talentfolder</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1785222859268218880/QKe4zDoG_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
         <is>
           <t>At Talentfolder, we wish you and your loved ones a joyful and blessed Vishu! 🌼💛
 Let this new beginning open doors to success and brighter futures.
@@ -4482,63 +4318,63 @@
 #HappyVishu #Vishu2026 #VishuCelebration #KeralaFestival #NewBeginnings https://t.co/tnPPiy9Gym</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Open Your Bank Account in Dubai Easily
 Looking to open a bank account in Dubai? We make it simple, fast, and stress-free!
 Whether you&amp;#39;re a resident, investor, or business owner, our experts help you open accounts with top UAE banks like ADCB, FAB, Emirates NBD, and more.</t>
         </is>
       </c>
-      <c r="K25" t="b">
-        <v>0</v>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
         <is>
           <t>20h</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>Apr 16, 2026 · 6:21 AM UTC</t>
         </is>
       </c>
-      <c r="P25" s="2" t="n">
+      <c r="P24" s="2" t="n">
         <v>46128.26458333333</v>
       </c>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
         <v>23</v>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>Open Your Bank Account in Dubai Easily
 Looking to open a bank account in Dubai? We make it simple, fast, and stress-free!
 Whether you're a resident, investor, or business owner, our experts help you open accounts with top UAE banks like ADCB, FAB, Emirates NBD, and more.</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>https://x.com/talent_folder/status/2044662520884179409</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>At Talentfolder, we wish you and your loved ones a joyful and blessed Vishu! 🌼💛
 Let this new beginning open doors to success and brighter futures.
@@ -4548,7 +4384,7 @@
 #HappyVishu #Vishu2026 #VishuCelebration #KeralaFestival #NewBeginnings https://t.co/tnPPiy9Gym</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>At Talentfolder, we wish you and your loved ones a joyful and blessed Vishu! 🌼💛
 Let this new beginning open doors to success and brighter futures.
@@ -4558,9 +4394,169 @@
 #HappyVishu #Vishu2026 #VishuCelebration #KeralaFestival #NewBeginnings https://t.co/tnPPiy9Gym</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>At Talentfolder, we wish you and your loved ones a joyful and blessed Vishu! Let this new beginning open doors to success and brighter futures.</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE24" s="2" t="n">
+        <v>46128.43125</v>
+      </c>
+      <c r="AF24" s="2" t="n">
+        <v>46128</v>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Let this new beginning open doors to success and brighter futures. • At Talentfolder, we wish you and your loved ones a joyful and blessed Vishu!</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK24" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2044659603196231971</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://x.com/khushbuag88/status/2044659603196231971</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://x.com/khushbuag88</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>khushbuag88</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Khushbu Agarwal</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1950530694746447872/VGZLi5fA_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE الإجابة هي الفائدة البسيطة #لغز_الأسبوع_للحاصلين_على_شهادة_الهندسة_المدنية #تعلم_المالية #أساسيات_المال</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>الإجابة هي الفائدة البسيطة &lt;a href="/search?f=tweets&amp;amp;q=%23لغز_الأسبوع_للحاصلين_على_شهادة_الهندسة_المدنية"&gt;#لغز_الأسبوع_للحاصلين_على_شهادة_الهندسة_المدنية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23تعلم_المالية"&gt;#تعلم_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23أساسيات_المال"&gt;#أساسيات_المال&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Apr 16, 2026 · 6:10 AM UTC</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="n">
+        <v>46128.25694444445</v>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23لغز_الأسبوع_للحاصلين_على_شهادة_الهندسة_المدنية', 'https://x.com/search?f=tweets&amp;q=%23تعلم_المالية', 'https://x.com/search?f=tweets&amp;q=%23أساسيات_المال']</t>
+        </is>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>7</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>الإجابة هي الفائدة البسيطة #لغز_الأسبوع_للحاصلين_على_شهادة_الهندسة_المدنية #تعلم_المالية #أساسيات_المال</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>https://x.com/khushbuag88/status/2044659603196231971</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE الإجابة هي الفائدة البسيطة #لغز_الأسبوع_للحاصلين_على_شهادة_الهندسة_المدنية #تعلم_المالية #أساسيات_المال</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE الإجابة هي الفائدة البسيطة #لغز_الأسبوع_للحاصلين_على_شهادة_الهندسة_المدنية #تعلم_المالية #أساسيات_المال</t>
+        </is>
+      </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>At Talentfolder, we wish you and your loved ones a joyful and blessed Vishu! Let this new beginning open doors to success and brighter futures.</t>
+          <t>The answer is simple interest #Puzzle_of_the_Week_for_Civil_Engineering_Graduates #Learn_Finance #Financial_Basics</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -4574,7 +4570,7 @@
         </is>
       </c>
       <c r="AE25" s="2" t="n">
-        <v>46128.43125</v>
+        <v>46128.42361111111</v>
       </c>
       <c r="AF25" s="2" t="n">
         <v>46128</v>
@@ -4591,7 +4587,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Let this new beginning open doors to success and brighter futures. • At Talentfolder, we wish you and your loved ones a joyful and blessed Vishu!</t>
+          <t>The answer is simple interest #Puzzle_of_the_Week_for_Civil_Engineering_Graduates #Learn_Finance #Financial_Basics</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -4604,7 +4600,7 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
@@ -4614,12 +4610,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2044659603196231971</t>
+          <t>2044659438011961784</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://x.com/khushbuag88/status/2044659603196231971</t>
+          <t>https://x.com/khushbuag88/status/2044659438011961784</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4645,12 +4641,12 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE الإجابة هي الفائدة البسيطة #لغز_الأسبوع_للحاصلين_على_شهادة_الهندسة_المدنية #تعلم_المالية #أساسيات_المال</t>
+          <t>@EmiratesNBD_AE Answer is Simple Interest     #ENBDRiddleOfTheWeek   #LearnFinance #MoneyBasics</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>الإجابة هي الفائدة البسيطة &lt;a href="/search?f=tweets&amp;amp;q=%23لغز_الأسبوع_للحاصلين_على_شهادة_الهندسة_المدنية"&gt;#لغز_الأسبوع_للحاصلين_على_شهادة_الهندسة_المدنية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23تعلم_المالية"&gt;#تعلم_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23أساسيات_المال"&gt;#أساسيات_المال&lt;/a&gt;</t>
+          <t>Answer is Simple Interest     &lt;a href="/search?f=tweets&amp;amp;q=%23ENBDRiddleOfTheWeek"&gt;#ENBDRiddleOfTheWeek&lt;/a&gt;   &lt;a href="/search?f=tweets&amp;amp;q=%23LearnFinance"&gt;#LearnFinance&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23MoneyBasics"&gt;#MoneyBasics&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K26" t="b">
@@ -4669,16 +4665,16 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Apr 16, 2026 · 6:10 AM UTC</t>
+          <t>Apr 16, 2026 · 6:09 AM UTC</t>
         </is>
       </c>
       <c r="P26" s="2" t="n">
-        <v>46128.25694444445</v>
+        <v>46128.25625</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23لغز_الأسبوع_للحاصلين_على_شهادة_الهندسة_المدنية', 'https://x.com/search?f=tweets&amp;q=%23تعلم_المالية', 'https://x.com/search?f=tweets&amp;q=%23أساسيات_المال']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23ENBDRiddleOfTheWeek', 'https://x.com/search?f=tweets&amp;q=%23LearnFinance', 'https://x.com/search?f=tweets&amp;q=%23MoneyBasics']</t>
         </is>
       </c>
       <c r="S26" t="n">
@@ -4691,7 +4687,7 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -4700,27 +4696,27 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>الإجابة هي الفائدة البسيطة #لغز_الأسبوع_للحاصلين_على_شهادة_الهندسة_المدنية #تعلم_المالية #أساسيات_المال</t>
+          <t>Answer is Simple Interest     #ENBDRiddleOfTheWeek   #LearnFinance #MoneyBasics</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>https://x.com/khushbuag88/status/2044659603196231971</t>
+          <t>https://x.com/khushbuag88/status/2044659438011961784</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE الإجابة هي الفائدة البسيطة #لغز_الأسبوع_للحاصلين_على_شهادة_الهندسة_المدنية #تعلم_المالية #أساسيات_المال</t>
+          <t>@EmiratesNBD_AE Answer is Simple Interest     #ENBDRiddleOfTheWeek   #LearnFinance #MoneyBasics</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE الإجابة هي الفائدة البسيطة #لغز_الأسبوع_للحاصلين_على_شهادة_الهندسة_المدنية #تعلم_المالية #أساسيات_المال</t>
+          <t>@EmiratesNBD_AE Answer is Simple Interest     #ENBDRiddleOfTheWeek   #LearnFinance #MoneyBasics</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>The answer is simple interest #Puzzle_of_the_Week_for_Civil_Engineering_Graduates #Learn_Finance #Financial_Basics</t>
+          <t>The answer is Simple Interest.</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4734,7 +4730,7 @@
         </is>
       </c>
       <c r="AE26" s="2" t="n">
-        <v>46128.42361111111</v>
+        <v>46128.42291666667</v>
       </c>
       <c r="AF26" s="2" t="n">
         <v>46128</v>
@@ -4751,7 +4747,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>The answer is simple interest #Puzzle_of_the_Week_for_Civil_Engineering_Graduates #Learn_Finance #Financial_Basics</t>
+          <t>The answer is Simple Interest.</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -4774,54 +4770,52 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2044659438011961784</t>
+          <t>2044654528956682747</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://x.com/khushbuag88/status/2044659438011961784</t>
+          <t>https://x.com/CBN_ME/status/2044654528956682747</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://x.com/khushbuag88</t>
+          <t>https://x.com/CBN_ME</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>khushbuag88</t>
+          <t>CBN_ME</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Khushbu Agarwal</t>
+          <t>Construction Business News ME</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1950530694746447872/VGZLi5fA_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/897015258631593985/lgLgqzSc_bigger.jpg</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Answer is Simple Interest     #ENBDRiddleOfTheWeek   #LearnFinance #MoneyBasics</t>
+          <t>@dubaiholding and @EmiratesNBD_AE have signed an MoU to introduce integrated mortgage solutions for off-plan homes across @MeraasDubai, @NakheelOfficial and @DubaiProperties.
+https://t.co/NE9RbJAFPP https://t.co/P6urCIn0qy</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Answer is Simple Interest     &lt;a href="/search?f=tweets&amp;amp;q=%23ENBDRiddleOfTheWeek"&gt;#ENBDRiddleOfTheWeek&lt;/a&gt;   &lt;a href="/search?f=tweets&amp;amp;q=%23LearnFinance"&gt;#LearnFinance&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23MoneyBasics"&gt;#MoneyBasics&lt;/a&gt;</t>
+          <t>&lt;a href="/dubaiholding" title="Dubai Holding"&gt;@dubaiholding&lt;/a&gt; and &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; have signed an MoU to introduce integrated mortgage solutions for off-plan homes across &lt;a href="/MeraasDubai" title="Meraas"&gt;@MeraasDubai&lt;/a&gt;, &lt;a href="/NakheelOfficial" title="Nakheel"&gt;@NakheelOfficial&lt;/a&gt; and &lt;a href="/DubaiProperties" title="Dubai Properties"&gt;@DubaiProperties&lt;/a&gt;.
+&lt;a href="https://www.cbnme.com/news/dubai-holding-real-estate-and-emirates-nbd-partner-on-off-plan-mortgage-solutions/"&gt;cbnme.com/news/dubai-holding…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K27" t="b">
         <v>0</v>
       </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>20h</t>
@@ -4829,29 +4823,29 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Apr 16, 2026 · 6:09 AM UTC</t>
+          <t>Apr 16, 2026 · 5:50 AM UTC</t>
         </is>
       </c>
       <c r="P27" s="2" t="n">
-        <v>46128.25625</v>
+        <v>46128.24305555555</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23ENBDRiddleOfTheWeek', 'https://x.com/search?f=tweets&amp;q=%23LearnFinance', 'https://x.com/search?f=tweets&amp;q=%23MoneyBasics']</t>
+          <t>['https://x.com/dubaiholding', 'https://x.com/EmiratesNBD_AE', 'https://x.com/MeraasDubai', 'https://x.com/NakheelOfficial', 'https://x.com/DubaiProperties', 'https://www.cbnme.com/news/dubai-holding-real-estate-and-emirates-nbd-partner-on-off-plan-mortgage-solutions/']</t>
         </is>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -4860,27 +4854,30 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Answer is Simple Interest     #ENBDRiddleOfTheWeek   #LearnFinance #MoneyBasics</t>
+          <t>@dubaiholding and @EmiratesNBD_AE have signed an MoU to introduce integrated mortgage solutions for off-plan homes across @MeraasDubai, @NakheelOfficial and @DubaiProperties.
+cbnme.com/news/dubai-holding…</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>https://x.com/khushbuag88/status/2044659438011961784</t>
+          <t>https://x.com/CBN_ME/status/2044654528956682747</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Answer is Simple Interest     #ENBDRiddleOfTheWeek   #LearnFinance #MoneyBasics</t>
+          <t>@dubaiholding and @EmiratesNBD_AE have signed an MoU to introduce integrated mortgage solutions for off-plan homes across @MeraasDubai, @NakheelOfficial and @DubaiProperties.
+https://t.co/NE9RbJAFPP https://t.co/P6urCIn0qy</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Answer is Simple Interest     #ENBDRiddleOfTheWeek   #LearnFinance #MoneyBasics</t>
+          <t>@dubaiholding and @EmiratesNBD_AE have signed an MoU to introduce integrated mortgage solutions for off-plan homes across @MeraasDubai, @NakheelOfficial and @DubaiProperties.
+https://t.co/NE9RbJAFPP https://t.co/P6urCIn0qy</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>The answer is Simple Interest.</t>
+          <t>Dubai Holding and Emirates NBD have signed a Memorandum of Understanding to introduce integrated mortgage solutions for off-plan homes across Meraas, Nakheel, and Dubai Properties.</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4890,11 +4887,11 @@
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE27" s="2" t="n">
-        <v>46128.42291666667</v>
+        <v>46128.40972222222</v>
       </c>
       <c r="AF27" s="2" t="n">
         <v>46128</v>
@@ -4911,7 +4908,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>The answer is Simple Interest.</t>
+          <t>Dubai Holding and Emirates NBD have signed a Memorandum of Understanding to introduce integrated mortgage solutions for off-plan homes across Meraas, Nakheel, and Dubai Properties.</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -4924,7 +4921,7 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4934,45 +4931,45 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2044654528956682747</t>
+          <t>2044647851410817502</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://x.com/CBN_ME/status/2044654528956682747</t>
+          <t>https://x.com/AdityaD_Shah/status/2044647851410817502</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://x.com/CBN_ME</t>
+          <t>https://x.com/AdityaD_Shah</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CBN_ME</t>
+          <t>AdityaD_Shah</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Construction Business News ME</t>
+          <t>Aditya Shah</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/897015258631593985/lgLgqzSc_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2021161561864404993/PJFHGfxw_bigger.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>@dubaiholding and @EmiratesNBD_AE have signed an MoU to introduce integrated mortgage solutions for off-plan homes across @MeraasDubai, @NakheelOfficial and @DubaiProperties.
-https://t.co/NE9RbJAFPP https://t.co/P6urCIn0qy</t>
+          <t>Can Emirates NBD really change the fortunes of RBL Bank?
+The market really thinks so! https://t.co/EBFkHPBULm</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>&lt;a href="/dubaiholding" title="Dubai Holding"&gt;@dubaiholding&lt;/a&gt; and &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; have signed an MoU to introduce integrated mortgage solutions for off-plan homes across &lt;a href="/MeraasDubai" title="Meraas"&gt;@MeraasDubai&lt;/a&gt;, &lt;a href="/NakheelOfficial" title="Nakheel"&gt;@NakheelOfficial&lt;/a&gt; and &lt;a href="/DubaiProperties" title="Dubai Properties"&gt;@DubaiProperties&lt;/a&gt;.
-&lt;a href="https://www.cbnme.com/news/dubai-holding-real-estate-and-emirates-nbd-partner-on-off-plan-mortgage-solutions/"&gt;cbnme.com/news/dubai-holding…&lt;/a&gt;</t>
+          <t>Can Emirates NBD really change the fortunes of RBL Bank?
+The market really thinks so!</t>
         </is>
       </c>
       <c r="K28" t="b">
@@ -4982,34 +4979,30 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Apr 16, 2026 · 5:50 AM UTC</t>
+          <t>Apr 16, 2026 · 5:23 AM UTC</t>
         </is>
       </c>
       <c r="P28" s="2" t="n">
-        <v>46128.24305555555</v>
+        <v>46128.22430555556</v>
       </c>
       <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>['https://x.com/dubaiholding', 'https://x.com/EmiratesNBD_AE', 'https://x.com/MeraasDubai', 'https://x.com/NakheelOfficial', 'https://x.com/DubaiProperties', 'https://www.cbnme.com/news/dubai-holding-real-estate-and-emirates-nbd-partner-on-off-plan-mortgage-solutions/']</t>
-        </is>
-      </c>
+      <c r="R28" t="inlineStr"/>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="V28" t="n">
-        <v>23</v>
+        <v>6112</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -5018,30 +5011,30 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>@dubaiholding and @EmiratesNBD_AE have signed an MoU to introduce integrated mortgage solutions for off-plan homes across @MeraasDubai, @NakheelOfficial and @DubaiProperties.
-cbnme.com/news/dubai-holding…</t>
+          <t>Can Emirates NBD really change the fortunes of RBL Bank?
+The market really thinks so!</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>https://x.com/CBN_ME/status/2044654528956682747</t>
+          <t>https://x.com/AdityaD_Shah/status/2044647851410817502</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>@dubaiholding and @EmiratesNBD_AE have signed an MoU to introduce integrated mortgage solutions for off-plan homes across @MeraasDubai, @NakheelOfficial and @DubaiProperties.
-https://t.co/NE9RbJAFPP https://t.co/P6urCIn0qy</t>
+          <t>Can Emirates NBD really change the fortunes of RBL Bank?
+The market really thinks so! https://t.co/EBFkHPBULm</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>@dubaiholding and @EmiratesNBD_AE have signed an MoU to introduce integrated mortgage solutions for off-plan homes across @MeraasDubai, @NakheelOfficial and @DubaiProperties.
-https://t.co/NE9RbJAFPP https://t.co/P6urCIn0qy</t>
+          <t>Can Emirates NBD really change the fortunes of RBL Bank?
+The market really thinks so! https://t.co/EBFkHPBULm</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Dubai Holding and Emirates NBD have signed a Memorandum of Understanding to introduce integrated mortgage solutions for off-plan homes across Meraas, Nakheel, and Dubai Properties.</t>
+          <t>Can Emirates NBD really change the fortunes of RBL Bank? The market really thinks so!</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -5051,11 +5044,11 @@
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE28" s="2" t="n">
-        <v>46128.40972222222</v>
+        <v>46128.39097222222</v>
       </c>
       <c r="AF28" s="2" t="n">
         <v>46128</v>
@@ -5072,7 +5065,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Dubai Holding and Emirates NBD have signed a Memorandum of Understanding to introduce integrated mortgage solutions for off-plan homes across Meraas, Nakheel, and Dubai Properties.</t>
+          <t>Can Emirates NBD really change the fortunes of RBL Bank? • The market really thinks so!</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -5095,64 +5088,66 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2044647851410817502</t>
+          <t>2044612515498496366</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://x.com/AdityaD_Shah/status/2044647851410817502</t>
+          <t>https://x.com/DustshotW/status/2044612515498496366</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://x.com/AdityaD_Shah</t>
+          <t>https://x.com/DustshotW</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AdityaD_Shah</t>
+          <t>DustshotW</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Aditya Shah</t>
+          <t>justice gaming</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2021161561864404993/PJFHGfxw_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2042550502014193664/yhlYRmG6_bigger.jpg</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Can Emirates NBD really change the fortunes of RBL Bank?
-The market really thinks so! https://t.co/EBFkHPBULm</t>
+          <t>anyone.....olease ......</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Can Emirates NBD really change the fortunes of RBL Bank?
-The market really thinks so!</t>
+          <t>s enbd</t>
         </is>
       </c>
       <c r="K29" t="b">
         <v>0</v>
       </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>['dorienotfish']</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Apr 16, 2026 · 5:23 AM UTC</t>
+          <t>Apr 16, 2026 · 3:03 AM UTC</t>
         </is>
       </c>
       <c r="P29" s="2" t="n">
-        <v>46128.22430555556</v>
+        <v>46128.12708333333</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
@@ -5160,13 +5155,13 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>6112</v>
+        <v>25</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -5175,30 +5170,27 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Can Emirates NBD really change the fortunes of RBL Bank?
-The market really thinks so!</t>
+          <t>s enbd</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>https://x.com/AdityaD_Shah/status/2044647851410817502</t>
+          <t>https://x.com/DustshotW/status/2044612515498496366</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>Can Emirates NBD really change the fortunes of RBL Bank?
-The market really thinks so! https://t.co/EBFkHPBULm</t>
+          <t>anyone.....olease ......</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>Can Emirates NBD really change the fortunes of RBL Bank?
-The market really thinks so! https://t.co/EBFkHPBULm</t>
+          <t>anyone.....olease ......</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Can Emirates NBD really change the fortunes of RBL Bank? The market really thinks so!</t>
+          <t>anyone.....please ......</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -5212,7 +5204,7 @@
         </is>
       </c>
       <c r="AE29" s="2" t="n">
-        <v>46128.39097222222</v>
+        <v>46128.29375</v>
       </c>
       <c r="AF29" s="2" t="n">
         <v>46128</v>
@@ -5229,7 +5221,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Can Emirates NBD really change the fortunes of RBL Bank? • The market really thinks so!</t>
+          <t>anyone.....please ......</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -5242,7 +5234,7 @@
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>dorienotfish</t>
         </is>
       </c>
     </row>
@@ -5252,192 +5244,36 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2044612515498496366</t>
+          <t>2044611289733878057</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://x.com/DustshotW/status/2044612515498496366</t>
+          <t>https://x.com/BehindNums/status/2044611289733878057</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://x.com/DustshotW</t>
+          <t>https://x.com/BehindNums</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>DustshotW</t>
+          <t>BehindNums</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>justice gaming</t>
+          <t>BehindNums | Business &amp; Data</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2042550502014193664/yhlYRmG6_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2025763865783345152/vXOr5RDQ_bigger.jpg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
-        <is>
-          <t>anyone.....olease ......</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>s enbd</t>
-        </is>
-      </c>
-      <c r="K30" t="b">
-        <v>0</v>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>['dorienotfish']</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>23h</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>Apr 16, 2026 · 3:03 AM UTC</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="n">
-        <v>46128.12708333333</v>
-      </c>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="n">
-        <v>1</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>25</v>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>s enbd</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>https://x.com/DustshotW/status/2044612515498496366</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>anyone.....olease ......</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>anyone.....olease ......</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>anyone.....please ......</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE30" s="2" t="n">
-        <v>46128.29375</v>
-      </c>
-      <c r="AF30" s="2" t="n">
-        <v>46128</v>
-      </c>
-      <c r="AG30" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>anyone.....please ......</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK30" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL30" t="inlineStr">
-        <is>
-          <t>dorienotfish</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2044611289733878057</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>https://x.com/BehindNums/status/2044611289733878057</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>https://x.com/BehindNums</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>BehindNums</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>BehindNums | Business &amp; Data</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2025763865783345152/vXOr5RDQ_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
         <is>
           <t>Top 5 Companies by Revenue 
 By Revenue (annual)
@@ -5449,7 +5285,7 @@
 @BehindNums</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>Top 5 Richest Companies in the Middle East 
 1️⃣ Saudi Aramco — ~$1.5T+
@@ -5461,48 +5297,48 @@
 &lt;a href="/BehindNums" title="BehindNums | Business &amp;amp; Data"&gt;@BehindNums&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K31" t="b">
-        <v>0</v>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
         <is>
           <t>23h</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>Apr 16, 2026 · 2:58 AM UTC</t>
         </is>
       </c>
-      <c r="P31" s="2" t="n">
+      <c r="P30" s="2" t="n">
         <v>46128.12361111111</v>
       </c>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr">
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
         <is>
           <t>['https://x.com/BehindNums']</t>
         </is>
       </c>
-      <c r="S31" t="n">
+      <c r="S30" t="n">
         <v>1</v>
       </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
         <v>29</v>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>Top 5 Richest Companies in the Middle East 
 1️⃣ Saudi Aramco — ~$1.5T+
@@ -5514,12 +5350,12 @@
 @BehindNums</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>https://x.com/BehindNums/status/2044611289733878057</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>Top 5 Companies by Revenue 
 By Revenue (annual)
@@ -5531,7 +5367,7 @@
 @BehindNums</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>Top 5 Companies by Revenue 
 By Revenue (annual)
@@ -5543,9 +5379,9 @@
 @BehindNums</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>Top 5 Companies by Revenue 
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>Top 5 Companies by Revenue
 By Revenue (annual)
 1️⃣ Walmart — ~$650B
 2️⃣ Amazon — ~$575B
@@ -5555,6 +5391,165 @@
 @BehindNums</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE30" s="2" t="n">
+        <v>46128.29027777778</v>
+      </c>
+      <c r="AF30" s="2" t="n">
+        <v>46128</v>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Top 5 Companies by Revenue By Revenue (annual) 1️⃣ Walmart — ~$650B 2️⃣ Amazon — ~$575B 3️⃣ Saudi Aramco — ~$500B 4️⃣ China State Grid — ~$480B 5️⃣ Apple — ~$390B @BehindNums</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK30" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2044582261102956879</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://x.com/zaydaklabhoqx/status/2044582261102956879</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://x.com/zaydaklabhoqx</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>zaydaklabhoqx</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>زيد أكلب</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2035350140782002176/Clcsao6J_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>🚨 JUST IN: 🇦🇪 EMIRATES NBD ELIMINATES ATM WITHDRAWAL &amp;amp; DEBIT CARD FEES ACROSS THE UAE &amp;amp; GCC UNTIL MARCH 31, 2026! 💳🔥
+#UAE #EmiratesNBD #Banking #Finance #ATM #NoFees #GCC #MoneySmart https://t.co/aI9H5crVgx</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>ماذا عن مجانيّة سحب النقود؟ مبروك لعملاء Emirates NBD في الإمارات ودول الخليج</t>
+        </is>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>['CryptoNewsHntrs']</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Apr 16</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Apr 16, 2026 · 1:02 AM UTC</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>46128.04305555556</v>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
+      </c>
+      <c r="V31" t="n">
+        <v>12</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>ماذا عن مجانيّة سحب النقود؟ مبروك لعملاء Emirates NBD في الإمارات ودول الخليج</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>https://x.com/zaydaklabhoqx/status/2044582261102956879</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>🚨 JUST IN: 🇦🇪 EMIRATES NBD ELIMINATES ATM WITHDRAWAL &amp;amp; DEBIT CARD FEES ACROSS THE UAE &amp;amp; GCC UNTIL MARCH 31, 2026! 💳🔥
+#UAE #EmiratesNBD #Banking #Finance #ATM #NoFees #GCC #MoneySmart https://t.co/aI9H5crVgx</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>🚨 JUST IN: 🇦🇪 EMIRATES NBD ELIMINATES ATM WITHDRAWAL &amp;amp; DEBIT CARD FEES ACROSS THE UAE &amp;amp; GCC UNTIL MARCH 31, 2026! 💳🔥
+#UAE #EmiratesNBD #Banking #Finance #ATM #NoFees #GCC #MoneySmart https://t.co/aI9H5crVgx</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>JUST IN: EMIRATES NBD ELIMINATES ATM WITHDRAWAL &amp; DEBIT CARD FEES ACROSS THE UAE &amp; GCC UNTIL MARCH 31, 2026!</t>
+        </is>
+      </c>
       <c r="AC31" t="inlineStr">
         <is>
           <t>Cust</t>
@@ -5562,11 +5557,11 @@
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE31" s="2" t="n">
-        <v>46128.29027777778</v>
+        <v>46128.20972222222</v>
       </c>
       <c r="AF31" s="2" t="n">
         <v>46128</v>
@@ -5583,7 +5578,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Top 5 Companies by Revenue By Revenue (annual) 1️⃣ Walmart — ~$650B 2️⃣ Amazon — ~$575B 3️⃣ Saudi Aramco — ~$500B 4️⃣ China State Grid — ~$480B 5️⃣ Apple — ~$390B @BehindNums</t>
+          <t>JUST IN: EMIRATES NBD ELIMINATES ATM WITHDRAWAL &amp; DEBIT CARD FEES ACROSS THE UAE &amp; GCC UNTIL MARCH 31, 2026!</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -5596,7 +5591,7 @@
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>CryptoNewsHntrs</t>
         </is>
       </c>
     </row>
@@ -5606,44 +5601,45 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2044582261102956879</t>
+          <t>2044805287459398125</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://x.com/zaydaklabhoqx/status/2044582261102956879</t>
+          <t>https://x.com/1ss9490ss1/status/2044805287459398125</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://x.com/zaydaklabhoqx</t>
+          <t>https://x.com/1ss9490ss1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>zaydaklabhoqx</t>
+          <t>1ss9490ss1</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>زيد أكلب</t>
+          <t>بوالسلطان</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2035350140782002176/Clcsao6J_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/777077466515079168/MKR49yEx_bigger.jpg</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>🚨 JUST IN: 🇦🇪 EMIRATES NBD ELIMINATES ATM WITHDRAWAL &amp;amp; DEBIT CARD FEES ACROSS THE UAE &amp;amp; GCC UNTIL MARCH 31, 2026! 💳🔥
-#UAE #EmiratesNBD #Banking #Finance #ATM #NoFees #GCC #MoneySmart https://t.co/aI9H5crVgx</t>
+          <t>Save and earn with your Emirates Islamic Super Savings Etihad Guest Account!
+💸 Get up to 750,000 Etihad Guest Miles every quarter and up to 3 million Etihad Guest Miles in a year https://t.co/y8cuMSrpQL</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>ماذا عن مجانيّة سحب النقود؟ مبروك لعملاء Emirates NBD في الإمارات ودول الخليج</t>
+          <t>السلام عليكم ورحمه الله وبركاته 
+الرجاء التواصل بي باحد من خدمة العملاء.</t>
         </is>
       </c>
       <c r="K32" t="b">
@@ -5652,21 +5648,21 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>['CryptoNewsHntrs']</t>
+          <t>['emiratesislamic']</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Apr 16</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Apr 16, 2026 · 1:02 AM UTC</t>
+          <t>Apr 16, 2026 · 3:49 PM UTC</t>
         </is>
       </c>
       <c r="P32" s="2" t="n">
-        <v>46128.04305555556</v>
+        <v>46128.65902777778</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
@@ -5677,41 +5673,43 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>ماذا عن مجانيّة سحب النقود؟ مبروك لعملاء Emirates NBD في الإمارات ودول الخليج</t>
+          <t>السلام عليكم ورحمه الله وبركاته 
+الرجاء التواصل بي باحد من خدمة العملاء.</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>https://x.com/zaydaklabhoqx/status/2044582261102956879</t>
+          <t>https://x.com/1ss9490ss1/status/2044805287459398125</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>🚨 JUST IN: 🇦🇪 EMIRATES NBD ELIMINATES ATM WITHDRAWAL &amp;amp; DEBIT CARD FEES ACROSS THE UAE &amp;amp; GCC UNTIL MARCH 31, 2026! 💳🔥
-#UAE #EmiratesNBD #Banking #Finance #ATM #NoFees #GCC #MoneySmart https://t.co/aI9H5crVgx</t>
+          <t>Save and earn with your Emirates Islamic Super Savings Etihad Guest Account!
+💸 Get up to 750,000 Etihad Guest Miles every quarter and up to 3 million Etihad Guest Miles in a year https://t.co/y8cuMSrpQL</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>🚨 JUST IN: 🇦🇪 EMIRATES NBD ELIMINATES ATM WITHDRAWAL &amp;amp; DEBIT CARD FEES ACROSS THE UAE &amp;amp; GCC UNTIL MARCH 31, 2026! 💳🔥
-#UAE #EmiratesNBD #Banking #Finance #ATM #NoFees #GCC #MoneySmart https://t.co/aI9H5crVgx</t>
+          <t>Save and earn with your Emirates Islamic Super Savings Etihad Guest Account!
+💸 Get up to 750,000 Etihad Guest Miles every quarter and up to 3 million Etihad Guest Miles in a year https://t.co/y8cuMSrpQL</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>JUST IN: EMIRATES NBD ELIMINATES ATM WITHDRAWAL &amp; DEBIT CARD FEES ACROSS THE UAE &amp; GCC UNTIL MARCH 31, 2026!</t>
+          <t>Save and earn with your Emirates Islamic Super Savings Etihad Guest Account! 
+Get up to 750,000 Etihad Guest Miles every quarter and up to 3 million Etihad Guest Miles in a year.</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -5725,29 +5723,29 @@
         </is>
       </c>
       <c r="AE32" s="2" t="n">
-        <v>46128.20972222222</v>
+        <v>46128.82569444444</v>
       </c>
       <c r="AF32" s="2" t="n">
         <v>46128</v>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
+          <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>JUST IN: EMIRATES NBD ELIMINATES ATM WITHDRAWAL &amp; DEBIT CARD FEES ACROSS THE UAE &amp; GCC UNTIL MARCH 31, 2026!</t>
+          <t>Get up to 750,000 Etihad Guest Miles every quarter and up to 3 million Etihad Guest Miles in a year. • Save and earn with your Emirates Islamic Super Savings Etihad Guest Account!</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank (ENBD)</t>
+          <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AK32" t="n">
@@ -5755,7 +5753,7 @@
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>CryptoNewsHntrs</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
     </row>
@@ -5765,45 +5763,43 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2044805287459398125</t>
+          <t>2044758862017007662</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://x.com/1ss9490ss1/status/2044805287459398125</t>
+          <t>https://x.com/RakeshMavath/status/2044758862017007662</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://x.com/1ss9490ss1</t>
+          <t>https://x.com/RakeshMavath</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1ss9490ss1</t>
+          <t>RakeshMavath</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>بوالسلطان</t>
+          <t>Rakesh Mavath</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/777077466515079168/MKR49yEx_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2013866142125957122/nsrKPIws_bigger.jpg</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Save and earn with your Emirates Islamic Super Savings Etihad Guest Account!
-💸 Get up to 750,000 Etihad Guest Miles every quarter and up to 3 million Etihad Guest Miles in a year https://t.co/y8cuMSrpQL</t>
+          <t>especially now they are not going to let go of your business easily. you can raise the issue with UAECB who will in turn contact the bank</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>السلام عليكم ورحمه الله وبركاته 
-الرجاء التواصل بي باحد من خدمة العملاء.</t>
+          <t>especially now they are not going to let go of your business easily. you can raise the issue with UAECB who will in turn contact the bank</t>
         </is>
       </c>
       <c r="K33" t="b">
@@ -5812,35 +5808,35 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>['emiratesislamic']</t>
+          <t>['aaditsh', 'emiratesislamic']</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Apr 16, 2026 · 3:49 PM UTC</t>
+          <t>Apr 16, 2026 · 12:44 PM UTC</t>
         </is>
       </c>
       <c r="P33" s="2" t="n">
-        <v>46128.65902777778</v>
+        <v>46128.53055555555</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T33" t="n">
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V33" t="n">
-        <v>2</v>
+        <v>136</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
@@ -5849,31 +5845,19 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>السلام عليكم ورحمه الله وبركاته 
-الرجاء التواصل بي باحد من خدمة العملاء.</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>https://x.com/1ss9490ss1/status/2044805287459398125</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>Save and earn with your Emirates Islamic Super Savings Etihad Guest Account!
-💸 Get up to 750,000 Etihad Guest Miles every quarter and up to 3 million Etihad Guest Miles in a year https://t.co/y8cuMSrpQL</t>
-        </is>
-      </c>
+          <t>especially now they are not going to let go of your business easily. you can raise the issue with UAECB who will in turn contact the bank</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>Save and earn with your Emirates Islamic Super Savings Etihad Guest Account!
-💸 Get up to 750,000 Etihad Guest Miles every quarter and up to 3 million Etihad Guest Miles in a year https://t.co/y8cuMSrpQL</t>
+          <t>especially now they are not going to let go of your business easily. you can raise the issue with UAECB who will in turn contact the bank</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Save and earn with your Emirates Islamic Super Savings Etihad Guest Account! 
-Get up to 750,000 Etihad Guest Miles every quarter and up to 3 million Etihad Guest Miles in a year.</t>
+          <t>Especially now, they are not going to let go of your business easily. You can raise the issue with UAECB, who will in turn contact the bank.</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -5883,11 +5867,11 @@
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE33" s="2" t="n">
-        <v>46128.82569444444</v>
+        <v>46128.69722222222</v>
       </c>
       <c r="AF33" s="2" t="n">
         <v>46128</v>
@@ -5904,7 +5888,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Get up to 750,000 Etihad Guest Miles every quarter and up to 3 million Etihad Guest Miles in a year. • Save and earn with your Emirates Islamic Super Savings Etihad Guest Account!</t>
+          <t>You can raise the issue with UAECB, who will in turn contact the bank. • Especially now, they are not going to let go of your business easily.</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -5917,7 +5901,7 @@
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>aaditsh, emiratesislamic</t>
         </is>
       </c>
     </row>
@@ -5927,80 +5911,86 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2044758862017007662</t>
+          <t>2044732404938702855</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://x.com/RakeshMavath/status/2044758862017007662</t>
+          <t>https://x.com/aaditsh/status/2044732404938702855</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://x.com/RakeshMavath</t>
+          <t>https://x.com/aaditsh</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RakeshMavath</t>
+          <t>aaditsh</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rakesh Mavath</t>
+          <t>Aadit Sheth</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2013866142125957122/nsrKPIws_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1989274279947694081/ggQkOhbP_bigger.jpg</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>especially now they are not going to let go of your business easily. you can raise the issue with UAECB who will in turn contact the bank</t>
+          <t>This is one of my favorite ideas in all of writing.
+Ed Sheeran calls it the dirty tap.
+Turn it on, dirty water flows out for a long time. Eventually clean water starts coming. He's talking about songs but it's true for all creative work.
+Every CEO memo that got quoted. Every keynote that landed. Every email that actually changed someone's mind. All of it came out of a dozen bad drafts first.
+The dirty water is necessary. You need to get the bad ideas out before the good ones come. That's just how it works.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>especially now they are not going to let go of your business easily. you can raise the issue with UAECB who will in turn contact the bank</t>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; probably the worst customer experience I’ve had in my life.
+Tried cancelling my cards. Have received 10+ phone calls from them trying to retain. Confirmed each time that I want to cancel (on call and on email confirmation). It’s been 4-5 months since I raised this complaint. No resolution yet.
+Impressed with how difficult they make this process. Wow!</t>
         </is>
       </c>
       <c r="K34" t="b">
         <v>0</v>
       </c>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>['aaditsh', 'emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Apr 16, 2026 · 12:44 PM UTC</t>
+          <t>Apr 16, 2026 · 10:59 AM UTC</t>
         </is>
       </c>
       <c r="P34" s="2" t="n">
-        <v>46128.53055555555</v>
+        <v>46128.45763888889</v>
       </c>
       <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V34" t="n">
-        <v>136</v>
+        <v>5653</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -6009,19 +5999,37 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>especially now they are not going to let go of your business easily. you can raise the issue with UAECB who will in turn contact the bank</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
+          <t>@emiratesislamic probably the worst customer experience I’ve had in my life.
+Tried cancelling my cards. Have received 10+ phone calls from them trying to retain. Confirmed each time that I want to cancel (on call and on email confirmation). It’s been 4-5 months since I raised this complaint. No resolution yet.
+Impressed with how difficult they make this process. Wow!</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>https://x.com/aaditsh/status/2044732404938702855</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>This is one of my favorite ideas in all of writing.
+Ed Sheeran calls it the dirty tap.
+Turn it on, dirty water flows out for a long time. Eventually clean water starts coming. He's talking about songs but it's true for all creative work.
+Every CEO memo that got quoted. Every keynote that landed. Every email that actually changed someone's mind. All of it came out of a dozen bad drafts first.
+The dirty water is necessary. You need to get the bad ideas out before the good ones come. That's just how it works.</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>especially now they are not going to let go of your business easily. you can raise the issue with UAECB who will in turn contact the bank</t>
+          <t>This is one of my favorite ideas in all of writing.
+Ed Sheeran calls it the dirty tap.
+Turn it on, dirty water flows out for a long time. Eventually clean water starts coming. He's talking about songs but it's true for all creative work.
+Every CEO memo that got quoted. Every keynote that landed. Every email that actually changed someone's mind. All of it came out of a dozen bad drafts first.
+The dirty water is necessary. You need to get the bad ideas out before the good ones come. That's just how it works.</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Especially now, they are not going to let go of your business easily. You can raise the issue with UAECB, who will in turn contact the bank.</t>
+          <t>This is one of my favorite ideas in all of writing. Ed Sheeran calls it the dirty tap. Turn it on, dirty water flows out for a long time. Eventually clean water starts coming. He's talking about songs but it's true for all creative work. Every CEO memo that got quoted. Every keynote that landed. Every email that actually changed someone's mind. All of it came out of a dozen bad drafts first. The dirty water is necessary. You need to get the bad ideas out before the good ones come. That's just how it works.</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -6035,7 +6043,7 @@
         </is>
       </c>
       <c r="AE34" s="2" t="n">
-        <v>46128.69722222222</v>
+        <v>46128.62430555555</v>
       </c>
       <c r="AF34" s="2" t="n">
         <v>46128</v>
@@ -6052,7 +6060,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>You can raise the issue with UAECB, who will in turn contact the bank. • Especially now, they are not going to let go of your business easily.</t>
+          <t>Turn it on, dirty water flows out for a long time. • You need to get the bad ideas out before the good ones come. • He's talking about songs but it's true for all creative work.</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
@@ -6065,7 +6073,7 @@
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>aaditsh, emiratesislamic</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7717,7 +7725,7 @@
           <t>ليست المشكلة فيما تنفقه، بل في ما يتسرّب منه بصمت.
 فالمبالغ الصغيرة التي نظنها "غير مهمّة"، هي غالباً ما تتراكم وتؤثر على ميزانيتك أكثر مما تتوقع.
 #نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-https://t.co/mgtIcQsyLZ</t>
+emiratesislamic.ae/ar/key-in…</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -7777,25 +7785,14 @@
 emiratesislamic.ae/ar/key-in…</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2044657039859757511</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr">
         <is>
           <t>ليست المشكلة فيما تنفقه، بل في ما يتسرّب منه بصمت.
 فالمبالغ الصغيرة التي نظنها "غير مهمّة"، هي غالباً ما تتراكم وتؤثر على ميزانيتك أكثر مما تتوقع.
 #نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-https://t.co/mgtIcQsyLZ</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>ليست المشكلة فيما تنفقه، بل في ما يتسرّب منه بصمت.
-فالمبالغ الصغيرة التي نظنها "غير مهمّة"، هي غالباً ما تتراكم وتؤثر على ميزانيتك أكثر مما تتوقع.
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-https://t.co/mgtIcQsyLZ</t>
+emiratesislamic.ae/ar/key-in…</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
@@ -8017,12 +8014,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2044732404938702855</t>
+          <t>2044759599656689929</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://x.com/aaditsh/status/2044732404938702855</t>
+          <t>https://x.com/aaditsh/status/2044759599656689929</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -8048,53 +8045,51 @@
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>@emiratesislamic probably the worst customer experience I’ve had in my life.
-Tried cancelling my cards. Have received 10+ phone calls from them trying to retain. Confirmed each time that I want to cancel (on call and on email confirmation). It’s been 4-5 months since I raised this complaint. No resolution yet.
-Impressed with how difficult they make this process. Wow!</t>
+          <t>Will do! So frustrating. They will call me, I’ll pick up. They will end the call within 10 seconds and message me “we called you. You didn’t pick up”.
+And it’s been extended like this for the past 4-5 months. What a joke.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; probably the worst customer experience I’ve had in my life.
-Tried cancelling my cards. Have received 10+ phone calls from them trying to retain. Confirmed each time that I want to cancel (on call and on email confirmation). It’s been 4-5 months since I raised this complaint. No resolution yet.
-Impressed with how difficult they make this process. Wow!</t>
+          <t>Will do! So frustrating. They will call me, I’ll pick up. They will end the call within 10 seconds and message me “we called you. You didn’t pick up”.
+And it’s been extended like this for the past 4-5 months. What a joke.</t>
         </is>
       </c>
       <c r="K47" t="b">
         <v>0</v>
       </c>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>['RakeshMavath', 'emiratesislamic']</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Apr 16, 2026 · 10:59 AM UTC</t>
+          <t>Apr 16, 2026 · 12:47 PM UTC</t>
         </is>
       </c>
       <c r="P47" s="2" t="n">
-        <v>46128.45763888889</v>
+        <v>46128.53263888889</v>
       </c>
       <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>['https://x.com/emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="R47" t="inlineStr"/>
       <c r="S47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T47" t="n">
         <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V47" t="n">
-        <v>5653</v>
+        <v>140</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
@@ -8103,23 +8098,22 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>@emiratesislamic probably the worst customer experience I’ve had in my life.
-Tried cancelling my cards. Have received 10+ phone calls from them trying to retain. Confirmed each time that I want to cancel (on call and on email confirmation). It’s been 4-5 months since I raised this complaint. No resolution yet.
-Impressed with how difficult they make this process. Wow!</t>
+          <t>Will do! So frustrating. They will call me, I’ll pick up. They will end the call within 10 seconds and message me “we called you. You didn’t pick up”.
+And it’s been extended like this for the past 4-5 months. What a joke.</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>@emiratesislamic probably the worst customer experience I’ve had in my life.
-Tried cancelling my cards. Have received 10+ phone calls from them trying to retain. Confirmed each time that I want to cancel (on call and on email confirmation). It’s been 4-5 months since I raised this complaint. No resolution yet.
-Impressed with how difficult they make this process. Wow!</t>
+          <t>Will do! So frustrating. They will call me, I’ll pick up. They will end the call within 10 seconds and message me “we called you. You didn’t pick up”.
+And it’s been extended like this for the past 4-5 months. What a joke.</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>probably the worst customer experience I’ve had in my life. Tried cancelling my cards. Have received 10+ phone calls from them trying to retain. Confirmed each time that I want to cancel (on call and on email confirmation). It’s been 4-5 months since I raised this complaint. No resolution yet. Impressed with how difficult they make this process. Wow!</t>
+          <t>Will do! So frustrating. They will call me, I’ll pick up. They will end the call within 10 seconds and message me “we called you. You didn’t pick up”. 
+And it’s been like this for the past 4-5 months. What a joke.</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -8133,7 +8127,7 @@
         </is>
       </c>
       <c r="AE47" s="2" t="n">
-        <v>46128.62430555555</v>
+        <v>46128.69930555556</v>
       </c>
       <c r="AF47" s="2" t="n">
         <v>46128</v>
@@ -8150,7 +8144,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Have received 10+ phone calls from them trying to retain. • Confirmed each time that I want to cancel (on call and on email confirmation). • It’s been 4-5 months since I raised this complaint.</t>
+          <t>They will end the call within 10 seconds and message me “we called you. • They will call me, I’ll pick up. • And it’s been like this for the past 4-5 months.</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -8163,7 +8157,7 @@
       </c>
       <c r="AL47" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>RakeshMavath, emiratesislamic</t>
         </is>
       </c>
     </row>
@@ -8293,7 +8287,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>Peace be upon you. I visited branch 06 at the mall last Tuesday to break the deposit and pay the remaining loan amount. The respectful employee informed me that an email would be sent to the management to find out the steps, and as of today, Thursday, the management has not responded to them. Is this delay justified or a lack of concern for customers?</t>
+          <t>Peace be upon you. I visited branch 06 at the mall last Tuesday to break the deposit and pay the remaining loan amount. The respectful employee informed me that an email would be sent to the management to find out the steps, and as of today, Thursday, the management has not responded to them. Is this delay justified or is it a lack of concern for customers?</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -8324,7 +8318,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>The respectful employee informed me that an email would be sent to the management to find out the steps, and as of today, Thursday, the management has not responded to them. • I visited branch 06 at the mall last Tuesday to break the deposit and pay the remaining loan amount. • Is this delay justified or a lack of concern for customers?</t>
+          <t>The respectful employee informed me that an email would be sent to the management to find out the steps, and as of today, Thursday, the management has not responded to them. • I visited branch 06 at the mall last Tuesday to break the deposit and pay the remaining loan amount. • Is this delay justified or is it a lack of concern for customers?</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -8507,36 +8501,197 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2044777257898578369</t>
+          <t>2044734491336282349</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://x.com/mohamed50575321/status/2044777257898578369</t>
+          <t>https://x.com/masryeng/status/2044734491336282349</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://x.com/mohamed50575321</t>
+          <t>https://x.com/masryeng</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>mohamed50575321</t>
+          <t>masryeng</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Alaa</t>
+          <t>El-Sayed El-Masry</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1651667220303429632/pOQsNF9e_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1768318685356130304/iD9SmaJ3_bigger.jpg</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE نزلتوا غرامه غير مستحقه علي بطاقة فيزا الائتمانية ورفعت ايميل بالمشكلة ولا تن الرد 
+لا انصح بالتعامل معهم</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>نزلتوا غرامه غير مستحقه علي بطاقة فيزا الائتمانية ورفعت ايميل بالمشكلة ولا تن الرد 
+لا انصح بالتعامل معهم</t>
+        </is>
+      </c>
+      <c r="K50" t="b">
+        <v>0</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Apr 16, 2026 · 11:07 AM UTC</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="n">
+        <v>46128.46319444444</v>
+      </c>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="n">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>15</v>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>نزلتوا غرامه غير مستحقه علي بطاقة فيزا الائتمانية ورفعت ايميل بالمشكلة ولا تن الرد 
+لا انصح بالتعامل معهم</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>https://x.com/masryeng/status/2044734491336282349</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE نزلتوا غرامه غير مستحقه علي بطاقة فيزا الائتمانية ورفعت ايميل بالمشكلة ولا تن الرد 
+لا انصح بالتعامل معهم</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE نزلتوا غرامه غير مستحقه علي بطاقة فيزا الائتمانية ورفعت ايميل بالمشكلة ولا تن الرد 
+لا انصح بالتعامل معهم</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>You charged an unjustified fee to my credit card, and I sent an email about the issue but received no response. I do not recommend dealing with them.</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AE50" s="2" t="n">
+        <v>46128.62986111111</v>
+      </c>
+      <c r="AF50" s="2" t="n">
+        <v>46128</v>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>You charged an unjustified fee to my credit card, and I sent an email about the issue but received no response. • I do not recommend dealing with them.</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK50" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL50" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2044777257898578369</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://x.com/mohamed50575321/status/2044777257898578369</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://x.com/mohamed50575321</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>mohamed50575321</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Alaa</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1651667220303429632/pOQsNF9e_bigger.png</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
         <is>
           <t>@EmiratesNBD_SA
 حدد visa campain
@@ -8547,7 +8702,7 @@
 طريقه احتيال يجب فيها التحقيق</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; تواصلت مع visa airport campain
 و اكدوا عدم خصم اى رسوم من قبلهم
@@ -8556,48 +8711,48 @@
 لانه البنك الوحيد اللى فعل هذا</t>
         </is>
       </c>
-      <c r="K50" t="b">
-        <v>0</v>
-      </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr">
+      <c r="K51" t="b">
+        <v>0</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
         <is>
           <t>12h</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>Apr 16, 2026 · 1:57 PM UTC</t>
         </is>
       </c>
-      <c r="P50" s="2" t="n">
+      <c r="P51" s="2" t="n">
         <v>46128.58125</v>
       </c>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr">
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr">
         <is>
           <t>['https://x.com/EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="S50" t="n">
+      <c r="S51" t="n">
         <v>1</v>
       </c>
-      <c r="T50" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" t="n">
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
         <v>11</v>
       </c>
-      <c r="W50" t="inlineStr">
+      <c r="W51" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE تواصلت مع visa airport campain
 و اكدوا عدم خصم اى رسوم من قبلهم
@@ -8606,12 +8761,12 @@
 لانه البنك الوحيد اللى فعل هذا</t>
         </is>
       </c>
-      <c r="Y50" t="inlineStr">
+      <c r="Y51" t="inlineStr">
         <is>
           <t>https://x.com/mohamed50575321/status/2044777257898578369</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
+      <c r="Z51" t="inlineStr">
         <is>
           <t>@EmiratesNBD_SA
 حدد visa campain
@@ -8622,7 +8777,7 @@
 طريقه احتيال يجب فيها التحقيق</t>
         </is>
       </c>
-      <c r="AA50" t="inlineStr">
+      <c r="AA51" t="inlineStr">
         <is>
           <t>@EmiratesNBD_SA
 حدد visa campain
@@ -8633,172 +8788,24 @@
 طريقه احتيال يجب فيها التحقيق</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
+      <c r="AB51" t="inlineStr">
         <is>
           <t>Emirates NBD_SA
 The visa campaign requires spending $100 to make the card valid for 90 days for lounge access. Meanwhile, Emirates NBD Saudi Arabia has imposed its own condition of spending 3,000 riyals in the same month. Additionally, the bank charged me a fee of $32 without justification. This is a fraudulent practice that needs to be investigated.</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
+      <c r="AC51" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="AD50" t="inlineStr">
+      <c r="AD51" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="AE50" s="2" t="n">
+      <c r="AE51" s="2" t="n">
         <v>46128.74791666667</v>
-      </c>
-      <c r="AF50" s="2" t="n">
-        <v>46128</v>
-      </c>
-      <c r="AG50" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>Emirates NBD_SA The visa campaign requires spending $100 to make the card valid for 90 days for lounge access. • Meanwhile, Emirates NBD Saudi Arabia has imposed its own condition of spending 3,000 riyals in the same month. • Additionally, the bank charged me a fee of $32 without justification.</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK50" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL50" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="n">
-        <v>49</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2044676172248690733</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>https://x.com/msa3474/status/2044676172248690733</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>https://x.com/msa3474</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>msa3474</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>AHMARI</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1943001907854802944/sB6fjZIf_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>السلام عليكم ورحمه الله وبركاته الساده بنك الإمارات دبي الوطني المحترمين الرجاء حل مشكلتي مع فرع شارع الامير سلطان بجدة حيث انني طلبت منهم إيصال سداد مديونية ولي الى الآن اسبوع كامل لم يصلني الرد.</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>السلام عليكم ورحمه الله وبركاته الساده بنك الإمارات دبي الوطني المحترمين الرجاء حل مشكلتي مع فرع شارع الامير سلطان بجدة حيث انني طلبت منهم إيصال سداد مديونية ولي الى الآن اسبوع كامل لم يصلني الرد.</t>
-        </is>
-      </c>
-      <c r="K51" t="b">
-        <v>0</v>
-      </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_KSA']</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>19h</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>Apr 16, 2026 · 7:16 AM UTC</t>
-        </is>
-      </c>
-      <c r="P51" s="2" t="n">
-        <v>46128.30277777778</v>
-      </c>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="n">
-        <v>1</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" t="n">
-        <v>71</v>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>السلام عليكم ورحمه الله وبركاته الساده بنك الإمارات دبي الوطني المحترمين الرجاء حل مشكلتي مع فرع شارع الامير سلطان بجدة حيث انني طلبت منهم إيصال سداد مديونية ولي الى الآن اسبوع كامل لم يصلني الرد.</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr"/>
-      <c r="Z51" t="inlineStr"/>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>السلام عليكم ورحمه الله وبركاته الساده بنك الإمارات دبي الوطني المحترمين الرجاء حل مشكلتي مع فرع شارع الامير سلطان بجدة حيث انني طلبت منهم إيصال سداد مديونية ولي الى الآن اسبوع كامل لم يصلني الرد.</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>Peace be upon you. Dear Emirates NBD Bank, I kindly request your assistance in resolving my issue with the Prince Sultan Street branch in Jeddah, as I requested a payment receipt for my debt and have not received a response for a full week.</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="AE51" s="2" t="n">
-        <v>46128.46944444445</v>
       </c>
       <c r="AF51" s="2" t="n">
         <v>46128</v>
@@ -8815,7 +8822,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Peace be upon you. Dear Emirates NBD Bank, I kindly request your assistance in resolving my issue with the Prince Sultan…</t>
+          <t>Emirates NBD_SA The visa campaign requires spending $100 to make the card valid for 90 days for lounge access. • Meanwhile, Emirates NBD Saudi Arabia has imposed its own condition of spending 3,000 riyals in the same month. • Additionally, the bank charged me a fee of $32 without justification.</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
@@ -8827,6 +8834,154 @@
         <v>2026</v>
       </c>
       <c r="AL51" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2044676172248690733</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://x.com/msa3474/status/2044676172248690733</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://x.com/msa3474</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>msa3474</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>AHMARI</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1943001907854802944/sB6fjZIf_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>السلام عليكم ورحمه الله وبركاته الساده بنك الإمارات دبي الوطني المحترمين الرجاء حل مشكلتي مع فرع شارع الامير سلطان بجدة حيث انني طلبت منهم إيصال سداد مديونية ولي الى الآن اسبوع كامل لم يصلني الرد.</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>السلام عليكم ورحمه الله وبركاته الساده بنك الإمارات دبي الوطني المحترمين الرجاء حل مشكلتي مع فرع شارع الامير سلطان بجدة حيث انني طلبت منهم إيصال سداد مديونية ولي الى الآن اسبوع كامل لم يصلني الرد.</t>
+        </is>
+      </c>
+      <c r="K52" t="b">
+        <v>0</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Apr 16, 2026 · 7:16 AM UTC</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="n">
+        <v>46128.30277777778</v>
+      </c>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="n">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" t="n">
+        <v>71</v>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>السلام عليكم ورحمه الله وبركاته الساده بنك الإمارات دبي الوطني المحترمين الرجاء حل مشكلتي مع فرع شارع الامير سلطان بجدة حيث انني طلبت منهم إيصال سداد مديونية ولي الى الآن اسبوع كامل لم يصلني الرد.</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>السلام عليكم ورحمه الله وبركاته الساده بنك الإمارات دبي الوطني المحترمين الرجاء حل مشكلتي مع فرع شارع الامير سلطان بجدة حيث انني طلبت منهم إيصال سداد مديونية ولي الى الآن اسبوع كامل لم يصلني الرد.</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>Peace be upon you. Dear Emirates NBD Bank, I kindly request your assistance in resolving my issue with the Prince Sultan Street branch in Jeddah. I requested a payment receipt for my debt, and it has been a full week without a response.</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AE52" s="2" t="n">
+        <v>46128.46944444445</v>
+      </c>
+      <c r="AF52" s="2" t="n">
+        <v>46128</v>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Dear Emirates NBD Bank, I kindly request your assistance in resolving my issue with the Prince Sultan Street branch in Jeddah. • I requested a payment receipt for my debt, and it has been a full week without a response.</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK52" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL52" t="inlineStr">
         <is>
           <t>EmiratesNBD_KSA</t>
         </is>

--- a/check2.xlsx
+++ b/check2.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL29"/>
+  <dimension ref="A1:AL22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,217 +625,36 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2045277395985526953</t>
+          <t>2046061240511082734</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/InnerSunshine9/status/2045277395985526953</t>
+          <t>https://x.com/she7ii88/status/2046061240511082734</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/InnerSunshine9</t>
+          <t>https://x.com/she7ii88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>InnerSunshine9</t>
+          <t>she7ii88</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>InnerSunshine</t>
+          <t>Rashed Sem</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1988072486542733312/nEKgrRmJ_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1752368468144316416/8qdE3N-C_bigger.png</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>Animated Kindness Video, share!
-CGI Animated Short Film: "Mr Indifferent" by Aryasb Feiz | CGMeetup
-https://t.co/jqAIbUi4ot
-Made for Emirates NBD Bank.
-Agency: Leo Burnett, Dubai
-Celebrating World Kindness Day</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Animated Kindness Video, share!
-CGI Animated Short Film: &amp;#34;Mr Indifferent&amp;#34; by Aryasb Feiz | CGMeetup
-&lt;a href="https://invidious.tiekoetter.com/watch?v=qLGNj-xrgvY"&gt;invidious.tiekoetter.com/watch?v=qLGNj-xr…&lt;/a&gt;
-Made for Emirates NBD Bank.
-Agency: Leo Burnett, Dubai
-Celebrating World Kindness Day</t>
-        </is>
-      </c>
-      <c r="K2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>4h</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Apr 17, 2026 · 11:05 PM UTC</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="n">
-        <v>46129.96180555555</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>['https://invidious.tiekoetter.com/watch?v=qLGNj-xrgvY']</t>
-        </is>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>20</v>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Animated Kindness Video, share!
-CGI Animated Short Film: "Mr Indifferent" by Aryasb Feiz | CGMeetup
-invidious.tiekoetter.com/watch?v=qLGNj-xr…
-Made for Emirates NBD Bank.
-Agency: Leo Burnett, Dubai
-Celebrating World Kindness Day</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>https://x.com/InnerSunshine9/status/2045277395985526953</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Animated Kindness Video, share!
-CGI Animated Short Film: "Mr Indifferent" by Aryasb Feiz | CGMeetup
-https://t.co/jqAIbUi4ot
-Made for Emirates NBD Bank.
-Agency: Leo Burnett, Dubai
-Celebrating World Kindness Day</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Animated Kindness Video, share!
-CGI Animated Short Film: "Mr Indifferent" by Aryasb Feiz | CGMeetup
-https://t.co/jqAIbUi4ot
-Made for Emirates NBD Bank.
-Agency: Leo Burnett, Dubai
-Celebrating World Kindness Day</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Animated Kindness Video, share! CGI Animated Short Film: "Mr Indifferent" by Aryasb Feiz | CGMeetup Made for Emirates NBD Bank. Agency: Leo Burnett, Dubai Celebrating World Kindness Day</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="AE2" s="2" t="n">
-        <v>46130.12847222222</v>
-      </c>
-      <c r="AF2" s="2" t="n">
-        <v>46130</v>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>CGI Animated Short Film: "Mr Indifferent" by Aryasb Feiz | CGMeetup Made for Emirates NBD Bank. • Agency: Leo Burnett, Dubai Celebrating World Kindness Day • Animated Kindness Video, share!</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2045251200086663547</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://x.com/xmn9oori/status/2045251200086663547</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>https://x.com/xmn9oori</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>xmn9oori</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>بوسلطان 💜</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2034089445235036165/s553Bp_u_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
         <is>
           <t>ندعم من يحمون الوطن
 مجموعة من مزايا الدعم المالي والخدمات المصرفية المخصصة للعاملين في الصفوف الأمامية
@@ -849,63 +668,67 @@
 https://t.co/I7DGlib9vt</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>لمدة كم الاسترداد؟</t>
-        </is>
-      </c>
-      <c r="K3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>هذا عرض صدق ؟! 
+٦% ؟! سلامات البنوك الاسلاميه المرابحه الثابته ٢.٧% ؟! 
+ولو سمحتوا علم الامارات و لبس القوات المسلحه ... ليست دعايه</t>
+        </is>
+      </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>6h</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Apr 17, 2026 · 9:20 PM UTC</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="n">
-        <v>46129.88888888889</v>
-      </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>70</v>
-      </c>
-      <c r="W3" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 2:59 AM UTC</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>46132.12430555555</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>11</v>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>لمدة كم الاسترداد؟</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>https://x.com/xmn9oori/status/2045251200086663547</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>هذا عرض صدق ؟! 
+٦% ؟! سلامات البنوك الاسلاميه المرابحه الثابته ٢.٧% ؟! 
+ولو سمحتوا علم الامارات و لبس القوات المسلحه ... ليست دعايه</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>https://x.com/she7ii88/status/2046061240511082734</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>ندعم من يحمون الوطن
 مجموعة من مزايا الدعم المالي والخدمات المصرفية المخصصة للعاملين في الصفوف الأمامية
@@ -919,7 +742,7 @@
 https://t.co/I7DGlib9vt</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>ندعم من يحمون الوطن
 مجموعة من مزايا الدعم المالي والخدمات المصرفية المخصصة للعاملين في الصفوف الأمامية
@@ -933,7 +756,7 @@
 https://t.co/I7DGlib9vt</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>We support those who protect the homeland
 A range of financial support and banking services dedicated to frontline workers:
@@ -946,6 +769,167 @@
 Terms and conditions apply.</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AE2" s="2" t="n">
+        <v>46132.29097222222</v>
+      </c>
+      <c r="AF2" s="2" t="n">
+        <v>46132</v>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Terms and conditions apply.</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2046033950339166455</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://x.com/Kyodonews_JBN/status/2046033950339166455</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://x.com/Kyodonews_JBN</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Kyodonews_JBN</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>KYODONEWS JBN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2003285704613462020/Gn9wk2B__bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Emirates NBD、Dar Global向け2億5,000万米ドルのシンジケート・タームローンを実行し、世界的な成長と事業拡大を加速【Dar Global】
+https://t.co/H82MnfRa04</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Emirates NBD、Dar Global向け2億5,000万米ドルのシンジケート・タームローンを実行し、世界的な成長と事業拡大を加速【Dar Global】
+&lt;a href="https://kyodonewsprwire.jp/release/202604177681"&gt;kyodonewsprwire.jp/release/2…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2h</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 1:11 AM UTC</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>46132.04930555556</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>['https://kyodonewsprwire.jp/release/202604177681']</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>4</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Emirates NBD、Dar Global向け2億5,000万米ドルのシンジケート・タームローンを実行し、世界的な成長と事業拡大を加速【Dar Global】
+kyodonewsprwire.jp/release/2…</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>https://x.com/Kyodonews_JBN/status/2046033950339166455</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Emirates NBD、Dar Global向け2億5,000万米ドルのシンジケート・タームローンを実行し、世界的な成長と事業拡大を加速【Dar Global】
+https://t.co/H82MnfRa04</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Emirates NBD、Dar Global向け2億5,000万米ドルのシンジケート・タームローンを実行し、世界的な成長と事業拡大を加速【Dar Global】
+https://t.co/H82MnfRa04</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Emirates NBD executed a $250 million syndicated term loan for Dar Global to accelerate global growth and business expansion.</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
           <t>Cust</t>
@@ -957,10 +941,10 @@
         </is>
       </c>
       <c r="AE3" s="2" t="n">
-        <v>46130.05555555555</v>
+        <v>46132.21597222222</v>
       </c>
       <c r="AF3" s="2" t="n">
-        <v>46130</v>
+        <v>46132</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
@@ -974,7 +958,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Terms and conditions apply.</t>
+          <t>Emirates NBD executed a $250 million syndicated term loan for Dar Global to accelerate global growth and business expansion.</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -987,7 +971,7 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -997,44 +981,48 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2045169182015139851</t>
+          <t>2045894623957278735</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/MC81236843/status/2045169182015139851</t>
+          <t>https://x.com/almidfa75/status/2045894623957278735</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/MC81236843</t>
+          <t>https://x.com/almidfa75</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MC81236843</t>
+          <t>almidfa75</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>M C</t>
+          <t>Faisal Al Midfa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1163517530822119426/IK5LwgTg_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/692030305365000192/rYQ6PWnr_bigger.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>🤫🤫🤫😉</t>
+          <t>🧵 1/
+في خطوة تعكس تطور المنتجات المالية في السوق العقاري بدولة الإمارات، أعلن بنك Emirates NBD عن إطلاق نموذج تمويل مبكر للعقارات قيد الإنشاء (Off-plan)، بالتعاون مع Dubai Holding Real Estate.
+#دبي #القطاع_العقاري #التمويل https://t.co/qdzz3FJ7io</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Emirates NBD und Nium bündeln ihre Kräfte, um den globalen grenzüberschreitenden Zahlungsverkehr im Nahen Osten zu transformieren
-&lt;a href="https://www.worldfinanceinforms.com/cards-payments/emirates-nbd-and-nium-join-forces-to-transform-global-cross-border-payments-in-the-middle-east"&gt;worldfinanceinforms.com/card…&lt;/a&gt;</t>
+          <t>🧵 6/
+🎯 خلاصة:
+يمثل هذا الإعلان خطوة نوعية في تطوير حلول التمويل العقاري، ويعكس توجه المؤسسات المالية نحو تقديم منتجات أكثر مرونة تدعم نمو واستدامة السوق العقاري في دولة الإمارات.
+&lt;a href="/search?f=tweets&amp;amp;q=%23دبي"&gt;#دبي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التمويل_العقاري"&gt;#التمويل_العقاري&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23استثمار"&gt;#استثمار&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23DubaiHolding"&gt;#DubaiHolding&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K4" t="b">
@@ -1049,29 +1037,29 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 3:55 PM UTC</t>
+          <t>Apr 19, 2026 · 3:57 PM UTC</t>
         </is>
       </c>
       <c r="P4" s="2" t="n">
-        <v>46129.66319444445</v>
+        <v>46131.66458333333</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t>['https://www.worldfinanceinforms.com/cards-payments/emirates-nbd-and-nium-join-forces-to-transform-global-cross-border-payments-in-the-middle-east']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23دبي', 'https://x.com/search?f=tweets&amp;q=%23التمويل_العقاري', 'https://x.com/search?f=tweets&amp;q=%23استثمار', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23DubaiHolding']</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>102</v>
+        <v>38</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -1080,28 +1068,34 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Emirates NBD und Nium bündeln ihre Kräfte, um den globalen grenzüberschreitenden Zahlungsverkehr im Nahen Osten zu transformieren
-worldfinanceinforms.com/card…</t>
+          <t>🧵 6/
+🎯 خلاصة:
+يمثل هذا الإعلان خطوة نوعية في تطوير حلول التمويل العقاري، ويعكس توجه المؤسسات المالية نحو تقديم منتجات أكثر مرونة تدعم نمو واستدامة السوق العقاري في دولة الإمارات.
+#دبي #التمويل_العقاري #استثمار #EmiratesNBD #DubaiHolding</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>https://x.com/MC81236843/status/2045169182015139851</t>
+          <t>https://x.com/almidfa75/status/2045894623957278735</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>🤫🤫🤫😉</t>
+          <t>🧵 1/
+في خطوة تعكس تطور المنتجات المالية في السوق العقاري بدولة الإمارات، أعلن بنك Emirates NBD عن إطلاق نموذج تمويل مبكر للعقارات قيد الإنشاء (Off-plan)، بالتعاون مع Dubai Holding Real Estate.
+#دبي #القطاع_العقاري #التمويل https://t.co/qdzz3FJ7io</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>🤫🤫🤫😉</t>
+          <t>🧵 1/
+في خطوة تعكس تطور المنتجات المالية في السوق العقاري بدولة الإمارات، أعلن بنك Emirates NBD عن إطلاق نموذج تمويل مبكر للعقارات قيد الإنشاء (Off-plan)، بالتعاون مع Dubai Holding Real Estate.
+#دبي #القطاع_العقاري #التمويل https://t.co/qdzz3FJ7io</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>The text consists of emojis and does not contain any language to translate.</t>
+          <t>In a move that reflects the evolution of financial products in the real estate market in the UAE, Emirates NBD Bank announced the launch of an early financing model for off-plan properties, in collaboration with Dubai Holding Real Estate.</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1111,14 +1105,14 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE4" s="2" t="n">
-        <v>46129.82986111111</v>
+        <v>46131.83125</v>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>46129</v>
+        <v>46131</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
@@ -1132,7 +1126,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>The text consists of emojis and does not contain any language to translate.</t>
+          <t>In a move that reflects the evolution of financial products in the real estate market in the UAE, Emirates NBD Bank anno…</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1155,45 +1149,47 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2045169009662763334</t>
+          <t>2045894611756048610</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/MC81236843/status/2045169009662763334</t>
+          <t>https://x.com/almidfa75/status/2045894611756048610</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/MC81236843</t>
+          <t>https://x.com/almidfa75</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MC81236843</t>
+          <t>almidfa75</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>M C</t>
+          <t>Faisal Al Midfa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1163517530822119426/IK5LwgTg_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/692030305365000192/rYQ6PWnr_bigger.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank PJSC und Berbank of Russia beziehen sich auf die Ankündigung vom 30. Juni 2019 bezüglich der Genehmigung durch die Bankenaufsichtsbehörden in den Vereinigten Arabischen Emiraten, der Türkei, Österreich und Russland
-emiratesnbd.com/en/media-cen…</t>
+          <t>🧵 1/
+في خطوة تعكس تطور المنتجات المالية في السوق العقاري بدولة الإمارات، أعلن بنك Emirates NBD عن إطلاق نموذج تمويل مبكر للعقارات قيد الإنشاء (Off-plan)، بالتعاون مع Dubai Holding Real Estate.
+#دبي #القطاع_العقاري #التمويل</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank PJSC und Berbank of Russia beziehen sich auf die Ankündigung vom 30. Juni 2019 bezüglich der Genehmigung durch die Bankenaufsichtsbehörden in den Vereinigten Arabischen Emiraten, der Türkei, Österreich und Russland
-&lt;a href="https://www.emiratesnbd.com/en/media-center/completion-of-the-sale-and-purchase-of-9985-of-the-shares-in-denizbank-as-by-emirates-nbd-from-sberb"&gt;emiratesnbd.com/en/media-cen…&lt;/a&gt;</t>
+          <t>🧵 1/
+في خطوة تعكس تطور المنتجات المالية في السوق العقاري بدولة الإمارات، أعلن بنك Emirates NBD عن إطلاق نموذج تمويل مبكر للعقارات قيد الإنشاء (Off-plan)، بالتعاون مع Dubai Holding Real Estate.
+&lt;a href="/search?f=tweets&amp;amp;q=%23دبي"&gt;#دبي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23القطاع_العقاري"&gt;#القطاع_العقاري&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التمويل"&gt;#التمويل&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K5" t="b">
@@ -1208,29 +1204,29 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 3:54 PM UTC</t>
+          <t>Apr 19, 2026 · 3:57 PM UTC</t>
         </is>
       </c>
       <c r="P5" s="2" t="n">
-        <v>46129.6625</v>
+        <v>46131.66458333333</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>['https://www.emiratesnbd.com/en/media-center/completion-of-the-sale-and-purchase-of-9985-of-the-shares-in-denizbank-as-by-emirates-nbd-from-sberb']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23دبي', 'https://x.com/search?f=tweets&amp;q=%23القطاع_العقاري', 'https://x.com/search?f=tweets&amp;q=%23التمويل']</t>
         </is>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
         <v>1</v>
       </c>
-      <c r="U5" t="n">
-        <v>3</v>
-      </c>
       <c r="V5" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1239,21 +1235,23 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank PJSC und Berbank of Russia beziehen sich auf die Ankündigung vom 30. Juni 2019 bezüglich der Genehmigung durch die Bankenaufsichtsbehörden in den Vereinigten Arabischen Emiraten, der Türkei, Österreich und Russland
-emiratesnbd.com/en/media-cen…</t>
+          <t>🧵 1/
+في خطوة تعكس تطور المنتجات المالية في السوق العقاري بدولة الإمارات، أعلن بنك Emirates NBD عن إطلاق نموذج تمويل مبكر للعقارات قيد الإنشاء (Off-plan)، بالتعاون مع Dubai Holding Real Estate.
+#دبي #القطاع_العقاري #التمويل</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank PJSC und Berbank of Russia beziehen sich auf die Ankündigung vom 30. Juni 2019 bezüglich der Genehmigung durch die Bankenaufsichtsbehörden in den Vereinigten Arabischen Emiraten, der Türkei, Österreich und Russland
-emiratesnbd.com/en/media-cen…</t>
+          <t>🧵 1/
+في خطوة تعكس تطور المنتجات المالية في السوق العقاري بدولة الإمارات، أعلن بنك Emirates NBD عن إطلاق نموذج تمويل مبكر للعقارات قيد الإنشاء (Off-plan)، بالتعاون مع Dubai Holding Real Estate.
+#دبي #القطاع_العقاري #التمويل</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank PJSC and Sberbank of Russia refer to the announcement from June 30, 2019, regarding the approval by the banking regulatory authorities in the United Arab Emirates, Turkey, Austria, and Russia.</t>
+          <t>In a move that reflects the evolution of financial products in the real estate market in the UAE, Emirates NBD Bank announced the launch of an early financing model for off-plan properties, in collaboration with Dubai Holding Real Estate.</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1263,14 +1261,14 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE5" s="2" t="n">
-        <v>46129.82916666667</v>
+        <v>46131.83125</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>46129</v>
+        <v>46131</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
@@ -1284,7 +1282,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank PJSC and Sberbank of Russia refer to the announcement from June 30, 2019, regarding the approval by th…</t>
+          <t>In a move that reflects the evolution of financial products in the real estate market in the UAE, Emirates NBD Bank anno…</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1307,50 +1305,54 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2045166464181702828</t>
+          <t>2045881062304456946</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/MBS_20121/status/2045166464181702828</t>
+          <t>https://x.com/ThisMadEngineer/status/2045881062304456946</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/MBS_20121</t>
+          <t>https://x.com/ThisMadEngineer</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MBS_20121</t>
+          <t>ThisMadEngineer</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>A h m a d A l h ar b i</t>
+          <t>Ankesh / MadEngineer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1357665933368696832/CgwgbAyQ_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/677437091211530240/U61xnBOL_bigger.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA متى يتم دعم إضافة بطاقة مزيد الي قوقل باي Google pay</t>
+          <t>We are extending our support to help you manage your finances with more confidence. https://t.co/EP2xuqo7Gb</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_KSA" title="Emirates NBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; متى يتم دعم إضافة بطاقة مزيد الي قوقل باي Google pay</t>
+          <t>Thanks!</t>
         </is>
       </c>
       <c r="K6" t="b">
         <v>0</v>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>12h</t>
@@ -1358,20 +1360,16 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 3:44 PM UTC</t>
+          <t>Apr 19, 2026 · 3:03 PM UTC</t>
         </is>
       </c>
       <c r="P6" s="2" t="n">
-        <v>46129.65555555555</v>
+        <v>46131.62708333333</v>
       </c>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_KSA']</t>
-        </is>
-      </c>
+      <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1380,7 +1378,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>36</v>
+        <v>287</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1389,27 +1387,27 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA متى يتم دعم إضافة بطاقة مزيد الي قوقل باي Google pay</t>
+          <t>Thanks!</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>https://x.com/MBS_20121/status/2045166464181702828</t>
+          <t>https://x.com/ThisMadEngineer/status/2045881062304456946</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA متى يتم دعم إضافة بطاقة مزيد الي قوقل باي Google pay</t>
+          <t>We are extending our support to help you manage your finances with more confidence. https://t.co/EP2xuqo7Gb</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA متى يتم دعم إضافة بطاقة مزيد الي قوقل باي Google pay</t>
+          <t>We are extending our support to help you manage your finances with more confidence. https://t.co/EP2xuqo7Gb</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>When will support for adding Mazid card to Google Pay be available?</t>
+          <t>We are extending our support to help you manage your finances with more confidence.</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1423,10 +1421,10 @@
         </is>
       </c>
       <c r="AE6" s="2" t="n">
-        <v>46129.82222222222</v>
+        <v>46131.79375</v>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>46129</v>
+        <v>46131</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
@@ -1440,7 +1438,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>When will support for adding Mazid card to Google Pay be available?</t>
+          <t>We are extending our support to help you manage your finances with more confidence.</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1453,7 +1451,7 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
@@ -1463,49 +1461,43 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2045155322356961286</t>
+          <t>2045850840196694451</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_EGY/status/2045155322356961286</t>
+          <t>https://x.com/r35sk/status/2045850840196694451</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_EGY</t>
+          <t>https://x.com/r35sk</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>EmiratesNBD_EGY</t>
+          <t>r35sk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>ريم</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427526482108416/qjFPlJ1n_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1976063720942968832/0TB4sf0G_bigger.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Your phone, Your smarter way to pay.
-Activate Apple Pay with your Emirates NBD cards in your Apple devices and enjoy fast, secure payments every day.
-Terms &amp;amp; Conditions Apply.
-Tax registration number: 204-897-319 https://t.co/uyaLjydHaw</t>
+          <t>الوداعيةةة https://t.co/p08tSNxQZ3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Your phone, Your smarter way to pay.
-Activate Apple Pay with your Emirates NBD cards in your Apple devices and enjoy fast, secure payments every day.
-Terms &amp;amp; Conditions Apply.
-Tax registration number: 204-897-319</t>
+          <t>الحمدلله الحمرا فيها صرافة enbd</t>
         </is>
       </c>
       <c r="K7" t="b">
@@ -1515,16 +1507,16 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 3:00 PM UTC</t>
+          <t>Apr 19, 2026 · 1:03 PM UTC</t>
         </is>
       </c>
       <c r="P7" s="2" t="n">
-        <v>46129.625</v>
+        <v>46131.54375</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
@@ -1538,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1547,53 +1539,44 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Your phone, Your smarter way to pay.
-Activate Apple Pay with your Emirates NBD cards in your Apple devices and enjoy fast, secure payments every day.
-Terms &amp; Conditions Apply.
-Tax registration number: 204-897-319</t>
+          <t>الحمدلله الحمرا فيها صرافة enbd</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_EGY/status/2045155322356961286</t>
+          <t>https://x.com/r35sk/status/2045850840196694451</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>Your phone, Your smarter way to pay.
-Activate Apple Pay with your Emirates NBD cards in your Apple devices and enjoy fast, secure payments every day.
-Terms &amp;amp; Conditions Apply.
-Tax registration number: 204-897-319 https://t.co/uyaLjydHaw</t>
+          <t>الوداعيةةة https://t.co/p08tSNxQZ3</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Your phone, Your smarter way to pay.
-Activate Apple Pay with your Emirates NBD cards in your Apple devices and enjoy fast, secure payments every day.
-Terms &amp;amp; Conditions Apply.
-Tax registration number: 204-897-319 https://t.co/uyaLjydHaw</t>
+          <t>الوداعيةةة https://t.co/p08tSNxQZ3</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Your phone, your smarter way to pay. Activate Apple Pay with your Emirates NBD cards on your Apple devices and enjoy fast, secure payments every day. Terms &amp; Conditions Apply. Tax registration number: 204-897-319</t>
+          <t>Farewell</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Cust</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE7" s="2" t="n">
-        <v>46129.79166666666</v>
+        <v>46131.71041666667</v>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>46129</v>
+        <v>46131</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
@@ -1607,7 +1590,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Tax registration number: 204-897-319 • Activate Apple Pay with your Emirates NBD cards on your Apple devices and enjoy fast, secure payments every day. • Your phone, your smarter way to pay.</t>
+          <t>Farewell</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1630,49 +1613,43 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2045138554464915956</t>
+          <t>2045850184811422052</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/yallaweb/status/2045138554464915956</t>
+          <t>https://x.com/AhmedAlhaq79518/status/2045850184811422052</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://x.com/yallaweb</t>
+          <t>https://x.com/AhmedAlhaq79518</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>yallaweb</t>
+          <t>AhmedAlhaq79518</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>M.G.</t>
+          <t>Ahmed Alhaìqi</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1840606846068875264/V7l0ThZZ_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2015365820088803328/seUb2ZG5_bigger.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>اطلعت اليوم على سير العمل في أول محطة للإقلاع والهبوط العمودي للتاكسي الجوي في دبي، الأولى من نوعها على مستوى العالم، والتي تم تنفيذها بالقرب من مطار دبي الدولي… المحطة جاهزة، وهي ضمن شبكة تشمل محطات في داون تاون ونخلة جميرا ومرسى دبي ستكون جاهزة مع نهاية العام الجاري. 
-ستخدم المحطة الأولى نحو 170 ألف راكب سنوياً، ووجهنا بتشغيل الخدمة وإطلاقها للجمهور خلال العام الجاري وفقاً لأرقى المعايير الدولية. 
-هذا المشروع خطوة مفصلية في مسيرة دبي نحو ريادة مستقبل التنقل الحضري عالمياً، واختصار الزمن وتقريب المسافات، ونشكر فريق هيئة الطرق والمواصلات والشركاء المحليين والعالميين على جهودهم في إنجاز هذا المشروع النوعي الذي يأتي تزامناً مع النسخة الأولى من اليوم العالمي للمواصلات العامة في 17 أبريل سنوياً.
-في دبي نحول الأفكار والطموحات إلى واقع ملموس… فدبي تجيد التحليق.</t>
+          <t>@EmiratesNBD_AE فعلا بنك مميز بمعني الكلمه والصقه بهم متوفره عندي علاجه.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>ابرؤا ذمتكم واعيدوا لنا ما سرقتموه من أموالنا لترضوا اسيادكم من حفدة القردة و الخنازير.
-&lt;a href="/search?f=tweets&amp;amp;q=%23الامارات"&gt;#الامارات&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23دبي"&gt;#دبي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23ابوظبي"&gt;#ابوظبي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Dubai"&gt;#Dubai&lt;/a&gt;    
-&lt;a href="/search?f=tweets&amp;amp;q=%23AbuDhabi"&gt;#AbuDhabi&lt;/a&gt; &lt;a href="/HHShkMohd" title="HH Sheikh Mohammed"&gt;@HHShkMohd&lt;/a&gt; 
-&lt;a href="/MohamedBinZayed" title="محمد بن زايد"&gt;@MohamedBinZayed&lt;/a&gt; &lt;a href="/emirates" title="Emirates"&gt;@emirates&lt;/a&gt; &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; &lt;a href="/WPP" title="WPP"&gt;@WPP&lt;/a&gt;</t>
+          <t>فعلا بنك مميز بمعني الكلمه والصقه بهم متوفره عندي علاجه.</t>
         </is>
       </c>
       <c r="K8" t="b">
@@ -1681,28 +1658,24 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>['HamdanMohammed']</t>
+          <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 1:53 PM UTC</t>
+          <t>Apr 19, 2026 · 1:01 PM UTC</t>
         </is>
       </c>
       <c r="P8" s="2" t="n">
-        <v>46129.57847222222</v>
+        <v>46131.54236111111</v>
       </c>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23الامارات', 'https://x.com/search?f=tweets&amp;q=%23دبي', 'https://x.com/search?f=tweets&amp;q=%23ابوظبي', 'https://x.com/search?f=tweets&amp;q=%23UAE', 'https://x.com/search?f=tweets&amp;q=%23Dubai', 'https://x.com/search?f=tweets&amp;q=%23AbuDhabi', 'https://x.com/HHShkMohd', 'https://x.com/MohamedBinZayed', 'https://x.com/emirates', 'https://x.com/EmiratesNBD_AE', 'https://x.com/WPP']</t>
-        </is>
-      </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
         <v>0</v>
       </c>
@@ -1710,10 +1683,10 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1722,39 +1695,27 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>ابرؤا ذمتكم واعيدوا لنا ما سرقتموه من أموالنا لترضوا اسيادكم من حفدة القردة و الخنازير.
-#الامارات #دبي #ابوظبي #UAE #Dubai    
-#AbuDhabi @HHShkMohd 
-@MohamedBinZayed @emirates @EmiratesNBD_AE @WPP</t>
+          <t>فعلا بنك مميز بمعني الكلمه والصقه بهم متوفره عندي علاجه.</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>https://x.com/yallaweb/status/2045138554464915956</t>
+          <t>https://x.com/AhmedAlhaq79518/status/2045850184811422052</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>اطلعت اليوم على سير العمل في أول محطة للإقلاع والهبوط العمودي للتاكسي الجوي في دبي، الأولى من نوعها على مستوى العالم، والتي تم تنفيذها بالقرب من مطار دبي الدولي… المحطة جاهزة، وهي ضمن شبكة تشمل محطات في داون تاون ونخلة جميرا ومرسى دبي ستكون جاهزة مع نهاية العام الجاري. 
-ستخدم المحطة الأولى نحو 170 ألف راكب سنوياً، ووجهنا بتشغيل الخدمة وإطلاقها للجمهور خلال العام الجاري وفقاً لأرقى المعايير الدولية. 
-هذا المشروع خطوة مفصلية في مسيرة دبي نحو ريادة مستقبل التنقل الحضري عالمياً، واختصار الزمن وتقريب المسافات، ونشكر فريق هيئة الطرق والمواصلات والشركاء المحليين والعالميين على جهودهم في إنجاز هذا المشروع النوعي الذي يأتي تزامناً مع النسخة الأولى من اليوم العالمي للمواصلات العامة في 17 أبريل سنوياً.
-في دبي نحول الأفكار والطموحات إلى واقع ملموس… فدبي تجيد التحليق.</t>
+          <t>@EmiratesNBD_AE فعلا بنك مميز بمعني الكلمه والصقه بهم متوفره عندي علاجه.</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>اطلعت اليوم على سير العمل في أول محطة للإقلاع والهبوط العمودي للتاكسي الجوي في دبي، الأولى من نوعها على مستوى العالم، والتي تم تنفيذها بالقرب من مطار دبي الدولي… المحطة جاهزة، وهي ضمن شبكة تشمل محطات في داون تاون ونخلة جميرا ومرسى دبي ستكون جاهزة مع نهاية العام الجاري. 
-ستخدم المحطة الأولى نحو 170 ألف راكب سنوياً، ووجهنا بتشغيل الخدمة وإطلاقها للجمهور خلال العام الجاري وفقاً لأرقى المعايير الدولية. 
-هذا المشروع خطوة مفصلية في مسيرة دبي نحو ريادة مستقبل التنقل الحضري عالمياً، واختصار الزمن وتقريب المسافات، ونشكر فريق هيئة الطرق والمواصلات والشركاء المحليين والعالميين على جهودهم في إنجاز هذا المشروع النوعي الذي يأتي تزامناً مع النسخة الأولى من اليوم العالمي للمواصلات العامة في 17 أبريل سنوياً.
-في دبي نحول الأفكار والطموحات إلى واقع ملموس… فدبي تجيد التحليق.</t>
+          <t>@EmiratesNBD_AE فعلا بنك مميز بمعني الكلمه والصقه بهم متوفره عندي علاجه.</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Today, I reviewed the progress of the first vertical takeoff and landing taxi station in Dubai, the first of its kind in the world, which has been implemented near Dubai International Airport. The station is ready and is part of a network that includes stations in Downtown, Palm Jumeirah, and Dubai Marina, which will be ready by the end of this year.
-The first station will serve about 170,000 passengers annually, and we have directed the operation and launch of the service to the public this year according to the highest international standards.
-This project is a pivotal step in Dubai's journey towards leading the future of urban mobility globally, shortening travel time and bridging distances. We thank the team from the Roads and Transport Authority and our local and global partners for their efforts in completing this innovative project, which coincides with the first edition of World Public Transport Day on April 17 each year.
-In Dubai, we turn ideas and ambitions into tangible reality... for Dubai knows how to soar.</t>
+          <t>Emirates NBD is truly a distinguished bank in every sense of the word, and I have their sticker available for my treatment.</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1764,14 +1725,14 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE8" s="2" t="n">
-        <v>46129.74513888889</v>
+        <v>46131.70902777778</v>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>46129</v>
+        <v>46131</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
@@ -1785,7 +1746,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Today, I reviewed the progress of the first vertical takeoff and landing taxi station in Dubai, the first of its kind in the world, which has been implemented near Dubai International Airport. • The first station will serve about 170,000 passengers annually, and we have directed the operation and launch of the service to the public this year according to the highest international standards. • The station is ready and is part of a network that includes stations in Downtown, Palm Jumeirah, and Dubai Marina, which will be ready by the end of this year.</t>
+          <t>Emirates NBD is truly a distinguished bank in every sense of the word, and I have their sticker available for my treatment.</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1798,7 +1759,7 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>HamdanMohammed</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
@@ -1808,43 +1769,47 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2045130309323071836</t>
+          <t>2045821589539733783</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://x.com/dar_global/status/2045130309323071836</t>
+          <t>https://x.com/CWSaudi/status/2045821589539733783</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://x.com/dar_global</t>
+          <t>https://x.com/CWSaudi</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>dar_global</t>
+          <t>CWSaudi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>DarGlobal</t>
+          <t>Construction Week Saudi</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1904290533372985344/OQZ0hS5Q_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1494269682098089989/5bK0V1be_bigger.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>LSE-listed Dar Global secures $250mln term loan https://t.co/6wbMOXS2Dg</t>
+          <t>#SaudiArabia extends the Landbridge rail bid deadline to April 29 as #Hormuz disruptions highlight its lack of a direct east–west freight rail link.
+Read more ll
+https://t.co/UvrhC24nWJ</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Emirates NBD successfully executes USD 250 Million Syndicated Term Loan facility for Dar Global, Accelerating Global Growth and Expansion &lt;a href="https://bebeez.eu/2026/04/16/emirates-nbd-successfully-executes-usd-250-million-syndicated-term-loan-facility-for-dar-global-accelerating-global-growth-and-expansion/"&gt;bebeez.eu/2026/04/16/emirate…&lt;/a&gt;</t>
+          <t>. &lt;a href="/dar_global" title="DarGlobal"&gt;@dar_global&lt;/a&gt;  has secured a $250M loan arranged by &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; , as the &lt;a href="/search?f=tweets&amp;amp;q=%23London"&gt;#London&lt;/a&gt; -listed developer behind &lt;a href="/realDonaldTrump" title="Donald J. Trump"&gt;@realDonaldTrump&lt;/a&gt; -branded projects expands its pipeline.
+Read more:
+&lt;a href="https://www.constructionweeksaudi.com/business/real-estate-darglobal-trump"&gt;constructionweeksaudi.com/bu…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K9" t="b">
@@ -1854,21 +1819,21 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 1:20 PM UTC</t>
+          <t>Apr 19, 2026 · 11:07 AM UTC</t>
         </is>
       </c>
       <c r="P9" s="2" t="n">
-        <v>46129.55555555555</v>
+        <v>46131.46319444444</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>['https://bebeez.eu/2026/04/16/emirates-nbd-successfully-executes-usd-250-million-syndicated-term-loan-facility-for-dar-global-accelerating-global-growth-and-expansion/']</t>
+          <t>['https://x.com/dar_global', 'https://x.com/EmiratesNBD_AE', 'https://x.com/search?f=tweets&amp;q=%23London', 'https://x.com/realDonaldTrump', 'https://www.constructionweeksaudi.com/business/real-estate-darglobal-trump']</t>
         </is>
       </c>
       <c r="S9" t="n">
@@ -1881,7 +1846,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1890,27 +1855,33 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Emirates NBD successfully executes USD 250 Million Syndicated Term Loan facility for Dar Global, Accelerating Global Growth and Expansion bebeez.eu/2026/04/16/emirate…</t>
+          <t>. @dar_global  has secured a $250M loan arranged by @EmiratesNBD_AE , as the #London -listed developer behind @realDonaldTrump -branded projects expands its pipeline.
+Read more:
+constructionweeksaudi.com/bu…</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>https://x.com/dar_global/status/2045130309323071836</t>
+          <t>https://x.com/CWSaudi/status/2045821589539733783</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>LSE-listed Dar Global secures $250mln term loan https://t.co/6wbMOXS2Dg</t>
+          <t>#SaudiArabia extends the Landbridge rail bid deadline to April 29 as #Hormuz disruptions highlight its lack of a direct east–west freight rail link.
+Read more ll
+https://t.co/UvrhC24nWJ</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>LSE-listed Dar Global secures $250mln term loan https://t.co/6wbMOXS2Dg</t>
+          <t>#SaudiArabia extends the Landbridge rail bid deadline to April 29 as #Hormuz disruptions highlight its lack of a direct east–west freight rail link.
+Read more ll
+https://t.co/UvrhC24nWJ</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>LSE-listed Dar Global secures $250 million term loan</t>
+          <t>Saudi Arabia extends the Landbridge rail bid deadline to April 29 as Hormuz disruptions highlight its lack of a direct east–west freight rail link.</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1924,10 +1895,10 @@
         </is>
       </c>
       <c r="AE9" s="2" t="n">
-        <v>46129.72222222222</v>
+        <v>46131.62986111111</v>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>46129</v>
+        <v>46131</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
@@ -1941,7 +1912,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>LSE-listed Dar Global secures $250 million term loan</t>
+          <t>Saudi Arabia extends the Landbridge rail bid deadline to April 29 as Hormuz disruptions highlight its lack of a direct east–west freight rail link.</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1964,50 +1935,45 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2045118948694470845</t>
+          <t>2045805999718903933</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://x.com/GeorgeDon5181/status/2045118948694470845</t>
+          <t>https://x.com/abasetaljanahi/status/2045805999718903933</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://x.com/GeorgeDon5181</t>
+          <t>https://x.com/abasetaljanahi</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>GeorgeDon5181</t>
+          <t>abasetaljanahi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Don George</t>
+          <t>Abdulbaset Al Janahi</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1997686160211243008/2Cf-bh5c_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1572294225240231936/Ew_orY09_bigger.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Fake Android updates are rising. They can trick you into installing unsafe apps or sharing details. 
-Turn on Smart Touch and Face Pass for secure login.
-تشهد التحديثات الوهمية على أجهزة أندرويد تزايداً ملحوظاً، وقد تُستخدم لخداعك لتثبيت تطبيقات غير آمنة أو مشاركة البيانات.
-احمِ حسابك من خلال تفعيل ميزة اللمس الذكي والتعرّف على الوجه
-لتسجيل دخول أكثر أماناً.</t>
+          <t>@EmiratesNBD_AE بس! 
+وايد عليكم</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>good (Iin in it+i8 
-I8. 8iii cf CT  FB
- FC m
- , (? +II in IIWII îîctffze</t>
+          <t>بس! 
+وايد عليكم</t>
         </is>
       </c>
       <c r="K10" t="b">
@@ -2021,21 +1987,21 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 12:35 PM UTC</t>
+          <t>Apr 19, 2026 · 10:05 AM UTC</t>
         </is>
       </c>
       <c r="P10" s="2" t="n">
-        <v>46129.52430555555</v>
+        <v>46131.42013888889</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -2044,7 +2010,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>4</v>
+        <v>211</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -2053,39 +2019,30 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>good (Iin in it+i8 
-I8. 8iii cf CT  FB
- FC m
- , (? +II in IIWII îîctffze</t>
+          <t>بس! 
+وايد عليكم</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>https://x.com/GeorgeDon5181/status/2045118948694470845</t>
+          <t>https://x.com/abasetaljanahi/status/2045805999718903933</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>Fake Android updates are rising. They can trick you into installing unsafe apps or sharing details. 
-Turn on Smart Touch and Face Pass for secure login.
-تشهد التحديثات الوهمية على أجهزة أندرويد تزايداً ملحوظاً، وقد تُستخدم لخداعك لتثبيت تطبيقات غير آمنة أو مشاركة البيانات.
-احمِ حسابك من خلال تفعيل ميزة اللمس الذكي والتعرّف على الوجه
-لتسجيل دخول أكثر أماناً.</t>
+          <t>@EmiratesNBD_AE بس! 
+وايد عليكم</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Fake Android updates are rising. They can trick you into installing unsafe apps or sharing details. 
-Turn on Smart Touch and Face Pass for secure login.
-تشهد التحديثات الوهمية على أجهزة أندرويد تزايداً ملحوظاً، وقد تُستخدم لخداعك لتثبيت تطبيقات غير آمنة أو مشاركة البيانات.
-احمِ حسابك من خلال تفعيل ميزة اللمس الذكي والتعرّف على الوجه
-لتسجيل دخول أكثر أماناً.</t>
+          <t>@EmiratesNBD_AE بس! 
+وايد عليكم</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Fake Android updates are on the rise. They can trick you into installing unsafe apps or sharing your details. 
-Protect your account by enabling Smart Touch and Face Recognition for a more secure login.</t>
+          <t>That's enough! You're overdoing it.</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -2099,10 +2056,10 @@
         </is>
       </c>
       <c r="AE10" s="2" t="n">
-        <v>46129.69097222222</v>
+        <v>46131.58680555555</v>
       </c>
       <c r="AF10" s="2" t="n">
-        <v>46129</v>
+        <v>46131</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
@@ -2116,7 +2073,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Protect your account by enabling Smart Touch and Face Recognition for a more secure login. • They can trick you into installing unsafe apps or sharing your details. • Fake Android updates are on the rise.</t>
+          <t>That's enough! You're overdoing it.</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -2139,92 +2096,80 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2045086967533031764</t>
+          <t>2045786366504796559</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2045086967533031764</t>
+          <t>https://x.com/SultanAbdu70381/status/2045786366504796559</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/SultanAbdu70381</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>SultanAbdu70381</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>Sultan Abdullah</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2042294543308242946/ScvMjarh_bigger.jpg</t>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Emirates NBD has successfully executed a USD 250 million syndicated term loan facility for @dar_global , strengthening its financial flexibility to support ongoing international development activity.
-This transaction reflects our continued role in structuring and delivering cross-border financing solutions for leading real estate developers, supported  by strong distribution capabilities and established lender relationships.
-We remain focused on helping clients scale with clarity, speed and disciplined access to capital across key markets.
-Read more here:
-https://t.co/91twU74VX9
-https://t.co/hfV7wLDhaI
-#EmiratesNBD #SyndicatedLoan #CapitalMarkets #Banking #Dubai</t>
+          <t>نحتاج تأجيل 3 شهور للازمه</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Emirates NBD has successfully executed a USD 250 million syndicated term loan facility for &lt;a href="/dar_global" title="DarGlobal"&gt;@dar_global&lt;/a&gt; , strengthening its financial flexibility to support ongoing international development activity.
-This transaction reflects our continued role in structuring and delivering cross-border financing solutions for leading real estate developers, supported  by strong distribution capabilities and established lender relationships.
-We remain focused on helping clients scale with clarity, speed and disciplined access to capital across key markets.
-Read more here:
-&lt;a href="https://www.emiratesnbd.com/en/media-center/emirates-nbd-successfully-executes-usd-250-million-syndicated-term-loan-facility-for-dar-global"&gt;emiratesnbd.com/en/media-cen…&lt;/a&gt;
-&lt;a href="https://www.emiratesnbd.com/ar/media-center/emirates-nbd-successfully-executes-usd-250-million-syndicated-term-loan-facility-for-dar-global"&gt;emiratesnbd.com/ar/media-cen…&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SyndicatedLoan"&gt;#SyndicatedLoan&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23CapitalMarkets"&gt;#CapitalMarkets&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Banking"&gt;#Banking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Dubai"&gt;#Dubai&lt;/a&gt;</t>
+          <t>اكثر البنوك فالدولة تساهلت مع متعامليها لتوفير راحتهم واحتياجاتهم وليس لزياده ضغط عليهم حيث قامو بتأجيل قروض لهم ٣ اشهر مساعده لهم لضروفهم خاصه دفاع الأول وشكرا لكم</t>
         </is>
       </c>
       <c r="K11" t="b">
         <v>0</v>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 10:28 AM UTC</t>
+          <t>Apr 19, 2026 · 8:47 AM UTC</t>
         </is>
       </c>
       <c r="P11" s="2" t="n">
-        <v>46129.43611111111</v>
+        <v>46131.36597222222</v>
       </c>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>['https://x.com/dar_global', 'https://www.emiratesnbd.com/en/media-center/emirates-nbd-successfully-executes-usd-250-million-syndicated-term-loan-facility-for-dar-global', 'https://www.emiratesnbd.com/ar/media-center/emirates-nbd-successfully-executes-usd-250-million-syndicated-term-loan-facility-for-dar-global', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23SyndicatedLoan', 'https://x.com/search?f=tweets&amp;q=%23CapitalMarkets', 'https://x.com/search?f=tweets&amp;q=%23Banking', 'https://x.com/search?f=tweets&amp;q=%23Dubai']</t>
-        </is>
-      </c>
+      <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>530</v>
+        <v>6</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -2233,62 +2178,44 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Emirates NBD has successfully executed a USD 250 million syndicated term loan facility for @dar_global , strengthening its financial flexibility to support ongoing international development activity.
-This transaction reflects our continued role in structuring and delivering cross-border financing solutions for leading real estate developers, supported  by strong distribution capabilities and established lender relationships.
-We remain focused on helping clients scale with clarity, speed and disciplined access to capital across key markets.
-Read more here:
-emiratesnbd.com/en/media-cen…
-emiratesnbd.com/ar/media-cen…
-#EmiratesNBD #SyndicatedLoan #CapitalMarkets #Banking #Dubai</t>
+          <t>اكثر البنوك فالدولة تساهلت مع متعامليها لتوفير راحتهم واحتياجاتهم وليس لزياده ضغط عليهم حيث قامو بتأجيل قروض لهم ٣ اشهر مساعده لهم لضروفهم خاصه دفاع الأول وشكرا لكم</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2045086967533031764</t>
+          <t>https://x.com/SultanAbdu70381/status/2045786366504796559</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>Emirates NBD has successfully executed a USD 250 million syndicated term loan facility for @dar_global , strengthening its financial flexibility to support ongoing international development activity.
-This transaction reflects our continued role in structuring and delivering cross-border financing solutions for leading real estate developers, supported  by strong distribution capabilities and established lender relationships.
-We remain focused on helping clients scale with clarity, speed and disciplined access to capital across key markets.
-Read more here:
-https://t.co/91twU74VX9
-https://t.co/hfV7wLDhaI
-#EmiratesNBD #SyndicatedLoan #CapitalMarkets #Banking #Dubai</t>
+          <t>نحتاج تأجيل 3 شهور للازمه</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Emirates NBD has successfully executed a USD 250 million syndicated term loan facility for @dar_global , strengthening its financial flexibility to support ongoing international development activity.
-This transaction reflects our continued role in structuring and delivering cross-border financing solutions for leading real estate developers, supported  by strong distribution capabilities and established lender relationships.
-We remain focused on helping clients scale with clarity, speed and disciplined access to capital across key markets.
-Read more here:
-https://t.co/91twU74VX9
-https://t.co/hfV7wLDhaI
-#EmiratesNBD #SyndicatedLoan #CapitalMarkets #Banking #Dubai</t>
+          <t>نحتاج تأجيل 3 شهور للازمه</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Emirates NBD has successfully executed a USD 250 million syndicated term loan facility for @dar_global, strengthening its financial flexibility to support ongoing international development activity. This transaction reflects our continued role in structuring and delivering cross-border financing solutions for leading real estate developers, supported by strong distribution capabilities and established lender relationships. We remain focused on helping clients scale with clarity, speed, and disciplined access to capital across key markets.</t>
+          <t>We need a 3-month postponement for the necessity.</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Cust</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE11" s="2" t="n">
-        <v>46129.60277777778</v>
+        <v>46131.53263888889</v>
       </c>
       <c r="AF11" s="2" t="n">
-        <v>46129</v>
+        <v>46131</v>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
@@ -2302,7 +2229,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Emirates NBD has successfully executed a USD 250 million syndicated term loan facility for @dar_global, strengthening its financial flexibility to support ongoing international development activity. • We remain focused on helping clients scale with clarity, speed, and disciplined access to capital across key markets.</t>
+          <t>We need a 3-month postponement for the necessity.</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -2315,7 +2242,7 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
@@ -2325,74 +2252,69 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2045079926013837337</t>
+          <t>2045785730023301620</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2045079926013837337</t>
+          <t>https://x.com/SultanAbdu70381/status/2045785730023301620</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals</t>
+          <t>https://x.com/SultanAbdu70381</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ENBDdeals</t>
+          <t>SultanAbdu70381</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Emirates NBD Deals</t>
+          <t>Sultan Abdullah</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1763624422294814720/EmRI1Aqu_bigger.jpg</t>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>دلّل نفسك مع جراند فلورا سبا 💅
-احصل على خصم 15% على فاتورتك بقيمة 150 درهم أو أكثر، حصريًا عبر تطبيق تستاهل.
-لمعرفة المزيد:
-https://t.co/NILbsZvhfk https://t.co/Elvcoo2HNL</t>
+          <t>@EmiratesNBD_AE عند الإعلان يجب وضع التوضيح وليس وضع إعلان بموضوع واتخاذ إجراءات وأوامر أخرى شكرا لكم</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Turn your bills into rewards
-Get AED 500 worth of Majid Al Futtaim voucher when you apply for an Emirates NBD SHARE Visa Credit Card.
-Apply Now: &lt;a href="https://apply.emiratesnbd.com/en/credit-card/maf"&gt;apply.emiratesnbd.com/en/cre…&lt;/a&gt;</t>
+          <t>عند الإعلان يجب وضع التوضيح وليس وضع إعلان بموضوع واتخاذ إجراءات وأوامر أخرى شكرا لكم</t>
         </is>
       </c>
       <c r="K12" t="b">
         <v>0</v>
       </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 10:00 AM UTC</t>
+          <t>Apr 19, 2026 · 8:45 AM UTC</t>
         </is>
       </c>
       <c r="P12" s="2" t="n">
-        <v>46129.41666666666</v>
+        <v>46131.36458333334</v>
       </c>
       <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>['https://apply.emiratesnbd.com/en/credit-card/maf']</t>
-        </is>
-      </c>
+      <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
         <v>0</v>
       </c>
@@ -2400,10 +2322,10 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>108</v>
+        <v>11</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -2412,40 +2334,32 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Turn your bills into rewards
-Get AED 500 worth of Majid Al Futtaim voucher when you apply for an Emirates NBD SHARE Visa Credit Card.
-Apply Now: apply.emiratesnbd.com/en/cre…</t>
+          <t>عند الإعلان يجب وضع التوضيح وليس وضع إعلان بموضوع واتخاذ إجراءات وأوامر أخرى شكرا لكم</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2045079926013837337</t>
+          <t>https://x.com/SultanAbdu70381/status/2045785730023301620</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>دلّل نفسك مع جراند فلورا سبا 💅
-احصل على خصم 15% على فاتورتك بقيمة 150 درهم أو أكثر، حصريًا عبر تطبيق تستاهل.
-لمعرفة المزيد:
-https://t.co/NILbsZvhfk https://t.co/Elvcoo2HNL</t>
+          <t>@EmiratesNBD_AE عند الإعلان يجب وضع التوضيح وليس وضع إعلان بموضوع واتخاذ إجراءات وأوامر أخرى شكرا لكم</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>دلّل نفسك مع جراند فلورا سبا 💅
-احصل على خصم 15% على فاتورتك بقيمة 150 درهم أو أكثر، حصريًا عبر تطبيق تستاهل.
-لمعرفة المزيد:
-https://t.co/NILbsZvhfk https://t.co/Elvcoo2HNL</t>
+          <t>@EmiratesNBD_AE عند الإعلان يجب وضع التوضيح وليس وضع إعلان بموضوع واتخاذ إجراءات وأوامر أخرى شكرا لكم</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Pamper yourself at Grand Flora Spa 💅 Get a 15% discount on your bill of 150 dirhams or more, exclusively through the Testahal app. To learn more:</t>
+          <t>When announcing, clarification should be provided instead of just making an announcement on the subject and taking other actions and orders. Thank you.</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Cust</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -2454,10 +2368,10 @@
         </is>
       </c>
       <c r="AE12" s="2" t="n">
-        <v>46129.58333333334</v>
+        <v>46131.53125</v>
       </c>
       <c r="AF12" s="2" t="n">
-        <v>46129</v>
+        <v>46131</v>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
@@ -2471,7 +2385,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Pamper yourself at Grand Flora Spa 💅 Get a 15% discount on your bill of 150 dirhams or more, exclusively through the Testahal app.</t>
+          <t>When announcing, clarification should be provided instead of just making an announcement on the subject and taking other actions and orders.</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2484,7 +2398,7 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
@@ -2494,81 +2408,80 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2045067912894201918</t>
+          <t>2045755517948272900</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://x.com/ForumRemittance/status/2045067912894201918</t>
+          <t>https://x.com/girluae11/status/2045755517948272900</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://x.com/ForumRemittance</t>
+          <t>https://x.com/girluae11</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ForumRemittance</t>
+          <t>girluae11</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>World Remittance Action Forum</t>
+          <t>girl</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1942959686417891328/FNdImGgE_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2043687946625368066/wksZEFYW_bigger.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Atradius, a global leader in trade credit insurance and risk management, has established operations in the Dubai International Financial Centre (DIFC), marking a key milestone in its Middle East growth strategy.#Atradius #DIFC #MiddleEast #Insurance #RiskManagement #TradeCredit https://t.co/0x6KlHhlpo</t>
+          <t>@EmiratesNBD_AE من هم حماه الوطن؟ الفئات ؟</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Emirates NBD, a leading banking group across the MENAT region, has successfully executed a USD 250 million syndicated term loan facility, “Project Radium II,” for DarGlobal.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23DarGlobal"&gt;#DarGlobal&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SyndicatedLoan"&gt;#SyndicatedLoan&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23RealEstate"&gt;#RealEstate&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23MENAT"&gt;#MENAT&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23BankingNews"&gt;#BankingNews&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Finance"&gt;#Finance&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23GlobalMarkets"&gt;#GlobalMarkets&lt;/a&gt;</t>
+          <t>من هم حماه الوطن؟ الفئات ؟</t>
         </is>
       </c>
       <c r="K13" t="b">
         <v>0</v>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 9:12 AM UTC</t>
+          <t>Apr 19, 2026 · 6:44 AM UTC</t>
         </is>
       </c>
       <c r="P13" s="2" t="n">
-        <v>46129.38333333333</v>
+        <v>46131.28055555555</v>
       </c>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23DarGlobal', 'https://x.com/search?f=tweets&amp;q=%23SyndicatedLoan', 'https://x.com/search?f=tweets&amp;q=%23RealEstate', 'https://x.com/search?f=tweets&amp;q=%23MENAT', 'https://x.com/search?f=tweets&amp;q=%23BankingNews', 'https://x.com/search?f=tweets&amp;q=%23Finance', 'https://x.com/search?f=tweets&amp;q=%23GlobalMarkets']</t>
-        </is>
-      </c>
+      <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>164</v>
+        <v>137</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -2577,28 +2490,27 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Emirates NBD, a leading banking group across the MENAT region, has successfully executed a USD 250 million syndicated term loan facility, “Project Radium II,” for DarGlobal.
-#EmiratesNBD #DarGlobal #SyndicatedLoan #RealEstate #MENAT #BankingNews #Finance #GlobalMarkets</t>
+          <t>من هم حماه الوطن؟ الفئات ؟</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>https://x.com/ForumRemittance/status/2045067912894201918</t>
+          <t>https://x.com/girluae11/status/2045755517948272900</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>Atradius, a global leader in trade credit insurance and risk management, has established operations in the Dubai International Financial Centre (DIFC), marking a key milestone in its Middle East growth strategy.#Atradius #DIFC #MiddleEast #Insurance #RiskManagement #TradeCredit https://t.co/0x6KlHhlpo</t>
+          <t>@EmiratesNBD_AE من هم حماه الوطن؟ الفئات ؟</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Atradius, a global leader in trade credit insurance and risk management, has established operations in the Dubai International Financial Centre (DIFC), marking a key milestone in its Middle East growth strategy.#Atradius #DIFC #MiddleEast #Insurance #RiskManagement #TradeCredit https://t.co/0x6KlHhlpo</t>
+          <t>@EmiratesNBD_AE من هم حماه الوطن؟ الفئات ؟</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Atradius, a global leader in trade credit insurance and risk management, has established operations in the Dubai International Financial Centre (DIFC), marking a key milestone in its Middle East growth strategy.</t>
+          <t>Who are the guardians of the homeland? The categories?</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2612,10 +2524,10 @@
         </is>
       </c>
       <c r="AE13" s="2" t="n">
-        <v>46129.55</v>
+        <v>46131.44722222222</v>
       </c>
       <c r="AF13" s="2" t="n">
-        <v>46129</v>
+        <v>46131</v>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
@@ -2629,7 +2541,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Atradius, a global leader in trade credit insurance and risk management, has established operations in the Dubai Interna…</t>
+          <t>Who are the guardians of the homeland?</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2642,7 +2554,7 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
@@ -2652,69 +2564,69 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2045063430139433260</t>
+          <t>2045729029614129456</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2045063430139433260</t>
+          <t>https://x.com/bu_rashed98/status/2045729029614129456</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide</t>
+          <t>https://x.com/bu_rashed98</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>dcgguide</t>
+          <t>bu_rashed98</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>DUBAI CITY GUIDE from Cyber Gear</t>
+          <t>﮼💛🇦🇪الامبراطور 🇦🇪💛</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1780203891230945280/ODQLZiT__bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2042287480335187974/x8vTEs88_bigger.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Dubai Holding Real Estate And Emirates NBD Partner To Introduce Integrated Off-Plan Mortgage Financing https://t.co/Iica48plSc</t>
+          <t>@EmiratesNBD_AE أنا وياهم 😁</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Dubai Holding Real Estate And Emirates NBD Partner To Introduce Integrated Off-Plan Mortgage Financing &lt;a href="https://dubaipropertyguide.io/dubai-holding-real-estate-and-emirates-nbd-partner-to-introduce-integrated-off-plan-mortgage-financing/"&gt;dubaipropertyguide.io/dubai-…&lt;/a&gt;</t>
+          <t>أنا وياهم 😁</t>
         </is>
       </c>
       <c r="K14" t="b">
         <v>0</v>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 8:54 AM UTC</t>
+          <t>Apr 19, 2026 · 4:59 AM UTC</t>
         </is>
       </c>
       <c r="P14" s="2" t="n">
-        <v>46129.37083333333</v>
+        <v>46131.20763888889</v>
       </c>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>['https://dubaipropertyguide.io/dubai-holding-real-estate-and-emirates-nbd-partner-to-introduce-integrated-off-plan-mortgage-financing/']</t>
-        </is>
-      </c>
+      <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
         <v>0</v>
       </c>
@@ -2725,7 +2637,7 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>34</v>
+        <v>141</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -2734,27 +2646,27 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Dubai Holding Real Estate And Emirates NBD Partner To Introduce Integrated Off-Plan Mortgage Financing dubaipropertyguide.io/dubai-…</t>
+          <t>أنا وياهم 😁</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2045063430139433260</t>
+          <t>https://x.com/bu_rashed98/status/2045729029614129456</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>Dubai Holding Real Estate And Emirates NBD Partner To Introduce Integrated Off-Plan Mortgage Financing https://t.co/Iica48plSc</t>
+          <t>@EmiratesNBD_AE أنا وياهم 😁</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Dubai Holding Real Estate And Emirates NBD Partner To Introduce Integrated Off-Plan Mortgage Financing https://t.co/Iica48plSc</t>
+          <t>@EmiratesNBD_AE أنا وياهم 😁</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Dubai Holding Real Estate and Emirates NBD partner to introduce integrated off-plan mortgage financing.</t>
+          <t>I am with them 😁</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2768,10 +2680,10 @@
         </is>
       </c>
       <c r="AE14" s="2" t="n">
-        <v>46129.5375</v>
+        <v>46131.37430555555</v>
       </c>
       <c r="AF14" s="2" t="n">
-        <v>46129</v>
+        <v>46131</v>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
@@ -2785,7 +2697,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Dubai Holding Real Estate and Emirates NBD partner to introduce integrated off-plan mortgage financing.</t>
+          <t>I am with them 😁</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2798,7 +2710,7 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
@@ -2808,76 +2720,78 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2045051886051688548</t>
+          <t>2045744202651226430</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://x.com/AdnanAf33353686/status/2045051886051688548</t>
+          <t>https://x.com/emiratesislamic/status/2045744202651226430</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://x.com/AdnanAf33353686</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AdnanAf33353686</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Adnan Afridi</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1695298421714804736/A6PpWdw3_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>في إطار مبادرة #متحدون_ضد_الاحتيال، قمنا بزيارة مجمّع إقامة عاملات من أجل رفع مستوى الوعي لديهن عن عمليات الاحتيال الإلكتروني وكيفية تجنبها.
-ومن خلال جلسات تفاعلية، ومسابقات، ونقاشات مفتوحة، تعرّفت المُشارِكات على كيفية اكتشاف عمليات الاحتيال، وتجنّبها وطرق الإبلاغ عنها.
-الوعي هو الخطوة الأولى نحو الحماية.
-ابقَ آمناً. كن متيقظاً.
-#متحدون_ضد_الاحتيال</t>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes.
+55 businesses will be winners. Will you be one of them?
+⭐️Grand cash prize: AED 250,000 (1 winner)
+💸 Second cash prize: AED 100,000 each (2 winners) https://t.co/V52QeTxHT6</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Hi I want to open account in nbd but my application was rejected 
-Live account is free with no minimum balance or need minimum balance</t>
+          <t>المدفوعات المستحقة تعني ضغطاً مستمراً.
+💡نصيحة: دوّن كل مدفوعاتك في مكان واحد.
+الوضوح يجعل الأمر أسهل في الإدارة. 
+&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K15" t="b">
         <v>0</v>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 8:08 AM UTC</t>
+          <t>Apr 19, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P15" s="2" t="n">
-        <v>46129.33888888889</v>
+        <v>46131.25</v>
       </c>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+        </is>
+      </c>
       <c r="S15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
@@ -2886,81 +2800,82 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Hi I want to open account in nbd but my application was rejected 
-Live account is free with no minimum balance or need minimum balance</t>
+          <t>المدفوعات المستحقة تعني ضغطاً مستمراً.
+💡نصيحة: دوّن كل مدفوعاتك في مكان واحد.
+الوضوح يجعل الأمر أسهل في الإدارة. 
+#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
+emiratesislamic.ae/ar/key-in…</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>https://x.com/AdnanAf33353686/status/2045051886051688548</t>
+          <t>https://x.com/emiratesislamic/status/2045744202651226430</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>في إطار مبادرة #متحدون_ضد_الاحتيال، قمنا بزيارة مجمّع إقامة عاملات من أجل رفع مستوى الوعي لديهن عن عمليات الاحتيال الإلكتروني وكيفية تجنبها.
-ومن خلال جلسات تفاعلية، ومسابقات، ونقاشات مفتوحة، تعرّفت المُشارِكات على كيفية اكتشاف عمليات الاحتيال، وتجنّبها وطرق الإبلاغ عنها.
-الوعي هو الخطوة الأولى نحو الحماية.
-ابقَ آمناً. كن متيقظاً.
-#متحدون_ضد_الاحتيال</t>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes.
+55 businesses will be winners. Will you be one of them?
+⭐️Grand cash prize: AED 250,000 (1 winner)
+💸 Second cash prize: AED 100,000 each (2 winners) https://t.co/V52QeTxHT6</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>في إطار مبادرة #متحدون_ضد_الاحتيال، قمنا بزيارة مجمّع إقامة عاملات من أجل رفع مستوى الوعي لديهن عن عمليات الاحتيال الإلكتروني وكيفية تجنبها.
-ومن خلال جلسات تفاعلية، ومسابقات، ونقاشات مفتوحة، تعرّفت المُشارِكات على كيفية اكتشاف عمليات الاحتيال، وتجنّبها وطرق الإبلاغ عنها.
-الوعي هو الخطوة الأولى نحو الحماية.
-ابقَ آمناً. كن متيقظاً.
-#متحدون_ضد_الاحتيال</t>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes.
+55 businesses will be winners. Will you be one of them?
+⭐️Grand cash prize: AED 250,000 (1 winner)
+💸 Second cash prize: AED 100,000 each (2 winners) https://t.co/V52QeTxHT6</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>As part of the #United_Against_Fraud initiative, we visited a residence for female workers to raise their awareness about online fraud and how to avoid it. Through interactive sessions, competitions, and open discussions, the participants learned how to detect fraud, avoid it, and report it. Awareness is the first step towards protection. Stay safe. Be vigilant. #United_Against_Fraud</t>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes. 55 businesses will be winners. Will you be one of them? ⭐️Grand cash prize: AED 250,000 (1 winner) 💸 Second cash prize: AED 100,000 each (2 winners)</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Cust</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE15" s="2" t="n">
-        <v>46129.50555555556</v>
+        <v>46131.41666666666</v>
       </c>
       <c r="AF15" s="2" t="n">
-        <v>46129</v>
+        <v>46131</v>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
+          <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>As part of the #United_Against_Fraud initiative, we visited a residence for female workers to raise their awareness about online fraud and how to avoid it. • Through interactive sessions, competitions, and open discussions, the participants learned how to detect fraud, avoid it, and report it. • Awareness is the first step towards protection.</t>
+          <t>⭐️Grand cash prize: AED 250,000 (1 winner) 💸 Second cash prize: AED 100,000 each (2 winners) • Get a chance to win a total of AED 1,000,000 in cash prizes. • 55 businesses will be winners.</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank (ENBD)</t>
+          <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AK15" t="n">
@@ -2968,7 +2883,7 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2978,70 +2893,79 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2045041596106781053</t>
+          <t>2045744202382807549</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://x.com/AnasYousiftpy0/status/2045041596106781053</t>
+          <t>https://x.com/emiratesislamic/status/2045744202382807549</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://x.com/AnasYousiftpy0</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AnasYousiftpy0</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Anas Yousif</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2020265249027289088/ZwoWrEZ3_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>🚨 JUST IN: 🇦🇪 EMIRATES NBD ELIMINATES ATM WITHDRAWAL &amp;amp; DEBIT CARD FEES ACROSS THE UAE &amp;amp; GCC UNTIL MARCH 31, 2026! 💳🔥
-#UAE #EmiratesNBD #Banking #Finance #ATM #NoFees #GCC #MoneySmart https://t.co/aI9H5crVgx</t>
+          <t>Outstanding payments = constant stress.
+💡 Tip:
+Write everything down in one place
+Clarity makes it feel manageable.
+#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
+https://t.co/XvyZgR87nM</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>هذه أخبار رائعة لعملاء Emirates NBD في المنطقة</t>
+          <t>Outstanding payments = constant stress.
+💡 Tip:
+Write everything down in one place
+Clarity makes it feel manageable.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K16" t="b">
         <v>0</v>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>['CryptoNewsHntrs']</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 7:28 AM UTC</t>
+          <t>Apr 19, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P16" s="2" t="n">
-        <v>46129.31111111111</v>
+        <v>46131.25</v>
       </c>
       <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+        </is>
+      </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
@@ -3049,77 +2973,92 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>هذه أخبار رائعة لعملاء Emirates NBD في المنطقة</t>
+          <t>Outstanding payments = constant stress.
+💡 Tip:
+Write everything down in one place
+Clarity makes it feel manageable.
+#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
+emiratesislamic.ae/en/key-in…</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>https://x.com/AnasYousiftpy0/status/2045041596106781053</t>
+          <t>https://x.com/emiratesislamic/status/2045744202382807549</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>🚨 JUST IN: 🇦🇪 EMIRATES NBD ELIMINATES ATM WITHDRAWAL &amp;amp; DEBIT CARD FEES ACROSS THE UAE &amp;amp; GCC UNTIL MARCH 31, 2026! 💳🔥
-#UAE #EmiratesNBD #Banking #Finance #ATM #NoFees #GCC #MoneySmart https://t.co/aI9H5crVgx</t>
+          <t>Outstanding payments = constant stress.
+💡 Tip:
+Write everything down in one place
+Clarity makes it feel manageable.
+#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
+https://t.co/XvyZgR87nM</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>🚨 JUST IN: 🇦🇪 EMIRATES NBD ELIMINATES ATM WITHDRAWAL &amp;amp; DEBIT CARD FEES ACROSS THE UAE &amp;amp; GCC UNTIL MARCH 31, 2026! 💳🔥
-#UAE #EmiratesNBD #Banking #Finance #ATM #NoFees #GCC #MoneySmart https://t.co/aI9H5crVgx</t>
+          <t>Outstanding payments = constant stress.
+💡 Tip:
+Write everything down in one place
+Clarity makes it feel manageable.
+#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
+https://t.co/XvyZgR87nM</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>JUST IN: EMIRATES NBD ELIMINATES ATM WITHDRAWAL &amp; DEBIT CARD FEES ACROSS THE UAE &amp; GCC UNTIL MARCH 31, 2026!</t>
+          <t>Outstanding payments equal constant stress. 
+Tip: Write everything down in one place. 
+Clarity makes it feel manageable.</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Cust</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE16" s="2" t="n">
-        <v>46129.47777777778</v>
+        <v>46131.41666666666</v>
       </c>
       <c r="AF16" s="2" t="n">
-        <v>46129</v>
+        <v>46131</v>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
+          <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>JUST IN: EMIRATES NBD ELIMINATES ATM WITHDRAWAL &amp; DEBIT CARD FEES ACROSS THE UAE &amp; GCC UNTIL MARCH 31, 2026!</t>
+          <t>Outstanding payments equal constant stress. • Tip: Write everything down in one place. • Clarity makes it feel manageable.</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank (ENBD)</t>
+          <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AK16" t="n">
@@ -3127,7 +3066,7 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>CryptoNewsHntrs</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3137,69 +3076,45 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2045034471821549807</t>
+          <t>2045771180469272971</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://x.com/Net_eqtisad/status/2045034471821549807</t>
+          <t>https://x.com/firstdiver4ever/status/2045771180469272971</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://x.com/Net_eqtisad</t>
+          <t>https://x.com/firstdiver4ever</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Net_eqtisad</t>
+          <t>firstdiver4ever</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>الشبكة الاقتصادية</t>
+          <t>اماراتى وافتخر</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1892643729745317888/Zh1HkNvX_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1974542718652280832/oqepMvc3_bigger.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>يتصدرها بنك الإمارات دبي الوطني .. أداء أكبر الأسهم الإماراتية خلال شهر أبريل 2026
-@ihc__official
-@TAQAGroup
-@ADNOCGas
-@FABConnects
-@EmiratesNBD_AE 
-@eAndUAE
-@DEWAOfficial
-@emaardubai
-@OfficialADCB
-@adnocdrillinguae
-#الإمارات 
-#الأسواق #أدنوك
-#الشبكة_الاقتصادية https://t.co/rO2sscergA</t>
+          <t>@emiratesislamic أتقدم لجميع العاملين في مصرف الإمارات الإسلامي بجزيل الشكر والتقدير على جهودهم وعملهم الدؤوب الذي قاموا به ، حيث تم مشكلتي في زمن قياسي بالوقت الذي كان من المفروض ان يتم انجازه خلال سبعة ايام عمل .
+شكرا من القلب مرة اخرى .</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>يتصدرها بنك الإمارات دبي الوطني .. أداء أكبر الأسهم الإماراتية خلال شهر أبريل 2026
-&lt;a href="/ihc__official" title="IHC"&gt;@ihc__official&lt;/a&gt;
-&lt;a href="/TAQAGroup" title="TAQA"&gt;@TAQAGroup&lt;/a&gt;
-&lt;a href="/ADNOCGas" title="ADNOC Gas"&gt;@ADNOCGas&lt;/a&gt;
-&lt;a href="/FABConnects" title="FAB Connects"&gt;@FABConnects&lt;/a&gt;
-&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; 
-&lt;a href="/eAndUAE" title="e&amp;amp; UAE"&gt;@eAndUAE&lt;/a&gt;
-&lt;a href="/DEWAOfficial" title="DEWA | Official Page"&gt;@DEWAOfficial&lt;/a&gt;
-&lt;a href="/emaardubai" title="Emaar Dubai"&gt;@emaardubai&lt;/a&gt;
-&lt;a href="/OfficialADCB" title="ADCB بنك أبوظبي التجاري"&gt;@OfficialADCB&lt;/a&gt;
-@adnocdrillinguae
-&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات"&gt;#الإمارات&lt;/a&gt; 
-&lt;a href="/search?f=tweets&amp;amp;q=%23الأسواق"&gt;#الأسواق&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23أدنوك"&gt;#أدنوك&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23الشبكة_الاقتصادية"&gt;#الشبكة_الاقتصادية&lt;/a&gt;</t>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; أتقدم لجميع العاملين في مصرف الإمارات الإسلامي بجزيل الشكر والتقدير على جهودهم وعملهم الدؤوب الذي قاموا به ، حيث تم مشكلتي في زمن قياسي بالوقت الذي كان من المفروض ان يتم انجازه خلال سبعة ايام عمل .
+شكرا من القلب مرة اخرى .</t>
         </is>
       </c>
       <c r="K17" t="b">
@@ -3209,21 +3124,21 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 6:59 AM UTC</t>
+          <t>Apr 19, 2026 · 7:47 AM UTC</t>
         </is>
       </c>
       <c r="P17" s="2" t="n">
-        <v>46129.29097222222</v>
+        <v>46131.32430555556</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
-          <t>['https://x.com/ihc__official', 'https://x.com/TAQAGroup', 'https://x.com/ADNOCGas', 'https://x.com/FABConnects', 'https://x.com/EmiratesNBD_AE', 'https://x.com/eAndUAE', 'https://x.com/DEWAOfficial', 'https://x.com/emaardubai', 'https://x.com/OfficialADCB', 'https://x.com/search?f=tweets&amp;q=%23الإمارات', 'https://x.com/search?f=tweets&amp;q=%23الأسواق', 'https://x.com/search?f=tweets&amp;q=%23أدنوك', 'https://x.com/search?f=tweets&amp;q=%23الشبكة_الاقتصادية']</t>
+          <t>['https://x.com/emiratesislamic']</t>
         </is>
       </c>
       <c r="S17" t="n">
@@ -3233,78 +3148,42 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>121</v>
+        <v>23</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>يتصدرها بنك الإمارات دبي الوطني .. أداء أكبر الأسهم الإماراتية خلال شهر أبريل 2026
-@ihc__official
-@TAQAGroup
-@ADNOCGas
-@FABConnects
-@EmiratesNBD_AE 
-@eAndUAE
-@DEWAOfficial
-@emaardubai
-@OfficialADCB
-@adnocdrillinguae
-#الإمارات 
-#الأسواق #أدنوك
-#الشبكة_الاقتصادية</t>
+          <t>@emiratesislamic أتقدم لجميع العاملين في مصرف الإمارات الإسلامي بجزيل الشكر والتقدير على جهودهم وعملهم الدؤوب الذي قاموا به ، حيث تم مشكلتي في زمن قياسي بالوقت الذي كان من المفروض ان يتم انجازه خلال سبعة ايام عمل .
+شكرا من القلب مرة اخرى .</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>https://x.com/Net_eqtisad/status/2045034471821549807</t>
+          <t>https://x.com/firstdiver4ever/status/2045771180469272971</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>يتصدرها بنك الإمارات دبي الوطني .. أداء أكبر الأسهم الإماراتية خلال شهر أبريل 2026
-@ihc__official
-@TAQAGroup
-@ADNOCGas
-@FABConnects
-@EmiratesNBD_AE 
-@eAndUAE
-@DEWAOfficial
-@emaardubai
-@OfficialADCB
-@adnocdrillinguae
-#الإمارات 
-#الأسواق #أدنوك
-#الشبكة_الاقتصادية https://t.co/rO2sscergA</t>
+          <t>@emiratesislamic أتقدم لجميع العاملين في مصرف الإمارات الإسلامي بجزيل الشكر والتقدير على جهودهم وعملهم الدؤوب الذي قاموا به ، حيث تم مشكلتي في زمن قياسي بالوقت الذي كان من المفروض ان يتم انجازه خلال سبعة ايام عمل .
+شكرا من القلب مرة اخرى .</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>يتصدرها بنك الإمارات دبي الوطني .. أداء أكبر الأسهم الإماراتية خلال شهر أبريل 2026
-@ihc__official
-@TAQAGroup
-@ADNOCGas
-@FABConnects
-@EmiratesNBD_AE 
-@eAndUAE
-@DEWAOfficial
-@emaardubai
-@OfficialADCB
-@adnocdrillinguae
-#الإمارات 
-#الأسواق #أدنوك
-#الشبكة_الاقتصادية https://t.co/rO2sscergA</t>
+          <t>@emiratesislamic أتقدم لجميع العاملين في مصرف الإمارات الإسلامي بجزيل الشكر والتقدير على جهودهم وعملهم الدؤوب الذي قاموا به ، حيث تم مشكلتي في زمن قياسي بالوقت الذي كان من المفروض ان يتم انجازه خلال سبعة ايام عمل .
+شكرا من القلب مرة اخرى .</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>The performance of the largest Emirati stocks in April 2026 is led by Emirates NBD Bank.</t>
+          <t>I would like to extend my heartfelt thanks and appreciation to all the employees at Emirates Islamic Bank for their efforts and hard work, as my issue was resolved in a record time that was supposed to take seven working days. Thank you from the heart once again.</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -3318,29 +3197,29 @@
         </is>
       </c>
       <c r="AE17" s="2" t="n">
-        <v>46129.45763888889</v>
+        <v>46131.49097222222</v>
       </c>
       <c r="AF17" s="2" t="n">
-        <v>46129</v>
+        <v>46131</v>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
+          <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>The performance of the largest Emirati stocks in April 2026 is led by Emirates NBD Bank.</t>
+          <t>Thank you from the heart once again.</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank (ENBD)</t>
+          <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AK17" t="n">
@@ -3358,80 +3237,88 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2045015539907772833</t>
+          <t>2045814764828516809</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2045015539907772833</t>
+          <t>https://x.com/UaeAlteneiji/status/2045814764828516809</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide</t>
+          <t>https://x.com/UaeAlteneiji</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>dcgguide</t>
+          <t>UaeAlteneiji</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>DUBAI CITY GUIDE from Cyber Gear</t>
+          <t>أبو عمر ، عبدالرحمن الطنيجي</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1780203891230945280/ODQLZiT__bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1906440728953204736/EXccdOZS_bigger.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Emirates NBD Successfully Executes USD 250 Million Syndicated Term Loan Facility For DAR Global, Accelerating Global Growth And Expansion https://t.co/ukTtwwan5a</t>
+          <t>@EmiratesNBD_AE من شكل الاعلان باين انه مجرد دعاية للبنك وليس دعماً لحماة الوطن
+اعلان غير موفق
+اعلان محدد بتاريخ صلاحية 
+اعلان تحكمه الشروط والاحكام المجهولة
+هنالك بنوك أخرى تقدم عروض تتافسية جذابة أكثر ومزايا أفضل وأحسن وتقدم لجميع العملاء ولعامة الشعب دون منية</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Emirates NBD Successfully Executes USD 250 Million Syndicated Term Loan Facility For DAR Global, Accelerating Global Growth And Expansion &lt;a href="https://blog.dubaicityguide.com/site/emirates-nbd-successfully-executes-usd-250-million-syndicated-term-loan-facility-for-dar-global-accelerating-global-growth-and-expansion/"&gt;blog.dubaicityguide.com/site…&lt;/a&gt;</t>
+          <t>من شكل الاعلان باين انه مجرد دعاية للبنك وليس دعماً لحماة الوطن
+اعلان غير موفق
+اعلان محدد بتاريخ صلاحية 
+اعلان تحكمه الشروط والاحكام المجهولة
+هنالك بنوك أخرى تقدم عروض تتافسية جذابة أكثر ومزايا أفضل وأحسن وتقدم لجميع العملاء ولعامة الشعب دون منية</t>
         </is>
       </c>
       <c r="K18" t="b">
         <v>0</v>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 5:44 AM UTC</t>
+          <t>Apr 19, 2026 · 10:40 AM UTC</t>
         </is>
       </c>
       <c r="P18" s="2" t="n">
-        <v>46129.23888888889</v>
+        <v>46131.44444444445</v>
       </c>
       <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>['https://blog.dubaicityguide.com/site/emirates-nbd-successfully-executes-usd-250-million-syndicated-term-loan-facility-for-dar-global-accelerating-global-growth-and-expansion/']</t>
-        </is>
-      </c>
+      <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>138</v>
+        <v>20</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -3440,27 +3327,39 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Emirates NBD Successfully Executes USD 250 Million Syndicated Term Loan Facility For DAR Global, Accelerating Global Growth And Expansion blog.dubaicityguide.com/site…</t>
+          <t>من شكل الاعلان باين انه مجرد دعاية للبنك وليس دعماً لحماة الوطن
+اعلان غير موفق
+اعلان محدد بتاريخ صلاحية 
+اعلان تحكمه الشروط والاحكام المجهولة
+هنالك بنوك أخرى تقدم عروض تتافسية جذابة أكثر ومزايا أفضل وأحسن وتقدم لجميع العملاء ولعامة الشعب دون منية</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2045015539907772833</t>
+          <t>https://x.com/UaeAlteneiji/status/2045814764828516809</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>Emirates NBD Successfully Executes USD 250 Million Syndicated Term Loan Facility For DAR Global, Accelerating Global Growth And Expansion https://t.co/ukTtwwan5a</t>
+          <t>@EmiratesNBD_AE من شكل الاعلان باين انه مجرد دعاية للبنك وليس دعماً لحماة الوطن
+اعلان غير موفق
+اعلان محدد بتاريخ صلاحية 
+اعلان تحكمه الشروط والاحكام المجهولة
+هنالك بنوك أخرى تقدم عروض تتافسية جذابة أكثر ومزايا أفضل وأحسن وتقدم لجميع العملاء ولعامة الشعب دون منية</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Emirates NBD Successfully Executes USD 250 Million Syndicated Term Loan Facility For DAR Global, Accelerating Global Growth And Expansion https://t.co/ukTtwwan5a</t>
+          <t>@EmiratesNBD_AE من شكل الاعلان باين انه مجرد دعاية للبنك وليس دعماً لحماة الوطن
+اعلان غير موفق
+اعلان محدد بتاريخ صلاحية 
+اعلان تحكمه الشروط والاحكام المجهولة
+هنالك بنوك أخرى تقدم عروض تتافسية جذابة أكثر ومزايا أفضل وأحسن وتقدم لجميع العملاء ولعامة الشعب دون منية</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Emirates NBD successfully executes a USD 250 million syndicated term loan facility for DAR Global, accelerating global growth and expansion.</t>
+          <t>From the shape of the advertisement, it is clear that it is just a promotion for the bank and not support for the nation's protectors. An unsuccessful advertisement. An advertisement with an expiration date. An advertisement governed by unknown terms and conditions. There are other banks that offer more attractive competitive offers and better advantages, available to all customers and the general public without favoritism.</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3470,14 +3369,14 @@
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="AE18" s="2" t="n">
-        <v>46129.40555555555</v>
+        <v>46131.61111111111</v>
       </c>
       <c r="AF18" s="2" t="n">
-        <v>46129</v>
+        <v>46131</v>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
@@ -3491,7 +3390,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Emirates NBD successfully executes a USD 250 million syndicated term loan facility for DAR Global, accelerating global growth and expansion.</t>
+          <t>There are other banks that offer more attractive competitive offers and better advantages, available to all customers and the general public without favoritism. • From the shape of the advertisement, it is clear that it is just a promotion for the bank and not support for the nation's protectors. • An advertisement governed by unknown terms and conditions.</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -3504,7 +3403,7 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
@@ -3514,43 +3413,49 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2045007726171099435</t>
+          <t>2045801203934925261</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://x.com/oppolutty_/status/2045007726171099435</t>
+          <t>https://x.com/amerbinhraiz/status/2045801203934925261</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://x.com/oppolutty_</t>
+          <t>https://x.com/amerbinhraiz</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>oppolutty_</t>
+          <t>amerbinhraiz</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>തവിട് തങ്കമ്മ ® 👒</t>
+          <t>بـتـال | Batal</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2037238374906683392/bv83nzp4_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2033838640934359040/zShxD0Gl_bigger.jpg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Is there any updates or changes regarding Installment deferment for the personal loan due to current geopolitical circumstances,</t>
+          <t>@EmiratesNBD_AE نريدكم تلغون الفايدة من اصحاب 
+المديونيات الطويلة القديمة
+كل شي واقف عليهم وماخذين فايدة
+ عليهم ضعف قيمة القرض !</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>for credit card payment?</t>
+          <t>نريدكم تلغون الفايدة من اصحاب 
+المديونيات الطويلة القديمة
+كل شي واقف عليهم وماخذين فايدة
+ عليهم ضعف قيمة القرض !</t>
         </is>
       </c>
       <c r="K19" t="b">
@@ -3559,26 +3464,26 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_AE', 'SunnyLusty']</t>
+          <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 5:13 AM UTC</t>
+          <t>Apr 19, 2026 · 9:46 AM UTC</t>
         </is>
       </c>
       <c r="P19" s="2" t="n">
-        <v>46129.21736111111</v>
+        <v>46131.40694444445</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -3587,7 +3492,7 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -3596,27 +3501,36 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>for credit card payment?</t>
+          <t>نريدكم تلغون الفايدة من اصحاب 
+المديونيات الطويلة القديمة
+كل شي واقف عليهم وماخذين فايدة
+ عليهم ضعف قيمة القرض !</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>https://x.com/oppolutty_/status/2045007726171099435</t>
+          <t>https://x.com/amerbinhraiz/status/2045801203934925261</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Is there any updates or changes regarding Installment deferment for the personal loan due to current geopolitical circumstances,</t>
+          <t>@EmiratesNBD_AE نريدكم تلغون الفايدة من اصحاب 
+المديونيات الطويلة القديمة
+كل شي واقف عليهم وماخذين فايدة
+ عليهم ضعف قيمة القرض !</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Is there any updates or changes regarding Installment deferment for the personal loan due to current geopolitical circumstances,</t>
+          <t>@EmiratesNBD_AE نريدكم تلغون الفايدة من اصحاب 
+المديونيات الطويلة القديمة
+كل شي واقف عليهم وماخذين فايدة
+ عليهم ضعف قيمة القرض !</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Is there any updates or changes regarding installment deferment for the personal loan due to current geopolitical circumstances?</t>
+          <t>We want you to cancel the interest for those with old long-term debts. Everything is stalled because of them, and they are paying double the value of the loan in interest!</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3626,14 +3540,14 @@
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="AE19" s="2" t="n">
-        <v>46129.38402777778</v>
+        <v>46131.57361111111</v>
       </c>
       <c r="AF19" s="2" t="n">
-        <v>46129</v>
+        <v>46131</v>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
@@ -3647,7 +3561,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Is there any updates or changes regarding installment deferment for the personal loan due to current geopolitical circumstances?</t>
+          <t>Everything is stalled because of them, and they are paying double the value of the loan in interest! • We want you to cancel the interest for those with old long-term debts.</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -3660,7 +3574,7 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE, SunnyLusty</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
@@ -3670,65 +3584,45 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2044992676236587055</t>
+          <t>2045958337494143476</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://x.com/arabtimesnews/status/2044992676236587055</t>
+          <t>https://x.com/ansariiarif/status/2045958337494143476</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://x.com/arabtimesnews</t>
+          <t>https://x.com/ansariiarif</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>arabtimesnews</t>
+          <t>ansariiarif</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Arab Times News</t>
+          <t>Arif</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1793936454734712832/oEtzciVg_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1268363851231383555/JkBzC9kT_bigger.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>UAE’s 10 Most Valuable Listed Companies in 2026.
-https://t.co/yZ0hDQKWQJ
-International Holding Company (@ihc__official )
-TAQA Group (@TAQAGroup)
-ADNOC Gas (@ADNOCGas)
-First Abu Dhabi Bank (@FABConnects)
-Emirates NBD Group (@EmiratesNBD_AE)
-e&amp; (@eAndGroup)
-Dubai Electricity and Water Authority (@DEWAOfficial)
-Emaar Properties (@emaardubai)
-Abu Dhabi Commercial Bank (@OfficialADCB)
-Alpha Dhabi Holding (@adh_uae)</t>
+          <t>@EmiratesNBD_AE 
+I have been chargd without any reason. Not expexted this from NDB as per their policy I have spent the required amount but still they have charged me for accessing the lounge which shouldn't be!!!</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>UAE’s 10 Most Valuable Listed Companies in 2026.
-&lt;a href="https://arabtimesnews.com/uaes-10-most-valuable-listed-companies-in-2026/"&gt;arabtimesnews.com/uaes-10-mo…&lt;/a&gt;
-International Holding Company (&lt;a href="/ihc__official" title="IHC"&gt;@ihc__official&lt;/a&gt; )
-TAQA Group (&lt;a href="/TAQAGroup" title="TAQA"&gt;@TAQAGroup&lt;/a&gt;)
-ADNOC Gas (&lt;a href="/ADNOCGas" title="ADNOC Gas"&gt;@ADNOCGas&lt;/a&gt;)
-First Abu Dhabi Bank (&lt;a href="/FABConnects" title="FAB Connects"&gt;@FABConnects&lt;/a&gt;)
-Emirates NBD Group (&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;)
-e&amp;amp; (&lt;a href="/eAndGroup" title="e&amp;amp;"&gt;@eAndGroup&lt;/a&gt;)
-Dubai Electricity and Water Authority (&lt;a href="/DEWAOfficial" title="DEWA | Official Page"&gt;@DEWAOfficial&lt;/a&gt;)
-Emaar Properties (&lt;a href="/emaardubai" title="Emaar Dubai"&gt;@emaardubai&lt;/a&gt;)
-Abu Dhabi Commercial Bank (&lt;a href="/OfficialADCB" title="ADCB بنك أبوظبي التجاري"&gt;@OfficialADCB&lt;/a&gt;)
-Alpha Dhabi Holding (&lt;a href="/adh_uae" title="Alpha Dhabi Holding"&gt;@adh_uae&lt;/a&gt;)</t>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; 
+I have been chargd without any reason. Not expexted this from NDB as per their policy I have spent the required amount but still they have charged me for accessing the lounge which shouldn&amp;#39;t be!!!</t>
         </is>
       </c>
       <c r="K20" t="b">
@@ -3738,21 +3632,21 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>7h</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 4:13 AM UTC</t>
+          <t>Apr 19, 2026 · 8:10 PM UTC</t>
         </is>
       </c>
       <c r="P20" s="2" t="n">
-        <v>46129.17569444444</v>
+        <v>46131.84027777778</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
-          <t>['https://arabtimesnews.com/uaes-10-most-valuable-listed-companies-in-2026/', 'https://x.com/ihc__official', 'https://x.com/TAQAGroup', 'https://x.com/ADNOCGas', 'https://x.com/FABConnects', 'https://x.com/EmiratesNBD_AE', 'https://x.com/eAndGroup', 'https://x.com/DEWAOfficial', 'https://x.com/emaardubai', 'https://x.com/OfficialADCB', 'https://x.com/adh_uae']</t>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="S20" t="n">
@@ -3765,7 +3659,7 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -3774,70 +3668,30 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>UAE’s 10 Most Valuable Listed Companies in 2026.
-arabtimesnews.com/uaes-10-mo…
-International Holding Company (@ihc__official )
-TAQA Group (@TAQAGroup)
-ADNOC Gas (@ADNOCGas)
-First Abu Dhabi Bank (@FABConnects)
-Emirates NBD Group (@EmiratesNBD_AE)
-e&amp; (@eAndGroup)
-Dubai Electricity and Water Authority (@DEWAOfficial)
-Emaar Properties (@emaardubai)
-Abu Dhabi Commercial Bank (@OfficialADCB)
-Alpha Dhabi Holding (@adh_uae)</t>
+          <t>@EmiratesNBD_AE 
+I have been chargd without any reason. Not expexted this from NDB as per their policy I have spent the required amount but still they have charged me for accessing the lounge which shouldn't be!!!</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>https://x.com/arabtimesnews/status/2044992676236587055</t>
+          <t>https://x.com/ansariiarif/status/2045958337494143476</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>UAE’s 10 Most Valuable Listed Companies in 2026.
-https://t.co/yZ0hDQKWQJ
-International Holding Company (@ihc__official )
-TAQA Group (@TAQAGroup)
-ADNOC Gas (@ADNOCGas)
-First Abu Dhabi Bank (@FABConnects)
-Emirates NBD Group (@EmiratesNBD_AE)
-e&amp; (@eAndGroup)
-Dubai Electricity and Water Authority (@DEWAOfficial)
-Emaar Properties (@emaardubai)
-Abu Dhabi Commercial Bank (@OfficialADCB)
-Alpha Dhabi Holding (@adh_uae)</t>
+          <t>@EmiratesNBD_AE 
+I have been chargd without any reason. Not expexted this from NDB as per their policy I have spent the required amount but still they have charged me for accessing the lounge which shouldn't be!!!</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>UAE’s 10 Most Valuable Listed Companies in 2026.
-https://t.co/yZ0hDQKWQJ
-International Holding Company (@ihc__official )
-TAQA Group (@TAQAGroup)
-ADNOC Gas (@ADNOCGas)
-First Abu Dhabi Bank (@FABConnects)
-Emirates NBD Group (@EmiratesNBD_AE)
-e&amp; (@eAndGroup)
-Dubai Electricity and Water Authority (@DEWAOfficial)
-Emaar Properties (@emaardubai)
-Abu Dhabi Commercial Bank (@OfficialADCB)
-Alpha Dhabi Holding (@adh_uae)</t>
+          <t>@EmiratesNBD_AE 
+I have been chargd without any reason. Not expexted this from NDB as per their policy I have spent the required amount but still they have charged me for accessing the lounge which shouldn't be!!!</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>UAE’s 10 Most Valuable Listed Companies in 2026. 
-International Holding Company 
-TAQA Group 
-ADNOC Gas 
-First Abu Dhabi Bank 
-Emirates NBD Group 
-e&amp; 
-Dubai Electricity and Water Authority 
-Emaar Properties 
-Abu Dhabi Commercial Bank 
-Alpha Dhabi Holding</t>
+          <t>I have been charged without any reason. I did not expect this from NDB; according to their policy, I have spent the required amount, but still, they have charged me for accessing the lounge, which shouldn't be the case!</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3847,14 +3701,14 @@
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="AE20" s="2" t="n">
-        <v>46129.34236111111</v>
+        <v>46132.00694444445</v>
       </c>
       <c r="AF20" s="2" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
@@ -3868,7 +3722,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>International Holding Company TAQA Group ADNOC Gas First Abu Dhabi Bank Emirates NBD Group e&amp; Dubai Electricity and Water Authority Emaar Properties Abu Dhabi Commercial Bank Alpha Dhabi Holding • UAE’s 10 Most Valuable Listed Companies in 2026.</t>
+          <t>I did not expect this from NDB; according to their policy, I have spent the required amount, but still, they have charged me for accessing the lounge, which shouldn't be the case! • I have been charged without any reason.</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3891,45 +3745,43 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2044988741345747256</t>
+          <t>2045922728868479327</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://x.com/AbdulAzizAbpv9/status/2044988741345747256</t>
+          <t>https://x.com/f3100000/status/2045922728868479327</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://x.com/AbdulAzizAbpv9</t>
+          <t>https://x.com/f3100000</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AbdulAzizAbpv9</t>
+          <t>f3100000</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>عبد العزيز المشاولة</t>
+          <t>F35</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2035325614547443712/Z6T88mVG_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2024219709168918529/LqA8XT-p_bigger.jpg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>A nation united. A pride we all share. 🇦🇪
-In line with the call of His Highness Sheikh Mohammed bin Rashid Al Maktoum, let’s raise the UAE flag high and take pride in the unity, strength, and spirit that define our nation.
-Join this moment of pride. #ProudOfUAE https://t.co/TWfYdjxwLN</t>
+          <t>@EmiratesNBD_AE دعم من اي نوع هذا</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>نفخر بأنفسنا@نعم نفرح كثير/&amp;lt; بالارهاب مطار البحرين/ فداك الوطن</t>
+          <t>دعم من اي نوع هذا</t>
         </is>
       </c>
       <c r="K21" t="b">
@@ -3943,21 +3795,21 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Apr 17</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 3:58 AM UTC</t>
+          <t>Apr 19, 2026 · 5:49 PM UTC</t>
         </is>
       </c>
       <c r="P21" s="2" t="n">
-        <v>46129.16527777778</v>
+        <v>46131.74236111111</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
@@ -3966,7 +3818,7 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -3975,33 +3827,27 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>نفخر بأنفسنا@نعم نفرح كثير/&lt; بالارهاب مطار البحرين/ فداك الوطن</t>
+          <t>دعم من اي نوع هذا</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>https://x.com/AbdulAzizAbpv9/status/2044988741345747256</t>
+          <t>https://x.com/f3100000/status/2045922728868479327</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>A nation united. A pride we all share. 🇦🇪
-In line with the call of His Highness Sheikh Mohammed bin Rashid Al Maktoum, let’s raise the UAE flag high and take pride in the unity, strength, and spirit that define our nation.
-Join this moment of pride. #ProudOfUAE https://t.co/TWfYdjxwLN</t>
+          <t>@EmiratesNBD_AE دعم من اي نوع هذا</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>A nation united. A pride we all share. 🇦🇪
-In line with the call of His Highness Sheikh Mohammed bin Rashid Al Maktoum, let’s raise the UAE flag high and take pride in the unity, strength, and spirit that define our nation.
-Join this moment of pride. #ProudOfUAE https://t.co/TWfYdjxwLN</t>
+          <t>@EmiratesNBD_AE دعم من اي نوع هذا</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>A nation united. A pride we all share. 
-In line with the call of His Highness Sheikh Mohammed bin Rashid Al Maktoum, let’s raise the UAE flag high and take pride in the unity, strength, and spirit that define our nation.
-Join this moment of pride. #ProudOfUAE</t>
+          <t>What kind of support is this?</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -4011,14 +3857,14 @@
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="AE21" s="2" t="n">
-        <v>46129.33194444444</v>
+        <v>46131.90902777778</v>
       </c>
       <c r="AF21" s="2" t="n">
-        <v>46129</v>
+        <v>46131</v>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
@@ -4032,7 +3878,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>In line with the call of His Highness Sheikh Mohammed bin Rashid Al Maktoum, let’s raise the UAE flag high and take pride in the unity, strength, and spirit that define our nation. • Join this moment of pride.</t>
+          <t>What kind of support is this?</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -4055,45 +3901,43 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2044955402941673971</t>
+          <t>2045824669907845529</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://x.com/Kyodonews_JBN/status/2044955402941673971</t>
+          <t>https://x.com/m_azeemq/status/2045824669907845529</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://x.com/Kyodonews_JBN</t>
+          <t>https://x.com/m_azeemq</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kyodonews_JBN</t>
+          <t>m_azeemq</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>KYODONEWS JBN</t>
+          <t>Muhammad Azeem Qureshi</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2003285704613462020/Gn9wk2B__bigger.jpg</t>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Emirates NBD successfully executes USD 250 Million Syndicated Term Loan facility for Dar Global, Accelerating Global Growth and Expansion【Dar Global】
-kyodonewsprwire.jp/release/2…</t>
+          <t>@EmiratesNBD_KSA ,It is extremely disappointing to experience such unprofessional customer support. Despite repeated attempts to contact you via email and phone, I have received no meaningful response/clarification on my issue which is pending now since more than 2.5 month</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Emirates NBD successfully executes USD 250 Million Syndicated Term Loan facility for Dar Global, Accelerating Global Growth and Expansion【Dar Global】
-&lt;a href="https://kyodonewsprwire.jp/release/202604167601"&gt;kyodonewsprwire.jp/release/2…&lt;/a&gt;</t>
+          <t>&lt;a href="/EmiratesNBD_KSA" title="Emirates NBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; ,It is extremely disappointing to experience such unprofessional customer support. Despite repeated attempts to contact you via email and phone, I have received no meaningful response/clarification on my issue which is pending now since more than 2.5 month</t>
         </is>
       </c>
       <c r="K22" t="b">
@@ -4103,34 +3947,34 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Apr 17</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 1:45 AM UTC</t>
+          <t>Apr 19, 2026 · 11:19 AM UTC</t>
         </is>
       </c>
       <c r="P22" s="2" t="n">
-        <v>46129.07291666666</v>
+        <v>46131.47152777778</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
-          <t>['https://kyodonewsprwire.jp/release/202604167601']</t>
+          <t>['https://x.com/EmiratesNBD_KSA']</t>
         </is>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>148</v>
+        <v>13</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -4139,21 +3983,27 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Emirates NBD successfully executes USD 250 Million Syndicated Term Loan facility for Dar Global, Accelerating Global Growth and Expansion【Dar Global】
-kyodonewsprwire.jp/release/2…</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
+          <t>@EmiratesNBD_KSA ,It is extremely disappointing to experience such unprofessional customer support. Despite repeated attempts to contact you via email and phone, I have received no meaningful response/clarification on my issue which is pending now since more than 2.5 month</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>https://x.com/m_azeemq/status/2045824669907845529</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA ,It is extremely disappointing to experience such unprofessional customer support. Despite repeated attempts to contact you via email and phone, I have received no meaningful response/clarification on my issue which is pending now since more than 2.5 month</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Emirates NBD successfully executes USD 250 Million Syndicated Term Loan facility for Dar Global, Accelerating Global Growth and Expansion【Dar Global】
-kyodonewsprwire.jp/release/2…</t>
+          <t>@EmiratesNBD_KSA ,It is extremely disappointing to experience such unprofessional customer support. Despite repeated attempts to contact you via email and phone, I have received no meaningful response/clarification on my issue which is pending now since more than 2.5 month</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Emirates NBD successfully executes a USD 250 million syndicated term loan facility for Dar Global, accelerating global growth and expansion.</t>
+          <t>It is extremely disappointing to experience such unprofessional customer support. Despite repeated attempts to contact you via email and phone, I have received no meaningful response or clarification on my issue, which has been pending for more than 2.5 months.</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -4163,14 +4013,14 @@
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="AE22" s="2" t="n">
-        <v>46129.23958333334</v>
+        <v>46131.63819444444</v>
       </c>
       <c r="AF22" s="2" t="n">
-        <v>46129</v>
+        <v>46131</v>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
@@ -4184,7 +4034,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Emirates NBD successfully executes a USD 250 million syndicated term loan facility for Dar Global, accelerating global growth and expansion.</t>
+          <t>Despite repeated attempts to contact you via email and phone, I have received no meaningful response or clarification on my issue, which has been pending for more than 2.5 months. • It is extremely disappointing to experience such unprofessional customer support.</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -4196,1181 +4046,6 @@
         <v>2026</v>
       </c>
       <c r="AL22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2045019425548452068</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2045019425548452068</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Always check fines through official RTA apps or websites - not SMS links.
-Do not fall for the traps. Stay alert to scams.
-#EIAgainstFraud with Emirates Islamic.
-#TogetherAgainstFraud
-https://t.co/y7eSpGNdfk</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Always check fines through official RTA apps or websites - not SMS links.
-Do not fall for the traps. Stay alert to scams.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
-&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K23" t="b">
-        <v>0</v>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Apr 17, 2026 · 6:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="n">
-        <v>46129.25</v>
-      </c>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud', 'https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security']</t>
-        </is>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>50</v>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>Always check fines through official RTA apps or websites - not SMS links.
-Do not fall for the traps. Stay alert to scams.
-#EIAgainstFraud with Emirates Islamic.
-#TogetherAgainstFraud
-emiratesislamic.ae/en/person…</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2045019425548452068</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>Always check fines through official RTA apps or websites - not SMS links.
-Do not fall for the traps. Stay alert to scams.
-#EIAgainstFraud with Emirates Islamic.
-#TogetherAgainstFraud
-https://t.co/y7eSpGNdfk</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>Always check fines through official RTA apps or websites - not SMS links.
-Do not fall for the traps. Stay alert to scams.
-#EIAgainstFraud with Emirates Islamic.
-#TogetherAgainstFraud
-https://t.co/y7eSpGNdfk</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>Always check fines through official RTA apps or websites - not SMS links. 
-Do not fall for the traps. Stay alert to scams. 
-#EIAgainstFraud with Emirates Islamic. 
-#TogetherAgainstFraud</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE23" s="2" t="n">
-        <v>46129.41666666666</v>
-      </c>
-      <c r="AF23" s="2" t="n">
-        <v>46129</v>
-      </c>
-      <c r="AG23" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Always check fines through official RTA apps or websites - not SMS links. • #EIAgainstFraud with Emirates Islamic. • Do not fall for the traps.</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK23" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2045083221952532551</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2045083221952532551</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Get a chance to win a total of AED 1,000,000 in cash prizes.
-55 businesses will be winners. Will you be one of them?
-⭐️Grand cash prize: AED 250,000 (1 winner)
-💸 Second cash prize: AED 100,000 each (2 winners) https://t.co/V52QeTxHT6</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>💸 Monthly cash prizes: from AED 5,000 up to AED 25,000 (52 winners)
-Valid until 30 June 2026.
-Terms and conditions apply.
-&lt;a href="https://www.emiratesislamic.ae/en/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=bb_offer"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K24" t="b">
-        <v>0</v>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Apr 17, 2026 · 10:13 AM UTC</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="n">
-        <v>46129.42569444444</v>
-      </c>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=bb_offer']</t>
-        </is>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>66</v>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>💸 Monthly cash prizes: from AED 5,000 up to AED 25,000 (52 winners)
-Valid until 30 June 2026.
-Terms and conditions apply.
-emiratesislamic.ae/en/offers…</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2045083221952532551</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>Get a chance to win a total of AED 1,000,000 in cash prizes.
-55 businesses will be winners. Will you be one of them?
-⭐️Grand cash prize: AED 250,000 (1 winner)
-💸 Second cash prize: AED 100,000 each (2 winners) https://t.co/V52QeTxHT6</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>Get a chance to win a total of AED 1,000,000 in cash prizes.
-55 businesses will be winners. Will you be one of them?
-⭐️Grand cash prize: AED 250,000 (1 winner)
-💸 Second cash prize: AED 100,000 each (2 winners) https://t.co/V52QeTxHT6</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>Get a chance to win a total of AED 1,000,000 in cash prizes. 55 businesses will be winners. Will you be one of them? ⭐️Grand cash prize: AED 250,000 (1 winner) 💸 Second cash prize: AED 100,000 each (2 winners)</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="AE24" s="2" t="n">
-        <v>46129.59236111111</v>
-      </c>
-      <c r="AF24" s="2" t="n">
-        <v>46129</v>
-      </c>
-      <c r="AG24" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>⭐️Grand cash prize: AED 250,000 (1 winner) 💸 Second cash prize: AED 100,000 each (2 winners) • Get a chance to win a total of AED 1,000,000 in cash prizes. • 55 businesses will be winners.</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK24" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL24" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2045083218303402442</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2045083218303402442</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Get a chance to win a total of AED 1,000,000 in cash prizes.
-55 businesses will be winners. Will you be one of them?
-⭐️Grand cash prize: AED 250,000 (1 winner)
-💸 Second cash prize: AED 100,000 each (2 winners)</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Get a chance to win a total of AED 1,000,000 in cash prizes.
-55 businesses will be winners. Will you be one of them?
-⭐️Grand cash prize: AED 250,000 (1 winner)
-💸 Second cash prize: AED 100,000 each (2 winners)</t>
-        </is>
-      </c>
-      <c r="K25" t="b">
-        <v>0</v>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>Apr 17, 2026 · 10:13 AM UTC</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="n">
-        <v>46129.42569444444</v>
-      </c>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="n">
-        <v>1</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1</v>
-      </c>
-      <c r="V25" t="n">
-        <v>93</v>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>Get a chance to win a total of AED 1,000,000 in cash prizes.
-55 businesses will be winners. Will you be one of them?
-⭐️Grand cash prize: AED 250,000 (1 winner)
-💸 Second cash prize: AED 100,000 each (2 winners)</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>Get a chance to win a total of AED 1,000,000 in cash prizes.
-55 businesses will be winners. Will you be one of them?
-⭐️Grand cash prize: AED 250,000 (1 winner)
-💸 Second cash prize: AED 100,000 each (2 winners)</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>Get a chance to win a total of AED 1,000,000 in cash prizes. 
-55 businesses will be winners. Will you be one of them? 
-⭐️Grand cash prize: AED 250,000 (1 winner) 
-💸 Second cash prize: AED 100,000 each (2 winners)</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE25" s="2" t="n">
-        <v>46129.59236111111</v>
-      </c>
-      <c r="AF25" s="2" t="n">
-        <v>46129</v>
-      </c>
-      <c r="AG25" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>⭐️Grand cash prize: AED 250,000 (1 winner) 💸 Second cash prize: AED 100,000 each (2 winners) • Get a chance to win a total of AED 1,000,000 in cash prizes. • 55 businesses will be winners.</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK25" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL25" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2045083209231221028</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2045083209231221028</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية التي تصل قيمتها إلى 1,000,000 درهم.
-اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟
-⭐️الجائزة النقدية الكبرى: 250,000 درهم (فائز واحد) 
-💸الجائزة النقدية الثانية: 100,000 درهم (فائزان اثنان) https://t.co/WPnaJpO7F4</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>💸الجوائز النقدية الشهرية: من 5,000 إلى 25,000 درهم (52 فائز)
-يسري العرض لغاية 30 يونيو 2026.
-تطبق الشروط والأحكام.
-&lt;a href="https://www.emiratesislamic.ae/ar/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=bb_offer"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K26" t="b">
-        <v>0</v>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Apr 17, 2026 · 10:13 AM UTC</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="n">
-        <v>46129.42569444444</v>
-      </c>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=bb_offer']</t>
-        </is>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>44</v>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>💸الجوائز النقدية الشهرية: من 5,000 إلى 25,000 درهم (52 فائز)
-يسري العرض لغاية 30 يونيو 2026.
-تطبق الشروط والأحكام.
-emiratesislamic.ae/ar/offers…</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2045083209231221028</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية التي تصل قيمتها إلى 1,000,000 درهم.
-اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟
-⭐️الجائزة النقدية الكبرى: 250,000 درهم (فائز واحد) 
-💸الجائزة النقدية الثانية: 100,000 درهم (فائزان اثنان) https://t.co/WPnaJpO7F4</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية التي تصل قيمتها إلى 1,000,000 درهم.
-اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟
-⭐️الجائزة النقدية الكبرى: 250,000 درهم (فائز واحد) 
-💸الجائزة النقدية الثانية: 100,000 درهم (فائزان اثنان) https://t.co/WPnaJpO7F4</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>Get a chance to win a share of cash prizes worth up to 1,000,000 dirhams. 
-Make your company one of the 55 winning companies. Will you be among them? 
-⭐️Grand cash prize: 250,000 dirhams (one winner) 
-💸Second cash prize: 100,000 dirhams (two winners)</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE26" s="2" t="n">
-        <v>46129.59236111111</v>
-      </c>
-      <c r="AF26" s="2" t="n">
-        <v>46129</v>
-      </c>
-      <c r="AG26" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>⭐️Grand cash prize: 250,000 dirhams (one winner) 💸Second cash prize: 100,000 dirhams (two winners) • Get a chance to win a share of cash prizes worth up to 1,000,000 dirhams. • Make your company one of the 55 winning companies.</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK26" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL26" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2045083206936908088</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2045083206936908088</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية التي تصل قيمتها إلى 1,000,000 درهم.
-اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟
-⭐️الجائزة النقدية الكبرى: 250,000 درهم (فائز واحد) 
-💸الجائزة النقدية الثانية: 100,000 درهم (فائزان اثنان)</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية التي تصل قيمتها إلى 1,000,000 درهم.
-اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟
-⭐️الجائزة النقدية الكبرى: 250,000 درهم (فائز واحد) 
-💸الجائزة النقدية الثانية: 100,000 درهم (فائزان اثنان)</t>
-        </is>
-      </c>
-      <c r="K27" t="b">
-        <v>0</v>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>Apr 17, 2026 · 10:13 AM UTC</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="n">
-        <v>46129.42569444444</v>
-      </c>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="n">
-        <v>1</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>69</v>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية التي تصل قيمتها إلى 1,000,000 درهم.
-اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟
-⭐️الجائزة النقدية الكبرى: 250,000 درهم (فائز واحد) 
-💸الجائزة النقدية الثانية: 100,000 درهم (فائزان اثنان)</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية التي تصل قيمتها إلى 1,000,000 درهم.
-اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟
-⭐️الجائزة النقدية الكبرى: 250,000 درهم (فائز واحد) 
-💸الجائزة النقدية الثانية: 100,000 درهم (فائزان اثنان)</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>Get a chance to win a share of cash prizes worth up to 1,000,000 dirhams. 
-Make your company one of the 55 winning companies. Will you be among them? 
-⭐️Grand cash prize: 250,000 dirhams (one winner) 
-💸Second cash prize: 100,000 dirhams (two winners)</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE27" s="2" t="n">
-        <v>46129.59236111111</v>
-      </c>
-      <c r="AF27" s="2" t="n">
-        <v>46129</v>
-      </c>
-      <c r="AG27" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>⭐️Grand cash prize: 250,000 dirhams (one winner) 💸Second cash prize: 100,000 dirhams (two winners) • Get a chance to win a share of cash prizes worth up to 1,000,000 dirhams. • Make your company one of the 55 winning companies.</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK27" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL27" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2045034534274540029</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2045034534274540029</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Save and earn with your Emirates Islamic Super Savings Etihad Guest Account!
-💸 Get up to 750,000 Etihad Guest Miles every quarter and up to 3 million Etihad Guest Miles in a year https://t.co/y8cuMSrpQL</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل.</t>
-        </is>
-      </c>
-      <c r="K28" t="b">
-        <v>0</v>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>['1ss9490ss1']</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>Apr 17, 2026 · 7:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="n">
-        <v>46129.29166666666</v>
-      </c>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>2</v>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل.</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2045034534274540029</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>Save and earn with your Emirates Islamic Super Savings Etihad Guest Account!
-💸 Get up to 750,000 Etihad Guest Miles every quarter and up to 3 million Etihad Guest Miles in a year https://t.co/y8cuMSrpQL</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>Save and earn with your Emirates Islamic Super Savings Etihad Guest Account!
-💸 Get up to 750,000 Etihad Guest Miles every quarter and up to 3 million Etihad Guest Miles in a year https://t.co/y8cuMSrpQL</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>Save and earn with your Emirates Islamic Super Savings Etihad Guest Account! 
-Get up to 750,000 Etihad Guest Miles every quarter and up to 3 million Etihad Guest Miles in a year.</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="AE28" s="2" t="n">
-        <v>46129.45833333334</v>
-      </c>
-      <c r="AF28" s="2" t="n">
-        <v>46129</v>
-      </c>
-      <c r="AG28" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Get up to 750,000 Etihad Guest Miles every quarter and up to 3 million Etihad Guest Miles in a year. • Save and earn with your Emirates Islamic Super Savings Etihad Guest Account!</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK28" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL28" t="inlineStr">
-        <is>
-          <t>1ss9490ss1</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2045019425548460066</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2045019425548460066</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>تحقق دائماً من المخالفات عبر تطبيقات أو مواقع هيئة الطرق والمواصلات الرسمية، وليس من خلال روابط الرسائل النصية.
-لا تقع في الفخ. احذر الاحتيال.
-#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
-https://t.co/ltnxcRlBOA</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>تحقق دائماً من المخالفات عبر تطبيقات أو مواقع هيئة الطرق والمواصلات الرسمية، وليس من خلال روابط الرسائل النصية.
-لا تقع في الفخ. احذر الاحتيال.
-&lt;a href="/search?f=tweets&amp;amp;q=%23متحّدون_ضد_الاحتيال"&gt;#متحّدون_ضد_الاحتيال&lt;/a&gt; مع الإمارات الإسلامي.
-&lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K29" t="b">
-        <v>0</v>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>Apr 17, 2026 · 6:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="n">
-        <v>46129.25</v>
-      </c>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23متحّدون_ضد_الاحتيال', 'https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security']</t>
-        </is>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>61</v>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>تحقق دائماً من المخالفات عبر تطبيقات أو مواقع هيئة الطرق والمواصلات الرسمية، وليس من خلال روابط الرسائل النصية.
-لا تقع في الفخ. احذر الاحتيال.
-#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
-emiratesislamic.ae/ar/person…</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2045019425548460066</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>تحقق دائماً من المخالفات عبر تطبيقات أو مواقع هيئة الطرق والمواصلات الرسمية، وليس من خلال روابط الرسائل النصية.
-لا تقع في الفخ. احذر الاحتيال.
-#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
-https://t.co/ltnxcRlBOA</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>تحقق دائماً من المخالفات عبر تطبيقات أو مواقع هيئة الطرق والمواصلات الرسمية، وليس من خلال روابط الرسائل النصية.
-لا تقع في الفخ. احذر الاحتيال.
-#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
-https://t.co/ltnxcRlBOA</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>Always check for violations through the official apps or websites of the Roads and Transport Authority, not through text message links.
-Don't fall into the trap. Beware of fraud.
-#United_Against_Fraud with Emirates Islamic.</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="AE29" s="2" t="n">
-        <v>46129.41666666666</v>
-      </c>
-      <c r="AF29" s="2" t="n">
-        <v>46129</v>
-      </c>
-      <c r="AG29" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Always check for violations through the official apps or websites of the Roads and Transport Authority, not through text message links. • #United_Against_Fraud with Emirates Islamic. • Don't fall into the trap.</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK29" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL29" t="inlineStr">
         <is>
           <t>None</t>
         </is>

--- a/check2.xlsx
+++ b/check2.xlsx
@@ -741,7 +741,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>God, I hate slow internet; it's a killer of productivity. I had 1000 Mbps in Mexico City, but genocidal Jews and genocidal gays sabotaged that, as they thought my high speed could hinder, expose, or endanger their crimes and conspiracies. Economic siege Mexico CDMX Islamophobia USA</t>
+          <t>God, I hate slow internet; it's a killer of productivity. I had 1000 Mbps in Mexico City, but genocidal Jews and genocidal gays sabotaged that, as they thought my high speed could hinder, expose, or endanger their crimes and conspiracies. Economic siege, Mexico, CDMX, Islamophobia, USA.</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>I had 1000 Mbps in Mexico City, but genocidal Jews and genocidal gays sabotaged that, as they thought my high speed could hinder, expose, or endanger their crimes and conspiracies. • Economic siege Mexico CDMX Islamophobia USA • God, I hate slow internet; it's a killer of productivity.</t>
+          <t>I had 1000 Mbps in Mexico City, but genocidal Jews and genocidal gays sabotaged that, as they thought my high speed could hinder, expose, or endanger their crimes and conspiracies. • Economic siege, Mexico, CDMX, Islamophobia, USA. • God, I hate slow internet; it's a killer of productivity.</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       <c r="AB9" t="inlineStr">
         <is>
           <t>We support those who protect the homeland
-A range of financial support and banking services dedicated to frontline workers:
+A range of financial support and banking services dedicated to frontline workers
 • 10% cashback up to a maximum of 400 dirhams
 • Fixed interest rate of 6% for all new employees who transfer their salaries
 • Extension of salary transfer period
@@ -2476,18 +2476,18 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE هذا عرض صدق ؟! 
-٦% ؟! سلامات البنوك الاسلاميه المرابحه الثابته ٢.٧% ؟! 
-ولو سمحتوا علم الامارات و لبس القوات المسلحه ... ليست دعايه</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
           <t>هذا عرض صدق ؟! 
 ٦% ؟! سلامات البنوك الاسلاميه المرابحه الثابته ٢.٧% ؟! 
 ولو سمحتوا علم الامارات و لبس القوات المسلحه ... ليست دعايه</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>هذا عرض صدق ؟! 
+٦% ؟! سلامات البنوك الاسلاميه المرابحه الثابته ٢.٧% ؟! 
+ولو سمحتوا علم الامارات و لبس القوات المسلحه ... ليست دعايه</t>
+        </is>
+      </c>
       <c r="K13" t="b">
         <v>0</v>
       </c>
@@ -2536,29 +2536,19 @@
 ولو سمحتوا علم الامارات و لبس القوات المسلحه ... ليست دعايه</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>https://x.com/she7ii88/status/2046061240511082734</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE هذا عرض صدق ؟! 
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>هذا عرض صدق ؟! 
 ٦% ؟! سلامات البنوك الاسلاميه المرابحه الثابته ٢.٧% ؟! 
 ولو سمحتوا علم الامارات و لبس القوات المسلحه ... ليست دعايه</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE هذا عرض صدق ؟! 
-٦% ؟! سلامات البنوك الاسلاميه المرابحه الثابته ٢.٧% ؟! 
-ولو سمحتوا علم الامارات و لبس القوات المسلحه ... ليست دعايه</t>
-        </is>
-      </c>
       <c r="AB13" t="inlineStr">
         <is>
           <t>Is this a genuine offer?! 
-6%?! What about Islamic banks with fixed profit rates of 2.7%?! 
+6%?! What about the Islamic banks with fixed profit rates of 2.7%?! 
 And please, the UAE flag and military uniforms... this is not an advertisement.</t>
         </is>
       </c>
@@ -2590,7 +2580,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>What about Islamic banks with fixed profit rates of 2.7%?! • And please, the UAE flag and military uniforms... • Is this a genuine offer?!</t>
+          <t>What about the Islamic banks with fixed profit rates of 2.7%?! • And please, the UAE flag and military uniforms... • Is this a genuine offer?!</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -3421,7 +3411,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Investment is not complicated; it requires smart planning. With the Emirates Islamic Digital Wealth platform, you can start confidently through a seamless digital experience that is compliant with Islamic law, designed to help you:
+          <t>Investment is not complicated; it requires smart planning. With the Emirates Islamic Digital Wealth platform, you can start with confidence through a seamless digital experience that is Sharia-compliant, designed to help you:
 ✔️ Access a wide range of Sharia-compliant investment options.</t>
         </is>
       </c>
@@ -3682,6 +3672,178 @@
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
+        <is>
+          <t>🚗 Complimentary valet parking
+✈️ Complimentary airport lounge access
+💳 Metal Card with unique design
+And much more!
+📅 Offer valid till 31 May 2026
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>🚗 Complimentary valet parking
+✈️ Complimentary airport lounge access
+💳 Metal Card with unique design
+And much more!
+📅 Offer valid till 31 May 2026
+&lt;a href="https://www.emiratesislamic.ae/en/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_emarati"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 1:12 PM UTC</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="n">
+        <v>46132.55</v>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_emarati']</t>
+        </is>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>46</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>🚗 Complimentary valet parking
+✈️ Complimentary airport lounge access
+💳 Metal Card with unique design
+And much more!
+📅 Offer valid till 31 May 2026
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>🚗 Complimentary valet parking
+✈️ Complimentary airport lounge access
+💳 Metal Card with unique design
+And much more!
+📅 Offer valid till 31 May 2026
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>Complimentary valet parking  
+Complimentary airport lounge access  
+Metal Card with unique design  
+And much more!  
+Offer valid till 31 May 2026</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AE20" s="2" t="n">
+        <v>46132.71666666667</v>
+      </c>
+      <c r="AF20" s="2" t="n">
+        <v>46132</v>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>2. Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Complimentary valet parking Complimentary airport lounge access Metal Card with unique design And much more! • Offer valid till 31 May 2026</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AK20" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2046215312949879234</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215312949879234</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
         <is>
           <t>🚗 Complimentary valet parking
 ✈️ Complimentary airport lounge access
@@ -3691,73 +3853,65 @@
 https://t.co/Rcpj14D3rn</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>🚗 Complimentary valet parking
-✈️ Complimentary airport lounge access
-💳 Metal Card with unique design
-And much more!
-📅 Offer valid till 31 May 2026
-&lt;a href="https://www.emiratesislamic.ae/en/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_emarati"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp;amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
+✅ No annual membership fee
+📈 Earn up to 3.75 EI SmartMiles back per AED spend
+🍔 50% discount on talabat</t>
+        </is>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
         <is>
           <t>13h</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>Apr 20, 2026 · 1:12 PM UTC</t>
         </is>
       </c>
-      <c r="P20" s="2" t="n">
+      <c r="P21" s="2" t="n">
         <v>46132.55</v>
       </c>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_emarati']</t>
-        </is>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>46</v>
-      </c>
-      <c r="W20" t="inlineStr">
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>58</v>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>🚗 Complimentary valet parking
-✈️ Complimentary airport lounge access
-💳 Metal Card with unique design
-And much more!
-📅 Offer valid till 31 May 2026
-emiratesislamic.ae/en/offers…</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046215315273486655</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
+✅ No annual membership fee
+📈 Earn up to 3.75 EI SmartMiles back per AED spend
+🍔 50% discount on talabat</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215312949879234</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
         <is>
           <t>🚗 Complimentary valet parking
 ✈️ Complimentary airport lounge access
@@ -3767,7 +3921,7 @@
 https://t.co/Rcpj14D3rn</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>🚗 Complimentary valet parking
 ✈️ Complimentary airport lounge access
@@ -3777,7 +3931,7 @@
 https://t.co/Rcpj14D3rn</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>Complimentary valet parking  
 Complimentary airport lounge access  
@@ -3786,165 +3940,6 @@
 Offer valid till 31 May 2026</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="AE20" s="2" t="n">
-        <v>46132.71666666667</v>
-      </c>
-      <c r="AF20" s="2" t="n">
-        <v>46132</v>
-      </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Complimentary valet parking Complimentary airport lounge access Metal Card with unique design And much more! • Offer valid till 31 May 2026</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK20" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2046215312949879234</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046215312949879234</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
-✅ No annual membership fee
-📈 Earn up to 3.75 EI SmartMiles back per AED spend
-🍔 50% discount on talabat</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp;amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
-✅ No annual membership fee
-📈 Earn up to 3.75 EI SmartMiles back per AED spend
-🍔 50% discount on talabat</t>
-        </is>
-      </c>
-      <c r="K21" t="b">
-        <v>0</v>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>13h</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Apr 20, 2026 · 1:12 PM UTC</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="n">
-        <v>46132.55</v>
-      </c>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>58</v>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
-✅ No annual membership fee
-📈 Earn up to 3.75 EI SmartMiles back per AED spend
-🍔 50% discount on talabat</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
-✅ No annual membership fee
-📈 Earn up to 3.75 EI SmartMiles back per AED spend
-🍔 50% discount on talabat</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>Exclusively for Emiratis. Apply for an Emirati Credit Card and get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
-✅ No annual membership fee
-📈 Earn up to 3.75 EI SmartMiles back per AED spent
-🍔 50% discount on talabat</t>
-        </is>
-      </c>
       <c r="AC21" t="inlineStr">
         <is>
           <t>Bank</t>
@@ -3973,7 +3968,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Exclusively for Emiratis.</t>
+          <t>Complimentary valet parking Complimentary airport lounge access Metal Card with unique design And much more! • Offer valid till 31 May 2026</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -4333,12 +4328,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2046200645498130445</t>
+          <t>2046200603928338537</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046200645498130445</t>
+          <t>https://x.com/emiratesislamic/status/2046200603928338537</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4364,7 +4359,8 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>@emiratesislamic أنا اريد إنهاء الإجراء ولا اريد رد كلمات</t>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -4407,7 +4403,7 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -4420,24 +4416,17 @@
 رسالتك الخاصه.</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046200645498130445</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>@emiratesislamic أنا اريد إنهاء الإجراء ولا اريد رد كلمات</t>
-        </is>
-      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>@emiratesislamic أنا اريد إنهاء الإجراء ولا اريد رد كلمات</t>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>I want to complete the procedure and I do not want a response.</t>
+          <t>Hello dear customer. Thank you for contacting us. To protect your privacy, we would like to inform you that we have responded to you in the same message within the previous post. In order for us to serve you better, please check your private message.</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -4468,7 +4457,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>I want to complete the procedure and I do not want a response.</t>
+          <t>To protect your privacy, we would like to inform you that we have responded to you in the same message within the previous post. • In order for us to serve you better, please check your private message. • Thank you for contacting us.</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -4900,7 +4889,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Hello dear customer. Thank you for contacting us. To protect your privacy, we would like to inform you that we have replied to you in the same message within the previous post. In order for us to serve you better, please check your private message.</t>
+          <t>Hello dear customer. Thank you for contacting us. To protect your privacy, we would like to inform you that we have responded to you in the same message within the previous post. In order for us to serve you better, please check your private message.</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4931,7 +4920,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>To protect your privacy, we would like to inform you that we have replied to you in the same message within the previous post. • In order for us to serve you better, please check your private message. • Thank you for contacting us.</t>
+          <t>To protect your privacy, we would like to inform you that we have responded to you in the same message within the previous post. • In order for us to serve you better, please check your private message. • Thank you for contacting us.</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -5242,7 +5231,7 @@
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE29" s="2" t="n">
@@ -5400,7 +5389,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>✔️ Track your investments in real time ✔️ Get smart insights to guide your decisions ✔️ Enjoy a fully digital experience Start small. Think long-term. Stay disciplined. To know more, visit: emiratesislamic.ae/en/Person…</t>
+          <t>✔️ Track your investments in real time  
+✔️ Get smart insights to guide your decisions  
+✔️ Enjoy a fully digital experience  
+Start small. Think long-term. Stay disciplined.  
+To know more, visit:  
+emiratesislamic.ae/en/Person…</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -5882,7 +5876,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>What are these offers, with all due respect? Don't exploit the defenders of the homeland with such embarrassing offers.</t>
+          <t>What are these offers, with all due respect to you? Don't exploit the defenders of the homeland with such embarrassing offers.</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -5913,7 +5907,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Don't exploit the defenders of the homeland with such embarrassing offers. • What are these offers, with all due respect?</t>
+          <t>Don't exploit the defenders of the homeland with such embarrassing offers. • What are these offers, with all due respect to you?</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -6215,8 +6209,8 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Reliable delivery companies do not ask for additional payments through insecure links. 
-Don't fall into the trap. Beware of fraud. 
+          <t>Reliable delivery companies do not ask for additional payments through insecure links.
+Don't fall into the trap. Beware of fraud.
 #United_Against_Fraud with Emirates Islamic.</t>
         </is>
       </c>

--- a/check2.xlsx
+++ b/check2.xlsx
@@ -750,7 +750,7 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>I called the National Bank of Dubai to inquire about the conditions for obtaining their new product, a card in exchange for a card.
-(The idea of the product in brief: If you have a credit card from another bank, Dubai Bank gives you a credit card with the same limit.)
+(The idea of the product in brief: If you have a credit card from another bank, Dubai Bank will give you a credit card with the same limit.)
 The response was as follows: The conditions for obtaining the card are:
 - Your salary must be 10,000 riyals or more
 - Your current card must have been active for 6 months
@@ -839,6 +839,154 @@
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>العمر كله 😊😊😊❤️</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>العمر كله 😊😊😊❤️</t>
+        </is>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>['bufalasi', 'Alraeesi1969', 'EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>6h</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Apr 21, 2026 · 9:44 PM UTC</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>46133.90555555555</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V3" t="n">
+        <v>17</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>العمر كله 😊😊😊❤️</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>العمر كله 😊😊😊❤️</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>A lifetime 😊😊😊❤️</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE3" s="2" t="n">
+        <v>46134.07222222222</v>
+      </c>
+      <c r="AF3" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>A lifetime 😊😊😊❤️</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>bufalasi, Alraeesi1969, EmiratesNBD_AE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2046706457295364506</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://x.com/bufalasi/status/2046706457295364506</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://x.com/bufalasi</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>bufalasi</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bani Yas</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2019845320071372800/XlNVpcnv_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
         <is>
           <t>هواتف “القناص” و“الأنيس” والبليب…
 ليست مجرد أجهزة قديمة، بل بداية قصة الاتصال في الإمارات 🇦🇪
@@ -853,63 +1001,63 @@
 قطعة من تاريخ… صنعت حاضرنا</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>العمر كله 😊😊😊❤️</t>
-        </is>
-      </c>
-      <c r="K3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>['bufalasi', 'Alraeesi1969', 'EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>يداج انا 👴🏼 انا متقاعد وانتي عمرج سنه 😂احسبي علي راحتج</t>
+        </is>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>['DanaAbdulla2006', 'Alraeesi1969', 'EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>6h</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Apr 21, 2026 · 9:44 PM UTC</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="n">
-        <v>46133.90555555555</v>
-      </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Apr 21, 2026 · 9:43 PM UTC</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>46133.90486111111</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
         <v>2</v>
       </c>
-      <c r="V3" t="n">
-        <v>17</v>
-      </c>
-      <c r="W3" t="inlineStr">
+      <c r="V4" t="n">
+        <v>22</v>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>العمر كله 😊😊😊❤️</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>https://x.com/DanaAbdulla2006/status/2046706553022238997</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>يداج انا 👴🏼 انا متقاعد وانتي عمرج سنه 😂احسبي علي راحتج</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>https://x.com/bufalasi/status/2046706457295364506</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>هواتف “القناص” و“الأنيس” والبليب…
 ليست مجرد أجهزة قديمة، بل بداية قصة الاتصال في الإمارات 🇦🇪
@@ -924,7 +1072,7 @@
 قطعة من تاريخ… صنعت حاضرنا</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>هواتف “القناص” و“الأنيس” والبليب…
 ليست مجرد أجهزة قديمة، بل بداية قصة الاتصال في الإمارات 🇦🇪
@@ -939,7 +1087,7 @@
 قطعة من تاريخ… صنعت حاضرنا</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>The "Al-Qanass," "Al-Anis," and "Pleb" phones are not just old devices, but the beginning of the communication story in the UAE. 
 In the 1990s, "Etisalat" led this phase, offering a new generation of communication that changed people's lives.
@@ -948,154 +1096,6 @@
 A piece of history that shaped our present.</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE3" s="2" t="n">
-        <v>46134.07222222222</v>
-      </c>
-      <c r="AF3" s="2" t="n">
-        <v>46134</v>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>The Pleb (Pager) was the fastest way to reach someone, a small device that received numbers and displayed the caller's number so you could call them back from the nearest phone. • The "Al-Qanass," "Al-Anis," and "Pleb" phones are not just old devices, but the beginning of the communication story in the UAE. • In the 1990s, "Etisalat" led this phase, offering a new generation of communication that changed people's lives.</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>bufalasi, Alraeesi1969, EmiratesNBD_AE</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2046706457295364506</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://x.com/bufalasi/status/2046706457295364506</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>https://x.com/bufalasi</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>bufalasi</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Bani Yas</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2019845320071372800/XlNVpcnv_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>يداج انا 👴🏼 انا متقاعد وانتي عمرج سنه 😂احسبي علي راحتج</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>يداج انا 👴🏼 انا متقاعد وانتي عمرج سنه 😂احسبي علي راحتج</t>
-        </is>
-      </c>
-      <c r="K4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>['DanaAbdulla2006', 'Alraeesi1969', 'EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>6h</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Apr 21, 2026 · 9:43 PM UTC</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="n">
-        <v>46133.90486111111</v>
-      </c>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2</v>
-      </c>
-      <c r="V4" t="n">
-        <v>22</v>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>يداج انا 👴🏼 انا متقاعد وانتي عمرج سنه 😂احسبي علي راحتج</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>يداج انا 👴🏼 انا متقاعد وانتي عمرج سنه 😂احسبي علي راحتج</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>I am retired and you are only one year old. Take care of yourself.</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
           <t>Cust</t>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>I am retired and you are only one year old.</t>
+          <t>The Pleb (Pager) was the fastest way to reach someone, a small device that received numbers and displayed the caller's number so you could call them back from the nearest phone. • The "Al-Qanass," "Al-Anis," and "Pleb" phones are not just old devices, but the beginning of the communication story in the UAE. • In the 1990s, "Etisalat" led this phase, offering a new generation of communication that changed people's lives.</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>The device was reserved at the telecommunications company and required a connection, and the price reached 15,000. I remember I went to Abdul Rahim at the telecommunications company and took my father's device that we had reserved. After the connection, I received it, and the buyer was with me, but because he knows me, I signed the transfer request. I was still there and received 15,000 and went to Emirates NBD Bank, Al Ras branch, to deposit the amount.</t>
+          <t>The device was reserved at the telecommunications company and required a connection, and the price reached 15,000. I remember I went to Abdul Rahim at the telecommunications company and took my father's device that we had reserved. After the connection, I received it, and the buyer was with me, but because he knows me, I signed the transfer request while I was still there. I received 15,000 and went to Emirates NBD Bank, Al Ras branch, to deposit the amount.</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>The device was reserved at the telecommunications company and required a connection, and the price reached 15,000. • I was still there and received 15,000 and went to Emirates NBD Bank, Al Ras branch, to deposit the amount. • I remember I went to Abdul Rahim at the telecommunications company and took my father's device that we had reserved.</t>
+          <t>The device was reserved at the telecommunications company and required a connection, and the price reached 15,000. • I received 15,000 and went to Emirates NBD Bank, Al Ras branch, to deposit the amount. • I remember I went to Abdul Rahim at the telecommunications company and took my father's device that we had reserved.</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1577,10 +1577,10 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>We support those who protect the homeland
-A range of financial support and banking services dedicated to frontline workers:
+A range of financial support and banking services dedicated to frontline workers
 • 10% cashback up to a maximum of 400 dirhams
-• A fixed interest rate of 6% for all new employees who transfer their salaries
-• Extension of the salary transfer period
+• Fixed interest rate of 6% for all new employees who transfer their salaries
+• Extension of salary transfer period
 • Waiver of minimum balance fees for customers whose salaries are not transferred
 • Loan fee waivers with priority processing of applications
 The offer is valid until June 30, 2026.
@@ -1761,7 +1761,7 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>Don't travel on these 320 aircraft and the like. Travel on the 380, especially with Emirates Airlines. 
-You won't regret it, my brother; the service is unmatched. We really canceled your flight, and you just have to deal with it. Sorry, the pilot is asleep, and we forgot your bags in America; there's nothing we can do.
+You won't regret it, my brother; the service is unmatched. We canceled your flight, and you just have to deal with it. Sorry, the pilot is asleep; we forgot your bags in America, there's nothing we can do.
 Which bank offers the best Emirates miles?</t>
         </is>
       </c>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Travel on the 380, especially with Emirates Airlines. • Don't travel on these 320 aircraft and the like. • Sorry, the pilot is asleep, and we forgot your bags in America; there's nothing we can do.</t>
+          <t>Travel on the 380, especially with Emirates Airlines. • Don't travel on these 320 aircraft and the like. • Sorry, the pilot is asleep; we forgot your bags in America, there's nothing we can do.</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -2530,8 +2530,8 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Tourism in Dubai ready to boom soon 
-#dubaï #unitedarabemirates🇦🇪 #uae🇦🇪 #tourism https://t.co/RgWWZHppDl</t>
+          <t>Dubai’s real estate market is entering a new era. Dubai Holding and EmiratesNBD have joined forces to transform how off-plan properties are financed. Now, buyers don’t need to wait until handover.
+They can access mortgage solutions right from the start.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2583,26 +2583,17 @@
 They can access mortgage solutions right from the start.</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>https://x.com/Soberrealestate/status/2046559580919144593</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Tourism in Dubai ready to boom soon 
-#dubaï #unitedarabemirates🇦🇪 #uae🇦🇪 #tourism https://t.co/RgWWZHppDl</t>
-        </is>
-      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Tourism in Dubai ready to boom soon 
-#dubaï #unitedarabemirates🇦🇪 #uae🇦🇪 #tourism https://t.co/RgWWZHppDl</t>
+          <t>Dubai’s real estate market is entering a new era. Dubai Holding and EmiratesNBD have joined forces to transform how off-plan properties are financed. Now, buyers don’t need to wait until handover.
+They can access mortgage solutions right from the start.</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Tourism in Dubai is set to boom soon.</t>
+          <t>Dubai's real estate market is entering a new era. Dubai Holding and EmiratesNBD have joined forces to transform how off-plan properties are financed. Now, buyers don’t need to wait until handover. They can access mortgage solutions right from the start.</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2612,7 +2603,7 @@
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE13" s="2" t="n">
@@ -2633,7 +2624,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Tourism in Dubai is set to boom soon.</t>
+          <t>Dubai Holding and EmiratesNBD have joined forces to transform how off-plan properties are financed. • Dubai's real estate market is entering a new era. • Now, buyers don’t need to wait until handover.</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2783,7 +2774,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>For the first time, buyers can secure mortgage approval early on off-plan properties through a powerful collaboration between Dubai Holding Real Estate and Emirates NBD. No more waiting until handover. No more uncertainty. With projects from Meraas, Nakheel, and Dubai Properties included, this is a big shift in how off-plan works in Dubai. Call / WhatsApp: +971523717167.</t>
+          <t>For the first time, buyers can secure mortgage approval early on off-plan properties through a powerful collaboration between Dubai Holding Real Estate and Emirates NBD. No more waiting until handover. No more uncertainty. With projects from Meraas, Nakheel, and Dubai Properties included, this is a big shift in how off-plan works in Dubai.</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2814,7 +2805,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>For the first time, buyers can secure mortgage approval early on off-plan properties through a powerful collaboration between Dubai Holding Real Estate and Emirates NBD. • Call / WhatsApp: +971523717167. • With projects from Meraas, Nakheel, and Dubai Properties included, this is a big shift in how off-plan works in Dubai.</t>
+          <t>For the first time, buyers can secure mortgage approval early on off-plan properties through a powerful collaboration between Dubai Holding Real Estate and Emirates NBD. • With projects from Meraas, Nakheel, and Dubai Properties included, this is a big shift in how off-plan works in Dubai. • No more waiting until handover.</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2872,7 +2863,7 @@
 Emirates NBD just dropped 0% interest + zero fees 💳
 This is your chance to reset your finances
 DM “PLAN” to optimize your debt
-#DubaiMoney #UAETwitter #FinanceTips #DebtFreeJourney #SmartMoney #DubaiLife https://t.co/PXNM3PdaUn</t>
+#DubaiMoney #UAETwitter #FinanceTips #DebtFreeJourney #SmartMoney #DubaiLife</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2934,27 +2925,15 @@
 #DubaiMoney #UAETwitter #FinanceTips #DebtFreeJourney #SmartMoney #DubaiLife</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>https://x.com/Blackstone_UAE/status/2046488790806806983</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr">
         <is>
           <t>Paying high interest? Stop.
 Emirates NBD just dropped 0% interest + zero fees 💳
 This is your chance to reset your finances
 DM “PLAN” to optimize your debt
-#DubaiMoney #UAETwitter #FinanceTips #DebtFreeJourney #SmartMoney #DubaiLife https://t.co/PXNM3PdaUn</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Paying high interest? Stop.
-Emirates NBD just dropped 0% interest + zero fees 💳
-This is your chance to reset your finances
-DM “PLAN” to optimize your debt
-#DubaiMoney #UAETwitter #FinanceTips #DebtFreeJourney #SmartMoney #DubaiLife https://t.co/PXNM3PdaUn</t>
+#DubaiMoney #UAETwitter #FinanceTips #DebtFreeJourney #SmartMoney #DubaiLife</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -3381,66 +3360,66 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
+          <t>فخرٌ لا يُحكى… بل يُشعَر. 🇦🇪
+تماشياً مع رؤية صاحب السمو الشيخ محمد بن راشد آل مكتوم، نرفع رايتنا عالياً، ونحتفي بوطنٍ توحّد على القيم، وتماسك بالقوة، وازدهر بروحٍ لا تعرف المستحيل.
+#فخورين_بالإمارات https://t.co/gqaQU5Dzuz</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>A pride beyond words… it’s felt. 🇦🇪
+Inspired by the vision of His Highness Sheikh Mohammed bin Rashid Al Maktoum, we raise our flag high, celebrating a nation united by values, strengthened by resilience, and driven by a spirit that knows no limits.
+&lt;a href="/search?f=tweets&amp;amp;q=%23ProudOfUAE"&gt;#ProudOfUAE&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Apr 21, 2026 · 7:42 AM UTC</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="n">
+        <v>46133.32083333333</v>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23ProudOfUAE', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic']</t>
+        </is>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>70</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
           <t>A pride beyond words… it’s felt. 🇦🇪
 Inspired by the vision of His Highness Sheikh Mohammed bin Rashid Al Maktoum, we raise our flag high, celebrating a nation united by values, strengthened by resilience, and driven by a spirit that knows no limits.
 #ProudOfUAE #EmiratesIslamic</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>A pride beyond words… it’s felt. 🇦🇪
-Inspired by the vision of His Highness Sheikh Mohammed bin Rashid Al Maktoum, we raise our flag high, celebrating a nation united by values, strengthened by resilience, and driven by a spirit that knows no limits.
-&lt;a href="/search?f=tweets&amp;amp;q=%23ProudOfUAE"&gt;#ProudOfUAE&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Apr 21, 2026 · 7:42 AM UTC</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="n">
-        <v>46133.32083333333</v>
-      </c>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23ProudOfUAE', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic']</t>
-        </is>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>70</v>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>A pride beyond words… it’s felt. 🇦🇪
-Inspired by the vision of His Highness Sheikh Mohammed bin Rashid Al Maktoum, we raise our flag high, celebrating a nation united by values, strengthened by resilience, and driven by a spirit that knows no limits.
-#ProudOfUAE #EmiratesIslamic</t>
-        </is>
-      </c>
       <c r="Y18" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046494860136346080</t>
@@ -3448,21 +3427,21 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>A pride beyond words… it’s felt. 🇦🇪
-Inspired by the vision of His Highness Sheikh Mohammed bin Rashid Al Maktoum, we raise our flag high, celebrating a nation united by values, strengthened by resilience, and driven by a spirit that knows no limits.
-#ProudOfUAE #EmiratesIslamic</t>
+          <t>فخرٌ لا يُحكى… بل يُشعَر. 🇦🇪
+تماشياً مع رؤية صاحب السمو الشيخ محمد بن راشد آل مكتوم، نرفع رايتنا عالياً، ونحتفي بوطنٍ توحّد على القيم، وتماسك بالقوة، وازدهر بروحٍ لا تعرف المستحيل.
+#فخورين_بالإمارات https://t.co/gqaQU5Dzuz</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>A pride beyond words… it’s felt. 🇦🇪
-Inspired by the vision of His Highness Sheikh Mohammed bin Rashid Al Maktoum, we raise our flag high, celebrating a nation united by values, strengthened by resilience, and driven by a spirit that knows no limits.
-#ProudOfUAE #EmiratesIslamic</t>
+          <t>فخرٌ لا يُحكى… بل يُشعَر. 🇦🇪
+تماشياً مع رؤية صاحب السمو الشيخ محمد بن راشد آل مكتوم، نرفع رايتنا عالياً، ونحتفي بوطنٍ توحّد على القيم، وتماسك بالقوة، وازدهر بروحٍ لا تعرف المستحيل.
+#فخورين_بالإمارات https://t.co/gqaQU5Dzuz</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>A pride beyond words… it’s felt. Inspired by the vision of His Highness Sheikh Mohammed bin Rashid Al Maktoum, we raise our flag high, celebrating a nation united by values, strengthened by resilience, and driven by a spirit that knows no limits.</t>
+          <t>A pride that cannot be spoken of... but felt. In line with the vision of His Highness Sheikh Mohammed bin Rashid Al Maktoum, we raise our flag high and celebrate a nation united by values, strengthened by resilience, and flourishing with a spirit that knows no impossibilities. #Proud_of_the_Emirates</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3493,7 +3472,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>A pride beyond words… it’s felt.</t>
+          <t>A pride that cannot be spoken of...</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -4007,7 +3986,7 @@
 The winner will be announced on May 5, 2026
 Please visit https://t.co/4RkTsyGuDX for terms and conditions
 Participation is limited to citizens of the United Arab Emirates or residents of the country who hold a valid ID card.
-#ADIB_Competition</t>
+#AbuDhabiIslamicBank_Competition</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -5054,7 +5033,7 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>@m_azeemq Hi Muhammad, we are extremely sorry for the delay, and we have sent followup email to our team to contact you as soon as possible with an update. And we have already replied you via other social media channel. Thanks</t>
+          <t>I am in followup with KSA team but there is no action taken from concern department till now and case is still unresolved/clarified. Even phone and Mails dont have any effect. I hope my escalated issue can be clarified, just want to Finish and Close the service from ENBD.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -5108,24 +5087,16 @@
           <t>I am in followup with KSA team but there is no action taken from concern department till now and case is still unresolved/clarified. Even phone and Mails dont have any effect. I hope my escalated issue can be clarified, just want to Finish and Close the service from ENBD.</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>https://x.com/m_azeemq/status/2046489809842065416</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>@m_azeemq Hi Muhammad, we are extremely sorry for the delay, and we have sent followup email to our team to contact you as soon as possible with an update. And we have already replied you via other social media channel. Thanks</t>
-        </is>
-      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>@m_azeemq Hi Muhammad, we are extremely sorry for the delay, and we have sent followup email to our team to contact you as soon as possible with an update. And we have already replied you via other social media channel. Thanks</t>
+          <t>I am in followup with KSA team but there is no action taken from concern department till now and case is still unresolved/clarified. Even phone and Mails dont have any effect. I hope my escalated issue can be clarified, just want to Finish and Close the service from ENBD.</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Hi Muhammad, we are extremely sorry for the delay, and we have sent a follow-up email to our team to contact you as soon as possible with an update. We have already replied to you via another social media channel. Thanks.</t>
+          <t>I am following up with the KSA team, but there has been no action taken by the concerned department so far, and the case is still unresolved. Even phone calls and emails have had no effect. I hope my escalated issue can be clarified; I just want to finish and close the service with ENBD.</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -5156,7 +5127,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Hi Muhammad, we are extremely sorry for the delay, and we have sent a follow-up email to our team to contact you as soon as possible with an update. • We have already replied to you via another social media channel.</t>
+          <t>I am following up with the KSA team, but there has been no action taken by the concerned department so far, and the case is still unresolved. • I hope my escalated issue can be clarified; I just want to finish and close the service with ENBD. • Even phone calls and emails have had no effect.</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -5301,7 +5272,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Emirates NBD sent me an account statement; they owe me 200,000 AED, which they won't pay. Lebanese banks stole my money. Emirates and Barack Obama owe me two years' pay. I am just too tired to give up.</t>
+          <t>Emirates NBD sent me an account statement; they owe me 200,000 AED which they won't pay. Lebanese banks stole my money. Emirates and Barack Obama owe me two years' pay. I am just too tired to give up.</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -5332,7 +5303,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Emirates NBD sent me an account statement; they owe me 200,000 AED, which they won't pay. • Emirates and Barack Obama owe me two years' pay. • Lebanese banks stole my money.</t>
+          <t>Emirates NBD sent me an account statement; they owe me 200,000 AED which they won't pay. • Emirates and Barack Obama owe me two years' pay. • Lebanese banks stole my money.</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">

--- a/check2.xlsx
+++ b/check2.xlsx
@@ -778,17 +778,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Code coupon special  
-e1HcWgcAZOk  
-Noon  
-⊵CBB54⊴  
-Path and body  
-Af8p⊴  
-Beloved tablecloth  
-⊵sm29⊴  
-We walk  
-⊵BLK13⊴  
-^^^^  
+          <t>Code coupon: e1HcWgcAZOk
+Non: CBB54
+Path and body: Af8p
+Beloved linens: sm29
+We walk: BLK13
+^^^^
 ENbd</t>
         </is>
       </c>
@@ -820,7 +815,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Code coupon special e1HcWgcAZOk Noon ⊵CBB54⊴ Path and body Af8p⊴ Beloved tablecloth ⊵sm29⊴ We walk ⊵BLK13⊴ ^^^^ ENbd</t>
+          <t>Code coupon: e1HcWgcAZOk Non: CBB54 Path and body: Af8p Beloved linens: sm29 We walk: BLK13 ^^^^ ENbd</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -1108,7 +1103,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Your wedding night, just as you wish and more 💍✨  
+          <t>On your wedding night, just as you wish and more 💍✨  
 Apply for personal financing with a competitive profit margin from #Emirates_NBD 💙  
 For details: https://t.co/5oaojOqJ8v https://t.co/6LHBU3Yt0q</t>
         </is>
@@ -1141,7 +1136,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Your wedding night, just as you wish and more 💍✨ Apply for personal financing with a competitive profit margin from #Emirates_NBD 💙 For details: https://t.co/5oaojOqJ8v https://t.co/6LHBU3Yt0q</t>
+          <t>On your wedding night, just as you wish and more 💍✨ Apply for personal financing with a competitive profit margin from #Emirates_NBD 💙 For details: https://t.co/5oaojOqJ8v https://t.co/6LHBU3Yt0q</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1942,7 +1937,7 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE9" s="2" t="n">
@@ -2440,7 +2435,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>FAB, Emirates NBD, and ADCB have posted combined net profits of $4 billion for Q1 2026, reaffirming the strength of the UAE banking sector despite ongoing regional challenges. Here’s how the nation’s top three banks managed a turbulent quarter.</t>
+          <t>FAB, Emirates NBD, and ADCB have posted combined Q1 2026 net profits of $4 billion, reaffirming the UAE banking sector’s strength despite persistent regional headwinds. Here’s how the nation’s top 3 banks navigated a turbulent quarter.</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2471,7 +2466,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>FAB, Emirates NBD, and ADCB have posted combined net profits of $4 billion for Q1 2026, reaffirming the strength of the UAE banking sector despite ongoing regional challenges. • Here’s how the nation’s top three banks managed a turbulent quarter.</t>
+          <t>FAB, Emirates NBD, and ADCB have posted combined Q1 2026 net profits of $4 billion, reaffirming the UAE banking sector’s strength despite persistent regional headwinds. • Here’s how the nation’s top 3 banks navigated a turbulent quarter.</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2614,10 +2609,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>“If your money isn’t growing, you’re losing purchasing power.” 💡
-In Dubai, there is no income tax, no capital gains tax, and active capital. Yields range from 6% to 12%, with off-plan appreciation between 15% and 40%.
-Global capital asks, “Where does my money perform better?” The answer: Dubai. 
-#InvestInDubai</t>
+          <t>If your money isn’t growing, you’re losing purchasing power. In Dubai, there is no income tax, no capital gains tax, and active capital. Yields range from 6% to 12%, with off-plan appreciation between 15% and 40%. Global capital asks, “Where does my money perform better?” The answer: Dubai.</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2648,7 +2640,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>“If your money isn’t growing, you’re losing purchasing power.” 💡 In Dubai, there is no income tax, no capital gains tax, and active capital. • Yields range from 6% to 12%, with off-plan appreciation between 15% and 40%. • Global capital asks, “Where does my money perform better?” The answer: Dubai.</t>
+          <t>Yields range from 6% to 12%, with off-plan appreciation between 15% and 40%. • In Dubai, there is no income tax, no capital gains tax, and active capital. • Global capital asks, “Where does my money perform better?” The answer: Dubai.</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -3092,7 +3084,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>It simplifies your tasks and accomplishes your needs with the push of a button. Carry out your daily banking operations easily and securely with the ENBD X app.</t>
+          <t>It simplifies your tasks and accomplishes them with the push of a button. Execute your daily banking operations easily and securely with the ENBD X app.</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -3123,7 +3115,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Carry out your daily banking operations easily and securely with the ENBD X app. • It simplifies your tasks and accomplishes your needs with the push of a button.</t>
+          <t>Execute your daily banking operations easily and securely with the ENBD X app. • It simplifies your tasks and accomplishes them with the push of a button.</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -3697,16 +3689,8 @@
           <t>@EmiratesNBD_AE أفضل ويتفوق رغماً عن الأزمة 👏🏻</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>https://x.com/abd11ulla/status/2047265666320011311</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE أفضل ويتفوق رغماً عن الأزمة 👏🏻</t>
-        </is>
-      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE أفضل ويتفوق رغماً عن الأزمة 👏🏻</t>
@@ -3799,7 +3783,7 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>SAQL: Exchange Ticker has secured Public Investment Fund (PIF) seed funding of $100m listed on Deutsche Borse &amp;amp; London Stock Exchange.. https://t.co/3dUD3f2sht</t>
+          <t>SABIC Agri-Nutrients Q1 2026 reports 24% YoY &amp;amp; QoQ growth in profitability attributed to higher selling price despite reduced quantities.. https://t.co/XDaNdBks8o</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3864,17 +3848,17 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>SAQL: Exchange Ticker has secured Public Investment Fund (PIF) seed funding of $100m listed on Deutsche Borse &amp;amp; London Stock Exchange.. https://t.co/3dUD3f2sht</t>
+          <t>SABIC Agri-Nutrients Q1 2026 reports 24% YoY &amp;amp; QoQ growth in profitability attributed to higher selling price despite reduced quantities.. https://t.co/XDaNdBks8o</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>SAQL: Exchange Ticker has secured Public Investment Fund (PIF) seed funding of $100m listed on Deutsche Borse &amp;amp; London Stock Exchange.. https://t.co/3dUD3f2sht</t>
+          <t>SABIC Agri-Nutrients Q1 2026 reports 24% YoY &amp;amp; QoQ growth in profitability attributed to higher selling price despite reduced quantities.. https://t.co/XDaNdBks8o</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>SAQL: Exchange Ticker has secured $100 million in seed funding from the Public Investment Fund (PIF), listed on Deutsche Börse and the London Stock Exchange.</t>
+          <t>SABIC Agri-Nutrients Q1 2026 reports 24% year-over-year and quarter-over-quarter growth in profitability attributed to higher selling prices despite reduced quantities.</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3905,7 +3889,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>SAQL: Exchange Ticker has secured $100 million in seed funding from the Public Investment Fund (PIF), listed on Deutsche Börse and the London Stock Exchange.</t>
+          <t>SABIC Agri-Nutrients Q1 2026 reports 24% year-over-year and quarter-over-quarter growth in profitability attributed to higher selling prices despite reduced quantities.</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -4107,7 +4091,8 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Speedinvest launches its first flagship fund for early-growth startups across the Middle East and Africa, backed by Mubadala Investment Company, Qatar Investment Authority, and European Investment Bank, expanding its regional investment strategy.#Speedinvest #MiddleEast #Africa https://t.co/2PFCFcHWJE</t>
+          <t>Emirates NBD, Dubai’s largest bank, reported a profit before tax of Dh8.2 billion for Q1 2026, up 6% year-on-year, supported by strong balance sheet growth, resilient margins, and record non-funded income.
+#EmiratesNBD #Dubai #Banking #Finance #UAE #Earnings #Q12026</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -4163,24 +4148,17 @@
 #EmiratesNBD #Dubai #Banking #Finance #UAE #Earnings #Q12026</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>https://x.com/ForumRemittance/status/2047260484458467333</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>Speedinvest launches its first flagship fund for early-growth startups across the Middle East and Africa, backed by Mubadala Investment Company, Qatar Investment Authority, and European Investment Bank, expanding its regional investment strategy.#Speedinvest #MiddleEast #Africa https://t.co/2PFCFcHWJE</t>
-        </is>
-      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>Speedinvest launches its first flagship fund for early-growth startups across the Middle East and Africa, backed by Mubadala Investment Company, Qatar Investment Authority, and European Investment Bank, expanding its regional investment strategy.#Speedinvest #MiddleEast #Africa https://t.co/2PFCFcHWJE</t>
+          <t>Emirates NBD, Dubai’s largest bank, reported a profit before tax of Dh8.2 billion for Q1 2026, up 6% year-on-year, supported by strong balance sheet growth, resilient margins, and record non-funded income.
+#EmiratesNBD #Dubai #Banking #Finance #UAE #Earnings #Q12026</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Speedinvest launches its first flagship fund for early-growth startups across the Middle East and Africa, backed by Mubadala Investment Company, Qatar Investment Authority, and European Investment Bank, expanding its regional investment strategy.</t>
+          <t>Emirates NBD, Dubai’s largest bank, reported a profit before tax of Dh8.2 billion for Q1 2026, up 6% year-on-year, supported by strong balance sheet growth, resilient margins, and record non-funded income.</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -4190,7 +4168,7 @@
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE23" s="2" t="n">
@@ -4211,7 +4189,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Speedinvest launches its first flagship fund for early-growth startups across the Middle East and Africa, backed by Muba…</t>
+          <t>Emirates NBD, Dubai’s largest bank, reported a profit before tax of Dh8.2 billion for Q1 2026, up 6% year-on-year, suppo…</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -4841,7 +4819,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>While Gulf economies struggle with issues in Hormuz, First Abu Dhabi Bank and Emirates NBD report strong Q1 earnings amid regional war uncertainty. Iran's conflict has closed the Strait of Hormuz, reduced Gulf exports, increased energy prices, and affected jet fuel in China, India, and South Korea; yet UAE lenders are thriving. Resilient banks indicate UAE stability as a 30-nation initiative led by the UK and France aims to reopen the strait, but the IEA warns of the biggest energy threat in history if tensions continue.</t>
+          <t>While Gulf economies struggle with issues in Hormuz, First Abu Dhabi Bank and Emirates NBD report strong Q1 earnings amid regional war uncertainty. Iran's conflict has closed the Strait of Hormuz, reduced Gulf exports, increased energy prices, and affected jet fuel in China, India, and South Korea; yet UAE lenders are thriving. Resilient banks indicate UAE stability as a 30-nation effort led by the UK and France aims to reopen the strait, but the IEA warns of the biggest energy threat in history if tensions continue.</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4872,7 +4850,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Iran's conflict has closed the Strait of Hormuz, reduced Gulf exports, increased energy prices, and affected jet fuel in China, India, and South Korea; yet UAE lenders are thriving. • Resilient banks indicate UAE stability as a 30-nation initiative led by the UK and France aims to reopen the strait, but the IEA warns of the biggest energy threat in history if tensions continue. • While Gulf economies struggle with issues in Hormuz, First Abu Dhabi Bank and Emirates NBD report strong Q1 earnings amid regional war uncertainty.</t>
+          <t>Iran's conflict has closed the Strait of Hormuz, reduced Gulf exports, increased energy prices, and affected jet fuel in China, India, and South Korea; yet UAE lenders are thriving. • Resilient banks indicate UAE stability as a 30-nation effort led by the UK and France aims to reopen the strait, but the IEA warns of the biggest energy threat in history if tensions continue. • While Gulf economies struggle with issues in Hormuz, First Abu Dhabi Bank and Emirates NBD report strong Q1 earnings amid regional war uncertainty.</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -6691,6 +6669,65 @@
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
+        <is>
+          <t>Emirates NBD reports Dh8.2 billion profit before tax in Q1 2026, up 6% YoY 
+Total income increased 21% year-on-year and 13% quarter-on-quarter to Dh14.4 billion, supported by strong asset growth and a sharp rise in non-funded income, which surged 42% year-on-year to Dh4.9 billion.
+Net profit stood at Dh6.4 billion, up 27% quarter-on-quarter but down 3% year-on-year, reflecting overall solid performance during the period.
+Read more: https://t.co/5WKoAM1fAJ 
+#AletihadNewsCenter #UAE #banking  @ENBDdeals</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Emirates NBD reports Dh8.2 billion profit before tax in Q1 2026, up 6% YoY 
+Total income increased 21% year-on-year and 13% quarter-on-quarter to Dh14.4 billion, supported by strong asset growth and a sharp rise in non-funded income, which surged 42% year-on-year to Dh4.9 billion.
+Net profit stood at Dh6.4 billion, up 27% quarter-on-quarter but down 3% year-on-year, reflecting overall solid performance during the period.
+Read more: &lt;a href="http://link.aletihad.ae/JYOQ"&gt;link.aletihad.ae/JYOQ&lt;/a&gt; 
+&lt;a href="/search?f=tweets&amp;amp;q=%23AletihadNewsCenter"&gt;#AletihadNewsCenter&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23banking"&gt;#banking&lt;/a&gt;  &lt;a href="/ENBDdeals" title="Emirates NBD Deals"&gt;@ENBDdeals&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K39" t="b">
+        <v>0</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Apr 23, 2026 · 6:16 AM UTC</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="n">
+        <v>46135.26111111111</v>
+      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>['http://link.aletihad.ae/JYOQ', 'https://x.com/search?f=tweets&amp;q=%23AletihadNewsCenter', 'https://x.com/search?f=tweets&amp;q=%23UAE', 'https://x.com/search?f=tweets&amp;q=%23banking', 'https://x.com/ENBDdeals']</t>
+        </is>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>30</v>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
         <is>
           <t>Emirates NBD reports Dh8.2 billion profit before tax in Q1 2026, up 6% YoY 
 Total income increased 21% year-on-year and 13% quarter-on-quarter to Dh14.4 billion, supported by strong asset growth and a sharp rise in non-funded income, which surged 42% year-on-year to Dh4.9 billion.
@@ -6699,80 +6736,33 @@
 #AletihadNewsCenter #UAE #banking  @ENBDdeals</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>https://x.com/AletihadEn/status/2047197832806072615</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
         <is>
           <t>Emirates NBD reports Dh8.2 billion profit before tax in Q1 2026, up 6% YoY 
 Total income increased 21% year-on-year and 13% quarter-on-quarter to Dh14.4 billion, supported by strong asset growth and a sharp rise in non-funded income, which surged 42% year-on-year to Dh4.9 billion.
 Net profit stood at Dh6.4 billion, up 27% quarter-on-quarter but down 3% year-on-year, reflecting overall solid performance during the period.
-Read more: &lt;a href="http://link.aletihad.ae/JYOQ"&gt;link.aletihad.ae/JYOQ&lt;/a&gt; 
-&lt;a href="/search?f=tweets&amp;amp;q=%23AletihadNewsCenter"&gt;#AletihadNewsCenter&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23banking"&gt;#banking&lt;/a&gt;  &lt;a href="/ENBDdeals" title="Emirates NBD Deals"&gt;@ENBDdeals&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K39" t="b">
-        <v>0</v>
-      </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>Apr 23, 2026 · 6:16 AM UTC</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="n">
-        <v>46135.26111111111</v>
-      </c>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>['http://link.aletihad.ae/JYOQ', 'https://x.com/search?f=tweets&amp;q=%23AletihadNewsCenter', 'https://x.com/search?f=tweets&amp;q=%23UAE', 'https://x.com/search?f=tweets&amp;q=%23banking', 'https://x.com/ENBDdeals']</t>
-        </is>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>30</v>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
+Read more: https://t.co/5WKoAM1fAJ 
+#AletihadNewsCenter #UAE #banking  @ENBDdeals</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
         <is>
           <t>Emirates NBD reports Dh8.2 billion profit before tax in Q1 2026, up 6% YoY 
 Total income increased 21% year-on-year and 13% quarter-on-quarter to Dh14.4 billion, supported by strong asset growth and a sharp rise in non-funded income, which surged 42% year-on-year to Dh4.9 billion.
 Net profit stood at Dh6.4 billion, up 27% quarter-on-quarter but down 3% year-on-year, reflecting overall solid performance during the period.
-Read more: link.aletihad.ae/JYOQ 
+Read more: https://t.co/5WKoAM1fAJ 
 #AletihadNewsCenter #UAE #banking  @ENBDdeals</t>
         </is>
       </c>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>Emirates NBD reports Dh8.2 billion profit before tax in Q1 2026, up 6% YoY 
-Total income increased 21% year-on-year and 13% quarter-on-quarter to Dh14.4 billion, supported by strong asset growth and a sharp rise in non-funded income, which surged 42% year-on-year to Dh4.9 billion.
-Net profit stood at Dh6.4 billion, up 27% quarter-on-quarter but down 3% year-on-year, reflecting overall solid performance during the period.
-Read more: link.aletihad.ae/JYOQ 
-#AletihadNewsCenter #UAE #banking  @ENBDdeals</t>
-        </is>
-      </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Emirates NBD reports a profit before tax of Dh8.2 billion in Q1 2026, up 6% year-on-year. 
-Total income increased by 21% year-on-year and 13% quarter-on-quarter to Dh14.4 billion, supported by strong asset growth and a sharp rise in non-funded income, which surged by 42% year-on-year to Dh4.9 billion.
+          <t>Emirates NBD reports a profit before tax of Dh8.2 billion in Q1 2026, up 6% year-on-year.
+Total income increased by 21% year-on-year and 13% quarter-on-quarter to Dh14.4 billion, supported by strong asset growth and a sharp rise in non-funded income, which surged 42% year-on-year to Dh4.9 billion.
 Net profit stood at Dh6.4 billion, up 27% quarter-on-quarter but down 3% year-on-year, reflecting an overall solid performance during the period.</t>
         </is>
       </c>
@@ -7202,7 +7192,7 @@
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>The National Bank of Ras Al Khaimah (RAKBANK) posted double-digit growth in earnings for the first quarter of the year, supported by a strategic asset sale and a robust balance sheet https://t.co/MKDO38bCYG</t>
+          <t>#EmiratesNBD, the region’s fourth largest lender by market capitalisation, posted a 3% year-on-year (YoY) rise in first quarter 2026 net profit to AED 6.4 billion ($1.74 billion) lseg.group/4e54WQT</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -7256,24 +7246,16 @@
           <t>#EmiratesNBD, the region’s fourth largest lender by market capitalisation, posted a 3% year-on-year (YoY) rise in first quarter 2026 net profit to AED 6.4 billion ($1.74 billion) lseg.group/4e54WQT</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>https://x.com/Zawya/status/2047185349089087886</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>The National Bank of Ras Al Khaimah (RAKBANK) posted double-digit growth in earnings for the first quarter of the year, supported by a strategic asset sale and a robust balance sheet https://t.co/MKDO38bCYG</t>
-        </is>
-      </c>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>The National Bank of Ras Al Khaimah (RAKBANK) posted double-digit growth in earnings for the first quarter of the year, supported by a strategic asset sale and a robust balance sheet https://t.co/MKDO38bCYG</t>
+          <t>#EmiratesNBD, the region’s fourth largest lender by market capitalisation, posted a 3% year-on-year (YoY) rise in first quarter 2026 net profit to AED 6.4 billion ($1.74 billion) lseg.group/4e54WQT</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>The National Bank of Ras Al Khaimah (RAKBANK) posted double-digit growth in earnings for the first quarter of the year, supported by a strategic asset sale and a robust balance sheet.</t>
+          <t>Emirates NBD, the region's fourth largest lender by market capitalization, posted a 3% year-on-year (YoY) rise in first quarter 2026 net profit to AED 6.4 billion ($1.74 billion).</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -7283,7 +7265,7 @@
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE42" s="2" t="n">
@@ -7304,7 +7286,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>The National Bank of Ras Al Khaimah (RAKBANK) posted double-digit growth in earnings for the first quarter of the year, supported by a strategic asset sale and a robust balance sheet.</t>
+          <t>Emirates NBD, the region's fourth largest lender by market capitalization, posted a 3% year-on-year (YoY) rise in first quarter 2026 net profit to AED 6.4 billion ($1.74 billion).</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
@@ -7743,7 +7725,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>Masha'Allah, the best bank in the UAE, ENBD.</t>
+          <t>Mashallah, the best bank in the UAE ENBD.</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -7774,7 +7756,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Masha'Allah, the best bank in the UAE, ENBD.</t>
+          <t>Mashallah, the best bank in the UAE ENBD.</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
@@ -8457,7 +8439,7 @@
       <c r="I50" t="inlineStr">
         <is>
           <t>Starting early and staying consistent can help your money grow over time. Small steps today can support a more secure and confident financial future.
-#Finwell #FinancialWellbeing #EmiratesIslamic #Investing</t>
+#Finwell #FinancialWellbeing #EmiratesIslamic #Investing https://t.co/7rh6hiRrKq</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -8513,12 +8495,21 @@
 #Finwell #FinancialWellbeing #EmiratesIslamic #Investing</t>
         </is>
       </c>
-      <c r="Y50" t="inlineStr"/>
-      <c r="Z50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047287763796427063</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>Starting early and staying consistent can help your money grow over time. Small steps today can support a more secure and confident financial future.
+#Finwell #FinancialWellbeing #EmiratesIslamic #Investing https://t.co/7rh6hiRrKq</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>Starting early and staying consistent can help your money grow over time. Small steps today can support a more secure and confident financial future.
-#Finwell #FinancialWellbeing #EmiratesIslamic #Investing</t>
+#Finwell #FinancialWellbeing #EmiratesIslamic #Investing https://t.co/7rh6hiRrKq</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
@@ -8950,8 +8941,7 @@
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Starting early and staying consistent can help your money grow over time. Small steps today can support a more secure and confident financial future.
-#Finwell #FinancialWellbeing #EmiratesIslamic #Investing https://t.co/7rh6hiRrKq</t>
+          <t>البدء مبكرًا والاستمرار بثبات يساعدان على نمو أموالك مع الوقت. خطوات بسيطة اليوم قد تساهم في بناء مستقبل مالي أكثر استقرارًا وثقة.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -9001,26 +8991,16 @@
           <t>البدء مبكرًا والاستمرار بثبات يساعدان على نمو أموالك مع الوقت. خطوات بسيطة اليوم قد تساهم في بناء مستقبل مالي أكثر استقرارًا وثقة.</t>
         </is>
       </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047289060557824183</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>Starting early and staying consistent can help your money grow over time. Small steps today can support a more secure and confident financial future.
-#Finwell #FinancialWellbeing #EmiratesIslamic #Investing https://t.co/7rh6hiRrKq</t>
-        </is>
-      </c>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>Starting early and staying consistent can help your money grow over time. Small steps today can support a more secure and confident financial future.
-#Finwell #FinancialWellbeing #EmiratesIslamic #Investing https://t.co/7rh6hiRrKq</t>
+          <t>البدء مبكرًا والاستمرار بثبات يساعدان على نمو أموالك مع الوقت. خطوات بسيطة اليوم قد تساهم في بناء مستقبل مالي أكثر استقرارًا وثقة.</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Starting early and staying consistent can help your money grow over time. Small steps today can support a more secure and confident financial future.</t>
+          <t>Starting early and staying consistent helps your money grow over time. Simple steps today can contribute to building a more stable and confident financial future.</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -9051,7 +9031,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Starting early and staying consistent can help your money grow over time. • Small steps today can support a more secure and confident financial future.</t>
+          <t>Simple steps today can contribute to building a more stable and confident financial future. • Starting early and staying consistent helps your money grow over time.</t>
         </is>
       </c>
       <c r="AJ53" t="inlineStr">
@@ -9528,12 +9508,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2047241499490807897</t>
+          <t>2047193755975917822</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047241499490807897</t>
+          <t>https://x.com/emiratesislamic/status/2047193755975917822</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9559,38 +9539,40 @@
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Dear Customer, Thanks for getting in touch. Your privacy is important to us, and to ensure your confidentiality, we've sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
+          <t>#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
+emiratesislamic.ae/ar/key-in…</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Dear Customer, Thanks for getting in touch. Your privacy is important to us, and to ensure your confidentiality, we&amp;#39;ve sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
+          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K57" t="b">
         <v>0</v>
       </c>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>['UpendraS83806']</t>
-        </is>
-      </c>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Apr 23, 2026 · 9:09 AM UTC</t>
+          <t>Apr 23, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P57" s="2" t="n">
-        <v>46135.38125</v>
+        <v>46135.25</v>
       </c>
       <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+        </is>
+      </c>
       <c r="S57" t="n">
         <v>0</v>
       </c>
@@ -9601,7 +9583,7 @@
         <v>0</v>
       </c>
       <c r="V57" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
@@ -9610,24 +9592,26 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Dear Customer, Thanks for getting in touch. Your privacy is important to us, and to ensure your confidentiality, we've sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
+          <t>#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
+emiratesislamic.ae/ar/key-in…</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>Dear Customer, Thanks for getting in touch. Your privacy is important to us, and to ensure your confidentiality, we've sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
+          <t>#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
+emiratesislamic.ae/ar/key-in…</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>Dear Customer, Thanks for getting in touch. Your privacy is important to us, and to ensure your confidentiality, we've sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
+          <t>#Your_Financial_View #Financial_Education #Emirates_Islamic</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Cust</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
@@ -9636,7 +9620,7 @@
         </is>
       </c>
       <c r="AE57" s="2" t="n">
-        <v>46135.54791666667</v>
+        <v>46135.41666666666</v>
       </c>
       <c r="AF57" s="2" t="n">
         <v>46135</v>
@@ -9653,7 +9637,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Your privacy is important to us, and to ensure your confidentiality, we've sent you a message requesting further details. • Please check your direct messages at your earliest convenience. • Dear Customer, Thanks for getting in touch.</t>
+          <t>#Your_Financial_View #Financial_Education #Emirates_Islamic</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
@@ -9666,7 +9650,7 @@
       </c>
       <c r="AL57" t="inlineStr">
         <is>
-          <t>UpendraS83806</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9676,12 +9660,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2047193755975917822</t>
+          <t>2047193753073357199</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047193755975917822</t>
+          <t>https://x.com/emiratesislamic/status/2047193753073357199</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9716,64 +9700,6 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K58" t="b">
-        <v>0</v>
-      </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>Apr 23, 2026 · 6:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P58" s="2" t="n">
-        <v>46135.25</v>
-      </c>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
-        </is>
-      </c>
-      <c r="S58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" t="n">
-        <v>0</v>
-      </c>
-      <c r="U58" t="n">
-        <v>0</v>
-      </c>
-      <c r="V58" t="n">
-        <v>53</v>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-emiratesislamic.ae/ar/key-in…</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047193755975917822</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
           <t>إنفاقك ليس مجرد أرقام عشوائية، هنالك نمط خفي في معاملاتك ينتظر أن تكتشفه.
 راجع آخر 10 معاملات لديك،
 وابحث عن التكرار لا عن المبالغ،
@@ -9781,7 +9707,44 @@
 فالأمر يتعلق بالعادات، لا بالمشتريات.</t>
         </is>
       </c>
-      <c r="AA58" t="inlineStr">
+      <c r="K58" t="b">
+        <v>0</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Apr 23, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="n">
+        <v>46135.25</v>
+      </c>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="n">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" t="n">
+        <v>58</v>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
         <is>
           <t>إنفاقك ليس مجرد أرقام عشوائية، هنالك نمط خفي في معاملاتك ينتظر أن تكتشفه.
 راجع آخر 10 معاملات لديك،
@@ -9790,6 +9753,29 @@
 فالأمر يتعلق بالعادات، لا بالمشتريات.</t>
         </is>
       </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047193753073357199</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>إنفاقك ليس مجرد أرقام عشوائية، هنالك نمط خفي في معاملاتك ينتظر أن تكتشفه.
+راجع آخر 10 معاملات لديك،
+وابحث عن التكرار لا عن المبالغ،
+وستكتشف سريعاً ما يستنزف أموالك أكثر.
+فالأمر يتعلق بالعادات، لا بالمشتريات.</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>إنفاقك ليس مجرد أرقام عشوائية، هنالك نمط خفي في معاملاتك ينتظر أن تكتشفه.
+راجع آخر 10 معاملات لديك،
+وابحث عن التكرار لا عن المبالغ،
+وستكتشف سريعاً ما يستنزف أموالك أكثر.
+فالأمر يتعلق بالعادات، لا بالمشتريات.</t>
+        </is>
+      </c>
       <c r="AB58" t="inlineStr">
         <is>
           <t>Your spending is not just random numbers; there is a hidden pattern in your transactions waiting to be discovered.
@@ -9850,51 +9836,43 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2047193753073357199</t>
+          <t>2047201786570907985</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047193753073357199</t>
+          <t>https://x.com/77dd14cbca18474/status/2047201786570907985</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/77dd14cbca18474</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>77dd14cbca18474</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Abid Khan</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2047207410419597312/bB5RzTBS_bigger.jpg</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>إنفاقك ليس مجرد أرقام عشوائية، هنالك نمط خفي في معاملاتك ينتظر أن تكتشفه.
-راجع آخر 10 معاملات لديك،
-وابحث عن التكرار لا عن المبالغ،
-وستكتشف سريعاً ما يستنزف أموالك أكثر.
-فالأمر يتعلق بالعادات، لا بالمشتريات.</t>
+          <t>@EmiratesNBD_AE Hello its been 1 year iam following for account cancellation called many times to call center posted in X also still not cancelled?? Whats happening</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>إنفاقك ليس مجرد أرقام عشوائية، هنالك نمط خفي في معاملاتك ينتظر أن تكتشفه.
-راجع آخر 10 معاملات لديك،
-وابحث عن التكرار لا عن المبالغ،
-وستكتشف سريعاً ما يستنزف أموالك أكثر.
-فالأمر يتعلق بالعادات، لا بالمشتريات.</t>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; Hello its been 1 year iam following for account cancellation called many times to call center posted in X also still not cancelled?? Whats happening</t>
         </is>
       </c>
       <c r="K59" t="b">
@@ -9904,21 +9882,25 @@
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Apr 23, 2026 · 6:00 AM UTC</t>
+          <t>Apr 23, 2026 · 6:31 AM UTC</t>
         </is>
       </c>
       <c r="P59" s="2" t="n">
-        <v>46135.25</v>
+        <v>46135.27152777778</v>
       </c>
       <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="S59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T59" t="n">
         <v>0</v>
@@ -9927,76 +9909,64 @@
         <v>0</v>
       </c>
       <c r="V59" t="n">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>إنفاقك ليس مجرد أرقام عشوائية، هنالك نمط خفي في معاملاتك ينتظر أن تكتشفه.
-راجع آخر 10 معاملات لديك،
-وابحث عن التكرار لا عن المبالغ،
-وستكتشف سريعاً ما يستنزف أموالك أكثر.
-فالأمر يتعلق بالعادات، لا بالمشتريات.</t>
+          <t>@EmiratesNBD_AE Hello its been 1 year iam following for account cancellation called many times to call center posted in X also still not cancelled?? Whats happening</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="inlineStr"/>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>إنفاقك ليس مجرد أرقام عشوائية، هنالك نمط خفي في معاملاتك ينتظر أن تكتشفه.
-راجع آخر 10 معاملات لديك،
-وابحث عن التكرار لا عن المبالغ،
-وستكتشف سريعاً ما يستنزف أموالك أكثر.
-فالأمر يتعلق بالعادات، لا بالمشتريات.</t>
+          <t>@EmiratesNBD_AE Hello its been 1 year iam following for account cancellation called many times to call center posted in X also still not cancelled?? Whats happening</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>Your spending is not just random numbers; there is a hidden pattern in your transactions waiting to be discovered.
-Review your last 10 transactions,
-and look for the repetition, not the amounts,
-and you will quickly discover what drains your money the most.
-It's about habits, not purchases.</t>
+          <t>Hello, it's been 1 year since I started following up on my account cancellation. I have called the call center many times and posted on X, but it is still not cancelled. What is happening?</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Cust</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="AE59" s="2" t="n">
-        <v>46135.41666666666</v>
+        <v>46135.43819444445</v>
       </c>
       <c r="AF59" s="2" t="n">
         <v>46135</v>
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
+          <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Review your last 10 transactions, and look for the repetition, not the amounts, and you will quickly discover what drains your money the most. • Your spending is not just random numbers; there is a hidden pattern in your transactions waiting to be discovered. • It's about habits, not purchases.</t>
+          <t>I have called the call center many times and posted on X, but it is still not cancelled. • Hello, it's been 1 year since I started following up on my account cancellation.</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>Emirates Islamic Bank (EIB)</t>
+          <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
       <c r="AK59" t="n">
@@ -10014,43 +9984,43 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2047201786570907985</t>
+          <t>2047136949702631667</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://x.com/77dd14cbca18474/status/2047201786570907985</t>
+          <t>https://x.com/Bosscollion/status/2047136949702631667</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://x.com/77dd14cbca18474</t>
+          <t>https://x.com/Bosscollion</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>77dd14cbca18474</t>
+          <t>Bosscollion</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Abid Khan</t>
+          <t>Mr. Wanjaa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2047207410419597312/bB5RzTBS_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1334239840104230922/Y-nkwQ3W_bigger.jpg</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Hello its been 1 year iam following for account cancellation called many times to call center posted in X also still not cancelled?? Whats happening</t>
+          <t>@EmiratesNBD_AE Wasl Village Deposit machine/ATM is not working from Wednesday night 22.04.2026. Please SEND A TEAM TO FIX IT! https://t.co/YDRya1jkz8</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; Hello its been 1 year iam following for account cancellation called many times to call center posted in X also still not cancelled?? Whats happening</t>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; Wasl Village Deposit machine/ATM is not working from Wednesday night 22.04.2026. Please SEND A TEAM TO FIX IT!</t>
         </is>
       </c>
       <c r="K60" t="b">
@@ -10060,16 +10030,16 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>Apr 23</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Apr 23, 2026 · 6:31 AM UTC</t>
+          <t>Apr 23, 2026 · 2:14 AM UTC</t>
         </is>
       </c>
       <c r="P60" s="2" t="n">
-        <v>46135.27152777778</v>
+        <v>46135.09305555555</v>
       </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr">
@@ -10078,7 +10048,7 @@
         </is>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T60" t="n">
         <v>0</v>
@@ -10087,7 +10057,7 @@
         <v>0</v>
       </c>
       <c r="V60" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
@@ -10096,27 +10066,27 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Hello its been 1 year iam following for account cancellation called many times to call center posted in X also still not cancelled?? Whats happening</t>
+          <t>@EmiratesNBD_AE Wasl Village Deposit machine/ATM is not working from Wednesday night 22.04.2026. Please SEND A TEAM TO FIX IT!</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>https://x.com/77dd14cbca18474/status/2047201786570907985</t>
+          <t>https://x.com/Bosscollion/status/2047136949702631667</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Hello its been 1 year iam following for account cancellation called many times to call center posted in X also still not cancelled?? Whats happening</t>
+          <t>@EmiratesNBD_AE Wasl Village Deposit machine/ATM is not working from Wednesday night 22.04.2026. Please SEND A TEAM TO FIX IT! https://t.co/YDRya1jkz8</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Hello its been 1 year iam following for account cancellation called many times to call center posted in X also still not cancelled?? Whats happening</t>
+          <t>@EmiratesNBD_AE Wasl Village Deposit machine/ATM is not working from Wednesday night 22.04.2026. Please SEND A TEAM TO FIX IT! https://t.co/YDRya1jkz8</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>Hello, it's been 1 year since I started following up on my account cancellation. I have called the call center many times and posted on X, but it is still not cancelled. What is happening?</t>
+          <t>The Wasl Village Deposit machine/ATM is not working since Wednesday night, April 22, 2026. Please send a team to fix it!</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -10130,7 +10100,7 @@
         </is>
       </c>
       <c r="AE60" s="2" t="n">
-        <v>46135.43819444445</v>
+        <v>46135.25972222222</v>
       </c>
       <c r="AF60" s="2" t="n">
         <v>46135</v>
@@ -10147,7 +10117,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>I have called the call center many times and posted on X, but it is still not cancelled. • Hello, it's been 1 year since I started following up on my account cancellation.</t>
+          <t>The Wasl Village Deposit machine/ATM is not working since Wednesday night, April 22, 2026. • Please send a team to fix it!</t>
         </is>
       </c>
       <c r="AJ60" t="inlineStr">
@@ -10170,43 +10140,48 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2047136949702631667</t>
+          <t>2047182474049106165</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://x.com/Bosscollion/status/2047136949702631667</t>
+          <t>https://x.com/HarshGada76429/status/2047182474049106165</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://x.com/Bosscollion</t>
+          <t>https://x.com/HarshGada76429</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bosscollion</t>
+          <t>HarshGada76429</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mr. Wanjaa</t>
+          <t>Harsh Gada</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1334239840104230922/Y-nkwQ3W_bigger.jpg</t>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Wasl Village Deposit machine/ATM is not working from Wednesday night 22.04.2026. Please SEND A TEAM TO FIX IT! https://t.co/YDRya1jkz8</t>
+          <t>@RBLBankCares
+@rblbank
+I have been a loyal customer for last 3yrs using your world safari credit card I have achieved the milestone but missed the redemption date by 7 days 
+Request you to send me new redemption link for 10000rs voucher or I will have to end the relationship now</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; Wasl Village Deposit machine/ATM is not working from Wednesday night 22.04.2026. Please SEND A TEAM TO FIX IT!</t>
+          <t>Pathetic services and poor client retention services by RBL Bank
+&lt;a href="/RBLBankCares" title="RBL Bank Cares"&gt;@RBLBankCares&lt;/a&gt; 
+&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K61" t="b">
@@ -10216,21 +10191,21 @@
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Apr 23</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Apr 23, 2026 · 2:14 AM UTC</t>
+          <t>Apr 23, 2026 · 5:15 AM UTC</t>
         </is>
       </c>
       <c r="P61" s="2" t="n">
-        <v>46135.09305555555</v>
+        <v>46135.21875</v>
       </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr">
         <is>
-          <t>['https://x.com/EmiratesNBD_AE']</t>
+          <t>['https://x.com/RBLBankCares', 'https://x.com/EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="S61" t="n">
@@ -10243,7 +10218,7 @@
         <v>0</v>
       </c>
       <c r="V61" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
@@ -10252,27 +10227,35 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Wasl Village Deposit machine/ATM is not working from Wednesday night 22.04.2026. Please SEND A TEAM TO FIX IT!</t>
+          <t>Pathetic services and poor client retention services by RBL Bank
+@RBLBankCares 
+@EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>https://x.com/Bosscollion/status/2047136949702631667</t>
+          <t>https://x.com/HarshGada76429/status/2047182474049106165</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Wasl Village Deposit machine/ATM is not working from Wednesday night 22.04.2026. Please SEND A TEAM TO FIX IT! https://t.co/YDRya1jkz8</t>
+          <t>@RBLBankCares
+@rblbank
+I have been a loyal customer for last 3yrs using your world safari credit card I have achieved the milestone but missed the redemption date by 7 days 
+Request you to send me new redemption link for 10000rs voucher or I will have to end the relationship now</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Wasl Village Deposit machine/ATM is not working from Wednesday night 22.04.2026. Please SEND A TEAM TO FIX IT! https://t.co/YDRya1jkz8</t>
+          <t>@RBLBankCares
+@rblbank
+I have been a loyal customer for last 3yrs using your world safari credit card I have achieved the milestone but missed the redemption date by 7 days 
+Request you to send me new redemption link for 10000rs voucher or I will have to end the relationship now</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>The Wasl Village deposit machine/ATM is not working since Wednesday night, April 22, 2026. Please send a team to fix it!</t>
+          <t>I have been a loyal customer for the last 3 years using your World Safari credit card. I have achieved the milestone but missed the redemption date by 7 days. I request you to send me a new redemption link for a 10,000 INR voucher, or I will have to end the relationship now.</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -10286,7 +10269,7 @@
         </is>
       </c>
       <c r="AE61" s="2" t="n">
-        <v>46135.25972222222</v>
+        <v>46135.38541666666</v>
       </c>
       <c r="AF61" s="2" t="n">
         <v>46135</v>
@@ -10303,7 +10286,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>The Wasl Village deposit machine/ATM is not working since Wednesday night, April 22, 2026. • Please send a team to fix it!</t>
+          <t>I request you to send me a new redemption link for a 10,000 INR voucher, or I will have to end the relationship now. • I have been a loyal customer for the last 3 years using your World Safari credit card. • I have achieved the milestone but missed the redemption date by 7 days.</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
@@ -10326,205 +10309,36 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2047182474049106165</t>
+          <t>2047246858716930242</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://x.com/HarshGada76429/status/2047182474049106165</t>
+          <t>https://x.com/abd11ulla/status/2047246858716930242</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://x.com/HarshGada76429</t>
+          <t>https://x.com/abd11ulla</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>HarshGada76429</t>
+          <t>abd11ulla</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Harsh Gada</t>
+          <t>Abdulla</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1882456476913901568/rFdTg6of_bigger.jpg</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
-        <is>
-          <t>@RBLBankCares
-@rblbank
-I have been a loyal customer for last 3yrs using your world safari credit card I have achieved the milestone but missed the redemption date by 7 days 
-Request you to send me new redemption link for 10000rs voucher or I will have to end the relationship now</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>Pathetic services and poor client retention services by RBL Bank
-&lt;a href="/RBLBankCares" title="RBL Bank Cares"&gt;@RBLBankCares&lt;/a&gt; 
-&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K62" t="b">
-        <v>0</v>
-      </c>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>Apr 23, 2026 · 5:15 AM UTC</t>
-        </is>
-      </c>
-      <c r="P62" s="2" t="n">
-        <v>46135.21875</v>
-      </c>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>['https://x.com/RBLBankCares', 'https://x.com/EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="S62" t="n">
-        <v>1</v>
-      </c>
-      <c r="T62" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" t="n">
-        <v>0</v>
-      </c>
-      <c r="V62" t="n">
-        <v>7</v>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>Pathetic services and poor client retention services by RBL Bank
-@RBLBankCares 
-@EmiratesNBD_AE</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>https://x.com/HarshGada76429/status/2047182474049106165</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>@RBLBankCares
-@rblbank
-I have been a loyal customer for last 3yrs using your world safari credit card I have achieved the milestone but missed the redemption date by 7 days 
-Request you to send me new redemption link for 10000rs voucher or I will have to end the relationship now</t>
-        </is>
-      </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>@RBLBankCares
-@rblbank
-I have been a loyal customer for last 3yrs using your world safari credit card I have achieved the milestone but missed the redemption date by 7 days 
-Request you to send me new redemption link for 10000rs voucher or I will have to end the relationship now</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>I have been a loyal customer for the last 3 years using your World Safari credit card. I have achieved the milestone but missed the redemption date by 7 days. I request you to send me a new redemption link for a 10,000 INR voucher, or I will have to end the relationship now.</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD62" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="AE62" s="2" t="n">
-        <v>46135.38541666666</v>
-      </c>
-      <c r="AF62" s="2" t="n">
-        <v>46135</v>
-      </c>
-      <c r="AG62" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>I request you to send me a new redemption link for a 10,000 INR voucher, or I will have to end the relationship now. • I have been a loyal customer for the last 3 years using your World Safari credit card. • I have achieved the milestone but missed the redemption date by 7 days.</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK62" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL62" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="1" t="n">
-        <v>61</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2047246858716930242</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>https://x.com/abd11ulla/status/2047246858716930242</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>https://x.com/abd11ulla</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>abd11ulla</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Abdulla</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1882456476913901568/rFdTg6of_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr">
         <is>
           <t>للأسف البنك من أسوء من تعامل مع الأزمة والظروف
 صافي الأرباح لم يسجل نمواً مقارنة بالفترة ذاتها من
@@ -10533,7 +10347,7 @@
 رغم الأزمة تفوق ENBD على FAB و سجل أرقاماً قياسية .</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>للأسف البنك من أسوء من تعامل مع الأزمة والظروف
 صافي الأرباح لم يسجل نمواً مقارنة بالفترة ذاتها من
@@ -10542,44 +10356,44 @@
 رغم الأزمة تفوق ENBD على FAB و سجل أرقاماً قياسية .</t>
         </is>
       </c>
-      <c r="K63" t="b">
-        <v>0</v>
-      </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr">
+      <c r="K62" t="b">
+        <v>0</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
         <is>
           <t>18h</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>Apr 23, 2026 · 9:31 AM UTC</t>
         </is>
       </c>
-      <c r="P63" s="2" t="n">
+      <c r="P62" s="2" t="n">
         <v>46135.39652777778</v>
       </c>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="n">
-        <v>0</v>
-      </c>
-      <c r="T63" t="n">
-        <v>0</v>
-      </c>
-      <c r="U63" t="n">
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="n">
         <v>2</v>
       </c>
-      <c r="V63" t="n">
+      <c r="V62" t="n">
         <v>300</v>
       </c>
-      <c r="W63" t="inlineStr">
+      <c r="W62" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>للأسف البنك من أسوء من تعامل مع الأزمة والظروف
 صافي الأرباح لم يسجل نمواً مقارنة بالفترة ذاتها من
@@ -10588,12 +10402,12 @@
 رغم الأزمة تفوق ENBD على FAB و سجل أرقاماً قياسية .</t>
         </is>
       </c>
-      <c r="Y63" t="inlineStr">
+      <c r="Y62" t="inlineStr">
         <is>
           <t>https://x.com/abd11ulla/status/2047246858716930242</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
+      <c r="Z62" t="inlineStr">
         <is>
           <t>للأسف البنك من أسوء من تعامل مع الأزمة والظروف
 صافي الأرباح لم يسجل نمواً مقارنة بالفترة ذاتها من
@@ -10602,7 +10416,7 @@
 رغم الأزمة تفوق ENBD على FAB و سجل أرقاماً قياسية .</t>
         </is>
       </c>
-      <c r="AA63" t="inlineStr">
+      <c r="AA62" t="inlineStr">
         <is>
           <t>للأسف البنك من أسوء من تعامل مع الأزمة والظروف
 صافي الأرباح لم يسجل نمواً مقارنة بالفترة ذاتها من
@@ -10611,9 +10425,165 @@
 رغم الأزمة تفوق ENBD على FAB و سجل أرقاماً قياسية .</t>
         </is>
       </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>Unfortunately, the bank has been one of the worst in dealing with the crisis and circumstances. Net profits did not show growth compared to the same period last year. On the other hand, Dubai National recorded growth in net profit compared to the same period last year. Despite the crisis, ENBD outperformed FAB and recorded record numbers.</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AE62" s="2" t="n">
+        <v>46135.56319444445</v>
+      </c>
+      <c r="AF62" s="2" t="n">
+        <v>46135</v>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>On the other hand, Dubai National recorded growth in net profit compared to the same period last year. • Net profits did not show growth compared to the same period last year. • Despite the crisis, ENBD outperformed FAB and recorded record numbers.</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK62" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL62" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2047511223839908158</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://x.com/abhiseksonusonu/status/2047511223839908158</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://x.com/abhiseksonusonu</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>abhiseksonusonu</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>A R mishra</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1912019334932611072/h2qIgZ-L_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>@LivBank @EmiratesNBD_AE I deposited cash via ENBD ATM toward my credit card on 21st April but amount got stuck. Complaint already raised, yet the amount is still not credited. My due date is this Monday. Request urgent resolution and credit of funds.</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>&lt;a href="/LivBank" title="Liv Digital Bank"&gt;@LivBank&lt;/a&gt; &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; I deposited cash via ENBD ATM toward my credit card on 21st April but amount got stuck. Complaint already raised, yet the amount is still not credited. My due date is this Monday. Request urgent resolution and credit of funds.</t>
+        </is>
+      </c>
+      <c r="K63" t="b">
+        <v>0</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 3:01 AM UTC</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="n">
+        <v>46136.12569444445</v>
+      </c>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>['https://x.com/LivBank', 'https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" t="n">
+        <v>29</v>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>@LivBank @EmiratesNBD_AE I deposited cash via ENBD ATM toward my credit card on 21st April but amount got stuck. Complaint already raised, yet the amount is still not credited. My due date is this Monday. Request urgent resolution and credit of funds.</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>https://x.com/abhiseksonusonu/status/2047511223839908158</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>@LivBank @EmiratesNBD_AE I deposited cash via ENBD ATM toward my credit card on 21st April but amount got stuck. Complaint already raised, yet the amount is still not credited. My due date is this Monday. Request urgent resolution and credit of funds.</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>@LivBank @EmiratesNBD_AE I deposited cash via ENBD ATM toward my credit card on 21st April but amount got stuck. Complaint already raised, yet the amount is still not credited. My due date is this Monday. Request urgent resolution and credit of funds.</t>
+        </is>
+      </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>Unfortunately, the bank has been one of the worst in dealing with the crisis and circumstances. Net profits did not show growth compared to the same period last year. On the other hand, Dubai National recorded growth in net profit compared to the same period last year. Despite the crisis, ENBD outperformed FAB and recorded record numbers.</t>
+          <t>I deposited cash via ENBD ATM toward my credit card on April 21, but the amount got stuck. A complaint has already been raised, yet the amount is still not credited. My due date is this Monday. I request an urgent resolution and credit of funds.</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -10627,10 +10597,10 @@
         </is>
       </c>
       <c r="AE63" s="2" t="n">
-        <v>46135.56319444445</v>
+        <v>46136.29236111111</v>
       </c>
       <c r="AF63" s="2" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="AG63" t="inlineStr">
         <is>
@@ -10644,7 +10614,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>On the other hand, Dubai National recorded growth in net profit compared to the same period last year. • Net profits did not show growth compared to the same period last year. • Despite the crisis, ENBD outperformed FAB and recorded record numbers.</t>
+          <t>I deposited cash via ENBD ATM toward my credit card on April 21, but the amount got stuck. • A complaint has already been raised, yet the amount is still not credited. • I request an urgent resolution and credit of funds.</t>
         </is>
       </c>
       <c r="AJ63" t="inlineStr">
@@ -10667,69 +10637,70 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2047511223839908158</t>
+          <t>2047241499490807897</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://x.com/abhiseksonusonu/status/2047511223839908158</t>
+          <t>https://x.com/emiratesislamic/status/2047241499490807897</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://x.com/abhiseksonusonu</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>abhiseksonusonu</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>A R mishra</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1912019334932611072/h2qIgZ-L_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>@LivBank @EmiratesNBD_AE I deposited cash via ENBD ATM toward my credit card on 21st April but amount got stuck. Complaint already raised, yet the amount is still not credited. My due date is this Monday. Request urgent resolution and credit of funds.</t>
+          <t>@emiratesislamic My client transferred payment from your bank but still not credited into my account.
+Please advise.</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>&lt;a href="/LivBank" title="Liv Digital Bank"&gt;@LivBank&lt;/a&gt; &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; I deposited cash via ENBD ATM toward my credit card on 21st April but amount got stuck. Complaint already raised, yet the amount is still not credited. My due date is this Monday. Request urgent resolution and credit of funds.</t>
+          <t>Dear Customer, Thanks for getting in touch. Your privacy is important to us, and to ensure your confidentiality, we&amp;#39;ve sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
         </is>
       </c>
       <c r="K64" t="b">
         <v>0</v>
       </c>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>['UpendraS83806']</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>1h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 3:01 AM UTC</t>
+          <t>Apr 23, 2026 · 9:09 AM UTC</t>
         </is>
       </c>
       <c r="P64" s="2" t="n">
-        <v>46136.12569444445</v>
+        <v>46135.38125</v>
       </c>
       <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>['https://x.com/LivBank', 'https://x.com/EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="R64" t="inlineStr"/>
       <c r="S64" t="n">
         <v>0</v>
       </c>
@@ -10740,36 +10711,38 @@
         <v>0</v>
       </c>
       <c r="V64" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>@LivBank @EmiratesNBD_AE I deposited cash via ENBD ATM toward my credit card on 21st April but amount got stuck. Complaint already raised, yet the amount is still not credited. My due date is this Monday. Request urgent resolution and credit of funds.</t>
+          <t>Dear Customer, Thanks for getting in touch. Your privacy is important to us, and to ensure your confidentiality, we've sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>https://x.com/abhiseksonusonu/status/2047511223839908158</t>
+          <t>https://x.com/emiratesislamic/status/2047241499490807897</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>@LivBank @EmiratesNBD_AE I deposited cash via ENBD ATM toward my credit card on 21st April but amount got stuck. Complaint already raised, yet the amount is still not credited. My due date is this Monday. Request urgent resolution and credit of funds.</t>
+          <t>@emiratesislamic My client transferred payment from your bank but still not credited into my account.
+Please advise.</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>@LivBank @EmiratesNBD_AE I deposited cash via ENBD ATM toward my credit card on 21st April but amount got stuck. Complaint already raised, yet the amount is still not credited. My due date is this Monday. Request urgent resolution and credit of funds.</t>
+          <t>@emiratesislamic My client transferred payment from your bank but still not credited into my account.
+Please advise.</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>I deposited cash via ENBD ATM toward my credit card on April 21, but the amount got stuck. A complaint has already been raised, yet the amount is still not credited. My due date is this Monday. I request an urgent resolution and credit of funds.</t>
+          <t>My client transferred payment from your bank but it has still not been credited to my account. Please advise.</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -10783,29 +10756,29 @@
         </is>
       </c>
       <c r="AE64" s="2" t="n">
-        <v>46136.29236111111</v>
+        <v>46135.54791666667</v>
       </c>
       <c r="AF64" s="2" t="n">
-        <v>46136</v>
+        <v>46135</v>
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
+          <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>I deposited cash via ENBD ATM toward my credit card on April 21, but the amount got stuck. • A complaint has already been raised, yet the amount is still not credited. • I request an urgent resolution and credit of funds.</t>
+          <t>My client transferred payment from your bank but it has still not been credited to my account.</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank (ENBD)</t>
+          <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AK64" t="n">
@@ -10813,7 +10786,7 @@
       </c>
       <c r="AL64" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>UpendraS83806</t>
         </is>
       </c>
     </row>

--- a/check2.xlsx
+++ b/check2.xlsx
@@ -739,7 +739,7 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>I wanted to open a gold account at Mashreq Bank, but they wanted me to be a millionaire for them to start talking to me. In the name of God, here are the conditions: 
-Your salary must be 80,000 dirhams or more, and your balance should not be less than 500,000 dirhams. There were third and fourth conditions, so I opened the account and paid the ADCB and ENBD cards and the National Bank of Egypt, and I prayed two units of gratitude.</t>
+Your salary must be 80,000 dirhams or more, and your balance should not be less than 500,000 dirhams. There were third and fourth conditions, so I opened the account and linked it to ADCB, ENBD, and the National Bank of Egypt cards, and I prayed two units of gratitude.</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>In the name of God, here are the conditions: Your salary must be 80,000 dirhams or more, and your balance should not be less than 500,000 dirhams. • There were third and fourth conditions, so I opened the account and paid the ADCB and ENBD cards and the National Bank of Egypt, and I prayed two units of gratitude. • I wanted to open a gold account at Mashreq Bank, but they wanted me to be a millionaire for them to start talking to me.</t>
+          <t>In the name of God, here are the conditions: Your salary must be 80,000 dirhams or more, and your balance should not be less than 500,000 dirhams. • There were third and fourth conditions, so I opened the account and linked it to ADCB, ENBD, and the National Bank of Egypt cards, and I prayed two units of gratitude. • I wanted to open a gold account at Mashreq Bank, but they wanted me to be a millionaire for them to start talking to me.</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>You can own the car of your dreams, whether new or used, with leasing financing for cars from Emirates NBD Bank.</t>
+          <t>You can own your dream car, whether new or used, with leasing financing for cars from Emirates NBD.</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>You can own the car of your dreams, whether new or used, with leasing financing for cars from Emirates NBD Bank.</t>
+          <t>You can own your dream car, whether new or used, with leasing financing for cars from Emirates NBD.</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>A bouquet of flowers for every special moment with Flaround 💐 Get a 20% discount on elegant flower arrangements, exclusively through the Testahl app. To learn more: https://t.co/quzlzhDcXR https://t.co/Pj8RmtMYOK</t>
+          <t>A bouquet of flowers for every special moment with Flarowd 💐 Get a 20% discount on elegant flower arrangements, exclusively through the Testahl app. To learn more: https://t.co/quzlzhDcXR https://t.co/Pj8RmtMYOK</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>A bouquet of flowers for every special moment with Flaround 💐 Get a 20% discount on elegant flower arrangements, exclusively through the Testahl app. • To learn more: https://t.co/quzlzhDcXR https://t.co/Pj8RmtMYOK</t>
+          <t>A bouquet of flowers for every special moment with Flarowd 💐 Get a 20% discount on elegant flower arrangements, exclusively through the Testahl app. • To learn more: https://t.co/quzlzhDcXR https://t.co/Pj8RmtMYOK</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1150,8 +1150,7 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>متى بتفعلون خدمة SAMSUNG PAY ؟
- @EmiratesNBD_KSA</t>
+          <t>الووووو .</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1205,26 +1204,16 @@
           <t>الووووو .</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>https://x.com/fortyxxl88/status/2047692228684878061</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>متى بتفعلون خدمة SAMSUNG PAY ؟
- @EmiratesNBD_KSA</t>
-        </is>
-      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>متى بتفعلون خدمة SAMSUNG PAY ؟
- @EmiratesNBD_KSA</t>
+          <t>الووووو .</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>When will you activate the SAMSUNG PAY service?</t>
+          <t>Hello.</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1255,7 +1244,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>When will you activate the SAMSUNG PAY service?</t>
+          <t>Hello.</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1309,7 +1298,8 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA تشترون مديونية قطاع خاص غير معتمد ؟</t>
+          <t>متى بتفعلون خدمة SAMSUNG PAY ؟
+ @EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1370,17 +1360,19 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA تشترون مديونية قطاع خاص غير معتمد ؟</t>
+          <t>متى بتفعلون خدمة SAMSUNG PAY ؟
+ @EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA تشترون مديونية قطاع خاص غير معتمد ؟</t>
+          <t>متى بتفعلون خدمة SAMSUNG PAY ؟
+ @EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Do you buy non-approved private sector debt?</t>
+          <t>When will you activate the SAMSUNG PAY service?</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1411,7 +1403,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Do you buy non-approved private sector debt?</t>
+          <t>When will you activate the SAMSUNG PAY service?</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2419,9 +2411,7 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>We just killed cold email: Introducing Draftboard.
-The world’s first AI Sales Director that outperforms any human.
-Comment your website and we’ll find you intros to 10 dream prospects for free. https://t.co/DK7wDKVQl7</t>
+          <t>@coiningmaxi Alright - found some of your customers: PayTabs, Telr, Network International, Magnati, Emirates NBD and Mashreq Bank. Sound right? Going to use these to track down real prospects at your dream customers and map intro paths to them</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2482,23 +2472,17 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>We just killed cold email: Introducing Draftboard.
-The world’s first AI Sales Director that outperforms any human.
-Comment your website and we’ll find you intros to 10 dream prospects for free. https://t.co/DK7wDKVQl7</t>
+          <t>@coiningmaxi Alright - found some of your customers: PayTabs, Telr, Network International, Magnati, Emirates NBD and Mashreq Bank. Sound right? Going to use these to track down real prospects at your dream customers and map intro paths to them</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>We just killed cold email: Introducing Draftboard.
-The world’s first AI Sales Director that outperforms any human.
-Comment your website and we’ll find you intros to 10 dream prospects for free. https://t.co/DK7wDKVQl7</t>
+          <t>@coiningmaxi Alright - found some of your customers: PayTabs, Telr, Network International, Magnati, Emirates NBD and Mashreq Bank. Sound right? Going to use these to track down real prospects at your dream customers and map intro paths to them</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>We just killed cold email: Introducing Draftboard.
-The world’s first AI Sales Director that outperforms any human.
-Comment your website and we’ll find you introductions to 10 dream prospects for free.</t>
+          <t>Alright - I found some of your customers: PayTabs, Telr, Network International, Magnati, Emirates NBD, and Mashreq Bank. Does that sound right? I'm going to use these to track down real prospects at your dream customers and map introduction paths to them.</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2529,7 +2513,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Comment your website and we’ll find you introductions to 10 dream prospects for free. • The world’s first AI Sales Director that outperforms any human. • We just killed cold email: Introducing Draftboard.</t>
+          <t>Alright - I found some of your customers: PayTabs, Telr, Network International, Magnati, Emirates NBD, and Mashreq Bank. • I'm going to use these to track down real prospects at your dream customers and map introduction paths to them.</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2667,7 +2651,7 @@
       <c r="AB14" t="inlineStr">
         <is>
           <t>Gulf Fintech Daily — April 24, 2026
-AI as infrastructure. Sovereign capital as a catalyst. 5 stories.</t>
+AI as infrastructure. Sovereign capital as a catalyst. 5 stories below.</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2908,10 +2892,12 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>🇦🇪 We salute the nation’s heroes 
-We value your commitment and have designed exclusive banking benefits for your peace of mind.
-📈 Attractive finance profit rates
-🏦 Zero processing fees https://t.co/Q8zlLDLLW1</t>
+          <t>⏳Payment holidays
+🎁 Exclusive prizes with Kunooz Millionaire Account
+Terms and conditions apply.
+Know more
+https://t.co/OfDhWyedzP
+#EmiratesIslamic #FrontlineHeroes</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2982,26 +2968,27 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>🇦🇪 We salute the nation’s heroes 
-We value your commitment and have designed exclusive banking benefits for your peace of mind.
-📈 Attractive finance profit rates
-🏦 Zero processing fees https://t.co/Q8zlLDLLW1</t>
+          <t>⏳Payment holidays
+🎁 Exclusive prizes with Kunooz Millionaire Account
+Terms and conditions apply.
+Know more
+https://t.co/OfDhWyedzP
+#EmiratesIslamic #FrontlineHeroes</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>🇦🇪 We salute the nation’s heroes 
-We value your commitment and have designed exclusive banking benefits for your peace of mind.
-📈 Attractive finance profit rates
-🏦 Zero processing fees https://t.co/Q8zlLDLLW1</t>
+          <t>⏳Payment holidays
+🎁 Exclusive prizes with Kunooz Millionaire Account
+Terms and conditions apply.
+Know more
+https://t.co/OfDhWyedzP
+#EmiratesIslamic #FrontlineHeroes</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>We salute the nation’s heroes 
-We value your commitment and have designed exclusive banking benefits for your peace of mind.
-Attractive finance profit rates
-Zero processing fees</t>
+          <t>Payment holidays Exclusive prizes with Kunooz Millionaire Account Terms and conditions apply. Know more</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -3032,7 +3019,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>We salute the nation’s heroes We value your commitment and have designed exclusive banking benefits for your peace of mind. • Attractive finance profit rates Zero processing fees</t>
+          <t>Payment holidays Exclusive prizes with Kunooz Millionaire Account Terms and conditions apply.</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -3683,7 +3670,7 @@
         <is>
           <t>A greeting of appreciation and gratitude to the heroes of the nation
 In recognition of your dedication and commitment to serving the nation, we have designed an exclusive package of banking benefits to give you peace of mind. 
-Special profit rates on financing.</t>
+Special profit rates on financing</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3714,7 +3701,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Special profit rates on financing.</t>
+          <t>Special profit rates on financing</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3767,6 +3754,69 @@
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
+        <is>
+          <t>🏦 بدون رسوم إجراءات
+⏳ تأجيل الأقساط
+🎁 جوائز حصرية مع حساب كنوز المليونير
+تطبق الشروط والأحكام.
+لمعرفة المزيد، تفضل بزيارة
+https://t.co/N2GRIcHWnS
+#الإمارات_الإسلامي #أبطال_الوطن</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>🏦 بدون رسوم إجراءات
+⏳ تأجيل الأقساط
+🎁 جوائز حصرية مع حساب كنوز المليونير
+تطبق الشروط والأحكام.
+لمعرفة المزيد، تفضل بزيارة
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=front_line"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23أبطال_الوطن"&gt;#أبطال_الوطن&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>9h</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 4:42 PM UTC</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="n">
+        <v>46136.69583333333</v>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=front_line', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23أبطال_الوطن']</t>
+        </is>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>212</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
         <is>
           <t>🏦 بدون رسوم إجراءات
 ⏳ تأجيل الأقساط
@@ -3777,174 +3827,12 @@
 #الإمارات_الإسلامي #أبطال_الوطن</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>🏦 بدون رسوم إجراءات
-⏳ تأجيل الأقساط
-🎁 جوائز حصرية مع حساب كنوز المليونير
-تطبق الشروط والأحكام.
-لمعرفة المزيد، تفضل بزيارة
-&lt;a href="https://www.emiratesislamic.ae/ar/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=front_line"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23أبطال_الوطن"&gt;#أبطال_الوطن&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K21" t="b">
-        <v>0</v>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>9h</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 4:42 PM UTC</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="n">
-        <v>46136.69583333333</v>
-      </c>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=front_line', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23أبطال_الوطن']</t>
-        </is>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>212</v>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>🏦 بدون رسوم إجراءات
-⏳ تأجيل الأقساط
-🎁 جوائز حصرية مع حساب كنوز المليونير
-تطبق الشروط والأحكام.
-لمعرفة المزيد، تفضل بزيارة
-emiratesislamic.ae/ar/offers…
-#الإمارات_الإسلامي #أبطال_الوطن</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>🏦 بدون رسوم إجراءات
-⏳ تأجيل الأقساط
-🎁 جوائز حصرية مع حساب كنوز المليونير
-تطبق الشروط والأحكام.
-لمعرفة المزيد، تفضل بزيارة
-emiratesislamic.ae/ar/offers…
-#الإمارات_الإسلامي #أبطال_الوطن</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>No processing fees  
-Installments deferred  
-Exclusive rewards with Millionaire Treasures account  
-Terms and conditions apply.  
-To learn more, please visit  
-emiratesislamic.ae/ar/offers…  
-#EmiratesIslamic #NationHeroes</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="AE21" s="2" t="n">
-        <v>46136.8625</v>
-      </c>
-      <c r="AF21" s="2" t="n">
-        <v>46136</v>
-      </c>
-      <c r="AG21" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>No processing fees Installments deferred Exclusive rewards with Millionaire Treasures account Terms and conditions apply. • To learn more, please visit emiratesislamic.ae/ar/offers… #EmiratesIslamic #NationHeroes</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK21" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2047717917324710124</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047717917324710124</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047717920193622257</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
         <is>
           <t>🏦 بدون رسوم إجراءات
 ⏳ تأجيل الأقساط
@@ -3955,63 +3843,7 @@
 #الإمارات_الإسلامي #أبطال_الوطن</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>🇦🇪 تحية تقدير وامتنان لأبطال الوطن
-تقديراً لإخلاصك وتفانيك في خدمة الوطن، قمنا بتصميم باقة حصرية من المزايا المصرفية لنمنحك راحة البال.
-📈 معدلات أرباح مميزة على التمويل</t>
-        </is>
-      </c>
-      <c r="K22" t="b">
-        <v>0</v>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>9h</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 4:42 PM UTC</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="n">
-        <v>46136.69583333333</v>
-      </c>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>36</v>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>🇦🇪 تحية تقدير وامتنان لأبطال الوطن
-تقديراً لإخلاصك وتفانيك في خدمة الوطن، قمنا بتصميم باقة حصرية من المزايا المصرفية لنمنحك راحة البال.
-📈 معدلات أرباح مميزة على التمويل</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047717917324710124</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>🏦 بدون رسوم إجراءات
 ⏳ تأجيل الأقساط
@@ -4022,18 +3854,7 @@
 #الإمارات_الإسلامي #أبطال_الوطن</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>🏦 بدون رسوم إجراءات
-⏳ تأجيل الأقساط
-🎁 جوائز حصرية مع حساب كنوز المليونير
-تطبق الشروط والأحكام.
-لمعرفة المزيد، تفضل بزيارة
-https://t.co/N2GRIcHWnS
-#الإمارات_الإسلامي #أبطال_الوطن</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>No processing fees  
 Installments deferred  
@@ -4041,7 +3862,161 @@
 Terms and conditions apply.  
 To learn more, please visit  
 https://t.co/N2GRIcHWnS  
-#EmiratesIslamic #NationHeroes</t>
+#EmiratesIslamic #HeroesOfTheNation</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AE21" s="2" t="n">
+        <v>46136.8625</v>
+      </c>
+      <c r="AF21" s="2" t="n">
+        <v>46136</v>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>2. Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>No processing fees Installments deferred Exclusive rewards with Millionaire Treasures account Terms and conditions apply. • To learn more, please visit https://t.co/N2GRIcHWnS #EmiratesIslamic #HeroesOfTheNation</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AK21" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2047717917324710124</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047717917324710124</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>🇦🇪 تحية تقدير وامتنان لأبطال الوطن
+تقديراً لإخلاصك وتفانيك في خدمة الوطن، قمنا بتصميم باقة حصرية من المزايا المصرفية لنمنحك راحة البال.
+📈 معدلات أرباح مميزة على التمويل</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>🇦🇪 تحية تقدير وامتنان لأبطال الوطن
+تقديراً لإخلاصك وتفانيك في خدمة الوطن، قمنا بتصميم باقة حصرية من المزايا المصرفية لنمنحك راحة البال.
+📈 معدلات أرباح مميزة على التمويل</t>
+        </is>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>9h</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 4:42 PM UTC</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>46136.69583333333</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>36</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>🇦🇪 تحية تقدير وامتنان لأبطال الوطن
+تقديراً لإخلاصك وتفانيك في خدمة الوطن، قمنا بتصميم باقة حصرية من المزايا المصرفية لنمنحك راحة البال.
+📈 معدلات أرباح مميزة على التمويل</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>🇦🇪 تحية تقدير وامتنان لأبطال الوطن
+تقديراً لإخلاصك وتفانيك في خدمة الوطن، قمنا بتصميم باقة حصرية من المزايا المصرفية لنمنحك راحة البال.
+📈 معدلات أرباح مميزة على التمويل</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>A greeting of appreciation and gratitude to the heroes of the nation
+In recognition of your dedication and commitment to serving the nation, we have designed an exclusive package of banking benefits to give you peace of mind. 
+Exceptional profit rates on financing</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -4072,7 +4047,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>No processing fees Installments deferred Exclusive rewards with Millionaire Treasures account Terms and conditions apply. • To learn more, please visit https://t.co/N2GRIcHWnS #EmiratesIslamic #NationHeroes</t>
+          <t>Exceptional profit rates on financing</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -5078,7 +5053,7 @@
         <is>
           <t>Transfer your salary now and enjoy rewarding benefits and guaranteed cashback of up to AED 6,000! 
 Enjoy more rewards:
-Exclusive Credit Card benefits, airport lounge access, rewards and more.</t>
+Exclusive credit card benefits, airport lounge access, rewards, and more.</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -5109,7 +5084,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Transfer your salary now and enjoy rewarding benefits and guaranteed cashback of up to AED 6,000! • Enjoy more rewards: Exclusive Credit Card benefits, airport lounge access, rewards and more.</t>
+          <t>Transfer your salary now and enjoy rewarding benefits and guaranteed cashback of up to AED 6,000! • Enjoy more rewards: Exclusive credit card benefits, airport lounge access, rewards, and more.</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -5315,9 +5290,12 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
-استمتع بالمزيد من المكافآت:
-💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد https://t.co/DfoSsbwLQd</t>
+          <t>💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني
+🎁 مكافأة 100 درهم مع حساب ALPHA للأبناء
+وغير ذلك الكثير.
+يسري العرض لغاية 31 مايو 2026.
+تطبق الشروط والأحكام.
+emiratesislamic.ae/en/offers…</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -5381,30 +5359,26 @@
 emiratesislamic.ae/en/offers…</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047632125583605871</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
-استمتع بالمزيد من المكافآت:
-💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد https://t.co/DfoSsbwLQd</t>
-        </is>
-      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
-استمتع بالمزيد من المكافآت:
-💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد https://t.co/DfoSsbwLQd</t>
+          <t>💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني
+🎁 مكافأة 100 درهم مع حساب ALPHA للأبناء
+وغير ذلك الكثير.
+يسري العرض لغاية 31 مايو 2026.
+تطبق الشروط والأحكام.
+emiratesislamic.ae/en/offers…</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Transfer your salary now and enjoy special benefits and guaranteed cash back of up to 6,000 dirhams!
-Enjoy more rewards:
-💳 Exclusive benefits on the credit card, access to airport lounges, rewards, and more.</t>
+          <t>Competitive profit rates on auto financing and housing financing  
+A 100 dirham reward with the ALPHA account for children  
+And much more.  
+The offer is valid until May 31, 2026.  
+Terms and conditions apply.  
+emiratesislamic.ae/en/offers…</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -5435,7 +5409,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Transfer your salary now and enjoy special benefits and guaranteed cash back of up to 6,000 dirhams! • Enjoy more rewards: 💳 Exclusive benefits on the credit card, access to airport lounges, rewards, and more.</t>
+          <t>Competitive profit rates on auto financing and housing financing A 100 dirham reward with the ALPHA account for children And much more. • The offer is valid until May 31, 2026. • Terms and conditions apply.</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -5491,7 +5465,7 @@
         <is>
           <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
 استمتع بالمزيد من المكافآت:
-💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد</t>
+💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد https://t.co/DfoSsbwLQd</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -5545,18 +5519,28 @@
 💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="inlineStr">
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047632116649689120</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
         <is>
           <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
 استمتع بالمزيد من المكافآت:
-💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد</t>
+💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد https://t.co/DfoSsbwLQd</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
+استمتع بالمزيد من المكافآت:
+💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد https://t.co/DfoSsbwLQd</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Transfer your salary now and enjoy special benefits and guaranteed cash back of up to 6,000 dirhams!
+          <t>Transfer your salary now and enjoy special benefits and earn guaranteed cash back of up to 6,000 dirhams!
 Enjoy more rewards:
 💳 Exclusive benefits on the credit card, access to airport lounges, rewards, and more.</t>
         </is>
@@ -5589,7 +5573,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Transfer your salary now and enjoy special benefits and guaranteed cash back of up to 6,000 dirhams! • Enjoy more rewards: 💳 Exclusive benefits on the credit card, access to airport lounges, rewards, and more.</t>
+          <t>Transfer your salary now and enjoy special benefits and earn guaranteed cash back of up to 6,000 dirhams! • Enjoy more rewards: 💳 Exclusive benefits on the credit card, access to airport lounges, rewards, and more.</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -6544,7 +6528,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>I raised an email to customer care regarding the discrepancy in the flight amount deduction twice but didn't hear from Emirates NBD. This is not acceptable at all. I am very disappointed with the customer care service of Emirates NBD. Zero stars.</t>
+          <t>I raised a mail to customer care regarding the flight amount deduction discrepancy twice but didn't hear from Emirates NBD. This is not acceptable at all. I am very disappointed with the customer care service of Emirates NBD. Zero stars.</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -6575,7 +6559,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>I raised an email to customer care regarding the discrepancy in the flight amount deduction twice but didn't hear from Emirates NBD. • I am very disappointed with the customer care service of Emirates NBD. • This is not acceptable at all.</t>
+          <t>I raised a mail to customer care regarding the flight amount deduction discrepancy twice but didn't hear from Emirates NBD. • I am very disappointed with the customer care service of Emirates NBD. • This is not acceptable at all.</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -7021,7 +7005,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>I have a problem with the card and when I try to withdraw from it, it says (system error), even though there is a balance. Unfortunately, your customer service is not cooperating at all.</t>
+          <t>I have a problem with my card and when I try to withdraw from it, it says (system error) even though there is a balance. Unfortunately, your customer service is not cooperative at all.</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -7052,7 +7036,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>I have a problem with the card and when I try to withdraw from it, it says (system error), even though there is a balance. • Unfortunately, your customer service is not cooperating at all.</t>
+          <t>I have a problem with my card and when I try to withdraw from it, it says (system error) even though there is a balance. • Unfortunately, your customer service is not cooperative at all.</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
@@ -7106,8 +7090,7 @@
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Very disappointed with @ENBDdeals 
-I moved from UAE since Sept 2025 and I’m paying my bills every month by 23rd. Since I’m out of country I won’t be having same time zone and I always see glitch in the ENBD app . I see the outstanding balance keep changing every time</t>
+          <t>As I was late to university I thought just downloading and then going through so I just opened and saw that I have been charged on JAN and Feb and so I contacted ENBD CS again and asked them to revert the previous charges and they told me they can only remove for April which</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -7157,26 +7140,16 @@
           <t>As I was late to university I thought just downloading and then going through so I just opened and saw that I have been charged on JAN and Feb and so I contacted ENBD CS again and asked them to revert the previous charges and they told me they can only remove for April which</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>https://x.com/ren_fernz/status/2047629586435817682</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>Very disappointed with @ENBDdeals 
-I moved from UAE since Sept 2025 and I’m paying my bills every month by 23rd. Since I’m out of country I won’t be having same time zone and I always see glitch in the ENBD app . I see the outstanding balance keep changing every time</t>
-        </is>
-      </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>Very disappointed with @ENBDdeals 
-I moved from UAE since Sept 2025 and I’m paying my bills every month by 23rd. Since I’m out of country I won’t be having same time zone and I always see glitch in the ENBD app . I see the outstanding balance keep changing every time</t>
+          <t>As I was late to university I thought just downloading and then going through so I just opened and saw that I have been charged on JAN and Feb and so I contacted ENBD CS again and asked them to revert the previous charges and they told me they can only remove for April which</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Very disappointed with @ENBDdeals. I moved from the UAE in September 2025 and I’m paying my bills every month by the 23rd. Since I’m out of the country, I won’t be in the same time zone and I always see glitches in the ENBD app. I notice the outstanding balance keeps changing every time.</t>
+          <t>As I was late to university, I thought I would just download and go through it, so I opened it and saw that I had been charged in January and February. I contacted ENBD customer service again and asked them to reverse the previous charges, and they told me they could only remove the charges for April.</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -7207,7 +7180,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>I moved from the UAE in September 2025 and I’m paying my bills every month by the 23rd. • Since I’m out of the country, I won’t be in the same time zone and I always see glitches in the ENBD app. • I notice the outstanding balance keeps changing every time.</t>
+          <t>I contacted ENBD customer service again and asked them to reverse the previous charges, and they told me they could only remove the charges for April. • As I was late to university, I thought I would just download and go through it, so I opened it and saw that I had been charged in January and February.</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">

--- a/check2.xlsx
+++ b/check2.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL41"/>
+  <dimension ref="A1:AL28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,49 +625,51 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2047809819265110291</t>
+          <t>2048234825199526119</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/karim_alharby/status/2047809819265110291</t>
+          <t>https://x.com/theprabhakars/status/2048234825199526119</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/karim_alharby</t>
+          <t>https://x.com/theprabhakars</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>karim_alharby</t>
+          <t>theprabhakars</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>KARIM 🎩</t>
+          <t>Prabhakar Singh Bais</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2042555658277654530/6XppkQ5x_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1985403950192033792/czvUF0FN_bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>حبيت أفتح حساب جولد في بنك المشرق لقيتهم عاوزني ابقى مليونير علشان يبدأو معايا الكلام بسم الله يا سيد الناس خد الشروط..
-راتبك 80 الف درهم فيما فوق 
-رصيدك مينزلش عن 500 الف درهم 
-كان في شرط تالت ورابع قومت فاتح المحفظة وبايس كروت ADCB و ENBD و البنك الأهلي المصري وصليت ركعتين شكر</t>
+          <t>India and New Zealand are set to sign a Free Trade Agreement (FTA) on 27 April, with the aim to more than double bilateral trade to $5 billion in five years.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>حبيت أفتح حساب جولد في بنك المشرق لقيتهم عاوزني ابقى مليونير علشان يبدأو معايا الكلام بسم الله يا سيد الناس خد الشروط..
-راتبك 80 الف درهم فيما فوق 
-رصيدك مينزلش عن 500 الف درهم 
-كان في شرط تالت ورابع قومت فاتح المحفظة وبايس كروت ADCB و ENBD و البنك الأهلي المصري وصليت ركعتين شكر</t>
+          <t>IDBI बैंक विनिवेश: क्या है ताजा अपडेट? 
+​IDBI बैंक के निजीकरण की प्रक्रिया एक बार फिर चर्चा में है। बाजार में चल रही ताजा रिपोर्ट्स के अनुसार, इस बड़े सौदे से जुड़ी कुछ महत्वपूर्ण बातें सामने आ रही हैं:
+​प्रमुख दावेदार: दुबई का Emirates NBD और कनाडा का Fairfax Group इस रेस में आगे बताए जा रहे हैं। दोनों की नजर बैंक में करीब 60.7% हिस्सेदारी पर है।
+​सरकार और LIC की भूमिका: भारत सरकार और LIC अपनी हिस्सेदारी बेचने की तैयारी में हैं। यह बैंकिंग सेक्टर के सबसे बड़े विनिवेश सौदों में से एक हो सकता है।
+​RBI की जांच जारी: वर्तमान में रिज़र्व बैंक (RBI) संभावित खरीदारों का Fit and Proper टेस्ट कर रहा है। बैंकिंग लाइसेंस के नियमों के तहत यह एक अनिवार्य और कड़ी प्रक्रिया है।
+​लक्ष्य: सरकार इस पूरी प्रक्रिया को अगले वित्त वर्ष तक पूरा करने का प्रयास कर रही है।
+​निष्कर्ष:
+हालांकि चर्चाएं तेज हैं, लेकिन अंतिम निर्णय RBI की मंजूरी और औपचारिक वित्तीय बोलियों के बाद ही होगा। बैंकिंग सेक्टर में यह बदलाव आने वाले समय में काफी दिलचस्प हो सकता है।
+​&lt;a href="/search?f=tweets&amp;amp;q=%23IDBIBank"&gt;#IDBIBank&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23BankingNews"&gt;#BankingNews&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EconomyUpdate"&gt;#EconomyUpdate&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Disinvestment"&gt;#Disinvestment&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23StockMarketIndia"&gt;#StockMarketIndia&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FinanceNews"&gt;#FinanceNews&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K2" t="b">
@@ -677,19 +679,23 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>3h</t>
+          <t>1h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 10:48 PM UTC</t>
+          <t>Apr 26, 2026 · 2:56 AM UTC</t>
         </is>
       </c>
       <c r="P2" s="2" t="n">
-        <v>46136.95</v>
+        <v>46138.12222222222</v>
       </c>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23IDBIBank', 'https://x.com/search?f=tweets&amp;q=%23BankingNews', 'https://x.com/search?f=tweets&amp;q=%23EconomyUpdate', 'https://x.com/search?f=tweets&amp;q=%23Disinvestment', 'https://x.com/search?f=tweets&amp;q=%23StockMarketIndia', 'https://x.com/search?f=tweets&amp;q=%23FinanceNews']</t>
+        </is>
+      </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
@@ -697,10 +703,10 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1905</v>
+        <v>27</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -709,37 +715,35 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>حبيت أفتح حساب جولد في بنك المشرق لقيتهم عاوزني ابقى مليونير علشان يبدأو معايا الكلام بسم الله يا سيد الناس خد الشروط..
-راتبك 80 الف درهم فيما فوق 
-رصيدك مينزلش عن 500 الف درهم 
-كان في شرط تالت ورابع قومت فاتح المحفظة وبايس كروت ADCB و ENBD و البنك الأهلي المصري وصليت ركعتين شكر</t>
+          <t>IDBI बैंक विनिवेश: क्या है ताजा अपडेट? 
+​IDBI बैंक के निजीकरण की प्रक्रिया एक बार फिर चर्चा में है। बाजार में चल रही ताजा रिपोर्ट्स के अनुसार, इस बड़े सौदे से जुड़ी कुछ महत्वपूर्ण बातें सामने आ रही हैं:
+​प्रमुख दावेदार: दुबई का Emirates NBD और कनाडा का Fairfax Group इस रेस में आगे बताए जा रहे हैं। दोनों की नजर बैंक में करीब 60.7% हिस्सेदारी पर है।
+​सरकार और LIC की भूमिका: भारत सरकार और LIC अपनी हिस्सेदारी बेचने की तैयारी में हैं। यह बैंकिंग सेक्टर के सबसे बड़े विनिवेश सौदों में से एक हो सकता है।
+​RBI की जांच जारी: वर्तमान में रिज़र्व बैंक (RBI) संभावित खरीदारों का Fit and Proper टेस्ट कर रहा है। बैंकिंग लाइसेंस के नियमों के तहत यह एक अनिवार्य और कड़ी प्रक्रिया है।
+​लक्ष्य: सरकार इस पूरी प्रक्रिया को अगले वित्त वर्ष तक पूरा करने का प्रयास कर रही है।
+​निष्कर्ष:
+हालांकि चर्चाएं तेज हैं, लेकिन अंतिम निर्णय RBI की मंजूरी और औपचारिक वित्तीय बोलियों के बाद ही होगा। बैंकिंग सेक्टर में यह बदलाव आने वाले समय में काफी दिलचस्प हो सकता है।
+​#IDBIBank #BankingNews #EconomyUpdate #Disinvestment #StockMarketIndia #FinanceNews</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>https://x.com/karim_alharby/status/2047809819265110291</t>
+          <t>https://x.com/theprabhakars/status/2048234825199526119</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>حبيت أفتح حساب جولد في بنك المشرق لقيتهم عاوزني ابقى مليونير علشان يبدأو معايا الكلام بسم الله يا سيد الناس خد الشروط..
-راتبك 80 الف درهم فيما فوق 
-رصيدك مينزلش عن 500 الف درهم 
-كان في شرط تالت ورابع قومت فاتح المحفظة وبايس كروت ADCB و ENBD و البنك الأهلي المصري وصليت ركعتين شكر</t>
+          <t>India and New Zealand are set to sign a Free Trade Agreement (FTA) on 27 April, with the aim to more than double bilateral trade to $5 billion in five years.</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>حبيت أفتح حساب جولد في بنك المشرق لقيتهم عاوزني ابقى مليونير علشان يبدأو معايا الكلام بسم الله يا سيد الناس خد الشروط..
-راتبك 80 الف درهم فيما فوق 
-رصيدك مينزلش عن 500 الف درهم 
-كان في شرط تالت ورابع قومت فاتح المحفظة وبايس كروت ADCB و ENBD و البنك الأهلي المصري وصليت ركعتين شكر</t>
+          <t>India and New Zealand are set to sign a Free Trade Agreement (FTA) on 27 April, with the aim to more than double bilateral trade to $5 billion in five years.</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>I wanted to open a gold account at Mashreq Bank, but they wanted me to be a millionaire for them to start talking to me. In the name of God, here are the conditions: 
-Your salary must be 80,000 dirhams or more, and your balance should not be less than 500,000 dirhams. There were third and fourth conditions, so I opened the account and linked it to ADCB, ENBD, and the National Bank of Egypt cards, and I prayed two units of gratitude.</t>
+          <t>India and New Zealand are set to sign a Free Trade Agreement (FTA) on April 27, aiming to more than double bilateral trade to $5 billion in five years.</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -753,10 +757,10 @@
         </is>
       </c>
       <c r="AE2" s="2" t="n">
-        <v>46137.11666666667</v>
+        <v>46138.28888888889</v>
       </c>
       <c r="AF2" s="2" t="n">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
@@ -770,7 +774,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>In the name of God, here are the conditions: Your salary must be 80,000 dirhams or more, and your balance should not be less than 500,000 dirhams. • There were third and fourth conditions, so I opened the account and linked it to ADCB, ENBD, and the National Bank of Egypt cards, and I prayed two units of gratitude. • I wanted to open a gold account at Mashreq Bank, but they wanted me to be a millionaire for them to start talking to me.</t>
+          <t>India and New Zealand are set to sign a Free Trade Agreement (FTA) on April 27, aiming to more than double bilateral trade to $5 billion in five years.</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -793,72 +797,67 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2047712208696614977</t>
+          <t>2048231285999759759</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/Barigiin7m/status/2047712208696614977</t>
+          <t>https://x.com/MultibaggAI/status/2048231285999759759</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/Barigiin7m</t>
+          <t>https://x.com/MultibaggAI</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Barigiin7m</t>
+          <t>MultibaggAI</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Barigi</t>
+          <t>multibagg.ai</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/2017665342756294656/o62zwaRv_bigger.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>سيارة حلمك تقدر تتملكها
-جديدة ولا مستعملة نمولها لك مع التمويل التأجيري للسيارات من بنك الإمارات دبي الوطني</t>
+          <t>RBLBANK: BOARD HAS PROPOSED DIVIDEND OF ₹1/SH, EMIRATES NBD STRATEGIC INVESTMENT SAID TO BE NEARING CLOSURE</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>اود تقديم قرض كيف أتواصل معكم</t>
+          <t>RBLBANK: BOARD HAS PROPOSED DIVIDEND OF ₹1/SH, EMIRATES NBD STRATEGIC INVESTMENT SAID TO BE NEARING CLOSURE</t>
         </is>
       </c>
       <c r="K3" t="b">
         <v>0</v>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_KSA']</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>1h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 4:20 PM UTC</t>
+          <t>Apr 26, 2026 · 2:42 AM UTC</t>
         </is>
       </c>
       <c r="P3" s="2" t="n">
-        <v>46136.68055555555</v>
+        <v>46138.1125</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -867,7 +866,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -876,29 +875,27 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>اود تقديم قرض كيف أتواصل معكم</t>
+          <t>RBLBANK: BOARD HAS PROPOSED DIVIDEND OF ₹1/SH, EMIRATES NBD STRATEGIC INVESTMENT SAID TO BE NEARING CLOSURE</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>https://x.com/Barigiin7m/status/2047712208696614977</t>
+          <t>https://x.com/MultibaggAI/status/2048231285999759759</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>سيارة حلمك تقدر تتملكها
-جديدة ولا مستعملة نمولها لك مع التمويل التأجيري للسيارات من بنك الإمارات دبي الوطني</t>
+          <t>RBLBANK: BOARD HAS PROPOSED DIVIDEND OF ₹1/SH, EMIRATES NBD STRATEGIC INVESTMENT SAID TO BE NEARING CLOSURE</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>سيارة حلمك تقدر تتملكها
-جديدة ولا مستعملة نمولها لك مع التمويل التأجيري للسيارات من بنك الإمارات دبي الوطني</t>
+          <t>RBLBANK: BOARD HAS PROPOSED DIVIDEND OF ₹1/SH, EMIRATES NBD STRATEGIC INVESTMENT SAID TO BE NEARING CLOSURE</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>You can own your dream car, whether new or used, with leasing financing for cars from Emirates NBD.</t>
+          <t>RBLBANK: THE BOARD HAS PROPOSED A DIVIDEND OF ₹1 PER SHARE, EMIRATES NBD STRATEGIC INVESTMENT IS REPORTEDLY NEARING CLOSURE.</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -908,14 +905,14 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE3" s="2" t="n">
-        <v>46136.84722222222</v>
+        <v>46138.27916666667</v>
       </c>
       <c r="AF3" s="2" t="n">
-        <v>46136</v>
+        <v>46138</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
@@ -929,7 +926,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>You can own your dream car, whether new or used, with leasing financing for cars from Emirates NBD.</t>
+          <t>RBLBANK: THE BOARD HAS PROPOSED A DIVIDEND OF ₹1 PER SHARE, EMIRATES NBD STRATEGIC INVESTMENT IS REPORTEDLY NEARING CLOSURE.</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -942,7 +939,7 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>EmiratesNBD_KSA</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -952,47 +949,45 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2047692986402643994</t>
+          <t>2048045177659404537</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2047692986402643994</t>
+          <t>https://x.com/Hafid505/status/2048045177659404537</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals</t>
+          <t>https://x.com/Hafid505</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ENBDdeals</t>
+          <t>Hafid505</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Emirates NBD Deals</t>
+          <t>Abdulhafid</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1763624422294814720/EmRI1Aqu_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1978176887374401536/PcrEaJ3v_bigger.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>باقة ورد لكل لحظة مميزة مع فلاورد 💐
-احصل على خصم 20% على تنسيقات الورود الأنيقة، حصريًا عبر تطبيق تستاهل.
-لمعرفة المزيد:
-https://t.co/quzlzhDcXR https://t.co/Pj8RmtMYOK</t>
+          <t>إقتراح تصميم مكينة الصراف الآلي لبنك الإمارات دبي الوطني،  على كورنيش خورفكان. 
+@EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Get an AED 500 Pet Corner Gift Card when you apply for an Emirates NBD noon One Visa Credit Card.
-Apply Now: &lt;a href="https://www.emiratesnbd.com/en/campaigns/noon-one-credit-card"&gt;emiratesnbd.com/en/campaigns…&lt;/a&gt;</t>
+          <t>إقتراح تصميم مكينة الصراف الآلي لبنك الإمارات دبي الوطني،  على كورنيش خورفكان. 
+&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K4" t="b">
@@ -1002,21 +997,21 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 3:03 PM UTC</t>
+          <t>Apr 25, 2026 · 2:23 PM UTC</t>
         </is>
       </c>
       <c r="P4" s="2" t="n">
-        <v>46136.62708333333</v>
+        <v>46137.59930555556</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t>['https://www.emiratesnbd.com/en/campaigns/noon-one-credit-card']</t>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="S4" t="n">
@@ -1026,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -1038,39 +1033,26 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Get an AED 500 Pet Corner Gift Card when you apply for an Emirates NBD noon One Visa Credit Card.
-Apply Now: emiratesnbd.com/en/campaigns…</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>https://x.com/ENBDdeals/status/2047692986402643994</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>باقة ورد لكل لحظة مميزة مع فلاورد 💐
-احصل على خصم 20% على تنسيقات الورود الأنيقة، حصريًا عبر تطبيق تستاهل.
-لمعرفة المزيد:
-https://t.co/quzlzhDcXR https://t.co/Pj8RmtMYOK</t>
-        </is>
-      </c>
+          <t>إقتراح تصميم مكينة الصراف الآلي لبنك الإمارات دبي الوطني،  على كورنيش خورفكان. 
+@EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>باقة ورد لكل لحظة مميزة مع فلاورد 💐
-احصل على خصم 20% على تنسيقات الورود الأنيقة، حصريًا عبر تطبيق تستاهل.
-لمعرفة المزيد:
-https://t.co/quzlzhDcXR https://t.co/Pj8RmtMYOK</t>
+          <t>إقتراح تصميم مكينة الصراف الآلي لبنك الإمارات دبي الوطني،  على كورنيش خورفكان. 
+@EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>A bouquet of flowers for every special moment with Flarowd 💐 Get a 20% discount on elegant flower arrangements, exclusively through the Testahl app. To learn more: https://t.co/quzlzhDcXR https://t.co/Pj8RmtMYOK</t>
+          <t>Proposal for the design of an ATM machine for Emirates NBD Bank, on the Corniche of Khorfakkan.</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Cust</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -1079,10 +1061,10 @@
         </is>
       </c>
       <c r="AE4" s="2" t="n">
-        <v>46136.79375</v>
+        <v>46137.76597222222</v>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
@@ -1096,7 +1078,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>A bouquet of flowers for every special moment with Flarowd 💐 Get a 20% discount on elegant flower arrangements, exclusively through the Testahl app. • To learn more: https://t.co/quzlzhDcXR https://t.co/Pj8RmtMYOK</t>
+          <t>Proposal for the design of an ATM machine for Emirates NBD Bank, on the Corniche of Khorfakkan.</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1119,69 +1101,117 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2047692228684878061</t>
+          <t>2048039331512864848</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/fortyxxl88/status/2047692228684878061</t>
+          <t>https://x.com/phd_capital/status/2048039331512864848</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/fortyxxl88</t>
+          <t>https://x.com/phd_capital</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>fortyxxl88</t>
+          <t>phd_capital</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>forty</t>
+          <t>PHD CAPITAL</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2043738450134749184/JdKcVTW__bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2045065540562259968/2sFZf-W-_bigger.png</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>الووووو .</t>
+          <t>#RBLBANK (#RBLBank) FY26 — The Turnaround is Real. Q4 Profit surges +233% YoY. Total Business crosses ₹2.5 Lakh Cr. The Emirates NBD era begins. 
+RBL Bank has delivered a pivotal "clean-up" year, exiting FY26 as a leaner, stronger, and significantly more valuable institution. While the profit surge is eye-popping, the real headline is the transformation into a foreign bank subsidiary, setting a massive valuation floor for the stock.
+Key Numbers:
+• Q4 PAT: ₹230 Cr (+233% YoY surge)
+• Annual PAT: ₹822 Cr (+18% YoY)
+• Total Business: ₹2.50 Lakh Cr (+24% YoY)
+• Gross NPA: 1.45% (Significant improvement from 1.88% QoQ)
+• CASA Ratio: 33.60% (Up from 30.90% QoQ)
+What's genuinely exciting:
+✅ The "Emirates NBD" Floor: The proposed $3 Billion acquisition for a 74% stake transforms RBL into a foreign bank subsidiary and provides immediate strategic alpha.
+✅ Asset Quality Triumph: GNPA at 1.45% and Net NPA at 0.39%. The legacy unsecured and microfinance (JLG) stress is effectively in the rearview mirror.
+✅ Deposit Granularity: Retail deposits (&lt;₹3 Cr) grew 16%, proving the bank is successfully rebuilding a stable, lower-cost funding base.
+✅ De-risking the Book: Reduced unsecured exposure (Cards/PL) to 24% from 28%. A safer, more balanced lending profile for the new cycle.
+✅ Liquidity Fortress: An LCR of 130% provides ample headroom for the next leg of credit deployment.
+What demands scrutiny:
+❌ NIM Erosion: Net Interest Margin (NIM) fell to 4.41% (a 5-quarter low). The rising cost of deposits is currently eating into the lending spread.
+❌ Operating RoE: Despite the profit jump, RoE remains in the mid-single digits (~5.5%). Capital efficiency needs to scale toward 10%+ in FY27.
+❌ FDI Regulatory Risk: The $3B deal still awaits final government/RBI clearance; any delay remains a sentiment wildcard.
+❌ Unsecured Slippages: While the overall share is down, fresh slippages in the retail book still require a hawk’s eye as the portfolio seasons.
+The number nobody is talking about
+RBL’s CASA jump of 26% QoQ (to ₹46,723 Cr). While most mid-cap banks are struggling to hold on to low-cost deposits, RBL managed a massive sequential surge. This suggests the branch-led sourcing strategy is finally working, providing the fuel needed to defend margins in FY27.
+The thesis is compelling
+RBL Bank is a classic "Deep Value Turnaround" play. With asset quality now better than several PSU peers and a global giant (Emirates NBD) coming in at a premium valuation, the structural re-rating has just begun.
+₹2.5 Lakh Cr Business. 233% Profit Surge. Asset quality is clean, now the focus shifts to Margin expansion.
+#RBLBank #BankingSector #StockMarketIndia #FundamentalAnalysis #Investing #PHDCapital #EquityResearch #NiftyBank #TurnaroundStory</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>الووووو .</t>
+          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23RBLBANK"&gt;#RBLBANK&lt;/a&gt; (&lt;a href="/search?f=tweets&amp;amp;q=%23RBLBank"&gt;#RBLBank&lt;/a&gt;) FY26 — The Turnaround is Real. Q4 Profit surges +233% YoY. Total Business crosses ₹2.5 Lakh Cr. The Emirates NBD era begins. 
+RBL Bank has delivered a pivotal &amp;#34;clean-up&amp;#34; year, exiting FY26 as a leaner, stronger, and significantly more valuable institution. While the profit surge is eye-popping, the real headline is the transformation into a foreign bank subsidiary, setting a massive valuation floor for the stock.
+Key Numbers:
+• Q4 PAT: ₹230 Cr (+233% YoY surge)
+• Annual PAT: ₹822 Cr (+18% YoY)
+• Total Business: ₹2.50 Lakh Cr (+24% YoY)
+• Gross NPA: 1.45% (Significant improvement from 1.88% QoQ)
+• CASA Ratio: 33.60% (Up from 30.90% QoQ)
+What&amp;#39;s genuinely exciting:
+✅ The &amp;#34;Emirates NBD&amp;#34; Floor: The proposed $3 Billion acquisition for a 74% stake transforms RBL into a foreign bank subsidiary and provides immediate strategic alpha.
+✅ Asset Quality Triumph: GNPA at 1.45% and Net NPA at 0.39%. The legacy unsecured and microfinance (JLG) stress is effectively in the rearview mirror.
+✅ Deposit Granularity: Retail deposits (&amp;lt;₹3 Cr) grew 16%, proving the bank is successfully rebuilding a stable, lower-cost funding base.
+✅ De-risking the Book: Reduced unsecured exposure (Cards/PL) to 24% from 28%. A safer, more balanced lending profile for the new cycle.
+✅ Liquidity Fortress: An LCR of 130% provides ample headroom for the next leg of credit deployment.
+What demands scrutiny:
+❌ NIM Erosion: Net Interest Margin (NIM) fell to 4.41% (a 5-quarter low). The rising cost of deposits is currently eating into the lending spread.
+❌ Operating RoE: Despite the profit jump, RoE remains in the mid-single digits (~5.5%). Capital efficiency needs to scale toward 10%+ in FY27.
+❌ FDI Regulatory Risk: The $3B deal still awaits final government/RBI clearance; any delay remains a sentiment wildcard.
+❌ Unsecured Slippages: While the overall share is down, fresh slippages in the retail book still require a hawk’s eye as the portfolio seasons.
+The number nobody is talking about
+RBL’s CASA jump of 26% QoQ (to ₹46,723 Cr). While most mid-cap banks are struggling to hold on to low-cost deposits, RBL managed a massive sequential surge. This suggests the branch-led sourcing strategy is finally working, providing the fuel needed to defend margins in FY27.
+The thesis is compelling
+RBL Bank is a classic &amp;#34;Deep Value Turnaround&amp;#34; play. With asset quality now better than several PSU peers and a global giant (Emirates NBD) coming in at a premium valuation, the structural re-rating has just begun.
+₹2.5 Lakh Cr Business. 233% Profit Surge. Asset quality is clean, now the focus shifts to Margin expansion.
+&lt;a href="/search?f=tweets&amp;amp;q=%23RBLBank"&gt;#RBLBank&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23BankingSector"&gt;#BankingSector&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23StockMarketIndia"&gt;#StockMarketIndia&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FundamentalAnalysis"&gt;#FundamentalAnalysis&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Investing"&gt;#Investing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23PHDCapital"&gt;#PHDCapital&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EquityResearch"&gt;#EquityResearch&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23NiftyBank"&gt;#NiftyBank&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23TurnaroundStory"&gt;#TurnaroundStory&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K5" t="b">
         <v>0</v>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_KSA']</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 3:00 PM UTC</t>
+          <t>Apr 25, 2026 · 2:00 PM UTC</t>
         </is>
       </c>
       <c r="P5" s="2" t="n">
-        <v>46136.625</v>
+        <v>46137.58333333334</v>
       </c>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23RBLBANK', 'https://x.com/search?f=tweets&amp;q=%23RBLBank', 'https://x.com/search?f=tweets&amp;q=%23RBLBank', 'https://x.com/search?f=tweets&amp;q=%23BankingSector', 'https://x.com/search?f=tweets&amp;q=%23StockMarketIndia', 'https://x.com/search?f=tweets&amp;q=%23FundamentalAnalysis', 'https://x.com/search?f=tweets&amp;q=%23Investing', 'https://x.com/search?f=tweets&amp;q=%23PHDCapital', 'https://x.com/search?f=tweets&amp;q=%23EquityResearch', 'https://x.com/search?f=tweets&amp;q=%23NiftyBank', 'https://x.com/search?f=tweets&amp;q=%23TurnaroundStory']</t>
+        </is>
+      </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
@@ -1192,7 +1222,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>15</v>
+        <v>199</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1201,19 +1231,122 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>الووووو .</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
+          <t>#RBLBANK (#RBLBank) FY26 — The Turnaround is Real. Q4 Profit surges +233% YoY. Total Business crosses ₹2.5 Lakh Cr. The Emirates NBD era begins. 
+RBL Bank has delivered a pivotal "clean-up" year, exiting FY26 as a leaner, stronger, and significantly more valuable institution. While the profit surge is eye-popping, the real headline is the transformation into a foreign bank subsidiary, setting a massive valuation floor for the stock.
+Key Numbers:
+• Q4 PAT: ₹230 Cr (+233% YoY surge)
+• Annual PAT: ₹822 Cr (+18% YoY)
+• Total Business: ₹2.50 Lakh Cr (+24% YoY)
+• Gross NPA: 1.45% (Significant improvement from 1.88% QoQ)
+• CASA Ratio: 33.60% (Up from 30.90% QoQ)
+What's genuinely exciting:
+✅ The "Emirates NBD" Floor: The proposed $3 Billion acquisition for a 74% stake transforms RBL into a foreign bank subsidiary and provides immediate strategic alpha.
+✅ Asset Quality Triumph: GNPA at 1.45% and Net NPA at 0.39%. The legacy unsecured and microfinance (JLG) stress is effectively in the rearview mirror.
+✅ Deposit Granularity: Retail deposits (&lt;₹3 Cr) grew 16%, proving the bank is successfully rebuilding a stable, lower-cost funding base.
+✅ De-risking the Book: Reduced unsecured exposure (Cards/PL) to 24% from 28%. A safer, more balanced lending profile for the new cycle.
+✅ Liquidity Fortress: An LCR of 130% provides ample headroom for the next leg of credit deployment.
+What demands scrutiny:
+❌ NIM Erosion: Net Interest Margin (NIM) fell to 4.41% (a 5-quarter low). The rising cost of deposits is currently eating into the lending spread.
+❌ Operating RoE: Despite the profit jump, RoE remains in the mid-single digits (~5.5%). Capital efficiency needs to scale toward 10%+ in FY27.
+❌ FDI Regulatory Risk: The $3B deal still awaits final government/RBI clearance; any delay remains a sentiment wildcard.
+❌ Unsecured Slippages: While the overall share is down, fresh slippages in the retail book still require a hawk’s eye as the portfolio seasons.
+The number nobody is talking about
+RBL’s CASA jump of 26% QoQ (to ₹46,723 Cr). While most mid-cap banks are struggling to hold on to low-cost deposits, RBL managed a massive sequential surge. This suggests the branch-led sourcing strategy is finally working, providing the fuel needed to defend margins in FY27.
+The thesis is compelling
+RBL Bank is a classic "Deep Value Turnaround" play. With asset quality now better than several PSU peers and a global giant (Emirates NBD) coming in at a premium valuation, the structural re-rating has just begun.
+₹2.5 Lakh Cr Business. 233% Profit Surge. Asset quality is clean, now the focus shifts to Margin expansion.
+#RBLBank #BankingSector #StockMarketIndia #FundamentalAnalysis #Investing #PHDCapital #EquityResearch #NiftyBank #TurnaroundStory</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>https://x.com/phd_capital/status/2048039331512864848</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>#RBLBANK (#RBLBank) FY26 — The Turnaround is Real. Q4 Profit surges +233% YoY. Total Business crosses ₹2.5 Lakh Cr. The Emirates NBD era begins. 
+RBL Bank has delivered a pivotal "clean-up" year, exiting FY26 as a leaner, stronger, and significantly more valuable institution. While the profit surge is eye-popping, the real headline is the transformation into a foreign bank subsidiary, setting a massive valuation floor for the stock.
+Key Numbers:
+• Q4 PAT: ₹230 Cr (+233% YoY surge)
+• Annual PAT: ₹822 Cr (+18% YoY)
+• Total Business: ₹2.50 Lakh Cr (+24% YoY)
+• Gross NPA: 1.45% (Significant improvement from 1.88% QoQ)
+• CASA Ratio: 33.60% (Up from 30.90% QoQ)
+What's genuinely exciting:
+✅ The "Emirates NBD" Floor: The proposed $3 Billion acquisition for a 74% stake transforms RBL into a foreign bank subsidiary and provides immediate strategic alpha.
+✅ Asset Quality Triumph: GNPA at 1.45% and Net NPA at 0.39%. The legacy unsecured and microfinance (JLG) stress is effectively in the rearview mirror.
+✅ Deposit Granularity: Retail deposits (&lt;₹3 Cr) grew 16%, proving the bank is successfully rebuilding a stable, lower-cost funding base.
+✅ De-risking the Book: Reduced unsecured exposure (Cards/PL) to 24% from 28%. A safer, more balanced lending profile for the new cycle.
+✅ Liquidity Fortress: An LCR of 130% provides ample headroom for the next leg of credit deployment.
+What demands scrutiny:
+❌ NIM Erosion: Net Interest Margin (NIM) fell to 4.41% (a 5-quarter low). The rising cost of deposits is currently eating into the lending spread.
+❌ Operating RoE: Despite the profit jump, RoE remains in the mid-single digits (~5.5%). Capital efficiency needs to scale toward 10%+ in FY27.
+❌ FDI Regulatory Risk: The $3B deal still awaits final government/RBI clearance; any delay remains a sentiment wildcard.
+❌ Unsecured Slippages: While the overall share is down, fresh slippages in the retail book still require a hawk’s eye as the portfolio seasons.
+The number nobody is talking about
+RBL’s CASA jump of 26% QoQ (to ₹46,723 Cr). While most mid-cap banks are struggling to hold on to low-cost deposits, RBL managed a massive sequential surge. This suggests the branch-led sourcing strategy is finally working, providing the fuel needed to defend margins in FY27.
+The thesis is compelling
+RBL Bank is a classic "Deep Value Turnaround" play. With asset quality now better than several PSU peers and a global giant (Emirates NBD) coming in at a premium valuation, the structural re-rating has just begun.
+₹2.5 Lakh Cr Business. 233% Profit Surge. Asset quality is clean, now the focus shifts to Margin expansion.
+#RBLBank #BankingSector #StockMarketIndia #FundamentalAnalysis #Investing #PHDCapital #EquityResearch #NiftyBank #TurnaroundStory</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>الووووو .</t>
+          <t>#RBLBANK (#RBLBank) FY26 — The Turnaround is Real. Q4 Profit surges +233% YoY. Total Business crosses ₹2.5 Lakh Cr. The Emirates NBD era begins. 
+RBL Bank has delivered a pivotal "clean-up" year, exiting FY26 as a leaner, stronger, and significantly more valuable institution. While the profit surge is eye-popping, the real headline is the transformation into a foreign bank subsidiary, setting a massive valuation floor for the stock.
+Key Numbers:
+• Q4 PAT: ₹230 Cr (+233% YoY surge)
+• Annual PAT: ₹822 Cr (+18% YoY)
+• Total Business: ₹2.50 Lakh Cr (+24% YoY)
+• Gross NPA: 1.45% (Significant improvement from 1.88% QoQ)
+• CASA Ratio: 33.60% (Up from 30.90% QoQ)
+What's genuinely exciting:
+✅ The "Emirates NBD" Floor: The proposed $3 Billion acquisition for a 74% stake transforms RBL into a foreign bank subsidiary and provides immediate strategic alpha.
+✅ Asset Quality Triumph: GNPA at 1.45% and Net NPA at 0.39%. The legacy unsecured and microfinance (JLG) stress is effectively in the rearview mirror.
+✅ Deposit Granularity: Retail deposits (&lt;₹3 Cr) grew 16%, proving the bank is successfully rebuilding a stable, lower-cost funding base.
+✅ De-risking the Book: Reduced unsecured exposure (Cards/PL) to 24% from 28%. A safer, more balanced lending profile for the new cycle.
+✅ Liquidity Fortress: An LCR of 130% provides ample headroom for the next leg of credit deployment.
+What demands scrutiny:
+❌ NIM Erosion: Net Interest Margin (NIM) fell to 4.41% (a 5-quarter low). The rising cost of deposits is currently eating into the lending spread.
+❌ Operating RoE: Despite the profit jump, RoE remains in the mid-single digits (~5.5%). Capital efficiency needs to scale toward 10%+ in FY27.
+❌ FDI Regulatory Risk: The $3B deal still awaits final government/RBI clearance; any delay remains a sentiment wildcard.
+❌ Unsecured Slippages: While the overall share is down, fresh slippages in the retail book still require a hawk’s eye as the portfolio seasons.
+The number nobody is talking about
+RBL’s CASA jump of 26% QoQ (to ₹46,723 Cr). While most mid-cap banks are struggling to hold on to low-cost deposits, RBL managed a massive sequential surge. This suggests the branch-led sourcing strategy is finally working, providing the fuel needed to defend margins in FY27.
+The thesis is compelling
+RBL Bank is a classic "Deep Value Turnaround" play. With asset quality now better than several PSU peers and a global giant (Emirates NBD) coming in at a premium valuation, the structural re-rating has just begun.
+₹2.5 Lakh Cr Business. 233% Profit Surge. Asset quality is clean, now the focus shifts to Margin expansion.
+#RBLBank #BankingSector #StockMarketIndia #FundamentalAnalysis #Investing #PHDCapital #EquityResearch #NiftyBank #TurnaroundStory</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Hello.</t>
+          <t>RBL Bank FY26 — The Turnaround is Real. Q4 Profit surges +233% YoY. Total Business crosses ₹2.5 Lakh Cr. The Emirates NBD era begins.
+RBL Bank has delivered a pivotal "clean-up" year, exiting FY26 as a leaner, stronger, and significantly more valuable institution. While the profit surge is eye-popping, the real headline is the transformation into a foreign bank subsidiary, setting a massive valuation floor for the stock.
+Key Numbers:
+• Q4 PAT: ₹230 Cr (+233% YoY surge)
+• Annual PAT: ₹822 Cr (+18% YoY)
+• Total Business: ₹2.50 Lakh Cr (+24% YoY)
+• Gross NPA: 1.45% (Significant improvement from 1.88% QoQ)
+• CASA Ratio: 33.60% (Up from 30.90% QoQ)
+What's genuinely exciting:
+✅ The "Emirates NBD" Floor: The proposed $3 Billion acquisition for a 74% stake transforms RBL into a foreign bank subsidiary and provides immediate strategic alpha.
+✅ Asset Quality Triumph: GNPA at 1.45% and Net NPA at 0.39%. The legacy unsecured and microfinance (JLG) stress is effectively in the rearview mirror.
+✅ Deposit Granularity: Retail deposits (&lt;₹3 Cr) grew 16%, proving the bank is successfully rebuilding a stable, lower-cost funding base.
+✅ De-risking the Book: Reduced unsecured exposure (Cards/PL) to 24% from 28%. A safer, more balanced lending profile for the new cycle.
+✅ Liquidity Fortress: An LCR of 130% provides ample headroom for the next leg of credit deployment.
+What demands scrutiny:
+❌ NIM Erosion: Net Interest Margin (NIM) fell to 4.41% (a 5-quarter low). The rising cost of deposits is currently eating into the lending spread.
+❌ Operating RoE: Despite the profit jump, RoE remains in the mid-single digits (~5.5%). Capital efficiency needs to scale toward 10%+ in FY27.
+❌ FDI Regulatory Risk: The $3B deal still awaits final government/RBI clearance; any delay remains a sentiment wildcard.
+❌ Unsecured Slippages: While the overall share is down, fresh slippages in the retail book still require a hawk’s eye as the portfolio seasons.
+The number nobody is talking about
+RBL’s CASA jump of 26% QoQ (to ₹46,723 Cr). While most mid-cap banks are struggling to hold on to low-cost deposits, RBL managed a massive sequential surge. This suggests the branch-led sourcing strategy is finally working, providing the fuel needed to defend margins in FY27.
+The thesis is compelling
+RBL Bank is a classic "Deep Value Turnaround" play. With asset quality now better than several PSU peers and a global giant (Emirates NBD) coming in at a premium valuation, the structural re-rating has just begun.
+₹2.5 Lakh Cr Business. 233% Profit Surge. Asset quality is clean, now the focus shifts to Margin expansion.</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1227,10 +1360,10 @@
         </is>
       </c>
       <c r="AE5" s="2" t="n">
-        <v>46136.79166666666</v>
+        <v>46137.75</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
@@ -1244,7 +1377,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Hello.</t>
+          <t>While the profit surge is eye-popping, the real headline is the transformation into a foreign bank subsidiary, setting a massive valuation floor for the stock. • RBL Bank has delivered a pivotal "clean-up" year, exiting FY26 as a leaner, stronger, and significantly more valuable institution. • ✅ Deposit Granularity: Retail deposits (&lt;₹3 Cr) grew 16%, proving the bank is successfully rebuilding a stable, lower-cost funding base.</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1257,7 +1390,7 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>EmiratesNBD_KSA</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1267,81 +1400,86 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2047691273159528852</t>
+          <t>2048029415465242975</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/fortyxxl88/status/2047691273159528852</t>
+          <t>https://x.com/moneycontrolcom/status/2048029415465242975</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/fortyxxl88</t>
+          <t>https://x.com/moneycontrolcom</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>fortyxxl88</t>
+          <t>moneycontrolcom</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>forty</t>
+          <t>Moneycontrol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2043738450134749184/JdKcVTW__bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/841519699632447488/ea4043nJ_bigger.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>متى بتفعلون خدمة SAMSUNG PAY ؟
- @EmiratesNBD_KSA</t>
+          <t>#Banking | RBL Bank expects Emirates NBD deal closure in Q1 FY27, hinges on govt approval
+@malvisundaresan with details: 
+https://t.co/rvjEkgafEY 
+#RBLBank #Emirates</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>تشترون مديونية قطاع خاص غير معتمد ؟</t>
+          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23Banking"&gt;#Banking&lt;/a&gt; | RBL Bank expects Emirates NBD deal closure in Q1 FY27, hinges on govt approval
+&lt;a href="/malvisundaresan" title="Malvi Sundaresan"&gt;@malvisundaresan&lt;/a&gt; with details: 
+&lt;a href="https://www.moneycontrol.com/banking/rbl-bank-expects-emirates-nbd-deal-closure-in-q1-fy27-hinges-on-govt-approval-article-13899325.html?utm_medium=social&amp;amp;utm_source=twitter&amp;amp;utm_campaign=regular-editorial"&gt;moneycontrol.com/banking/rbl…&lt;/a&gt; 
+&lt;a href="/search?f=tweets&amp;amp;q=%23RBLBank"&gt;#RBLBank&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Emirates"&gt;#Emirates&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K6" t="b">
         <v>0</v>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_KSA']</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 2:56 PM UTC</t>
+          <t>Apr 25, 2026 · 1:20 PM UTC</t>
         </is>
       </c>
       <c r="P6" s="2" t="n">
-        <v>46136.62222222222</v>
+        <v>46137.55555555555</v>
       </c>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23Banking', 'https://x.com/malvisundaresan', 'https://www.moneycontrol.com/banking/rbl-bank-expects-emirates-nbd-deal-closure-in-q1-fy27-hinges-on-govt-approval-article-13899325.html?utm_medium=social&amp;utm_source=twitter&amp;utm_campaign=regular-editorial', 'https://x.com/search?f=tweets&amp;q=%23RBLBank', 'https://x.com/search?f=tweets&amp;q=%23Emirates']</t>
+        </is>
+      </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V6" t="n">
-        <v>13</v>
+        <v>2202</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1350,29 +1488,36 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>تشترون مديونية قطاع خاص غير معتمد ؟</t>
+          <t>#Banking | RBL Bank expects Emirates NBD deal closure in Q1 FY27, hinges on govt approval
+@malvisundaresan with details: 
+moneycontrol.com/banking/rbl… 
+#RBLBank #Emirates</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>https://x.com/fortyxxl88/status/2047691273159528852</t>
+          <t>https://x.com/moneycontrolcom/status/2048029415465242975</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>متى بتفعلون خدمة SAMSUNG PAY ؟
- @EmiratesNBD_KSA</t>
+          <t>#Banking | RBL Bank expects Emirates NBD deal closure in Q1 FY27, hinges on govt approval
+@malvisundaresan with details: 
+https://t.co/rvjEkgafEY 
+#RBLBank #Emirates</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>متى بتفعلون خدمة SAMSUNG PAY ؟
- @EmiratesNBD_KSA</t>
+          <t>#Banking | RBL Bank expects Emirates NBD deal closure in Q1 FY27, hinges on govt approval
+@malvisundaresan with details: 
+https://t.co/rvjEkgafEY 
+#RBLBank #Emirates</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>When will you activate the SAMSUNG PAY service?</t>
+          <t>RBL Bank expects the closure of the Emirates NBD deal in the first quarter of FY27, pending government approval.</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1386,10 +1531,10 @@
         </is>
       </c>
       <c r="AE6" s="2" t="n">
-        <v>46136.78888888889</v>
+        <v>46137.72222222222</v>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
@@ -1403,7 +1548,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>When will you activate the SAMSUNG PAY service?</t>
+          <t>RBL Bank expects the closure of the Emirates NBD deal in the first quarter of FY27, pending government approval.</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1416,7 +1561,7 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>EmiratesNBD_KSA</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1426,43 +1571,61 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2047678055070757117</t>
+          <t>2047998474441146821</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/abhiseksonusonu/status/2047678055070757117</t>
+          <t>https://x.com/EdgeOverHype/status/2047998474441146821</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://x.com/abhiseksonusonu</t>
+          <t>https://x.com/EdgeOverHype</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>abhiseksonusonu</t>
+          <t>EdgeOverHype</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>A R mishra</t>
+          <t>Edge Over Hype</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1912019334932611072/h2qIgZ-L_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2046645838068453376/rEjcgFgN_bigger.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>@LivBank @EmiratesNBD_AE  My issue regarding the credit card payment has now been successfully resolved.I would like to extend my sincere thanks to the bank’s support team for their prompt response and professional assistance throughout the process.Thank you once again.</t>
+          <t>$RBLBANK PAT up 234% YoY sounds massive.
+#RBLBank #PrivateBanks
+But dig in — most of that jump came from lower provisions (₹678 Cr vs ₹785 Cr) and a very low base last year, not a core income explosion.
+Meanwhile, NIM dropped to 4.41% — lowest in 5 quarters. The bank is earning less from each rupee it lends.
+The real story nobody's talking about yet:
+Emirates NBD is about to take 60-74% stake for ~$3 Bn. RBI + CCI approved. This bank is weeks away from becoming a foreign bank subsidiary.
+→ Loans up 23% YoY to ₹1.14L Cr
+→ Deposits up 25% to ₹1.39L Cr
+→ Bad loans (GNPA) down sharply: 2.60% → 1.45%
+→ But NIM falling: 4.89% → 4.41%
+I'm watching NIM more than PAT here. Growing loans fast while margins shrink is a pattern that can look great for a few quarters — until it doesn't.
+[1/2]</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>&lt;a href="/LivBank" title="Liv Digital Bank"&gt;@LivBank&lt;/a&gt; &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;  My issue regarding the credit card payment has now been successfully resolved.I would like to extend my sincere thanks to the bank’s support team for their prompt response and professional assistance throughout the process.Thank you once again.</t>
+          <t>The Emirates NBD deal changes everything about how to evaluate this bank.
+New parent. New capital. New identity. Possibly new strategy, new risk appetite, new cost structure.
+At this point you&amp;#39;re not just buying Q4 results — you&amp;#39;re betting on what RBL looks like under foreign ownership.
+Watch: Can NIM stabilize above 4.3% next 2 quarters? That&amp;#39;s the real test of whether this growth is profitable or just aggressive.
+Would you buy &lt;a href="/search?f=tweets&amp;amp;q=%23RBLBANK"&gt;$RBLBANK&lt;/a&gt; for the turnaround story — or does the ownership change make it too uncertain to bet on right now?
+For educational purposes only. Not SEBI registered investment advice.
+Bookmark 🔖 Follow + 🔔
+[2/2]</t>
         </is>
       </c>
       <c r="K7" t="b">
@@ -1472,25 +1635,25 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>12h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 2:04 PM UTC</t>
+          <t>Apr 25, 2026 · 11:17 AM UTC</t>
         </is>
       </c>
       <c r="P7" s="2" t="n">
-        <v>46136.58611111111</v>
+        <v>46137.47013888889</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>['https://x.com/LivBank', 'https://x.com/EmiratesNBD_AE']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23RBLBANK']</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1499,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>15</v>
+        <v>71</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1508,27 +1671,63 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>@LivBank @EmiratesNBD_AE  My issue regarding the credit card payment has now been successfully resolved.I would like to extend my sincere thanks to the bank’s support team for their prompt response and professional assistance throughout the process.Thank you once again.</t>
+          <t>The Emirates NBD deal changes everything about how to evaluate this bank.
+New parent. New capital. New identity. Possibly new strategy, new risk appetite, new cost structure.
+At this point you're not just buying Q4 results — you're betting on what RBL looks like under foreign ownership.
+Watch: Can NIM stabilize above 4.3% next 2 quarters? That's the real test of whether this growth is profitable or just aggressive.
+Would you buy $RBLBANK for the turnaround story — or does the ownership change make it too uncertain to bet on right now?
+For educational purposes only. Not SEBI registered investment advice.
+Bookmark 🔖 Follow + 🔔
+[2/2]</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>https://x.com/abhiseksonusonu/status/2047678055070757117</t>
+          <t>https://x.com/EdgeOverHype/status/2047998474441146821</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>@LivBank @EmiratesNBD_AE  My issue regarding the credit card payment has now been successfully resolved.I would like to extend my sincere thanks to the bank’s support team for their prompt response and professional assistance throughout the process.Thank you once again.</t>
+          <t>$RBLBANK PAT up 234% YoY sounds massive.
+#RBLBank #PrivateBanks
+But dig in — most of that jump came from lower provisions (₹678 Cr vs ₹785 Cr) and a very low base last year, not a core income explosion.
+Meanwhile, NIM dropped to 4.41% — lowest in 5 quarters. The bank is earning less from each rupee it lends.
+The real story nobody's talking about yet:
+Emirates NBD is about to take 60-74% stake for ~$3 Bn. RBI + CCI approved. This bank is weeks away from becoming a foreign bank subsidiary.
+→ Loans up 23% YoY to ₹1.14L Cr
+→ Deposits up 25% to ₹1.39L Cr
+→ Bad loans (GNPA) down sharply: 2.60% → 1.45%
+→ But NIM falling: 4.89% → 4.41%
+I'm watching NIM more than PAT here. Growing loans fast while margins shrink is a pattern that can look great for a few quarters — until it doesn't.
+[1/2]</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>@LivBank @EmiratesNBD_AE  My issue regarding the credit card payment has now been successfully resolved.I would like to extend my sincere thanks to the bank’s support team for their prompt response and professional assistance throughout the process.Thank you once again.</t>
+          <t>$RBLBANK PAT up 234% YoY sounds massive.
+#RBLBank #PrivateBanks
+But dig in — most of that jump came from lower provisions (₹678 Cr vs ₹785 Cr) and a very low base last year, not a core income explosion.
+Meanwhile, NIM dropped to 4.41% — lowest in 5 quarters. The bank is earning less from each rupee it lends.
+The real story nobody's talking about yet:
+Emirates NBD is about to take 60-74% stake for ~$3 Bn. RBI + CCI approved. This bank is weeks away from becoming a foreign bank subsidiary.
+→ Loans up 23% YoY to ₹1.14L Cr
+→ Deposits up 25% to ₹1.39L Cr
+→ Bad loans (GNPA) down sharply: 2.60% → 1.45%
+→ But NIM falling: 4.89% → 4.41%
+I'm watching NIM more than PAT here. Growing loans fast while margins shrink is a pattern that can look great for a few quarters — until it doesn't.
+[1/2]</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>My issue regarding the credit card payment has now been successfully resolved. I would like to extend my sincere thanks to the bank’s support team for their prompt response and professional assistance throughout the process. Thank you once again.</t>
+          <t>RBL Bank's profit after tax (PAT) is up 234% year-on-year, which sounds impressive. However, most of this increase is due to lower provisions (₹678 crore compared to ₹785 crore) and a very low base from last year, rather than a significant increase in core income. 
+Meanwhile, the net interest margin (NIM) has dropped to 4.41%, the lowest in five quarters, indicating that the bank is earning less from each rupee it lends. 
+The real story that hasn't been discussed yet is that Emirates NBD is about to acquire a 60-74% stake for approximately $3 billion, with approvals from the Reserve Bank of India (RBI) and the Competition Commission of India (CCI). This bank is just weeks away from becoming a foreign bank subsidiary.
+→ Loans have increased by 23% year-on-year to ₹1.14 lakh crore.  
+→ Deposits have risen by 25% to ₹1.39 lakh crore.  
+→ Bad loans (Gross Non-Performing Assets) have decreased significantly from 2.60% to 1.45%.  
+→ However, NIM is falling from 4.89% to 4.41%.  
+I am paying more attention to NIM than to PAT in this case. Rapidly growing loans while margins shrink is a trend that may appear favorable for a few quarters, but it can change quickly.</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1538,14 +1737,14 @@
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE7" s="2" t="n">
-        <v>46136.75277777778</v>
+        <v>46137.63680555556</v>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
@@ -1559,7 +1758,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>I would like to extend my sincere thanks to the bank’s support team for their prompt response and professional assistance throughout the process. • My issue regarding the credit card payment has now been successfully resolved.</t>
+          <t>However, most of this increase is due to lower provisions (₹678 crore compared to ₹785 crore) and a very low base from last year, rather than a significant increase in core income. • → Loans have increased by 23% year-on-year to ₹1.14 lakh crore. • RBL Bank's profit after tax (PAT) is up 234% year-on-year, which sounds impressive.</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1582,82 +1781,92 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2047666831612149831</t>
+          <t>2047968374798635160</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/AmalaAyesha/status/2047666831612149831</t>
+          <t>https://x.com/CNBCTV18Live/status/2047968374798635160</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://x.com/AmalaAyesha</t>
+          <t>https://x.com/CNBCTV18Live</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AmalaAyesha</t>
+          <t>CNBCTV18Live</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ayesha.amala</t>
+          <t>CNBC-TV18</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1525897615388327937/W-HZKLQ2_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2038419270393380864/bwlCFCb9_bigger.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>You get an unexpected payment request. What do you do?
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud
-https://t.co/YpRWtBZrhq</t>
+          <t>#4QWithCNBCTV18 | #RBLBank Says | From Concall
+--Have Received RBI &amp; CCI Approval For The Emirates NBD Deal; SEBI &amp; Govt Of India Nods Awaited
+---We issued 3.3 lakh cards in Q4
+--Our CASA ratio stands at 33.6%
+--Gross NPA Is Down 43 Bps QoQ And Net NPA Down 16 Bps QoQ
+--PCR At 73.6% And Credit Cost For Q4 At 65 Bps
+--Total CFAF At 14.25% &amp; CET-1 Ratio At 12.77%</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Is this biggest joke ?</t>
+          <t>&lt;a href="/search?f=tweets&amp;amp;q=%234QWithCNBCTV18"&gt;#4QWithCNBCTV18&lt;/a&gt; | &lt;a href="/search?f=tweets&amp;amp;q=%23RBLBank"&gt;#RBLBank&lt;/a&gt; Says | From Concall
+--Have Received RBI &amp;amp; CCI Approval For The Emirates NBD Deal; SEBI &amp;amp; Govt Of India Nods Awaited
+---We issued 3.3 lakh cards in Q4
+--Our CASA ratio stands at 33.6%
+--Gross NPA Is Down 43 Bps QoQ And Net NPA Down 16 Bps QoQ
+--PCR At 73.6% And Credit Cost For Q4 At 65 Bps
+--Total CFAF At 14.25% &amp;amp; CET-1 Ratio At 12.77%</t>
         </is>
       </c>
       <c r="K8" t="b">
         <v>0</v>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 1:19 PM UTC</t>
+          <t>Apr 25, 2026 · 9:18 AM UTC</t>
         </is>
       </c>
       <c r="P8" s="2" t="n">
-        <v>46136.55486111111</v>
+        <v>46137.3875</v>
       </c>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%234QWithCNBCTV18', 'https://x.com/search?f=tweets&amp;q=%23RBLBank']</t>
+        </is>
+      </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="V8" t="n">
-        <v>28</v>
+        <v>7953</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1666,32 +1875,31 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Is this biggest joke ?</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>https://x.com/AmalaAyesha/status/2047666831612149831</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>You get an unexpected payment request. What do you do?
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud
-https://t.co/YpRWtBZrhq</t>
-        </is>
-      </c>
+          <t>#4QWithCNBCTV18 | #RBLBank Says | From Concall
+--Have Received RBI &amp; CCI Approval For The Emirates NBD Deal; SEBI &amp; Govt Of India Nods Awaited
+---We issued 3.3 lakh cards in Q4
+--Our CASA ratio stands at 33.6%
+--Gross NPA Is Down 43 Bps QoQ And Net NPA Down 16 Bps QoQ
+--PCR At 73.6% And Credit Cost For Q4 At 65 Bps
+--Total CFAF At 14.25% &amp; CET-1 Ratio At 12.77%</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>You get an unexpected payment request. What do you do?
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud
-https://t.co/YpRWtBZrhq</t>
+          <t>#4QWithCNBCTV18 | #RBLBank Says | From Concall
+--Have Received RBI &amp; CCI Approval For The Emirates NBD Deal; SEBI &amp; Govt Of India Nods Awaited
+---We issued 3.3 lakh cards in Q4
+--Our CASA ratio stands at 33.6%
+--Gross NPA Is Down 43 Bps QoQ And Net NPA Down 16 Bps QoQ
+--PCR At 73.6% And Credit Cost For Q4 At 65 Bps
+--Total CFAF At 14.25% &amp; CET-1 Ratio At 12.77%</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>You receive an unexpected payment request. What do you do? 
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud</t>
+          <t>RBL Bank says it has received RBI and CCI approval for the Emirates NBD deal; SEBI and Government of India approvals are awaited. We issued 330,000 cards in Q4. Our CASA ratio stands at 33.6%. Gross NPA is down 43 basis points quarter-on-quarter and net NPA is down 16 basis points quarter-on-quarter. PCR is at 73.6% and credit cost for Q4 is at 65 basis points. Total CFAF is at 14.25% and CET-1 ratio is at 12.77%.</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1705,10 +1913,10 @@
         </is>
       </c>
       <c r="AE8" s="2" t="n">
-        <v>46136.72152777778</v>
+        <v>46137.55416666667</v>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
@@ -1722,7 +1930,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Stay Safe, Stay Vigilant. • You receive an unexpected payment request.</t>
+          <t>Gross NPA is down 43 basis points quarter-on-quarter and net NPA is down 16 basis points quarter-on-quarter. • Total CFAF is at 14.25% and CET-1 ratio is at 12.77%. • PCR is at 73.6% and credit cost for Q4 is at 65 basis points.</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1735,7 +1943,7 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1745,86 +1953,80 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2047663017521774593</t>
+          <t>2047956082497323013</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://x.com/buib102/status/2047663017521774593</t>
+          <t>https://x.com/marketalertsz/status/2047956082497323013</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://x.com/buib102</t>
+          <t>https://x.com/marketalertsz</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>buib102</t>
+          <t>marketalertsz</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>kal</t>
+          <t>Market Alerts By Tijori</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1864603995450339328/60x2qVQI_bigger.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>حولت اليوم مبلغ مالي اكثر من 20 الف من حسابي لديكم لبنك @alinma
-متى توصل الحواله ؟</t>
+          <t>Company: RBL Bank
+Update Type: Press Release 📰 | Sentiment: Positive 🟢
+Summary: RBL Bank Q4 net profit surged 234% YoY to ₹230 crore. Advances grew 23% and deposits 25% YoY. GNPA improved to 1.45% from 1.88% QoQ. Strategic investment by Emirates NBD P.J.S.C is in the final stages of closure following RBI and CCI approvals. Dividend of ₹1 per share proposed.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>حولت اليوم مبلغ مالي اكثر من 20 الف من حسابي لديكم لبنك &lt;a href="/alinma" title="الإنماء"&gt;@alinma&lt;/a&gt;
-متى توصل الحواله ؟</t>
+          <t>Company: RBL Bank
+Update Type: Press Release 📰 | Sentiment: Positive 🟢
+Summary: RBL Bank Q4 net profit surged 234% YoY to ₹230 crore. Advances grew 23% and deposits 25% YoY. GNPA improved to 1.45% from 1.88% QoQ. Strategic investment by Emirates NBD P.J.S.C is in the final stages of closure following RBI and CCI approvals. Dividend of ₹1 per share proposed.</t>
         </is>
       </c>
       <c r="K9" t="b">
         <v>0</v>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_KSA', 'AbdulrhmanRF']</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 1:04 PM UTC</t>
+          <t>Apr 25, 2026 · 8:29 AM UTC</t>
         </is>
       </c>
       <c r="P9" s="2" t="n">
-        <v>46136.54444444444</v>
+        <v>46137.35347222222</v>
       </c>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>['https://x.com/alinma']</t>
-        </is>
-      </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V9" t="n">
-        <v>11</v>
+        <v>978</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1833,21 +2035,33 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>حولت اليوم مبلغ مالي اكثر من 20 الف من حسابي لديكم لبنك @alinma
-متى توصل الحواله ؟</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
+          <t>Company: RBL Bank
+Update Type: Press Release 📰 | Sentiment: Positive 🟢
+Summary: RBL Bank Q4 net profit surged 234% YoY to ₹230 crore. Advances grew 23% and deposits 25% YoY. GNPA improved to 1.45% from 1.88% QoQ. Strategic investment by Emirates NBD P.J.S.C is in the final stages of closure following RBI and CCI approvals. Dividend of ₹1 per share proposed.</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>https://x.com/marketalertsz/status/2047956082497323013</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Company: RBL Bank
+Update Type: Press Release 📰 | Sentiment: Positive 🟢
+Summary: RBL Bank Q4 net profit surged 234% YoY to ₹230 crore. Advances grew 23% and deposits 25% YoY. GNPA improved to 1.45% from 1.88% QoQ. Strategic investment by Emirates NBD P.J.S.C is in the final stages of closure following RBI and CCI approvals. Dividend of ₹1 per share proposed.</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>حولت اليوم مبلغ مالي اكثر من 20 الف من حسابي لديكم لبنك @alinma
-متى توصل الحواله ؟</t>
+          <t>Company: RBL Bank
+Update Type: Press Release 📰 | Sentiment: Positive 🟢
+Summary: RBL Bank Q4 net profit surged 234% YoY to ₹230 crore. Advances grew 23% and deposits 25% YoY. GNPA improved to 1.45% from 1.88% QoQ. Strategic investment by Emirates NBD P.J.S.C is in the final stages of closure following RBI and CCI approvals. Dividend of ₹1 per share proposed.</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>I transferred an amount of more than 20,000 from my account with you to Alinma Bank today. When will the transfer arrive?</t>
+          <t>RBL Bank's Q4 net profit surged 234% year-on-year to ₹230 crore. Advances grew 23% and deposits 25% year-on-year. Gross Non-Performing Assets improved to 1.45% from 1.88% quarter-on-quarter. The strategic investment by Emirates NBD P.J.S.C is in the final stages of closure following approvals from the RBI and CCI. A dividend of ₹1 per share has been proposed.</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1861,10 +2075,10 @@
         </is>
       </c>
       <c r="AE9" s="2" t="n">
-        <v>46136.71111111111</v>
+        <v>46137.52013888889</v>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
@@ -1878,7 +2092,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>I transferred an amount of more than 20,000 from my account with you to Alinma Bank today. • When will the transfer arrive?</t>
+          <t>RBL Bank's Q4 net profit surged 234% year-on-year to ₹230 crore. • Gross Non-Performing Assets improved to 1.45% from 1.88% quarter-on-quarter. • Advances grew 23% and deposits 25% year-on-year.</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1891,7 +2105,7 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>EmiratesNBD_KSA, AbdulrhmanRF</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1901,43 +2115,45 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2047647028012876081</t>
+          <t>2047948728103800903</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://x.com/NovoCinemas/status/2047647028012876081</t>
+          <t>https://x.com/EmiratesNBD_EGY/status/2047948728103800903</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://x.com/NovoCinemas</t>
+          <t>https://x.com/EmiratesNBD_EGY</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>NovoCinemas</t>
+          <t>EmiratesNBD_EGY</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Novo Cinemas</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2008888282768429056/a3q3GqDa_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427526482108416/qjFPlJ1n_bigger.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Bro life… but extra chaos 🍻🔥#VaazhaII continues to pull crowds with fun, madness and those “this is so real” moments. Watch it now at Novo Cinemas. Book on https://t.co/w2yAiSn6ht or the Novo App. https://t.co/ycxZoinbXq</t>
+          <t>Emirates NBD celebrates Sinai Liberation Day, honoring Egypt’s strength and enduring spirit.
+Tax Registration Number: 204-897-319 https://t.co/qXPkhBDY06</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Sometimes, all you need is a quiet escape into a great story. 🎞️🤍 Use your Emirates NBD card at Novo Cinemas to enjoy 15% off tickets any day of the week. A simple way to reward yourself with a moment of peace. Book your tickets now by visiting &lt;a href="http://www.NovoCinemas.com"&gt;NovoCinemas.com&lt;/a&gt; or the App</t>
+          <t>Emirates NBD celebrates Sinai Liberation Day, honoring Egypt’s strength and enduring spirit.
+Tax Registration Number: 204-897-319</t>
         </is>
       </c>
       <c r="K10" t="b">
@@ -1947,23 +2163,19 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 12:01 PM UTC</t>
+          <t>Apr 25, 2026 · 8:00 AM UTC</t>
         </is>
       </c>
       <c r="P10" s="2" t="n">
-        <v>46136.50069444445</v>
+        <v>46137.33333333334</v>
       </c>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>['http://www.NovoCinemas.com']</t>
-        </is>
-      </c>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
         <v>0</v>
       </c>
@@ -1974,7 +2186,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1983,44 +2195,47 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Sometimes, all you need is a quiet escape into a great story. 🎞️🤍 Use your Emirates NBD card at Novo Cinemas to enjoy 15% off tickets any day of the week. A simple way to reward yourself with a moment of peace. Book your tickets now by visiting NovoCinemas.com or the App</t>
+          <t>Emirates NBD celebrates Sinai Liberation Day, honoring Egypt’s strength and enduring spirit.
+Tax Registration Number: 204-897-319</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>https://x.com/NovoCinemas/status/2047647028012876081</t>
+          <t>https://x.com/EmiratesNBD_EGY/status/2047948728103800903</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>Bro life… but extra chaos 🍻🔥#VaazhaII continues to pull crowds with fun, madness and those “this is so real” moments. Watch it now at Novo Cinemas. Book on https://t.co/w2yAiSn6ht or the Novo App. https://t.co/ycxZoinbXq</t>
+          <t>Emirates NBD celebrates Sinai Liberation Day, honoring Egypt’s strength and enduring spirit.
+Tax Registration Number: 204-897-319 https://t.co/qXPkhBDY06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Bro life… but extra chaos 🍻🔥#VaazhaII continues to pull crowds with fun, madness and those “this is so real” moments. Watch it now at Novo Cinemas. Book on https://t.co/w2yAiSn6ht or the Novo App. https://t.co/ycxZoinbXq</t>
+          <t>Emirates NBD celebrates Sinai Liberation Day, honoring Egypt’s strength and enduring spirit.
+Tax Registration Number: 204-897-319 https://t.co/qXPkhBDY06</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Bro life… but extra chaos 🍻🔥#VaazhaII continues to pull crowds with fun, madness and those “this is so real” moments. Watch it now at Novo Cinemas. Book on https://t.co/w2yAiSn6ht or the Novo App. https://t.co/ycxZoinbXq</t>
+          <t>Emirates NBD celebrates Sinai Liberation Day, honoring Egypt’s strength and enduring spirit.</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Cust</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE10" s="2" t="n">
-        <v>46136.66736111111</v>
+        <v>46137.5</v>
       </c>
       <c r="AF10" s="2" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
@@ -2034,7 +2249,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Bro life… but extra chaos 🍻🔥#VaazhaII continues to pull crowds with fun, madness and those “this is so real” moments. • Book on https://t.co/w2yAiSn6ht or the Novo App. • Watch it now at Novo Cinemas.</t>
+          <t>Emirates NBD celebrates Sinai Liberation Day, honoring Egypt’s strength and enduring spirit.</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -2057,49 +2272,52 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2047628468545110433</t>
+          <t>2047919811624312884</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/dandbdubai/status/2047628468545110433</t>
+          <t>https://x.com/Harryhwrqx/status/2047919811624312884</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://x.com/dandbdubai</t>
+          <t>https://x.com/Harryhwrqx</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>dandbdubai</t>
+          <t>Harryhwrqx</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>D&amp;B Properties</t>
+          <t>Harry</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1696029705600708608/mr6ZIB0B_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2047289177281277952/64g0LbSJ_bigger.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Proud to call the UAE home 🇦🇪
-The UAE continues to inspire, build, and lead and we’re proud to be part of that story.
-Here’s to growth, innovation, and everything ahead
-#UAE #ProudOfUAE #UAENationalPride #Dubai #DubaiLife https://t.co/bnUJHbF5lp</t>
+          <t>1.The SEC has been regulating crypto for 10 years.
+No clear RWA framework. No tokenization path. Just lawsuits.
+Meanwhile, UAE built the entire system in 3 years.
+🧵 Why VARA is what the SEC wishes it could be.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Breaking News 📢 Dubai Real Estate Just Entered a New Era 🌇
-▪️50/50 Strategy: Pay 50% and leverage ENBD financing for the rest.
-▪️Project Readiness: Available on premium projects at least 30% complete.
-▪️Maximum Liquidity: Grow your portfolio without tying up all your cash.</t>
+          <t>5.What happened after regulatory clarity?
+→ Mantra: $1B DAMAC deal
+→ Mavryk: $10B UAE pipeline
+→ 40%+ of EU DeFi traders moved to UAE platforms
+→ Emirates NBD actively building crypto services
+Clarity attracts capital.
+Confusion repels it.</t>
         </is>
       </c>
       <c r="K11" t="b">
@@ -2109,21 +2327,21 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 10:47 AM UTC</t>
+          <t>Apr 25, 2026 · 6:05 AM UTC</t>
         </is>
       </c>
       <c r="P11" s="2" t="n">
-        <v>46136.44930555556</v>
+        <v>46137.25347222222</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -2132,7 +2350,7 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -2141,36 +2359,42 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Breaking News 📢 Dubai Real Estate Just Entered a New Era 🌇
-▪️50/50 Strategy: Pay 50% and leverage ENBD financing for the rest.
-▪️Project Readiness: Available on premium projects at least 30% complete.
-▪️Maximum Liquidity: Grow your portfolio without tying up all your cash.</t>
+          <t>5.What happened after regulatory clarity?
+→ Mantra: $1B DAMAC deal
+→ Mavryk: $10B UAE pipeline
+→ 40%+ of EU DeFi traders moved to UAE platforms
+→ Emirates NBD actively building crypto services
+Clarity attracts capital.
+Confusion repels it.</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>https://x.com/dandbdubai/status/2047628468545110433</t>
+          <t>https://x.com/Harryhwrqx/status/2047919811624312884</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>Proud to call the UAE home 🇦🇪
-The UAE continues to inspire, build, and lead and we’re proud to be part of that story.
-Here’s to growth, innovation, and everything ahead
-#UAE #ProudOfUAE #UAENationalPride #Dubai #DubaiLife https://t.co/bnUJHbF5lp</t>
+          <t>1.The SEC has been regulating crypto for 10 years.
+No clear RWA framework. No tokenization path. Just lawsuits.
+Meanwhile, UAE built the entire system in 3 years.
+🧵 Why VARA is what the SEC wishes it could be.</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Proud to call the UAE home 🇦🇪
-The UAE continues to inspire, build, and lead and we’re proud to be part of that story.
-Here’s to growth, innovation, and everything ahead
-#UAE #ProudOfUAE #UAENationalPride #Dubai #DubaiLife https://t.co/bnUJHbF5lp</t>
+          <t>1.The SEC has been regulating crypto for 10 years.
+No clear RWA framework. No tokenization path. Just lawsuits.
+Meanwhile, UAE built the entire system in 3 years.
+🧵 Why VARA is what the SEC wishes it could be.</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Proud to call the UAE home. The UAE continues to inspire, build, and lead, and we’re proud to be part of that story. Here’s to growth, innovation, and everything ahead.</t>
+          <t>The SEC has been regulating crypto for 10 years. 
+No clear RWA framework. No tokenization path. Just lawsuits. 
+Meanwhile, the UAE built the entire system in 3 years. 
+Why VARA is what the SEC wishes it could be.</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2184,10 +2408,10 @@
         </is>
       </c>
       <c r="AE11" s="2" t="n">
-        <v>46136.61597222222</v>
+        <v>46137.42013888889</v>
       </c>
       <c r="AF11" s="2" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
@@ -2201,7 +2425,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>The UAE continues to inspire, build, and lead, and we’re proud to be part of that story. • Proud to call the UAE home. • Here’s to growth, innovation, and everything ahead.</t>
+          <t>The SEC has been regulating crypto for 10 years. • Meanwhile, the UAE built the entire system in 3 years. • Why VARA is what the SEC wishes it could be.</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -2224,43 +2448,47 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2047601280143724646</t>
+          <t>2047895879798186062</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://x.com/XSilverMermaidX/status/2047601280143724646</t>
+          <t>https://x.com/titledeednews/status/2047895879798186062</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://x.com/XSilverMermaidX</t>
+          <t>https://x.com/titledeednews</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>XSilverMermaidX</t>
+          <t>titledeednews</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kang Hori</t>
+          <t>The Title Deed</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/419562448748695552/bW8b5d7__bigger.jpeg</t>
+          <t>https://pbs.twimg.com/profile_images/2032863974820294659/y_r3-sNy_bigger.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE  hello, i want to check, is there an issue with the SMS server? I stopped receiving SMS after April 7th</t>
+          <t>Dubai Holding and Emirates NBD roll out new off-plan mortgage solutions, lowering entry barriers for buyers.
+More financing = more demand = more deals.
+#DubaiRealEstate #BreakingNews #OffPlanDubai #PropertyInvestment #DubaiBrokers #InvestInDubai https://t.co/6kZs3vX1Ui</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;  hello, i want to check, is there an issue with the SMS server? I stopped receiving SMS after April 7th</t>
+          <t>Dubai Holding and Emirates NBD roll out new off-plan mortgage solutions, lowering entry barriers for buyers.
+More financing = more demand = more deals.
+&lt;a href="/search?f=tweets&amp;amp;q=%23DubaiRealEstate"&gt;#DubaiRealEstate&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23BreakingNews"&gt;#BreakingNews&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23OffPlanDubai"&gt;#OffPlanDubai&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23PropertyInvestment"&gt;#PropertyInvestment&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23DubaiBrokers"&gt;#DubaiBrokers&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23InvestInDubai"&gt;#InvestInDubai&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K12" t="b">
@@ -2270,25 +2498,25 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 8:59 AM UTC</t>
+          <t>Apr 25, 2026 · 4:30 AM UTC</t>
         </is>
       </c>
       <c r="P12" s="2" t="n">
-        <v>46136.37430555555</v>
+        <v>46137.1875</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>['https://x.com/EmiratesNBD_AE']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23DubaiRealEstate', 'https://x.com/search?f=tweets&amp;q=%23BreakingNews', 'https://x.com/search?f=tweets&amp;q=%23OffPlanDubai', 'https://x.com/search?f=tweets&amp;q=%23PropertyInvestment', 'https://x.com/search?f=tweets&amp;q=%23DubaiBrokers', 'https://x.com/search?f=tweets&amp;q=%23InvestInDubai']</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -2297,7 +2525,7 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -2306,27 +2534,34 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE  hello, i want to check, is there an issue with the SMS server? I stopped receiving SMS after April 7th</t>
+          <t>Dubai Holding and Emirates NBD roll out new off-plan mortgage solutions, lowering entry barriers for buyers.
+More financing = more demand = more deals.
+#DubaiRealEstate #BreakingNews #OffPlanDubai #PropertyInvestment #DubaiBrokers #InvestInDubai</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>https://x.com/XSilverMermaidX/status/2047601280143724646</t>
+          <t>https://x.com/titledeednews/status/2047895879798186062</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE  hello, i want to check, is there an issue with the SMS server? I stopped receiving SMS after April 7th</t>
+          <t>Dubai Holding and Emirates NBD roll out new off-plan mortgage solutions, lowering entry barriers for buyers.
+More financing = more demand = more deals.
+#DubaiRealEstate #BreakingNews #OffPlanDubai #PropertyInvestment #DubaiBrokers #InvestInDubai https://t.co/6kZs3vX1Ui</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE  hello, i want to check, is there an issue with the SMS server? I stopped receiving SMS after April 7th</t>
+          <t>Dubai Holding and Emirates NBD roll out new off-plan mortgage solutions, lowering entry barriers for buyers.
+More financing = more demand = more deals.
+#DubaiRealEstate #BreakingNews #OffPlanDubai #PropertyInvestment #DubaiBrokers #InvestInDubai https://t.co/6kZs3vX1Ui</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Hello, I want to check if there is an issue with the SMS server? I stopped receiving SMS after April 7th.</t>
+          <t>Dubai Holding and Emirates NBD have launched new off-plan mortgage solutions, reducing entry barriers for buyers. 
+More financing equals more demand equals more deals.</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2336,14 +2571,14 @@
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE12" s="2" t="n">
-        <v>46136.54097222222</v>
+        <v>46137.35416666666</v>
       </c>
       <c r="AF12" s="2" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
@@ -2357,7 +2592,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>I stopped receiving SMS after April 7th. • Hello, I want to check if there is an issue with the SMS server?</t>
+          <t>Dubai Holding and Emirates NBD have launched new off-plan mortgage solutions, reducing entry barriers for buyers. • More financing equals more demand equals more deals.</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2380,69 +2615,75 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2047564934997762494</t>
+          <t>2047892921970794814</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://x.com/zachrose51/status/2047564934997762494</t>
+          <t>https://x.com/hkayyal/status/2047892921970794814</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://x.com/zachrose51</t>
+          <t>https://x.com/hkayyal</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>zachrose51</t>
+          <t>hkayyal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zach Roseman</t>
+          <t>Houssam Kayyal حسام كيال</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1709989703842164737/7VJMa5sV_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2044832438078275584/VB1YBCs5_bigger.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>@coiningmaxi Alright - found some of your customers: PayTabs, Telr, Network International, Magnati, Emirates NBD and Mashreq Bank. Sound right? Going to use these to track down real prospects at your dream customers and map intro paths to them</t>
+          <t>🧵 Gulf Fintech Daily — April 25, 2026
+WhatsApp bans. Wealthtech licenses. B2B credit. Cross-border corridors.
+5 stories shaping Gulf finance today 👇
+#GulfFintech #MENA #FinTech</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Alright - found some of your customers: PayTabs, Telr, Network International, Magnati, Emirates NBD and Mashreq Bank. Sound right? Going to use these to track down real prospects at your dream customers and map intro paths to them</t>
+          <t>4️⃣ UAE B2B BNPL market hits $1.97B — 23.9% CAGR → $4.66B by 2030.
+Tabby for Business, Tamara, Beehive embedding payment terms in trade platforms.
+ENBD, ADCB, FAB building digital trade finance. SME credit competition intensifies.
+&lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23BNPL"&gt;#BNPL&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Fintech"&gt;#Fintech&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K13" t="b">
         <v>0</v>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>['coiningmaxi']</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 6:34 AM UTC</t>
+          <t>Apr 25, 2026 · 4:18 AM UTC</t>
         </is>
       </c>
       <c r="P13" s="2" t="n">
-        <v>46136.27361111111</v>
+        <v>46137.17916666667</v>
       </c>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23UAE', 'https://x.com/search?f=tweets&amp;q=%23BNPL', 'https://x.com/search?f=tweets&amp;q=%23Fintech']</t>
+        </is>
+      </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
@@ -2450,10 +2691,10 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -2462,27 +2703,38 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Alright - found some of your customers: PayTabs, Telr, Network International, Magnati, Emirates NBD and Mashreq Bank. Sound right? Going to use these to track down real prospects at your dream customers and map intro paths to them</t>
+          <t>4️⃣ UAE B2B BNPL market hits $1.97B — 23.9% CAGR → $4.66B by 2030.
+Tabby for Business, Tamara, Beehive embedding payment terms in trade platforms.
+ENBD, ADCB, FAB building digital trade finance. SME credit competition intensifies.
+#UAE #BNPL #Fintech</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>https://x.com/zachrose51/status/2047564934997762494</t>
+          <t>https://x.com/hkayyal/status/2047892921970794814</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>@coiningmaxi Alright - found some of your customers: PayTabs, Telr, Network International, Magnati, Emirates NBD and Mashreq Bank. Sound right? Going to use these to track down real prospects at your dream customers and map intro paths to them</t>
+          <t>🧵 Gulf Fintech Daily — April 25, 2026
+WhatsApp bans. Wealthtech licenses. B2B credit. Cross-border corridors.
+5 stories shaping Gulf finance today 👇
+#GulfFintech #MENA #FinTech</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>@coiningmaxi Alright - found some of your customers: PayTabs, Telr, Network International, Magnati, Emirates NBD and Mashreq Bank. Sound right? Going to use these to track down real prospects at your dream customers and map intro paths to them</t>
+          <t>🧵 Gulf Fintech Daily — April 25, 2026
+WhatsApp bans. Wealthtech licenses. B2B credit. Cross-border corridors.
+5 stories shaping Gulf finance today 👇
+#GulfFintech #MENA #FinTech</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Alright - I found some of your customers: PayTabs, Telr, Network International, Magnati, Emirates NBD, and Mashreq Bank. Does that sound right? I'm going to use these to track down real prospects at your dream customers and map introduction paths to them.</t>
+          <t>Gulf Fintech Daily — April 25, 2026
+WhatsApp bans. Wealthtech licenses. B2B credit. Cross-border corridors.
+5 stories shaping Gulf finance today.</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2496,10 +2748,10 @@
         </is>
       </c>
       <c r="AE13" s="2" t="n">
-        <v>46136.44027777778</v>
+        <v>46137.34583333333</v>
       </c>
       <c r="AF13" s="2" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
@@ -2513,7 +2765,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Alright - I found some of your customers: PayTabs, Telr, Network International, Magnati, Emirates NBD, and Mashreq Bank. • I'm going to use these to track down real prospects at your dream customers and map introduction paths to them.</t>
+          <t>Gulf Fintech Daily — April 25, 2026 WhatsApp bans. • 5 stories shaping Gulf finance today.</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2526,7 +2778,7 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>coiningmaxi</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2536,48 +2788,43 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2047530498705195395</t>
+          <t>2048143516644016239</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://x.com/hkayyal/status/2047530498705195395</t>
+          <t>https://x.com/gold_hadas/status/2048143516644016239</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://x.com/hkayyal</t>
+          <t>https://x.com/gold_hadas</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>hkayyal</t>
+          <t>gold_hadas</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Houssam Kayyal حسام كيال</t>
+          <t>Nicholas MOLODYKO, writer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2044832438078275584/VB1YBCs5_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2026237940993552385/baDKDoMV_bigger.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>🧵 Gulf Fintech Daily — April 24, 2026
-AI as infrastructure. Sovereign capital as catalyst. 5 stories 👇
-#GulfFintech #MENA #FinTech</t>
+          <t>Emirates Islamic Q1 2026 Results: Operating Profit Rises to Dh1.1 Billion on Higher Financing and Deposits https://t.co/DsNXQRIxdO</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3️⃣ Dubai South × Emirates NBD sign MoU for streamlined SME banking access.
-Corporate account opening + tailored banking within the free zone.
-94% of UAE businesses are SMEs. Financial onboarding friction is being systematically removed.
-&lt;a href="/search?f=tweets&amp;amp;q=%23Dubai"&gt;#Dubai&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SME"&gt;#SME&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23D33"&gt;#D33&lt;/a&gt;</t>
+          <t>Emirates Islamic Q1 2026 Results: Operating Profit Rises to Dh1.1 Billion on Higher Financing and Deposits &lt;a href="https://gulfnews.com/business/banking/emirates-islamic-q1-2026-profit-rises-to-dh11-billion-1.500516602"&gt;gulfnews.com/business/bankin…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K14" t="b">
@@ -2587,21 +2834,21 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>7h</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 4:18 AM UTC</t>
+          <t>Apr 25, 2026 · 8:54 PM UTC</t>
         </is>
       </c>
       <c r="P14" s="2" t="n">
-        <v>46136.17916666667</v>
+        <v>46137.87083333333</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23Dubai', 'https://x.com/search?f=tweets&amp;q=%23SME', 'https://x.com/search?f=tweets&amp;q=%23D33']</t>
+          <t>['https://gulfnews.com/business/banking/emirates-islamic-q1-2026-profit-rises-to-dh11-billion-1.500516602']</t>
         </is>
       </c>
       <c r="S14" t="n">
@@ -2614,44 +2861,36 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>3️⃣ Dubai South × Emirates NBD sign MoU for streamlined SME banking access.
-Corporate account opening + tailored banking within the free zone.
-94% of UAE businesses are SMEs. Financial onboarding friction is being systematically removed.
-#Dubai #SME #D33</t>
+          <t>Emirates Islamic Q1 2026 Results: Operating Profit Rises to Dh1.1 Billion on Higher Financing and Deposits gulfnews.com/business/bankin…</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>https://x.com/hkayyal/status/2047530498705195395</t>
+          <t>https://x.com/gold_hadas/status/2048143516644016239</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>🧵 Gulf Fintech Daily — April 24, 2026
-AI as infrastructure. Sovereign capital as catalyst. 5 stories 👇
-#GulfFintech #MENA #FinTech</t>
+          <t>Emirates Islamic Q1 2026 Results: Operating Profit Rises to Dh1.1 Billion on Higher Financing and Deposits https://t.co/DsNXQRIxdO</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>🧵 Gulf Fintech Daily — April 24, 2026
-AI as infrastructure. Sovereign capital as catalyst. 5 stories 👇
-#GulfFintech #MENA #FinTech</t>
+          <t>Emirates Islamic Q1 2026 Results: Operating Profit Rises to Dh1.1 Billion on Higher Financing and Deposits https://t.co/DsNXQRIxdO</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Gulf Fintech Daily — April 24, 2026
-AI as infrastructure. Sovereign capital as a catalyst. 5 stories below.</t>
+          <t>Emirates Islamic Q1 2026 Results: Operating Profit Rises to Dh1.1 Billion on Higher Financing and Deposits</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2661,33 +2900,33 @@
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE14" s="2" t="n">
-        <v>46136.34583333333</v>
+        <v>46138.0375</v>
       </c>
       <c r="AF14" s="2" t="n">
-        <v>46136</v>
+        <v>46138</v>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
+          <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Gulf Fintech Daily — April 24, 2026 AI as infrastructure. • Sovereign capital as a catalyst.</t>
+          <t>Emirates Islamic Q1 2026 Results: Operating Profit Rises to Dh1.1 Billion on Higher Financing and Deposits</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank (ENBD)</t>
+          <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AK14" t="n">
@@ -2705,66 +2944,71 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2047835274818748466</t>
+          <t>2047978927268696148</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://x.com/iDenville/status/2047835274818748466</t>
+          <t>https://x.com/emiratesislamic/status/2047978927268696148</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://x.com/iDenville</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>iDenville</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>DenvilleCommunity</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2016182960915918848/VD9PxabL_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Judge overturns election after Democrats caught ballot stuffing. https://t.co/sCEs1CS21j</t>
+          <t>احصل على بطاقة ائتمانية من الإمارات الإسلامي واستفد من مزايا خاصة:
+🌟 مكافأة ترحيبية تصل قيمتها إلى 1,000 درهم (قسيمة هدايا من https://t.co/iCieKmtWAq)
+✈️ الدخول إلى صالات المطارات وخدمات الاستقبال والترحيب والتوصيل من وإلى المطار https://t.co/dIBJO6jPay</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Most of the Islamic banking is done through a different system, Bai&amp;#39; al-Sarf.  They have their own banks: Emirates Islamic Bank, Al Rajhi Bank, Abu Dhabi Islamic Bank and more.  They come with apps.</t>
+          <t>The Amazon Emirates Islamic Mastercard Credit Card
+Meet the card that turns every purchase into Unlimited Joy 💳✨
+✨ Up to 6% back, unlimited
+🎁 Up to AED 750 welcome bonus
+💳 No annual fee
+🌍 Exclusive travel &amp;amp; lifestyle benefits
+And much more.
+Terms &amp;amp; conditions apply.</t>
         </is>
       </c>
       <c r="K15" t="b">
         <v>0</v>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>['stelpetla', 'JDunlap1974']</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Apr 25, 2026 · 12:29 AM UTC</t>
+          <t>Apr 25, 2026 · 10:00 AM UTC</t>
         </is>
       </c>
       <c r="P15" s="2" t="n">
-        <v>46137.02013888889</v>
+        <v>46137.41666666666</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
@@ -2775,10 +3019,10 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -2787,41 +3031,54 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Most of the Islamic banking is done through a different system, Bai' al-Sarf.  They have their own banks: Emirates Islamic Bank, Al Rajhi Bank, Abu Dhabi Islamic Bank and more.  They come with apps.</t>
+          <t>The Amazon Emirates Islamic Mastercard Credit Card
+Meet the card that turns every purchase into Unlimited Joy 💳✨
+✨ Up to 6% back, unlimited
+🎁 Up to AED 750 welcome bonus
+💳 No annual fee
+🌍 Exclusive travel &amp; lifestyle benefits
+And much more.
+Terms &amp; conditions apply.</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>https://x.com/iDenville/status/2047835274818748466</t>
+          <t>https://x.com/emiratesislamic/status/2047978927268696148</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>Judge overturns election after Democrats caught ballot stuffing. https://t.co/sCEs1CS21j</t>
+          <t>احصل على بطاقة ائتمانية من الإمارات الإسلامي واستفد من مزايا خاصة:
+🌟 مكافأة ترحيبية تصل قيمتها إلى 1,000 درهم (قسيمة هدايا من https://t.co/iCieKmtWAq)
+✈️ الدخول إلى صالات المطارات وخدمات الاستقبال والترحيب والتوصيل من وإلى المطار https://t.co/dIBJO6jPay</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Judge overturns election after Democrats caught ballot stuffing. https://t.co/sCEs1CS21j</t>
+          <t>احصل على بطاقة ائتمانية من الإمارات الإسلامي واستفد من مزايا خاصة:
+🌟 مكافأة ترحيبية تصل قيمتها إلى 1,000 درهم (قسيمة هدايا من https://t.co/iCieKmtWAq)
+✈️ الدخول إلى صالات المطارات وخدمات الاستقبال والترحيب والتوصيل من وإلى المطار https://t.co/dIBJO6jPay</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Judge overturns election after Democrats were caught ballot stuffing.</t>
+          <t>Get a credit card from Emirates Islamic and enjoy special benefits:
+🌟 A welcome bonus of up to 1,000 dirhams (gift voucher from https://t.co/iCieKmtWAq)
+✈️ Access to airport lounges and reception, welcome, and transfer services to and from the airport https://t.co/dIBJO6jPay</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Cust</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE15" s="2" t="n">
-        <v>46137.18680555555</v>
+        <v>46137.58333333334</v>
       </c>
       <c r="AF15" s="2" t="n">
         <v>46137</v>
@@ -2838,7 +3095,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Judge overturns election after Democrats were caught ballot stuffing.</t>
+          <t>Get a credit card from Emirates Islamic and enjoy special benefits: 🌟 A welcome bonus of up to 1,000 dirhams (gift vouch…</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -2851,7 +3108,7 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>stelpetla, JDunlap1974</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2861,12 +3118,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2047717990762782723</t>
+          <t>2047963834812334213</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047717990762782723</t>
+          <t>https://x.com/emiratesislamic/status/2047963834812334213</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2892,22 +3149,16 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>⏳Payment holidays
-🎁 Exclusive prizes with Kunooz Millionaire Account
-Terms and conditions apply.
-Know more
-https://t.co/OfDhWyedzP
-#EmiratesIslamic #FrontlineHeroes</t>
+          <t>تملّك منزلك الجديد بسهولة مع حلول التمويل السكني المرنة من الإمارات الإسلامي واستمتع بمزايا استثنائية
+تمويل يصل إلى %85 من قيمة العقار
+رسوم إجراءات منخفضة ومعدلات ربح تنافسية https://t.co/skou0cynsQ</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>⏳Payment holidays
-🎁 Exclusive prizes with Kunooz Millionaire Account
-Terms and conditions apply.
-Know more
-&lt;a href="https://www.emiratesislamic.ae/en/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=front_line"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FrontlineHeroes"&gt;#FrontlineHeroes&lt;/a&gt;</t>
+          <t>Step into your new home with ease with flexible Home Finance solutions from Emirates Islamic and enjoy exclusive benefits.
+Financing up to 85% of the property value.  
+Low processing fees and competitive profit rates.</t>
         </is>
       </c>
       <c r="K16" t="b">
@@ -2917,34 +3168,30 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 4:43 PM UTC</t>
+          <t>Apr 25, 2026 · 9:00 AM UTC</t>
         </is>
       </c>
       <c r="P16" s="2" t="n">
-        <v>46136.69652777778</v>
+        <v>46137.375</v>
       </c>
       <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=front_line', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23FrontlineHeroes']</t>
-        </is>
-      </c>
+      <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -2953,42 +3200,35 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>⏳Payment holidays
-🎁 Exclusive prizes with Kunooz Millionaire Account
-Terms and conditions apply.
-Know more
-emiratesislamic.ae/en/offers…
-#EmiratesIslamic #FrontlineHeroes</t>
+          <t>Step into your new home with ease with flexible Home Finance solutions from Emirates Islamic and enjoy exclusive benefits.
+Financing up to 85% of the property value.  
+Low processing fees and competitive profit rates.</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047717990762782723</t>
+          <t>https://x.com/emiratesislamic/status/2047963834812334213</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>⏳Payment holidays
-🎁 Exclusive prizes with Kunooz Millionaire Account
-Terms and conditions apply.
-Know more
-https://t.co/OfDhWyedzP
-#EmiratesIslamic #FrontlineHeroes</t>
+          <t>تملّك منزلك الجديد بسهولة مع حلول التمويل السكني المرنة من الإمارات الإسلامي واستمتع بمزايا استثنائية
+تمويل يصل إلى %85 من قيمة العقار
+رسوم إجراءات منخفضة ومعدلات ربح تنافسية https://t.co/skou0cynsQ</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>⏳Payment holidays
-🎁 Exclusive prizes with Kunooz Millionaire Account
-Terms and conditions apply.
-Know more
-https://t.co/OfDhWyedzP
-#EmiratesIslamic #FrontlineHeroes</t>
+          <t>تملّك منزلك الجديد بسهولة مع حلول التمويل السكني المرنة من الإمارات الإسلامي واستمتع بمزايا استثنائية
+تمويل يصل إلى %85 من قيمة العقار
+رسوم إجراءات منخفضة ومعدلات ربح تنافسية https://t.co/skou0cynsQ</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Payment holidays Exclusive prizes with Kunooz Millionaire Account Terms and conditions apply. Know more</t>
+          <t>Own your new home easily with flexible housing finance solutions from Emirates Islamic and enjoy exceptional benefits
+Financing of up to 85% of the property value
+Low processing fees and competitive profit rates</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -3002,10 +3242,10 @@
         </is>
       </c>
       <c r="AE16" s="2" t="n">
-        <v>46136.86319444444</v>
+        <v>46137.54166666666</v>
       </c>
       <c r="AF16" s="2" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
@@ -3019,7 +3259,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Payment holidays Exclusive prizes with Kunooz Millionaire Account Terms and conditions apply.</t>
+          <t>Own your new home easily with flexible housing finance solutions from Emirates Islamic and enjoy exceptional benefits Fi…</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -3042,12 +3282,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2047631640168374617</t>
+          <t>2047933636054245884</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047631640168374617</t>
+          <t>https://x.com/emiratesislamic/status/2047933636054245884</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3073,18 +3313,17 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.
-Also, enjoy exclusive benefits:
-📊 Profit rates starting from 2.59% flat p.a.(approximately equivalent to 4.74% p.a. reducing profit rate)
-🏦 Finance amount of up to AED 4,000,000 https://t.co/QSbM2ZKbuH</t>
+          <t>💸مكافآت فورية وأميال يمكن استردادها بشكل فوري
+👍 استرداد نقدي، وخصومات، وجولات غولف، وخدمة صف السيارات في مواقع مختارة والمزيد
+يسري العرض لغاية 30 يونيو 2026
+https://t.co/kS1kj9YbcM</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.
-Also, enjoy exclusive benefits:
-📊 Profit rates starting from 2.59% flat p.a.(approximately equivalent to 4.74% p.a. reducing profit rate)
-🏦 Finance amount of up to AED 4,000,000</t>
+          <t>Apply for an Emirates Islamic Credit Card and enjoy unmatched rewards:
+🌟 Welcome bonus worth up to AED 1,000 &lt;a href="http://noon.com"&gt;noon.com&lt;/a&gt; gift voucher
+✈️ Airport lounge access, meet &amp;amp; greet services and airport transfers</t>
         </is>
       </c>
       <c r="K17" t="b">
@@ -3094,19 +3333,23 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 11:00 AM UTC</t>
+          <t>Apr 25, 2026 · 7:00 AM UTC</t>
         </is>
       </c>
       <c r="P17" s="2" t="n">
-        <v>46136.45833333334</v>
+        <v>46137.29166666666</v>
       </c>
       <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>['http://noon.com']</t>
+        </is>
+      </c>
       <c r="S17" t="n">
         <v>1</v>
       </c>
@@ -3117,7 +3360,7 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -3126,39 +3369,37 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.
-Also, enjoy exclusive benefits:
-📊 Profit rates starting from 2.59% flat p.a.(approximately equivalent to 4.74% p.a. reducing profit rate)
-🏦 Finance amount of up to AED 4,000,000</t>
+          <t>Apply for an Emirates Islamic Credit Card and enjoy unmatched rewards:
+🌟 Welcome bonus worth up to AED 1,000 noon.com gift voucher
+✈️ Airport lounge access, meet &amp; greet services and airport transfers</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047631640168374617</t>
+          <t>https://x.com/emiratesislamic/status/2047933636054245884</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.
-Also, enjoy exclusive benefits:
-📊 Profit rates starting from 2.59% flat p.a.(approximately equivalent to 4.74% p.a. reducing profit rate)
-🏦 Finance amount of up to AED 4,000,000 https://t.co/QSbM2ZKbuH</t>
+          <t>💸مكافآت فورية وأميال يمكن استردادها بشكل فوري
+👍 استرداد نقدي، وخصومات، وجولات غولف، وخدمة صف السيارات في مواقع مختارة والمزيد
+يسري العرض لغاية 30 يونيو 2026
+https://t.co/kS1kj9YbcM</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.
-Also, enjoy exclusive benefits:
-📊 Profit rates starting from 2.59% flat p.a.(approximately equivalent to 4.74% p.a. reducing profit rate)
-🏦 Finance amount of up to AED 4,000,000 https://t.co/QSbM2ZKbuH</t>
+          <t>💸مكافآت فورية وأميال يمكن استردادها بشكل فوري
+👍 استرداد نقدي، وخصومات، وجولات غولف، وخدمة صف السيارات في مواقع مختارة والمزيد
+يسري العرض لغاية 30 يونيو 2026
+https://t.co/kS1kj9YbcM</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.
-Also, enjoy exclusive benefits:
-📊 Profit rates starting from 2.59% flat per annum (approximately equivalent to 4.74% per annum reducing profit rate)
-🏦 Finance amount of up to AED 4,000,000</t>
+          <t>Instant rewards and redeemable miles  
+Cashback, discounts, golf rounds, valet service at selected locations, and more  
+The offer is valid until June 30, 2026.</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -3172,10 +3413,10 @@
         </is>
       </c>
       <c r="AE17" s="2" t="n">
-        <v>46136.625</v>
+        <v>46137.45833333334</v>
       </c>
       <c r="AF17" s="2" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
@@ -3189,7 +3430,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Also, enjoy exclusive benefits: 📊 Profit rates starting from 2.59% flat per annum (approximately equivalent to 4.74% per annum reducing profit rate) 🏦 Finance amount of up to AED 4,000,000 • Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.</t>
+          <t>Instant rewards and redeemable miles Cashback, discounts, golf rounds, valet service at selected locations, and more The offer is valid until June 30, 2026.</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -3212,84 +3453,80 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2047575014564921667</t>
+          <t>2047835274818748466</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://x.com/ABCinGCC/status/2047575014564921667</t>
+          <t>https://x.com/iDenville/status/2047835274818748466</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://x.com/ABCinGCC</t>
+          <t>https://x.com/iDenville</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ABCinGCC</t>
+          <t>iDenville</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Arabian Business Community (ABC GCC)</t>
+          <t>DenvilleCommunity</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1782384725962653696/jF3qtc02_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2016182960915918848/VD9PxabL_bigger.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Emirates Islamic has reported an operating profit of AED1.1 billion ($299.52 million) for the quarter ending March 31, 2026, 7% growth over the same period last year.
-Read more on https://t.co/I3d8g2xghd
-#ABCNews #Profit #Banking #FinancialInstitution https://t.co/jfJF6uK62j</t>
+          <t>Judge overturns election after Democrats caught ballot stuffing. https://t.co/sCEs1CS21j</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Emirates Islamic has reported an operating profit of AED1.1 billion ($299.52 million) for the quarter ending March 31, 2026, 7% growth over the same period last year.
-Read more on &lt;a href="https://abc-gcc.net/News/1/395058"&gt;abc-gcc.net/News/1/395058&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23ABCNews"&gt;#ABCNews&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Profit"&gt;#Profit&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Banking"&gt;#Banking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FinancialInstitution"&gt;#FinancialInstitution&lt;/a&gt;</t>
+          <t>Most of the Islamic banking is done through a different system, Bai&amp;#39; al-Sarf.  They have their own banks: Emirates Islamic Bank, Al Rajhi Bank, Abu Dhabi Islamic Bank and more.  They come with apps.</t>
         </is>
       </c>
       <c r="K18" t="b">
         <v>0</v>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>['stelpetla', 'JDunlap1974']</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>Apr 25</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 7:15 AM UTC</t>
+          <t>Apr 25, 2026 · 12:29 AM UTC</t>
         </is>
       </c>
       <c r="P18" s="2" t="n">
-        <v>46136.30208333334</v>
+        <v>46137.02013888889</v>
       </c>
       <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>['https://abc-gcc.net/News/1/395058', 'https://x.com/search?f=tweets&amp;q=%23ABCNews', 'https://x.com/search?f=tweets&amp;q=%23Profit', 'https://x.com/search?f=tweets&amp;q=%23Banking', 'https://x.com/search?f=tweets&amp;q=%23FinancialInstitution']</t>
-        </is>
-      </c>
+      <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -3298,33 +3535,27 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Emirates Islamic has reported an operating profit of AED1.1 billion ($299.52 million) for the quarter ending March 31, 2026, 7% growth over the same period last year.
-Read more on abc-gcc.net/News/1/395058
-#ABCNews #Profit #Banking #FinancialInstitution</t>
+          <t>Most of the Islamic banking is done through a different system, Bai' al-Sarf.  They have their own banks: Emirates Islamic Bank, Al Rajhi Bank, Abu Dhabi Islamic Bank and more.  They come with apps.</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>https://x.com/ABCinGCC/status/2047575014564921667</t>
+          <t>https://x.com/iDenville/status/2047835274818748466</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>Emirates Islamic has reported an operating profit of AED1.1 billion ($299.52 million) for the quarter ending March 31, 2026, 7% growth over the same period last year.
-Read more on https://t.co/I3d8g2xghd
-#ABCNews #Profit #Banking #FinancialInstitution https://t.co/jfJF6uK62j</t>
+          <t>Judge overturns election after Democrats caught ballot stuffing. https://t.co/sCEs1CS21j</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Emirates Islamic has reported an operating profit of AED1.1 billion ($299.52 million) for the quarter ending March 31, 2026, 7% growth over the same period last year.
-Read more on https://t.co/I3d8g2xghd
-#ABCNews #Profit #Banking #FinancialInstitution https://t.co/jfJF6uK62j</t>
+          <t>Judge overturns election after Democrats caught ballot stuffing. https://t.co/sCEs1CS21j</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Emirates Islamic has reported an operating profit of AED1.1 billion ($299.52 million) for the quarter ending March 31, 2026, a 7% growth over the same period last year.</t>
+          <t>Judge overturns election after Democrats were caught ballot stuffing.</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3334,14 +3565,14 @@
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE18" s="2" t="n">
-        <v>46136.46875</v>
+        <v>46137.18680555555</v>
       </c>
       <c r="AF18" s="2" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
@@ -3355,7 +3586,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Emirates Islamic has reported an operating profit of AED1.1 billion ($299.52 million) for the quarter ending March 31, 2026, a 7% growth over the same period last year.</t>
+          <t>Judge overturns election after Democrats were caught ballot stuffing.</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -3368,7 +3599,7 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>stelpetla, JDunlap1974</t>
         </is>
       </c>
     </row>
@@ -3378,12 +3609,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2047556140431556611</t>
+          <t>2047978927205781948</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047556140431556611</t>
+          <t>https://x.com/emiratesislamic/status/2047978927205781948</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3409,20 +3640,24 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>You have an unpaid fine – click here
-Do not fall for the traps. Stay alert to scams.
-#EIAgainstFraud with Emirates Islamic.
-#TogetherAgainstFraud
-https://t.co/y7eSpGNdfk</t>
+          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
+سعادة بلا حدود!
+تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
+🌟 استرداد يصل إلى 6%، بلا حدود
+🎁 مكافأة ترحيبية تصل إلى 750 درهم
+💳 بدون رسوم سنوية
+🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية https://t.co/NhNzx3Mewv</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>You have an unpaid fine – click here
-Do not fall for the traps. Stay alert to scams.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
-&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
+          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
+سعادة بلا حدود!
+تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
+🌟 استرداد يصل إلى 6%، بلا حدود
+🎁 مكافأة ترحيبية تصل إلى 750 درهم
+💳 بدون رسوم سنوية
+🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية</t>
         </is>
       </c>
       <c r="K19" t="b">
@@ -3432,23 +3667,19 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 6:00 AM UTC</t>
+          <t>Apr 25, 2026 · 10:00 AM UTC</t>
         </is>
       </c>
       <c r="P19" s="2" t="n">
-        <v>46136.25</v>
+        <v>46137.41666666666</v>
       </c>
       <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud', 'https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security']</t>
-        </is>
-      </c>
+      <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
         <v>0</v>
       </c>
@@ -3459,7 +3690,7 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>37</v>
+        <v>85</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -3468,43 +3699,45 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>You have an unpaid fine – click here
-Do not fall for the traps. Stay alert to scams.
-#EIAgainstFraud with Emirates Islamic.
-#TogetherAgainstFraud
-emiratesislamic.ae/en/person…</t>
+          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
+سعادة بلا حدود!
+تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
+🌟 استرداد يصل إلى 6%، بلا حدود
+🎁 مكافأة ترحيبية تصل إلى 750 درهم
+💳 بدون رسوم سنوية
+🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047556140431556611</t>
+          <t>https://x.com/emiratesislamic/status/2047978927205781948</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>You have an unpaid fine – click here
-Do not fall for the traps. Stay alert to scams.
-#EIAgainstFraud with Emirates Islamic.
-#TogetherAgainstFraud
-https://t.co/y7eSpGNdfk</t>
+          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
+سعادة بلا حدود!
+تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
+🌟 استرداد يصل إلى 6%، بلا حدود
+🎁 مكافأة ترحيبية تصل إلى 750 درهم
+💳 بدون رسوم سنوية
+🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية https://t.co/NhNzx3Mewv</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>You have an unpaid fine – click here
-Do not fall for the traps. Stay alert to scams.
-#EIAgainstFraud with Emirates Islamic.
-#TogetherAgainstFraud
-https://t.co/y7eSpGNdfk</t>
+          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
+سعادة بلا حدود!
+تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
+🌟 استرداد يصل إلى 6%، بلا حدود
+🎁 مكافأة ترحيبية تصل إلى 750 درهم
+💳 بدون رسوم سنوية
+🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية https://t.co/NhNzx3Mewv</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>You have an unpaid fine – click here
-Do not fall for the traps. Stay alert to scams.
-#EIAgainstFraud with Emirates Islamic.
-#TogetherAgainstFraud
-https://t.co/y7eSpGNdfk</t>
+          <t>Amazon credit card from Emirates Islamic and MasterCard Unlimited happiness! Discover the card that turns every purchase into unlimited happiness 💳✨ 🌟 Cashback up to 6%, no limits 🎁 Welcome bonus up to 750 dirhams 💳 No annual fees 🌍 Exclusive travel and lifestyle features and discounts</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3514,14 +3747,14 @@
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE19" s="2" t="n">
-        <v>46136.41666666666</v>
+        <v>46137.58333333334</v>
       </c>
       <c r="AF19" s="2" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
@@ -3535,7 +3768,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>You have an unpaid fine – click here Do not fall for the traps. • #TogetherAgainstFraud https://t.co/y7eSpGNdfk • #EIAgainstFraud with Emirates Islamic.</t>
+          <t>Amazon credit card from Emirates Islamic and MasterCard Unlimited happiness!</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -3558,12 +3791,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2047717988195852322</t>
+          <t>2047963837182156928</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047717988195852322</t>
+          <t>https://x.com/emiratesislamic/status/2047963837182156928</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3589,17 +3822,18 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>🇦🇪 تحية تقدير وامتنان لأبطال الوطن
-تقديراً لإخلاصك وتفانيك في خدمة الوطن، قمنا بتصميم باقة حصرية من المزايا المصرفية لنمنحك راحة البال.
-📈 معدلات أرباح مميزة على التمويل https://t.co/DrYnMIk6Zd</t>
+          <t>Quick approvals and easy digital documentation.
+Takaful coverage for yourself and your property.
+Terms &amp; Conditions apply.
+emiratesislamic.ae/en/campai…</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>🇦🇪 We salute the nation’s heroes 
-We value your commitment and have designed exclusive banking benefits for your peace of mind.
-📈 Attractive finance profit rates
-🏦 Zero processing fees</t>
+          <t>Quick approvals and easy digital documentation.
+Takaful coverage for yourself and your property.
+Terms &amp;amp; Conditions apply.
+&lt;a href="https://www.emiratesislamic.ae/en/campaigns/home-finance-for-uae-nationals?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=home_finance"&gt;emiratesislamic.ae/en/campai…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K20" t="b">
@@ -3609,30 +3843,34 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 4:43 PM UTC</t>
+          <t>Apr 25, 2026 · 9:00 AM UTC</t>
         </is>
       </c>
       <c r="P20" s="2" t="n">
-        <v>46136.69652777778</v>
+        <v>46137.375</v>
       </c>
       <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/campaigns/home-finance-for-uae-nationals?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=home_finance']</t>
+        </is>
+      </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -3641,36 +3879,25 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>🇦🇪 We salute the nation’s heroes 
-We value your commitment and have designed exclusive banking benefits for your peace of mind.
-📈 Attractive finance profit rates
-🏦 Zero processing fees</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047717988195852322</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>🇦🇪 تحية تقدير وامتنان لأبطال الوطن
-تقديراً لإخلاصك وتفانيك في خدمة الوطن، قمنا بتصميم باقة حصرية من المزايا المصرفية لنمنحك راحة البال.
-📈 معدلات أرباح مميزة على التمويل https://t.co/DrYnMIk6Zd</t>
-        </is>
-      </c>
+          <t>Quick approvals and easy digital documentation.
+Takaful coverage for yourself and your property.
+Terms &amp; Conditions apply.
+emiratesislamic.ae/en/campai…</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>🇦🇪 تحية تقدير وامتنان لأبطال الوطن
-تقديراً لإخلاصك وتفانيك في خدمة الوطن، قمنا بتصميم باقة حصرية من المزايا المصرفية لنمنحك راحة البال.
-📈 معدلات أرباح مميزة على التمويل https://t.co/DrYnMIk6Zd</t>
+          <t>Quick approvals and easy digital documentation.
+Takaful coverage for yourself and your property.
+Terms &amp; Conditions apply.
+emiratesislamic.ae/en/campai…</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>A greeting of appreciation and gratitude to the heroes of the nation
-In recognition of your dedication and commitment to serving the nation, we have designed an exclusive package of banking benefits to give you peace of mind. 
-Special profit rates on financing</t>
+          <t>Quick approvals and easy digital documentation. Takaful coverage for yourself and your property. Terms &amp; Conditions apply.</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3684,10 +3911,10 @@
         </is>
       </c>
       <c r="AE20" s="2" t="n">
-        <v>46136.86319444444</v>
+        <v>46137.54166666666</v>
       </c>
       <c r="AF20" s="2" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
@@ -3701,7 +3928,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Special profit rates on financing</t>
+          <t>Quick approvals and easy digital documentation. • Takaful coverage for yourself and your property. • Terms &amp; Conditions apply.</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3724,12 +3951,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2047717920193622257</t>
+          <t>2047963832136433706</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047717920193622257</t>
+          <t>https://x.com/emiratesislamic/status/2047963832136433706</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3755,24 +3982,18 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>🏦 بدون رسوم إجراءات
-⏳ تأجيل الأقساط
-🎁 جوائز حصرية مع حساب كنوز المليونير
+          <t>موافقات سريعة ووثائق رقمية سهلة
+تغطية "تكافل" لك ولعقارك للحماية وراحة البال
 تطبق الشروط والأحكام.
-لمعرفة المزيد، تفضل بزيارة
-https://t.co/N2GRIcHWnS
-#الإمارات_الإسلامي #أبطال_الوطن</t>
+emiratesislamic.ae/ar/campai…</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>🏦 بدون رسوم إجراءات
-⏳ تأجيل الأقساط
-🎁 جوائز حصرية مع حساب كنوز المليونير
+          <t>موافقات سريعة ووثائق رقمية سهلة
+تغطية &amp;#34;تكافل&amp;#34; لك ولعقارك للحماية وراحة البال
 تطبق الشروط والأحكام.
-لمعرفة المزيد، تفضل بزيارة
-&lt;a href="https://www.emiratesislamic.ae/ar/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=front_line"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23أبطال_الوطن"&gt;#أبطال_الوطن&lt;/a&gt;</t>
+&lt;a href="https://www.emiratesislamic.ae/ar/campaigns/home-finance-for-uae-nationals?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=home_finance"&gt;emiratesislamic.ae/ar/campai…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K21" t="b">
@@ -3782,25 +4003,25 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 4:42 PM UTC</t>
+          <t>Apr 25, 2026 · 9:00 AM UTC</t>
         </is>
       </c>
       <c r="P21" s="2" t="n">
-        <v>46136.69583333333</v>
+        <v>46137.375</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/ar/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=front_line', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23أبطال_الوطن']</t>
+          <t>['https://www.emiratesislamic.ae/ar/campaigns/home-finance-for-uae-nationals?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=home_finance']</t>
         </is>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
@@ -3809,7 +4030,7 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>212</v>
+        <v>12</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -3818,51 +4039,27 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>🏦 بدون رسوم إجراءات
-⏳ تأجيل الأقساط
-🎁 جوائز حصرية مع حساب كنوز المليونير
+          <t>موافقات سريعة ووثائق رقمية سهلة
+تغطية "تكافل" لك ولعقارك للحماية وراحة البال
 تطبق الشروط والأحكام.
-لمعرفة المزيد، تفضل بزيارة
-emiratesislamic.ae/ar/offers…
-#الإمارات_الإسلامي #أبطال_الوطن</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047717920193622257</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>🏦 بدون رسوم إجراءات
-⏳ تأجيل الأقساط
-🎁 جوائز حصرية مع حساب كنوز المليونير
+emiratesislamic.ae/ar/campai…</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>موافقات سريعة ووثائق رقمية سهلة
+تغطية "تكافل" لك ولعقارك للحماية وراحة البال
 تطبق الشروط والأحكام.
-لمعرفة المزيد، تفضل بزيارة
-https://t.co/N2GRIcHWnS
-#الإمارات_الإسلامي #أبطال_الوطن</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>🏦 بدون رسوم إجراءات
-⏳ تأجيل الأقساط
-🎁 جوائز حصرية مع حساب كنوز المليونير
-تطبق الشروط والأحكام.
-لمعرفة المزيد، تفضل بزيارة
-https://t.co/N2GRIcHWnS
-#الإمارات_الإسلامي #أبطال_الوطن</t>
+emiratesislamic.ae/ar/campai…</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>No processing fees  
-Installments deferred  
-Exclusive rewards with Millionaire Treasures account  
-Terms and conditions apply.  
-To learn more, please visit  
-https://t.co/N2GRIcHWnS  
-#EmiratesIslamic #HeroesOfTheNation</t>
+          <t>Quick approvals and easy digital documents  
+"Takaful" coverage for you and your property for protection and peace of mind  
+Terms and conditions apply.</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3876,10 +4073,10 @@
         </is>
       </c>
       <c r="AE21" s="2" t="n">
-        <v>46136.8625</v>
+        <v>46137.54166666666</v>
       </c>
       <c r="AF21" s="2" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
@@ -3893,7 +4090,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>No processing fees Installments deferred Exclusive rewards with Millionaire Treasures account Terms and conditions apply. • To learn more, please visit https://t.co/N2GRIcHWnS #EmiratesIslamic #HeroesOfTheNation</t>
+          <t>Quick approvals and easy digital documents "Takaful" coverage for you and your property for protection and peace of mind Terms and conditions apply.</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3916,12 +4113,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2047717917324710124</t>
+          <t>2047963827363299676</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047717917324710124</t>
+          <t>https://x.com/emiratesislamic/status/2047963827363299676</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3947,16 +4144,16 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>🇦🇪 تحية تقدير وامتنان لأبطال الوطن
-تقديراً لإخلاصك وتفانيك في خدمة الوطن، قمنا بتصميم باقة حصرية من المزايا المصرفية لنمنحك راحة البال.
-📈 معدلات أرباح مميزة على التمويل</t>
+          <t>تملّك منزلك الجديد بسهولة مع حلول التمويل السكني المرنة من الإمارات الإسلامي واستمتع بمزايا استثنائية
+تمويل يصل إلى %85 من قيمة العقار
+رسوم إجراءات منخفضة ومعدلات ربح تنافسية</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>🇦🇪 تحية تقدير وامتنان لأبطال الوطن
-تقديراً لإخلاصك وتفانيك في خدمة الوطن، قمنا بتصميم باقة حصرية من المزايا المصرفية لنمنحك راحة البال.
-📈 معدلات أرباح مميزة على التمويل</t>
+          <t>تملّك منزلك الجديد بسهولة مع حلول التمويل السكني المرنة من الإمارات الإسلامي واستمتع بمزايا استثنائية
+تمويل يصل إلى %85 من قيمة العقار
+رسوم إجراءات منخفضة ومعدلات ربح تنافسية</t>
         </is>
       </c>
       <c r="K22" t="b">
@@ -3966,16 +4163,16 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 4:42 PM UTC</t>
+          <t>Apr 25, 2026 · 9:00 AM UTC</t>
         </is>
       </c>
       <c r="P22" s="2" t="n">
-        <v>46136.69583333333</v>
+        <v>46137.375</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
@@ -3989,7 +4186,7 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -3998,25 +4195,25 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>🇦🇪 تحية تقدير وامتنان لأبطال الوطن
-تقديراً لإخلاصك وتفانيك في خدمة الوطن، قمنا بتصميم باقة حصرية من المزايا المصرفية لنمنحك راحة البال.
-📈 معدلات أرباح مميزة على التمويل</t>
+          <t>تملّك منزلك الجديد بسهولة مع حلول التمويل السكني المرنة من الإمارات الإسلامي واستمتع بمزايا استثنائية
+تمويل يصل إلى %85 من قيمة العقار
+رسوم إجراءات منخفضة ومعدلات ربح تنافسية</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>🇦🇪 تحية تقدير وامتنان لأبطال الوطن
-تقديراً لإخلاصك وتفانيك في خدمة الوطن، قمنا بتصميم باقة حصرية من المزايا المصرفية لنمنحك راحة البال.
-📈 معدلات أرباح مميزة على التمويل</t>
+          <t>تملّك منزلك الجديد بسهولة مع حلول التمويل السكني المرنة من الإمارات الإسلامي واستمتع بمزايا استثنائية
+تمويل يصل إلى %85 من قيمة العقار
+رسوم إجراءات منخفضة ومعدلات ربح تنافسية</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>A greeting of appreciation and gratitude to the heroes of the nation
-In recognition of your dedication and commitment to serving the nation, we have designed an exclusive package of banking benefits to give you peace of mind. 
-Exceptional profit rates on financing</t>
+          <t>Own your new home easily with flexible housing finance solutions from Emirates Islamic and enjoy exceptional benefits
+Financing of up to 85% of the property value
+Low processing fees and competitive profit rates</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -4030,10 +4227,10 @@
         </is>
       </c>
       <c r="AE22" s="2" t="n">
-        <v>46136.8625</v>
+        <v>46137.54166666666</v>
       </c>
       <c r="AF22" s="2" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
@@ -4047,7 +4244,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Exceptional profit rates on financing</t>
+          <t>Own your new home easily with flexible housing finance solutions from Emirates Islamic and enjoy exceptional benefits Fi…</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -4070,12 +4267,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2047657988064727443</t>
+          <t>2047933638453366977</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047657988064727443</t>
+          <t>https://x.com/emiratesislamic/status/2047933638453366977</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4101,26 +4298,18 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
-📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
-💳 بطاقة خصم للأبناء
-⭐عروض وخصومات حصرية
-🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
-🏆جوائز نقدية يومية وشهرية
-علمهم صغار!
-تطبق الشروط والأحكام. https://t.co/j3JLeVQTou</t>
+          <t>💸 Miles &amp; instant rewards and multiple redemption options
+👍 Cashback, discounts, golf, valet parking at select locations and much more
+Offer valid till 30 June 2026
+emiratesislamic.ae/en/offers…</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
-📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
-💳 بطاقة خصم للأبناء
-⭐عروض وخصومات حصرية
-🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
-🏆جوائز نقدية يومية وشهرية
-علمهم صغار!
-تطبق الشروط والأحكام.</t>
+          <t>💸 Miles &amp;amp; instant rewards and multiple redemption options
+👍 Cashback, discounts, golf, valet parking at select locations and much more
+Offer valid till 30 June 2026
+&lt;a href="https://www.emiratesislamic.ae/en/offers/credit-card-noon-gift-card-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_noon"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K23" t="b">
@@ -4130,19 +4319,23 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 12:44 PM UTC</t>
+          <t>Apr 25, 2026 · 7:00 AM UTC</t>
         </is>
       </c>
       <c r="P23" s="2" t="n">
-        <v>46136.53055555555</v>
+        <v>46137.29166666666</v>
       </c>
       <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/credit-card-noon-gift-card-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_noon']</t>
+        </is>
+      </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
@@ -4153,7 +4346,7 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -4162,55 +4355,25 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
-📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
-💳 بطاقة خصم للأبناء
-⭐عروض وخصومات حصرية
-🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
-🏆جوائز نقدية يومية وشهرية
-علمهم صغار!
-تطبق الشروط والأحكام.</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047657988064727443</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
-📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
-💳 بطاقة خصم للأبناء
-⭐عروض وخصومات حصرية
-🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
-🏆جوائز نقدية يومية وشهرية
-علمهم صغار!
-تطبق الشروط والأحكام. https://t.co/j3JLeVQTou</t>
-        </is>
-      </c>
+          <t>💸 Miles &amp; instant rewards and multiple redemption options
+👍 Cashback, discounts, golf, valet parking at select locations and much more
+Offer valid till 30 June 2026
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
-📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
-💳 بطاقة خصم للأبناء
-⭐عروض وخصومات حصرية
-🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
-🏆جوائز نقدية يومية وشهرية
-علمهم صغار!
-تطبق الشروط والأحكام. https://t.co/j3JLeVQTou</t>
+          <t>💸 Miles &amp; instant rewards and multiple redemption options
+👍 Cashback, discounts, golf, valet parking at select locations and much more
+Offer valid till 30 June 2026
+emiratesislamic.ae/en/offers…</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>We offer you a unique banking experience with the ALPHA account for children, which provides:
-📱 A mobile banking app dedicated to your children
-💳 A debit card for children
-⭐ Exclusive offers and discounts
-🎁 A reward of 100 dirhams on your children's birthday
-🏆 Daily and monthly cash prizes
-Teach them young!
-Terms and conditions apply.</t>
+          <t>Miles and instant rewards with multiple redemption options. Cashback, discounts, golf, valet parking at select locations, and much more. Offer valid until June 30, 2026.</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -4224,10 +4387,10 @@
         </is>
       </c>
       <c r="AE23" s="2" t="n">
-        <v>46136.69722222222</v>
+        <v>46137.45833333334</v>
       </c>
       <c r="AF23" s="2" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
@@ -4241,7 +4404,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Terms and conditions apply.</t>
+          <t>Offer valid until June 30, 2026. • Cashback, discounts, golf, valet parking at select locations, and much more. • Miles and instant rewards with multiple redemption options.</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -4264,12 +4427,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2047657974936604881</t>
+          <t>2047933633118228811</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047657974936604881</t>
+          <t>https://x.com/emiratesislamic/status/2047933633118228811</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4295,14 +4458,18 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Terms &amp; condition apply.
-To know more, please visit emiratesislamic.ae/en/person…</t>
+          <t>💸مكافآت فورية وأميال يمكن استردادها بشكل فوري
+👍 استرداد نقدي، وخصومات، وجولات غولف، وخدمة صف السيارات في مواقع مختارة والمزيد
+يسري العرض لغاية 30 يونيو 2026
+emiratesislamic.ae/ar/offers…</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Terms &amp;amp; condition apply.
-To know more, please visit &lt;a href="https://www.emiratesislamic.ae/en/personal-banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=alpha_youth"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
+          <t>💸مكافآت فورية وأميال يمكن استردادها بشكل فوري
+👍 استرداد نقدي، وخصومات، وجولات غولف، وخدمة صف السيارات في مواقع مختارة والمزيد
+يسري العرض لغاية 30 يونيو 2026
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/credit-card-noon-gift-card-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_noon"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K24" t="b">
@@ -4312,25 +4479,25 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 12:44 PM UTC</t>
+          <t>Apr 25, 2026 · 7:00 AM UTC</t>
         </is>
       </c>
       <c r="P24" s="2" t="n">
-        <v>46136.53055555555</v>
+        <v>46137.29166666666</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/en/personal-banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=alpha_youth']</t>
+          <t>['https://www.emiratesislamic.ae/ar/offers/credit-card-noon-gift-card-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_noon']</t>
         </is>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
@@ -4339,7 +4506,7 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -4348,21 +4515,27 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Terms &amp; condition apply.
-To know more, please visit emiratesislamic.ae/en/person…</t>
+          <t>💸مكافآت فورية وأميال يمكن استردادها بشكل فوري
+👍 استرداد نقدي، وخصومات، وجولات غولف، وخدمة صف السيارات في مواقع مختارة والمزيد
+يسري العرض لغاية 30 يونيو 2026
+emiratesislamic.ae/ar/offers…</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>Terms &amp; condition apply.
-To know more, please visit emiratesislamic.ae/en/person…</t>
+          <t>💸مكافآت فورية وأميال يمكن استردادها بشكل فوري
+👍 استرداد نقدي، وخصومات، وجولات غولف، وخدمة صف السيارات في مواقع مختارة والمزيد
+يسري العرض لغاية 30 يونيو 2026
+emiratesislamic.ae/ar/offers…</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Terms and conditions apply. To know more, please visit emiratesislamic.ae/en/person…</t>
+          <t>Instant rewards and redeemable miles  
+Cashback, discounts, golf rounds, valet service at selected locations, and more  
+The offer is valid until June 30, 2026.</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -4372,14 +4545,14 @@
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE24" s="2" t="n">
-        <v>46136.69722222222</v>
+        <v>46137.45833333334</v>
       </c>
       <c r="AF24" s="2" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
@@ -4393,7 +4566,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>To know more, please visit emiratesislamic.ae/en/person… • Terms and conditions apply.</t>
+          <t>Instant rewards and redeemable miles Cashback, discounts, golf rounds, valet service at selected locations, and more The offer is valid until June 30, 2026.</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -4416,12 +4589,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2047657972390560162</t>
+          <t>2047933629662155095</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047657972390560162</t>
+          <t>https://x.com/emiratesislamic/status/2047933629662155095</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4447,25 +4620,16 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
-📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
-💳 بطاقة خصم للأبناء
-⭐عروض وخصومات حصرية
-🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
-🏆جوائز نقدية يومية وشهرية
-علمهم صغار!
-تطبق الشروط والأحكام. https://t.co/PUCOpaLwMF</t>
+          <t>احصل على بطاقة ائتمانية من الإمارات الإسلامي واستفد من مزايا خاصة:
+🌟 مكافأة ترحيبية تصل قيمتها إلى 1,000 درهم (قسيمة هدايا من noon.com)
+✈️ الدخول إلى صالات المطارات وخدمات الاستقبال والترحيب والتوصيل من وإلى المطار</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Introducing the ALPHA Youth Account, a banking experience that offers:
-📱 Access to a dedicated mobile app
-💳 Complimentary Debit Card for youth
-🏆 Daily &amp;amp; monthly cash prizes
-🎁 A birthday reward of AED 100 for your child
-⭐ Exclusive offers &amp;amp; discounts
-Start them young!</t>
+          <t>احصل على بطاقة ائتمانية من الإمارات الإسلامي واستفد من مزايا خاصة:
+🌟 مكافأة ترحيبية تصل قيمتها إلى 1,000 درهم (قسيمة هدايا من &lt;a href="http://noon.com"&gt;noon.com&lt;/a&gt;)
+✈️ الدخول إلى صالات المطارات وخدمات الاستقبال والترحيب والتوصيل من وإلى المطار</t>
         </is>
       </c>
       <c r="K25" t="b">
@@ -4475,19 +4639,23 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 12:44 PM UTC</t>
+          <t>Apr 25, 2026 · 7:00 AM UTC</t>
         </is>
       </c>
       <c r="P25" s="2" t="n">
-        <v>46136.53055555555</v>
+        <v>46137.29166666666</v>
       </c>
       <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>['http://noon.com']</t>
+        </is>
+      </c>
       <c r="S25" t="n">
         <v>1</v>
       </c>
@@ -4495,10 +4663,10 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" t="n">
-        <v>47</v>
+        <v>137</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -4507,54 +4675,25 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Introducing the ALPHA Youth Account, a banking experience that offers:
-📱 Access to a dedicated mobile app
-💳 Complimentary Debit Card for youth
-🏆 Daily &amp; monthly cash prizes
-🎁 A birthday reward of AED 100 for your child
-⭐ Exclusive offers &amp; discounts
-Start them young!</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047657972390560162</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
-📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
-💳 بطاقة خصم للأبناء
-⭐عروض وخصومات حصرية
-🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
-🏆جوائز نقدية يومية وشهرية
-علمهم صغار!
-تطبق الشروط والأحكام. https://t.co/PUCOpaLwMF</t>
-        </is>
-      </c>
+          <t>احصل على بطاقة ائتمانية من الإمارات الإسلامي واستفد من مزايا خاصة:
+🌟 مكافأة ترحيبية تصل قيمتها إلى 1,000 درهم (قسيمة هدايا من noon.com)
+✈️ الدخول إلى صالات المطارات وخدمات الاستقبال والترحيب والتوصيل من وإلى المطار</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
-📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
-💳 بطاقة خصم للأبناء
-⭐عروض وخصومات حصرية
-🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
-🏆جوائز نقدية يومية وشهرية
-علمهم صغار!
-تطبق الشروط والأحكام. https://t.co/PUCOpaLwMF</t>
+          <t>احصل على بطاقة ائتمانية من الإمارات الإسلامي واستفد من مزايا خاصة:
+🌟 مكافأة ترحيبية تصل قيمتها إلى 1,000 درهم (قسيمة هدايا من noon.com)
+✈️ الدخول إلى صالات المطارات وخدمات الاستقبال والترحيب والتوصيل من وإلى المطار</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>We offer you a unique banking experience with the ALPHA account for children, which provides:
-📱 A mobile banking app dedicated to your children
-💳 A debit card for children
-⭐ Exclusive offers and discounts
-🎁 A reward of 100 dirhams on your children's birthday
-🏆 Daily and monthly cash prizes
-Teach them young!
-Terms and conditions apply.</t>
+          <t>Get a credit card from Emirates Islamic and enjoy special benefits:
+🌟 A welcome bonus of up to 1,000 dirhams (gift voucher from noon.com)
+✈️ Access to airport lounges and reception, welcome, and transportation services to and from the airport</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -4568,10 +4707,10 @@
         </is>
       </c>
       <c r="AE25" s="2" t="n">
-        <v>46136.69722222222</v>
+        <v>46137.45833333334</v>
       </c>
       <c r="AF25" s="2" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
@@ -4585,7 +4724,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Terms and conditions apply.</t>
+          <t>Get a credit card from Emirates Islamic and enjoy special benefits: 🌟 A welcome bonus of up to 1,000 dirhams (gift vouch…</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -4608,12 +4747,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2047657962978558100</t>
+          <t>2047918534362030486</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047657962978558100</t>
+          <t>https://x.com/emiratesislamic/status/2047918534362030486</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4639,12 +4778,12 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>لمعرفة المزيد، يرجى زيارة emiratesislamic.ae/ar/person…</t>
+          <t>من فتح حساب فوري للاستثمارات حسب أحكام الشريعة الإسلامية، يمكنك الآن الحصول على أكثر من 200 خدمة مصرفية عبر تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك. https://t.co/KcPGd1gMey</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>لمعرفة المزيد، يرجى زيارة &lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=alpha_youth"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
+          <t>From instant account opening to shariah-compliant investments, benefit from 200+ banking services via the EI + Mobile Banking App.</t>
         </is>
       </c>
       <c r="K26" t="b">
@@ -4654,25 +4793,21 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 12:44 PM UTC</t>
+          <t>Apr 25, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P26" s="2" t="n">
-        <v>46136.53055555555</v>
+        <v>46137.25</v>
       </c>
       <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/personal-banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=alpha_youth']</t>
-        </is>
-      </c>
+      <c r="R26" t="inlineStr"/>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
@@ -4681,7 +4816,7 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -4690,19 +4825,27 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>لمعرفة المزيد، يرجى زيارة emiratesislamic.ae/ar/person…</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
+          <t>From instant account opening to shariah-compliant investments, benefit from 200+ banking services via the EI + Mobile Banking App.</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047918534362030486</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>من فتح حساب فوري للاستثمارات حسب أحكام الشريعة الإسلامية، يمكنك الآن الحصول على أكثر من 200 خدمة مصرفية عبر تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك. https://t.co/KcPGd1gMey</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>لمعرفة المزيد، يرجى زيارة emiratesislamic.ae/ar/person…</t>
+          <t>من فتح حساب فوري للاستثمارات حسب أحكام الشريعة الإسلامية، يمكنك الآن الحصول على أكثر من 200 خدمة مصرفية عبر تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك. https://t.co/KcPGd1gMey</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>To learn more, please visit emiratesislamic.ae/ar/person…</t>
+          <t>If you open an instant investment account according to Islamic law, you can now access more than 200 banking services through the + EI mobile banking app.</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4712,14 +4855,14 @@
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE26" s="2" t="n">
-        <v>46136.69722222222</v>
+        <v>46137.41666666666</v>
       </c>
       <c r="AF26" s="2" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
@@ -4733,7 +4876,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>To learn more, please visit emiratesislamic.ae/ar/person…</t>
+          <t>If you open an instant investment account according to Islamic law, you can now access more than 200 banking services through the + EI mobile banking app.</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -4756,12 +4899,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2047657960227176876</t>
+          <t>2047918530113266095</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047657960227176876</t>
+          <t>https://x.com/emiratesislamic/status/2047918530113266095</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4787,26 +4930,12 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
-📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
-💳 بطاقة خصم للأبناء
-⭐عروض وخصومات حصرية
-🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
-🏆جوائز نقدية يومية وشهرية
-علمهم صغار!
-تطبق الشروط والأحكام.</t>
+          <t>من فتح حساب فوري للاستثمارات حسب أحكام الشريعة الإسلامية، يمكنك الآن الحصول على أكثر من 200 خدمة مصرفية عبر تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
-📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
-💳 بطاقة خصم للأبناء
-⭐عروض وخصومات حصرية
-🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
-🏆جوائز نقدية يومية وشهرية
-علمهم صغار!
-تطبق الشروط والأحكام.</t>
+          <t>من فتح حساب فوري للاستثمارات حسب أحكام الشريعة الإسلامية، يمكنك الآن الحصول على أكثر من 200 خدمة مصرفية عبر تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك.</t>
         </is>
       </c>
       <c r="K27" t="b">
@@ -4816,16 +4945,16 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 12:44 PM UTC</t>
+          <t>Apr 25, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P27" s="2" t="n">
-        <v>46136.53055555555</v>
+        <v>46137.25</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
@@ -4839,7 +4968,7 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -4848,40 +4977,19 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
-📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
-💳 بطاقة خصم للأبناء
-⭐عروض وخصومات حصرية
-🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
-🏆جوائز نقدية يومية وشهرية
-علمهم صغار!
-تطبق الشروط والأحكام.</t>
+          <t>من فتح حساب فوري للاستثمارات حسب أحكام الشريعة الإسلامية، يمكنك الآن الحصول على أكثر من 200 خدمة مصرفية عبر تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك.</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
-📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
-💳 بطاقة خصم للأبناء
-⭐عروض وخصومات حصرية
-🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
-🏆جوائز نقدية يومية وشهرية
-علمهم صغار!
-تطبق الشروط والأحكام.</t>
+          <t>من فتح حساب فوري للاستثمارات حسب أحكام الشريعة الإسلامية، يمكنك الآن الحصول على أكثر من 200 خدمة مصرفية عبر تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك.</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>We offer you a unique banking experience with the ALPHA account for children, which provides:
-📱 A mobile banking app dedicated to your children
-💳 A debit card for children
-⭐ Exclusive offers and discounts
-🎁 A reward of 100 dirhams on your children's birthday
-🏆 Daily and monthly cash prizes
-Teach them young!
-Terms and conditions apply.</t>
+          <t>If you open an instant investment account according to Islamic law, you can now access more than 200 banking services through the + EI mobile banking app.</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4895,10 +5003,10 @@
         </is>
       </c>
       <c r="AE27" s="2" t="n">
-        <v>46136.69722222222</v>
+        <v>46137.41666666666</v>
       </c>
       <c r="AF27" s="2" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
@@ -4912,7 +5020,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Terms and conditions apply.</t>
+          <t>If you open an instant investment account according to Islamic law, you can now access more than 200 banking services through the + EI mobile banking app.</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -4935,49 +5043,43 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2047632173461561410</t>
+          <t>2047936203438362829</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047632173461561410</t>
+          <t>https://x.com/AmritMohanty1/status/2047936203438362829</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/AmritMohanty1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>AmritMohanty1</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Amrit Mohanty</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1798792220885307395/ZFbORVL__bigger.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Transfer your salary now &amp;amp; enjoy rewarding benefits and guaranteed cashback of up to AED 6,000!
-Enjoy more rewards:
-💳 Exclusive Credit Card benefits, airport lounge access, rewards &amp;amp; more https://t.co/w9nMkMnJJb</t>
+          <t>Disappointed with @EmiratesNBD_AE support on reported fraudulent credit card charges. Disputed amounts still show as payable and due date is near. Requested urgent review, temporary credit, and waiver of fees/interest pending investigation. Please assist urgently. #EmiratesNBD</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>🎁 Reward of AED 100 with an ALPHA Youth Account
-And much more.
-Offer valid till 31 May 2026.
-Terms &amp;amp; conditions apply.
-&lt;a href="https://www.emiratesislamic.ae/ar/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=salary_transfer"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+          <t>Disappointed with &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; support on reported fraudulent credit card charges. Disputed amounts still show as payable and due date is near. Requested urgent review, temporary credit, and waiver of fees/interest pending investigation. Please assist urgently. &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K28" t="b">
@@ -4987,25 +5089,25 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 11:02 AM UTC</t>
+          <t>Apr 25, 2026 · 7:10 AM UTC</t>
         </is>
       </c>
       <c r="P28" s="2" t="n">
-        <v>46136.45972222222</v>
+        <v>46137.29861111111</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/ar/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=salary_transfer']</t>
+          <t>['https://x.com/EmiratesNBD_AE', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBD']</t>
         </is>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -5014,2184 +5116,70 @@
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>24</v>
+        <v>140</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>🎁 Reward of AED 100 with an ALPHA Youth Account
-And much more.
-Offer valid till 31 May 2026.
-Terms &amp; conditions apply.
-emiratesislamic.ae/ar/offers…</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047632173461561410</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>Transfer your salary now &amp;amp; enjoy rewarding benefits and guaranteed cashback of up to AED 6,000!
-Enjoy more rewards:
-💳 Exclusive Credit Card benefits, airport lounge access, rewards &amp;amp; more https://t.co/w9nMkMnJJb</t>
-        </is>
-      </c>
+          <t>Disappointed with @EmiratesNBD_AE support on reported fraudulent credit card charges. Disputed amounts still show as payable and due date is near. Requested urgent review, temporary credit, and waiver of fees/interest pending investigation. Please assist urgently. #EmiratesNBD</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>Transfer your salary now &amp;amp; enjoy rewarding benefits and guaranteed cashback of up to AED 6,000!
-Enjoy more rewards:
-💳 Exclusive Credit Card benefits, airport lounge access, rewards &amp;amp; more https://t.co/w9nMkMnJJb</t>
+          <t>Disappointed with @EmiratesNBD_AE support on reported fraudulent credit card charges. Disputed amounts still show as payable and due date is near. Requested urgent review, temporary credit, and waiver of fees/interest pending investigation. Please assist urgently. #EmiratesNBD</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Transfer your salary now and enjoy rewarding benefits and guaranteed cashback of up to AED 6,000! 
-Enjoy more rewards:
-Exclusive credit card benefits, airport lounge access, rewards, and more.</t>
+          <t>Disappointed with Emirates NBD's support regarding reported fraudulent credit card charges. The disputed amounts still show as payable and the due date is approaching. I requested an urgent review, temporary credit, and a waiver of fees/interest pending investigation. Please assist urgently.</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Cust</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="AE28" s="2" t="n">
-        <v>46136.62638888889</v>
+        <v>46137.46527777778</v>
       </c>
       <c r="AF28" s="2" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
+          <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Transfer your salary now and enjoy rewarding benefits and guaranteed cashback of up to AED 6,000! • Enjoy more rewards: Exclusive credit card benefits, airport lounge access, rewards, and more.</t>
+          <t>Disappointed with Emirates NBD's support regarding reported fraudulent credit card charges. • I requested an urgent review, temporary credit, and a waiver of fees/interest pending investigation. • The disputed amounts still show as payable and the due date is approaching.</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>Emirates Islamic Bank (EIB)</t>
+          <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
       <c r="AK28" t="n">
         <v>2026</v>
       </c>
       <c r="AL28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2047632164863250935</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047632164863250935</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Transfer your salary now &amp; enjoy rewarding benefits and guaranteed cashback of up to AED 6,000!
-Enjoy more rewards:
-💳 Exclusive Credit Card benefits, airport lounge access, rewards &amp; more</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Transfer your salary now &amp;amp; enjoy rewarding benefits and guaranteed cashback of up to AED 6,000!
-Enjoy more rewards:
-💳 Exclusive Credit Card benefits, airport lounge access, rewards &amp;amp; more</t>
-        </is>
-      </c>
-      <c r="K29" t="b">
-        <v>0</v>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 11:02 AM UTC</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="n">
-        <v>46136.45972222222</v>
-      </c>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>35</v>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>Transfer your salary now &amp; enjoy rewarding benefits and guaranteed cashback of up to AED 6,000!
-Enjoy more rewards:
-💳 Exclusive Credit Card benefits, airport lounge access, rewards &amp; more</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>Transfer your salary now &amp; enjoy rewarding benefits and guaranteed cashback of up to AED 6,000!
-Enjoy more rewards:
-💳 Exclusive Credit Card benefits, airport lounge access, rewards &amp; more</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>Transfer your salary now and enjoy rewarding benefits and guaranteed cashback of up to AED 6,000! Enjoy more rewards: Exclusive credit card benefits, airport lounge access, rewards, and more.</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="AE29" s="2" t="n">
-        <v>46136.62638888889</v>
-      </c>
-      <c r="AF29" s="2" t="n">
-        <v>46136</v>
-      </c>
-      <c r="AG29" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Transfer your salary now and enjoy rewarding benefits and guaranteed cashback of up to AED 6,000! • Enjoy more rewards: Exclusive credit card benefits, airport lounge access, rewards, and more.</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK29" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL29" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2047632125583605871</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047632125583605871</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني
-🎁 مكافأة 100 درهم مع حساب ALPHA للأبناء
-وغير ذلك الكثير.
-يسري العرض لغاية 31 مايو 2026.
-تطبق الشروط والأحكام.
-emiratesislamic.ae/en/offers…</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني
-🎁 مكافأة 100 درهم مع حساب ALPHA للأبناء
-وغير ذلك الكثير.
-يسري العرض لغاية 31 مايو 2026.
-تطبق الشروط والأحكام.
-&lt;a href="https://www.emiratesislamic.ae/en/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=salary_transfer"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K30" t="b">
-        <v>0</v>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 11:01 AM UTC</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="n">
-        <v>46136.45902777778</v>
-      </c>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=salary_transfer']</t>
-        </is>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>41</v>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني
-🎁 مكافأة 100 درهم مع حساب ALPHA للأبناء
-وغير ذلك الكثير.
-يسري العرض لغاية 31 مايو 2026.
-تطبق الشروط والأحكام.
-emiratesislamic.ae/en/offers…</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني
-🎁 مكافأة 100 درهم مع حساب ALPHA للأبناء
-وغير ذلك الكثير.
-يسري العرض لغاية 31 مايو 2026.
-تطبق الشروط والأحكام.
-emiratesislamic.ae/en/offers…</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>Competitive profit rates on auto financing and housing financing  
-A 100 dirham reward with the ALPHA account for children  
-And much more.  
-The offer is valid until May 31, 2026.  
-Terms and conditions apply.  
-emiratesislamic.ae/en/offers…</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="AE30" s="2" t="n">
-        <v>46136.62569444445</v>
-      </c>
-      <c r="AF30" s="2" t="n">
-        <v>46136</v>
-      </c>
-      <c r="AG30" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Competitive profit rates on auto financing and housing financing A 100 dirham reward with the ALPHA account for children And much more. • The offer is valid until May 31, 2026. • Terms and conditions apply.</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK30" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL30" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2047632116649689120</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047632116649689120</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
-استمتع بالمزيد من المكافآت:
-💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد https://t.co/DfoSsbwLQd</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
-استمتع بالمزيد من المكافآت:
-💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد</t>
-        </is>
-      </c>
-      <c r="K31" t="b">
-        <v>0</v>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 11:01 AM UTC</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="n">
-        <v>46136.45902777778</v>
-      </c>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="n">
-        <v>1</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>37</v>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
-استمتع بالمزيد من المكافآت:
-💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047632116649689120</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
-استمتع بالمزيد من المكافآت:
-💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد https://t.co/DfoSsbwLQd</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
-استمتع بالمزيد من المكافآت:
-💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد https://t.co/DfoSsbwLQd</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>Transfer your salary now and enjoy special benefits and earn guaranteed cash back of up to 6,000 dirhams!
-Enjoy more rewards:
-💳 Exclusive benefits on the credit card, access to airport lounges, rewards, and more.</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="AE31" s="2" t="n">
-        <v>46136.62569444445</v>
-      </c>
-      <c r="AF31" s="2" t="n">
-        <v>46136</v>
-      </c>
-      <c r="AG31" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Transfer your salary now and enjoy special benefits and earn guaranteed cash back of up to 6,000 dirhams! • Enjoy more rewards: 💳 Exclusive benefits on the credit card, access to airport lounges, rewards, and more.</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK31" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2047631643926483032</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047631643926483032</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>احصل على iPhone 17 مضمون عند التقدم بطلب تمويل شخصي من الإمارات الإسلامي.
-استمتع أيضاً بالمزايا الحصرية:
-📊 معدلات ربح تبدأ من %2.59 ثابتة سنوياً (ما يعادل تقريباً %4.74 كمعدل متناقص سنوياً).
-🏦 مبلغ تمويلي يصل إلى 4,000,000 درهم https://t.co/eMEYGVmxwY</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>✈️ تأجيل القسط الأول لمدة تصل إلى 6 شهور
-🔒 تغطية تكافلية
-يسري العرض لغاية 30 أبريل 2026.
-تطبق الشروط والأحكام.
-&lt;a href="https://www.emiratesislamic.ae/ar/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=pf_iphone17"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K32" t="b">
-        <v>0</v>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 11:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="n">
-        <v>46136.45833333334</v>
-      </c>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=pf_iphone17']</t>
-        </is>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>25</v>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>✈️ تأجيل القسط الأول لمدة تصل إلى 6 شهور
-🔒 تغطية تكافلية
-يسري العرض لغاية 30 أبريل 2026.
-تطبق الشروط والأحكام.
-emiratesislamic.ae/ar/offers…</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047631643926483032</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>احصل على iPhone 17 مضمون عند التقدم بطلب تمويل شخصي من الإمارات الإسلامي.
-استمتع أيضاً بالمزايا الحصرية:
-📊 معدلات ربح تبدأ من %2.59 ثابتة سنوياً (ما يعادل تقريباً %4.74 كمعدل متناقص سنوياً).
-🏦 مبلغ تمويلي يصل إلى 4,000,000 درهم https://t.co/eMEYGVmxwY</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>احصل على iPhone 17 مضمون عند التقدم بطلب تمويل شخصي من الإمارات الإسلامي.
-استمتع أيضاً بالمزايا الحصرية:
-📊 معدلات ربح تبدأ من %2.59 ثابتة سنوياً (ما يعادل تقريباً %4.74 كمعدل متناقص سنوياً).
-🏦 مبلغ تمويلي يصل إلى 4,000,000 درهم https://t.co/eMEYGVmxwY</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>Get a guaranteed iPhone 17 when applying for a personal loan from Emirates Islamic.
-Also enjoy exclusive benefits:
-📊 Profit rates starting from 2.59% fixed annually (equivalent to approximately 4.74% as a declining annual rate).
-🏦 Financing amount up to 4,000,000 AED.</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="AD32" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="AE32" s="2" t="n">
-        <v>46136.625</v>
-      </c>
-      <c r="AF32" s="2" t="n">
-        <v>46136</v>
-      </c>
-      <c r="AG32" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>Also enjoy exclusive benefits: 📊 Profit rates starting from 2.59% fixed annually (equivalent to approximately 4.74% as a declining annual rate). • 🏦 Financing amount up to 4,000,000 AED. • Get a guaranteed iPhone 17 when applying for a personal loan from Emirates Islamic.</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK32" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>31</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2047631643901390924</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047631643901390924</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>✈️Payment holiday up to 6 months 
-🔒 Complimentary Takaful coverage
-Offer valid until 30 April 2026.
-T&amp;Cs apply.
-emiratesislamic.ae/en/offers…</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>✈️Payment holiday up to 6 months 
-🔒 Complimentary Takaful coverage
-Offer valid until 30 April 2026.
-T&amp;amp;Cs apply.
-&lt;a href="https://www.emiratesislamic.ae/en/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=pf_iphone17"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K33" t="b">
-        <v>0</v>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 11:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="n">
-        <v>46136.45833333334</v>
-      </c>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=pf_iphone17']</t>
-        </is>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>19</v>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>✈️Payment holiday up to 6 months 
-🔒 Complimentary Takaful coverage
-Offer valid until 30 April 2026.
-T&amp;Cs apply.
-emiratesislamic.ae/en/offers…</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>✈️Payment holiday up to 6 months 
-🔒 Complimentary Takaful coverage
-Offer valid until 30 April 2026.
-T&amp;Cs apply.
-emiratesislamic.ae/en/offers…</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>Payment holiday up to 6 months  
-Complimentary Takaful coverage  
-Offer valid until 30 April 2026.  
-T&amp;Cs apply.  
-emiratesislamic.ae/en/offers…</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="AE33" s="2" t="n">
-        <v>46136.625</v>
-      </c>
-      <c r="AF33" s="2" t="n">
-        <v>46136</v>
-      </c>
-      <c r="AG33" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Payment holiday up to 6 months Complimentary Takaful coverage Offer valid until 30 April 2026. • emiratesislamic.ae/en/offers…</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK33" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL33" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2047631639946093018</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047631639946093018</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>احصل على iPhone 17 مضمون عند التقدم بطلب تمويل شخصي من الإمارات الإسلامي.
-استمتع أيضاً بالمزايا الحصرية:
-📊 معدلات ربح تبدأ من %2.59 ثابتة سنوياً (ما يعادل تقريباً %4.74 كمعدل متناقص سنوياً).
-🏦 مبلغ تمويلي يصل إلى 4,000,000 درهم</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>احصل على iPhone 17 مضمون عند التقدم بطلب تمويل شخصي من الإمارات الإسلامي.
-استمتع أيضاً بالمزايا الحصرية:
-📊 معدلات ربح تبدأ من %2.59 ثابتة سنوياً (ما يعادل تقريباً %4.74 كمعدل متناقص سنوياً).
-🏦 مبلغ تمويلي يصل إلى 4,000,000 درهم</t>
-        </is>
-      </c>
-      <c r="K34" t="b">
-        <v>0</v>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 11:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="n">
-        <v>46136.45833333334</v>
-      </c>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="n">
-        <v>1</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>41</v>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>احصل على iPhone 17 مضمون عند التقدم بطلب تمويل شخصي من الإمارات الإسلامي.
-استمتع أيضاً بالمزايا الحصرية:
-📊 معدلات ربح تبدأ من %2.59 ثابتة سنوياً (ما يعادل تقريباً %4.74 كمعدل متناقص سنوياً).
-🏦 مبلغ تمويلي يصل إلى 4,000,000 درهم</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>احصل على iPhone 17 مضمون عند التقدم بطلب تمويل شخصي من الإمارات الإسلامي.
-استمتع أيضاً بالمزايا الحصرية:
-📊 معدلات ربح تبدأ من %2.59 ثابتة سنوياً (ما يعادل تقريباً %4.74 كمعدل متناقص سنوياً).
-🏦 مبلغ تمويلي يصل إلى 4,000,000 درهم</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>Get a guaranteed iPhone 17 when applying for a personal loan from Emirates Islamic.
-Also enjoy exclusive benefits:
-📊 Profit rates starting from 2.59% fixed annually (equivalent to approximately 4.74% as a declining annual rate).
-🏦 Financing amount up to 4,000,000 AED.</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="AE34" s="2" t="n">
-        <v>46136.625</v>
-      </c>
-      <c r="AF34" s="2" t="n">
-        <v>46136</v>
-      </c>
-      <c r="AG34" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>Also enjoy exclusive benefits: 📊 Profit rates starting from 2.59% fixed annually (equivalent to approximately 4.74% as a declining annual rate). • 🏦 Financing amount up to 4,000,000 AED. • Get a guaranteed iPhone 17 when applying for a personal loan from Emirates Islamic.</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK34" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL34" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>33</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2047541045768962304</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047541045768962304</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Together, we raise the flag with pride, celebrating the UAE and its enduring values 🇦🇪
-Across our branches, staff and customers came together in a patriotic atmosphere that embodied unity, belonging, and a deep sense of pride in the nation.
-#ProudOfUAE</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Together, we raise the flag with pride, celebrating the UAE and its enduring values 🇦🇪
-Across our branches, staff and customers came together in a patriotic atmosphere that embodied unity, belonging, and a deep sense of pride in the nation.
-&lt;a href="/search?f=tweets&amp;amp;q=%23ProudOfUAE"&gt;#ProudOfUAE&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K35" t="b">
-        <v>0</v>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 5:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="n">
-        <v>46136.20833333334</v>
-      </c>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23ProudOfUAE']</t>
-        </is>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>49</v>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>Together, we raise the flag with pride, celebrating the UAE and its enduring values 🇦🇪
-Across our branches, staff and customers came together in a patriotic atmosphere that embodied unity, belonging, and a deep sense of pride in the nation.
-#ProudOfUAE</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>Together, we raise the flag with pride, celebrating the UAE and its enduring values 🇦🇪
-Across our branches, staff and customers came together in a patriotic atmosphere that embodied unity, belonging, and a deep sense of pride in the nation.
-#ProudOfUAE</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>Together, we raise the flag with pride, celebrating the UAE and its enduring values. Across our branches, staff and customers came together in a patriotic atmosphere that embodied unity, belonging, and a deep sense of pride in the nation.</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE35" s="2" t="n">
-        <v>46136.375</v>
-      </c>
-      <c r="AF35" s="2" t="n">
-        <v>46136</v>
-      </c>
-      <c r="AG35" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Across our branches, staff and customers came together in a patriotic atmosphere that embodied unity, belonging, and a deep sense of pride in the nation. • Together, we raise the flag with pride, celebrating the UAE and its enduring values.</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK35" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL35" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>34</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2047541041612427486</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047541041612427486</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>معًا، نُعلي راية الفخر احتفاءً بالإمارات وقيمها الراسخة 🇦🇪
-من قلب فروعنا، اجتمع الموظفون والعملاء في أجواء وطنية جسّدت روح الانتماء والوحدة، وعكست مشاعر الفخر بالوطن.
-#فخورين_بالإمارات https://t.co/b3HOjAP5Rw</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>معًا، نُعلي راية الفخر احتفاءً بالإمارات وقيمها الراسخة 🇦🇪
-من قلب فروعنا، اجتمع الموظفون والعملاء في أجواء وطنية جسّدت روح الانتماء والوحدة، وعكست مشاعر الفخر بالوطن.
-&lt;a href="/search?f=tweets&amp;amp;q=%23فخورين_بالإمارات"&gt;#فخورين_بالإمارات&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K36" t="b">
-        <v>0</v>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 5:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="n">
-        <v>46136.20833333334</v>
-      </c>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23فخورين_بالإمارات']</t>
-        </is>
-      </c>
-      <c r="S36" t="n">
-        <v>1</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>3</v>
-      </c>
-      <c r="V36" t="n">
-        <v>207</v>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>معًا، نُعلي راية الفخر احتفاءً بالإمارات وقيمها الراسخة 🇦🇪
-من قلب فروعنا، اجتمع الموظفون والعملاء في أجواء وطنية جسّدت روح الانتماء والوحدة، وعكست مشاعر الفخر بالوطن.
-#فخورين_بالإمارات</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047541041612427486</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>معًا، نُعلي راية الفخر احتفاءً بالإمارات وقيمها الراسخة 🇦🇪
-من قلب فروعنا، اجتمع الموظفون والعملاء في أجواء وطنية جسّدت روح الانتماء والوحدة، وعكست مشاعر الفخر بالوطن.
-#فخورين_بالإمارات https://t.co/b3HOjAP5Rw</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>معًا، نُعلي راية الفخر احتفاءً بالإمارات وقيمها الراسخة 🇦🇪
-من قلب فروعنا، اجتمع الموظفون والعملاء في أجواء وطنية جسّدت روح الانتماء والوحدة، وعكست مشاعر الفخر بالوطن.
-#فخورين_بالإمارات https://t.co/b3HOjAP5Rw</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>Together, we raise the flag of pride in celebration of the UAE and its enduring values 🇦🇪
-From the heart of our branches, employees and customers gathered in a national atmosphere that embodied the spirit of belonging and unity, reflecting feelings of pride in the homeland.
-#Proud_of_the_UAE</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="AD36" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE36" s="2" t="n">
-        <v>46136.375</v>
-      </c>
-      <c r="AF36" s="2" t="n">
-        <v>46136</v>
-      </c>
-      <c r="AG36" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>Together, we raise the flag of pride in celebration of the UAE and its enduring values 🇦🇪 From the heart of our branches…</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK36" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL36" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>35</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2047725724354633861</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>https://x.com/RakshtVaghasiya/status/2047725724354633861</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>https://x.com/RakshtVaghasiya</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>RakshtVaghasiya</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Rakshit Vaghasiya</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2030191909399105536/cFPhY9vR_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_KSA 
-I raised mail to customer care regarding flight amount deduction descripancy twice but didn't hear from Emirates NBD. This is not acceptable at all. I am very much disappointed with customer care service of Emirates NBD. Zero star.</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Same reply every time but no concrete solutions. Just a pathetic approach..</t>
-        </is>
-      </c>
-      <c r="K37" t="b">
-        <v>0</v>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_KSA']</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>9h</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 5:13 PM UTC</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="n">
-        <v>46136.71736111111</v>
-      </c>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="n">
-        <v>1</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>5</v>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>Same reply every time but no concrete solutions. Just a pathetic approach..</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>https://x.com/RakshtVaghasiya/status/2047725724354633861</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_KSA 
-I raised mail to customer care regarding flight amount deduction descripancy twice but didn't hear from Emirates NBD. This is not acceptable at all. I am very much disappointed with customer care service of Emirates NBD. Zero star.</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_KSA 
-I raised mail to customer care regarding flight amount deduction descripancy twice but didn't hear from Emirates NBD. This is not acceptable at all. I am very much disappointed with customer care service of Emirates NBD. Zero star.</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>I raised a mail to customer care regarding the flight amount deduction discrepancy twice but didn't hear from Emirates NBD. This is not acceptable at all. I am very disappointed with the customer care service of Emirates NBD. Zero stars.</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD37" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="AE37" s="2" t="n">
-        <v>46136.88402777778</v>
-      </c>
-      <c r="AF37" s="2" t="n">
-        <v>46136</v>
-      </c>
-      <c r="AG37" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>I raised a mail to customer care regarding the flight amount deduction discrepancy twice but didn't hear from Emirates NBD. • I am very disappointed with the customer care service of Emirates NBD. • This is not acceptable at all.</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK37" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL37" t="inlineStr">
-        <is>
-          <t>EmiratesNBD_KSA</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>36</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2047511223839908158</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>https://x.com/abhiseksonusonu/status/2047511223839908158</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>https://x.com/abhiseksonusonu</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>abhiseksonusonu</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>A R mishra</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1912019334932611072/h2qIgZ-L_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>@LivBank @EmiratesNBD_AE I deposited cash via ENBD ATM toward my credit card on 21st April but amount got stuck. Complaint already raised, yet the amount is still not credited. My due date is this Monday. Request urgent resolution and credit of funds.</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>&lt;a href="/LivBank" title="Liv Digital Bank"&gt;@LivBank&lt;/a&gt; &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; I deposited cash via ENBD ATM toward my credit card on 21st April but amount got stuck. Complaint already raised, yet the amount is still not credited. My due date is this Monday. Request urgent resolution and credit of funds.</t>
-        </is>
-      </c>
-      <c r="K38" t="b">
-        <v>0</v>
-      </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>23h</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 3:01 AM UTC</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="n">
-        <v>46136.12569444445</v>
-      </c>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>['https://x.com/LivBank', 'https://x.com/EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="S38" t="n">
-        <v>1</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>65</v>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>@LivBank @EmiratesNBD_AE I deposited cash via ENBD ATM toward my credit card on 21st April but amount got stuck. Complaint already raised, yet the amount is still not credited. My due date is this Monday. Request urgent resolution and credit of funds.</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>https://x.com/abhiseksonusonu/status/2047511223839908158</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>@LivBank @EmiratesNBD_AE I deposited cash via ENBD ATM toward my credit card on 21st April but amount got stuck. Complaint already raised, yet the amount is still not credited. My due date is this Monday. Request urgent resolution and credit of funds.</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>@LivBank @EmiratesNBD_AE I deposited cash via ENBD ATM toward my credit card on 21st April but amount got stuck. Complaint already raised, yet the amount is still not credited. My due date is this Monday. Request urgent resolution and credit of funds.</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>I deposited cash via ENBD ATM toward my credit card on April 21, but the amount got stuck. A complaint has already been raised, yet the amount is still not credited. My due date is this Monday. I request an urgent resolution and credit of funds.</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD38" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="AE38" s="2" t="n">
-        <v>46136.29236111111</v>
-      </c>
-      <c r="AF38" s="2" t="n">
-        <v>46136</v>
-      </c>
-      <c r="AG38" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>I deposited cash via ENBD ATM toward my credit card on April 21, but the amount got stuck. • A complaint has already been raised, yet the amount is still not credited. • I request an urgent resolution and credit of funds.</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK38" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL38" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>37</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2047556140511162463</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047556140511162463</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>عليك غرامة لم تُسدّد بعد – اضغط هنا
-لا تقع في الفخ. احذر الاحتيال.
-#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
-https://t.co/ltnxcRlBOA</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>عليك غرامة لم تُسدّد بعد – اضغط هنا
-لا تقع في الفخ. احذر الاحتيال.
-&lt;a href="/search?f=tweets&amp;amp;q=%23متحّدون_ضد_الاحتيال"&gt;#متحّدون_ضد_الاحتيال&lt;/a&gt; مع الإمارات الإسلامي.
-&lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K39" t="b">
-        <v>0</v>
-      </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 6:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="n">
-        <v>46136.25</v>
-      </c>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23متحّدون_ضد_الاحتيال', 'https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security']</t>
-        </is>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>59</v>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>عليك غرامة لم تُسدّد بعد – اضغط هنا
-لا تقع في الفخ. احذر الاحتيال.
-#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
-emiratesislamic.ae/ar/person…</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047556140511162463</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>عليك غرامة لم تُسدّد بعد – اضغط هنا
-لا تقع في الفخ. احذر الاحتيال.
-#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
-https://t.co/ltnxcRlBOA</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>عليك غرامة لم تُسدّد بعد – اضغط هنا
-لا تقع في الفخ. احذر الاحتيال.
-#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
-https://t.co/ltnxcRlBOA</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>You have an unpaid fine - click here
-Don't fall into the trap. Beware of fraud.
-#United_Against_Fraud with Emirates Islamic.</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="AD39" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="AE39" s="2" t="n">
-        <v>46136.41666666666</v>
-      </c>
-      <c r="AF39" s="2" t="n">
-        <v>46136</v>
-      </c>
-      <c r="AG39" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>You have an unpaid fine - click here Don't fall into the trap. • #United_Against_Fraud with Emirates Islamic.</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK39" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL39" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>38</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2047671039249846621</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>https://x.com/i_rh9590/status/2047671039249846621</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>https://x.com/i_rh9590</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>i_rh9590</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>رغد الحربي</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1739034755394334722/UaY05npO_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>عندي مشكلة في البطاقة و احاول اسحب منها يطلع ( خطأ في النظام ) مع العلم يوجد بها رصيد ، و خدمة العملاء عندكم للاسف مافي اي تعاون .</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>عندي مشكلة في البطاقة و احاول اسحب منها يطلع ( خطأ في النظام ) مع العلم يوجد بها رصيد ، و خدمة العملاء عندكم للاسف مافي اي تعاون .</t>
-        </is>
-      </c>
-      <c r="K40" t="b">
-        <v>0</v>
-      </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_KSA']</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>12h</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 1:36 PM UTC</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="n">
-        <v>46136.56666666667</v>
-      </c>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="n">
-        <v>1</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>8</v>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>عندي مشكلة في البطاقة و احاول اسحب منها يطلع ( خطأ في النظام ) مع العلم يوجد بها رصيد ، و خدمة العملاء عندكم للاسف مافي اي تعاون .</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>عندي مشكلة في البطاقة و احاول اسحب منها يطلع ( خطأ في النظام ) مع العلم يوجد بها رصيد ، و خدمة العملاء عندكم للاسف مافي اي تعاون .</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>I have a problem with my card and when I try to withdraw from it, it says (system error) even though there is a balance. Unfortunately, your customer service is not cooperative at all.</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD40" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="AE40" s="2" t="n">
-        <v>46136.73333333333</v>
-      </c>
-      <c r="AF40" s="2" t="n">
-        <v>46136</v>
-      </c>
-      <c r="AG40" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>I have a problem with my card and when I try to withdraw from it, it says (system error) even though there is a balance. • Unfortunately, your customer service is not cooperative at all.</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK40" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL40" t="inlineStr">
-        <is>
-          <t>EmiratesNBD_KSA</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>39</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2047629586435817682</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>https://x.com/ren_fernz/status/2047629586435817682</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>https://x.com/ren_fernz</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>ren_fernz</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Ren</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1840857882364940288/r858YoNc_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>As I was late to university I thought just downloading and then going through so I just opened and saw that I have been charged on JAN and Feb and so I contacted ENBD CS again and asked them to revert the previous charges and they told me they can only remove for April which</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>As I was late to university I thought just downloading and then going through so I just opened and saw that I have been charged on JAN and Feb and so I contacted ENBD CS again and asked them to revert the previous charges and they told me they can only remove for April which</t>
-        </is>
-      </c>
-      <c r="K41" t="b">
-        <v>0</v>
-      </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 10:51 AM UTC</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="n">
-        <v>46136.45208333333</v>
-      </c>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="n">
-        <v>1</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" t="n">
-        <v>11</v>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>As I was late to university I thought just downloading and then going through so I just opened and saw that I have been charged on JAN and Feb and so I contacted ENBD CS again and asked them to revert the previous charges and they told me they can only remove for April which</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr"/>
-      <c r="Z41" t="inlineStr"/>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>As I was late to university I thought just downloading and then going through so I just opened and saw that I have been charged on JAN and Feb and so I contacted ENBD CS again and asked them to revert the previous charges and they told me they can only remove for April which</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>As I was late to university, I thought I would just download and go through it, so I opened it and saw that I had been charged in January and February. I contacted ENBD customer service again and asked them to reverse the previous charges, and they told me they could only remove the charges for April.</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD41" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="AE41" s="2" t="n">
-        <v>46136.61875</v>
-      </c>
-      <c r="AF41" s="2" t="n">
-        <v>46136</v>
-      </c>
-      <c r="AG41" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>I contacted ENBD customer service again and asked them to reverse the previous charges, and they told me they could only remove the charges for April. • As I was late to university, I thought I would just download and go through it, so I opened it and saw that I had been charged in January and February.</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK41" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL41" t="inlineStr">
         <is>
           <t>None</t>
         </is>

--- a/check2.xlsx
+++ b/check2.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL27"/>
+  <dimension ref="A1:AL34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -656,80 +656,118 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
+          <t>The best companies don't look like winners every quarter.
+They spend on brands, enter new markets, accept lower margins — knowing it'll pay off in 5–10 years.
+Markets hate this. Stock drops. Analysts complain.
+But Thomas Russo calls this the real edge: the "capacity to suffer."
+→ A company willing to sacrifice today's profit for tomorrow's moat is rare
+→ Rarer still: one that does this when the economy is tough, not just when times are easy
+Most investors screen for fast profit growth.
+The actual filter should be: is this company investing through pain — or cutting corners to protect one quarter's numbers?
+The best compounders look uncomfortable in the short term. That's the point.
+#LongTermInvesting #CompoundingWorks</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23RBLBANK"&gt;$RBLBANK&lt;/a&gt; under Emirates NBD ownership — what&amp;#39;s your read?
+○ Bullish — new capital + cleanup = re-rating ahead
+○ Cautious — too much uncertainty, wait for FY27 clarity</t>
+        </is>
+      </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>26m</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 2:30 AM UTC</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>46139.10416666666</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23RBLBANK']</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" t="n">
+        <v>11</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
           <t>$RBLBANK under Emirates NBD ownership — what's your read?
 ○ Bullish — new capital + cleanup = re-rating ahead
 ○ Cautious — too much uncertainty, wait for FY27 clarity</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23RBLBANK"&gt;$RBLBANK&lt;/a&gt; under Emirates NBD ownership — what&amp;#39;s your read?
-○ Bullish — new capital + cleanup = re-rating ahead
-○ Cautious — too much uncertainty, wait for FY27 clarity</t>
-        </is>
-      </c>
-      <c r="K2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>26m</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Apr 27, 2026 · 2:30 AM UTC</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="n">
-        <v>46139.10416666666</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23RBLBANK']</t>
-        </is>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V2" t="n">
-        <v>11</v>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>$RBLBANK under Emirates NBD ownership — what's your read?
-○ Bullish — new capital + cleanup = re-rating ahead
-○ Cautious — too much uncertainty, wait for FY27 clarity</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>https://x.com/EdgeOverHype/status/2048590455336841432</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>The best companies don't look like winners every quarter.
+They spend on brands, enter new markets, accept lower margins — knowing it'll pay off in 5–10 years.
+Markets hate this. Stock drops. Analysts complain.
+But Thomas Russo calls this the real edge: the "capacity to suffer."
+→ A company willing to sacrifice today's profit for tomorrow's moat is rare
+→ Rarer still: one that does this when the economy is tough, not just when times are easy
+Most investors screen for fast profit growth.
+The actual filter should be: is this company investing through pain — or cutting corners to protect one quarter's numbers?
+The best compounders look uncomfortable in the short term. That's the point.
+#LongTermInvesting #CompoundingWorks</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>$RBLBANK under Emirates NBD ownership — what's your read?
-○ Bullish — new capital + cleanup = re-rating ahead
-○ Cautious — too much uncertainty, wait for FY27 clarity</t>
+          <t>The best companies don't look like winners every quarter.
+They spend on brands, enter new markets, accept lower margins — knowing it'll pay off in 5–10 years.
+Markets hate this. Stock drops. Analysts complain.
+But Thomas Russo calls this the real edge: the "capacity to suffer."
+→ A company willing to sacrifice today's profit for tomorrow's moat is rare
+→ Rarer still: one that does this when the economy is tough, not just when times are easy
+Most investors screen for fast profit growth.
+The actual filter should be: is this company investing through pain — or cutting corners to protect one quarter's numbers?
+The best compounders look uncomfortable in the short term. That's the point.
+#LongTermInvesting #CompoundingWorks</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>RBLBANK under Emirates NBD ownership — what's your opinion?
-○ Bullish — new capital + cleanup = re-rating ahead
-○ Cautious — too much uncertainty, wait for FY27 clarity</t>
+          <t>The best companies don't look like winners every quarter.
+They spend on brands, enter new markets, accept lower margins — knowing it'll pay off in 5–10 years.
+Markets hate this. Stock drops. Analysts complain.
+But Thomas Russo calls this the real edge: the "capacity to suffer."
+→ A company willing to sacrifice today's profit for tomorrow's moat is rare
+→ Rarer still: one that does this when the economy is tough, not just when times are easy
+Most investors screen for fast profit growth.
+The actual filter should be: is this company investing through pain — or cutting corners to protect one quarter's numbers?
+The best compounders look uncomfortable in the short term. That's the point.
+#LongTermInvesting #CompoundingWorks</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -760,7 +798,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>○ Bullish — new capital + cleanup = re-rating ahead ○ Cautious — too much uncertainty, wait for FY27 clarity • RBLBANK under Emirates NBD ownership — what's your opinion?</t>
+          <t>They spend on brands, enter new markets, accept lower margins — knowing it'll pay off in 5–10 years. • The actual filter should be: is this company investing through pain — or cutting corners to protect one quarter's numbers? • The best companies don't look like winners every quarter.</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -1145,8 +1183,10 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6/6 
-RBLBANK Strategy: Emirates NBD infusion has RBI/CCI nods, pending GOI/SEBI. Also, RBLBANK is targeting a $135B monthly cross-border remittance flow, leveraging tech pipelines for a 23-25% partner bank share.</t>
+          <t>1/6 🧵 
+RBLBANK Q4 FY26 Concall: Moving past headline advances growth. Here are asset quality triggers, transient deposit impacts, and margin trajectories. 
+A concall summary PDF of RBLBANK attached for sharing. 👇
+https://t.co/PUnR70G7tT</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1198,17 +1238,31 @@
 RBLBANK Strategy: Emirates NBD infusion has RBI/CCI nods, pending GOI/SEBI. Also, RBLBANK is targeting a $135B monthly cross-border remittance flow, leveraging tech pipelines for a 23-25% partner bank share.</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>https://x.com/compoundingaiin/status/2048363390700306583</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>1/6 🧵 
+RBLBANK Q4 FY26 Concall: Moving past headline advances growth. Here are asset quality triggers, transient deposit impacts, and margin trajectories. 
+A concall summary PDF of RBLBANK attached for sharing. 👇
+https://t.co/PUnR70G7tT</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>6/6 
-RBLBANK Strategy: Emirates NBD infusion has RBI/CCI nods, pending GOI/SEBI. Also, RBLBANK is targeting a $135B monthly cross-border remittance flow, leveraging tech pipelines for a 23-25% partner bank share.</t>
+          <t>1/6 🧵 
+RBLBANK Q4 FY26 Concall: Moving past headline advances growth. Here are asset quality triggers, transient deposit impacts, and margin trajectories. 
+A concall summary PDF of RBLBANK attached for sharing. 👇
+https://t.co/PUnR70G7tT</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>RBLBANK Strategy: The infusion from Emirates NBD has received approvals from RBI/CCI, pending GOI/SEBI. Additionally, RBLBANK is aiming for a $135 billion monthly cross-border remittance flow, utilizing technology pipelines for a 23-25% share among partner banks.</t>
+          <t>RBLBANK Q4 FY26 Conference Call: Moving beyond headline advances growth. Here are the asset quality triggers, temporary deposit impacts, and margin trajectories. 
+A summary PDF of the RBLBANK conference call is attached for sharing.</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1239,7 +1293,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Additionally, RBLBANK is aiming for a $135 billion monthly cross-border remittance flow, utilizing technology pipelines for a 23-25% share among partner banks. • RBLBANK Strategy: The infusion from Emirates NBD has received approvals from RBI/CCI, pending GOI/SEBI.</t>
+          <t>RBLBANK Q4 FY26 Conference Call: Moving beyond headline advances growth. • A summary PDF of the RBLBANK conference call is attached for sharing. • Here are the asset quality triggers, temporary deposit impacts, and margin trajectories.</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1449,8 +1503,8 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Get an AED 500 Pet Corner Gift Card when you apply for an Emirates NBD SHARE Visa Credit Card.
-Apply Now: apply.emiratesnbd.com/en/cre…</t>
+          <t>Get an AED 500 Pet Corner Gift Card when you apply for an Emirates NBD noon One Visa Credit Card.
+Apply Now: https://t.co/vPejTs11gM https://t.co/RjpetrwLd9</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1506,18 +1560,26 @@
 Apply Now: apply.emiratesnbd.com/en/cre…</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>https://x.com/ENBDdeals/status/2048329007666528266</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Get an AED 500 Pet Corner Gift Card when you apply for an Emirates NBD noon One Visa Credit Card.
+Apply Now: https://t.co/vPejTs11gM https://t.co/RjpetrwLd9</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Get an AED 500 Pet Corner Gift Card when you apply for an Emirates NBD SHARE Visa Credit Card.
-Apply Now: apply.emiratesnbd.com/en/cre…</t>
+          <t>Get an AED 500 Pet Corner Gift Card when you apply for an Emirates NBD noon One Visa Credit Card.
+Apply Now: https://t.co/vPejTs11gM https://t.co/RjpetrwLd9</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Get a AED 500 Pet Corner Gift Card when you apply for an Emirates NBD SHARE Visa Credit Card. 
-Apply Now: apply.emiratesnbd.com/en/cre…</t>
+          <t>Get an AED 500 Pet Corner Gift Card when you apply for an Emirates NBD noon One Visa Credit Card.</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1548,7 +1610,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Get a AED 500 Pet Corner Gift Card when you apply for an Emirates NBD SHARE Visa Credit Card. • Apply Now: apply.emiratesnbd.com/en/cre…</t>
+          <t>Get an AED 500 Pet Corner Gift Card when you apply for an Emirates NBD noon One Visa Credit Card.</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1785,7 +1847,7 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Big news from RBL Bank - Emirates NBD is investing and will own up to 74% of the bank by Q1 FY27. This means RBL Bank will become a foreign bank in India.</t>
+          <t>Big news from RBL Bank - Emirates NBD is investing up to $3 billion to acquire a 60% stake, the largest foreign investment in India's financial sector</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1835,24 +1897,16 @@
           <t>Big news from RBL Bank - Emirates NBD is investing up to $3 billion to acquire a 60% stake, the largest foreign investment in India's financial sector</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>https://x.com/FiDecoded/status/2048298339524124826</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Big news from RBL Bank - Emirates NBD is investing and will own up to 74% of the bank by Q1 FY27. This means RBL Bank will become a foreign bank in India.</t>
-        </is>
-      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Big news from RBL Bank - Emirates NBD is investing and will own up to 74% of the bank by Q1 FY27. This means RBL Bank will become a foreign bank in India.</t>
+          <t>Big news from RBL Bank - Emirates NBD is investing up to $3 billion to acquire a 60% stake, the largest foreign investment in India's financial sector</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Big news from RBL Bank - Emirates NBD is investing and will own up to 74% of the bank by Q1 FY27. This means RBL Bank will become a foreign bank in India.</t>
+          <t>Big news from RBL Bank - Emirates NBD is investing up to $3 billion to acquire a 60% stake, the largest foreign investment in India's financial sector.</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1883,7 +1937,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Big news from RBL Bank - Emirates NBD is investing and will own up to 74% of the bank by Q1 FY27. • This means RBL Bank will become a foreign bank in India.</t>
+          <t>Big news from RBL Bank - Emirates NBD is investing up to $3 billion to acquire a 60% stake, the largest foreign investment in India's financial sector.</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -2144,9 +2198,12 @@
 #الأعمال #التمويل #تاسي #البنوك #السعودية #تداول</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>https://x.com/Fyan2016/status/2048291487721345391</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
         <is>
           <t>💰 مجموعة الأعمال المتعددة توقع اتفاقية تسهيلات ائتمانية مع بنك الإمارات دبي الوطني (Emirates NBD) بقيمة 15 مليون ريال
 تم استكمال التوقيعات للاتفاقية، التي تعد متوافقة مع أحكام الشريعة الإسلامية، ومنحها مدة 12 شهراً، وتم تقديم سند لأمر يمثل ضماناً بقيمة التمويل.
@@ -2154,11 +2211,19 @@
 #الأعمال #التمويل #تاسي #البنوك #السعودية #تداول</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>💰 مجموعة الأعمال المتعددة توقع اتفاقية تسهيلات ائتمانية مع بنك الإمارات دبي الوطني (Emirates NBD) بقيمة 15 مليون ريال
+تم استكمال التوقيعات للاتفاقية، التي تعد متوافقة مع أحكام الشريعة الإسلامية، ومنحها مدة 12 شهراً، وتم تقديم سند لأمر يمثل ضماناً بقيمة التمويل.
+الهدف من التسهيل هو دعم أعمال الشركة العامة، وتغطية إصدار خطابات الضمان (الابتدائية والنهائية) وتأمين دفعات المشاريع المختلفة.
+#الأعمال #التمويل #تاسي #البنوك #السعودية #تداول</t>
+        </is>
+      </c>
       <c r="AB11" t="inlineStr">
         <is>
           <t>The multi-business group has signed a credit facility agreement with Emirates NBD worth 15 million riyals.
 The signatures for the agreement, which is compliant with Islamic law, have been completed, and it has a duration of 12 months. A promissory note representing a guarantee for the financing has been provided.
-The purpose of the facility is to support the company's general operations, cover the issuance of guarantees (both preliminary and final), and secure payments for various projects.</t>
+The purpose of the facility is to support the general operations of the company, cover the issuance of guarantees (both preliminary and final), and secure payments for various projects.</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2189,7 +2254,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>The multi-business group has signed a credit facility agreement with Emirates NBD worth 15 million riyals. • The signatures for the agreement, which is compliant with Islamic law, have been completed, and it has a duration of 12 months. • The purpose of the facility is to support the company's general operations, cover the issuance of guarantees (both preliminary and final), and secure payments for various projects.</t>
+          <t>The multi-business group has signed a credit facility agreement with Emirates NBD worth 15 million riyals. • The signatures for the agreement, which is compliant with Islamic law, have been completed, and it has a duration of 12 months. • The purpose of the facility is to support the general operations of the company, cover the issuance of guarantees (both preliminary and final), and secure payments for various projects.</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -2299,8 +2364,18 @@
 RBL Bank's card will be accepted as part of the National Common Mobility Card initiative for Bengaluru's metro and buses.</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>https://x.com/Normal_2610/status/2048287911771308484</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>RBL Bank - Expects the Emirates NBD investment to close in Q1 FY27, pending government approvals. The deal is firm and not affected by geopolitical tensions. 
+RBI approval received, working on Government of India and SEBI clearances. 
+RBL Bank's card will be accepted as part of the National Common Mobility Card initiative for Bengaluru's metro and buses.</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>RBL Bank - Expects the Emirates NBD investment to close in Q1 FY27, pending government approvals. The deal is firm and not affected by geopolitical tensions. 
@@ -2366,54 +2441,52 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2048286728524284019</t>
+          <t>2048284259559874976</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://x.com/X3_3y3/status/2048286728524284019</t>
+          <t>https://x.com/ArgaamPlus/status/2048284259559874976</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://x.com/X3_3y3</t>
+          <t>https://x.com/ArgaamPlus</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>X3_3y3</t>
+          <t>ArgaamPlus</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>:(</t>
+          <t>Argaam Plus</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1724458468550053888/zEyLH6k2_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1330817158545354753/l1A8p5ic_bigger.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>السلام عليكم ممكن تتواصلون معي خاص ؟</t>
+          <t>Multi Business Group signed a SAR 15 million Shariah-compliant credit facilities agreement with Emirates NBD.
+Show more: https://t.co/FldwIQXk1i https://t.co/prZbq1JMi8</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>السلام عليكم ممكن تتواصلون معي خاص ؟</t>
+          <t>Multi Business Group signed a SAR 15 million Shariah-compliant credit facilities agreement with Emirates NBD.
+Show more: &lt;a href="https://www.argaam.com/en/article/articledetail/id/1899425?utm_source=ArgaamSM&amp;amp;utm_medium=twitter"&gt;argaam.com/en/article/articl…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K13" t="b">
         <v>0</v>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>['AmritMohanty1', 'EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>20h</t>
@@ -2421,14 +2494,18 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Apr 26, 2026 · 6:23 AM UTC</t>
+          <t>Apr 26, 2026 · 6:13 AM UTC</t>
         </is>
       </c>
       <c r="P13" s="2" t="n">
-        <v>46138.26597222222</v>
+        <v>46138.25902777778</v>
       </c>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>['https://www.argaam.com/en/article/articledetail/id/1899425?utm_source=ArgaamSM&amp;utm_medium=twitter']</t>
+        </is>
+      </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
@@ -2439,7 +2516,7 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>4</v>
+        <v>188</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -2448,19 +2525,30 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>السلام عليكم ممكن تتواصلون معي خاص ؟</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
+          <t>Multi Business Group signed a SAR 15 million Shariah-compliant credit facilities agreement with Emirates NBD.
+Show more: argaam.com/en/article/articl…</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>https://x.com/ArgaamPlus/status/2048284259559874976</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Multi Business Group signed a SAR 15 million Shariah-compliant credit facilities agreement with Emirates NBD.
+Show more: https://t.co/FldwIQXk1i https://t.co/prZbq1JMi8</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>السلام عليكم ممكن تتواصلون معي خاص ؟</t>
+          <t>Multi Business Group signed a SAR 15 million Shariah-compliant credit facilities agreement with Emirates NBD.
+Show more: https://t.co/FldwIQXk1i https://t.co/prZbq1JMi8</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Peace be upon you. Can you contact me privately?</t>
+          <t>Multi Business Group signed a SAR 15 million Shariah-compliant credit facilities agreement with Emirates NBD.</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2470,11 +2558,11 @@
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE13" s="2" t="n">
-        <v>46138.43263888889</v>
+        <v>46138.42569444444</v>
       </c>
       <c r="AF13" s="2" t="n">
         <v>46138</v>
@@ -2491,7 +2579,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Can you contact me privately?</t>
+          <t>Multi Business Group signed a SAR 15 million Shariah-compliant credit facilities agreement with Emirates NBD.</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2504,7 +2592,7 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>AmritMohanty1, EmiratesNBD_AE</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2514,45 +2602,47 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2048284259559874976</t>
+          <t>2048281389733183899</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://x.com/ArgaamPlus/status/2048284259559874976</t>
+          <t>https://x.com/Fyan2016/status/2048281389733183899</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://x.com/ArgaamPlus</t>
+          <t>https://x.com/Fyan2016</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ArgaamPlus</t>
+          <t>Fyan2016</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Argaam Plus</t>
+          <t>فايز المالكي</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1330817158545354753/l1A8p5ic_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2032433376779493376/JtvzzBEP_bigger.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Multi Business Group signed a SAR 15 million Shariah-compliant credit facilities agreement with Emirates NBD.
-Show more: argaam.com/en/article/articl…</t>
+          <t>💰 أعلنت مجموعة الأعمال المتعددة عن إبرام اتفاقية تسهيلات ائتمانية (متوافقة مع الشريعة) مع بنك الإمارات دبي الوطني (Emirates NBD).
+تغطي الاتفاقية مبلغاً يبلغ 15 مليون ريال سعودي، وتمتد لمدة اثني عشر شهراً، وتهدف لتوفير تسهيلات عامة لخطابات الضمان ومستحقات الدفعات الأولية للمشاريع.
+#تاسي #أعمال #الرياض #تمويل #السعودية #اقتصاد</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Multi Business Group signed a SAR 15 million Shariah-compliant credit facilities agreement with Emirates NBD.
-Show more: &lt;a href="https://www.argaam.com/en/article/articledetail/id/1899425?utm_source=ArgaamSM&amp;amp;utm_medium=twitter"&gt;argaam.com/en/article/articl…&lt;/a&gt;</t>
+          <t>💰 أعلنت مجموعة الأعمال المتعددة عن إبرام اتفاقية تسهيلات ائتمانية (متوافقة مع الشريعة) مع بنك الإمارات دبي الوطني (Emirates NBD).
+تغطي الاتفاقية مبلغاً يبلغ 15 مليون ريال سعودي، وتمتد لمدة اثني عشر شهراً، وتهدف لتوفير تسهيلات عامة لخطابات الضمان ومستحقات الدفعات الأولية للمشاريع.
+&lt;a href="/search?f=tweets&amp;amp;q=%23تاسي"&gt;#تاسي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23أعمال"&gt;#أعمال&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الرياض"&gt;#الرياض&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23تمويل"&gt;#تمويل&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23السعودية"&gt;#السعودية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23اقتصاد"&gt;#اقتصاد&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K14" t="b">
@@ -2567,29 +2657,29 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Apr 26, 2026 · 6:13 AM UTC</t>
+          <t>Apr 26, 2026 · 6:01 AM UTC</t>
         </is>
       </c>
       <c r="P14" s="2" t="n">
-        <v>46138.25902777778</v>
+        <v>46138.25069444445</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
-          <t>['https://www.argaam.com/en/article/articledetail/id/1899425?utm_source=ArgaamSM&amp;utm_medium=twitter']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23تاسي', 'https://x.com/search?f=tweets&amp;q=%23أعمال', 'https://x.com/search?f=tweets&amp;q=%23الرياض', 'https://x.com/search?f=tweets&amp;q=%23تمويل', 'https://x.com/search?f=tweets&amp;q=%23السعودية', 'https://x.com/search?f=tweets&amp;q=%23اقتصاد']</t>
         </is>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>188</v>
+        <v>144</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -2598,21 +2688,33 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Multi Business Group signed a SAR 15 million Shariah-compliant credit facilities agreement with Emirates NBD.
-Show more: argaam.com/en/article/articl…</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
+          <t>💰 أعلنت مجموعة الأعمال المتعددة عن إبرام اتفاقية تسهيلات ائتمانية (متوافقة مع الشريعة) مع بنك الإمارات دبي الوطني (Emirates NBD).
+تغطي الاتفاقية مبلغاً يبلغ 15 مليون ريال سعودي، وتمتد لمدة اثني عشر شهراً، وتهدف لتوفير تسهيلات عامة لخطابات الضمان ومستحقات الدفعات الأولية للمشاريع.
+#تاسي #أعمال #الرياض #تمويل #السعودية #اقتصاد</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>https://x.com/Fyan2016/status/2048281389733183899</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>💰 أعلنت مجموعة الأعمال المتعددة عن إبرام اتفاقية تسهيلات ائتمانية (متوافقة مع الشريعة) مع بنك الإمارات دبي الوطني (Emirates NBD).
+تغطي الاتفاقية مبلغاً يبلغ 15 مليون ريال سعودي، وتمتد لمدة اثني عشر شهراً، وتهدف لتوفير تسهيلات عامة لخطابات الضمان ومستحقات الدفعات الأولية للمشاريع.
+#تاسي #أعمال #الرياض #تمويل #السعودية #اقتصاد</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Multi Business Group signed a SAR 15 million Shariah-compliant credit facilities agreement with Emirates NBD.
-Show more: argaam.com/en/article/articl…</t>
+          <t>💰 أعلنت مجموعة الأعمال المتعددة عن إبرام اتفاقية تسهيلات ائتمانية (متوافقة مع الشريعة) مع بنك الإمارات دبي الوطني (Emirates NBD).
+تغطي الاتفاقية مبلغاً يبلغ 15 مليون ريال سعودي، وتمتد لمدة اثني عشر شهراً، وتهدف لتوفير تسهيلات عامة لخطابات الضمان ومستحقات الدفعات الأولية للمشاريع.
+#تاسي #أعمال #الرياض #تمويل #السعودية #اقتصاد</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Multi Business Group signed a SAR 15 million Shariah-compliant credit facilities agreement with Emirates NBD.</t>
+          <t>The multi-business group announced the signing of a Sharia-compliant credit facility agreement with Emirates NBD. The agreement covers an amount of 15 million Saudi Riyals and extends for a period of twelve months, aiming to provide general facilities for guarantees and initial payment receivables for projects.</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2622,11 +2724,11 @@
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE14" s="2" t="n">
-        <v>46138.42569444444</v>
+        <v>46138.41736111111</v>
       </c>
       <c r="AF14" s="2" t="n">
         <v>46138</v>
@@ -2643,7 +2745,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Multi Business Group signed a SAR 15 million Shariah-compliant credit facilities agreement with Emirates NBD.</t>
+          <t>The agreement covers an amount of 15 million Saudi Riyals and extends for a period of twelve months, aiming to provide general facilities for guarantees and initial payment receivables for projects. • The multi-business group announced the signing of a Sharia-compliant credit facility agreement with Emirates NBD.</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2666,47 +2768,50 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2048281389733183899</t>
+          <t>2048266647291748727</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://x.com/Fyan2016/status/2048281389733183899</t>
+          <t>https://x.com/arjunjain_96/status/2048266647291748727</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://x.com/Fyan2016</t>
+          <t>https://x.com/arjunjain_96</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fyan2016</t>
+          <t>arjunjain_96</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>فايز المالكي</t>
+          <t>Arjun Jain</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2032433376779493376/JtvzzBEP_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1922114227054997504/uwVDJ9GD_bigger.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>💰 أعلنت مجموعة الأعمال المتعددة عن إبرام اتفاقية تسهيلات ائتمانية (متوافقة مع الشريعة) مع بنك الإمارات دبي الوطني (Emirates NBD).
-تغطي الاتفاقية مبلغاً يبلغ 15 مليون ريال سعودي، وتمتد لمدة اثني عشر شهراً، وتهدف لتوفير تسهيلات عامة لخطابات الضمان ومستحقات الدفعات الأولية للمشاريع.
-#تاسي #أعمال #الرياض #تمويل #السعودية #اقتصاد</t>
+          <t>RBL Bank Q4 FY26 results are out.
+Net profit: ₹230 crore — up 234% YoY, 7% QoQ. 
+NII: ₹1,671 crore — up 7% YoY. Operating profit: ₹955 crore — up 11% YoY.
+Good headline numbers. But as always, the ratios tell the fuller story. https://t.co/A0sxjq4y5B</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>💰 أعلنت مجموعة الأعمال المتعددة عن إبرام اتفاقية تسهيلات ائتمانية (متوافقة مع الشريعة) مع بنك الإمارات دبي الوطني (Emirates NBD).
-تغطي الاتفاقية مبلغاً يبلغ 15 مليون ريال سعودي، وتمتد لمدة اثني عشر شهراً، وتهدف لتوفير تسهيلات عامة لخطابات الضمان ومستحقات الدفعات الأولية للمشاريع.
-&lt;a href="/search?f=tweets&amp;amp;q=%23تاسي"&gt;#تاسي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23أعمال"&gt;#أعمال&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الرياض"&gt;#الرياض&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23تمويل"&gt;#تمويل&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23السعودية"&gt;#السعودية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23اقتصاد"&gt;#اقتصاد&lt;/a&gt;</t>
+          <t>Profitability
+NIM at 4.41% - this is the one number to watch.
+It was 4.89% a year ago and 4.63% last quarter. That&amp;#39;s 48 bps of compression YoY.
+Management has guided that Q1 FY27 margins will remain similar to Q4. The expectation is that the Emirates NBD capital infusion will then drive expansion.
+Cost-to-income improving - 65.1% vs 66.3% last quarter. Still high, but moving in the right direction.</t>
         </is>
       </c>
       <c r="K15" t="b">
@@ -2716,34 +2821,30 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Apr 26, 2026 · 6:01 AM UTC</t>
+          <t>Apr 26, 2026 · 5:03 AM UTC</t>
         </is>
       </c>
       <c r="P15" s="2" t="n">
-        <v>46138.25069444445</v>
+        <v>46138.21041666667</v>
       </c>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23تاسي', 'https://x.com/search?f=tweets&amp;q=%23أعمال', 'https://x.com/search?f=tweets&amp;q=%23الرياض', 'https://x.com/search?f=tweets&amp;q=%23تمويل', 'https://x.com/search?f=tweets&amp;q=%23السعودية', 'https://x.com/search?f=tweets&amp;q=%23اقتصاد']</t>
-        </is>
-      </c>
+      <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
         <v>1</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
       <c r="V15" t="n">
-        <v>144</v>
+        <v>17</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -2751,117 +2852,6 @@
         </is>
       </c>
       <c r="X15" t="inlineStr">
-        <is>
-          <t>💰 أعلنت مجموعة الأعمال المتعددة عن إبرام اتفاقية تسهيلات ائتمانية (متوافقة مع الشريعة) مع بنك الإمارات دبي الوطني (Emirates NBD).
-تغطي الاتفاقية مبلغاً يبلغ 15 مليون ريال سعودي، وتمتد لمدة اثني عشر شهراً، وتهدف لتوفير تسهيلات عامة لخطابات الضمان ومستحقات الدفعات الأولية للمشاريع.
-#تاسي #أعمال #الرياض #تمويل #السعودية #اقتصاد</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>https://x.com/Fyan2016/status/2048281389733183899</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>💰 أعلنت مجموعة الأعمال المتعددة عن إبرام اتفاقية تسهيلات ائتمانية (متوافقة مع الشريعة) مع بنك الإمارات دبي الوطني (Emirates NBD).
-تغطي الاتفاقية مبلغاً يبلغ 15 مليون ريال سعودي، وتمتد لمدة اثني عشر شهراً، وتهدف لتوفير تسهيلات عامة لخطابات الضمان ومستحقات الدفعات الأولية للمشاريع.
-#تاسي #أعمال #الرياض #تمويل #السعودية #اقتصاد</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>💰 أعلنت مجموعة الأعمال المتعددة عن إبرام اتفاقية تسهيلات ائتمانية (متوافقة مع الشريعة) مع بنك الإمارات دبي الوطني (Emirates NBD).
-تغطي الاتفاقية مبلغاً يبلغ 15 مليون ريال سعودي، وتمتد لمدة اثني عشر شهراً، وتهدف لتوفير تسهيلات عامة لخطابات الضمان ومستحقات الدفعات الأولية للمشاريع.
-#تاسي #أعمال #الرياض #تمويل #السعودية #اقتصاد</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>The multi-business group announced the signing of a Sharia-compliant credit facility agreement with Emirates NBD. The agreement covers an amount of 15 million Saudi Riyals and extends for a period of twelve months, aiming to provide general facilities for guarantees and initial payment receivables for projects.</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE15" s="2" t="n">
-        <v>46138.41736111111</v>
-      </c>
-      <c r="AF15" s="2" t="n">
-        <v>46138</v>
-      </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>The agreement covers an amount of 15 million Saudi Riyals and extends for a period of twelve months, aiming to provide general facilities for guarantees and initial payment receivables for projects. • The multi-business group announced the signing of a Sharia-compliant credit facility agreement with Emirates NBD.</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK15" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2048266647291748727</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>https://x.com/arjunjain_96/status/2048266647291748727</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>https://x.com/arjunjain_96</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>arjunjain_96</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Arjun Jain</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1922114227054997504/uwVDJ9GD_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
         <is>
           <t>Profitability
 NIM at 4.41% - this is the one number to watch.
@@ -2870,163 +2860,121 @@
 Cost-to-income improving - 65.1% vs 66.3% last quarter. Still high, but moving in the right direction.</t>
         </is>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>https://x.com/arjunjain_96/status/2048266647291748727</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>RBL Bank Q4 FY26 results are out.
+Net profit: ₹230 crore — up 234% YoY, 7% QoQ. 
+NII: ₹1,671 crore — up 7% YoY. Operating profit: ₹955 crore — up 11% YoY.
+Good headline numbers. But as always, the ratios tell the fuller story. https://t.co/A0sxjq4y5B</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>RBL Bank Q4 FY26 results are out.
+Net profit: ₹230 crore — up 234% YoY, 7% QoQ. 
+NII: ₹1,671 crore — up 7% YoY. Operating profit: ₹955 crore — up 11% YoY.
+Good headline numbers. But as always, the ratios tell the fuller story. https://t.co/A0sxjq4y5B</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>RBL Bank's Q4 FY26 results are out.
+Net profit: ₹230 crore — up 234% year-on-year, 7% quarter-on-quarter. 
+NII: ₹1,671 crore — up 7% year-on-year. Operating profit: ₹955 crore — up 11% year-on-year.
+Good headline numbers. But as always, the ratios tell the fuller story.</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE15" s="2" t="n">
+        <v>46138.37708333333</v>
+      </c>
+      <c r="AF15" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Net profit: ₹230 crore — up 234% year-on-year, 7% quarter-on-quarter. • Operating profit: ₹955 crore — up 11% year-on-year. • NII: ₹1,671 crore — up 7% year-on-year.</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK15" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2048234825199526119</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://x.com/theprabhakars/status/2048234825199526119</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://x.com/theprabhakars</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>theprabhakars</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Prabhakar Singh Bais</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1985403950192033792/czvUF0FN_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>India and New Zealand are set to sign a Free Trade Agreement (FTA) on 27 April, with the aim to more than double bilateral trade to $5 billion in five years.</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
-        <is>
-          <t>Profitability
-NIM at 4.41% - this is the one number to watch.
-It was 4.89% a year ago and 4.63% last quarter. That&amp;#39;s 48 bps of compression YoY.
-Management has guided that Q1 FY27 margins will remain similar to Q4. The expectation is that the Emirates NBD capital infusion will then drive expansion.
-Cost-to-income improving - 65.1% vs 66.3% last quarter. Still high, but moving in the right direction.</t>
-        </is>
-      </c>
-      <c r="K16" t="b">
-        <v>0</v>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Apr 26, 2026 · 5:03 AM UTC</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="n">
-        <v>46138.21041666667</v>
-      </c>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1</v>
-      </c>
-      <c r="V16" t="n">
-        <v>17</v>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>Profitability
-NIM at 4.41% - this is the one number to watch.
-It was 4.89% a year ago and 4.63% last quarter. That's 48 bps of compression YoY.
-Management has guided that Q1 FY27 margins will remain similar to Q4. The expectation is that the Emirates NBD capital infusion will then drive expansion.
-Cost-to-income improving - 65.1% vs 66.3% last quarter. Still high, but moving in the right direction.</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Profitability
-NIM at 4.41% - this is the one number to watch.
-It was 4.89% a year ago and 4.63% last quarter. That's 48 bps of compression YoY.
-Management has guided that Q1 FY27 margins will remain similar to Q4. The expectation is that the Emirates NBD capital infusion will then drive expansion.
-Cost-to-income improving - 65.1% vs 66.3% last quarter. Still high, but moving in the right direction.</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Profitability NIM at 4.41% - this is the one number to watch. It was 4.89% a year ago and 4.63% last quarter. That's 48 bps of compression YoY. Management has guided that Q1 FY27 margins will remain similar to Q4. The expectation is that the Emirates NBD capital infusion will then drive expansion. Cost-to-income improving - 65.1% vs 66.3% last quarter. Still high, but moving in the right direction.</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE16" s="2" t="n">
-        <v>46138.37708333333</v>
-      </c>
-      <c r="AF16" s="2" t="n">
-        <v>46138</v>
-      </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>It was 4.89% a year ago and 4.63% last quarter. • Cost-to-income improving - 65.1% vs 66.3% last quarter. • Management has guided that Q1 FY27 margins will remain similar to Q4.</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK16" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2048234825199526119</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>https://x.com/theprabhakars/status/2048234825199526119</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>https://x.com/theprabhakars</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>theprabhakars</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Prabhakar Singh Bais</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1985403950192033792/czvUF0FN_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>India and New Zealand are set to sign a Free Trade Agreement (FTA) on 27 April, with the aim to more than double bilateral trade to $5 billion in five years.</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
         <is>
           <t>IDBI बैंक विनिवेश: क्या है ताजा अपडेट? 
 ​IDBI बैंक के निजीकरण की प्रक्रिया एक बार फिर चर्चा में है। बाजार में चल रही ताजा रिपोर्ट्स के अनुसार, इस बड़े सौदे से जुड़ी कुछ महत्वपूर्ण बातें सामने आ रही हैं:
@@ -3039,48 +2987,48 @@
 ​&lt;a href="/search?f=tweets&amp;amp;q=%23IDBIBank"&gt;#IDBIBank&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23BankingNews"&gt;#BankingNews&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EconomyUpdate"&gt;#EconomyUpdate&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Disinvestment"&gt;#Disinvestment&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23StockMarketIndia"&gt;#StockMarketIndia&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FinanceNews"&gt;#FinanceNews&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K17" t="b">
-        <v>0</v>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
         <is>
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>Apr 26, 2026 · 2:56 AM UTC</t>
         </is>
       </c>
-      <c r="P17" s="2" t="n">
+      <c r="P16" s="2" t="n">
         <v>46138.12222222222</v>
       </c>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr">
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
         <is>
           <t>['https://x.com/search?f=tweets&amp;q=%23IDBIBank', 'https://x.com/search?f=tweets&amp;q=%23BankingNews', 'https://x.com/search?f=tweets&amp;q=%23EconomyUpdate', 'https://x.com/search?f=tweets&amp;q=%23Disinvestment', 'https://x.com/search?f=tweets&amp;q=%23StockMarketIndia', 'https://x.com/search?f=tweets&amp;q=%23FinanceNews']</t>
         </is>
       </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
         <v>86</v>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>IDBI बैंक विनिवेश: क्या है ताजा अपडेट? 
 ​IDBI बैंक के निजीकरण की प्रक्रिया एक बार फिर चर्चा में है। बाजार में चल रही ताजा रिपोर्ट्स के अनुसार, इस बड़े सौदे से जुड़ी कुछ महत्वपूर्ण बातें सामने आ रही हैं:
@@ -3093,24 +3041,176 @@
 ​#IDBIBank #BankingNews #EconomyUpdate #Disinvestment #StockMarketIndia #FinanceNews</t>
         </is>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>https://x.com/theprabhakars/status/2048234825199526119</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>India and New Zealand are set to sign a Free Trade Agreement (FTA) on 27 April, with the aim to more than double bilateral trade to $5 billion in five years.</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>India and New Zealand are set to sign a Free Trade Agreement (FTA) on 27 April, with the aim to more than double bilateral trade to $5 billion in five years.</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>India and New Zealand are set to sign a Free Trade Agreement (FTA) on April 27, aiming to more than double bilateral trade to $5 billion in five years.</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE16" s="2" t="n">
+        <v>46138.28888888889</v>
+      </c>
+      <c r="AF16" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>India and New Zealand are set to sign a Free Trade Agreement (FTA) on April 27, aiming to more than double bilateral trade to $5 billion in five years.</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK16" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2048231285999759759</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://x.com/MultibaggAI/status/2048231285999759759</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://x.com/MultibaggAI</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>MultibaggAI</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>multibagg.ai</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2017665342756294656/o62zwaRv_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>RBLBANK: BOARD HAS PROPOSED DIVIDEND OF ₹1/SH, EMIRATES NBD STRATEGIC INVESTMENT SAID TO BE NEARING CLOSURE</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>RBLBANK: BOARD HAS PROPOSED DIVIDEND OF ₹1/SH, EMIRATES NBD STRATEGIC INVESTMENT SAID TO BE NEARING CLOSURE</t>
+        </is>
+      </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Apr 26, 2026 · 2:42 AM UTC</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="n">
+        <v>46138.1125</v>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>82</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>RBLBANK: BOARD HAS PROPOSED DIVIDEND OF ₹1/SH, EMIRATES NBD STRATEGIC INVESTMENT SAID TO BE NEARING CLOSURE</t>
+        </is>
+      </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>https://x.com/theprabhakars/status/2048234825199526119</t>
+          <t>https://x.com/MultibaggAI/status/2048231285999759759</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>India and New Zealand are set to sign a Free Trade Agreement (FTA) on 27 April, with the aim to more than double bilateral trade to $5 billion in five years.</t>
+          <t>RBLBANK: BOARD HAS PROPOSED DIVIDEND OF ₹1/SH, EMIRATES NBD STRATEGIC INVESTMENT SAID TO BE NEARING CLOSURE</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>India and New Zealand are set to sign a Free Trade Agreement (FTA) on 27 April, with the aim to more than double bilateral trade to $5 billion in five years.</t>
+          <t>RBLBANK: BOARD HAS PROPOSED DIVIDEND OF ₹1/SH, EMIRATES NBD STRATEGIC INVESTMENT SAID TO BE NEARING CLOSURE</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>India and New Zealand are set to sign a Free Trade Agreement (FTA) on April 27, aiming to more than double bilateral trade to $5 billion in five years.</t>
+          <t>RBLBANK: THE BOARD HAS PROPOSED A DIVIDEND OF ₹1 PER SHARE, EMIRATES NBD STRATEGIC INVESTMENT IS REPORTEDLY NEARING CLOSURE.</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -3124,7 +3224,7 @@
         </is>
       </c>
       <c r="AE17" s="2" t="n">
-        <v>46138.28888888889</v>
+        <v>46138.27916666667</v>
       </c>
       <c r="AF17" s="2" t="n">
         <v>46138</v>
@@ -3141,7 +3241,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>India and New Zealand are set to sign a Free Trade Agreement (FTA) on April 27, aiming to more than double bilateral trade to $5 billion in five years.</t>
+          <t>RBLBANK: THE BOARD HAS PROPOSED A DIVIDEND OF ₹1 PER SHARE, EMIRATES NBD STRATEGIC INVESTMENT IS REPORTEDLY NEARING CLOSURE.</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -3164,43 +3264,53 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2048231285999759759</t>
+          <t>2048386618873024952</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://x.com/MultibaggAI/status/2048231285999759759</t>
+          <t>https://x.com/emiratesislamic/status/2048386618873024952</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://x.com/MultibaggAI</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MultibaggAI</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>multibagg.ai</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2017665342756294656/o62zwaRv_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>RBLBANK: BOARD HAS PROPOSED DIVIDEND OF ₹1/SH, EMIRATES NBD STRATEGIC INVESTMENT SAID TO BE NEARING CLOSURE</t>
+          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
+سعادة بلا حدود!
+تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
+🌟 استرداد يصل إلى 6%، بلا حدود
+🎁 مكافأة ترحيبية تصل إلى 750 درهم https://t.co/n80kD0Ihou</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>RBLBANK: BOARD HAS PROPOSED DIVIDEND OF ₹1/SH, EMIRATES NBD STRATEGIC INVESTMENT SAID TO BE NEARING CLOSURE</t>
+          <t>💳 بدون رسوم سنوية
+🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية
+وغير ذلك الكثير!
+تُطبّق الشروط والأحكام.
+تقدم بطلبك الآن &lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/cards/credit-cards/amazon-redirection?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_amazon"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;
+The Amazon Emirates Islamic Mastercard Credit Card
+Meet the card that turns every purchase into Unlimited Joy 💳✨</t>
         </is>
       </c>
       <c r="K18" t="b">
@@ -3210,21 +3320,25 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Apr 26</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Apr 26, 2026 · 2:42 AM UTC</t>
+          <t>Apr 26, 2026 · 1:00 PM UTC</t>
         </is>
       </c>
       <c r="P18" s="2" t="n">
-        <v>46138.1125</v>
+        <v>46138.54166666666</v>
       </c>
       <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/personal-banking/cards/credit-cards/amazon-redirection?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_amazon']</t>
+        </is>
+      </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
@@ -3233,64 +3347,86 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>RBLBANK: BOARD HAS PROPOSED DIVIDEND OF ₹1/SH, EMIRATES NBD STRATEGIC INVESTMENT SAID TO BE NEARING CLOSURE</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
+          <t>💳 بدون رسوم سنوية
+🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية
+وغير ذلك الكثير!
+تُطبّق الشروط والأحكام.
+تقدم بطلبك الآن emiratesislamic.ae/ar/person…
+The Amazon Emirates Islamic Mastercard Credit Card
+Meet the card that turns every purchase into Unlimited Joy 💳✨</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048386618873024952</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
+سعادة بلا حدود!
+تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
+🌟 استرداد يصل إلى 6%، بلا حدود
+🎁 مكافأة ترحيبية تصل إلى 750 درهم https://t.co/n80kD0Ihou</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RBLBANK: BOARD HAS PROPOSED DIVIDEND OF ₹1/SH, EMIRATES NBD STRATEGIC INVESTMENT SAID TO BE NEARING CLOSURE</t>
+          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
+سعادة بلا حدود!
+تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
+🌟 استرداد يصل إلى 6%، بلا حدود
+🎁 مكافأة ترحيبية تصل إلى 750 درهم https://t.co/n80kD0Ihou</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>RBLBANK: THE BOARD HAS PROPOSED A DIVIDEND OF ₹1 PER SHARE, EMIRATES NBD STRATEGIC INVESTMENT IS REPORTEDLY NEARING CLOSURE.</t>
+          <t>Amazon credit card from Emirates Islamic and MasterCard Unlimited happiness! Discover the card that turns every purchase into unlimited happiness 💳✨ 🌟 Cashback up to 6%, no limits 🎁 Welcome bonus up to 750 dirhams</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Cust</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE18" s="2" t="n">
-        <v>46138.27916666667</v>
+        <v>46138.70833333334</v>
       </c>
       <c r="AF18" s="2" t="n">
         <v>46138</v>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
+          <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>RBLBANK: THE BOARD HAS PROPOSED A DIVIDEND OF ₹1 PER SHARE, EMIRATES NBD STRATEGIC INVESTMENT IS REPORTEDLY NEARING CLOSURE.</t>
+          <t>Discover the card that turns every purchase into unlimited happiness 💳✨ 🌟 Cashback up to 6%, no limits 🎁 Welcome bonus up to 750 dirhams • Amazon credit card from Emirates Islamic and MasterCard Unlimited happiness!</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank (ENBD)</t>
+          <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AK18" t="n">
@@ -3308,71 +3444,72 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2048213606257570300</t>
+          <t>2048341326358253773</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://x.com/AmritMohanty1/status/2048213606257570300</t>
+          <t>https://x.com/emiratesislamic/status/2048341326358253773</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://x.com/AmritMohanty1</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AmritMohanty1</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Amrit Mohanty</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1798792220885307395/ZFbORVL__bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Thank you. I have emailed from my registered email ID quoting Case #234234532915. Kindly review urgently and confirm no fees/interest will apply while the dispute is under investigation, as the due date is near.</t>
+          <t>كل استثمار هو بداية قصة تحتاج إلى اهتمام استثنائي. مع الخدمات المصرفية المميزة من الإمارات الإسلامي، إن استثمارك الأول اليوم هو إرث الغد لأبنائك. اكشتف التميز الذي يصنع الفارق. https://t.co/dwvwUupGPZ</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Thank you. I have emailed from my registered email ID quoting Case #234234532915. Kindly review urgently and confirm no fees/interest will apply while the dispute is under investigation, as the due date is near.</t>
+          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23PriorityBanking"&gt;#PriorityBanking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23UAEBanking"&gt;#UAEBanking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamicBank"&gt;#EmiratesIslamicBank&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/en/priority-banking?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=prb"&gt;emiratesislamic.ae/en/priori…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K19" t="b">
         <v>0</v>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Apr 26</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Apr 26, 2026 · 1:32 AM UTC</t>
+          <t>Apr 26, 2026 · 10:00 AM UTC</t>
         </is>
       </c>
       <c r="P19" s="2" t="n">
-        <v>46138.06388888889</v>
+        <v>46138.41666666666</v>
       </c>
       <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23PriorityBanking', 'https://x.com/search?f=tweets&amp;q=%23UAEBanking', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamicBank', 'https://www.emiratesislamic.ae/en/priority-banking?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=prb']</t>
+        </is>
+      </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -3381,64 +3518,73 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Thank you. I have emailed from my registered email ID quoting Case #234234532915. Kindly review urgently and confirm no fees/interest will apply while the dispute is under investigation, as the due date is near.</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
+          <t>#EmiratesIslamic #PriorityBanking #UAEBanking #EmiratesIslamicBank
+emiratesislamic.ae/en/priori…</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048341326358253773</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>كل استثمار هو بداية قصة تحتاج إلى اهتمام استثنائي. مع الخدمات المصرفية المميزة من الإمارات الإسلامي، إن استثمارك الأول اليوم هو إرث الغد لأبنائك. اكشتف التميز الذي يصنع الفارق. https://t.co/dwvwUupGPZ</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Thank you. I have emailed from my registered email ID quoting Case #234234532915. Kindly review urgently and confirm no fees/interest will apply while the dispute is under investigation, as the due date is near.</t>
+          <t>كل استثمار هو بداية قصة تحتاج إلى اهتمام استثنائي. مع الخدمات المصرفية المميزة من الإمارات الإسلامي، إن استثمارك الأول اليوم هو إرث الغد لأبنائك. اكشتف التميز الذي يصنع الفارق. https://t.co/dwvwUupGPZ</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Thank you. I have emailed from my registered email ID quoting Case #234234532915. Please review urgently and confirm that no fees or interest will apply while the dispute is under investigation, as the due date is approaching.</t>
+          <t>Every investment is the beginning of a story that requires exceptional attention. With the premium banking services from Emirates Islamic, your first investment today is the legacy of tomorrow for your children. Discover the excellence that makes a difference.</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Cust</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE19" s="2" t="n">
-        <v>46138.23055555556</v>
+        <v>46138.58333333334</v>
       </c>
       <c r="AF19" s="2" t="n">
         <v>46138</v>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
+          <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>I have emailed from my registered email ID quoting Case #234234532915. • Please review urgently and confirm that no fees or interest will apply while the dispute is under investigation, as the due date is approaching.</t>
+          <t>With the premium banking services from Emirates Islamic, your first investment today is the legacy of tomorrow for your children. • Every investment is the beginning of a story that requires exceptional attention. • Discover the excellence that makes a difference.</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank (ENBD)</t>
+          <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AK19" t="n">
@@ -3446,7 +3592,7 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3456,12 +3602,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2048386621989335442</t>
+          <t>2048341323271336150</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048386621989335442</t>
+          <t>https://x.com/emiratesislamic/status/2048341323271336150</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3486,6 +3632,328 @@
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
+        <is>
+          <t>Every financial journey deserves personal attention. From your first investment to building generational wealth, Emirates Islamic Priority Banking is by your side. Discover the difference today.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Every financial journey deserves personal attention. From your first investment to building generational wealth, Emirates Islamic Priority Banking is by your side. Discover the difference today.</t>
+        </is>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Apr 26, 2026 · 10:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="n">
+        <v>46138.41666666666</v>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>51</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Every financial journey deserves personal attention. From your first investment to building generational wealth, Emirates Islamic Priority Banking is by your side. Discover the difference today.</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>Every financial journey deserves personal attention. From your first investment to building generational wealth, Emirates Islamic Priority Banking is by your side. Discover the difference today.</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>Every financial journey deserves personal attention. From your first investment to building generational wealth, Emirates Islamic Priority Banking is by your side. Discover the difference today.</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AE20" s="2" t="n">
+        <v>46138.58333333334</v>
+      </c>
+      <c r="AF20" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>2. Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>From your first investment to building generational wealth, Emirates Islamic Priority Banking is by your side. • Every financial journey deserves personal attention. • Discover the difference today.</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AK20" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2048280917039276118</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048280917039276118</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>You don’t need to fix everything at once.
+Focus on one big expense.
+Consistency creates real progress.
+#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
+https://t.co/XvyZgR87nM</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>You don’t need to fix everything at once.
+Focus on one big expense.
+Consistency creates real progress.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Apr 26, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="n">
+        <v>46138.25</v>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+        </is>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>48</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>You don’t need to fix everything at once.
+Focus on one big expense.
+Consistency creates real progress.
+#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
+emiratesislamic.ae/en/key-in…</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048280917039276118</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>You don’t need to fix everything at once.
+Focus on one big expense.
+Consistency creates real progress.
+#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
+https://t.co/XvyZgR87nM</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>You don’t need to fix everything at once.
+Focus on one big expense.
+Consistency creates real progress.
+#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
+https://t.co/XvyZgR87nM</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>You don’t need to fix everything at once.
+Focus on one big expense.
+Consistency creates real progress.</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE21" s="2" t="n">
+        <v>46138.41666666666</v>
+      </c>
+      <c r="AF21" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>2. Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>You don’t need to fix everything at once. • Focus on one big expense. • Consistency creates real progress.</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AK21" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2048386621989335442</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048386621989335442</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
         <is>
           <t>✨ Up to 6% back, unlimited
 🎁 Up to AED 750 welcome bonus
@@ -3497,7 +3965,7 @@
 emiratesislamic.ae/en/person…</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>✨ Up to 6% back, unlimited
 🎁 Up to AED 750 welcome bonus
@@ -3509,48 +3977,48 @@
 &lt;a href="https://www.emiratesislamic.ae/en/personal-banking/cards/credit-cards/amazon-redirection?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_amazon"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>13h</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>14h</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
         <is>
           <t>Apr 26, 2026 · 1:00 PM UTC</t>
         </is>
       </c>
-      <c r="P20" s="2" t="n">
+      <c r="P22" s="2" t="n">
         <v>46138.54166666666</v>
       </c>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr">
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
         <is>
           <t>['https://www.emiratesislamic.ae/en/personal-banking/cards/credit-cards/amazon-redirection?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_amazon']</t>
         </is>
       </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
         <v>2</v>
       </c>
-      <c r="V20" t="n">
+      <c r="V22" t="n">
         <v>56</v>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>✨ Up to 6% back, unlimited
 🎁 Up to AED 750 welcome bonus
@@ -3562,9 +4030,9 @@
 emiratesislamic.ae/en/person…</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr">
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
         <is>
           <t>✨ Up to 6% back, unlimited
 🎁 Up to AED 750 welcome bonus
@@ -3576,7 +4044,7 @@
 emiratesislamic.ae/en/person…</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>Up to 6% back, unlimited  
 Up to AED 750 welcome bonus  
@@ -3587,348 +4055,18 @@
 Apply now</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
+      <c r="AC22" t="inlineStr">
         <is>
           <t>Bank</t>
         </is>
       </c>
-      <c r="AD20" t="inlineStr">
+      <c r="AD22" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="AE20" s="2" t="n">
+      <c r="AE22" s="2" t="n">
         <v>46138.70833333334</v>
-      </c>
-      <c r="AF20" s="2" t="n">
-        <v>46138</v>
-      </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Up to 6% back, unlimited Up to AED 750 welcome bonus No annual fee Exclusive travel &amp; lifestyle benefits And much more. • Terms &amp; conditions apply.</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK20" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2048386618873024952</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2048386618873024952</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>💳 بدون رسوم سنوية
-🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية
-وغير ذلك الكثير!
-تُطبّق الشروط والأحكام.
-تقدم بطلبك الآن emiratesislamic.ae/ar/person…
-The Amazon Emirates Islamic Mastercard Credit Card
-Meet the card that turns every purchase into Unlimited Joy 💳✨</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>💳 بدون رسوم سنوية
-🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية
-وغير ذلك الكثير!
-تُطبّق الشروط والأحكام.
-تقدم بطلبك الآن &lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/cards/credit-cards/amazon-redirection?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_amazon"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;
-The Amazon Emirates Islamic Mastercard Credit Card
-Meet the card that turns every purchase into Unlimited Joy 💳✨</t>
-        </is>
-      </c>
-      <c r="K21" t="b">
-        <v>0</v>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>13h</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Apr 26, 2026 · 1:00 PM UTC</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="n">
-        <v>46138.54166666666</v>
-      </c>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/personal-banking/cards/credit-cards/amazon-redirection?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_amazon']</t>
-        </is>
-      </c>
-      <c r="S21" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>53</v>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>💳 بدون رسوم سنوية
-🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية
-وغير ذلك الكثير!
-تُطبّق الشروط والأحكام.
-تقدم بطلبك الآن emiratesislamic.ae/ar/person…
-The Amazon Emirates Islamic Mastercard Credit Card
-Meet the card that turns every purchase into Unlimited Joy 💳✨</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>💳 بدون رسوم سنوية
-🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية
-وغير ذلك الكثير!
-تُطبّق الشروط والأحكام.
-تقدم بطلبك الآن emiratesislamic.ae/ar/person…
-The Amazon Emirates Islamic Mastercard Credit Card
-Meet the card that turns every purchase into Unlimited Joy 💳✨</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>No annual fees  
-Special travel and exclusive lifestyle features and discounts  
-And much more!  
-Terms and conditions apply.  
-Apply now at emiratesislamic.ae/ar/person…  
-The Amazon Emirates Islamic Mastercard Credit Card  
-Meet the card that turns every purchase into Unlimited Joy 💳✨</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="AE21" s="2" t="n">
-        <v>46138.70833333334</v>
-      </c>
-      <c r="AF21" s="2" t="n">
-        <v>46138</v>
-      </c>
-      <c r="AG21" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Apply now at emiratesislamic.ae/ar/person… The Amazon Emirates Islamic Mastercard Credit Card Meet the card that turns every purchase into Unlimited Joy 💳✨ • No annual fees Special travel and exclusive lifestyle features and discounts And much more! • Terms and conditions apply.</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK21" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2048341326358253773</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2048341326358253773</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>#EmiratesIslamic #PriorityBanking #UAEBanking #EmiratesIslamicBank
-emiratesislamic.ae/en/priori…</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23PriorityBanking"&gt;#PriorityBanking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23UAEBanking"&gt;#UAEBanking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamicBank"&gt;#EmiratesIslamicBank&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/en/priority-banking?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=prb"&gt;emiratesislamic.ae/en/priori…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K22" t="b">
-        <v>0</v>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>16h</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Apr 26, 2026 · 10:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="n">
-        <v>46138.41666666666</v>
-      </c>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23PriorityBanking', 'https://x.com/search?f=tweets&amp;q=%23UAEBanking', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamicBank', 'https://www.emiratesislamic.ae/en/priority-banking?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=prb']</t>
-        </is>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>35</v>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>#EmiratesIslamic #PriorityBanking #UAEBanking #EmiratesIslamicBank
-emiratesislamic.ae/en/priori…</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>#EmiratesIslamic #PriorityBanking #UAEBanking #EmiratesIslamicBank
-emiratesislamic.ae/en/priori…</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Priority Banking UAE Banking Emirates Islamic Bank</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE22" s="2" t="n">
-        <v>46138.58333333334</v>
       </c>
       <c r="AF22" s="2" t="n">
         <v>46138</v>
@@ -3945,7 +4083,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Emirates Islamic Priority Banking UAE Banking Emirates Islamic Bank</t>
+          <t>Up to 6% back, unlimited Up to AED 750 welcome bonus No annual fee Exclusive travel &amp; lifestyle benefits And much more. • Terms &amp; conditions apply.</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -3968,12 +4106,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2048341323271336150</t>
+          <t>2048386615450435972</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048341323271336150</t>
+          <t>https://x.com/emiratesislamic/status/2048386615450435972</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3999,12 +4137,20 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Every financial journey deserves personal attention. From your first investment to building generational wealth, Emirates Islamic Priority Banking is by your side. Discover the difference today.</t>
+          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
+سعادة بلا حدود!
+تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
+🌟 استرداد يصل إلى 6%، بلا حدود
+🎁 مكافأة ترحيبية تصل إلى 750 درهم</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Every financial journey deserves personal attention. From your first investment to building generational wealth, Emirates Islamic Priority Banking is by your side. Discover the difference today.</t>
+          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
+سعادة بلا حدود!
+تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
+🌟 استرداد يصل إلى 6%، بلا حدود
+🎁 مكافأة ترحيبية تصل إلى 750 درهم</t>
         </is>
       </c>
       <c r="K23" t="b">
@@ -4014,16 +4160,16 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Apr 26, 2026 · 10:00 AM UTC</t>
+          <t>Apr 26, 2026 · 1:00 PM UTC</t>
         </is>
       </c>
       <c r="P23" s="2" t="n">
-        <v>46138.41666666666</v>
+        <v>46138.54166666666</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
@@ -4037,7 +4183,7 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -4046,19 +4192,27 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Every financial journey deserves personal attention. From your first investment to building generational wealth, Emirates Islamic Priority Banking is by your side. Discover the difference today.</t>
+          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
+سعادة بلا حدود!
+تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
+🌟 استرداد يصل إلى 6%، بلا حدود
+🎁 مكافأة ترحيبية تصل إلى 750 درهم</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>Every financial journey deserves personal attention. From your first investment to building generational wealth, Emirates Islamic Priority Banking is by your side. Discover the difference today.</t>
+          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
+سعادة بلا حدود!
+تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
+🌟 استرداد يصل إلى 6%، بلا حدود
+🎁 مكافأة ترحيبية تصل إلى 750 درهم</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Every financial journey deserves personal attention. From your first investment to building generational wealth, Emirates Islamic Priority Banking is by your side. Discover the difference today.</t>
+          <t>Amazon credit card from Emirates Islamic and MasterCard Unlimited happiness! Discover the card that turns every purchase into unlimited happiness 💳✨ 🌟 Cashback up to 6%, no limits 🎁 Welcome bonus up to 750 dirhams</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -4072,7 +4226,7 @@
         </is>
       </c>
       <c r="AE23" s="2" t="n">
-        <v>46138.58333333334</v>
+        <v>46138.70833333334</v>
       </c>
       <c r="AF23" s="2" t="n">
         <v>46138</v>
@@ -4089,7 +4243,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>From your first investment to building generational wealth, Emirates Islamic Priority Banking is by your side. • Every financial journey deserves personal attention. • Discover the difference today.</t>
+          <t>Discover the card that turns every purchase into unlimited happiness 💳✨ 🌟 Cashback up to 6%, no limits 🎁 Welcome bonus up to 750 dirhams • Amazon credit card from Emirates Islamic and MasterCard Unlimited happiness!</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -4160,7 +4314,7 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -4264,43 +4418,43 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2048469042315337899</t>
+          <t>2048341316237426944</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://x.com/Nidhinkn/status/2048469042315337899</t>
+          <t>https://x.com/emiratesislamic/status/2048341316237426944</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://x.com/Nidhinkn</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nidhinkn</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nidhin</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/862744582882308096/PYF7ziU7_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>I am using @EmiratesNBD_KSA InfiniteCard for 3years. On 01/02/2026 I made a Purchase of 100$ as per the rule of VisaAirportComp @VisaCEMEA to avail LoungeAccess. #ENBD never notified me about the monthly spend req of SAR 3000. They charged me 460 SAR @SAMA_GOV @EmiratesNBD_AE</t>
+          <t>كل استثمار هو بداية قصة تحتاج إلى اهتمام استثنائي. مع الخدمات المصرفية المميزة من الإمارات الإسلامي، إن استثمارك الأول اليوم هو إرث الغد لأبنائك. اكشتف التميز الذي يصنع الفارق.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>I am using &lt;a href="/EmiratesNBD_KSA" title="Emirates NBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; InfiniteCard for 3years. On 01/02/2026 I made a Purchase of 100$ as per the rule of VisaAirportComp &lt;a href="/VisaCEMEA" title="Visa Central &amp;amp; Eastern Europe,Middle East &amp;amp; Africa"&gt;@VisaCEMEA&lt;/a&gt; to avail LoungeAccess. &lt;a href="/search?f=tweets&amp;amp;q=%23ENBD"&gt;#ENBD&lt;/a&gt; never notified me about the monthly spend req of SAR 3000. They charged me 460 SAR &lt;a href="/SAMA_GOV" title="SAMA | البنك المركزي السعودي"&gt;@SAMA_GOV&lt;/a&gt; &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;</t>
+          <t>كل استثمار هو بداية قصة تحتاج إلى اهتمام استثنائي. مع الخدمات المصرفية المميزة من الإمارات الإسلامي، إن استثمارك الأول اليوم هو إرث الغد لأبنائك. اكشتف التميز الذي يصنع الفارق.</t>
         </is>
       </c>
       <c r="K25" t="b">
@@ -4310,23 +4464,19 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>8h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Apr 26, 2026 · 6:27 PM UTC</t>
+          <t>Apr 26, 2026 · 10:00 AM UTC</t>
         </is>
       </c>
       <c r="P25" s="2" t="n">
-        <v>46138.76875</v>
+        <v>46138.41666666666</v>
       </c>
       <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_KSA', 'https://x.com/VisaCEMEA', 'https://x.com/search?f=tweets&amp;q=%23ENBD', 'https://x.com/SAMA_GOV', 'https://x.com/EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
         <v>1</v>
       </c>
@@ -4337,64 +4487,64 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>I am using @EmiratesNBD_KSA InfiniteCard for 3years. On 01/02/2026 I made a Purchase of 100$ as per the rule of VisaAirportComp @VisaCEMEA to avail LoungeAccess. #ENBD never notified me about the monthly spend req of SAR 3000. They charged me 460 SAR @SAMA_GOV @EmiratesNBD_AE</t>
+          <t>كل استثمار هو بداية قصة تحتاج إلى اهتمام استثنائي. مع الخدمات المصرفية المميزة من الإمارات الإسلامي، إن استثمارك الأول اليوم هو إرث الغد لأبنائك. اكشتف التميز الذي يصنع الفارق.</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>I am using @EmiratesNBD_KSA InfiniteCard for 3years. On 01/02/2026 I made a Purchase of 100$ as per the rule of VisaAirportComp @VisaCEMEA to avail LoungeAccess. #ENBD never notified me about the monthly spend req of SAR 3000. They charged me 460 SAR @SAMA_GOV @EmiratesNBD_AE</t>
+          <t>كل استثمار هو بداية قصة تحتاج إلى اهتمام استثنائي. مع الخدمات المصرفية المميزة من الإمارات الإسلامي، إن استثمارك الأول اليوم هو إرث الغد لأبنائك. اكشتف التميز الذي يصنع الفارق.</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>I have been using the @EmiratesNBD_KSA InfiniteCard for 3 years. On 01/02/2026, I made a purchase of $100 according to the rule of VisaAirportComp @VisaCEMEA to avail Lounge Access. #ENBD never notified me about the monthly spending requirement of SAR 3000. They charged me 460 SAR @SAMA_GOV @EmiratesNBD_AE</t>
+          <t>Every investment is the beginning of a story that requires exceptional attention. With the premium banking services from Emirates Islamic, your first investment today is the legacy of tomorrow for your children. Discover the excellence that makes a difference.</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Cust</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE25" s="2" t="n">
-        <v>46138.93541666667</v>
+        <v>46138.58333333334</v>
       </c>
       <c r="AF25" s="2" t="n">
         <v>46138</v>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
+          <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>On 01/02/2026, I made a purchase of $100 according to the rule of VisaAirportComp @VisaCEMEA to avail Lounge Access. • #ENBD never notified me about the monthly spending requirement of SAR 3000. • They charged me 460 SAR @SAMA_GOV @EmiratesNBD_AE</t>
+          <t>With the premium banking services from Emirates Islamic, your first investment today is the legacy of tomorrow for your children. • Every investment is the beginning of a story that requires exceptional attention. • Discover the excellence that makes a difference.</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank (ENBD)</t>
+          <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AK25" t="n">
@@ -4412,43 +4562,47 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2048587742964015122</t>
+          <t>2048326216122335689</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://x.com/OhManal72060/status/2048587742964015122</t>
+          <t>https://x.com/emiratesislamic/status/2048326216122335689</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://x.com/OhManal72060</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>OhManal72060</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Manal OH</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE تم تحويل الراتب اليكم ولم ينزل ؟</t>
+          <t>دع مدخراتك تنمو بمعدل ربح متوقع يصل إلى %6.00 سنوياً مع حساب التوفير الإلكتروني الخاص بك من الإمارات الإسلامي. يسري العرض من 1 فبراير ولغاية 30 أبريل 2026. تطبق الشروط والأحكام.
+تفضل بزيارة
+https://t.co/V3u06n9tmn https://t.co/J0Ld7tXCk7</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; تم تحويل الراتب اليكم ولم ينزل ؟</t>
+          <t>دع مدخراتك تنمو بمعدل ربح متوقع يصل إلى %6.00 سنوياً مع حساب التوفير الإلكتروني الخاص بك من الإمارات الإسلامي. يسري العرض من 1 فبراير ولغاية 30 أبريل 2026. تطبق الشروط والأحكام.
+تفضل بزيارة
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/exclusive-e-savings-account-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=esavings"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K26" t="b">
@@ -4458,21 +4612,21 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>37m</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Apr 27, 2026 · 2:19 AM UTC</t>
+          <t>Apr 26, 2026 · 9:00 AM UTC</t>
         </is>
       </c>
       <c r="P26" s="2" t="n">
-        <v>46139.09652777778</v>
+        <v>46138.375</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
-          <t>['https://x.com/EmiratesNBD_AE']</t>
+          <t>['https://www.emiratesislamic.ae/ar/offers/exclusive-e-savings-account-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=esavings']</t>
         </is>
       </c>
       <c r="S26" t="n">
@@ -4485,64 +4639,78 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE تم تحويل الراتب اليكم ولم ينزل ؟</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
+          <t>دع مدخراتك تنمو بمعدل ربح متوقع يصل إلى %6.00 سنوياً مع حساب التوفير الإلكتروني الخاص بك من الإمارات الإسلامي. يسري العرض من 1 فبراير ولغاية 30 أبريل 2026. تطبق الشروط والأحكام.
+تفضل بزيارة
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048326216122335689</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>دع مدخراتك تنمو بمعدل ربح متوقع يصل إلى %6.00 سنوياً مع حساب التوفير الإلكتروني الخاص بك من الإمارات الإسلامي. يسري العرض من 1 فبراير ولغاية 30 أبريل 2026. تطبق الشروط والأحكام.
+تفضل بزيارة
+https://t.co/V3u06n9tmn https://t.co/J0Ld7tXCk7</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE تم تحويل الراتب اليكم ولم ينزل ؟</t>
+          <t>دع مدخراتك تنمو بمعدل ربح متوقع يصل إلى %6.00 سنوياً مع حساب التوفير الإلكتروني الخاص بك من الإمارات الإسلامي. يسري العرض من 1 فبراير ولغاية 30 أبريل 2026. تطبق الشروط والأحكام.
+تفضل بزيارة
+https://t.co/V3u06n9tmn https://t.co/J0Ld7tXCk7</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>The salary has been transferred to you but has not been deposited?</t>
+          <t>Let your savings grow at an expected profit rate of up to 6.00% annually with your electronic savings account from Emirates Islamic. The offer is valid from February 1 to April 30, 2026. Terms and conditions apply.</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Cust</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE26" s="2" t="n">
-        <v>46139.26319444444</v>
+        <v>46138.54166666666</v>
       </c>
       <c r="AF26" s="2" t="n">
-        <v>46139</v>
+        <v>46138</v>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
+          <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>The salary has been transferred to you but has not been deposited?</t>
+          <t>Let your savings grow at an expected profit rate of up to 6.00% annually with your electronic savings account from Emirates Islamic. • The offer is valid from February 1 to April 30, 2026. • Terms and conditions apply.</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank (ENBD)</t>
+          <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AK26" t="n">
@@ -4560,36 +4728,1122 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2048297636403315015</t>
+          <t>2048311115751342110</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://x.com/safoo6764/status/2048297636403315015</t>
+          <t>https://x.com/emiratesislamic/status/2048311115751342110</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://x.com/safoo6764</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>safoo6764</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Abu Turki</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1183801906721886210/Xmzcum3R_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
+        <is>
+          <t>ابدأ بفتح حساب "الثروات الرقمية" على الفور للوصول إلى مجموعة كاملة من الاستثمارات العالمية المتوافقة مع أحكام الشريعة الإسلامية. احصل على إمكانية التداول في الأسهم الدولية والمحلية بالإضافة إلى صناديق الاستثمار العالمية.
+قم بتحميل تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك. https://t.co/WhwAacgo92</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>ابدأ بفتح حساب &amp;#34;الثروات الرقمية&amp;#34; على الفور للوصول إلى مجموعة كاملة من الاستثمارات العالمية المتوافقة مع أحكام الشريعة الإسلامية. احصل على إمكانية التداول في الأسهم الدولية والمحلية بالإضافة إلى صناديق الاستثمار العالمية.
+قم بتحميل تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك.</t>
+        </is>
+      </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Apr 26, 2026 · 8:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="n">
+        <v>46138.33333333334</v>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>92</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>ابدأ بفتح حساب "الثروات الرقمية" على الفور للوصول إلى مجموعة كاملة من الاستثمارات العالمية المتوافقة مع أحكام الشريعة الإسلامية. احصل على إمكانية التداول في الأسهم الدولية والمحلية بالإضافة إلى صناديق الاستثمار العالمية.
+قم بتحميل تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك.</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048311115751342110</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>ابدأ بفتح حساب "الثروات الرقمية" على الفور للوصول إلى مجموعة كاملة من الاستثمارات العالمية المتوافقة مع أحكام الشريعة الإسلامية. احصل على إمكانية التداول في الأسهم الدولية والمحلية بالإضافة إلى صناديق الاستثمار العالمية.
+قم بتحميل تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك. https://t.co/WhwAacgo92</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>ابدأ بفتح حساب "الثروات الرقمية" على الفور للوصول إلى مجموعة كاملة من الاستثمارات العالمية المتوافقة مع أحكام الشريعة الإسلامية. احصل على إمكانية التداول في الأسهم الدولية والمحلية بالإضافة إلى صناديق الاستثمار العالمية.
+قم بتحميل تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك. https://t.co/WhwAacgo92</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>Start by opening a "Digital Wealth" account immediately to access a full range of global investments compliant with Islamic law. Get the ability to trade in international and local stocks as well as global investment funds.
+Download the + EI mobile banking app. https://t.co/WhwAacgo92</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AE27" s="2" t="n">
+        <v>46138.5</v>
+      </c>
+      <c r="AF27" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>2. Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Start by opening a "Digital Wealth" account immediately to access a full range of global investments compliant with Islamic law. • Get the ability to trade in international and local stocks as well as global investment funds. • Download the + EI mobile banking app.</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AK27" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2048311115730288881</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048311115730288881</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Open a Digital Wealth Account instantly to enjoy a complete suite of Shariah-compliant global investments. Get access to International &amp; UAE stocks as well as Global Mutual Funds.
+Download the EI + Mobile Banking App today.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Open a Digital Wealth Account instantly to enjoy a complete suite of Shariah-compliant global investments. Get access to International &amp;amp; UAE stocks as well as Global Mutual Funds.
+Download the EI + Mobile Banking App today.</t>
+        </is>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Apr 26, 2026 · 8:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="n">
+        <v>46138.33333333334</v>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>61</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Open a Digital Wealth Account instantly to enjoy a complete suite of Shariah-compliant global investments. Get access to International &amp; UAE stocks as well as Global Mutual Funds.
+Download the EI + Mobile Banking App today.</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>Open a Digital Wealth Account instantly to enjoy a complete suite of Shariah-compliant global investments. Get access to International &amp; UAE stocks as well as Global Mutual Funds.
+Download the EI + Mobile Banking App today.</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>Open a Digital Wealth Account instantly to enjoy a complete suite of Shariah-compliant global investments. Get access to international and UAE stocks as well as global mutual funds. Download the EI + Mobile Banking App today.</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AE28" s="2" t="n">
+        <v>46138.5</v>
+      </c>
+      <c r="AF28" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>2. Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Open a Digital Wealth Account instantly to enjoy a complete suite of Shariah-compliant global investments. • Get access to international and UAE stocks as well as global mutual funds. • Download the EI + Mobile Banking App today.</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AK28" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2048280917030867217</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048280917030867217</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>لا تحتاج إلى معالجة كل شيء دفعة واحدة.
+ابدأ بمصروف رئيسي واحد.
+الاستمرارية تصنع تقدّماً حقيقياً.
+#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
+emiratesislamic.ae/ar/key-in…</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>لا تحتاج إلى معالجة كل شيء دفعة واحدة.
+ابدأ بمصروف رئيسي واحد.
+الاستمرارية تصنع تقدّماً حقيقياً.
+&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Apr 26, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="n">
+        <v>46138.25</v>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+        </is>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>50</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>لا تحتاج إلى معالجة كل شيء دفعة واحدة.
+ابدأ بمصروف رئيسي واحد.
+الاستمرارية تصنع تقدّماً حقيقياً.
+#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
+emiratesislamic.ae/ar/key-in…</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>لا تحتاج إلى معالجة كل شيء دفعة واحدة.
+ابدأ بمصروف رئيسي واحد.
+الاستمرارية تصنع تقدّماً حقيقياً.
+#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
+emiratesislamic.ae/ar/key-in…</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>You don't need to tackle everything at once. Start with one main expense. Consistency leads to real progress.</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE29" s="2" t="n">
+        <v>46138.41666666666</v>
+      </c>
+      <c r="AF29" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>2. Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>You don't need to tackle everything at once. • Start with one main expense. • Consistency leads to real progress.</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AK29" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2048213606257570300</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://x.com/AmritMohanty1/status/2048213606257570300</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://x.com/AmritMohanty1</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AmritMohanty1</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Amrit Mohanty</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1798792220885307395/ZFbORVL__bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>@AmritMohanty1 Hi Amrit! Thanks for reaching us. Apologies for any inconvenience caused. We kindly request you to reach out to us from your registered email address at social@emiratesnbd.com quoting case #1001922 in the subject line of the email.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Thank you. I have emailed from my registered email ID quoting Case #234234532915. Kindly review urgently and confirm no fees/interest will apply while the dispute is under investigation, as the due date is near.</t>
+        </is>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Apr 26, 2026 · 1:32 AM UTC</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="n">
+        <v>46138.06388888889</v>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>20</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Thank you. I have emailed from my registered email ID quoting Case #234234532915. Kindly review urgently and confirm no fees/interest will apply while the dispute is under investigation, as the due date is near.</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>https://x.com/AmritMohanty1/status/2048213606257570300</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>@AmritMohanty1 Hi Amrit! Thanks for reaching us. Apologies for any inconvenience caused. We kindly request you to reach out to us from your registered email address at social@emiratesnbd.com quoting case #1001922 in the subject line of the email.</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>@AmritMohanty1 Hi Amrit! Thanks for reaching us. Apologies for any inconvenience caused. We kindly request you to reach out to us from your registered email address at social@emiratesnbd.com quoting case #1001922 in the subject line of the email.</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>Hi Amrit! Thanks for reaching us. Apologies for any inconvenience caused. We kindly request you to reach out to us from your registered email address at social@emiratesnbd.com quoting case #1001922 in the subject line of the email.</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AE30" s="2" t="n">
+        <v>46138.23055555556</v>
+      </c>
+      <c r="AF30" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>We kindly request you to reach out to us from your registered email address at social@emiratesnbd.com quoting case #1001922 in the subject line of the email. • Apologies for any inconvenience caused.</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK30" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2048469042315337899</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://x.com/Nidhinkn/status/2048469042315337899</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://x.com/Nidhinkn</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Nidhinkn</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Nidhin</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/862744582882308096/PYF7ziU7_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>I am using @EmiratesNBD_KSA InfiniteCard for 3years. On 01/02/2026 I made a Purchase of 100$ as per the rule of VisaAirportComp @VisaCEMEA to avail LoungeAccess. #ENBD never notified me about the monthly spend req of SAR 3000. They charged me 460 SAR @SAMA_GOV @EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>I am using &lt;a href="/EmiratesNBD_KSA" title="Emirates NBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; InfiniteCard for 3years. On 01/02/2026 I made a Purchase of 100$ as per the rule of VisaAirportComp &lt;a href="/VisaCEMEA" title="Visa Central &amp;amp; Eastern Europe,Middle East &amp;amp; Africa"&gt;@VisaCEMEA&lt;/a&gt; to avail LoungeAccess. &lt;a href="/search?f=tweets&amp;amp;q=%23ENBD"&gt;#ENBD&lt;/a&gt; never notified me about the monthly spend req of SAR 3000. They charged me 460 SAR &lt;a href="/SAMA_GOV" title="SAMA | البنك المركزي السعودي"&gt;@SAMA_GOV&lt;/a&gt; &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>8h</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Apr 26, 2026 · 6:27 PM UTC</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>46138.76875</v>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_KSA', 'https://x.com/VisaCEMEA', 'https://x.com/search?f=tweets&amp;q=%23ENBD', 'https://x.com/SAMA_GOV', 'https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="S31" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>17</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>I am using @EmiratesNBD_KSA InfiniteCard for 3years. On 01/02/2026 I made a Purchase of 100$ as per the rule of VisaAirportComp @VisaCEMEA to avail LoungeAccess. #ENBD never notified me about the monthly spend req of SAR 3000. They charged me 460 SAR @SAMA_GOV @EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>I am using @EmiratesNBD_KSA InfiniteCard for 3years. On 01/02/2026 I made a Purchase of 100$ as per the rule of VisaAirportComp @VisaCEMEA to avail LoungeAccess. #ENBD never notified me about the monthly spend req of SAR 3000. They charged me 460 SAR @SAMA_GOV @EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>I have been using the @EmiratesNBD_KSA Infinite Card for 3 years. On 01/02/2026, I made a purchase of $100 according to the rule of VisaAirportComp @VisaCEMEA to avail Lounge Access. #ENBD never notified me about the monthly spending requirement of SAR 3000. They charged me 460 SAR @SAMA_GOV @EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AE31" s="2" t="n">
+        <v>46138.93541666667</v>
+      </c>
+      <c r="AF31" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>On 01/02/2026, I made a purchase of $100 according to the rule of VisaAirportComp @VisaCEMEA to avail Lounge Access. • #ENBD never notified me about the monthly spending requirement of SAR 3000. • They charged me 460 SAR @SAMA_GOV @EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK31" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2048587742964015122</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://x.com/OhManal72060/status/2048587742964015122</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://x.com/OhManal72060</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>OhManal72060</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Manal OH</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE تم تحويل الراتب اليكم ولم ينزل ؟</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; تم تحويل الراتب اليكم ولم ينزل ؟</t>
+        </is>
+      </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>37m</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Apr 27, 2026 · 2:19 AM UTC</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>46139.09652777778</v>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>15</v>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE تم تحويل الراتب اليكم ولم ينزل ؟</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>https://x.com/OhManal72060/status/2048587742964015122</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE تم تحويل الراتب اليكم ولم ينزل ؟</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE تم تحويل الراتب اليكم ولم ينزل ؟</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>The salary has been transferred to you but it hasn't been deposited?</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AE32" s="2" t="n">
+        <v>46139.26319444444</v>
+      </c>
+      <c r="AF32" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>The salary has been transferred to you but it hasn't been deposited?</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK32" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2048286728524284019</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://x.com/X3_3y3/status/2048286728524284019</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://x.com/X3_3y3</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>X3_3y3</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>:(</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1724458468550053888/zEyLH6k2_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Disappointed with @EmiratesNBD_AE support on reported fraudulent credit card charges. Disputed amounts still show as payable and due date is near. Requested urgent review, temporary credit, and waiver of fees/interest pending investigation. Please assist urgently. #EmiratesNBD</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>السلام عليكم ممكن تتواصلون معي خاص ؟</t>
+        </is>
+      </c>
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>['AmritMohanty1', 'EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Apr 26, 2026 · 6:23 AM UTC</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="n">
+        <v>46138.26597222222</v>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>4</v>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>السلام عليكم ممكن تتواصلون معي خاص ؟</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>https://x.com/X3_3y3/status/2048286728524284019</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>Disappointed with @EmiratesNBD_AE support on reported fraudulent credit card charges. Disputed amounts still show as payable and due date is near. Requested urgent review, temporary credit, and waiver of fees/interest pending investigation. Please assist urgently. #EmiratesNBD</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>Disappointed with @EmiratesNBD_AE support on reported fraudulent credit card charges. Disputed amounts still show as payable and due date is near. Requested urgent review, temporary credit, and waiver of fees/interest pending investigation. Please assist urgently. #EmiratesNBD</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>Disappointed with Emirates NBD's support regarding reported fraudulent credit card charges. Disputed amounts still show as payable and the due date is approaching. I requested an urgent review, temporary credit, and a waiver of fees/interest pending investigation. Please assist urgently.</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AE33" s="2" t="n">
+        <v>46138.43263888889</v>
+      </c>
+      <c r="AF33" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Disappointed with Emirates NBD's support regarding reported fraudulent credit card charges. • I requested an urgent review, temporary credit, and a waiver of fees/interest pending investigation. • Disputed amounts still show as payable and the due date is approaching.</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK33" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>AmritMohanty1, EmiratesNBD_AE</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2048297636403315015</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://x.com/safoo6764/status/2048297636403315015</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://x.com/safoo6764</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>safoo6764</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Abu Turki</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1183801906721886210/Xmzcum3R_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
         <is>
           <t>@EmiratesNBD_KSA السلام عليكم ورحمة الله وبركاتة 
 لماذا هذا التأخير في بنك الامارات 
@@ -4598,7 +5852,7 @@
 جميع البنوك بالمملكة تاني الرد خلال ٤٨ ساعة</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>&lt;a href="/EmiratesNBD_KSA" title="Emirates NBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; السلام عليكم ورحمة الله وبركاتة 
 لماذا هذا التأخير في بنك الامارات 
@@ -4607,48 +5861,48 @@
 جميع البنوك بالمملكة تاني الرد خلال ٤٨ ساعة</t>
         </is>
       </c>
-      <c r="K27" t="b">
-        <v>0</v>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
         <is>
           <t>19h</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>Apr 26, 2026 · 7:06 AM UTC</t>
         </is>
       </c>
-      <c r="P27" s="2" t="n">
+      <c r="P34" s="2" t="n">
         <v>46138.29583333333</v>
       </c>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr">
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
         <is>
           <t>['https://x.com/EmiratesNBD_KSA']</t>
         </is>
       </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
         <v>31</v>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>@EmiratesNBD_KSA السلام عليكم ورحمة الله وبركاتة 
 لماذا هذا التأخير في بنك الامارات 
@@ -4657,9 +5911,12 @@
 جميع البنوك بالمملكة تاني الرد خلال ٤٨ ساعة</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr">
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>https://x.com/safoo6764/status/2048297636403315015</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
         <is>
           <t>@EmiratesNBD_KSA السلام عليكم ورحمة الله وبركاتة 
 لماذا هذا التأخير في بنك الامارات 
@@ -4668,51 +5925,60 @@
 جميع البنوك بالمملكة تاني الرد خلال ٤٨ ساعة</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>Peace be upon you. Why is there this delay at Emirates Bank? There has been a request since last Sunday, and until now there has been no response. All banks in the kingdom respond within 48 hours.</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA السلام عليكم ورحمة الله وبركاتة 
+لماذا هذا التأخير في بنك الامارات 
+يوجد طلب من يوم الاحد إلى فات 
+والى الان ما ياتي رد عليه 
+جميع البنوك بالمملكة تاني الرد خلال ٤٨ ساعة</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>Peace be upon you. Why is there this delay at Emirates Bank? There has been a request since last Sunday, and until now there has been no response. All banks in the Kingdom respond within 48 hours.</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="AD27" t="inlineStr">
+      <c r="AD34" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="AE27" s="2" t="n">
+      <c r="AE34" s="2" t="n">
         <v>46138.4625</v>
       </c>
-      <c r="AF27" s="2" t="n">
+      <c r="AF34" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="AG27" t="inlineStr">
+      <c r="AG34" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="AH27" t="inlineStr">
+      <c r="AH34" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>There has been a request since last Sunday, and until now there has been no response. • All banks in the kingdom respond within 48 hours. • Why is there this delay at Emirates Bank?</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>There has been a request since last Sunday, and until now there has been no response. • All banks in the Kingdom respond within 48 hours. • Why is there this delay at Emirates Bank?</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AK27" t="n">
+      <c r="AK34" t="n">
         <v>2026</v>
       </c>
-      <c r="AL27" t="inlineStr">
+      <c r="AL34" t="inlineStr">
         <is>
           <t>None</t>
         </is>

--- a/check2.xlsx
+++ b/check2.xlsx
@@ -1249,7 +1249,9 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Email: 2</t>
+          <t>Email: 2 
+#UnitedAgainstFraud
+#EmiratesNBD</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1280,7 +1282,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Email: 2</t>
+          <t>Email: 2 #UnitedAgainstFraud #EmiratesNBD</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1419,7 +1421,9 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Email: 2</t>
+          <t>Email: 2 
+#UnitedAgainstFraud
+#EmiratesNBD</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1450,7 +1454,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Email: 2</t>
+          <t>Email: 2 #UnitedAgainstFraud #EmiratesNBD</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1891,7 +1895,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>What bank do you use? HSBC or DIB or Emirates NBD or Mashreq? I used HSBC that year. 😎</t>
+          <t>What bank do you use? HSBC or DIB or Emirates NBD or Mashreq? I used HSBC that year.😎</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1976,7 +1980,10 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>هل أنت #بخير؟</t>
+          <t>🇦🇪 A prestigious milestone strengthening the UAE’s financial leadership
+Visa has officially appointed Emirates NBD as the National Net Settlement Agent in the country.
+Now, all local Visa card transactions will be settled domestically in AED — a strategic step that enhances financial sovereignty and drives digital innovation.
+@EmiratesNBD_AE @Visa</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2043,17 +2050,23 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>هل أنت #بخير؟</t>
+          <t>🇦🇪 A prestigious milestone strengthening the UAE’s financial leadership
+Visa has officially appointed Emirates NBD as the National Net Settlement Agent in the country.
+Now, all local Visa card transactions will be settled domestically in AED — a strategic step that enhances financial sovereignty and drives digital innovation.
+@EmiratesNBD_AE @Visa</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>هل أنت #بخير؟</t>
+          <t>🇦🇪 A prestigious milestone strengthening the UAE’s financial leadership
+Visa has officially appointed Emirates NBD as the National Net Settlement Agent in the country.
+Now, all local Visa card transactions will be settled domestically in AED — a strategic step that enhances financial sovereignty and drives digital innovation.
+@EmiratesNBD_AE @Visa</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Are you okay?</t>
+          <t>A prestigious milestone strengthening the UAE’s financial leadership. Visa has officially appointed Emirates NBD as the National Net Settlement Agent in the country. Now, all local Visa card transactions will be settled domestically in AED — a strategic step that enhances financial sovereignty and drives digital innovation.</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -2063,7 +2076,7 @@
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE10" s="2" t="n">
@@ -2084,7 +2097,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Are you okay?</t>
+          <t>Now, all local Visa card transactions will be settled domestically in AED — a strategic step that enhances financial sovereignty and drives digital innovation. • Visa has officially appointed Emirates NBD as the National Net Settlement Agent in the country. • A prestigious milestone strengthening the UAE’s financial leadership.</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -2383,7 +2396,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Visa has appointed Emirates NBD as the UAE NNSS agent, facilitating quicker domestic card settlements in dirhams and enhancing payment efficiency.</t>
+          <t>Visa has appointed Emirates NBD as the UAE NNSS agent, allowing for faster domestic card settlements in dirhams and enhancing payment efficiency.</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2414,7 +2427,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Visa has appointed Emirates NBD as the UAE NNSS agent, facilitating quicker domestic card settlements in dirhams and enhancing payment efficiency.</t>
+          <t>Visa has appointed Emirates NBD as the UAE NNSS agent, allowing for faster domestic card settlements in dirhams and enhancing payment efficiency.</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2673,8 +2686,17 @@
 @EmiratesNBD_AE I @Visa</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>https://x.com/DXBMediaOffice/status/2049841391577260274</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Visa, a world leader in digital payments, has appointed Emirates NBD, a leading banking group in the Middle East, North Africa and Türkiye (MENAT) region, as its official National Net Settlement Service (NNSS) Agent in the UAE, allowing Visa’s domestic card transactions to be settled by Emirates NBD locally in UAE Dirhams (AED) in lieu of international settlement. The collaboration enhances the UAE’s domestic settlement capabilities. 
+@EmiratesNBD_AE I @Visa</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>Visa, a world leader in digital payments, has appointed Emirates NBD, a leading banking group in the Middle East, North Africa and Türkiye (MENAT) region, as its official National Net Settlement Service (NNSS) Agent in the UAE, allowing Visa’s domestic card transactions to be settled by Emirates NBD locally in UAE Dirhams (AED) in lieu of international settlement. The collaboration enhances the UAE’s domestic settlement capabilities. 
@@ -2768,7 +2790,7 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>DM 📥, great project, let’s collab 💯✨</t>
+          <t>@Universal_USDU @ADGlobalMarket @EmiratesNBD_AE @MashreqTweets @almaryahbank @aquanow DM 📥, great project, let’s collab 💯✨</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2822,16 +2844,24 @@
           <t>DM 📥, great project, let’s collab 💯✨</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>https://x.com/MrDariBoss/status/2049839188913320262</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>@Universal_USDU @ADGlobalMarket @EmiratesNBD_AE @MashreqTweets @almaryahbank @aquanow DM 📥, great project, let’s collab 💯✨</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>DM 📥, great project, let’s collab 💯✨</t>
+          <t>@Universal_USDU @ADGlobalMarket @EmiratesNBD_AE @MashreqTweets @almaryahbank @aquanow DM 📥, great project, let’s collab 💯✨</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>DM me, great project, let’s collaborate.</t>
+          <t>DM, great project, let’s collaborate.</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2862,7 +2892,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>DM me, great project, let’s collaborate.</t>
+          <t>DM, great project, let’s collaborate.</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -2919,7 +2949,7 @@
           <t>🏦 Emirates NBD takes control of RBL Bank
 Emirates NBD invests ₹38,489 crore in  for a 74% stake. This massive capital infusion targets top five private bank status within 3-5 years.
 #RBLBank
-Read more: askfuzz.ai/discover/news/con…</t>
+Read more: https://t.co/jql9PSe3AI https://t.co/KAcb3dolMK</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2979,14 +3009,25 @@
 Read more: askfuzz.ai/discover/news/con…</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>https://x.com/insightsbyfuzz/status/2049836484035793204</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
         <is>
           <t>🏦 Emirates NBD takes control of RBL Bank
 Emirates NBD invests ₹38,489 crore in  for a 74% stake. This massive capital infusion targets top five private bank status within 3-5 years.
 #RBLBank
-Read more: askfuzz.ai/discover/news/con…</t>
+Read more: https://t.co/jql9PSe3AI https://t.co/KAcb3dolMK</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>🏦 Emirates NBD takes control of RBL Bank
+Emirates NBD invests ₹38,489 crore in  for a 74% stake. This massive capital infusion targets top five private bank status within 3-5 years.
+#RBLBank
+Read more: https://t.co/jql9PSe3AI https://t.co/KAcb3dolMK</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -3077,7 +3118,7 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Emirates NBD prices $750mln PNC6 AT1 bond in first GCC public debt sale since Iran war zawya.com/en/capital-markets…</t>
+          <t>Emirates NBD prices $750mln PNC6 AT1 bond in first GCC public debt sale since Iran war https://t.co/jGs3XiGvP7</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -3131,11 +3172,19 @@
           <t>Emirates NBD prices $750mln PNC6 AT1 bond in first GCC public debt sale since Iran war zawya.com/en/capital-markets…</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>https://x.com/deegrose/status/2049834695249088852</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Emirates NBD prices $750mln PNC6 AT1 bond in first GCC public debt sale since Iran war https://t.co/jGs3XiGvP7</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Emirates NBD prices $750mln PNC6 AT1 bond in first GCC public debt sale since Iran war zawya.com/en/capital-markets…</t>
+          <t>Emirates NBD prices $750mln PNC6 AT1 bond in first GCC public debt sale since Iran war https://t.co/jGs3XiGvP7</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -3225,7 +3274,7 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Really solid concept here, open to connect anytime</t>
+          <t>@Universal_USDU @ADGlobalMarket @EmiratesNBD_AE @MashreqTweets @almaryahbank @aquanow Really solid concept here, open to connect anytime</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -3279,11 +3328,19 @@
           <t>Really solid concept here, open to connect anytime</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>https://x.com/00Q__/status/2049833166224216504</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>@Universal_USDU @ADGlobalMarket @EmiratesNBD_AE @MashreqTweets @almaryahbank @aquanow Really solid concept here, open to connect anytime</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Really solid concept here, open to connect anytime</t>
+          <t>@Universal_USDU @ADGlobalMarket @EmiratesNBD_AE @MashreqTweets @almaryahbank @aquanow Really solid concept here, open to connect anytime</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -3373,7 +3430,7 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Free assistance anytime, drop me a DM.</t>
+          <t>@Universal_USDU @ADGlobalMarket @EmiratesNBD_AE @MashreqTweets @almaryahbank @aquanow Free assistance anytime, drop me a DM.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -3427,16 +3484,24 @@
           <t>Free assistance anytime, drop me a DM.</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>https://x.com/raynft_/status/2049828036577460592</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>@Universal_USDU @ADGlobalMarket @EmiratesNBD_AE @MashreqTweets @almaryahbank @aquanow Free assistance anytime, drop me a DM.</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
+          <t>@Universal_USDU @ADGlobalMarket @EmiratesNBD_AE @MashreqTweets @almaryahbank @aquanow Free assistance anytime, drop me a DM.</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>Free assistance anytime, drop me a DM.</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Free assistance anytime, send me a direct message.</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3467,7 +3532,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Free assistance anytime, send me a direct message.</t>
+          <t>Free assistance anytime, drop me a DM.</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -3522,9 +3587,9 @@
       <c r="I20" t="inlineStr">
         <is>
           <t>🟥 نجاح كبير لصندوق فاندستار لأسهم الإمارات العربية المتحدة ذات الدخل من "الإمارات دبي الوطني لإدارة الأصول" والشركة تطلق صندوقاً جديداً للصكوك العالمية ذات العائد المرتفع. اقرأ المزيد:
-emiratesnbd.com/ar/media-cen……
+https://t.co/NvmepCllAn…
 Emirates NBD Asset Management highlights success of FundStar UAE Equities Income Fund and expands access to new global high-yield sukuk fund. Read more: 
-emiratesnbd.com/en/media-cen……</t>
+https://t.co/ncw3Zv5gtY…</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3584,20 +3649,31 @@
 emiratesnbd.com/en/media-cen……</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>https://x.com/SUAL6AN_UAE/status/2049819862168699318</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>🟥 نجاح كبير لصندوق فاندستار لأسهم الإمارات العربية المتحدة ذات الدخل من "الإمارات دبي الوطني لإدارة الأصول" والشركة تطلق صندوقاً جديداً للصكوك العالمية ذات العائد المرتفع. اقرأ المزيد:
+https://t.co/NvmepCllAn…
+Emirates NBD Asset Management highlights success of FundStar UAE Equities Income Fund and expands access to new global high-yield sukuk fund. Read more: 
+https://t.co/ncw3Zv5gtY…</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>🟥 نجاح كبير لصندوق فاندستار لأسهم الإمارات العربية المتحدة ذات الدخل من "الإمارات دبي الوطني لإدارة الأصول" والشركة تطلق صندوقاً جديداً للصكوك العالمية ذات العائد المرتفع. اقرأ المزيد:
-emiratesnbd.com/ar/media-cen……
+https://t.co/NvmepCllAn…
 Emirates NBD Asset Management highlights success of FundStar UAE Equities Income Fund and expands access to new global high-yield sukuk fund. Read more: 
-emiratesnbd.com/en/media-cen……</t>
+https://t.co/ncw3Zv5gtY…</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
           <t>Great success for the FundStar UAE Equities Income Fund from Emirates NBD Asset Management as the company launches a new global high-yield sukuk fund. Read more: 
-emiratesnbd.com/en/media-cen……</t>
+https://t.co/NvmepCllAn…</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3628,7 +3704,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Great success for the FundStar UAE Equities Income Fund from Emirates NBD Asset Management as the company launches a new global high-yield sukuk fund. • Read more: emiratesnbd.com/en/media-cen……</t>
+          <t>Great success for the FundStar UAE Equities Income Fund from Emirates NBD Asset Management as the company launches a new global high-yield sukuk fund. • Read more: https://t.co/NvmepCllAn…</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3681,6 +3757,74 @@
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
+        <is>
+          <t>Start your banking journey today with Emirates NBD.
+ابدأ رحلتك المصرفية اليوم مع بنك الإمارات دبي الوطني. https://t.co/tIpnLZ2ain</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Why settle for someone else’s highlights?
+Start your own journey with an Emirates NBD Voyager credit card. Apply today to get up to AED 700 in &lt;a href="http://Trip.com"&gt;Trip.com&lt;/a&gt; vouchers.
+Access benefits like:
+- AED 300 &lt;a href="http://Trip.com"&gt;Trip.com&lt;/a&gt; voucher with a new Emirates NBD Voyager World Credit Card
+- AED 700 &lt;a href="http://Trip.com"&gt;Trip.com&lt;/a&gt; voucher with a new Emirates NBD Voyager World Elite Credit Card
+Offer is valid until 15 May 2026. Apply now.
+Terms and Conditions apply.
+Apply Now: &lt;a href="https://www.emiratesnbd.com/en/campaigns/voyager-credit-cards"&gt;emiratesnbd.com/en/campaigns…&lt;/a&gt;
+النص المرافق للمنشور:
+لماذا تكتفي بمشاهدة اللقطات المميزة للآخرين؟
+ابدأ رحلتك الخاصة مع بطاقة فويجر من بنك الإمارات دبي الوطني. قدّم طلبك اليوم لتحصل على قسائم من &lt;a href="http://Trip.com"&gt;Trip.com&lt;/a&gt; بقيمة تصل إلى 700 درهم.
+استفد من المزايا التالية:
+- قسيمة &lt;a href="http://Trip.com"&gt;Trip.com&lt;/a&gt; بقيمة 300 درهم مع بطاقة فويجر وورلد الائتمانية الجديدة من بنك الإمارات دبي الوطني
+- قسيمة &lt;a href="http://Trip.com"&gt;Trip.com&lt;/a&gt; بقيمة 700 درهم مع بطاقة فويجر وورلد إيليت الائتمانية الجديدة من بنك الإمارات دبي الوطني
+يسري العرض حتى 15 مايو 2026. قدّم طلبك الآن.
+تطبّق الشروط والأحكام.
+ تقدم بطلبك الآن: &lt;a href="https://www.emiratesnbd.com/ar/campaigns/voyager-credit-cards"&gt;emiratesnbd.com/ar/campaigns…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Apr 30, 2026 · 11:03 AM UTC</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="n">
+        <v>46142.46041666667</v>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>['http://Trip.com', 'http://Trip.com', 'http://Trip.com', 'https://www.emiratesnbd.com/en/campaigns/voyager-credit-cards', 'http://Trip.com', 'http://Trip.com', 'http://Trip.com', 'https://www.emiratesnbd.com/ar/campaigns/voyager-credit-cards']</t>
+        </is>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
+      </c>
+      <c r="V21" t="n">
+        <v>636</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
         <is>
           <t>Why settle for someone else’s highlights?
 Start your own journey with an Emirates NBD Voyager credit card. Apply today to get up to AED 700 in Trip.com vouchers.
@@ -3701,122 +3845,26 @@
  تقدم بطلبك الآن: emiratesnbd.com/ar/campaigns…</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Why settle for someone else’s highlights?
-Start your own journey with an Emirates NBD Voyager credit card. Apply today to get up to AED 700 in &lt;a href="http://Trip.com"&gt;Trip.com&lt;/a&gt; vouchers.
-Access benefits like:
-- AED 300 &lt;a href="http://Trip.com"&gt;Trip.com&lt;/a&gt; voucher with a new Emirates NBD Voyager World Credit Card
-- AED 700 &lt;a href="http://Trip.com"&gt;Trip.com&lt;/a&gt; voucher with a new Emirates NBD Voyager World Elite Credit Card
-Offer is valid until 15 May 2026. Apply now.
-Terms and Conditions apply.
-Apply Now: &lt;a href="https://www.emiratesnbd.com/en/campaigns/voyager-credit-cards"&gt;emiratesnbd.com/en/campaigns…&lt;/a&gt;
-النص المرافق للمنشور:
-لماذا تكتفي بمشاهدة اللقطات المميزة للآخرين؟
-ابدأ رحلتك الخاصة مع بطاقة فويجر من بنك الإمارات دبي الوطني. قدّم طلبك اليوم لتحصل على قسائم من &lt;a href="http://Trip.com"&gt;Trip.com&lt;/a&gt; بقيمة تصل إلى 700 درهم.
-استفد من المزايا التالية:
-- قسيمة &lt;a href="http://Trip.com"&gt;Trip.com&lt;/a&gt; بقيمة 300 درهم مع بطاقة فويجر وورلد الائتمانية الجديدة من بنك الإمارات دبي الوطني
-- قسيمة &lt;a href="http://Trip.com"&gt;Trip.com&lt;/a&gt; بقيمة 700 درهم مع بطاقة فويجر وورلد إيليت الائتمانية الجديدة من بنك الإمارات دبي الوطني
-يسري العرض حتى 15 مايو 2026. قدّم طلبك الآن.
-تطبّق الشروط والأحكام.
- تقدم بطلبك الآن: &lt;a href="https://www.emiratesnbd.com/ar/campaigns/voyager-credit-cards"&gt;emiratesnbd.com/ar/campaigns…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K21" t="b">
-        <v>0</v>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>16h</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Apr 30, 2026 · 11:03 AM UTC</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="n">
-        <v>46142.46041666667</v>
-      </c>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>['http://Trip.com', 'http://Trip.com', 'http://Trip.com', 'https://www.emiratesnbd.com/en/campaigns/voyager-credit-cards', 'http://Trip.com', 'http://Trip.com', 'http://Trip.com', 'https://www.emiratesnbd.com/ar/campaigns/voyager-credit-cards']</t>
-        </is>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V21" t="n">
-        <v>636</v>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>Why settle for someone else’s highlights?
-Start your own journey with an Emirates NBD Voyager credit card. Apply today to get up to AED 700 in Trip.com vouchers.
-Access benefits like:
-- AED 300 Trip.com voucher with a new Emirates NBD Voyager World Credit Card
-- AED 700 Trip.com voucher with a new Emirates NBD Voyager World Elite Credit Card
-Offer is valid until 15 May 2026. Apply now.
-Terms and Conditions apply.
-Apply Now: emiratesnbd.com/en/campaigns…
-النص المرافق للمنشور:
-لماذا تكتفي بمشاهدة اللقطات المميزة للآخرين؟
-ابدأ رحلتك الخاصة مع بطاقة فويجر من بنك الإمارات دبي الوطني. قدّم طلبك اليوم لتحصل على قسائم من Trip.com بقيمة تصل إلى 700 درهم.
-استفد من المزايا التالية:
-- قسيمة Trip.com بقيمة 300 درهم مع بطاقة فويجر وورلد الائتمانية الجديدة من بنك الإمارات دبي الوطني
-- قسيمة Trip.com بقيمة 700 درهم مع بطاقة فويجر وورلد إيليت الائتمانية الجديدة من بنك الإمارات دبي الوطني
-يسري العرض حتى 15 مايو 2026. قدّم طلبك الآن.
-تطبّق الشروط والأحكام.
- تقدم بطلبك الآن: emiratesnbd.com/ar/campaigns…</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2049806904768045275</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Start your banking journey today with Emirates NBD.
+ابدأ رحلتك المصرفية اليوم مع بنك الإمارات دبي الوطني. https://t.co/tIpnLZ2ain</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>Why settle for someone else’s highlights?
-Start your own journey with an Emirates NBD Voyager credit card. Apply today to get up to AED 700 in Trip.com vouchers.
-Access benefits like:
-- AED 300 Trip.com voucher with a new Emirates NBD Voyager World Credit Card
-- AED 700 Trip.com voucher with a new Emirates NBD Voyager World Elite Credit Card
-Offer is valid until 15 May 2026. Apply now.
-Terms and Conditions apply.
-Apply Now: emiratesnbd.com/en/campaigns…
-النص المرافق للمنشور:
-لماذا تكتفي بمشاهدة اللقطات المميزة للآخرين؟
-ابدأ رحلتك الخاصة مع بطاقة فويجر من بنك الإمارات دبي الوطني. قدّم طلبك اليوم لتحصل على قسائم من Trip.com بقيمة تصل إلى 700 درهم.
-استفد من المزايا التالية:
-- قسيمة Trip.com بقيمة 300 درهم مع بطاقة فويجر وورلد الائتمانية الجديدة من بنك الإمارات دبي الوطني
-- قسيمة Trip.com بقيمة 700 درهم مع بطاقة فويجر وورلد إيليت الائتمانية الجديدة من بنك الإمارات دبي الوطني
-يسري العرض حتى 15 مايو 2026. قدّم طلبك الآن.
-تطبّق الشروط والأحكام.
- تقدم بطلبك الآن: emiratesnbd.com/ar/campaigns…</t>
+          <t>Start your banking journey today with Emirates NBD.
+ابدأ رحلتك المصرفية اليوم مع بنك الإمارات دبي الوطني. https://t.co/tIpnLZ2ain</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Why settle for someone else’s highlights? 
-Start your own journey with an Emirates NBD Voyager credit card. Apply today to get up to AED 700 in Trip.com vouchers. 
-Access benefits like: 
-- AED 300 Trip.com voucher with a new Emirates NBD Voyager World Credit Card 
-- AED 700 Trip.com voucher with a new Emirates NBD Voyager World Elite Credit Card 
-Offer is valid until 15 May 2026. Apply now. 
-Terms and Conditions apply. 
-Apply Now: emiratesnbd.com/en/campaigns…</t>
+          <t>Start your banking journey today with Emirates NBD.</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3847,7 +3895,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Apply today to get up to AED 700 in Trip.com vouchers. • Start your own journey with an Emirates NBD Voyager credit card. • Apply Now: emiratesnbd.com/en/campaigns…</t>
+          <t>Start your banking journey today with Emirates NBD.</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3901,7 +3949,7 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>@Universal_USDU @ADGlobalMarket @EmiratesNBD_AE @MashreqTweets @almaryahbank @aquanow This carries strong intent, open to meaningful engagement 👑</t>
+          <t>This carries strong intent, open to meaningful engagement 👑</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3955,19 +4003,11 @@
           <t>This carries strong intent, open to meaningful engagement 👑</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>https://x.com/apex_led/status/2049804951631900789</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>@Universal_USDU @ADGlobalMarket @EmiratesNBD_AE @MashreqTweets @almaryahbank @aquanow This carries strong intent, open to meaningful engagement 👑</t>
-        </is>
-      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>@Universal_USDU @ADGlobalMarket @EmiratesNBD_AE @MashreqTweets @almaryahbank @aquanow This carries strong intent, open to meaningful engagement 👑</t>
+          <t>This carries strong intent, open to meaningful engagement 👑</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -4057,9 +4097,7 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>للتفاصيل البسيطة في يومك وكل لحظة فيها
-حمّل تطبيق تستاهل لاكتشاف مكافآت حصرية باستخدام بطاقة الخصم إماراتي فيزا سيغنتشر الخاصة بك من بنك الإمارات دبي الوطني.
-https://t.co/S5JMIMnH7I https://t.co/hF7o7qZlTY</t>
+          <t>تطبيق "تستاهل" يقدّرنا وتفاصيله تدلعنا، وبطاقة الخصم إماراتي فيزا سيغنتشر فعلًا تفتح أبواب لمكافآت وخدمات استثنائية، كفو بنك الإمارات دبي الوطني على هالدلال.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -4113,28 +4151,16 @@
           <t>تطبيق "تستاهل" يقدّرنا وتفاصيله تدلعنا، وبطاقة الخصم إماراتي فيزا سيغنتشر فعلًا تفتح أبواب لمكافآت وخدمات استثنائية، كفو بنك الإمارات دبي الوطني على هالدلال.</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>https://x.com/BaraaNabilUAE/status/2049804711268610244</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>للتفاصيل البسيطة في يومك وكل لحظة فيها
-حمّل تطبيق تستاهل لاكتشاف مكافآت حصرية باستخدام بطاقة الخصم إماراتي فيزا سيغنتشر الخاصة بك من بنك الإمارات دبي الوطني.
-https://t.co/S5JMIMnH7I https://t.co/hF7o7qZlTY</t>
-        </is>
-      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>للتفاصيل البسيطة في يومك وكل لحظة فيها
-حمّل تطبيق تستاهل لاكتشاف مكافآت حصرية باستخدام بطاقة الخصم إماراتي فيزا سيغنتشر الخاصة بك من بنك الإمارات دبي الوطني.
-https://t.co/S5JMIMnH7I https://t.co/hF7o7qZlTY</t>
+          <t>تطبيق "تستاهل" يقدّرنا وتفاصيله تدلعنا، وبطاقة الخصم إماراتي فيزا سيغنتشر فعلًا تفتح أبواب لمكافآت وخدمات استثنائية، كفو بنك الإمارات دبي الوطني على هالدلال.</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>For the simple details in your day and every moment in it, download the Tastahel app to discover exclusive rewards using your Emirates NBD Visa Signature debit card.</t>
+          <t>The "Testahl" app appreciates us, and its details pamper us. The Emirati Visa Signature debit card truly opens doors to exceptional rewards and services. Kudos to Emirates NBD for this pampering.</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -4165,7 +4191,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>For the simple details in your day and every moment in it, download the Tastahel app to discover exclusive rewards using your Emirates NBD Visa Signature debit card.</t>
+          <t>The Emirati Visa Signature debit card truly opens doors to exceptional rewards and services. • The "Testahl" app appreciates us, and its details pamper us. • Kudos to Emirates NBD for this pampering.</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -4219,9 +4245,8 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Experience the future with Ray- Ban Meta Glasses.
-Apply for Emirates noon One Visa Credit Card and get a chance to win Ray-Ban Meta Sunglasses.
-Apply Now: https://t.co/vPejTs1z6k https://t.co/SgAX32aKRG</t>
+          <t>From pantry staples to farm-fresh picks, enjoy 10% off at Choithrams on spends of AED 50 and above with your Emirates NBD card.
+Learn More: emiratesnbd.com/en/promotion…</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -4277,30 +4302,17 @@
 Learn More: emiratesnbd.com/en/promotion…</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>https://x.com/ENBDdeals/status/2049802474387566693</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>Experience the future with Ray- Ban Meta Glasses.
-Apply for Emirates noon One Visa Credit Card and get a chance to win Ray-Ban Meta Sunglasses.
-Apply Now: https://t.co/vPejTs1z6k https://t.co/SgAX32aKRG</t>
-        </is>
-      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>Experience the future with Ray- Ban Meta Glasses.
-Apply for Emirates noon One Visa Credit Card and get a chance to win Ray-Ban Meta Sunglasses.
-Apply Now: https://t.co/vPejTs1z6k https://t.co/SgAX32aKRG</t>
+          <t>From pantry staples to farm-fresh picks, enjoy 10% off at Choithrams on spends of AED 50 and above with your Emirates NBD card.
+Learn More: emiratesnbd.com/en/promotion…</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Experience the future with Ray-Ban Meta Glasses. 
-Apply for the Emirates Noon One Visa Credit Card and get a chance to win Ray-Ban Meta Sunglasses. 
-Apply Now: https://t.co/vPejTs1z6k https://t.co/SgAX32aKRG</t>
+          <t>From pantry staples to farm-fresh picks, enjoy 10% off at Choithrams on purchases of AED 50 and above with your Emirates NBD card.</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -4331,7 +4343,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Apply for the Emirates Noon One Visa Credit Card and get a chance to win Ray-Ban Meta Sunglasses. • Apply Now: https://t.co/vPejTs1z6k https://t.co/SgAX32aKRG • Experience the future with Ray-Ban Meta Glasses.</t>
+          <t>From pantry staples to farm-fresh picks, enjoy 10% off at Choithrams on purchases of AED 50 and above with your Emirates NBD card.</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -4386,7 +4398,7 @@
       <c r="I25" t="inlineStr">
         <is>
           <t>Start your banking journey today with Emirates NBD.
-ابدأ رحلتك المصرفية اليوم مع بنك الإمارات دبي الوطني. https://t.co/tIpnLZ2ain</t>
+ابدأ رحلتك المصرفية اليوم مع بنك الإمارات دبي الوطني.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -4438,21 +4450,12 @@
 ابدأ رحلتك المصرفية اليوم مع بنك الإمارات دبي الوطني.</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2049799676367343838</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr">
         <is>
           <t>Start your banking journey today with Emirates NBD.
-ابدأ رحلتك المصرفية اليوم مع بنك الإمارات دبي الوطني. https://t.co/tIpnLZ2ain</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>Start your banking journey today with Emirates NBD.
-ابدأ رحلتك المصرفية اليوم مع بنك الإمارات دبي الوطني. https://t.co/tIpnLZ2ain</t>
+ابدأ رحلتك المصرفية اليوم مع بنك الإمارات دبي الوطني.</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -4542,7 +4545,7 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>India's markets regulator approves change of control at RBL Bank in Emirates NBD stake deal https://t.co/I1NP5RZdeq</t>
+          <t>India's markets regulator approves change of control at RBL Bank in Emirates NBD stake deal reuters.com/sustainability/b…</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -4596,19 +4599,11 @@
           <t>India's markets regulator approves change of control at RBL Bank in Emirates NBD stake deal reuters.com/sustainability/b…</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>https://x.com/ReutersAsia/status/2049798571990323555</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>India's markets regulator approves change of control at RBL Bank in Emirates NBD stake deal https://t.co/I1NP5RZdeq</t>
-        </is>
-      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>India's markets regulator approves change of control at RBL Bank in Emirates NBD stake deal https://t.co/I1NP5RZdeq</t>
+          <t>India's markets regulator approves change of control at RBL Bank in Emirates NBD stake deal reuters.com/sustainability/b…</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -4698,7 +4693,7 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>@Universal_USDU @ADGlobalMarket @EmiratesNBD_AE @MashreqTweets @almaryahbank @aquanow This project gives strong confidence vibes 💪📊</t>
+          <t>This project gives strong confidence vibes 💪📊</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4752,24 +4747,16 @@
           <t>This project gives strong confidence vibes 💪📊</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>https://x.com/T0m_Calls/status/2049797480003588407</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>@Universal_USDU @ADGlobalMarket @EmiratesNBD_AE @MashreqTweets @almaryahbank @aquanow This project gives strong confidence vibes 💪📊</t>
-        </is>
-      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>@Universal_USDU @ADGlobalMarket @EmiratesNBD_AE @MashreqTweets @almaryahbank @aquanow This project gives strong confidence vibes 💪📊</t>
+          <t>This project gives strong confidence vibes 💪📊</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>This project gives strong confidence vibes.</t>
+          <t>This project exudes strong confidence.</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4800,7 +4787,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>This project gives strong confidence vibes.</t>
+          <t>This project exudes strong confidence.</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -4856,7 +4843,7 @@
         <is>
           <t>Visa appoints Emirates NBD for local UAE Dirham settlements. 
 The move allows domestic card transactions to clear locally in dirhams rather than routing through international settlement networks.
-https://t.co/aSnsVTOcjD</t>
+fintechnews.ae/31474/payment…</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4914,23 +4901,13 @@
 fintechnews.ae/31474/payment…</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>https://x.com/__racha/status/2049796434447503575</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr">
         <is>
           <t>Visa appoints Emirates NBD for local UAE Dirham settlements. 
 The move allows domestic card transactions to clear locally in dirhams rather than routing through international settlement networks.
-https://t.co/aSnsVTOcjD</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>Visa appoints Emirates NBD for local UAE Dirham settlements. 
-The move allows domestic card transactions to clear locally in dirhams rather than routing through international settlement networks.
-https://t.co/aSnsVTOcjD</t>
+fintechnews.ae/31474/payment…</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -5021,8 +4998,8 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Mashreq and Cashew deepen their collaboration to build an embedded lending framework that blends regulated banking expertise with digital platform innovation across the MENA region.
-#MENA #UAE #Fintech #Banking #EmbeddedFinance #DigitalLending #Innovation #Partnership https://t.co/i4vg7CBB0B</t>
+          <t>Visa appoints Emirates NBD as its official National Net Settlement Service (NNSS) Agent in the UAE, strengthening the country’s digital payments and settlement infrastructure.
+#Visa #EmiratesNBD #UAE #Payments #Fintech #DigitalPayments #Banking #Innovation</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -5078,26 +5055,17 @@
 #Visa #EmiratesNBD #UAE #Payments #Fintech #DigitalPayments #Banking #Innovation</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>https://x.com/ForumRemittance/status/2049796315736084692</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>Mashreq and Cashew deepen their collaboration to build an embedded lending framework that blends regulated banking expertise with digital platform innovation across the MENA region.
-#MENA #UAE #Fintech #Banking #EmbeddedFinance #DigitalLending #Innovation #Partnership https://t.co/i4vg7CBB0B</t>
-        </is>
-      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>Mashreq and Cashew deepen their collaboration to build an embedded lending framework that blends regulated banking expertise with digital platform innovation across the MENA region.
-#MENA #UAE #Fintech #Banking #EmbeddedFinance #DigitalLending #Innovation #Partnership https://t.co/i4vg7CBB0B</t>
+          <t>Visa appoints Emirates NBD as its official National Net Settlement Service (NNSS) Agent in the UAE, strengthening the country’s digital payments and settlement infrastructure.
+#Visa #EmiratesNBD #UAE #Payments #Fintech #DigitalPayments #Banking #Innovation</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Mashreq and Cashew deepen their collaboration to build an embedded lending framework that combines regulated banking expertise with digital platform innovation across the MENA region.</t>
+          <t>Visa appoints Emirates NBD as its official National Net Settlement Service (NNSS) Agent in the UAE, strengthening the country’s digital payments and settlement infrastructure.</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -5107,7 +5075,7 @@
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE29" s="2" t="n">
@@ -5128,7 +5096,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Mashreq and Cashew deepen their collaboration to build an embedded lending framework that combines regulated banking expertise with digital platform innovation across the MENA region.</t>
+          <t>Visa appoints Emirates NBD as its official National Net Settlement Service (NNSS) Agent in the UAE, strengthening the country’s digital payments and settlement infrastructure.</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -5182,11 +5150,13 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Dubai records the world’s lowest electricity customer minutes lost at just 49 seconds per year
-@DEWAofficial
-#Dubai #Utilities #Electricity
-#MiddleEast
-https://t.co/NGMV8s8zn6 https://t.co/KY6IAkc9f1</t>
+          <t>#Sebi approves change of control at #RBL_Bank in #EmiratesNBD stake deal
+@RBLBank
+@EmiratesNBD_AE
+#India #Banking #Dubai
+#UAE #MiddleEast
+infoblaze.com/news/details/1…
+Via business-standard.com</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -5252,115 +5222,9 @@
 Via business-standard.com</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>https://x.com/infoblazeme/status/2049794079647826046</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>Dubai records the world’s lowest electricity customer minutes lost at just 49 seconds per year
-@DEWAofficial
-#Dubai #Utilities #Electricity
-#MiddleEast
-https://t.co/NGMV8s8zn6 https://t.co/KY6IAkc9f1</t>
-        </is>
-      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
-        <is>
-          <t>Dubai records the world’s lowest electricity customer minutes lost at just 49 seconds per year
-@DEWAofficial
-#Dubai #Utilities #Electricity
-#MiddleEast
-https://t.co/NGMV8s8zn6 https://t.co/KY6IAkc9f1</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>Dubai records the world’s lowest electricity customer minutes lost at just 49 seconds per year.</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE30" s="2" t="n">
-        <v>46142.59166666667</v>
-      </c>
-      <c r="AF30" s="2" t="n">
-        <v>46142</v>
-      </c>
-      <c r="AG30" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Dubai records the world’s lowest electricity customer minutes lost at just 49 seconds per year.</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK30" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL30" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2049793969677291575</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>https://x.com/letstalkdubai/status/2049793969677291575</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>https://x.com/letstalkdubai</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>letstalkdubai</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Let's Talk Dubai</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526561120164921344/W-lU0fbd_bigger.png</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
         <is>
           <t>#Sebi approves change of control at #RBL_Bank in #EmiratesNBD stake deal
 @RBLBank
@@ -5371,6 +5235,102 @@
 Via business-standard.com</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>Sebi approves the change of control at RBL Bank in the Emirates NBD stake deal.</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE30" s="2" t="n">
+        <v>46142.59166666667</v>
+      </c>
+      <c r="AF30" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Sebi approves the change of control at RBL Bank in the Emirates NBD stake deal.</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK30" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2049793969677291575</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://x.com/letstalkdubai/status/2049793969677291575</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://x.com/letstalkdubai</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>letstalkdubai</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Let's Talk Dubai</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526561120164921344/W-lU0fbd_bigger.png</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>#Sebi approves change of control at #RBL_Bank in #EmiratesNBD stake deal
+@RBLBank
+@EmiratesNBD_AE
+#India #Banking #Dubai
+#UAE #MiddleEast
+https://t.co/P8Ax5vNbhn
+Via https://t.co/xfccX701ON https://t.co/qf4uWzDcTz</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
           <t>&lt;a href="/search?f=tweets&amp;amp;q=%23Sebi"&gt;#Sebi&lt;/a&gt; approves change of control at &lt;a href="/search?f=tweets&amp;amp;q=%23RBL_Bank"&gt;#RBL_Bank&lt;/a&gt; in &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; stake deal
@@ -5434,17 +5394,31 @@
 Via business-standard.com</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="inlineStr">
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>https://x.com/letstalkdubai/status/2049793969677291575</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
         <is>
           <t>#Sebi approves change of control at #RBL_Bank in #EmiratesNBD stake deal
 @RBLBank
 @EmiratesNBD_AE
 #India #Banking #Dubai
 #UAE #MiddleEast
-infoblaze.com/news/details/1…
-Via business-standard.com</t>
+https://t.co/P8Ax5vNbhn
+Via https://t.co/xfccX701ON https://t.co/qf4uWzDcTz</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>#Sebi approves change of control at #RBL_Bank in #EmiratesNBD stake deal
+@RBLBank
+@EmiratesNBD_AE
+#India #Banking #Dubai
+#UAE #MiddleEast
+https://t.co/P8Ax5vNbhn
+Via https://t.co/xfccX701ON https://t.co/qf4uWzDcTz</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -5533,6 +5507,69 @@
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
+        <is>
+          <t>#Sebi approves change of control at #RBL_Bank in #EmiratesNBD stake deal 
+@RBLBank 
+@EmiratesNBD_AE 
+#India #Banking #Dubai
+#UAE #MiddleEast 
+https://t.co/5caG5iFvBn
+Via https://t.co/E6tc2Xk72c https://t.co/cZjuG5eIoY</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23Sebi"&gt;#Sebi&lt;/a&gt; approves change of control at &lt;a href="/search?f=tweets&amp;amp;q=%23RBL_Bank"&gt;#RBL_Bank&lt;/a&gt; in &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; stake deal 
+&lt;a href="/rblbank" title="RBL Bank"&gt;@RBLBank&lt;/a&gt; 
+&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; 
+&lt;a href="/search?f=tweets&amp;amp;q=%23India"&gt;#India&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Banking"&gt;#Banking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Dubai"&gt;#Dubai&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23MiddleEast"&gt;#MiddleEast&lt;/a&gt; 
+&lt;a href="http://infoblaze.com/news/details/117426"&gt;infoblaze.com/news/details/1…&lt;/a&gt;
+Via &lt;a href="http://business-standard.com"&gt;business-standard.com&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Apr 30, 2026 · 10:11 AM UTC</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>46142.42430555556</v>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23Sebi', 'https://x.com/search?f=tweets&amp;q=%23RBL_Bank', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/rblbank', 'https://x.com/EmiratesNBD_AE', 'https://x.com/search?f=tweets&amp;q=%23India', 'https://x.com/search?f=tweets&amp;q=%23Banking', 'https://x.com/search?f=tweets&amp;q=%23Dubai', 'https://x.com/search?f=tweets&amp;q=%23UAE', 'https://x.com/search?f=tweets&amp;q=%23MiddleEast', 'http://infoblaze.com/news/details/117426', 'http://business-standard.com']</t>
+        </is>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>29</v>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
         <is>
           <t>#Sebi approves change of control at #RBL_Bank in #EmiratesNBD stake deal 
 @RBLBank 
@@ -5543,71 +5580,22 @@
 Via business-standard.com</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23Sebi"&gt;#Sebi&lt;/a&gt; approves change of control at &lt;a href="/search?f=tweets&amp;amp;q=%23RBL_Bank"&gt;#RBL_Bank&lt;/a&gt; in &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; stake deal 
-&lt;a href="/rblbank" title="RBL Bank"&gt;@RBLBank&lt;/a&gt; 
-&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; 
-&lt;a href="/search?f=tweets&amp;amp;q=%23India"&gt;#India&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Banking"&gt;#Banking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Dubai"&gt;#Dubai&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23MiddleEast"&gt;#MiddleEast&lt;/a&gt; 
-&lt;a href="http://infoblaze.com/news/details/117426"&gt;infoblaze.com/news/details/1…&lt;/a&gt;
-Via &lt;a href="http://business-standard.com"&gt;business-standard.com&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K32" t="b">
-        <v>0</v>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>Apr 30, 2026 · 10:11 AM UTC</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="n">
-        <v>46142.42430555556</v>
-      </c>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23Sebi', 'https://x.com/search?f=tweets&amp;q=%23RBL_Bank', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/rblbank', 'https://x.com/EmiratesNBD_AE', 'https://x.com/search?f=tweets&amp;q=%23India', 'https://x.com/search?f=tweets&amp;q=%23Banking', 'https://x.com/search?f=tweets&amp;q=%23Dubai', 'https://x.com/search?f=tweets&amp;q=%23UAE', 'https://x.com/search?f=tweets&amp;q=%23MiddleEast', 'http://infoblaze.com/news/details/117426', 'http://business-standard.com']</t>
-        </is>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>29</v>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>https://x.com/InfoblazeINDIA/status/2049793884012830907</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
         <is>
           <t>#Sebi approves change of control at #RBL_Bank in #EmiratesNBD stake deal 
 @RBLBank 
 @EmiratesNBD_AE 
 #India #Banking #Dubai
 #UAE #MiddleEast 
-infoblaze.com/news/details/1…
-Via business-standard.com</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
+https://t.co/5caG5iFvBn
+Via https://t.co/E6tc2Xk72c https://t.co/cZjuG5eIoY</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>#Sebi approves change of control at #RBL_Bank in #EmiratesNBD stake deal 
@@ -5615,8 +5603,8 @@
 @EmiratesNBD_AE 
 #India #Banking #Dubai
 #UAE #MiddleEast 
-infoblaze.com/news/details/1…
-Via business-standard.com</t>
+https://t.co/5caG5iFvBn
+Via https://t.co/E6tc2Xk72c https://t.co/cZjuG5eIoY</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -5705,6 +5693,65 @@
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
+        <is>
+          <t>ویزا نے امارات این بی ڈی کو NNSS ایجنٹ مقرر کیا، جس سے لین دین مقامی AED میں مکمل ہوں گے۔
+#NNSS
+#UAE #Dubai #EmiratesNBD #NBD #Visa 
+@EmiratesNBD_AE
+@Visa https://t.co/87utaLSJAb</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>ویزا نے امارات این بی ڈی کو NNSS ایجنٹ مقرر کیا، جس سے لین دین مقامی AED میں مکمل ہوں گے۔
+&lt;a href="/search?f=tweets&amp;amp;q=%23NNSS"&gt;#NNSS&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Dubai"&gt;#Dubai&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23NBD"&gt;#NBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Visa"&gt;#Visa&lt;/a&gt; 
+&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;
+&lt;a href="/Visa" title="Visa"&gt;@Visa&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Apr 30, 2026 · 10:09 AM UTC</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="n">
+        <v>46142.42291666667</v>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23NNSS', 'https://x.com/search?f=tweets&amp;q=%23UAE', 'https://x.com/search?f=tweets&amp;q=%23Dubai', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23NBD', 'https://x.com/search?f=tweets&amp;q=%23Visa', 'https://x.com/EmiratesNBD_AE', 'https://x.com/Visa']</t>
+        </is>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>39</v>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
         <is>
           <t>ویزا نے امارات این بی ڈی کو NNSS ایجنٹ مقرر کیا، جس سے لین دین مقامی AED میں مکمل ہوں گے۔
 #NNSS
@@ -5713,74 +5760,27 @@
 @Visa</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>ویزا نے امارات این بی ڈی کو NNSS ایجنٹ مقرر کیا، جس سے لین دین مقامی AED میں مکمل ہوں گے۔
-&lt;a href="/search?f=tweets&amp;amp;q=%23NNSS"&gt;#NNSS&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Dubai"&gt;#Dubai&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23NBD"&gt;#NBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Visa"&gt;#Visa&lt;/a&gt; 
-&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;
-&lt;a href="/Visa" title="Visa"&gt;@Visa&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K33" t="b">
-        <v>0</v>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>Apr 30, 2026 · 10:09 AM UTC</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="n">
-        <v>46142.42291666667</v>
-      </c>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23NNSS', 'https://x.com/search?f=tweets&amp;q=%23UAE', 'https://x.com/search?f=tweets&amp;q=%23Dubai', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23NBD', 'https://x.com/search?f=tweets&amp;q=%23Visa', 'https://x.com/EmiratesNBD_AE', 'https://x.com/Visa']</t>
-        </is>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>39</v>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>https://x.com/ForsanUrdu/status/2049793228564480371</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
         <is>
           <t>ویزا نے امارات این بی ڈی کو NNSS ایجنٹ مقرر کیا، جس سے لین دین مقامی AED میں مکمل ہوں گے۔
 #NNSS
 #UAE #Dubai #EmiratesNBD #NBD #Visa 
 @EmiratesNBD_AE
-@Visa</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
+@Visa https://t.co/87utaLSJAb</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>ویزا نے امارات این بی ڈی کو NNSS ایجنٹ مقرر کیا، جس سے لین دین مقامی AED میں مکمل ہوں گے۔
 #NNSS
 #UAE #Dubai #EmiratesNBD #NBD #Visa 
 @EmiratesNBD_AE
-@Visa</t>
+@Visa https://t.co/87utaLSJAb</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE33" s="2" t="n">
@@ -5933,9 +5933,12 @@
 @Visa</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
-      <c r="AA34" t="inlineStr">
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>https://x.com/UAE_Forsan/status/2049790865460154569</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
         <is>
           <t>Visa, a world leader in digital payments, has appointed Emirates NBD as its official National Net Settlement Service (#NNSS) Agent in the UAE, allowing Visa’s domestic card transactions to be settled by Emirates NBD locally in UAE Dirhams (AED) in lieu of international settlement
 #UAE #Dubai #EmiratesNBD #NBD #Visa 
@@ -5943,6 +5946,14 @@
 @Visa</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>Visa, a world leader in digital payments, has appointed Emirates NBD as its official National Net Settlement Service (#NNSS) Agent in the UAE, allowing Visa’s domestic card transactions to be settled by Emirates NBD locally in UAE Dirhams (AED) in lieu of international settlement
+#UAE #Dubai #EmiratesNBD #NBD #Visa 
+@EmiratesNBD_AE 
+@Visa</t>
+        </is>
+      </c>
       <c r="AB34" t="inlineStr">
         <is>
           <t>Visa, a world leader in digital payments, has appointed Emirates NBD as its official National Net Settlement Service (#NNSS) Agent in the UAE, allowing Visa’s domestic card transactions to be settled by Emirates NBD locally in UAE Dirhams (AED) instead of through international settlement.</t>
@@ -6031,7 +6042,7 @@
       <c r="I35" t="inlineStr">
         <is>
           <t>Emirates NBD successfully prices a $750 million Additional Tier 1 (AT1) capital issuance, marking the first GCC debt capital markets transaction since late February 2026 and reinforcing investor confidence in the region’s banking sector.
-#EmiratesNBD #GCC #Banking #CapitalMarket</t>
+#EmiratesNBD #GCC #Banking #CapitalMarket https://t.co/4KQWxk0bOP</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -6087,12 +6098,21 @@
 #EmiratesNBD #GCC #Banking #CapitalMarket</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>https://x.com/ForumRemittance/status/2049788923015012684</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>Emirates NBD successfully prices a $750 million Additional Tier 1 (AT1) capital issuance, marking the first GCC debt capital markets transaction since late February 2026 and reinforcing investor confidence in the region’s banking sector.
+#EmiratesNBD #GCC #Banking #CapitalMarket https://t.co/4KQWxk0bOP</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>Emirates NBD successfully prices a $750 million Additional Tier 1 (AT1) capital issuance, marking the first GCC debt capital markets transaction since late February 2026 and reinforcing investor confidence in the region’s banking sector.
-#EmiratesNBD #GCC #Banking #CapitalMarket</t>
+#EmiratesNBD #GCC #Banking #CapitalMarket https://t.co/4KQWxk0bOP</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
@@ -6553,7 +6573,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>The Emirati Human Resources Development Council launches the Emirati Talent Empowerment Programme in Wealth Management and Financial Technology, in partnership with DIFC, EIF, and Emirates NBD.</t>
+          <t>The Emirati Human Resources Development Council launches the Emirati Talent Empowerment Programme in Wealth Management and Financial Technology, in partnership with DIFC, the EIF, and Emirates NBD.</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -6584,7 +6604,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>The Emirati Human Resources Development Council launches the Emirati Talent Empowerment Programme in Wealth Management and Financial Technology, in partnership with DIFC, EIF, and Emirates NBD.</t>
+          <t>The Emirati Human Resources Development Council launches the Emirati Talent Empowerment Programme in Wealth Management and Financial Technology, in partnership with DIFC, the EIF, and Emirates NBD.</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -6901,7 +6921,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>You lapdogs. STOP bribing corrupt leaders in Pakistan. Banks owned by the UAE in Pakistan: 1. Alfalah 2. Dubai Islamic 3. Mashreq 4. Emirates NBD 5. Emirates Global Islamic 6. First Women 7. Al Baraka 8. Ubank 9. EasyPaisa 10. Jazzcash 11. BML.</t>
+          <t>You lapdogs. STOP bribing corrupt leaders in Pakistan. Banks owned by the UAE in Pakistan: 1. Alfalah 2. Dubai Islamic 3. Mashreq 4. Emirates NBD 5. Emirates Global Islamic 6. First Women 7. Al Baraka 8. Ubank 9. EasyPaisa 10. Jazzcash 11. BML #Islamabad #Pakistan #UAE</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -6932,7 +6952,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Banks owned by the UAE in Pakistan: 1. • Emirates Global Islamic 6. • STOP bribing corrupt leaders in Pakistan.</t>
+          <t>Banks owned by the UAE in Pakistan: 1. • STOP bribing corrupt leaders in Pakistan. • BML #Islamabad #Pakistan #UAE</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
@@ -7693,7 +7713,7 @@
 Stock already in strong uptrend
 Now consolidating near resistance zone
 Breakout + strong hands backing = interesting setup 🔥
-#RBLBank #Banking #Stocks #Breakout https://t.co/QAjBOhRXXT</t>
+#RBLBank #Banking #Stocks #Breakout</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -7759,12 +7779,9 @@
 #RBLBank #Banking #Stocks #Breakout</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>https://x.com/TrendwithAvnash/status/2049759263707529446</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr">
         <is>
           <t>• SEBI nod received for Emirates NBD deal
 • Major change of control incoming (big trigger)
@@ -7772,18 +7789,7 @@
 Stock already in strong uptrend
 Now consolidating near resistance zone
 Breakout + strong hands backing = interesting setup 🔥
-#RBLBank #Banking #Stocks #Breakout https://t.co/QAjBOhRXXT</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>• SEBI nod received for Emirates NBD deal
-• Major change of control incoming (big trigger)
-📊 Chart view:
-Stock already in strong uptrend
-Now consolidating near resistance zone
-Breakout + strong hands backing = interesting setup 🔥
-#RBLBank #Banking #Stocks #Breakout https://t.co/QAjBOhRXXT</t>
+#RBLBank #Banking #Stocks #Breakout</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
@@ -7842,48 +7848,45 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2049758371734229151</t>
+          <t>2049754202373517793</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis/status/2049758371734229151</t>
+          <t>https://x.com/Di6111690294628/status/2049754202373517793</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis</t>
+          <t>https://x.com/Di6111690294628</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>STKgenghis</t>
+          <t>Di6111690294628</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>khana-b-dosh</t>
+          <t>Di</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1243248207293026305/b_s7UBzl_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1771339403266301952/e98W4Q7k_bigger.jpg</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Open an Emirates NBD Millionaire Account to be the next winner, with over 1,400 cash prizes worth AED 50,000,000.
-- Monthly prizes up to AED 1,000,000
-- Grand prizes up to AED 5,000,000
-Dedicated prizes for Emiratis, expats, and businesses 🇦🇪</t>
+          <t>السلام عليكم 
+كم نسبة التمويل العقاري</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>So once again routed to the &amp;#39;team&amp;#39;. 
-I will soon travel and will not be able to use my credit card through no fault of my own. 
-Why should a customer with a 40 year track record of no loans and good credit standing trust a bank that doesnt value the relationship?</t>
+          <t>السلام عليكم 
+كم نسبة التمويل العقاري</t>
         </is>
       </c>
       <c r="K46" t="b">
@@ -7892,7 +7895,7 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_AE']</t>
+          <t>['EmiratesNBD_KSA', 'cvcv32827179']</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -7902,11 +7905,11 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 · 7:50 AM UTC</t>
+          <t>Apr 30, 2026 · 7:34 AM UTC</t>
         </is>
       </c>
       <c r="P46" s="2" t="n">
-        <v>46142.32638888889</v>
+        <v>46142.31527777778</v>
       </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
@@ -7914,13 +7917,13 @@
         <v>1</v>
       </c>
       <c r="T46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>28</v>
+        <v>115</v>
       </c>
       <c r="W46" t="inlineStr">
         <is>
@@ -7929,38 +7932,21 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>So once again routed to the 'team'. 
-I will soon travel and will not be able to use my credit card through no fault of my own. 
-Why should a customer with a 40 year track record of no loans and good credit standing trust a bank that doesnt value the relationship?</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>https://x.com/STKgenghis/status/2049758371734229151</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>Open an Emirates NBD Millionaire Account to be the next winner, with over 1,400 cash prizes worth AED 50,000,000.
-- Monthly prizes up to AED 1,000,000
-- Grand prizes up to AED 5,000,000
-Dedicated prizes for Emiratis, expats, and businesses 🇦🇪</t>
-        </is>
-      </c>
+          <t>السلام عليكم 
+كم نسبة التمويل العقاري</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>Open an Emirates NBD Millionaire Account to be the next winner, with over 1,400 cash prizes worth AED 50,000,000.
-- Monthly prizes up to AED 1,000,000
-- Grand prizes up to AED 5,000,000
-Dedicated prizes for Emiratis, expats, and businesses 🇦🇪</t>
+          <t>السلام عليكم 
+كم نسبة التمويل العقاري</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>Open an Emirates NBD Millionaire Account to be the next winner, with over 1,400 cash prizes worth AED 50,000,000. 
-- Monthly prizes up to AED 1,000,000 
-- Grand prizes up to AED 5,000,000 
-Dedicated prizes for Emiratis, expats, and businesses.</t>
+          <t>Peace be upon you. What is the percentage of real estate financing?</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -7970,11 +7956,11 @@
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE46" s="2" t="n">
-        <v>46142.49305555555</v>
+        <v>46142.48194444444</v>
       </c>
       <c r="AF46" s="2" t="n">
         <v>46142</v>
@@ -7991,7 +7977,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>- Monthly prizes up to AED 1,000,000 - Grand prizes up to AED 5,000,000 Dedicated prizes for Emiratis, expats, and businesses. • Open an Emirates NBD Millionaire Account to be the next winner, with over 1,400 cash prizes worth AED 50,000,000.</t>
+          <t>What is the percentage of real estate financing?</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
@@ -8004,7 +7990,7 @@
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>EmiratesNBD_KSA, cvcv32827179</t>
         </is>
       </c>
     </row>
@@ -8014,76 +8000,71 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2049754202373517793</t>
+          <t>2049748153239253308</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://x.com/Di6111690294628/status/2049754202373517793</t>
+          <t>https://x.com/i_v_v_krishna/status/2049748153239253308</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://x.com/Di6111690294628</t>
+          <t>https://x.com/i_v_v_krishna</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Di6111690294628</t>
+          <t>i_v_v_krishna</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Di</t>
+          <t>Venkata Krishna</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1771339403266301952/e98W4Q7k_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1844766448989655044/kCqFDtmd_bigger.jpg</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA 
-السلام عليكم
-يعطيكم العافيه
-متى يتم تفعيل اضافة بطاقات بنك دبي الامارات في سامسونج باي في السعودية 
-وشكرا</t>
+          <t>SEBI greenlights change in control for RBL Bank, linked to Emirates NBD Bank's preferential equity investment. #RBLBank</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>السلام عليكم 
-كم نسبة التمويل العقاري</t>
+          <t>SEBI greenlights change in control for RBL Bank, linked to Emirates NBD Bank&amp;#39;s preferential equity investment. &lt;a href="/search?f=tweets&amp;amp;q=%23RBLBank"&gt;#RBLBank&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K47" t="b">
         <v>0</v>
       </c>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_KSA', 'cvcv32827179']</t>
-        </is>
-      </c>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 · 7:34 AM UTC</t>
+          <t>Apr 30, 2026 · 7:10 AM UTC</t>
         </is>
       </c>
       <c r="P47" s="2" t="n">
-        <v>46142.31527777778</v>
+        <v>46142.29861111111</v>
       </c>
       <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23RBLBank']</t>
+        </is>
+      </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
         <v>0</v>
@@ -8092,7 +8073,7 @@
         <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>115</v>
+        <v>46</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
@@ -8101,36 +8082,27 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>السلام عليكم 
-كم نسبة التمويل العقاري</t>
+          <t>SEBI greenlights change in control for RBL Bank, linked to Emirates NBD Bank's preferential equity investment. #RBLBank</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>https://x.com/Di6111690294628/status/2049754202373517793</t>
+          <t>https://x.com/i_v_v_krishna/status/2049748153239253308</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA 
-السلام عليكم
-يعطيكم العافيه
-متى يتم تفعيل اضافة بطاقات بنك دبي الامارات في سامسونج باي في السعودية 
-وشكرا</t>
+          <t>SEBI greenlights change in control for RBL Bank, linked to Emirates NBD Bank's preferential equity investment. #RBLBank</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA 
-السلام عليكم
-يعطيكم العافيه
-متى يتم تفعيل اضافة بطاقات بنك دبي الامارات في سامسونج باي في السعودية 
-وشكرا</t>
+          <t>SEBI greenlights change in control for RBL Bank, linked to Emirates NBD Bank's preferential equity investment. #RBLBank</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>Hello, peace be upon you. Thank you. When will the addition of Dubai Emirates Bank cards be activated in Samsung Pay in Saudi Arabia? Thank you.</t>
+          <t>SEBI approves the change in control for RBL Bank, associated with Emirates NBD Bank's preferential equity investment.</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -8144,7 +8116,7 @@
         </is>
       </c>
       <c r="AE47" s="2" t="n">
-        <v>46142.48194444444</v>
+        <v>46142.46527777778</v>
       </c>
       <c r="AF47" s="2" t="n">
         <v>46142</v>
@@ -8161,7 +8133,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>When will the addition of Dubai Emirates Bank cards be activated in Samsung Pay in Saudi Arabia? • Hello, peace be upon you.</t>
+          <t>SEBI approves the change in control for RBL Bank, associated with Emirates NBD Bank's preferential equity investment.</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -8174,7 +8146,7 @@
       </c>
       <c r="AL47" t="inlineStr">
         <is>
-          <t>EmiratesNBD_KSA, cvcv32827179</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8184,43 +8156,55 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2049748153239253308</t>
+          <t>2049745228039331992</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://x.com/i_v_v_krishna/status/2049748153239253308</t>
+          <t>https://x.com/FintechGate1/status/2049745228039331992</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://x.com/i_v_v_krishna</t>
+          <t>https://x.com/FintechGate1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>i_v_v_krishna</t>
+          <t>FintechGate1</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Venkata Krishna</t>
+          <t>FinTech Gate-بوابة التكنولوجيا المالية</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1844766448989655044/kCqFDtmd_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1630704388531470336/_2WZb_12_bigger.jpg</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>SEBI greenlights change in control for RBL Bank, linked to Emirates NBD Bank's preferential equity investment. #RBLBank</t>
+          <t>«فيزا» تعين «الإمارات دبي الوطني» وكيلاً رسمياً لخدمة التسوية الصافية الوطنية في «الإمارات»
+https://t.co/GrqbX1n7wi | التفاصيل 
+@Visa
+@EmiratesNBD_AE
+#fintech_gate
+#فيزا #الإمارات_دبي_الوطني
+#التسوية_الصافية_الوطنية #الإمارات https://t.co/lnb8tIyr0w</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>SEBI greenlights change in control for RBL Bank, linked to Emirates NBD Bank&amp;#39;s preferential equity investment. &lt;a href="/search?f=tweets&amp;amp;q=%23RBLBank"&gt;#RBLBank&lt;/a&gt;</t>
+          <t>«فيزا» تعين «الإمارات دبي الوطني» وكيلاً رسمياً لخدمة التسوية الصافية الوطنية في «الإمارات»
+&lt;a href="https://fintechgate.net/ptyq"&gt;fintechgate.net/ptyq&lt;/a&gt; | التفاصيل 
+&lt;a href="/Visa" title="Visa"&gt;@Visa&lt;/a&gt;
+&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23fintech_gate"&gt;#fintech_gate&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23فيزا"&gt;#فيزا&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_دبي_الوطني"&gt;#الإمارات_دبي_الوطني&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23التسوية_الصافية_الوطنية"&gt;#التسوية_الصافية_الوطنية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات"&gt;#الإمارات&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K48" t="b">
@@ -8235,16 +8219,16 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 · 7:10 AM UTC</t>
+          <t>Apr 30, 2026 · 6:58 AM UTC</t>
         </is>
       </c>
       <c r="P48" s="2" t="n">
-        <v>46142.29861111111</v>
+        <v>46142.29027777778</v>
       </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23RBLBank']</t>
+          <t>['https://fintechgate.net/ptyq', 'https://x.com/Visa', 'https://x.com/EmiratesNBD_AE', 'https://x.com/search?f=tweets&amp;q=%23fintech_gate', 'https://x.com/search?f=tweets&amp;q=%23فيزا', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_دبي_الوطني', 'https://x.com/search?f=tweets&amp;q=%23التسوية_الصافية_الوطنية', 'https://x.com/search?f=tweets&amp;q=%23الإمارات']</t>
         </is>
       </c>
       <c r="S48" t="n">
@@ -8257,7 +8241,7 @@
         <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
@@ -8265,103 +8249,6 @@
         </is>
       </c>
       <c r="X48" t="inlineStr">
-        <is>
-          <t>SEBI greenlights change in control for RBL Bank, linked to Emirates NBD Bank's preferential equity investment. #RBLBank</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr"/>
-      <c r="Z48" t="inlineStr"/>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>SEBI greenlights change in control for RBL Bank, linked to Emirates NBD Bank's preferential equity investment. #RBLBank</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>SEBI approves the change in control for RBL Bank, associated with Emirates NBD Bank's preferential equity investment.</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD48" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE48" s="2" t="n">
-        <v>46142.46527777778</v>
-      </c>
-      <c r="AF48" s="2" t="n">
-        <v>46142</v>
-      </c>
-      <c r="AG48" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>SEBI approves the change in control for RBL Bank, associated with Emirates NBD Bank's preferential equity investment.</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL48" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="n">
-        <v>47</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2049745228039331992</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>https://x.com/FintechGate1/status/2049745228039331992</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>https://x.com/FintechGate1</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>FintechGate1</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>FinTech Gate-بوابة التكنولوجيا المالية</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1630704388531470336/_2WZb_12_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr">
         <is>
           <t>«فيزا» تعين «الإمارات دبي الوطني» وكيلاً رسمياً لخدمة التسوية الصافية الوطنية في «الإمارات»
 fintechgate.net/ptyq | التفاصيل 
@@ -8372,168 +8259,119 @@
 #التسوية_الصافية_الوطنية #الإمارات</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>https://x.com/FintechGate1/status/2049745228039331992</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
         <is>
           <t>«فيزا» تعين «الإمارات دبي الوطني» وكيلاً رسمياً لخدمة التسوية الصافية الوطنية في «الإمارات»
-&lt;a href="https://fintechgate.net/ptyq"&gt;fintechgate.net/ptyq&lt;/a&gt; | التفاصيل 
-&lt;a href="/Visa" title="Visa"&gt;@Visa&lt;/a&gt;
-&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23fintech_gate"&gt;#fintech_gate&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23فيزا"&gt;#فيزا&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_دبي_الوطني"&gt;#الإمارات_دبي_الوطني&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23التسوية_الصافية_الوطنية"&gt;#التسوية_الصافية_الوطنية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات"&gt;#الإمارات&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K49" t="b">
-        <v>0</v>
-      </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>Apr 30, 2026 · 6:58 AM UTC</t>
-        </is>
-      </c>
-      <c r="P49" s="2" t="n">
-        <v>46142.29027777778</v>
-      </c>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>['https://fintechgate.net/ptyq', 'https://x.com/Visa', 'https://x.com/EmiratesNBD_AE', 'https://x.com/search?f=tweets&amp;q=%23fintech_gate', 'https://x.com/search?f=tweets&amp;q=%23فيزا', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_دبي_الوطني', 'https://x.com/search?f=tweets&amp;q=%23التسوية_الصافية_الوطنية', 'https://x.com/search?f=tweets&amp;q=%23الإمارات']</t>
-        </is>
-      </c>
-      <c r="S49" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" t="n">
-        <v>27</v>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>«فيزا» تعين «الإمارات دبي الوطني» وكيلاً رسمياً لخدمة التسوية الصافية الوطنية في «الإمارات»
-fintechgate.net/ptyq | التفاصيل 
+https://t.co/GrqbX1n7wi | التفاصيل 
 @Visa
 @EmiratesNBD_AE
 #fintech_gate
 #فيزا #الإمارات_دبي_الوطني
-#التسوية_الصافية_الوطنية #الإمارات</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr"/>
-      <c r="Z49" t="inlineStr"/>
-      <c r="AA49" t="inlineStr">
+#التسوية_الصافية_الوطنية #الإمارات https://t.co/lnb8tIyr0w</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
         <is>
           <t>«فيزا» تعين «الإمارات دبي الوطني» وكيلاً رسمياً لخدمة التسوية الصافية الوطنية في «الإمارات»
-fintechgate.net/ptyq | التفاصيل 
+https://t.co/GrqbX1n7wi | التفاصيل 
 @Visa
 @EmiratesNBD_AE
 #fintech_gate
 #فيزا #الإمارات_دبي_الوطني
-#التسوية_الصافية_الوطنية #الإمارات</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
+#التسوية_الصافية_الوطنية #الإمارات https://t.co/lnb8tIyr0w</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
         <is>
           <t>Visa appoints Emirates NBD as the official agent for the National Net Settlement Service in the UAE.</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
+      <c r="AC48" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="AD49" t="inlineStr">
+      <c r="AD48" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="AE49" s="2" t="n">
+      <c r="AE48" s="2" t="n">
         <v>46142.45694444444</v>
       </c>
-      <c r="AF49" s="2" t="n">
+      <c r="AF48" s="2" t="n">
         <v>46142</v>
       </c>
-      <c r="AG49" t="inlineStr">
+      <c r="AG48" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="AH49" t="inlineStr">
+      <c r="AH48" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AI49" t="inlineStr">
+      <c r="AI48" t="inlineStr">
         <is>
           <t>Visa appoints Emirates NBD as the official agent for the National Net Settlement Service in the UAE.</t>
         </is>
       </c>
-      <c r="AJ49" t="inlineStr">
+      <c r="AJ48" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AK49" t="n">
+      <c r="AK48" t="n">
         <v>2026</v>
       </c>
-      <c r="AL49" t="inlineStr">
+      <c r="AL48" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="1" t="n">
-        <v>48</v>
-      </c>
-      <c r="B50" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="inlineStr">
         <is>
           <t>2049741305845338378</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>https://x.com/CapitalInsight3/status/2049741305845338378</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>https://x.com/CapitalInsight3</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>CapitalInsight3</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>CapitalInsight</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/2002729415823036416/MHU6IO-8_bigger.jpg</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr">
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
         <is>
           <t>#RBLBank #Breaking
 ✅ SEBI approves change in control for Emirates NBD Bank’s preferential equity investment
@@ -8542,7 +8380,7 @@
 #RBLBank #BankingSector #SEBI</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>&lt;a href="/search?f=tweets&amp;amp;q=%23RBLBank"&gt;#RBLBank&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Breaking"&gt;#Breaking&lt;/a&gt;
 ✅ SEBI approves change in control for Emirates NBD Bank’s preferential equity investment
@@ -8551,48 +8389,48 @@
 &lt;a href="/search?f=tweets&amp;amp;q=%23RBLBank"&gt;#RBLBank&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23BankingSector"&gt;#BankingSector&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SEBI"&gt;#SEBI&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K50" t="b">
-        <v>0</v>
-      </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr">
+      <c r="K49" t="b">
+        <v>0</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
         <is>
           <t>20h</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>Apr 30, 2026 · 6:43 AM UTC</t>
         </is>
       </c>
-      <c r="P50" s="2" t="n">
+      <c r="P49" s="2" t="n">
         <v>46142.27986111111</v>
       </c>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr">
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr">
         <is>
           <t>['https://x.com/search?f=tweets&amp;q=%23RBLBank', 'https://x.com/search?f=tweets&amp;q=%23Breaking', 'https://x.com/search?f=tweets&amp;q=%23RBLBank', 'https://x.com/search?f=tweets&amp;q=%23BankingSector', 'https://x.com/search?f=tweets&amp;q=%23SEBI']</t>
         </is>
       </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" t="n">
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
         <v>1</v>
       </c>
-      <c r="V50" t="n">
+      <c r="V49" t="n">
         <v>91</v>
       </c>
-      <c r="W50" t="inlineStr">
+      <c r="W49" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>#RBLBank #Breaking
 ✅ SEBI approves change in control for Emirates NBD Bank’s preferential equity investment
@@ -8601,9 +8439,12 @@
 #RBLBank #BankingSector #SEBI</t>
         </is>
       </c>
-      <c r="Y50" t="inlineStr"/>
-      <c r="Z50" t="inlineStr"/>
-      <c r="AA50" t="inlineStr">
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>https://x.com/CapitalInsight3/status/2049741305845338378</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
         <is>
           <t>#RBLBank #Breaking
 ✅ SEBI approves change in control for Emirates NBD Bank’s preferential equity investment
@@ -8612,9 +8453,184 @@
 #RBLBank #BankingSector #SEBI</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>#RBLBank #Breaking
+✅ SEBI approves change in control for Emirates NBD Bank’s preferential equity investment
+✅ Key regulatory clearance received for proposed stake acquisition
+✅ Strengthens strategic partnership and capital position
+#RBLBank #BankingSector #SEBI</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>SEBI approves change in control for Emirates NBD Bank’s preferential equity investment. Key regulatory clearance received for proposed stake acquisition. Strengthens strategic partnership and capital position.</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AE49" s="2" t="n">
+        <v>46142.44652777778</v>
+      </c>
+      <c r="AF49" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>SEBI approves change in control for Emirates NBD Bank’s preferential equity investment. • Key regulatory clearance received for proposed stake acquisition. • Strengthens strategic partnership and capital position.</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK49" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL49" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2049739477845942383</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://x.com/mirabusinessfm/status/2049739477845942383</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://x.com/mirabusinessfm</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>mirabusinessfm</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Mira Business FM</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1899053705057517571/DRCaJqKX_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Emirates NBD raises $750M in strong bond deal. 💵📈
+Issue is over three times oversubscribed, showing strong investor confidence.
+#UAE #Banking #Markets #MiraBusinessFM 🎙️</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Emirates NBD raises $750M in strong bond deal. 💵📈
+Issue is over three times oversubscribed, showing strong investor confidence.
+&lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Banking"&gt;#Banking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Markets"&gt;#Markets&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23MiraBusinessFM"&gt;#MiraBusinessFM&lt;/a&gt; 🎙️</t>
+        </is>
+      </c>
+      <c r="K50" t="b">
+        <v>0</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Apr 30, 2026 · 6:35 AM UTC</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="n">
+        <v>46142.27430555555</v>
+      </c>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23UAE', 'https://x.com/search?f=tweets&amp;q=%23Banking', 'https://x.com/search?f=tweets&amp;q=%23Markets', 'https://x.com/search?f=tweets&amp;q=%23MiraBusinessFM']</t>
+        </is>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>8</v>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Emirates NBD raises $750M in strong bond deal. 💵📈
+Issue is over three times oversubscribed, showing strong investor confidence.
+#UAE #Banking #Markets #MiraBusinessFM 🎙️</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>https://x.com/mirabusinessfm/status/2049739477845942383</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>Emirates NBD raises $750M in strong bond deal. 💵📈
+Issue is over three times oversubscribed, showing strong investor confidence.
+#UAE #Banking #Markets #MiraBusinessFM 🎙️</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>Emirates NBD raises $750M in strong bond deal. 💵📈
+Issue is over three times oversubscribed, showing strong investor confidence.
+#UAE #Banking #Markets #MiraBusinessFM 🎙️</t>
+        </is>
+      </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>SEBI approves change in control for Emirates NBD Bank’s preferential equity investment. Key regulatory clearance received for proposed stake acquisition. Strengthens strategic partnership and capital position.</t>
+          <t>Emirates NBD raises $750M in a strong bond deal. The issue is over three times oversubscribed, showing strong investor confidence.</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -8628,7 +8644,7 @@
         </is>
       </c>
       <c r="AE50" s="2" t="n">
-        <v>46142.44652777778</v>
+        <v>46142.44097222222</v>
       </c>
       <c r="AF50" s="2" t="n">
         <v>46142</v>
@@ -8645,7 +8661,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>SEBI approves change in control for Emirates NBD Bank’s preferential equity investment. • Key regulatory clearance received for proposed stake acquisition. • Strengthens strategic partnership and capital position.</t>
+          <t>Emirates NBD raises $750M in a strong bond deal. • The issue is over three times oversubscribed, showing strong investor confidence.</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -8668,47 +8684,43 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2049739477845942383</t>
+          <t>2049738442230362395</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://x.com/mirabusinessfm/status/2049739477845942383</t>
+          <t>https://x.com/InvestmentDunia/status/2049738442230362395</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://x.com/mirabusinessfm</t>
+          <t>https://x.com/InvestmentDunia</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>mirabusinessfm</t>
+          <t>InvestmentDunia</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mira Business FM</t>
+          <t>Investment Dunia™</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1899053705057517571/DRCaJqKX_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2037166533034774528/zl9oJGJm_bigger.jpg</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Emirates NBD raises $750M in strong bond deal. 💵📈
-Issue is over three times oversubscribed, showing strong investor confidence.
-#UAE #Banking #Markets #MiraBusinessFM 🎙️</t>
+          <t>RBL BANK LIMITED: SEBI APPROVES CHANGE IN CONTROL FOR EMIRATES NBD BANK'S PREFERENTIAL EQUITY INVESTMENT</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Emirates NBD raises $750M in strong bond deal. 💵📈
-Issue is over three times oversubscribed, showing strong investor confidence.
-&lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Banking"&gt;#Banking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Markets"&gt;#Markets&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23MiraBusinessFM"&gt;#MiraBusinessFM&lt;/a&gt; 🎙️</t>
+          <t>RBL BANK LIMITED: SEBI APPROVES CHANGE IN CONTROL FOR EMIRATES NBD BANK&amp;#39;S PREFERENTIAL EQUITY INVESTMENT</t>
         </is>
       </c>
       <c r="K51" t="b">
@@ -8723,18 +8735,14 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 · 6:35 AM UTC</t>
+          <t>Apr 30, 2026 · 6:31 AM UTC</t>
         </is>
       </c>
       <c r="P51" s="2" t="n">
-        <v>46142.27430555555</v>
+        <v>46142.27152777778</v>
       </c>
       <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23UAE', 'https://x.com/search?f=tweets&amp;q=%23Banking', 'https://x.com/search?f=tweets&amp;q=%23Markets', 'https://x.com/search?f=tweets&amp;q=%23MiraBusinessFM']</t>
-        </is>
-      </c>
+      <c r="R51" t="inlineStr"/>
       <c r="S51" t="n">
         <v>0</v>
       </c>
@@ -8745,7 +8753,7 @@
         <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
@@ -8754,23 +8762,27 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Emirates NBD raises $750M in strong bond deal. 💵📈
-Issue is over three times oversubscribed, showing strong investor confidence.
-#UAE #Banking #Markets #MiraBusinessFM 🎙️</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr"/>
-      <c r="Z51" t="inlineStr"/>
+          <t>RBL BANK LIMITED: SEBI APPROVES CHANGE IN CONTROL FOR EMIRATES NBD BANK'S PREFERENTIAL EQUITY INVESTMENT</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>https://x.com/InvestmentDunia/status/2049738442230362395</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>RBL BANK LIMITED: SEBI APPROVES CHANGE IN CONTROL FOR EMIRATES NBD BANK'S PREFERENTIAL EQUITY INVESTMENT</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>Emirates NBD raises $750M in strong bond deal. 💵📈
-Issue is over three times oversubscribed, showing strong investor confidence.
-#UAE #Banking #Markets #MiraBusinessFM 🎙️</t>
+          <t>RBL BANK LIMITED: SEBI APPROVES CHANGE IN CONTROL FOR EMIRATES NBD BANK'S PREFERENTIAL EQUITY INVESTMENT</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>Emirates NBD raises $750M in a strong bond deal. The issue is over three times oversubscribed, showing strong investor confidence.</t>
+          <t>RBL BANK LIMITED: SEBI APPROVES CHANGE IN CONTROL FOR EMIRATES NBD BANK'S PREFERENTIAL EQUITY INVESTMENT</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -8780,11 +8792,11 @@
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE51" s="2" t="n">
-        <v>46142.44097222222</v>
+        <v>46142.43819444445</v>
       </c>
       <c r="AF51" s="2" t="n">
         <v>46142</v>
@@ -8801,7 +8813,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Emirates NBD raises $750M in a strong bond deal. • The issue is over three times oversubscribed, showing strong investor confidence.</t>
+          <t>RBL BANK LIMITED: SEBI APPROVES CHANGE IN CONTROL FOR EMIRATES NBD BANK'S PREFERENTIAL EQUITY INVESTMENT</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
@@ -8824,43 +8836,45 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2049738442230362395</t>
+          <t>2049737832798081056</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://x.com/InvestmentDunia/status/2049738442230362395</t>
+          <t>https://x.com/RuchirPurohit/status/2049737832798081056</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://x.com/InvestmentDunia</t>
+          <t>https://x.com/RuchirPurohit</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>InvestmentDunia</t>
+          <t>RuchirPurohit</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Investment Dunia™</t>
+          <t>Ruchir Purohit</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2037166533034774528/zl9oJGJm_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2025127726013968384/EgluwC1Y_bigger.jpg</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>RBL BANK LIMITED: SEBI APPROVES CHANGE IN CONTROL FOR EMIRATES NBD BANK'S PREFERENTIAL EQUITY INVESTMENT</t>
+          <t>Thanks @EmiratesNBD_AE for prioritizing customer privacy.
+WhatsApp,like other META products, doesn’t respect customer data privacy.</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>RBL BANK LIMITED: SEBI APPROVES CHANGE IN CONTROL FOR EMIRATES NBD BANK&amp;#39;S PREFERENTIAL EQUITY INVESTMENT</t>
+          <t>Thanks &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; for prioritizing customer privacy.
+WhatsApp,like other META products, doesn’t respect customer data privacy.</t>
         </is>
       </c>
       <c r="K52" t="b">
@@ -8870,19 +8884,23 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 · 6:31 AM UTC</t>
+          <t>Apr 30, 2026 · 6:29 AM UTC</t>
         </is>
       </c>
       <c r="P52" s="2" t="n">
-        <v>46142.27152777778</v>
+        <v>46142.27013888889</v>
       </c>
       <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="S52" t="n">
         <v>0</v>
       </c>
@@ -8893,7 +8911,7 @@
         <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
@@ -8902,19 +8920,21 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>RBL BANK LIMITED: SEBI APPROVES CHANGE IN CONTROL FOR EMIRATES NBD BANK'S PREFERENTIAL EQUITY INVESTMENT</t>
+          <t>Thanks @EmiratesNBD_AE for prioritizing customer privacy.
+WhatsApp,like other META products, doesn’t respect customer data privacy.</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>RBL BANK LIMITED: SEBI APPROVES CHANGE IN CONTROL FOR EMIRATES NBD BANK'S PREFERENTIAL EQUITY INVESTMENT</t>
+          <t>Thanks @EmiratesNBD_AE for prioritizing customer privacy.
+WhatsApp,like other META products, doesn’t respect customer data privacy.</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>RBL BANK LIMITED: SEBI APPROVES CHANGE IN CONTROL FOR EMIRATES NBD BANK'S PREFERENTIAL EQUITY INVESTMENT</t>
+          <t>Thanks @EmiratesNBD_AE for prioritizing customer privacy. WhatsApp, like other META products, doesn’t respect customer data privacy.</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -8928,7 +8948,7 @@
         </is>
       </c>
       <c r="AE52" s="2" t="n">
-        <v>46142.43819444445</v>
+        <v>46142.43680555555</v>
       </c>
       <c r="AF52" s="2" t="n">
         <v>46142</v>
@@ -8945,7 +8965,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>RBL BANK LIMITED: SEBI APPROVES CHANGE IN CONTROL FOR EMIRATES NBD BANK'S PREFERENTIAL EQUITY INVESTMENT</t>
+          <t>WhatsApp, like other META products, doesn’t respect customer data privacy. • Thanks @EmiratesNBD_AE for prioritizing customer privacy.</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
@@ -8968,188 +8988,36 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2049737832798081056</t>
+          <t>2049736445594886612</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://x.com/RuchirPurohit/status/2049737832798081056</t>
+          <t>https://x.com/Sharemarketinf/status/2049736445594886612</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://x.com/RuchirPurohit</t>
+          <t>https://x.com/Sharemarketinf</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RuchirPurohit</t>
+          <t>Sharemarketinf</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ruchir Purohit</t>
+          <t>ShareMarket InfoMania</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2025127726013968384/EgluwC1Y_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1962784190417850368/uD4cHYmj_bigger.jpg</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
-        <is>
-          <t>Thanks @EmiratesNBD_AE for prioritizing customer privacy.
-WhatsApp,like other META products, doesn’t respect customer data privacy.</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>Thanks &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; for prioritizing customer privacy.
-WhatsApp,like other META products, doesn’t respect customer data privacy.</t>
-        </is>
-      </c>
-      <c r="K53" t="b">
-        <v>0</v>
-      </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>Apr 30, 2026 · 6:29 AM UTC</t>
-        </is>
-      </c>
-      <c r="P53" s="2" t="n">
-        <v>46142.27013888889</v>
-      </c>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" t="n">
-        <v>8</v>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>Thanks @EmiratesNBD_AE for prioritizing customer privacy.
-WhatsApp,like other META products, doesn’t respect customer data privacy.</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr"/>
-      <c r="Z53" t="inlineStr"/>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>Thanks @EmiratesNBD_AE for prioritizing customer privacy.
-WhatsApp,like other META products, doesn’t respect customer data privacy.</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>Thanks Emirates NBD for prioritizing customer privacy. WhatsApp, like other META products, doesn’t respect customer data privacy.</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD53" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE53" s="2" t="n">
-        <v>46142.43680555555</v>
-      </c>
-      <c r="AF53" s="2" t="n">
-        <v>46142</v>
-      </c>
-      <c r="AG53" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>WhatsApp, like other META products, doesn’t respect customer data privacy. • Thanks Emirates NBD for prioritizing customer privacy.</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK53" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL53" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="n">
-        <v>52</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2049736445594886612</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>https://x.com/Sharemarketinf/status/2049736445594886612</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>https://x.com/Sharemarketinf</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Sharemarketinf</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>ShareMarket InfoMania</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1962784190417850368/uD4cHYmj_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr">
         <is>
           <t>RBL Bank Limited Update 🏦
 • SEBI approves change in control
@@ -9158,7 +9026,7 @@
 #RBLBank #EmiratesNBD #Banking #SEBI #CapitalRaise #IndianMarkets</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>RBL Bank Limited Update 🏦
 • SEBI approves change in control
@@ -9167,48 +9035,48 @@
 &lt;a href="/search?f=tweets&amp;amp;q=%23RBLBank"&gt;#RBLBank&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Banking"&gt;#Banking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SEBI"&gt;#SEBI&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23CapitalRaise"&gt;#CapitalRaise&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23IndianMarkets"&gt;#IndianMarkets&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K54" t="b">
-        <v>0</v>
-      </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr">
+      <c r="K53" t="b">
+        <v>0</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
         <is>
           <t>21h</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>Apr 30, 2026 · 6:23 AM UTC</t>
         </is>
       </c>
-      <c r="P54" s="2" t="n">
+      <c r="P53" s="2" t="n">
         <v>46142.26597222222</v>
       </c>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr">
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr">
         <is>
           <t>['https://x.com/search?f=tweets&amp;q=%23RBLBank', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23Banking', 'https://x.com/search?f=tweets&amp;q=%23SEBI', 'https://x.com/search?f=tweets&amp;q=%23CapitalRaise', 'https://x.com/search?f=tweets&amp;q=%23IndianMarkets']</t>
         </is>
       </c>
-      <c r="S54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V54" t="n">
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
         <v>116</v>
       </c>
-      <c r="W54" t="inlineStr">
+      <c r="W53" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>RBL Bank Limited Update 🏦
 • SEBI approves change in control
@@ -9217,9 +9085,9 @@
 #RBLBank #EmiratesNBD #Banking #SEBI #CapitalRaise #IndianMarkets</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr"/>
-      <c r="Z54" t="inlineStr"/>
-      <c r="AA54" t="inlineStr">
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr">
         <is>
           <t>RBL Bank Limited Update 🏦
 • SEBI approves change in control
@@ -9228,7 +9096,7 @@
 #RBLBank #EmiratesNBD #Banking #SEBI #CapitalRaise #IndianMarkets</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
+      <c r="AB53" t="inlineStr">
         <is>
           <t>RBL Bank Limited Update
 • SEBI approves change in control
@@ -9236,6 +9104,150 @@
 Regulatory clearance marks a key step for the proposed stake infusion, strengthening capital base and strategic backing.</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE53" s="2" t="n">
+        <v>46142.43263888889</v>
+      </c>
+      <c r="AF53" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>RBL Bank Limited Update • SEBI approves change in control • Linked to preferential equity investment by Emirates NBD Ban…</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK53" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL53" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2049735568989532292</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://x.com/REDBOXINDIA/status/2049735568989532292</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://x.com/REDBOXINDIA</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>REDBOXINDIA</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>RedboxGlobal India</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1140541977672474624/zVreIDF1_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>RBL BANK LIMITED: SEBI APPROVES CHANGE IN CONTROL FOR EMIRATES NBD BANK'S PREFERENTIAL EQUITY INVESTMENT</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>RBL BANK LIMITED: SEBI APPROVES CHANGE IN CONTROL FOR EMIRATES NBD BANK&amp;#39;S PREFERENTIAL EQUITY INVESTMENT</t>
+        </is>
+      </c>
+      <c r="K54" t="b">
+        <v>0</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Apr 30, 2026 · 6:20 AM UTC</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="n">
+        <v>46142.26388888889</v>
+      </c>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>62</v>
+      </c>
+      <c r="V54" t="n">
+        <v>9549</v>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>RBL BANK LIMITED: SEBI APPROVES CHANGE IN CONTROL FOR EMIRATES NBD BANK'S PREFERENTIAL EQUITY INVESTMENT</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>RBL BANK LIMITED: SEBI APPROVES CHANGE IN CONTROL FOR EMIRATES NBD BANK'S PREFERENTIAL EQUITY INVESTMENT</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>RBL BANK LIMITED: SEBI APPROVES CHANGE IN CONTROL FOR EMIRATES NBD BANK'S PREFERENTIAL EQUITY INVESTMENT</t>
+        </is>
+      </c>
       <c r="AC54" t="inlineStr">
         <is>
           <t>Cust</t>
@@ -9247,7 +9259,7 @@
         </is>
       </c>
       <c r="AE54" s="2" t="n">
-        <v>46142.43263888889</v>
+        <v>46142.43055555555</v>
       </c>
       <c r="AF54" s="2" t="n">
         <v>46142</v>
@@ -9264,7 +9276,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>RBL Bank Limited Update • SEBI approves change in control • Linked to preferential equity investment by Emirates NBD Ban…</t>
+          <t>RBL BANK LIMITED: SEBI APPROVES CHANGE IN CONTROL FOR EMIRATES NBD BANK'S PREFERENTIAL EQUITY INVESTMENT</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
@@ -9287,43 +9299,49 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2049735568989532292</t>
+          <t>2049735062812496323</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://x.com/REDBOXINDIA/status/2049735568989532292</t>
+          <t>https://x.com/wegro_app/status/2049735062812496323</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://x.com/REDBOXINDIA</t>
+          <t>https://x.com/wegro_app</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>REDBOXINDIA</t>
+          <t>wegro_app</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>RedboxGlobal India</t>
+          <t>Wegro App</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1140541977672474624/zVreIDF1_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1793658188497117184/T9pfyA67_bigger.jpg</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>RBL BANK LIMITED: SEBI APPROVES CHANGE IN CONTROL FOR EMIRATES NBD BANK'S PREFERENTIAL EQUITY INVESTMENT</t>
+          <t>RBL Bank announced that SEBI has granted prior approval for a change in control pursuant to the proposed investment by Emirates NBD Bank via preferential issue of equity shares. This is a continuation of the disclosure dated Oct 18, 2025. The transaction is still subject to other regulatory approvals &amp; customary conditions. 🏦
+📊 RBL BANK LTD | 🏷️ General
+🌐 Details: wegro.app/XnwlpK
+⚡️Instant stock alerts on WhatsApp - Try FREE 👉 wegro.app/go</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>RBL BANK LIMITED: SEBI APPROVES CHANGE IN CONTROL FOR EMIRATES NBD BANK&amp;#39;S PREFERENTIAL EQUITY INVESTMENT</t>
+          <t>RBL Bank announced that SEBI has granted prior approval for a change in control pursuant to the proposed investment by Emirates NBD Bank via preferential issue of equity shares. This is a continuation of the disclosure dated Oct 18, 2025. The transaction is still subject to other regulatory approvals &amp;amp; customary conditions. 🏦
+📊 RBL BANK LTD | 🏷️ General
+🌐 Details: &lt;a href="https://www.wegro.app/XnwlpK"&gt;wegro.app/XnwlpK&lt;/a&gt;
+⚡️Instant stock alerts on WhatsApp - Try FREE 👉 &lt;a href="https://www.wegro.app/go"&gt;wegro.app/go&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K55" t="b">
@@ -9338,25 +9356,29 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 · 6:20 AM UTC</t>
+          <t>Apr 30, 2026 · 6:18 AM UTC</t>
         </is>
       </c>
       <c r="P55" s="2" t="n">
-        <v>46142.26388888889</v>
+        <v>46142.2625</v>
       </c>
       <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>['https://www.wegro.app/XnwlpK', 'https://www.wegro.app/go']</t>
+        </is>
+      </c>
       <c r="S55" t="n">
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>9549</v>
+        <v>73</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
@@ -9365,19 +9387,25 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>RBL BANK LIMITED: SEBI APPROVES CHANGE IN CONTROL FOR EMIRATES NBD BANK'S PREFERENTIAL EQUITY INVESTMENT</t>
+          <t>RBL Bank announced that SEBI has granted prior approval for a change in control pursuant to the proposed investment by Emirates NBD Bank via preferential issue of equity shares. This is a continuation of the disclosure dated Oct 18, 2025. The transaction is still subject to other regulatory approvals &amp; customary conditions. 🏦
+📊 RBL BANK LTD | 🏷️ General
+🌐 Details: wegro.app/XnwlpK
+⚡️Instant stock alerts on WhatsApp - Try FREE 👉 wegro.app/go</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>RBL BANK LIMITED: SEBI APPROVES CHANGE IN CONTROL FOR EMIRATES NBD BANK'S PREFERENTIAL EQUITY INVESTMENT</t>
+          <t>RBL Bank announced that SEBI has granted prior approval for a change in control pursuant to the proposed investment by Emirates NBD Bank via preferential issue of equity shares. This is a continuation of the disclosure dated Oct 18, 2025. The transaction is still subject to other regulatory approvals &amp; customary conditions. 🏦
+📊 RBL BANK LTD | 🏷️ General
+🌐 Details: wegro.app/XnwlpK
+⚡️Instant stock alerts on WhatsApp - Try FREE 👉 wegro.app/go</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>RBL BANK LIMITED: SEBI APPROVES CHANGE IN CONTROL FOR EMIRATES NBD BANK'S PREFERENTIAL EQUITY INVESTMENT</t>
+          <t>RBL Bank announced that SEBI has granted prior approval for a change in control pursuant to the proposed investment by Emirates NBD Bank via preferential issue of equity shares. This is a continuation of the disclosure dated Oct 18, 2025. The transaction is still subject to other regulatory approvals and customary conditions.</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -9391,7 +9419,7 @@
         </is>
       </c>
       <c r="AE55" s="2" t="n">
-        <v>46142.43055555555</v>
+        <v>46142.42916666667</v>
       </c>
       <c r="AF55" s="2" t="n">
         <v>46142</v>
@@ -9408,7 +9436,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>RBL BANK LIMITED: SEBI APPROVES CHANGE IN CONTROL FOR EMIRATES NBD BANK'S PREFERENTIAL EQUITY INVESTMENT</t>
+          <t>RBL Bank announced that SEBI has granted prior approval for a change in control pursuant to the proposed investment by Emirates NBD Bank via preferential issue of equity shares. • This is a continuation of the disclosure dated Oct 18, 2025. • The transaction is still subject to other regulatory approvals and customary conditions.</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
@@ -9431,196 +9459,36 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2049735062812496323</t>
+          <t>2049735038691160351</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://x.com/wegro_app/status/2049735062812496323</t>
+          <t>https://x.com/speedystox/status/2049735038691160351</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://x.com/wegro_app</t>
+          <t>https://x.com/speedystox</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>wegro_app</t>
+          <t>speedystox</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Wegro App</t>
+          <t>Speedy Stox</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1793658188497117184/T9pfyA67_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2038007871141765120/Kceaen5L_bigger.jpg</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
-        <is>
-          <t>RBL Bank announced that SEBI has granted prior approval for a change in control pursuant to the proposed investment by Emirates NBD Bank via preferential issue of equity shares. This is a continuation of the disclosure dated Oct 18, 2025. The transaction is still subject to other regulatory approvals &amp; customary conditions. 🏦
-📊 RBL BANK LTD | 🏷️ General
-🌐 Details: wegro.app/XnwlpK
-⚡️Instant stock alerts on WhatsApp - Try FREE 👉 wegro.app/go</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>RBL Bank announced that SEBI has granted prior approval for a change in control pursuant to the proposed investment by Emirates NBD Bank via preferential issue of equity shares. This is a continuation of the disclosure dated Oct 18, 2025. The transaction is still subject to other regulatory approvals &amp;amp; customary conditions. 🏦
-📊 RBL BANK LTD | 🏷️ General
-🌐 Details: &lt;a href="https://www.wegro.app/XnwlpK"&gt;wegro.app/XnwlpK&lt;/a&gt;
-⚡️Instant stock alerts on WhatsApp - Try FREE 👉 &lt;a href="https://www.wegro.app/go"&gt;wegro.app/go&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K56" t="b">
-        <v>0</v>
-      </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>Apr 30, 2026 · 6:18 AM UTC</t>
-        </is>
-      </c>
-      <c r="P56" s="2" t="n">
-        <v>46142.2625</v>
-      </c>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>['https://www.wegro.app/XnwlpK', 'https://www.wegro.app/go']</t>
-        </is>
-      </c>
-      <c r="S56" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" t="n">
-        <v>73</v>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>RBL Bank announced that SEBI has granted prior approval for a change in control pursuant to the proposed investment by Emirates NBD Bank via preferential issue of equity shares. This is a continuation of the disclosure dated Oct 18, 2025. The transaction is still subject to other regulatory approvals &amp; customary conditions. 🏦
-📊 RBL BANK LTD | 🏷️ General
-🌐 Details: wegro.app/XnwlpK
-⚡️Instant stock alerts on WhatsApp - Try FREE 👉 wegro.app/go</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr"/>
-      <c r="Z56" t="inlineStr"/>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>RBL Bank announced that SEBI has granted prior approval for a change in control pursuant to the proposed investment by Emirates NBD Bank via preferential issue of equity shares. This is a continuation of the disclosure dated Oct 18, 2025. The transaction is still subject to other regulatory approvals &amp; customary conditions. 🏦
-📊 RBL BANK LTD | 🏷️ General
-🌐 Details: wegro.app/XnwlpK
-⚡️Instant stock alerts on WhatsApp - Try FREE 👉 wegro.app/go</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>RBL Bank announced that SEBI has granted prior approval for a change in control pursuant to the proposed investment by Emirates NBD Bank via preferential issue of equity shares. This is a continuation of the disclosure dated Oct 18, 2025. The transaction is still subject to other regulatory approvals and customary conditions.</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD56" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE56" s="2" t="n">
-        <v>46142.42916666667</v>
-      </c>
-      <c r="AF56" s="2" t="n">
-        <v>46142</v>
-      </c>
-      <c r="AG56" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>RBL Bank announced that SEBI has granted prior approval for a change in control pursuant to the proposed investment by Emirates NBD Bank via preferential issue of equity shares. • This is a continuation of the disclosure dated Oct 18, 2025. • The transaction is still subject to other regulatory approvals and customary conditions.</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK56" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL56" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="n">
-        <v>55</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2049735038691160351</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>https://x.com/speedystox/status/2049735038691160351</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>https://x.com/speedystox</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>speedystox</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Speedy Stox</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2038007871141765120/Kceaen5L_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr">
         <is>
           <t>📊 RBL BANK LTD - 540065 | 🏷️ General
 Received prior approval from SEBI on April 29, 2026 for a change in control related to a proposed investment by Emirates NBD Bank via a preferential issue of equity shares. The transaction is still subject to further regulatory approvals and conditions from the investment agreement dated October 18, 2025.
@@ -9630,7 +9498,7 @@
 ⚡️Instant stock alerts on WhatsApp - link in bio.</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>📊 RBL BANK LTD - 540065 | 🏷️ General
 Received prior approval from SEBI on April 29, 2026 for a change in control related to a proposed investment by Emirates NBD Bank via a preferential issue of equity shares. The transaction is still subject to further regulatory approvals and conditions from the investment agreement dated October 18, 2025.
@@ -9640,44 +9508,44 @@
 ⚡️Instant stock alerts on WhatsApp - link in bio.</t>
         </is>
       </c>
-      <c r="K57" t="b">
-        <v>0</v>
-      </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr">
+      <c r="K56" t="b">
+        <v>0</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
         <is>
           <t>21h</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>Apr 30, 2026 · 6:18 AM UTC</t>
         </is>
       </c>
-      <c r="P57" s="2" t="n">
+      <c r="P56" s="2" t="n">
         <v>46142.2625</v>
       </c>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" t="n">
-        <v>0</v>
-      </c>
-      <c r="U57" t="n">
-        <v>0</v>
-      </c>
-      <c r="V57" t="n">
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" t="n">
         <v>52</v>
       </c>
-      <c r="W57" t="inlineStr">
+      <c r="W56" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>📊 RBL BANK LTD - 540065 | 🏷️ General
 Received prior approval from SEBI on April 29, 2026 for a change in control related to a proposed investment by Emirates NBD Bank via a preferential issue of equity shares. The transaction is still subject to further regulatory approvals and conditions from the investment agreement dated October 18, 2025.
@@ -9687,9 +9555,9 @@
 ⚡️Instant stock alerts on WhatsApp - link in bio.</t>
         </is>
       </c>
-      <c r="Y57" t="inlineStr"/>
-      <c r="Z57" t="inlineStr"/>
-      <c r="AA57" t="inlineStr">
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr">
         <is>
           <t>📊 RBL BANK LTD - 540065 | 🏷️ General
 Received prior approval from SEBI on April 29, 2026 for a change in control related to a proposed investment by Emirates NBD Bank via a preferential issue of equity shares. The transaction is still subject to further regulatory approvals and conditions from the investment agreement dated October 18, 2025.
@@ -9699,7 +9567,7 @@
 ⚡️Instant stock alerts on WhatsApp - link in bio.</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
+      <c r="AB56" t="inlineStr">
         <is>
           <t>RBL BANK LTD - 540065 | General
 Received prior approval from SEBI on April 29, 2026, for a change in control related to a proposed investment by Emirates NBD Bank via a preferential issue of equity shares. The transaction is still subject to further regulatory approvals and conditions from the investment agreement dated October 18, 2025.
@@ -9709,6 +9577,154 @@
 Instant stock alerts on WhatsApp - link in bio.</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE56" s="2" t="n">
+        <v>46142.42916666667</v>
+      </c>
+      <c r="AF56" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>CMP: ₹338.55 (-0.79%) MCap: ₹20,934 Cr Refer to exchange for filings. • The transaction is still subject to further regulatory approvals and conditions from the investment agreement dated October 18, 2025. • Instant stock alerts on WhatsApp - link in bio.</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK56" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL56" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2049721813379522964</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://x.com/dcgguide/status/2049721813379522964</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://x.com/dcgguide</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>dcgguide</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>DUBAI CITY GUIDE from Cyber Gear</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1780203891230945280/ODQLZiT__bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Emirates NBD Reopens New GCC Debt Capital Markets Activity With Landmark USD AT1 Issuance blog.dubaicityguide.com/site…</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Emirates NBD Reopens New GCC Debt Capital Markets Activity With Landmark USD AT1 Issuance &lt;a href="https://blog.dubaicityguide.com/site/emirates-nbd-reopens-new-gcc-debt-capital-markets-activity-with-landmark-usd-at1-issuance/"&gt;blog.dubaicityguide.com/site…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K57" t="b">
+        <v>0</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Apr 30, 2026 · 5:25 AM UTC</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="n">
+        <v>46142.22569444445</v>
+      </c>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>['https://blog.dubaicityguide.com/site/emirates-nbd-reopens-new-gcc-debt-capital-markets-activity-with-landmark-usd-at1-issuance/']</t>
+        </is>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
+      </c>
+      <c r="V57" t="n">
+        <v>38</v>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Emirates NBD Reopens New GCC Debt Capital Markets Activity With Landmark USD AT1 Issuance blog.dubaicityguide.com/site…</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>Emirates NBD Reopens New GCC Debt Capital Markets Activity With Landmark USD AT1 Issuance blog.dubaicityguide.com/site…</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>Emirates NBD reopens new GCC debt capital markets activity with landmark USD AT1 issuance.</t>
+        </is>
+      </c>
       <c r="AC57" t="inlineStr">
         <is>
           <t>Cust</t>
@@ -9716,11 +9732,11 @@
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE57" s="2" t="n">
-        <v>46142.42916666667</v>
+        <v>46142.39236111111</v>
       </c>
       <c r="AF57" s="2" t="n">
         <v>46142</v>
@@ -9737,7 +9753,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>CMP: ₹338.55 (-0.79%) MCap: ₹20,934 Cr Refer to exchange for filings. • The transaction is still subject to further regulatory approvals and conditions from the investment agreement dated October 18, 2025. • Instant stock alerts on WhatsApp - link in bio.</t>
+          <t>Emirates NBD reopens new GCC debt capital markets activity with landmark USD AT1 issuance.</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
@@ -9760,43 +9776,45 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2049721813379522964</t>
+          <t>2049720588764377543</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2049721813379522964</t>
+          <t>https://x.com/ArabianBusiness/status/2049720588764377543</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide</t>
+          <t>https://x.com/ArabianBusiness</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>dcgguide</t>
+          <t>ArabianBusiness</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>DUBAI CITY GUIDE from Cyber Gear</t>
+          <t>ArabianBusiness.com</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1780203891230945280/ODQLZiT__bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1993579995382661127/_FaUxwqe_bigger.jpg</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Emirates NBD Reopens New GCC Debt Capital Markets Activity With Landmark USD AT1 Issuance https://t.co/Q2me9NkKIX</t>
+          <t>Emirates NBD has raised $750m (AED2.75bn) through an Additional Tier 1 (AT1) capital issuance, marking the first public debt capital markets deal by a GCC issuer since the Iran conflict started.
+Read the full story: arabianbusiness.com/abnews/e…</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Emirates NBD Reopens New GCC Debt Capital Markets Activity With Landmark USD AT1 Issuance &lt;a href="https://blog.dubaicityguide.com/site/emirates-nbd-reopens-new-gcc-debt-capital-markets-activity-with-landmark-usd-at1-issuance/"&gt;blog.dubaicityguide.com/site…&lt;/a&gt;</t>
+          <t>Emirates NBD has raised $750m (AED2.75bn) through an Additional Tier 1 (AT1) capital issuance, marking the first public debt capital markets deal by a GCC issuer since the Iran conflict started.
+Read the full story: &lt;a href="http://arabianbusiness.com/abnews/emirates-nbd-raises-750m-in-landmark-bond-deal-signalling-gcc-market-reopening"&gt;arabianbusiness.com/abnews/e…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K58" t="b">
@@ -9811,29 +9829,29 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 · 5:25 AM UTC</t>
+          <t>Apr 30, 2026 · 5:20 AM UTC</t>
         </is>
       </c>
       <c r="P58" s="2" t="n">
-        <v>46142.22569444445</v>
+        <v>46142.22222222222</v>
       </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr">
         <is>
-          <t>['https://blog.dubaicityguide.com/site/emirates-nbd-reopens-new-gcc-debt-capital-markets-activity-with-landmark-usd-at1-issuance/']</t>
+          <t>['http://arabianbusiness.com/abnews/emirates-nbd-raises-750m-in-landmark-bond-deal-signalling-gcc-market-reopening']</t>
         </is>
       </c>
       <c r="S58" t="n">
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V58" t="n">
-        <v>38</v>
+        <v>253</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
@@ -9842,27 +9860,21 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Emirates NBD Reopens New GCC Debt Capital Markets Activity With Landmark USD AT1 Issuance blog.dubaicityguide.com/site…</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>https://x.com/dcgguide/status/2049721813379522964</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>Emirates NBD Reopens New GCC Debt Capital Markets Activity With Landmark USD AT1 Issuance https://t.co/Q2me9NkKIX</t>
-        </is>
-      </c>
+          <t>Emirates NBD has raised $750m (AED2.75bn) through an Additional Tier 1 (AT1) capital issuance, marking the first public debt capital markets deal by a GCC issuer since the Iran conflict started.
+Read the full story: arabianbusiness.com/abnews/e…</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>Emirates NBD Reopens New GCC Debt Capital Markets Activity With Landmark USD AT1 Issuance https://t.co/Q2me9NkKIX</t>
+          <t>Emirates NBD has raised $750m (AED2.75bn) through an Additional Tier 1 (AT1) capital issuance, marking the first public debt capital markets deal by a GCC issuer since the Iran conflict started.
+Read the full story: arabianbusiness.com/abnews/e…</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>Emirates NBD reopens new GCC debt capital markets activity with landmark USD AT1 issuance.</t>
+          <t>Emirates NBD has raised $750 million (AED 2.75 billion) through an Additional Tier 1 (AT1) capital issuance, marking the first public debt capital markets deal by a GCC issuer since the Iran conflict started.</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -9872,11 +9884,11 @@
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE58" s="2" t="n">
-        <v>46142.39236111111</v>
+        <v>46142.38888888889</v>
       </c>
       <c r="AF58" s="2" t="n">
         <v>46142</v>
@@ -9893,7 +9905,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>Emirates NBD reopens new GCC debt capital markets activity with landmark USD AT1 issuance.</t>
+          <t>Emirates NBD has raised $750 million (AED 2.75 billion) through an Additional Tier 1 (AT1) capital issuance, marking the…</t>
         </is>
       </c>
       <c r="AJ58" t="inlineStr">
@@ -9916,52 +9928,58 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2049720588764377543</t>
+          <t>2049715289319723379</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://x.com/ArabianBusiness/status/2049720588764377543</t>
+          <t>https://x.com/Emy191990/status/2049715289319723379</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://x.com/ArabianBusiness</t>
+          <t>https://x.com/Emy191990</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ArabianBusiness</t>
+          <t>Emy191990</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ArabianBusiness.com</t>
+          <t>Eman Mohamed</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1993579995382661127/_FaUxwqe_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1764477948709449728/7Vvv4RHu_bigger.jpg</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Emirates NBD has raised $750m (AED2.75bn) through an Additional Tier 1 (AT1) capital issuance, marking the first public debt capital markets deal by a GCC issuer since the Iran conflict started.
-Read the full story: https://t.co/0syC2PDlI7 https://t.co/Ox0c4flEhh</t>
+          <t>Email : 2 
+#UnitedAgainstFraud
+#EmiratesNBD</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Emirates NBD has raised $750m (AED2.75bn) through an Additional Tier 1 (AT1) capital issuance, marking the first public debt capital markets deal by a GCC issuer since the Iran conflict started.
-Read the full story: &lt;a href="http://arabianbusiness.com/abnews/emirates-nbd-raises-750m-in-landmark-bond-deal-signalling-gcc-market-reopening"&gt;arabianbusiness.com/abnews/e…&lt;/a&gt;</t>
+          <t>Email : 2 
+&lt;a href="/search?f=tweets&amp;amp;q=%23UnitedAgainstFraud"&gt;#UnitedAgainstFraud&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K59" t="b">
         <v>0</v>
       </c>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr">
         <is>
           <t>22h</t>
@@ -9969,30 +9987,30 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 · 5:20 AM UTC</t>
+          <t>Apr 30, 2026 · 4:59 AM UTC</t>
         </is>
       </c>
       <c r="P59" s="2" t="n">
-        <v>46142.22222222222</v>
+        <v>46142.20763888889</v>
       </c>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr">
         <is>
-          <t>['http://arabianbusiness.com/abnews/emirates-nbd-raises-750m-in-landmark-bond-deal-signalling-gcc-market-reopening']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23UnitedAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBD']</t>
         </is>
       </c>
       <c r="S59" t="n">
         <v>0</v>
       </c>
       <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" t="n">
         <v>4</v>
       </c>
-      <c r="U59" t="n">
-        <v>2</v>
-      </c>
-      <c r="V59" t="n">
-        <v>253</v>
-      </c>
       <c r="W59" t="inlineStr">
         <is>
           <t>ENBD</t>
@@ -10000,30 +10018,25 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Emirates NBD has raised $750m (AED2.75bn) through an Additional Tier 1 (AT1) capital issuance, marking the first public debt capital markets deal by a GCC issuer since the Iran conflict started.
-Read the full story: arabianbusiness.com/abnews/e…</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>https://x.com/ArabianBusiness/status/2049720588764377543</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>Emirates NBD has raised $750m (AED2.75bn) through an Additional Tier 1 (AT1) capital issuance, marking the first public debt capital markets deal by a GCC issuer since the Iran conflict started.
-Read the full story: https://t.co/0syC2PDlI7 https://t.co/Ox0c4flEhh</t>
-        </is>
-      </c>
+          <t>Email : 2 
+#UnitedAgainstFraud
+#EmiratesNBD</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>Emirates NBD has raised $750m (AED2.75bn) through an Additional Tier 1 (AT1) capital issuance, marking the first public debt capital markets deal by a GCC issuer since the Iran conflict started.
-Read the full story: https://t.co/0syC2PDlI7 https://t.co/Ox0c4flEhh</t>
+          <t>Email : 2 
+#UnitedAgainstFraud
+#EmiratesNBD</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>Emirates NBD has raised $750 million (AED 2.75 billion) through an Additional Tier 1 (AT1) capital issuance, marking the first public debt capital markets deal by a GCC issuer since the Iran conflict started.</t>
+          <t>Email: 2 
+#UnitedAgainstFraud
+#EmiratesNBD</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -10037,7 +10050,7 @@
         </is>
       </c>
       <c r="AE59" s="2" t="n">
-        <v>46142.38888888889</v>
+        <v>46142.37430555555</v>
       </c>
       <c r="AF59" s="2" t="n">
         <v>46142</v>
@@ -10054,7 +10067,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Emirates NBD has raised $750 million (AED 2.75 billion) through an Additional Tier 1 (AT1) capital issuance, marking the…</t>
+          <t>Email: 2 #UnitedAgainstFraud #EmiratesNBD</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
@@ -10067,7 +10080,7 @@
       </c>
       <c r="AL59" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
@@ -10077,47 +10090,43 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2049715289319723379</t>
+          <t>2049712002503999763</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://x.com/Emy191990/status/2049715289319723379</t>
+          <t>https://x.com/Ahmed_44714/status/2049712002503999763</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://x.com/Emy191990</t>
+          <t>https://x.com/Ahmed_44714</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Emy191990</t>
+          <t>Ahmed_44714</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Eman Mohamed</t>
+          <t>Smart green Landscape</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1764477948709449728/7Vvv4RHu_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2014210440059068416/Jmp9M-bM_bigger.png</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Email : 2 
-#UnitedAgainstFraud
-#EmiratesNBD</t>
+          <t>Benefits of having borrowed money. Not earned</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Email : 2 
-&lt;a href="/search?f=tweets&amp;amp;q=%23UnitedAgainstFraud"&gt;#UnitedAgainstFraud&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt;</t>
+          <t>Benefits of having borrowed money. Not earned</t>
         </is>
       </c>
       <c r="K60" t="b">
@@ -10136,18 +10145,14 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 · 4:59 AM UTC</t>
+          <t>Apr 30, 2026 · 4:46 AM UTC</t>
         </is>
       </c>
       <c r="P60" s="2" t="n">
-        <v>46142.20763888889</v>
+        <v>46142.19861111111</v>
       </c>
       <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23UnitedAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBD']</t>
-        </is>
-      </c>
+      <c r="R60" t="inlineStr"/>
       <c r="S60" t="n">
         <v>0</v>
       </c>
@@ -10158,7 +10163,7 @@
         <v>0</v>
       </c>
       <c r="V60" t="n">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
@@ -10167,35 +10172,19 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Email : 2 
-#UnitedAgainstFraud
-#EmiratesNBD</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>https://x.com/Emy191990/status/2049715289319723379</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Email : 2 
-#UnitedAgainstFraud
-#EmiratesNBD</t>
-        </is>
-      </c>
+          <t>Benefits of having borrowed money. Not earned</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Email : 2 
-#UnitedAgainstFraud
-#EmiratesNBD</t>
+          <t>Benefits of having borrowed money. Not earned</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>Email: 2 
-#UnitedAgainstFraud
-#EmiratesNBD</t>
+          <t>Benefits of having borrowed money. Not earned.</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -10209,7 +10198,7 @@
         </is>
       </c>
       <c r="AE60" s="2" t="n">
-        <v>46142.37430555555</v>
+        <v>46142.36527777778</v>
       </c>
       <c r="AF60" s="2" t="n">
         <v>46142</v>
@@ -10226,7 +10215,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>Email: 2 #UnitedAgainstFraud #EmiratesNBD</t>
+          <t>Benefits of having borrowed money.</t>
         </is>
       </c>
       <c r="AJ60" t="inlineStr">
@@ -10249,71 +10238,71 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2049712002503999763</t>
+          <t>2049697262050410936</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://x.com/Ahmed_44714/status/2049712002503999763</t>
+          <t>https://x.com/vinod_yadav108/status/2049697262050410936</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://x.com/Ahmed_44714</t>
+          <t>https://x.com/vinod_yadav108</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ahmed_44714</t>
+          <t>vinod_yadav108</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Smart green Landscape</t>
+          <t>🇮🇳Vinod Yadav🇮🇳</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2014210440059068416/Jmp9M-bM_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1356183744563064834/uMPcj-Di_bigger.jpg</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Hear it from our Digital Credit Card winners. Apply now and get exclusive rewards. https://t.co/jWiWe48LMi</t>
+          <t>@EmiratesNBD_AE https://t.co/CUmsbv1vD5</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Benefits of having borrowed money. Not earned</t>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K61" t="b">
         <v>0</v>
       </c>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 · 4:46 AM UTC</t>
+          <t>Apr 30, 2026 · 3:48 AM UTC</t>
         </is>
       </c>
       <c r="P61" s="2" t="n">
-        <v>46142.19861111111</v>
+        <v>46142.15833333333</v>
       </c>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="S61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T61" t="n">
         <v>0</v>
@@ -10322,7 +10311,7 @@
         <v>0</v>
       </c>
       <c r="V61" t="n">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
@@ -10331,27 +10320,27 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Benefits of having borrowed money. Not earned</t>
+          <t>@EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>https://x.com/Ahmed_44714/status/2049712002503999763</t>
+          <t>https://x.com/vinod_yadav108/status/2049697262050410936</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>Hear it from our Digital Credit Card winners. Apply now and get exclusive rewards. https://t.co/jWiWe48LMi</t>
+          <t>@EmiratesNBD_AE https://t.co/CUmsbv1vD5</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>Hear it from our Digital Credit Card winners. Apply now and get exclusive rewards. https://t.co/jWiWe48LMi</t>
+          <t>@EmiratesNBD_AE https://t.co/CUmsbv1vD5</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>Hear it from our Digital Credit Card winners. Apply now and get exclusive rewards.</t>
+          <t>The text appears to be a social media handle and a link, which do not require translation.</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -10361,11 +10350,11 @@
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE61" s="2" t="n">
-        <v>46142.36527777778</v>
+        <v>46142.325</v>
       </c>
       <c r="AF61" s="2" t="n">
         <v>46142</v>
@@ -10382,7 +10371,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Hear it from our Digital Credit Card winners. • Apply now and get exclusive rewards.</t>
+          <t>The text appears to be a social media handle and a link, which do not require translation.</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
@@ -10395,7 +10384,7 @@
       </c>
       <c r="AL61" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -10405,71 +10394,71 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2049697262050410936</t>
+          <t>2049690184342741376</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://x.com/vinod_yadav108/status/2049697262050410936</t>
+          <t>https://x.com/amiiirrraaahhh/status/2049690184342741376</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://x.com/vinod_yadav108</t>
+          <t>https://x.com/amiiirrraaahhh</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>vinod_yadav108</t>
+          <t>amiiirrraaahhh</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>🇮🇳Vinod Yadav🇮🇳</t>
+          <t>Amirrah 🩷</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1356183744563064834/uMPcj-Di_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2006451721372053507/QsQWGucv_bigger.jpg</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE https://t.co/CUmsbv1vD5</t>
+          <t>@EmiratesNBD_AE Email 2</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="K62" t="b">
         <v>0</v>
       </c>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>Apr 30</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 · 3:48 AM UTC</t>
+          <t>Apr 30, 2026 · 3:19 AM UTC</t>
         </is>
       </c>
       <c r="P62" s="2" t="n">
-        <v>46142.15833333333</v>
+        <v>46142.13819444444</v>
       </c>
       <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="R62" t="inlineStr"/>
       <c r="S62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T62" t="n">
         <v>0</v>
@@ -10487,27 +10476,27 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>https://x.com/vinod_yadav108/status/2049697262050410936</t>
+          <t>https://x.com/amiiirrraaahhh/status/2049690184342741376</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE https://t.co/CUmsbv1vD5</t>
+          <t>@EmiratesNBD_AE Email 2</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE https://t.co/CUmsbv1vD5</t>
+          <t>@EmiratesNBD_AE Email 2</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>The text appears to be a social media handle and a link, which do not require translation.</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -10521,7 +10510,7 @@
         </is>
       </c>
       <c r="AE62" s="2" t="n">
-        <v>46142.325</v>
+        <v>46142.30486111111</v>
       </c>
       <c r="AF62" s="2" t="n">
         <v>46142</v>
@@ -10538,7 +10527,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>The text appears to be a social media handle and a link, which do not require translation.</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
@@ -10551,7 +10540,7 @@
       </c>
       <c r="AL62" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
@@ -10561,54 +10550,54 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2049690184342741376</t>
+          <t>2049689910093946994</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://x.com/amiiirrraaahhh/status/2049690184342741376</t>
+          <t>https://x.com/ENBDdeals/status/2049689910093946994</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://x.com/amiiirrraaahhh</t>
+          <t>https://x.com/ENBDdeals</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>amiiirrraaahhh</t>
+          <t>ENBDdeals</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Amirrah 🩷</t>
+          <t>Emirates NBD Deals</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2006451721372053507/QsQWGucv_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1763624422294814720/EmRI1Aqu_bigger.jpg</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Email 2</t>
+          <t>Experience the future with Ray- Ban Meta Glasses.
+Apply for Emirates NBD SHARE Visa Credit Card and get a chance to win Ray-Ban Meta Sunglasses.
+Apply Now: https://t.co/XpFUmumwP4 https://t.co/mnBSMa6sd3</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Email 2</t>
+          <t>Experience the future with Ray- Ban Meta Glasses.
+Apply for Emirates NBD SHARE Visa Credit Card and get a chance to win Ray-Ban Meta Sunglasses.
+Apply Now: &lt;a href="https://apply.emiratesnbd.com/en/credit-card/maf"&gt;apply.emiratesnbd.com/en/cre…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K63" t="b">
         <v>0</v>
       </c>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
           <t>Apr 30</t>
@@ -10616,14 +10605,18 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 · 3:19 AM UTC</t>
+          <t>Apr 30, 2026 · 3:18 AM UTC</t>
         </is>
       </c>
       <c r="P63" s="2" t="n">
-        <v>46142.13819444444</v>
+        <v>46142.1375</v>
       </c>
       <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>['https://apply.emiratesnbd.com/en/credit-card/maf']</t>
+        </is>
+      </c>
       <c r="S63" t="n">
         <v>0</v>
       </c>
@@ -10634,7 +10627,7 @@
         <v>0</v>
       </c>
       <c r="V63" t="n">
-        <v>4</v>
+        <v>87</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
@@ -10643,41 +10636,49 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Email 2</t>
+          <t>Experience the future with Ray- Ban Meta Glasses.
+Apply for Emirates NBD SHARE Visa Credit Card and get a chance to win Ray-Ban Meta Sunglasses.
+Apply Now: apply.emiratesnbd.com/en/cre…</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>https://x.com/amiiirrraaahhh/status/2049690184342741376</t>
+          <t>https://x.com/ENBDdeals/status/2049689910093946994</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Email 2</t>
+          <t>Experience the future with Ray- Ban Meta Glasses.
+Apply for Emirates NBD SHARE Visa Credit Card and get a chance to win Ray-Ban Meta Sunglasses.
+Apply Now: https://t.co/XpFUmumwP4 https://t.co/mnBSMa6sd3</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Email 2</t>
+          <t>Experience the future with Ray- Ban Meta Glasses.
+Apply for Emirates NBD SHARE Visa Credit Card and get a chance to win Ray-Ban Meta Sunglasses.
+Apply Now: https://t.co/XpFUmumwP4 https://t.co/mnBSMa6sd3</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>Email 2</t>
+          <t>Experience the future with Ray-Ban Meta Glasses. 
+Apply for the Emirates NBD SHARE Visa Credit Card and get a chance to win Ray-Ban Meta Sunglasses. 
+Apply Now: https://t.co/XpFUmumwP4 https://t.co/mnBSMa6sd3</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Cust</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE63" s="2" t="n">
-        <v>46142.30486111111</v>
+        <v>46142.30416666667</v>
       </c>
       <c r="AF63" s="2" t="n">
         <v>46142</v>
@@ -10694,7 +10695,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Email 2</t>
+          <t>Apply for the Emirates NBD SHARE Visa Credit Card and get a chance to win Ray-Ban Meta Sunglasses. • Apply Now: https://t.co/XpFUmumwP4 https://t.co/mnBSMa6sd3 • Experience the future with Ray-Ban Meta Glasses.</t>
         </is>
       </c>
       <c r="AJ63" t="inlineStr">
@@ -10707,7 +10708,7 @@
       </c>
       <c r="AL63" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -10717,47 +10718,45 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2049689910093946994</t>
+          <t>2049660884436533486</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2049689910093946994</t>
+          <t>https://x.com/2n_ah/status/2049660884436533486</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals</t>
+          <t>https://x.com/2n_ah</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ENBDdeals</t>
+          <t>2n_ah</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Emirates NBD Deals</t>
+          <t>Ahmad Omran</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1763624422294814720/EmRI1Aqu_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2033688949219323904/9kdoW_hY_bigger.jpg</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Experience the future with Ray- Ban Meta Glasses.
-Apply for Emirates NBD SHARE Visa Credit Card and get a chance to win Ray-Ban Meta Sunglasses.
-Apply Now: https://t.co/XpFUmumwP4 https://t.co/mnBSMa6sd3</t>
+          <t>Off-Plan Financing is Now a Reality in Dubai
+A significant milestone has been reached in our real estate sector. Emirates NBD, in collaboration with top-tier developers including Emaar, Nakheel, Dubai Holding, and Meraas, is now providing mortgage facilities for off plan projects https://t.co/PaG58Z14Yu</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Experience the future with Ray- Ban Meta Glasses.
-Apply for Emirates NBD SHARE Visa Credit Card and get a chance to win Ray-Ban Meta Sunglasses.
-Apply Now: &lt;a href="https://apply.emiratesnbd.com/en/credit-card/maf"&gt;apply.emiratesnbd.com/en/cre…&lt;/a&gt;</t>
+          <t>Off-Plan Financing is Now a Reality in Dubai
+A significant milestone has been reached in our real estate sector. Emirates NBD, in collaboration with top-tier developers including Emaar, Nakheel, Dubai Holding, and Meraas, is now providing mortgage facilities for off plan projects</t>
         </is>
       </c>
       <c r="K64" t="b">
@@ -10772,18 +10771,14 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 · 3:18 AM UTC</t>
+          <t>Apr 30, 2026 · 1:23 AM UTC</t>
         </is>
       </c>
       <c r="P64" s="2" t="n">
-        <v>46142.1375</v>
+        <v>46142.05763888889</v>
       </c>
       <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>['https://apply.emiratesnbd.com/en/credit-card/maf']</t>
-        </is>
-      </c>
+      <c r="R64" t="inlineStr"/>
       <c r="S64" t="n">
         <v>0</v>
       </c>
@@ -10794,7 +10789,7 @@
         <v>0</v>
       </c>
       <c r="V64" t="n">
-        <v>87</v>
+        <v>35</v>
       </c>
       <c r="W64" t="inlineStr">
         <is>
@@ -10803,40 +10798,35 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Experience the future with Ray- Ban Meta Glasses.
-Apply for Emirates NBD SHARE Visa Credit Card and get a chance to win Ray-Ban Meta Sunglasses.
-Apply Now: apply.emiratesnbd.com/en/cre…</t>
+          <t>Off-Plan Financing is Now a Reality in Dubai
+A significant milestone has been reached in our real estate sector. Emirates NBD, in collaboration with top-tier developers including Emaar, Nakheel, Dubai Holding, and Meraas, is now providing mortgage facilities for off plan projects</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2049689910093946994</t>
+          <t>https://x.com/2n_ah/status/2049660884436533486</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>Experience the future with Ray- Ban Meta Glasses.
-Apply for Emirates NBD SHARE Visa Credit Card and get a chance to win Ray-Ban Meta Sunglasses.
-Apply Now: https://t.co/XpFUmumwP4 https://t.co/mnBSMa6sd3</t>
+          <t>Off-Plan Financing is Now a Reality in Dubai
+A significant milestone has been reached in our real estate sector. Emirates NBD, in collaboration with top-tier developers including Emaar, Nakheel, Dubai Holding, and Meraas, is now providing mortgage facilities for off plan projects https://t.co/PaG58Z14Yu</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>Experience the future with Ray- Ban Meta Glasses.
-Apply for Emirates NBD SHARE Visa Credit Card and get a chance to win Ray-Ban Meta Sunglasses.
-Apply Now: https://t.co/XpFUmumwP4 https://t.co/mnBSMa6sd3</t>
+          <t>Off-Plan Financing is Now a Reality in Dubai
+A significant milestone has been reached in our real estate sector. Emirates NBD, in collaboration with top-tier developers including Emaar, Nakheel, Dubai Holding, and Meraas, is now providing mortgage facilities for off plan projects https://t.co/PaG58Z14Yu</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>Experience the future with Ray-Ban Meta Glasses. 
-Apply for the Emirates NBD SHARE Visa Credit Card and get a chance to win Ray-Ban Meta Sunglasses. 
-Apply Now: https://t.co/XpFUmumwP4 https://t.co/mnBSMa6sd3</t>
+          <t>Off-Plan Financing is Now a Reality in Dubai A significant milestone has been reached in our real estate sector. Emirates NBD, in collaboration with top-tier developers including Emaar, Nakheel, Dubai Holding, and Meraas, is now providing mortgage facilities for off-plan projects.</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Cust</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr">
@@ -10845,7 +10835,7 @@
         </is>
       </c>
       <c r="AE64" s="2" t="n">
-        <v>46142.30416666667</v>
+        <v>46142.22430555556</v>
       </c>
       <c r="AF64" s="2" t="n">
         <v>46142</v>
@@ -10862,7 +10852,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Apply for the Emirates NBD SHARE Visa Credit Card and get a chance to win Ray-Ban Meta Sunglasses. • Apply Now: https://t.co/XpFUmumwP4 https://t.co/mnBSMa6sd3 • Experience the future with Ray-Ban Meta Glasses.</t>
+          <t>Emirates NBD, in collaboration with top-tier developers including Emaar, Nakheel, Dubai Holding, and Meraas, is now providing mortgage facilities for off-plan projects. • Off-Plan Financing is Now a Reality in Dubai A significant milestone has been reached in our real estate sector.</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
@@ -10885,45 +10875,43 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2049660884436533486</t>
+          <t>2049768124615143524</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://x.com/2n_ah/status/2049660884436533486</t>
+          <t>https://x.com/dcgguide/status/2049768124615143524</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://x.com/2n_ah</t>
+          <t>https://x.com/dcgguide</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2n_ah</t>
+          <t>dcgguide</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ahmad Omran</t>
+          <t>DUBAI CITY GUIDE from Cyber Gear</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2033688949219323904/9kdoW_hY_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1780203891230945280/ODQLZiT__bigger.jpg</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Off-Plan Financing is Now a Reality in Dubai
-A significant milestone has been reached in our real estate sector. Emirates NBD, in collaboration with top-tier developers including Emaar, Nakheel, Dubai Holding, and Meraas, is now providing mortgage facilities for off plan projects</t>
+          <t>Emirates Islamic Launches Tailored Banking Benefits To Support UAE’s Frontline Heroes https://t.co/RAeuzYLE2y</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Off-Plan Financing is Now a Reality in Dubai
-A significant milestone has been reached in our real estate sector. Emirates NBD, in collaboration with top-tier developers including Emaar, Nakheel, Dubai Holding, and Meraas, is now providing mortgage facilities for off plan projects</t>
+          <t>Emirates Islamic Launches Tailored Banking Benefits To Support UAE’s Frontline Heroes &lt;a href="https://blog.uaetoday.com/emirates-islamic-launches-tailored-banking-benefits-to-support-uaes-frontline-heroes/"&gt;blog.uaetoday.com/emirates-i…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K65" t="b">
@@ -10933,19 +10921,23 @@
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
-          <t>Apr 30</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 · 1:23 AM UTC</t>
+          <t>Apr 30, 2026 · 8:29 AM UTC</t>
         </is>
       </c>
       <c r="P65" s="2" t="n">
-        <v>46142.05763888889</v>
+        <v>46142.35347222222</v>
       </c>
       <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>['https://blog.uaetoday.com/emirates-islamic-launches-tailored-banking-benefits-to-support-uaes-frontline-heroes/']</t>
+        </is>
+      </c>
       <c r="S65" t="n">
         <v>0</v>
       </c>
@@ -10953,33 +10945,39 @@
         <v>0</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V65" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Off-Plan Financing is Now a Reality in Dubai
-A significant milestone has been reached in our real estate sector. Emirates NBD, in collaboration with top-tier developers including Emaar, Nakheel, Dubai Holding, and Meraas, is now providing mortgage facilities for off plan projects</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr"/>
-      <c r="Z65" t="inlineStr"/>
+          <t>Emirates Islamic Launches Tailored Banking Benefits To Support UAE’s Frontline Heroes blog.uaetoday.com/emirates-i…</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>https://x.com/dcgguide/status/2049768124615143524</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>Emirates Islamic Launches Tailored Banking Benefits To Support UAE’s Frontline Heroes https://t.co/RAeuzYLE2y</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>Off-Plan Financing is Now a Reality in Dubai
-A significant milestone has been reached in our real estate sector. Emirates NBD, in collaboration with top-tier developers including Emaar, Nakheel, Dubai Holding, and Meraas, is now providing mortgage facilities for off plan projects</t>
+          <t>Emirates Islamic Launches Tailored Banking Benefits To Support UAE’s Frontline Heroes https://t.co/RAeuzYLE2y</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>Off-Plan Financing is Now a Reality in Dubai A significant milestone has been reached in our real estate sector. Emirates NBD, in collaboration with top-tier developers including Emaar, Nakheel, Dubai Holding, and Meraas, is now providing mortgage facilities for off-plan projects.</t>
+          <t>Emirates Islamic Launches Tailored Banking Benefits To Support UAE’s Frontline Heroes</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
@@ -10993,29 +10991,29 @@
         </is>
       </c>
       <c r="AE65" s="2" t="n">
-        <v>46142.22430555556</v>
+        <v>46142.52013888889</v>
       </c>
       <c r="AF65" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
+          <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>Emirates NBD, in collaboration with top-tier developers including Emaar, Nakheel, Dubai Holding, and Meraas, is now providing mortgage facilities for off-plan projects. • Off-Plan Financing is Now a Reality in Dubai A significant milestone has been reached in our real estate sector.</t>
+          <t>Emirates Islamic Launches Tailored Banking Benefits To Support UAE’s Frontline Heroes</t>
         </is>
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank (ENBD)</t>
+          <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AK65" t="n">
@@ -11033,43 +11031,55 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2049768124615143524</t>
+          <t>2049760670133178628</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2049768124615143524</t>
+          <t>https://x.com/blocknewsint/status/2049760670133178628</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide</t>
+          <t>https://x.com/blocknewsint</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>dcgguide</t>
+          <t>blocknewsint</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>DUBAI CITY GUIDE from Cyber Gear</t>
+          <t>Block News International</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1780203891230945280/ODQLZiT__bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1881352530807959552/YV-Uq6jL_bigger.jpg</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Emirates Islamic Launches Tailored Banking Benefits To Support UAE’s Frontline Heroes blog.uaetoday.com/emirates-i…</t>
+          <t>Dubai is taking a new step in the evolution of financial centers by aiming to build the world’s first AI-native financial ecosystem.
+The Dubai International Financial Centre (DIFC) is planning to embed artificial intelligence across its core systems, from regulation and infrastructure to financial services and talent development. Rather than using AI as an add-on, the model integrates it into how the entire financial environment operates.
+The initiative is expected to generate approximately $3.5 billion in economic value and create around 25,000 jobs, reflecting the scale of transformation underway.
+By positioning itself as a hub for AI-driven finance, DIFC aims to attract global startups, capital, and talent, reinforcing Dubai’s role in shaping the future of financial innovation.
+Read more: https://t.co/z8jtwV3U0M
+#Dubai #DIFC #ArtificialIntelligence #Fintech #DigitalTransformation #BlockNews</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Emirates Islamic Launches Tailored Banking Benefits To Support UAE’s Frontline Heroes &lt;a href="https://blog.uaetoday.com/emirates-islamic-launches-tailored-banking-benefits-to-support-uaes-frontline-heroes/"&gt;blog.uaetoday.com/emirates-i…&lt;/a&gt;</t>
+          <t>Emirates Islamic (&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt;) has introduced a new way for investors in the UAE to access gold and silver directly through their smartphones.
+The bank has launched a Shariah-compliant digital investment platform that allows customers to buy, sell and hold physical bullion through its mobile app. The offering is positioned as a first for an Islamic bank in the UAE, combining traditional asset ownership with a fully digital experience.
+All bullion is backed by physical gold and silver stored in secure vaults and meets internationally recognized standards, including London Bullion Market Association (LBMA) and UAE Good Delivery requirements.
+The initiative reflects a broader shift toward digital wealth solutions, as investors look for more accessible and flexible ways to diversify their portfolios.
+Customers can trade at market-linked prices, redeem their holdings in cash or physical form, and manage their investments entirely through the bank’s mobile platform.
+With demand for alternative assets continuing to rise, Emirates Islamic’s latest offering signals how traditional finance is adapting to a mobile-first world, without stepping outside the framework of Islamic finance.
+Read more: &lt;a href="https://www.blocknewsint.com/articles/emirates-islamic-bank-launches-digital-precious-metals-investing-in-uae"&gt;blocknewsint.com/articles/em…&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23DigitalBanking"&gt;#DigitalBanking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23IslamicFinance"&gt;#IslamicFinance&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23PreciousMetals"&gt;#PreciousMetals&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K66" t="b">
@@ -11079,21 +11089,21 @@
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 · 8:29 AM UTC</t>
+          <t>Apr 30, 2026 · 8:00 AM UTC</t>
         </is>
       </c>
       <c r="P66" s="2" t="n">
-        <v>46142.35347222222</v>
+        <v>46142.33333333334</v>
       </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr">
         <is>
-          <t>['https://blog.uaetoday.com/emirates-islamic-launches-tailored-banking-benefits-to-support-uaes-frontline-heroes/']</t>
+          <t>['https://x.com/emiratesislamic', 'https://www.blocknewsint.com/articles/emirates-islamic-bank-launches-digital-precious-metals-investing-in-uae', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23DigitalBanking', 'https://x.com/search?f=tweets&amp;q=%23IslamicFinance', 'https://x.com/search?f=tweets&amp;q=%23PreciousMetals']</t>
         </is>
       </c>
       <c r="S66" t="n">
@@ -11103,10 +11113,10 @@
         <v>0</v>
       </c>
       <c r="U66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V66" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="W66" t="inlineStr">
         <is>
@@ -11114,103 +11124,6 @@
         </is>
       </c>
       <c r="X66" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Launches Tailored Banking Benefits To Support UAE’s Frontline Heroes blog.uaetoday.com/emirates-i…</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr"/>
-      <c r="Z66" t="inlineStr"/>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Launches Tailored Banking Benefits To Support UAE’s Frontline Heroes blog.uaetoday.com/emirates-i…</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Launches Tailored Banking Benefits To Support UAE’s Frontline Heroes</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD66" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="AE66" s="2" t="n">
-        <v>46142.52013888889</v>
-      </c>
-      <c r="AF66" s="2" t="n">
-        <v>46142</v>
-      </c>
-      <c r="AG66" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Launches Tailored Banking Benefits To Support UAE’s Frontline Heroes</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK66" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL66" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="1" t="n">
-        <v>65</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>2049760670133178628</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>https://x.com/blocknewsint/status/2049760670133178628</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>https://x.com/blocknewsint</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>blocknewsint</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Block News International</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1881352530807959552/YV-Uq6jL_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr">
         <is>
           <t>Emirates Islamic (@emiratesislamic) has introduced a new way for investors in the UAE to access gold and silver directly through their smartphones.
 The bank has launched a Shariah-compliant digital investment platform that allows customers to buy, sell and hold physical bullion through its mobile app. The offering is positioned as a first for an Islamic bank in the UAE, combining traditional asset ownership with a fully digital experience.
@@ -11222,16 +11135,126 @@
 #EmiratesIslamic #DigitalBanking #IslamicFinance #PreciousMetals</t>
         </is>
       </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>https://x.com/blocknewsint/status/2049760670133178628</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>Dubai is taking a new step in the evolution of financial centers by aiming to build the world’s first AI-native financial ecosystem.
+The Dubai International Financial Centre (DIFC) is planning to embed artificial intelligence across its core systems, from regulation and infrastructure to financial services and talent development. Rather than using AI as an add-on, the model integrates it into how the entire financial environment operates.
+The initiative is expected to generate approximately $3.5 billion in economic value and create around 25,000 jobs, reflecting the scale of transformation underway.
+By positioning itself as a hub for AI-driven finance, DIFC aims to attract global startups, capital, and talent, reinforcing Dubai’s role in shaping the future of financial innovation.
+Read more: https://t.co/z8jtwV3U0M
+#Dubai #DIFC #ArtificialIntelligence #Fintech #DigitalTransformation #BlockNews</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>Dubai is taking a new step in the evolution of financial centers by aiming to build the world’s first AI-native financial ecosystem.
+The Dubai International Financial Centre (DIFC) is planning to embed artificial intelligence across its core systems, from regulation and infrastructure to financial services and talent development. Rather than using AI as an add-on, the model integrates it into how the entire financial environment operates.
+The initiative is expected to generate approximately $3.5 billion in economic value and create around 25,000 jobs, reflecting the scale of transformation underway.
+By positioning itself as a hub for AI-driven finance, DIFC aims to attract global startups, capital, and talent, reinforcing Dubai’s role in shaping the future of financial innovation.
+Read more: https://t.co/z8jtwV3U0M
+#Dubai #DIFC #ArtificialIntelligence #Fintech #DigitalTransformation #BlockNews</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>Dubai is taking a new step in the evolution of financial centers by aiming to build the world’s first AI-native financial ecosystem. The Dubai International Financial Centre (DIFC) is planning to embed artificial intelligence across its core systems, from regulation and infrastructure to financial services and talent development. Rather than using AI as an add-on, the model integrates it into how the entire financial environment operates. The initiative is expected to generate approximately $3.5 billion in economic value and create around 25,000 jobs, reflecting the scale of transformation underway. By positioning itself as a hub for AI-driven finance, DIFC aims to attract global startups, capital, and talent, reinforcing Dubai’s role in shaping the future of financial innovation.</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE66" s="2" t="n">
+        <v>46142.5</v>
+      </c>
+      <c r="AF66" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="AG66" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>2. Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>The Dubai International Financial Centre (DIFC) is planning to embed artificial intelligence across its core systems, from regulation and infrastructure to financial services and talent development. • By positioning itself as a hub for AI-driven finance, DIFC aims to attract global startups, capital, and talent, reinforcing Dubai’s role in shaping the future of financial innovation. • Dubai is taking a new step in the evolution of financial centers by aiming to build the world’s first AI-native financial ecosystem.</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AK66" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL66" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2049745585540894884</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2049745585540894884</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Rank your debts, clear the smallest first, and roll that momentum over to the next. You don’t have to do it all at once, you just have to start with one. 
+#EmiratesIslamic</t>
+        </is>
+      </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Emirates Islamic (&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt;) has introduced a new way for investors in the UAE to access gold and silver directly through their smartphones.
-The bank has launched a Shariah-compliant digital investment platform that allows customers to buy, sell and hold physical bullion through its mobile app. The offering is positioned as a first for an Islamic bank in the UAE, combining traditional asset ownership with a fully digital experience.
-All bullion is backed by physical gold and silver stored in secure vaults and meets internationally recognized standards, including London Bullion Market Association (LBMA) and UAE Good Delivery requirements.
-The initiative reflects a broader shift toward digital wealth solutions, as investors look for more accessible and flexible ways to diversify their portfolios.
-Customers can trade at market-linked prices, redeem their holdings in cash or physical form, and manage their investments entirely through the bank’s mobile platform.
-With demand for alternative assets continuing to rise, Emirates Islamic’s latest offering signals how traditional finance is adapting to a mobile-first world, without stepping outside the framework of Islamic finance.
-Read more: &lt;a href="https://www.blocknewsint.com/articles/emirates-islamic-bank-launches-digital-precious-metals-investing-in-uae"&gt;blocknewsint.com/articles/em…&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23DigitalBanking"&gt;#DigitalBanking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23IslamicFinance"&gt;#IslamicFinance&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23PreciousMetals"&gt;#PreciousMetals&lt;/a&gt;</t>
+          <t>Rank your debts, clear the smallest first, and roll that momentum over to the next. You don’t have to do it all at once, you just have to start with one. 
+&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K67" t="b">
@@ -11241,21 +11264,21 @@
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 · 8:00 AM UTC</t>
+          <t>Apr 30, 2026 · 7:00 AM UTC</t>
         </is>
       </c>
       <c r="P67" s="2" t="n">
-        <v>46142.33333333334</v>
+        <v>46142.29166666666</v>
       </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr">
         <is>
-          <t>['https://x.com/emiratesislamic', 'https://www.blocknewsint.com/articles/emirates-islamic-bank-launches-digital-precious-metals-investing-in-uae', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23DigitalBanking', 'https://x.com/search?f=tweets&amp;q=%23IslamicFinance', 'https://x.com/search?f=tweets&amp;q=%23PreciousMetals']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic']</t>
         </is>
       </c>
       <c r="S67" t="n">
@@ -11268,7 +11291,7 @@
         <v>0</v>
       </c>
       <c r="V67" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="W67" t="inlineStr">
         <is>
@@ -11277,47 +11300,35 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Emirates Islamic (@emiratesislamic) has introduced a new way for investors in the UAE to access gold and silver directly through their smartphones.
-The bank has launched a Shariah-compliant digital investment platform that allows customers to buy, sell and hold physical bullion through its mobile app. The offering is positioned as a first for an Islamic bank in the UAE, combining traditional asset ownership with a fully digital experience.
-All bullion is backed by physical gold and silver stored in secure vaults and meets internationally recognized standards, including London Bullion Market Association (LBMA) and UAE Good Delivery requirements.
-The initiative reflects a broader shift toward digital wealth solutions, as investors look for more accessible and flexible ways to diversify their portfolios.
-Customers can trade at market-linked prices, redeem their holdings in cash or physical form, and manage their investments entirely through the bank’s mobile platform.
-With demand for alternative assets continuing to rise, Emirates Islamic’s latest offering signals how traditional finance is adapting to a mobile-first world, without stepping outside the framework of Islamic finance.
-Read more: blocknewsint.com/articles/em…
-#EmiratesIslamic #DigitalBanking #IslamicFinance #PreciousMetals</t>
+          <t>Rank your debts, clear the smallest first, and roll that momentum over to the next. You don’t have to do it all at once, you just have to start with one. 
+#EmiratesIslamic</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="inlineStr"/>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>Emirates Islamic (@emiratesislamic) has introduced a new way for investors in the UAE to access gold and silver directly through their smartphones.
-The bank has launched a Shariah-compliant digital investment platform that allows customers to buy, sell and hold physical bullion through its mobile app. The offering is positioned as a first for an Islamic bank in the UAE, combining traditional asset ownership with a fully digital experience.
-All bullion is backed by physical gold and silver stored in secure vaults and meets internationally recognized standards, including London Bullion Market Association (LBMA) and UAE Good Delivery requirements.
-The initiative reflects a broader shift toward digital wealth solutions, as investors look for more accessible and flexible ways to diversify their portfolios.
-Customers can trade at market-linked prices, redeem their holdings in cash or physical form, and manage their investments entirely through the bank’s mobile platform.
-With demand for alternative assets continuing to rise, Emirates Islamic’s latest offering signals how traditional finance is adapting to a mobile-first world, without stepping outside the framework of Islamic finance.
-Read more: blocknewsint.com/articles/em…
-#EmiratesIslamic #DigitalBanking #IslamicFinance #PreciousMetals</t>
+          <t>Rank your debts, clear the smallest first, and roll that momentum over to the next. You don’t have to do it all at once, you just have to start with one. 
+#EmiratesIslamic</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>Emirates Islamic has introduced a new way for investors in the UAE to access gold and silver directly through their smartphones. The bank has launched a Shariah-compliant digital investment platform that allows customers to buy, sell, and hold physical bullion through its mobile app. The offering is positioned as a first for an Islamic bank in the UAE, combining traditional asset ownership with a fully digital experience. All bullion is backed by physical gold and silver stored in secure vaults and meets internationally recognized standards, including London Bullion Market Association (LBMA) and UAE Good Delivery requirements. The initiative reflects a broader shift toward digital wealth solutions, as investors look for more accessible and flexible ways to diversify their portfolios. Customers can trade at market-linked prices, redeem their holdings in cash or physical form, and manage their investments entirely through the bank’s mobile platform. With demand for alternative assets continuing to rise, Emirates Islamic’s latest offering signals how traditional finance is adapting to a mobile-first world, without stepping outside the framework of Islamic finance.</t>
+          <t>Rank your debts, clear the smallest first, and roll that momentum over to the next. You don’t have to do it all at once, you just have to start with one.</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Cust</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE67" s="2" t="n">
-        <v>46142.5</v>
+        <v>46142.45833333334</v>
       </c>
       <c r="AF67" s="2" t="n">
         <v>46142</v>
@@ -11334,7 +11345,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>The bank has launched a Shariah-compliant digital investment platform that allows customers to buy, sell, and hold physical bullion through its mobile app. • Customers can trade at market-linked prices, redeem their holdings in cash or physical form, and manage their investments entirely through the bank’s mobile platform. • Emirates Islamic has introduced a new way for investors in the UAE to access gold and silver directly through their smartphones.</t>
+          <t>You don’t have to do it all at once, you just have to start with one. • Rank your debts, clear the smallest first, and roll that momentum over to the next.</t>
         </is>
       </c>
       <c r="AJ67" t="inlineStr">
@@ -11357,12 +11368,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2049745585540894884</t>
+          <t>2049730468916908361</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2049745585540894884</t>
+          <t>https://x.com/emiratesislamic/status/2049730468916908361</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11388,14 +11399,16 @@
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Rank your debts, clear the smallest first, and roll that momentum over to the next. You don’t have to do it all at once, you just have to start with one. 
-#EmiratesIslamic</t>
+          <t>Are you paying for something you don’t use?
+#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
+emiratesislamic.ae/en/key-in…</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Rank your debts, clear the smallest first, and roll that momentum over to the next. You don’t have to do it all at once, you just have to start with one. 
-&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;</t>
+          <t>Are you paying for something you don’t use?
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K68" t="b">
@@ -11405,21 +11418,21 @@
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 · 7:00 AM UTC</t>
+          <t>Apr 30, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P68" s="2" t="n">
-        <v>46142.29166666666</v>
+        <v>46142.25</v>
       </c>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
         </is>
       </c>
       <c r="S68" t="n">
@@ -11429,10 +11442,10 @@
         <v>0</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V68" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W68" t="inlineStr">
         <is>
@@ -11441,21 +11454,23 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Rank your debts, clear the smallest first, and roll that momentum over to the next. You don’t have to do it all at once, you just have to start with one. 
-#EmiratesIslamic</t>
+          <t>Are you paying for something you don’t use?
+#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
+emiratesislamic.ae/en/key-in…</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="inlineStr"/>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>Rank your debts, clear the smallest first, and roll that momentum over to the next. You don’t have to do it all at once, you just have to start with one. 
-#EmiratesIslamic</t>
+          <t>Are you paying for something you don’t use?
+#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
+emiratesislamic.ae/en/key-in…</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>Rank your debts, clear the smallest first, and roll that momentum over to the next. You don’t have to do it all at once, you just have to start with one.</t>
+          <t>Are you paying for something you don’t use?</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
@@ -11469,7 +11484,7 @@
         </is>
       </c>
       <c r="AE68" s="2" t="n">
-        <v>46142.45833333334</v>
+        <v>46142.41666666666</v>
       </c>
       <c r="AF68" s="2" t="n">
         <v>46142</v>
@@ -11486,7 +11501,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>You don’t have to do it all at once, you just have to start with one. • Rank your debts, clear the smallest first, and roll that momentum over to the next.</t>
+          <t>Are you paying for something you don’t use?</t>
         </is>
       </c>
       <c r="AJ68" t="inlineStr">
@@ -11509,12 +11524,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2049730468916908361</t>
+          <t>2049730468522713462</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2049730468916908361</t>
+          <t>https://x.com/emiratesislamic/status/2049730468522713462</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11539,162 +11554,6 @@
       </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
-        <is>
-          <t>Are you paying for something you don’t use?
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
-emiratesislamic.ae/en/key-in…</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>Are you paying for something you don’t use?
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K69" t="b">
-        <v>0</v>
-      </c>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>Apr 30, 2026 · 6:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P69" s="2" t="n">
-        <v>46142.25</v>
-      </c>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
-        </is>
-      </c>
-      <c r="S69" t="n">
-        <v>0</v>
-      </c>
-      <c r="T69" t="n">
-        <v>0</v>
-      </c>
-      <c r="U69" t="n">
-        <v>1</v>
-      </c>
-      <c r="V69" t="n">
-        <v>52</v>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>Are you paying for something you don’t use?
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
-emiratesislamic.ae/en/key-in…</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr"/>
-      <c r="Z69" t="inlineStr"/>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>Are you paying for something you don’t use?
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
-emiratesislamic.ae/en/key-in…</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>Are you paying for something you don’t use?</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="AD69" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE69" s="2" t="n">
-        <v>46142.41666666666</v>
-      </c>
-      <c r="AF69" s="2" t="n">
-        <v>46142</v>
-      </c>
-      <c r="AG69" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>Are you paying for something you don’t use?</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK69" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL69" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="1" t="n">
-        <v>68</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>2049730468522713462</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2049730468522713462</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr">
         <is>
           <t>Scam messages often come from random or international numbers - not official IDs.
 Do not fall for the traps. Stay alert to scams.
@@ -11703,7 +11562,7 @@
 emiratesislamic.ae/en/person…</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>Scam messages often come from random or international numbers - not official IDs.
 Do not fall for the traps. Stay alert to scams.
@@ -11712,48 +11571,48 @@
 &lt;a href="https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K70" t="b">
-        <v>0</v>
-      </c>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr">
+      <c r="K69" t="b">
+        <v>0</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
         <is>
           <t>21h</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t>Apr 30, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
-      <c r="P70" s="2" t="n">
+      <c r="P69" s="2" t="n">
         <v>46142.25</v>
       </c>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr">
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr">
         <is>
           <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud', 'https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security']</t>
         </is>
       </c>
-      <c r="S70" t="n">
-        <v>0</v>
-      </c>
-      <c r="T70" t="n">
-        <v>0</v>
-      </c>
-      <c r="U70" t="n">
-        <v>0</v>
-      </c>
-      <c r="V70" t="n">
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" t="n">
         <v>62</v>
       </c>
-      <c r="W70" t="inlineStr">
+      <c r="W69" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>Scam messages often come from random or international numbers - not official IDs.
 Do not fall for the traps. Stay alert to scams.
@@ -11762,9 +11621,9 @@
 emiratesislamic.ae/en/person…</t>
         </is>
       </c>
-      <c r="Y70" t="inlineStr"/>
-      <c r="Z70" t="inlineStr"/>
-      <c r="AA70" t="inlineStr">
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr">
         <is>
           <t>Scam messages often come from random or international numbers - not official IDs.
 Do not fall for the traps. Stay alert to scams.
@@ -11773,7 +11632,7 @@
 emiratesislamic.ae/en/person…</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
+      <c r="AB69" t="inlineStr">
         <is>
           <t>Scam messages often come from random or international numbers - not official IDs.
 Do not fall for the traps. Stay alert to scams.
@@ -11782,87 +11641,87 @@
 emiratesislamic.ae/en/person…</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
+      <c r="AC69" t="inlineStr">
         <is>
           <t>Bank</t>
         </is>
       </c>
-      <c r="AD70" t="inlineStr">
+      <c r="AD69" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="AE70" s="2" t="n">
+      <c r="AE69" s="2" t="n">
         <v>46142.41666666666</v>
       </c>
-      <c r="AF70" s="2" t="n">
+      <c r="AF69" s="2" t="n">
         <v>46142</v>
       </c>
-      <c r="AG70" t="inlineStr">
+      <c r="AG69" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="AH70" t="inlineStr">
+      <c r="AH69" t="inlineStr">
         <is>
           <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
-      <c r="AI70" t="inlineStr">
+      <c r="AI69" t="inlineStr">
         <is>
           <t>Scam messages often come from random or international numbers - not official IDs. • #EIAgainstFraud with Emirates Islamic. • #TogetherAgainstFraud emiratesislamic.ae/en/person…</t>
         </is>
       </c>
-      <c r="AJ70" t="inlineStr">
+      <c r="AJ69" t="inlineStr">
         <is>
           <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
-      <c r="AK70" t="n">
+      <c r="AK69" t="n">
         <v>2026</v>
       </c>
-      <c r="AL70" t="inlineStr">
+      <c r="AL69" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="1" t="n">
-        <v>69</v>
-      </c>
-      <c r="B71" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" t="inlineStr">
         <is>
           <t>2049775771418308967</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2049775771418308967</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr">
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
         <is>
           <t>⭐️Shariah-compliant offering
 ⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
@@ -11871,7 +11730,7 @@
 emiratesislamic.ae/en/person…</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>⭐️Shariah-compliant offering
 ⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
@@ -11880,48 +11739,48 @@
 &lt;a href="https://www.emiratesislamic.ae/en/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organic-linkedin&amp;amp;utm_medium=social&amp;amp;utm_campaign=psb_wealth"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K71" t="b">
-        <v>0</v>
-      </c>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr">
+      <c r="K70" t="b">
+        <v>0</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
         <is>
           <t>18h</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t>Apr 30, 2026 · 9:00 AM UTC</t>
         </is>
       </c>
-      <c r="P71" s="2" t="n">
+      <c r="P70" s="2" t="n">
         <v>46142.375</v>
       </c>
-      <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="inlineStr">
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr">
         <is>
           <t>['https://www.emiratesislamic.ae/en/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organic-linkedin&amp;utm_medium=social&amp;utm_campaign=psb_wealth']</t>
         </is>
       </c>
-      <c r="S71" t="n">
-        <v>0</v>
-      </c>
-      <c r="T71" t="n">
-        <v>0</v>
-      </c>
-      <c r="U71" t="n">
-        <v>0</v>
-      </c>
-      <c r="V71" t="n">
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" t="n">
         <v>44</v>
       </c>
-      <c r="W71" t="inlineStr">
+      <c r="W70" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>⭐️Shariah-compliant offering
 ⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
@@ -11930,9 +11789,9 @@
 emiratesislamic.ae/en/person…</t>
         </is>
       </c>
-      <c r="Y71" t="inlineStr"/>
-      <c r="Z71" t="inlineStr"/>
-      <c r="AA71" t="inlineStr">
+      <c r="Y70" t="inlineStr"/>
+      <c r="Z70" t="inlineStr"/>
+      <c r="AA70" t="inlineStr">
         <is>
           <t>⭐️Shariah-compliant offering
 ⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
@@ -11941,92 +11800,92 @@
 emiratesislamic.ae/en/person…</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
+      <c r="AB70" t="inlineStr">
         <is>
           <t>Shariah-compliant offering Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards Certified silver bars compliant with UAE Good Delivery (UAE GD) standards Terms and conditions apply.</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
+      <c r="AC70" t="inlineStr">
         <is>
           <t>Bank</t>
         </is>
       </c>
-      <c r="AD71" t="inlineStr">
+      <c r="AD70" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="AE71" s="2" t="n">
+      <c r="AE70" s="2" t="n">
         <v>46142.54166666666</v>
       </c>
-      <c r="AF71" s="2" t="n">
+      <c r="AF70" s="2" t="n">
         <v>46142</v>
       </c>
-      <c r="AG71" t="inlineStr">
+      <c r="AG70" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="AH71" t="inlineStr">
+      <c r="AH70" t="inlineStr">
         <is>
           <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
-      <c r="AI71" t="inlineStr">
+      <c r="AI70" t="inlineStr">
         <is>
           <t>Shariah-compliant offering Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery …</t>
         </is>
       </c>
-      <c r="AJ71" t="inlineStr">
+      <c r="AJ70" t="inlineStr">
         <is>
           <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
-      <c r="AK71" t="n">
+      <c r="AK70" t="n">
         <v>2026</v>
       </c>
-      <c r="AL71" t="inlineStr">
+      <c r="AL70" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="1" t="n">
-        <v>70</v>
-      </c>
-      <c r="B72" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" t="inlineStr">
         <is>
           <t>2049775771397288351</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2049775771397288351</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr">
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
         <is>
           <t>⭐️منتج متوافق مع أحكام الشريعة الإسلامية
 ⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
@@ -12035,7 +11894,7 @@
 emiratesislamic.ae/ar/person…</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>⭐️منتج متوافق مع أحكام الشريعة الإسلامية
 ⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
@@ -12044,48 +11903,48 @@
 &lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organiic-twitter&amp;amp;utm_medium=socal&amp;amp;utm_campaign=psb_wealth"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K72" t="b">
-        <v>0</v>
-      </c>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr">
+      <c r="K71" t="b">
+        <v>0</v>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
         <is>
           <t>18h</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr">
+      <c r="O71" t="inlineStr">
         <is>
           <t>Apr 30, 2026 · 9:00 AM UTC</t>
         </is>
       </c>
-      <c r="P72" s="2" t="n">
+      <c r="P71" s="2" t="n">
         <v>46142.375</v>
       </c>
-      <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="inlineStr">
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr">
         <is>
           <t>['https://www.emiratesislamic.ae/ar/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organiic-twitter&amp;utm_medium=socal&amp;utm_campaign=psb_wealth']</t>
         </is>
       </c>
-      <c r="S72" t="n">
-        <v>0</v>
-      </c>
-      <c r="T72" t="n">
-        <v>0</v>
-      </c>
-      <c r="U72" t="n">
-        <v>0</v>
-      </c>
-      <c r="V72" t="n">
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" t="n">
         <v>56</v>
       </c>
-      <c r="W72" t="inlineStr">
+      <c r="W71" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>⭐️منتج متوافق مع أحكام الشريعة الإسلامية
 ⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
@@ -12094,9 +11953,9 @@
 emiratesislamic.ae/ar/person…</t>
         </is>
       </c>
-      <c r="Y72" t="inlineStr"/>
-      <c r="Z72" t="inlineStr"/>
-      <c r="AA72" t="inlineStr">
+      <c r="Y71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr"/>
+      <c r="AA71" t="inlineStr">
         <is>
           <t>⭐️منتج متوافق مع أحكام الشريعة الإسلامية
 ⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
@@ -12105,7 +11964,7 @@
 emiratesislamic.ae/ar/person…</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
+      <c r="AB71" t="inlineStr">
         <is>
           <t>⭐️Product compliant with Islamic law
 ⭐️Gold bars certified and compliant with the standards of the London Bullion Market Association and Dubai Good Delivery
@@ -12113,6 +11972,159 @@
 Terms and conditions apply.</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE71" s="2" t="n">
+        <v>46142.54166666666</v>
+      </c>
+      <c r="AF71" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>2. Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>⭐️Product compliant with Islamic law ⭐️Gold bars certified and compliant with the standards of the London Bullion Market…</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AK71" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL71" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2049775768025137608</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2049775768025137608</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
+EI + للخدمات المصرفية عبر الهاتف المتحرك
+⭐️ادخل إلى منصة "الثروات" في تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
+EI + للخدمات المصرفية عبر الهاتف المتحرك
+⭐️ادخل إلى منصة &amp;#34;الثروات&amp;#34; في تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.</t>
+        </is>
+      </c>
+      <c r="K72" t="b">
+        <v>0</v>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Apr 30, 2026 · 9:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="n">
+        <v>46142.375</v>
+      </c>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="n">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" t="n">
+        <v>2</v>
+      </c>
+      <c r="V72" t="n">
+        <v>53</v>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
+EI + للخدمات المصرفية عبر الهاتف المتحرك
+⭐️ادخل إلى منصة "الثروات" في تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr"/>
+      <c r="Z72" t="inlineStr"/>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
+EI + للخدمات المصرفية عبر الهاتف المتحرك
+⭐️ادخل إلى منصة "الثروات" في تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>Invest in gold and silver digitally and easily on the EI+ mobile banking app. 
+⭐️Access the "Wealth" platform in the EI+ mobile banking app and start investing with complete ease and security.</t>
+        </is>
+      </c>
       <c r="AC72" t="inlineStr">
         <is>
           <t>Bank</t>
@@ -12120,7 +12132,7 @@
       </c>
       <c r="AD72" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE72" s="2" t="n">
@@ -12141,7 +12153,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>⭐️Product compliant with Islamic law ⭐️Gold bars certified and compliant with the standards of the London Bullion Market…</t>
+          <t>⭐️Access the "Wealth" platform in the EI+ mobile banking app and start investing with complete ease and security. • Invest in gold and silver digitally and easily on the EI+ mobile banking app.</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
@@ -12164,12 +12176,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2049775768025137608</t>
+          <t>2049775767735722193</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2049775768025137608</t>
+          <t>https://x.com/emiratesislamic/status/2049775767735722193</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12195,16 +12207,14 @@
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
-          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
-EI + للخدمات المصرفية عبر الهاتف المتحرك
-⭐️ادخل إلى منصة "الثروات" في تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان. https://t.co/LsfzdBKINN</t>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
-EI + للخدمات المصرفية عبر الهاتف المتحرك
-⭐️ادخل إلى منصة &amp;#34;الثروات&amp;#34; في تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.</t>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.</t>
         </is>
       </c>
       <c r="K73" t="b">
@@ -12234,10 +12244,10 @@
         <v>0</v>
       </c>
       <c r="U73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V73" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="W73" t="inlineStr">
         <is>
@@ -12246,34 +12256,22 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
-EI + للخدمات المصرفية عبر الهاتف المتحرك
-⭐️ادخل إلى منصة "الثروات" في تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2049775768025137608</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
-EI + للخدمات المصرفية عبر الهاتف المتحرك
-⭐️ادخل إلى منصة "الثروات" في تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان. https://t.co/LsfzdBKINN</t>
-        </is>
-      </c>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr"/>
+      <c r="Z73" t="inlineStr"/>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
-EI + للخدمات المصرفية عبر الهاتف المتحرك
-⭐️ادخل إلى منصة "الثروات" في تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان. https://t.co/LsfzdBKINN</t>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>Invest in gold and silver digitally and easily on the EI+ mobile banking app. 
-⭐️Access the "Wealth" platform in the EI+ mobile banking app and start investing with complete ease and security.</t>
+          <t>Invest in gold and silver easily and digitally with the EI + Mobile Banking App. 
+Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
@@ -12304,7 +12302,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>⭐️Access the "Wealth" platform in the EI+ mobile banking app and start investing with complete ease and security. • Invest in gold and silver digitally and easily on the EI+ mobile banking app.</t>
+          <t>Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly. • Invest in gold and silver easily and digitally with the EI + Mobile Banking App.</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
@@ -12327,12 +12325,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2049775767735722193</t>
+          <t>2049764863933649269</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2049775767735722193</t>
+          <t>https://x.com/emiratesislamic/status/2049764863933649269</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12358,41 +12356,40 @@
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
-          <t>⭐️Shariah-compliant offering
-⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
-⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
-Terms and conditions apply.
-https://t.co/oqJQgZ2H6v</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
-⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
         </is>
       </c>
       <c r="K74" t="b">
         <v>0</v>
       </c>
       <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>['murtazaali2101']</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 · 9:00 AM UTC</t>
+          <t>Apr 30, 2026 · 8:16 AM UTC</t>
         </is>
       </c>
       <c r="P74" s="2" t="n">
-        <v>46142.375</v>
+        <v>46142.34444444445</v>
       </c>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T74" t="n">
         <v>0</v>
@@ -12401,7 +12398,7 @@
         <v>1</v>
       </c>
       <c r="V74" t="n">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="W74" t="inlineStr">
         <is>
@@ -12410,41 +12407,24 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
-⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2049775767735722193</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>⭐️Shariah-compliant offering
-⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
-⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
-Terms and conditions apply.
-https://t.co/oqJQgZ2H6v</t>
-        </is>
-      </c>
+          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr"/>
+      <c r="Z74" t="inlineStr"/>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>⭐️Shariah-compliant offering
-⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
-⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
-Terms and conditions apply.
-https://t.co/oqJQgZ2H6v</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>Shariah-compliant offering Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards Certified silver bars compliant with UAE Good Delivery (UAE GD) standards Terms and conditions apply.</t>
+          <t>Dear customer, we will connect with you through private messaging to serve you better.</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Cust</t>
         </is>
       </c>
       <c r="AD74" t="inlineStr">
@@ -12453,7 +12433,7 @@
         </is>
       </c>
       <c r="AE74" s="2" t="n">
-        <v>46142.54166666666</v>
+        <v>46142.51111111111</v>
       </c>
       <c r="AF74" s="2" t="n">
         <v>46142</v>
@@ -12470,7 +12450,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>Shariah-compliant offering Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery …</t>
+          <t>Dear customer, we will connect with you through private messaging to serve you better.</t>
         </is>
       </c>
       <c r="AJ74" t="inlineStr">
@@ -12483,7 +12463,7 @@
       </c>
       <c r="AL74" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>murtazaali2101</t>
         </is>
       </c>
     </row>
@@ -12525,7 +12505,7 @@
       <c r="I75" t="inlineStr">
         <is>
           <t>رتّب التزاماتك حسب الأولوية وابدأ بالأصغر، ثم تقدّم تدريجياً نحو الأكبر، فليس عليك إنهاء كل شيء دفعة واحدة، الأهم أن تبدأ.
-#الإمارات_الإسلامي https://t.co/8zwjHWfzM3</t>
+#الإمارات_الإسلامي</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -12581,26 +12561,17 @@
 #الإمارات_الإسلامي</t>
         </is>
       </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2049745576544084269</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
+      <c r="Y75" t="inlineStr"/>
+      <c r="Z75" t="inlineStr"/>
+      <c r="AA75" t="inlineStr">
         <is>
           <t>رتّب التزاماتك حسب الأولوية وابدأ بالأصغر، ثم تقدّم تدريجياً نحو الأكبر، فليس عليك إنهاء كل شيء دفعة واحدة، الأهم أن تبدأ.
-#الإمارات_الإسلامي https://t.co/8zwjHWfzM3</t>
-        </is>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>رتّب التزاماتك حسب الأولوية وابدأ بالأصغر، ثم تقدّم تدريجياً نحو الأكبر، فليس عليك إنهاء كل شيء دفعة واحدة، الأهم أن تبدأ.
-#الإمارات_الإسلامي https://t.co/8zwjHWfzM3</t>
+#الإمارات_الإسلامي</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>Organize your commitments by priority and start with the smallest, then gradually move towards the larger ones. You don't have to finish everything at once; the important thing is to start.</t>
+          <t>Organize your commitments by priority and start with the smallest, then gradually move on to the larger ones. You don't have to finish everything at once; the important thing is to start.</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
@@ -12631,7 +12602,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>Organize your commitments by priority and start with the smallest, then gradually move towards the larger ones. • You don't have to finish everything at once; the important thing is to start.</t>
+          <t>Organize your commitments by priority and start with the smallest, then gradually move on to the larger ones. • You don't have to finish everything at once; the important thing is to start.</t>
         </is>
       </c>
       <c r="AJ75" t="inlineStr">
@@ -12687,7 +12658,7 @@
         <is>
           <t>هل تنفق مقابل أمور لا تستخدمها؟
 #نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-https://t.co/mgtIcQsyLZ</t>
+emiratesislamic.ae/ar/key-in…</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -12745,23 +12716,13 @@
 emiratesislamic.ae/ar/key-in…</t>
         </is>
       </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2049730468619108404</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
+      <c r="Y76" t="inlineStr"/>
+      <c r="Z76" t="inlineStr"/>
+      <c r="AA76" t="inlineStr">
         <is>
           <t>هل تنفق مقابل أمور لا تستخدمها؟
 #نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-https://t.co/mgtIcQsyLZ</t>
-        </is>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>هل تنفق مقابل أمور لا تستخدمها؟
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-https://t.co/mgtIcQsyLZ</t>
+emiratesislamic.ae/ar/key-in…</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
@@ -12937,7 +12898,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>Fraud messages often come from random or international numbers and are not from official sources with a trusted identity.
+          <t>Fraud messages often come from random or international numbers, and not from official entities with a trusted identity.
 Don't fall into the trap. Beware of fraud.
 #United_Against_Fraud with Emirates Islamic.</t>
         </is>
@@ -12970,7 +12931,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>Fraud messages often come from random or international numbers and are not from official sources with a trusted identity. • #United_Against_Fraud with Emirates Islamic. • Don't fall into the trap.</t>
+          <t>Fraud messages often come from random or international numbers, and not from official entities with a trusted identity. • #United_Against_Fraud with Emirates Islamic. • Don't fall into the trap.</t>
         </is>
       </c>
       <c r="AJ77" t="inlineStr">
@@ -13091,7 +13052,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>The last thing I expected from a bank like this, which is well-known, is that my account has been frozen for 3 days without any reason. When I contact them, they say there is no response from management! Every time I speak to a different employee, one tells me a different timeframe; one says one business day, another says 20 hours, and the third says they have no idea!!! This is how a bank operates while I have commitments and expenses!</t>
+          <t>The last thing I expected from a bank like this is that my account has been frozen for 3 days without any reason, and when I contact them, they say there is no response from management!! Every time I speak to an employee, one tells me a different timeframe; one says one business day, another says 20 hours, and the third says they have no idea!!! This is how a bank operates while I have commitments and expenses!!</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
@@ -13122,7 +13083,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>Every time I speak to a different employee, one tells me a different timeframe; one says one business day, another says 20 hours, and the third says they have no idea!!! • The last thing I expected from a bank like this, which is well-known, is that my account has been frozen for 3 days without any reason. • This is how a bank operates while I have commitments and expenses!</t>
+          <t>Every time I speak to an employee, one tells me a different timeframe; one says one business day, another says 20 hours, and the third says they have no idea!!! • The last thing I expected from a bank like this is that my account has been frozen for 3 days without any reason, and when I contact them, they say there is no response from management!! • This is how a bank operates while I have commitments and expenses!!</t>
         </is>
       </c>
       <c r="AJ78" t="inlineStr">
@@ -13145,12 +13106,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2049927131657081284</t>
+          <t>2049758371734229151</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis/status/2049927131657081284</t>
+          <t>https://x.com/STKgenghis/status/2049758371734229151</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -13176,12 +13137,16 @@
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Right. So its now almost 14 days with credit card not functioning.</t>
+          <t>So once again routed to the 'team'. 
+I will soon travel and will not be able to use my credit card through no fault of my own. 
+Why should a customer with a 40 year track record of no loans and good credit standing trust a bank that doesnt value the relationship?</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Right. So its now almost 14 days with credit card not functioning.</t>
+          <t>So once again routed to the &amp;#39;team&amp;#39;. 
+I will soon travel and will not be able to use my credit card through no fault of my own. 
+Why should a customer with a 40 year track record of no loans and good credit standing trust a bank that doesnt value the relationship?</t>
         </is>
       </c>
       <c r="K79" t="b">
@@ -13195,30 +13160,30 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>8h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 · 7:01 PM UTC</t>
+          <t>Apr 30, 2026 · 7:50 AM UTC</t>
         </is>
       </c>
       <c r="P79" s="2" t="n">
-        <v>46142.79236111111</v>
+        <v>46142.32638888889</v>
       </c>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V79" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="W79" t="inlineStr">
         <is>
@@ -13227,19 +13192,25 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Right. So its now almost 14 days with credit card not functioning.</t>
+          <t>So once again routed to the 'team'. 
+I will soon travel and will not be able to use my credit card through no fault of my own. 
+Why should a customer with a 40 year track record of no loans and good credit standing trust a bank that doesnt value the relationship?</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr"/>
       <c r="Z79" t="inlineStr"/>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>Right. So its now almost 14 days with credit card not functioning.</t>
+          <t>So once again routed to the 'team'. 
+I will soon travel and will not be able to use my credit card through no fault of my own. 
+Why should a customer with a 40 year track record of no loans and good credit standing trust a bank that doesnt value the relationship?</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>Right. So it's now almost 14 days with the credit card not functioning.</t>
+          <t>So once again routed to the 'team'. 
+I will soon travel and will not be able to use my credit card through no fault of my own. 
+Why should a customer with a 40-year track record of no loans and good credit standing trust a bank that doesn't value the relationship?</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
@@ -13253,7 +13224,7 @@
         </is>
       </c>
       <c r="AE79" s="2" t="n">
-        <v>46142.95902777778</v>
+        <v>46142.49305555555</v>
       </c>
       <c r="AF79" s="2" t="n">
         <v>46142</v>
@@ -13270,7 +13241,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>So it's now almost 14 days with the credit card not functioning.</t>
+          <t>Why should a customer with a 40-year track record of no loans and good credit standing trust a bank that doesn't value the relationship? • I will soon travel and will not be able to use my credit card through no fault of my own. • So once again routed to the 'team'.</t>
         </is>
       </c>
       <c r="AJ79" t="inlineStr">
@@ -13526,8 +13497,16 @@
           <t>@emiratesislamic I have been a client for over 10 years. I have never had any problem paying my mortgages or loans. All my loans never exceeded 30% of my old salary, and with my new salary they do not reach 15%. Most of my loans were cleared before the due date. Over 2 weeks ago, I applied for a small amount and every day the verification department asks for new requirements. My salary is deposited every month, and I have never missed any payment. The branch manager and customer service have done everything they can, but your back office is still making it difficult. When I apply via phone, the transaction goes smoothly, but every time I apply from the branch, the main office creates problems. Why??? I really regret not transferring to another bank that respects customers more.</t>
         </is>
       </c>
-      <c r="Y81" t="inlineStr"/>
-      <c r="Z81" t="inlineStr"/>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>https://x.com/alnuaimi1979/status/2049808521357914559</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>@emiratesislamic I have been a client for over 10 years. I have never had any problem paying my mortgages or loans. All my loans never exceeded 30% of my old salary, and with my new salary they do not reach 15%. Most of my loans were cleared before the due date. Over 2 weeks ago, I applied for a small amount and every day the verification department asks for new requirements. My salary is deposited every month, and I have never missed any payment. The branch manager and customer service have done everything they can, but your back office is still making it difficult. When I apply via phone, the transaction goes smoothly, but every time I apply from the branch, the main office creates problems. Why??? I really regret not transferring to another bank that respects customers more.</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>@emiratesislamic I have been a client for over 10 years. I have never had any problem paying my mortgages or loans. All my loans never exceeded 30% of my old salary, and with my new salary they do not reach 15%. Most of my loans were cleared before the due date. Over 2 weeks ago, I applied for a small amount and every day the verification department asks for new requirements. My salary is deposited every month, and I have never missed any payment. The branch manager and customer service have done everything they can, but your back office is still making it difficult. When I apply via phone, the transaction goes smoothly, but every time I apply from the branch, the main office creates problems. Why??? I really regret not transferring to another bank that respects customers more.</t>
@@ -13978,24 +13957,16 @@
           <t>@OfficialADCB  dear team, i had submitted the no liability letter from ENBD. Still the fund is not credited in my account. Rent Cheque is deposited and the account is negative now. 0551746879 pls take immediate action</t>
         </is>
       </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>https://x.com/jibinsymphony/status/2049728649910497496</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
+      <c r="Y84" t="inlineStr"/>
+      <c r="Z84" t="inlineStr"/>
+      <c r="AA84" t="inlineStr">
         <is>
           <t>@OfficialADCB  dear team, i had submitted the no liability letter from ENBD. Still the fund is not credited in my account. Rent Cheque is deposited and the account is negative now. 0551746879 pls take immediate action</t>
         </is>
       </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>@OfficialADCB  dear team, i had submitted the no liability letter from ENBD. Still the fund is not credited in my account. Rent Cheque is deposited and the account is negative now. 0551746879 pls take immediate action</t>
-        </is>
-      </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>Dear team, I submitted the no liability letter from ENBD. Still, the funds have not been credited to my account. The rent cheque has been deposited, and the account is now negative. Please take immediate action.</t>
+          <t>Dear team, I submitted the no liability letter from ENBD. Still, the fund has not been credited to my account. The rent cheque has been deposited, and the account is now negative. Please take immediate action.</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
@@ -14026,7 +13997,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>The rent cheque has been deposited, and the account is now negative. • Dear team, I submitted the no liability letter from ENBD. • Still, the funds have not been credited to my account.</t>
+          <t>The rent cheque has been deposited, and the account is now negative. • Still, the fund has not been credited to my account. • Dear team, I submitted the no liability letter from ENBD.</t>
         </is>
       </c>
       <c r="AJ84" t="inlineStr">
@@ -14080,7 +14051,7 @@
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
-          <t>@emiratesislamic unable to update my passport details on the website, the page keeps loading kindly assist</t>
+          <t>@emiratesislamic unable to update my passport details on the website, the page keeps loading kindly assist https://t.co/wq3X2I5DVm</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -14134,11 +14105,19 @@
           <t>@emiratesislamic unable to update my passport details on the website, the page keeps loading kindly assist</t>
         </is>
       </c>
-      <c r="Y85" t="inlineStr"/>
-      <c r="Z85" t="inlineStr"/>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>https://x.com/murtazaali2101/status/2049751774542848395</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>@emiratesislamic unable to update my passport details on the website, the page keeps loading kindly assist https://t.co/wq3X2I5DVm</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>@emiratesislamic unable to update my passport details on the website, the page keeps loading kindly assist</t>
+          <t>@emiratesislamic unable to update my passport details on the website, the page keeps loading kindly assist https://t.co/wq3X2I5DVm</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
@@ -14228,7 +14207,7 @@
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE pls note have reached out twice to CS Team, registered complaint on portal plus addressing system glitch while booking a service. Expected response is to support client with booking with manual intervention since there is known system constraint.</t>
+          <t>Instead as a response I have been offered to book with reducing interest while eligible to book at 0%. Customer are often asked to share their feedback so please help me understand how would you rate this. Evidently this has not come to rightful attention.</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -14285,17 +14264,17 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE pls note have reached out twice to CS Team, registered complaint on portal plus addressing system glitch while booking a service. Expected response is to support client with booking with manual intervention since there is known system constraint.</t>
+          <t>Instead as a response I have been offered to book with reducing interest while eligible to book at 0%. Customer are often asked to share their feedback so please help me understand how would you rate this. Evidently this has not come to rightful attention.</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE pls note have reached out twice to CS Team, registered complaint on portal plus addressing system glitch while booking a service. Expected response is to support client with booking with manual intervention since there is known system constraint.</t>
+          <t>Instead as a response I have been offered to book with reducing interest while eligible to book at 0%. Customer are often asked to share their feedback so please help me understand how would you rate this. Evidently this has not come to rightful attention.</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>Please note that I have reached out twice to the Customer Service Team, registered a complaint on the portal, and addressed a system glitch while booking a service. The expected response is to support the client with the booking through manual intervention since there is a known system constraint.</t>
+          <t>Instead, as a response, I have been offered to book with reduced interest while being eligible to book at 0%. Customers are often asked to share their feedback, so please help me understand how you would rate this. Evidently, this has not received the attention it deserves.</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
@@ -14326,7 +14305,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Please note that I have reached out twice to the Customer Service Team, registered a complaint on the portal, and addressed a system glitch while booking a service. • The expected response is to support the client with the booking through manual intervention since there is a known system constraint.</t>
+          <t>Instead, as a response, I have been offered to book with reduced interest while being eligible to book at 0%. • Customers are often asked to share their feedback, so please help me understand how you would rate this. • Evidently, this has not received the attention it deserves.</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
@@ -14430,16 +14409,8 @@
           <t>ENBD portal literally loads like you’re porting yourself to another universe 💫</t>
         </is>
       </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>https://x.com/safakayani1/status/2049806132303258013</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>ENBD portal literally loads like you’re porting yourself to another universe 💫</t>
-        </is>
-      </c>
+      <c r="Y87" t="inlineStr"/>
+      <c r="Z87" t="inlineStr"/>
       <c r="AA87" t="inlineStr">
         <is>
           <t>ENBD portal literally loads like you’re porting yourself to another universe 💫</t>

--- a/check2.xlsx
+++ b/check2.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL26"/>
+  <dimension ref="A1:AL27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -754,7 +754,7 @@
           <t>Do you have a credit card from Alinma Bank? 
 Today, the statement for credit cards has been issued. 
 Two important tips: 
-* Pay the total amount due. (Be careful not to pay only the minimum amount) 
+* Pay the total amount due. (Beware of paying only the minimum amount) 
 ** Pay before the due date of May 25, 2026.</t>
         </is>
       </c>
@@ -786,7 +786,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>(Be careful not to pay only the minimum amount) ** Pay before the due date of May 25, 2026. • Two important tips: * Pay the total amount due. • Today, the statement for credit cards has been issued.</t>
+          <t>(Beware of paying only the minimum amount) ** Pay before the due date of May 25, 2026. • Two important tips: * Pay the total amount due. • Today, the statement for credit cards has been issued.</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -991,6 +991,71 @@
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
+        <is>
+          <t>A great shortcut tool to analyse your mutual fund portfolio:- 
+The test takes 30 seconds: 
+Open your fund’s factsheet. If 60-70%+ of the portfolio is concentrated in the top 15-20 stocks by market cap (HDFC Bank, Reliance, TCS, ICICI, Infosys, SBI etc.) 
+Then you’re actively paying fees for what is effectively a Nifty 50 ETF. 
+Even despite such holdings, 76% of large cap funds have failed to beat the index over a 10 year period. 
+84% over five years. 
+The solution is also fairly simple:- 
+You can consider switching these to a low cost Nifty 50 ETF and pocket the TER expense. 
+Incase you need help with your portfolio, feel free to reach out to me.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>In the last 6-12 months:
+1. Emirates NBD Bank has acquired a controlling stake (54%) in RBL Bank
+2. IHC (International Holding Company, Abu Dhabi) has acquired a 41.5% stake in Sammaan Capital, with a mandatory open offer for an additional 26%, which could take IHC&amp;#39;s total stake to ~63-67% on a fully diluted basis.
+3. Sumitomo Mitsui Banking Corporation (SMBC) bought a 24.2% stake in Yes Bank
+4. Mitsubishi UFJ Financial Group (MUFG) Bank acquired a 20% stake in Shriram Finance
+FIIs must be net sellers but select foreign institutions are clearly positioning to capitalise on India&amp;#39;s long term credit growth thesis.
+&lt;a href="/search?f=tweets&amp;amp;q=%23Banking"&gt;#Banking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23NBFC"&gt;#NBFC&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23NSE"&gt;#NSE&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>9h</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>May 2, 2026 · 5:53 PM UTC</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>46144.74513888889</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23Banking', 'https://x.com/search?f=tweets&amp;q=%23NBFC', 'https://x.com/search?f=tweets&amp;q=%23NSE']</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
+      </c>
+      <c r="V4" t="n">
+        <v>59</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>In the last 6-12 months:
 1. Emirates NBD Bank has acquired a controlling stake (54%) in RBL Bank
@@ -1001,90 +1066,48 @@
 #Banking #NBFC #NSE</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>In the last 6-12 months:
-1. Emirates NBD Bank has acquired a controlling stake (54%) in RBL Bank
-2. IHC (International Holding Company, Abu Dhabi) has acquired a 41.5% stake in Sammaan Capital, with a mandatory open offer for an additional 26%, which could take IHC&amp;#39;s total stake to ~63-67% on a fully diluted basis.
-3. Sumitomo Mitsui Banking Corporation (SMBC) bought a 24.2% stake in Yes Bank
-4. Mitsubishi UFJ Financial Group (MUFG) Bank acquired a 20% stake in Shriram Finance
-FIIs must be net sellers but select foreign institutions are clearly positioning to capitalise on India&amp;#39;s long term credit growth thesis.
-&lt;a href="/search?f=tweets&amp;amp;q=%23Banking"&gt;#Banking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23NBFC"&gt;#NBFC&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23NSE"&gt;#NSE&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>9h</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>May 2, 2026 · 5:53 PM UTC</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="n">
-        <v>46144.74513888889</v>
-      </c>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23Banking', 'https://x.com/search?f=tweets&amp;q=%23NBFC', 'https://x.com/search?f=tweets&amp;q=%23NSE']</t>
-        </is>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2</v>
-      </c>
-      <c r="V4" t="n">
-        <v>59</v>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>In the last 6-12 months:
-1. Emirates NBD Bank has acquired a controlling stake (54%) in RBL Bank
-2. IHC (International Holding Company, Abu Dhabi) has acquired a 41.5% stake in Sammaan Capital, with a mandatory open offer for an additional 26%, which could take IHC's total stake to ~63-67% on a fully diluted basis.
-3. Sumitomo Mitsui Banking Corporation (SMBC) bought a 24.2% stake in Yes Bank
-4. Mitsubishi UFJ Financial Group (MUFG) Bank acquired a 20% stake in Shriram Finance
-FIIs must be net sellers but select foreign institutions are clearly positioning to capitalise on India's long term credit growth thesis.
-#Banking #NBFC #NSE</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>https://x.com/VedantKabra19/status/2050634843697152368</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>A great shortcut tool to analyse your mutual fund portfolio:- 
+The test takes 30 seconds: 
+Open your fund’s factsheet. If 60-70%+ of the portfolio is concentrated in the top 15-20 stocks by market cap (HDFC Bank, Reliance, TCS, ICICI, Infosys, SBI etc.) 
+Then you’re actively paying fees for what is effectively a Nifty 50 ETF. 
+Even despite such holdings, 76% of large cap funds have failed to beat the index over a 10 year period. 
+84% over five years. 
+The solution is also fairly simple:- 
+You can consider switching these to a low cost Nifty 50 ETF and pocket the TER expense. 
+Incase you need help with your portfolio, feel free to reach out to me.</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>In the last 6-12 months:
-1. Emirates NBD Bank has acquired a controlling stake (54%) in RBL Bank
-2. IHC (International Holding Company, Abu Dhabi) has acquired a 41.5% stake in Sammaan Capital, with a mandatory open offer for an additional 26%, which could take IHC's total stake to ~63-67% on a fully diluted basis.
-3. Sumitomo Mitsui Banking Corporation (SMBC) bought a 24.2% stake in Yes Bank
-4. Mitsubishi UFJ Financial Group (MUFG) Bank acquired a 20% stake in Shriram Finance
-FIIs must be net sellers but select foreign institutions are clearly positioning to capitalise on India's long term credit growth thesis.
-#Banking #NBFC #NSE</t>
+          <t>A great shortcut tool to analyse your mutual fund portfolio:- 
+The test takes 30 seconds: 
+Open your fund’s factsheet. If 60-70%+ of the portfolio is concentrated in the top 15-20 stocks by market cap (HDFC Bank, Reliance, TCS, ICICI, Infosys, SBI etc.) 
+Then you’re actively paying fees for what is effectively a Nifty 50 ETF. 
+Even despite such holdings, 76% of large cap funds have failed to beat the index over a 10 year period. 
+84% over five years. 
+The solution is also fairly simple:- 
+You can consider switching these to a low cost Nifty 50 ETF and pocket the TER expense. 
+Incase you need help with your portfolio, feel free to reach out to me.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>In the last 6-12 months:
-1. Emirates NBD Bank has acquired a controlling stake (54%) in RBL Bank.
-2. IHC (International Holding Company, Abu Dhabi) has acquired a 41.5% stake in Sammaan Capital, with a mandatory open offer for an additional 26%, which could take IHC's total stake to approximately 63-67% on a fully diluted basis.
-3. Sumitomo Mitsui Banking Corporation (SMBC) bought a 24.2% stake in Yes Bank.
-4. Mitsubishi UFJ Financial Group (MUFG) Bank acquired a 20% stake in Shriram Finance.
-Foreign Institutional Investors (FIIs) must be net sellers, but select foreign institutions are clearly positioning to capitalize on India's long-term credit growth thesis.</t>
+          <t>A great shortcut tool to analyze your mutual fund portfolio: 
+The test takes 30 seconds: 
+Open your fund’s factsheet. If 60-70%+ of the portfolio is concentrated in the top 15-20 stocks by market cap (HDFC Bank, Reliance, TCS, ICICI, Infosys, SBI, etc.) 
+Then you’re actively paying fees for what is effectively a Nifty 50 ETF. 
+Even despite such holdings, 76% of large cap funds have failed to beat the index over a 10-year period. 
+84% over five years. 
+The solution is also fairly simple: 
+You can consider switching these to a low-cost Nifty 50 ETF and pocket the TER expense. 
+In case you need help with your portfolio, feel free to reach out to me.</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1115,7 +1138,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank has acquired a controlling stake (54%) in RBL Bank. • Mitsubishi UFJ Financial Group (MUFG) Bank acquired a 20% stake in Shriram Finance. • Foreign Institutional Investors (FIIs) must be net sellers, but select foreign institutions are clearly positioning to capitalize on India's long-term credit growth thesis.</t>
+          <t>Even despite such holdings, 76% of large cap funds have failed to beat the index over a 10-year period. • A great shortcut tool to analyze your mutual fund portfolio: The test takes 30 seconds: Open your fund’s factsheet. • The solution is also fairly simple: You can consider switching these to a low-cost Nifty 50 ETF and pocket the TER expense.</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1250,7 +1273,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Emirates NBD is proud to participate in the Neurovirus Race in Celia, the new administrative capital. 
+          <t>Emirates NBD is proud to participate in the Neurovirus Race in Celia, the New Administrative Capital. 
 We run together to raise awareness about neurodiversity, including autism, attention deficit hyperactivity disorder (ADHD), dyslexia, and other mental differences, as every step brings us closer to a more inclusive, understanding, and empowering community. 
 Tax registration number: 319-897-204</t>
         </is>
@@ -1283,7 +1306,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Tax registration number: 319-897-204 • Emirates NBD is proud to participate in the Neurovirus Race in Celia, the new administrative capital.</t>
+          <t>Tax registration number: 319-897-204 • Emirates NBD is proud to participate in the Neurovirus Race in Celia, the New Administrative Capital.</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1340,7 +1363,7 @@
           <t>عندك بطاقات بنك الإمارات دبي الوطني ؟ العرض من نصيبك 😎
 تذكرة عليك والثانية مجانًا في #ڤوكس_سينما 
 للحجز ولتفاصيل اكثر,  اضغط على الرابط 👇
-tps://ksa.voxcinemas.com/ar/ticket-offer/emirates-nbd https://t.co/96UbGdATfB</t>
+tps://ksa.voxcinemas.com/ar/ticket-offer/emirates-nbd</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1400,32 +1423,21 @@
 tps://ksa.voxcinemas.com/ar/ticket-offer/emirates-nbd</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>https://x.com/VOX_Cinemas_KSA/status/2050591142492651968</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr">
         <is>
           <t>عندك بطاقات بنك الإمارات دبي الوطني ؟ العرض من نصيبك 😎
 تذكرة عليك والثانية مجانًا في #ڤوكس_سينما 
 للحجز ولتفاصيل اكثر,  اضغط على الرابط 👇
-tps://ksa.voxcinemas.com/ar/ticket-offer/emirates-nbd https://t.co/96UbGdATfB</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>عندك بطاقات بنك الإمارات دبي الوطني ؟ العرض من نصيبك 😎
-تذكرة عليك والثانية مجانًا في #ڤوكس_سينما 
-للحجز ولتفاصيل اكثر,  اضغط على الرابط 👇
-tps://ksa.voxcinemas.com/ar/ticket-offer/emirates-nbd https://t.co/96UbGdATfB</t>
+tps://ksa.voxcinemas.com/ar/ticket-offer/emirates-nbd</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Do you have Emirates NBD bank cards? The offer is for you 😎 One ticket is on you and the second is free at #Vox_Cinemas. 
-For booking and more details, click the link 👇 
-tps://ksa.voxcinemas.com/ar/ticket-offer/emirates-nbd https://t.co/96UbGdATfB</t>
+          <t>Do you have Emirates NBD bank cards? The offer is for you 😎 One ticket is on you and the second is free at #Vox_Cinemas 
+For booking and more details, click on the link 👇
+tps://ksa.voxcinemas.com/ar/ticket-offer/emirates-nbd</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1456,7 +1468,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>For booking and more details, click the link 👇 tps://ksa.voxcinemas.com/ar/ticket-offer/emirates-nbd https://t.co/96UbGdATfB • The offer is for you 😎 One ticket is on you and the second is free at #Vox_Cinemas. • Do you have Emirates NBD bank cards?</t>
+          <t>The offer is for you 😎 One ticket is on you and the second is free at #Vox_Cinemas For booking and more details, click on the link 👇 tps://ksa.voxcinemas.com/ar/ticket-offer/emirates-nbd • Do you have Emirates NBD bank cards?</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1510,17 +1522,7 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>هذا ملف مقارنة بين أقوى ٤ بطاقات ائتمانية كاش باك حالياً في السعودية 🇸🇦💳:
-🔹 بطاقة الأهلي للاسترداد النقدي الفئة المميزة (@snbalahli)
-🔹 بطاقة الراجحي كاش باك بلس (@alrajhibank)
-🔹 بطاقة مزيد بنك الإمارات دبي الوطني (@EmiratesNBD_KSA)
-🔹 بطاقة لايف ستايل من الفرنسي (@BSF_sa)
-📊 جمعت لكم كل التفاصيل + مثال على كل بطاقة + أفضل بطاقة فعلياً حسب الاستخدام.
-📝 أضفت المزايا والسلبيات لكل بطاقة من وجهة نظري.
-تفضلوا الملف:
-https://t.co/wzDtkBVVZM
-وأعطوني أي اقتراحات أو ملاحظات 🙌🗨️
-💡 بالنسبة لبطاقة النايفات، جاري تجربتها، وبعطيكم العلم الأكيد بعد ما أجربها فعلياً وأشوف كل شيء عندهم 👍✨</t>
+          <t>هل ممكن تضيف معها بطاقات انكان و النايفات خصوصاً انها تعطي بعض الفئات اعلى لايف ستايل</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1574,54 +1576,16 @@
           <t>هل ممكن تضيف معها بطاقات انكان و النايفات خصوصاً انها تعطي بعض الفئات اعلى لايف ستايل</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>https://x.com/moha60062/status/2050582653036888115</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>هذا ملف مقارنة بين أقوى ٤ بطاقات ائتمانية كاش باك حالياً في السعودية 🇸🇦💳:
-🔹 بطاقة الأهلي للاسترداد النقدي الفئة المميزة (@snbalahli)
-🔹 بطاقة الراجحي كاش باك بلس (@alrajhibank)
-🔹 بطاقة مزيد بنك الإمارات دبي الوطني (@EmiratesNBD_KSA)
-🔹 بطاقة لايف ستايل من الفرنسي (@BSF_sa)
-📊 جمعت لكم كل التفاصيل + مثال على كل بطاقة + أفضل بطاقة فعلياً حسب الاستخدام.
-📝 أضفت المزايا والسلبيات لكل بطاقة من وجهة نظري.
-تفضلوا الملف:
-https://t.co/wzDtkBVVZM
-وأعطوني أي اقتراحات أو ملاحظات 🙌🗨️
-💡 بالنسبة لبطاقة النايفات، جاري تجربتها، وبعطيكم العلم الأكيد بعد ما أجربها فعلياً وأشوف كل شيء عندهم 👍✨</t>
-        </is>
-      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>هذا ملف مقارنة بين أقوى ٤ بطاقات ائتمانية كاش باك حالياً في السعودية 🇸🇦💳:
-🔹 بطاقة الأهلي للاسترداد النقدي الفئة المميزة (@snbalahli)
-🔹 بطاقة الراجحي كاش باك بلس (@alrajhibank)
-🔹 بطاقة مزيد بنك الإمارات دبي الوطني (@EmiratesNBD_KSA)
-🔹 بطاقة لايف ستايل من الفرنسي (@BSF_sa)
-📊 جمعت لكم كل التفاصيل + مثال على كل بطاقة + أفضل بطاقة فعلياً حسب الاستخدام.
-📝 أضفت المزايا والسلبيات لكل بطاقة من وجهة نظري.
-تفضلوا الملف:
-https://t.co/wzDtkBVVZM
-وأعطوني أي اقتراحات أو ملاحظات 🙌🗨️
-💡 بالنسبة لبطاقة النايفات، جاري تجربتها، وبعطيكم العلم الأكيد بعد ما أجربها فعلياً وأشوف كل شيء عندهم 👍✨</t>
+          <t>هل ممكن تضيف معها بطاقات انكان و النايفات خصوصاً انها تعطي بعض الفئات اعلى لايف ستايل</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>This is a comparison file between the top 4 cash back credit cards currently in Saudi Arabia 🇸🇦💳:
-🔹 Al Ahli Cash Back Premium Card (@snbalahli)
-🔹 Al Rajhi Cash Back Plus Card (@alrajhibank)
-🔹 Mazid Emirates NBD Card (@EmiratesNBD_KSA)
-🔹 Lifestyle Card from Banque Saudi Fransi (@BSF_sa)
-📊 I have gathered all the details + an example for each card + the best card based on actual usage.
-📝 I added the pros and cons for each card from my perspective.
-Here is the file:
-https://t.co/wzDtkBVVZM
-And please give me any suggestions or feedback 🙌🗨️
-💡 As for the Nayifat card, I am currently testing it, and I will let you know for sure after I try it out and see everything they offer 👍✨</t>
+          <t>Could you please add Inkan and Naif cards with it, especially since they offer some categories a higher lifestyle?</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1652,7 +1616,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>📝 I added the pros and cons for each card from my perspective.</t>
+          <t>Could you please add Inkan and Naif cards with it, especially since they offer some categories a higher lifestyle?</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1706,7 +1670,7 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>🔥 Power. Politics. Survival… with an upgrade 🍿 Book #Patriot tickets and get a FREE popcorn upsize (Regular to Large) with every ticket. Show your ticket at the counter. Valid May 1–6. T&amp;amp;Cs apply. Watch at Novo Cinemas. Book now on our website or app. T&amp;amp;C's apply. https://t.co/jxjZGKejZi</t>
+          <t>Sometimes, all you need is a quiet escape into a great story. 🎞️🤍 Use your Emirates NBD card at Novo Cinemas to enjoy 15% off tickets any day of the week. A simple way to reward yourself with a moment of peace. Book your tickets now by visiting NovoCinemas.com or the App</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1760,24 +1724,16 @@
           <t>Sometimes, all you need is a quiet escape into a great story. 🎞️🤍 Use your Emirates NBD card at Novo Cinemas to enjoy 15% off tickets any day of the week. A simple way to reward yourself with a moment of peace. Book your tickets now by visiting NovoCinemas.com or the App</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>https://x.com/NovoCinemas/status/2050546053124923502</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>🔥 Power. Politics. Survival… with an upgrade 🍿 Book #Patriot tickets and get a FREE popcorn upsize (Regular to Large) with every ticket. Show your ticket at the counter. Valid May 1–6. T&amp;amp;Cs apply. Watch at Novo Cinemas. Book now on our website or app. T&amp;amp;C's apply. https://t.co/jxjZGKejZi</t>
-        </is>
-      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>🔥 Power. Politics. Survival… with an upgrade 🍿 Book #Patriot tickets and get a FREE popcorn upsize (Regular to Large) with every ticket. Show your ticket at the counter. Valid May 1–6. T&amp;amp;Cs apply. Watch at Novo Cinemas. Book now on our website or app. T&amp;amp;C's apply. https://t.co/jxjZGKejZi</t>
+          <t>Sometimes, all you need is a quiet escape into a great story. 🎞️🤍 Use your Emirates NBD card at Novo Cinemas to enjoy 15% off tickets any day of the week. A simple way to reward yourself with a moment of peace. Book your tickets now by visiting NovoCinemas.com or the App</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Power. Politics. Survival… with an upgrade. Book #Patriot tickets and get a FREE popcorn upsize (Regular to Large) with every ticket. Show your ticket at the counter. Valid May 1–6. Terms and conditions apply. Watch at Novo Cinemas. Book now on our website or app. Terms and conditions apply.</t>
+          <t>Sometimes, all you need is a quiet escape into a great story. Use your Emirates NBD card at Novo Cinemas to enjoy 15% off tickets any day of the week. A simple way to reward yourself with a moment of peace. Book your tickets now by visiting NovoCinemas.com or the App.</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1787,7 +1743,7 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE8" s="2" t="n">
@@ -1808,7 +1764,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Book #Patriot tickets and get a FREE popcorn upsize (Regular to Large) with every ticket. • Terms and conditions apply. • Terms and conditions apply.</t>
+          <t>Use your Emirates NBD card at Novo Cinemas to enjoy 15% off tickets any day of the week. • Book your tickets now by visiting NovoCinemas.com or the App. • Sometimes, all you need is a quiet escape into a great story.</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1862,14 +1818,7 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Embrace higher earnings with your salary transfer
- Transfer your salary to Emirates NBD and earn up to 6% on your balance. Get started today:
- 1. Open a Millionaire Account, Current Account or Savings Account
- 2. Transfer your salary of AED 10,000 or more
- 3. Maintain an average monthly balance of AED 25,000 or more
- 4. Earn bonus interest with a credit card
- Terms and conditions apply
- https://t.co/u4ZGMVsftb</t>
+          <t>Please update the promotions on the mobile banking app also.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1923,45 +1872,16 @@
           <t>Please update the promotions on the mobile banking app also.</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>https://x.com/adrianD36740715/status/2050530525820109288</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Embrace higher earnings with your salary transfer
- Transfer your salary to Emirates NBD and earn up to 6% on your balance. Get started today:
- 1. Open a Millionaire Account, Current Account or Savings Account
- 2. Transfer your salary of AED 10,000 or more
- 3. Maintain an average monthly balance of AED 25,000 or more
- 4. Earn bonus interest with a credit card
- Terms and conditions apply
- https://t.co/u4ZGMVsftb</t>
-        </is>
-      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Embrace higher earnings with your salary transfer
- Transfer your salary to Emirates NBD and earn up to 6% on your balance. Get started today:
- 1. Open a Millionaire Account, Current Account or Savings Account
- 2. Transfer your salary of AED 10,000 or more
- 3. Maintain an average monthly balance of AED 25,000 or more
- 4. Earn bonus interest with a credit card
- Terms and conditions apply
- https://t.co/u4ZGMVsftb</t>
+          <t>Please update the promotions on the mobile banking app also.</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Embrace higher earnings with your salary transfer
-Transfer your salary to Emirates NBD and earn up to 6% on your balance. Get started today:
-1. Open a Millionaire Account, Current Account or Savings Account
-2. Transfer your salary of AED 10,000 or more
-3. Maintain an average monthly balance of AED 25,000 or more
-4. Earn bonus interest with a credit card
-Terms and conditions apply
-https://t.co/u4ZGMVsftb</t>
+          <t>Please update the promotions on the mobile banking app as well.</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1971,7 +1891,7 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE9" s="2" t="n">
@@ -1992,7 +1912,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Embrace higher earnings with your salary transfer Transfer your salary to Emirates NBD and earn up to 6% on your balance. • Transfer your salary of AED 10,000 or more 3. • Maintain an average monthly balance of AED 25,000 or more 4.</t>
+          <t>Please update the promotions on the mobile banking app as well.</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -2045,6 +1965,87 @@
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
+        <is>
+          <t>UAE controls banking sector of PK after bribing leaders 
+BANKS owned by UAE in PK(not complete list)
+1. Alfalah 
+2. Dubai Islamic  
+3. Mashreq   
+4. Emirates NBD  
+5. Emirates Global 
+6. FirstWomen
+7. Al Baraka
+8. Ubank
+9. EasyPaisa
+10. Jazzcash
+11. BML
+#Islamabad
+#Pakistan 
+#UAE https://t.co/hEotNuuvdl</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>UAE controls banking sector of PK after bribing leaders 
+BANKS owned by UAE in PK(not complete list)
+1. Alfalah 
+2. Dubai Islamic  
+3. Mashreq   
+4. Emirates NBD  
+5. Emirates Global 
+6. FirstWomen
+7. Al Baraka
+8. Ubank
+9. EasyPaisa
+10. Jazzcash
+11. BML
+&lt;a href="/search?f=tweets&amp;amp;q=%23Islamabad"&gt;#Islamabad&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23Pakistan"&gt;#Pakistan&lt;/a&gt; 
+&lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>May 2, 2026 · 10:44 AM UTC</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>46144.44722222222</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23Islamabad', 'https://x.com/search?f=tweets&amp;q=%23Pakistan', 'https://x.com/search?f=tweets&amp;q=%23UAE']</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>110</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>UAE controls banking sector of PK after bribing leaders 
 BANKS owned by UAE in PK(not complete list)
@@ -2064,68 +2065,12 @@
 #UAE</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>UAE controls banking sector of PK after bribing leaders 
-BANKS owned by UAE in PK(not complete list)
-1. Alfalah 
-2. Dubai Islamic  
-3. Mashreq   
-4. Emirates NBD  
-5. Emirates Global 
-6. FirstWomen
-7. Al Baraka
-8. Ubank
-9. EasyPaisa
-10. Jazzcash
-11. BML
-&lt;a href="/search?f=tweets&amp;amp;q=%23Islamabad"&gt;#Islamabad&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23Pakistan"&gt;#Pakistan&lt;/a&gt; 
-&lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K10" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>16h</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>May 2, 2026 · 10:44 AM UTC</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="n">
-        <v>46144.44722222222</v>
-      </c>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23Islamabad', 'https://x.com/search?f=tweets&amp;q=%23Pakistan', 'https://x.com/search?f=tweets&amp;q=%23UAE']</t>
-        </is>
-      </c>
-      <c r="S10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>110</v>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>https://x.com/Kashif111144/status/2050526894626427022</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>UAE controls banking sector of PK after bribing leaders 
 BANKS owned by UAE in PK(not complete list)
@@ -2142,11 +2087,9 @@
 11. BML
 #Islamabad
 #Pakistan 
-#UAE</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
+#UAE https://t.co/hEotNuuvdl</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>UAE controls banking sector of PK after bribing leaders 
@@ -2164,7 +2107,7 @@
 11. BML
 #Islamabad
 #Pakistan 
-#UAE</t>
+#UAE https://t.co/hEotNuuvdl</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -2254,7 +2197,7 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Style, comfort, and cashback… that's how we do it at TMG with Emirates NBD✨</t>
+          <t>Style, comfort, and cashback… that's how we do it at TMG with Emirates NBD✨ https://t.co/bt4VAtCnZL</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -2304,11 +2247,19 @@
           <t>Style, comfort, and cashback… that's how we do it at TMG with Emirates NBD✨</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>https://x.com/SavannahP57037/status/2050510080127455613</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Style, comfort, and cashback… that's how we do it at TMG with Emirates NBD✨ https://t.co/bt4VAtCnZL</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Style, comfort, and cashback… that's how we do it at TMG with Emirates NBD✨</t>
+          <t>Style, comfort, and cashback… that's how we do it at TMG with Emirates NBD✨ https://t.co/bt4VAtCnZL</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -2399,9 +2350,9 @@
       <c r="I12" t="inlineStr">
         <is>
           <t>@Visa  has officially appointed @EmiratesNBD_AE  as its National Net Settlement Service (NNSS) agent.
-Read more: uaefintechvibes.com/local-ua…
+Read more: https://t.co/zL56RMfxRn
 Follow @uaefintechvibes for daily fintech updates. 
-#uaefintech #visapayments #enbd</t>
+#uaefintech #visapayments #enbd https://t.co/8gN1xEE7BN</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2461,22 +2412,33 @@
 #uaefintech #visapayments #enbd</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>https://x.com/uaefintechvibes/status/2050500266760478726</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>@Visa  has officially appointed @EmiratesNBD_AE  as its National Net Settlement Service (NNSS) agent.
+Read more: https://t.co/zL56RMfxRn
+Follow @uaefintechvibes for daily fintech updates. 
+#uaefintech #visapayments #enbd https://t.co/8gN1xEE7BN</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>@Visa  has officially appointed @EmiratesNBD_AE  as its National Net Settlement Service (NNSS) agent.
-Read more: uaefintechvibes.com/local-ua…
+Read more: https://t.co/zL56RMfxRn
 Follow @uaefintechvibes for daily fintech updates. 
-#uaefintech #visapayments #enbd</t>
+#uaefintech #visapayments #enbd https://t.co/8gN1xEE7BN</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
           <t>Visa has officially appointed Emirates NBD as its National Net Settlement Service (NNSS) agent. 
-Read more: uaefintechvibes.com/local-ua…
+Read more: https://t.co/zL56RMfxRn
 Follow uaefintechvibes for daily fintech updates. 
-#uaefintech #visapayments #enbd</t>
+#uaefintech #visapayments #enbd https://t.co/8gN1xEE7BN</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2507,7 +2469,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Visa has officially appointed Emirates NBD as its National Net Settlement Service (NNSS) agent. • Read more: uaefintechvibes.com/local-ua… Follow uaefintechvibes for daily fintech updates. • #uaefintech #visapayments #enbd</t>
+          <t>Visa has officially appointed Emirates NBD as its National Net Settlement Service (NNSS) agent. • Read more: https://t.co/zL56RMfxRn Follow uaefintechvibes for daily fintech updates. • #uaefintech #visapayments #enbd https://t.co/8gN1xEE7BN</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2562,8 +2524,8 @@
       <c r="I13" t="inlineStr">
         <is>
           <t>Visa has appointed Emirates NBD, a leading banking group in the Middle East, North Africa and Türkiye (MENAT) region, as its official National Net Settlement Service (NNSS) Agent in the UAE.
-Read more on abc-gcc.net/News/1/395250
-#ABCnews #Digital #Payment #Services</t>
+Read more on https://t.co/RPTuv9uD9h
+#ABCnews #Digital #Payment #Services https://t.co/Fs9eVfVeuP</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2621,13 +2583,23 @@
 #ABCnews #Digital #Payment #Services</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>https://x.com/ABCinGCC/status/2050470345820565788</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Visa has appointed Emirates NBD, a leading banking group in the Middle East, North Africa and Türkiye (MENAT) region, as its official National Net Settlement Service (NNSS) Agent in the UAE.
+Read more on https://t.co/RPTuv9uD9h
+#ABCnews #Digital #Payment #Services https://t.co/Fs9eVfVeuP</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>Visa has appointed Emirates NBD, a leading banking group in the Middle East, North Africa and Türkiye (MENAT) region, as its official National Net Settlement Service (NNSS) Agent in the UAE.
-Read more on abc-gcc.net/News/1/395250
-#ABCnews #Digital #Payment #Services</t>
+Read more on https://t.co/RPTuv9uD9h
+#ABCnews #Digital #Payment #Services https://t.co/Fs9eVfVeuP</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -2716,6 +2688,67 @@
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
+        <is>
+          <t>Shop, save, and earn with the Emirates NBD noon One Visa Credit Card
+🛍️ Get up to 20% back on noon, noon Food, noon minutes, Namshi &amp; more
+🌟 Enjoy a FREE 1-year noon One membership
+🎁 Earn AED 500 welcome bonus
+Apply now in just a few clicks and start enjoying exclusive benefits! T&amp;C Apply!
+Apply Now: https://t.co/9cutEjf788</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Shop, save, and earn with the Emirates NBD noon One Visa Credit Card
+🛍️ Get up to 20% back on noon, noon Food, noon minutes, Namshi &amp;amp; more
+🌟 Enjoy a FREE 1-year noon One membership
+🎁 Earn AED 500 welcome bonus
+Apply now in just a few clicks and start enjoying exclusive benefits! T&amp;amp;C Apply!
+Apply Now: &lt;a href="https://www.emiratesnbd.com/en/campaigns/noon-one-credit-card"&gt;emiratesnbd.com/en/campaigns…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>May 2, 2026 · 6:04 AM UTC</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>46144.25277777778</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesnbd.com/en/campaigns/noon-one-credit-card']</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>12</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1216</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
         <is>
           <t>Shop, save, and earn with the Emirates NBD noon One Visa Credit Card
 🛍️ Get up to 20% back on noon, noon Food, noon minutes, Namshi &amp; more
@@ -2725,69 +2758,21 @@
 Apply Now: emiratesnbd.com/en/campaigns…</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Shop, save, and earn with the Emirates NBD noon One Visa Credit Card
-🛍️ Get up to 20% back on noon, noon Food, noon minutes, Namshi &amp;amp; more
-🌟 Enjoy a FREE 1-year noon One membership
-🎁 Earn AED 500 welcome bonus
-Apply now in just a few clicks and start enjoying exclusive benefits! T&amp;amp;C Apply!
-Apply Now: &lt;a href="https://www.emiratesnbd.com/en/campaigns/noon-one-credit-card"&gt;emiratesnbd.com/en/campaigns…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K14" t="b">
-        <v>0</v>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>May 2, 2026 · 6:04 AM UTC</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="n">
-        <v>46144.25277777778</v>
-      </c>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesnbd.com/en/campaigns/noon-one-credit-card']</t>
-        </is>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>12</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1216</v>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2050456364728680817</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
         <is>
           <t>Shop, save, and earn with the Emirates NBD noon One Visa Credit Card
 🛍️ Get up to 20% back on noon, noon Food, noon minutes, Namshi &amp; more
 🌟 Enjoy a FREE 1-year noon One membership
 🎁 Earn AED 500 welcome bonus
 Apply now in just a few clicks and start enjoying exclusive benefits! T&amp;C Apply!
-Apply Now: emiratesnbd.com/en/campaigns…</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
+Apply Now: https://t.co/9cutEjf788</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>Shop, save, and earn with the Emirates NBD noon One Visa Credit Card
@@ -2795,17 +2780,17 @@
 🌟 Enjoy a FREE 1-year noon One membership
 🎁 Earn AED 500 welcome bonus
 Apply now in just a few clicks and start enjoying exclusive benefits! T&amp;C Apply!
-Apply Now: emiratesnbd.com/en/campaigns…</t>
+Apply Now: https://t.co/9cutEjf788</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
           <t>Shop, save, and earn with the Emirates NBD noon One Visa Credit Card
-Get up to 20% back on noon, noon Food, noon minutes, Namshi &amp; more
+Get up to 20% back on noon, noon Food, noon minutes, Namshi, and more
 Enjoy a FREE 1-year noon One membership
 Earn AED 500 welcome bonus
 Apply now in just a few clicks and start enjoying exclusive benefits! Terms and Conditions apply!
-Apply Now: emiratesnbd.com/en/campaigns…</t>
+Apply Now: https://t.co/9cutEjf788</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2836,7 +2821,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Apply Now: emiratesnbd.com/en/campaigns… • Terms and Conditions apply!</t>
+          <t>Apply Now: https://t.co/9cutEjf788 • Terms and Conditions apply!</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2890,7 +2875,8 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>RBL takenover by ENBD(Largest bank in UAE) is a bad investment according to you?</t>
+          <t>Bandhan Bank and RBL Bank 👇
+Both are crap stock - Avoid for Investing 🎯</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2944,16 +2930,27 @@
           <t>RBL takenover by ENBD(Largest bank in UAE) is a bad investment according to you?</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>https://x.com/Jami076152121/status/2050399772591399146</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Bandhan Bank and RBL Bank 👇
+Both are crap stock - Avoid for Investing 🎯</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RBL takenover by ENBD(Largest bank in UAE) is a bad investment according to you?</t>
+          <t>Bandhan Bank and RBL Bank 👇
+Both are crap stock - Avoid for Investing 🎯</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Is RBL's takeover by ENBD (the largest bank in the UAE) a bad investment in your opinion?</t>
+          <t>Bandhan Bank and RBL Bank
+Both are poor stocks - Avoid for investing.</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2984,7 +2981,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Is RBL's takeover by ENBD (the largest bank in the UAE) a bad investment in your opinion?</t>
+          <t>Bandhan Bank and RBL Bank Both are poor stocks - Avoid for investing.</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -3038,7 +3035,14 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>👍</t>
+          <t>Make Eid surprises even more valuable.
+From silver to gold, discover a smarter way to own or gift something truly precious.
+Watch this episode and tell us:
+How can you buy gold and silver from the bank?
+To participate:
+Follow Emirates NBD
+Tag 3 friends
+Drop your answer below for a chance to win AED 10,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -3092,16 +3096,38 @@
           <t>👍</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>https://x.com/Bushrasabih2/status/2050382263129620695</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>Make Eid surprises even more valuable.
+From silver to gold, discover a smarter way to own or gift something truly precious.
+Watch this episode and tell us:
+How can you buy gold and silver from the bank?
+To participate:
+Follow Emirates NBD
+Tag 3 friends
+Drop your answer below for a chance to win AED 10,000</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>👍</t>
+          <t>Make Eid surprises even more valuable.
+From silver to gold, discover a smarter way to own or gift something truly precious.
+Watch this episode and tell us:
+How can you buy gold and silver from the bank?
+To participate:
+Follow Emirates NBD
+Tag 3 friends
+Drop your answer below for a chance to win AED 10,000</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>The text is an emoji and does not require translation.</t>
+          <t>Make Eid surprises even more valuable. From silver to gold, discover a smarter way to own or gift something truly precious. Watch this episode and tell us: How can you buy gold and silver from the bank? To participate: Follow Emirates NBD Tag 3 friends Drop your answer below for a chance to win AED 10,000</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -3111,7 +3137,7 @@
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE16" s="2" t="n">
@@ -3132,7 +3158,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>The text is an emoji and does not require translation.</t>
+          <t>To participate: Follow Emirates NBD Tag 3 friends Drop your answer below for a chance to win AED 10,000 • From silver to gold, discover a smarter way to own or gift something truly precious. • Watch this episode and tell us: How can you buy gold and silver from the bank?</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -3155,54 +3181,57 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2050364684251893892</t>
+          <t>2050374137852670288</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://x.com/yasmeenalja/status/2050364684251893892</t>
+          <t>https://x.com/STKgenghis/status/2050374137852670288</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://x.com/yasmeenalja</t>
+          <t>https://x.com/STKgenghis</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>yasmeenalja</t>
+          <t>STKgenghis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Yasmeen Aljadah</t>
+          <t>khana-b-dosh</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2042291734583877632/pJUn80Vi_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1243248207293026305/b_s7UBzl_bigger.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Personal financing in Saudi Arabia made easy for expats.💸🙏🏻
-Emirates NBD – Dammam Branch | Financial Consultant
-#SaudiArabia #ExpatsInKSA #Financing #PersonalFinance #KSAJobs</t>
+          <t>Open an Emirates NBD Millionaire Account to be the next winner, with over 1,400 cash prizes worth AED 50,000,000.
+- Monthly prizes up to AED 1,000,000
+- Grand prizes up to AED 5,000,000
+Dedicated prizes for Emiratis, expats, and businesses 🇦🇪</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Personal financing in Saudi Arabia made easy for expats.💸🙏🏻
-Emirates NBD – Dammam Branch | Financial Consultant
-&lt;a href="/search?f=tweets&amp;amp;q=%23SaudiArabia"&gt;#SaudiArabia&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23ExpatsInKSA"&gt;#ExpatsInKSA&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Financing"&gt;#Financing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23PersonalFinance"&gt;#PersonalFinance&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23KSAJobs"&gt;#KSAJobs&lt;/a&gt;</t>
+          <t>Had i the energy I would report this to &lt;a href="/centralbankuae" title="Central Bank of the UAE"&gt;@centralbankuae&lt;/a&gt; but no energy or time. I will now be silent. I blocked the card 17 April. No service since.</t>
         </is>
       </c>
       <c r="K17" t="b">
         <v>0</v>
       </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>May 2</t>
@@ -3210,20 +3239,20 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 12:00 AM UTC</t>
+          <t>May 2, 2026 · 12:37 AM UTC</t>
         </is>
       </c>
       <c r="P17" s="2" t="n">
-        <v>46144</v>
+        <v>46144.02569444444</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23SaudiArabia', 'https://x.com/search?f=tweets&amp;q=%23ExpatsInKSA', 'https://x.com/search?f=tweets&amp;q=%23Financing', 'https://x.com/search?f=tweets&amp;q=%23PersonalFinance', 'https://x.com/search?f=tweets&amp;q=%23KSAJobs']</t>
+          <t>['https://x.com/centralbankuae']</t>
         </is>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -3232,7 +3261,7 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>143</v>
+        <v>17</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -3241,25 +3270,36 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Personal financing in Saudi Arabia made easy for expats.💸🙏🏻
-Emirates NBD – Dammam Branch | Financial Consultant
-#SaudiArabia #ExpatsInKSA #Financing #PersonalFinance #KSAJobs</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
+          <t>Had i the energy I would report this to @centralbankuae but no energy or time. I will now be silent. I blocked the card 17 April. No service since.</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>https://x.com/STKgenghis/status/2050374137852670288</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Open an Emirates NBD Millionaire Account to be the next winner, with over 1,400 cash prizes worth AED 50,000,000.
+- Monthly prizes up to AED 1,000,000
+- Grand prizes up to AED 5,000,000
+Dedicated prizes for Emiratis, expats, and businesses 🇦🇪</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Personal financing in Saudi Arabia made easy for expats.💸🙏🏻
-Emirates NBD – Dammam Branch | Financial Consultant
-#SaudiArabia #ExpatsInKSA #Financing #PersonalFinance #KSAJobs</t>
+          <t>Open an Emirates NBD Millionaire Account to be the next winner, with over 1,400 cash prizes worth AED 50,000,000.
+- Monthly prizes up to AED 1,000,000
+- Grand prizes up to AED 5,000,000
+Dedicated prizes for Emiratis, expats, and businesses 🇦🇪</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Personal financing in Saudi Arabia made easy for expats.💸🙏🏻
-Emirates NBD – Dammam Branch | Financial Consultant
-#SaudiArabia #ExpatsInKSA #Financing #PersonalFinance #KSAJobs</t>
+          <t>Open an Emirates NBD Millionaire Account to be the next winner, with over 1,400 cash prizes worth AED 50,000,000. 
+- Monthly prizes up to AED 1,000,000 
+- Grand prizes up to AED 5,000,000 
+Dedicated prizes for Emiratis, expats, and businesses.</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -3269,11 +3309,11 @@
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE17" s="2" t="n">
-        <v>46144.16666666666</v>
+        <v>46144.19236111111</v>
       </c>
       <c r="AF17" s="2" t="n">
         <v>46144</v>
@@ -3290,7 +3330,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Personal financing in Saudi Arabia made easy for expats.💸🙏🏻 Emirates NBD – Dammam Branch | Financial Consultant #SaudiArabia #ExpatsInKSA #Financing #PersonalFinance #KSAJobs</t>
+          <t>- Monthly prizes up to AED 1,000,000 - Grand prizes up to AED 5,000,000 Dedicated prizes for Emiratis, expats, and businesses. • Open an Emirates NBD Millionaire Account to be the next winner, with over 1,400 cash prizes worth AED 50,000,000.</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -3303,7 +3343,7 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
@@ -3313,45 +3353,46 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2050477438539297270</t>
+          <t>2050364684251893892</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://x.com/patelumarjiarif/status/2050477438539297270</t>
+          <t>https://x.com/yasmeenalja/status/2050364684251893892</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://x.com/patelumarjiarif</t>
+          <t>https://x.com/yasmeenalja</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>patelumarjiarif</t>
+          <t>yasmeenalja</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Arif Patel - Preston Trading in UK</t>
+          <t>Yasmeen Aljadah</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1650401956072943616/wfZaFWCV_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2042291734583877632/pJUn80Vi_bigger.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Located on Yas Bay Waterfront's three kilometer-long promenade, Hilton Abu Dhabi - Yas Island features 545 rooms and offers an exceptional array of culinary options across several dining venues. Guests enjoy access to Yas Island's exciting theme parks.
-#hiltonabudhabi https://t.co/HOnNG0kw9t</t>
+          <t>Expats in KSA — your salary might qualify you for better financing options.
+#SaudiArabia #ExpatsInKSA #Financing #PersonalFinance #KSAJobs https://t.co/CJ5MydF5fu</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Emirates Islamic, announce the launch of a Shari’ah-compliant digital investment solution in gold and silver, seamlessly integrated into the bank’s EI + Mobile Banking App. The new offering is a first-of-its-kind by an Islamic bank in the UAE.
-&lt;a href="/search?f=tweets&amp;amp;q=%23dubai"&gt;#dubai&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23emiratesislamic"&gt;#emiratesislamic&lt;/a&gt;</t>
+          <t>Personal financing in Saudi Arabia made easy for expats.💸🙏🏻
+Emirates NBD – Dammam Branch | Financial Consultant
+&lt;a href="/search?f=tweets&amp;amp;q=%23SaudiArabia"&gt;#SaudiArabia&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23ExpatsInKSA"&gt;#ExpatsInKSA&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Financing"&gt;#Financing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23PersonalFinance"&gt;#PersonalFinance&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23KSAJobs"&gt;#KSAJobs&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K18" t="b">
@@ -3361,21 +3402,21 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>May 2</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 7:28 AM UTC</t>
+          <t>May 2, 2026 · 12:00 AM UTC</t>
         </is>
       </c>
       <c r="P18" s="2" t="n">
-        <v>46144.31111111111</v>
+        <v>46144</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23dubai', 'https://x.com/search?f=tweets&amp;q=%23emiratesislamic']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23SaudiArabia', 'https://x.com/search?f=tweets&amp;q=%23ExpatsInKSA', 'https://x.com/search?f=tweets&amp;q=%23Financing', 'https://x.com/search?f=tweets&amp;q=%23PersonalFinance', 'https://x.com/search?f=tweets&amp;q=%23KSAJobs']</t>
         </is>
       </c>
       <c r="S18" t="n">
@@ -3388,39 +3429,40 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>28</v>
+        <v>143</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Emirates Islamic, announce the launch of a Shari’ah-compliant digital investment solution in gold and silver, seamlessly integrated into the bank’s EI + Mobile Banking App. The new offering is a first-of-its-kind by an Islamic bank in the UAE.
-#dubai #emiratesislamic</t>
+          <t>Personal financing in Saudi Arabia made easy for expats.💸🙏🏻
+Emirates NBD – Dammam Branch | Financial Consultant
+#SaudiArabia #ExpatsInKSA #Financing #PersonalFinance #KSAJobs</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>https://x.com/patelumarjiarif/status/2050477438539297270</t>
+          <t>https://x.com/yasmeenalja/status/2050364684251893892</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>Located on Yas Bay Waterfront's three kilometer-long promenade, Hilton Abu Dhabi - Yas Island features 545 rooms and offers an exceptional array of culinary options across several dining venues. Guests enjoy access to Yas Island's exciting theme parks.
-#hiltonabudhabi https://t.co/HOnNG0kw9t</t>
+          <t>Expats in KSA — your salary might qualify you for better financing options.
+#SaudiArabia #ExpatsInKSA #Financing #PersonalFinance #KSAJobs https://t.co/CJ5MydF5fu</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Located on Yas Bay Waterfront's three kilometer-long promenade, Hilton Abu Dhabi - Yas Island features 545 rooms and offers an exceptional array of culinary options across several dining venues. Guests enjoy access to Yas Island's exciting theme parks.
-#hiltonabudhabi https://t.co/HOnNG0kw9t</t>
+          <t>Expats in KSA — your salary might qualify you for better financing options.
+#SaudiArabia #ExpatsInKSA #Financing #PersonalFinance #KSAJobs https://t.co/CJ5MydF5fu</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Located on Yas Bay Waterfront's three kilometer-long promenade, Hilton Abu Dhabi - Yas Island features 545 rooms and offers an exceptional array of culinary options across several dining venues. Guests enjoy access to Yas Island's exciting theme parks.</t>
+          <t>Expats in KSA — your salary might qualify you for better financing options.</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3434,29 +3476,29 @@
         </is>
       </c>
       <c r="AE18" s="2" t="n">
-        <v>46144.47777777778</v>
+        <v>46144.16666666666</v>
       </c>
       <c r="AF18" s="2" t="n">
         <v>46144</v>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
+          <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Located on Yas Bay Waterfront's three kilometer-long promenade, Hilton Abu Dhabi - Yas Island features 545 rooms and offers an exceptional array of culinary options across several dining venues. • Guests enjoy access to Yas Island's exciting theme parks.</t>
+          <t>Expats in KSA — your salary might qualify you for better financing options.</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>Emirates Islamic Bank (EIB)</t>
+          <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
       <c r="AK18" t="n">
@@ -3474,45 +3516,45 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2050455246686527975</t>
+          <t>2050477438539297270</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2050455246686527975</t>
+          <t>https://x.com/patelumarjiarif/status/2050477438539297270</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/patelumarjiarif</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>patelumarjiarif</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Arif Patel - Preston Trading in UK</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1650401956072943616/wfZaFWCV_bigger.jpg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Did You Know Emirates Islamic offers fully Shariah-compliant Corporate Finance solutions?
-From Working Capital to Structured Finance, Emirates Islamic provides tailored Islamic finance offerings designed to help businesses grow sustainably. https://t.co/Qugg6bzXoN</t>
+          <t>Emirates Islamic, announce the launch of a Shari’ah-compliant digital investment solution in gold and silver, seamlessly integrated into the bank’s EI + Mobile Banking App. The new offering is a first-of-its-kind by an Islamic bank in the UAE.
+#dubai #emiratesislamic</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Did You Know Emirates Islamic offers fully Shariah-compliant Corporate Finance solutions?
-From Working Capital to Structured Finance, Emirates Islamic provides tailored Islamic finance offerings designed to help businesses grow sustainably.</t>
+          <t>Emirates Islamic, announce the launch of a Shari’ah-compliant digital investment solution in gold and silver, seamlessly integrated into the bank’s EI + Mobile Banking App. The new offering is a first-of-its-kind by an Islamic bank in the UAE.
+&lt;a href="/search?f=tweets&amp;amp;q=%23dubai"&gt;#dubai&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23emiratesislamic"&gt;#emiratesislamic&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K19" t="b">
@@ -3522,30 +3564,34 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 6:00 AM UTC</t>
+          <t>May 2, 2026 · 7:28 AM UTC</t>
         </is>
       </c>
       <c r="P19" s="2" t="n">
-        <v>46144.25</v>
+        <v>46144.31111111111</v>
       </c>
       <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23dubai', 'https://x.com/search?f=tweets&amp;q=%23emiratesislamic']</t>
+        </is>
+      </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -3554,35 +3600,26 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Did You Know Emirates Islamic offers fully Shariah-compliant Corporate Finance solutions?
-From Working Capital to Structured Finance, Emirates Islamic provides tailored Islamic finance offerings designed to help businesses grow sustainably.</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2050455246686527975</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Did You Know Emirates Islamic offers fully Shariah-compliant Corporate Finance solutions?
-From Working Capital to Structured Finance, Emirates Islamic provides tailored Islamic finance offerings designed to help businesses grow sustainably. https://t.co/Qugg6bzXoN</t>
-        </is>
-      </c>
+          <t>Emirates Islamic, announce the launch of a Shari’ah-compliant digital investment solution in gold and silver, seamlessly integrated into the bank’s EI + Mobile Banking App. The new offering is a first-of-its-kind by an Islamic bank in the UAE.
+#dubai #emiratesislamic</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Did You Know Emirates Islamic offers fully Shariah-compliant Corporate Finance solutions?
-From Working Capital to Structured Finance, Emirates Islamic provides tailored Islamic finance offerings designed to help businesses grow sustainably. https://t.co/Qugg6bzXoN</t>
+          <t>Emirates Islamic, announce the launch of a Shari’ah-compliant digital investment solution in gold and silver, seamlessly integrated into the bank’s EI + Mobile Banking App. The new offering is a first-of-its-kind by an Islamic bank in the UAE.
+#dubai #emiratesislamic</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Did you know Emirates Islamic offers fully Shariah-compliant corporate finance solutions? From working capital to structured finance, Emirates Islamic provides tailored Islamic finance offerings designed to help businesses grow sustainably.</t>
+          <t>Emirates Islamic announces the launch of a Shari’ah-compliant digital investment solution in gold and silver, seamlessly integrated into the bank’s EI + Mobile Banking App. The new offering is a first-of-its-kind by an Islamic bank in the UAE.</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Cust</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -3591,7 +3628,7 @@
         </is>
       </c>
       <c r="AE19" s="2" t="n">
-        <v>46144.41666666666</v>
+        <v>46144.47777777778</v>
       </c>
       <c r="AF19" s="2" t="n">
         <v>46144</v>
@@ -3608,7 +3645,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>From working capital to structured finance, Emirates Islamic provides tailored Islamic finance offerings designed to help businesses grow sustainably. • Did you know Emirates Islamic offers fully Shariah-compliant corporate finance solutions?</t>
+          <t>Emirates Islamic announces the launch of a Shari’ah-compliant digital investment solution in gold and silver, seamlessly integrated into the bank’s EI + Mobile Banking App. • The new offering is a first-of-its-kind by an Islamic bank in the UAE.</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -3631,12 +3668,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2050485448754004332</t>
+          <t>2050455246686527975</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2050485448754004332</t>
+          <t>https://x.com/emiratesislamic/status/2050455246686527975</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3662,16 +3699,14 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Tailor-made home financing solutions to ease the process of owning a home.
-Learn More
-https://t.co/9ZNjxE7BhS https://t.co/1SYIepscqy</t>
+          <t>Did You Know Emirates Islamic offers fully Shariah-compliant Corporate Finance solutions?
+From Working Capital to Structured Finance, Emirates Islamic provides tailored Islamic finance offerings designed to help businesses grow sustainably.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Tailor-made home financing solutions to ease the process of owning a home.
-Learn More
-&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=home_finance"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
+          <t>Did You Know Emirates Islamic offers fully Shariah-compliant Corporate Finance solutions?
+From Working Capital to Structured Finance, Emirates Islamic provides tailored Islamic finance offerings designed to help businesses grow sustainably.</t>
         </is>
       </c>
       <c r="K20" t="b">
@@ -3681,34 +3716,30 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 8:00 AM UTC</t>
+          <t>May 2, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P20" s="2" t="n">
-        <v>46144.33333333334</v>
+        <v>46144.25</v>
       </c>
       <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/personal-banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=home_finance']</t>
-        </is>
-      </c>
+      <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" t="n">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -3717,33 +3748,21 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Tailor-made home financing solutions to ease the process of owning a home.
-Learn More
-emiratesislamic.ae/en/person…</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2050485448754004332</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>Tailor-made home financing solutions to ease the process of owning a home.
-Learn More
-https://t.co/9ZNjxE7BhS https://t.co/1SYIepscqy</t>
-        </is>
-      </c>
+          <t>Did You Know Emirates Islamic offers fully Shariah-compliant Corporate Finance solutions?
+From Working Capital to Structured Finance, Emirates Islamic provides tailored Islamic finance offerings designed to help businesses grow sustainably.</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>Tailor-made home financing solutions to ease the process of owning a home.
-Learn More
-https://t.co/9ZNjxE7BhS https://t.co/1SYIepscqy</t>
+          <t>Did You Know Emirates Islamic offers fully Shariah-compliant Corporate Finance solutions?
+From Working Capital to Structured Finance, Emirates Islamic provides tailored Islamic finance offerings designed to help businesses grow sustainably.</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Tailor-made home financing solutions to ease the process of owning a home.</t>
+          <t>Did you know Emirates Islamic offers fully Shariah-compliant Corporate Finance solutions? From Working Capital to Structured Finance, Emirates Islamic provides tailored Islamic finance offerings designed to help businesses grow sustainably.</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3757,7 +3776,7 @@
         </is>
       </c>
       <c r="AE20" s="2" t="n">
-        <v>46144.5</v>
+        <v>46144.41666666666</v>
       </c>
       <c r="AF20" s="2" t="n">
         <v>46144</v>
@@ -3774,7 +3793,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Tailor-made home financing solutions to ease the process of owning a home.</t>
+          <t>From Working Capital to Structured Finance, Emirates Islamic provides tailored Islamic finance offerings designed to help businesses grow sustainably. • Did you know Emirates Islamic offers fully Shariah-compliant Corporate Finance solutions?</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3797,12 +3816,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2050485444593246460</t>
+          <t>2050485448754004332</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2050485444593246460</t>
+          <t>https://x.com/emiratesislamic/status/2050485448754004332</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3828,16 +3847,16 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>حلول للتمويل السكني مصممة خصيصاً لتتيح لك امتلاك منزلك في منتهى الراحة.
-اطلع على المزيد
-emiratesislamic.ae/ar/person…</t>
+          <t>Tailor-made home financing solutions to ease the process of owning a home.
+Learn More
+emiratesislamic.ae/en/person…</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>حلول للتمويل السكني مصممة خصيصاً لتتيح لك امتلاك منزلك في منتهى الراحة.
-اطلع على المزيد
-&lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=home_finance"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
+          <t>Tailor-made home financing solutions to ease the process of owning a home.
+Learn More
+&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=home_finance"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K21" t="b">
@@ -3861,20 +3880,20 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/ar/personal-banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=home_finance']</t>
+          <t>['https://www.emiratesislamic.ae/en/personal-banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=home_finance']</t>
         </is>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -3883,24 +3902,23 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>حلول للتمويل السكني مصممة خصيصاً لتتيح لك امتلاك منزلك في منتهى الراحة.
-اطلع على المزيد
-emiratesislamic.ae/ar/person…</t>
+          <t>Tailor-made home financing solutions to ease the process of owning a home.
+Learn More
+emiratesislamic.ae/en/person…</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>حلول للتمويل السكني مصممة خصيصاً لتتيح لك امتلاك منزلك في منتهى الراحة.
-اطلع على المزيد
-emiratesislamic.ae/ar/person…</t>
+          <t>Tailor-made home financing solutions to ease the process of owning a home.
+Learn More
+emiratesislamic.ae/en/person…</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Solutions for home financing designed specifically to allow you to own your home with utmost comfort. 
-Learn more.</t>
+          <t>Tailor-made home financing solutions to ease the process of owning a home.</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3910,7 +3928,7 @@
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE21" s="2" t="n">
@@ -3931,7 +3949,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Solutions for home financing designed specifically to allow you to own your home with utmost comfort.</t>
+          <t>Tailor-made home financing solutions to ease the process of owning a home.</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3954,12 +3972,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2050455250096541870</t>
+          <t>2050485444593246460</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2050455250096541870</t>
+          <t>https://x.com/emiratesislamic/status/2050485444593246460</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3985,14 +4003,16 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Financing that aligns with both values and vision.
-Learn more: emiratesislamic.ae/en/corpor…</t>
+          <t>حلول للتمويل السكني مصممة خصيصاً لتتيح لك امتلاك منزلك في منتهى الراحة.
+اطلع على المزيد
+emiratesislamic.ae/ar/person…</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Financing that aligns with both values and vision.
-Learn more: &lt;a href="http://emiratesislamic.ae/en/corporate-and-institutional-banking"&gt;emiratesislamic.ae/en/corpor…&lt;/a&gt;</t>
+          <t>حلول للتمويل السكني مصممة خصيصاً لتتيح لك امتلاك منزلك في منتهى الراحة.
+اطلع على المزيد
+&lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=home_finance"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K22" t="b">
@@ -4002,34 +4022,34 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 6:00 AM UTC</t>
+          <t>May 2, 2026 · 8:00 AM UTC</t>
         </is>
       </c>
       <c r="P22" s="2" t="n">
-        <v>46144.25</v>
+        <v>46144.33333333334</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
-          <t>['http://emiratesislamic.ae/en/corporate-and-institutional-banking']</t>
+          <t>['https://www.emiratesislamic.ae/ar/personal-banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=home_finance']</t>
         </is>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -4038,21 +4058,24 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Financing that aligns with both values and vision.
-Learn more: emiratesislamic.ae/en/corpor…</t>
+          <t>حلول للتمويل السكني مصممة خصيصاً لتتيح لك امتلاك منزلك في منتهى الراحة.
+اطلع على المزيد
+emiratesislamic.ae/ar/person…</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Financing that aligns with both values and vision.
-Learn more: emiratesislamic.ae/en/corpor…</t>
+          <t>حلول للتمويل السكني مصممة خصيصاً لتتيح لك امتلاك منزلك في منتهى الراحة.
+اطلع على المزيد
+emiratesislamic.ae/ar/person…</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Financing that aligns with both values and vision.</t>
+          <t>Solutions for housing finance designed specifically to allow you to own your home with utmost comfort. 
+Learn more</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -4066,7 +4089,7 @@
         </is>
       </c>
       <c r="AE22" s="2" t="n">
-        <v>46144.41666666666</v>
+        <v>46144.5</v>
       </c>
       <c r="AF22" s="2" t="n">
         <v>46144</v>
@@ -4083,7 +4106,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Financing that aligns with both values and vision.</t>
+          <t>Solutions for housing finance designed specifically to allow you to own your home with utmost comfort.</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -4106,12 +4129,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2050448328266063924</t>
+          <t>2050455250096541870</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2050448328266063924</t>
+          <t>https://x.com/emiratesislamic/status/2050455250096541870</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4137,38 +4160,40 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
+          <t>Financing that aligns with both values and vision.
+Learn more: emiratesislamic.ae/en/corpor…</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
+          <t>Financing that aligns with both values and vision.
+Learn more: &lt;a href="http://emiratesislamic.ae/en/corporate-and-institutional-banking"&gt;emiratesislamic.ae/en/corpor…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K23" t="b">
         <v>0</v>
       </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>['AnkitMittal1403']</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 5:32 AM UTC</t>
+          <t>May 2, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P23" s="2" t="n">
-        <v>46144.23055555556</v>
+        <v>46144.25</v>
       </c>
       <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>['http://emiratesislamic.ae/en/corporate-and-institutional-banking']</t>
+        </is>
+      </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
@@ -4179,7 +4204,7 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -4188,24 +4213,26 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
+          <t>Financing that aligns with both values and vision.
+Learn more: emiratesislamic.ae/en/corpor…</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
+          <t>Financing that aligns with both values and vision.
+Learn more: emiratesislamic.ae/en/corpor…</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Dear customer, we have tried to reach you through direct message, but unfortunately, we were not successful because you are not following our page. Please direct message us back so we can assist you better.</t>
+          <t>Financing that aligns with both values and vision.</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Cust</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -4214,7 +4241,7 @@
         </is>
       </c>
       <c r="AE23" s="2" t="n">
-        <v>46144.39722222222</v>
+        <v>46144.41666666666</v>
       </c>
       <c r="AF23" s="2" t="n">
         <v>46144</v>
@@ -4231,7 +4258,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Dear customer, we have tried to reach you through direct message, but unfortunately, we were not successful because you are not following our page. • Please direct message us back so we can assist you better.</t>
+          <t>Financing that aligns with both values and vision.</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -4244,7 +4271,7 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>AnkitMittal1403</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4254,47 +4281,43 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2050373118900977885</t>
+          <t>2050448328266063924</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis/status/2050373118900977885</t>
+          <t>https://x.com/emiratesislamic/status/2050448328266063924</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>STKgenghis</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>khana-b-dosh</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1243248207293026305/b_s7UBzl_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>I will not be able to use airport lounge access because my card is blocked. 
-No one from your 'team' has reached out. I have no dues. 
-Why should I continue an approx 40 year old relationship? You have denied me access without notification.</t>
+          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>I will not be able to use airport lounge access because my card is blocked. 
-No one from your &amp;#39;team&amp;#39; has reached out. I have no dues. 
-Why should I continue an approx 40 year old relationship? You have denied me access without notification.</t>
+          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
         </is>
       </c>
       <c r="K24" t="b">
@@ -4303,21 +4326,21 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_AE']</t>
+          <t>['AnkitMittal1403']</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>May 2</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 12:33 AM UTC</t>
+          <t>May 2, 2026 · 5:32 AM UTC</t>
         </is>
       </c>
       <c r="P24" s="2" t="n">
-        <v>46144.02291666667</v>
+        <v>46144.23055555556</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
@@ -4331,34 +4354,28 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>I will not be able to use airport lounge access because my card is blocked. 
-No one from your 'team' has reached out. I have no dues. 
-Why should I continue an approx 40 year old relationship? You have denied me access without notification.</t>
+          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>I will not be able to use airport lounge access because my card is blocked. 
-No one from your 'team' has reached out. I have no dues. 
-Why should I continue an approx 40 year old relationship? You have denied me access without notification.</t>
+          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>I will not be able to use airport lounge access because my card is blocked. 
-No one from your team has reached out. I have no dues. 
-Why should I continue a relationship that has lasted approximately 40 years? You have denied me access without notification.</t>
+          <t>Dear customer, we have tried to reach you through direct message, but unfortunately, we were not successful because you are not following our page. Please DM us back so we can assist you better.</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -4368,33 +4385,33 @@
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE24" s="2" t="n">
-        <v>46144.18958333333</v>
+        <v>46144.39722222222</v>
       </c>
       <c r="AF24" s="2" t="n">
         <v>46144</v>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
+          <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Why should I continue a relationship that has lasted approximately 40 years? • I will not be able to use airport lounge access because my card is blocked. • You have denied me access without notification.</t>
+          <t>Dear customer, we have tried to reach you through direct message, but unfortunately, we were not successful because you are not following our page. • Please DM us back so we can assist you better.</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank (ENBD)</t>
+          <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AK24" t="n">
@@ -4402,7 +4419,7 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>AnkitMittal1403</t>
         </is>
       </c>
     </row>
@@ -4412,43 +4429,47 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2050596951385944148</t>
+          <t>2050373118900977885</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://x.com/chin2to/status/2050596951385944148</t>
+          <t>https://x.com/STKgenghis/status/2050373118900977885</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://x.com/chin2to</t>
+          <t>https://x.com/STKgenghis</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>chin2to</t>
+          <t>STKgenghis</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Chintn S. Padhya</t>
+          <t>khana-b-dosh</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2006918638885060609/VLnYZV2k_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1243248207293026305/b_s7UBzl_bigger.jpg</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Finally thought I'll get an @EmiratesNBD_AE Skywards Credit Card, but applying for one is such a hassle. Changed my mind immediately after speaking to them for 2 months.</t>
+          <t>@EmiratesNBD_AE I will not be able to use airport lounge access because my card is blocked. 
+No one from your 'team' has reached out. I have no dues. 
+Why should I continue an approx 40 year old relationship? You have denied me access without notification.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>This is such a nightmare. The entire experience has been a nightmare and nothing more. Every time I call you guys, you say 48 working hours and then nothing! I can&amp;#39;t even cancel the credit card. It isn&amp;#39;t rocket science. Just call me back and cancel the card. Simple.</t>
+          <t>I will not be able to use airport lounge access because my card is blocked. 
+No one from your &amp;#39;team&amp;#39; has reached out. I have no dues. 
+Why should I continue an approx 40 year old relationship? You have denied me access without notification.</t>
         </is>
       </c>
       <c r="K25" t="b">
@@ -4462,21 +4483,21 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>May 2</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 3:23 PM UTC</t>
+          <t>May 2, 2026 · 12:33 AM UTC</t>
         </is>
       </c>
       <c r="P25" s="2" t="n">
-        <v>46144.64097222222</v>
+        <v>46144.02291666667</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -4485,7 +4506,7 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -4494,27 +4515,35 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>This is such a nightmare. The entire experience has been a nightmare and nothing more. Every time I call you guys, you say 48 working hours and then nothing! I can't even cancel the credit card. It isn't rocket science. Just call me back and cancel the card. Simple.</t>
+          <t>I will not be able to use airport lounge access because my card is blocked. 
+No one from your 'team' has reached out. I have no dues. 
+Why should I continue an approx 40 year old relationship? You have denied me access without notification.</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>https://x.com/chin2to/status/2050596951385944148</t>
+          <t>https://x.com/STKgenghis/status/2050373118900977885</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>Finally thought I'll get an @EmiratesNBD_AE Skywards Credit Card, but applying for one is such a hassle. Changed my mind immediately after speaking to them for 2 months.</t>
+          <t>@EmiratesNBD_AE I will not be able to use airport lounge access because my card is blocked. 
+No one from your 'team' has reached out. I have no dues. 
+Why should I continue an approx 40 year old relationship? You have denied me access without notification.</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>Finally thought I'll get an @EmiratesNBD_AE Skywards Credit Card, but applying for one is such a hassle. Changed my mind immediately after speaking to them for 2 months.</t>
+          <t>@EmiratesNBD_AE I will not be able to use airport lounge access because my card is blocked. 
+No one from your 'team' has reached out. I have no dues. 
+Why should I continue an approx 40 year old relationship? You have denied me access without notification.</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Finally thought I'd get an Emirates NBD Skywards Credit Card, but applying for one is such a hassle. I changed my mind immediately after speaking to them for 2 months.</t>
+          <t>I will not be able to use airport lounge access because my card is blocked. 
+No one from your team has reached out. I have no dues. 
+Why should I continue a relationship of approximately 40 years? You have denied me access without notification.</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -4528,7 +4557,7 @@
         </is>
       </c>
       <c r="AE25" s="2" t="n">
-        <v>46144.80763888889</v>
+        <v>46144.18958333333</v>
       </c>
       <c r="AF25" s="2" t="n">
         <v>46144</v>
@@ -4545,7 +4574,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Finally thought I'd get an Emirates NBD Skywards Credit Card, but applying for one is such a hassle. • I changed my mind immediately after speaking to them for 2 months.</t>
+          <t>I will not be able to use airport lounge access because my card is blocked. • Why should I continue a relationship of approximately 40 years? • You have denied me access without notification.</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -4568,69 +4597,69 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2050424878524940571</t>
+          <t>2050596951385944148</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://x.com/praksoni/status/2050424878524940571</t>
+          <t>https://x.com/chin2to/status/2050596951385944148</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://x.com/praksoni</t>
+          <t>https://x.com/chin2to</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>praksoni</t>
+          <t>chin2to</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>prakash soni</t>
+          <t>Chintn S. Padhya</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/2006918638885060609/VLnYZV2k_bigger.jpg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>@EmiratesIslamic You claim an AED 22k theft is "secure" just because it’s Apple Wallet? Your system failed to see that a UAE "Darb" enrollment turned into a massive London spending spree. I reported it at the exact minute it happened. This is a failure of your fraud monitoring.</t>
+          <t>Finally thought I'll get an @EmiratesNBD_AE Skywards Credit Card, but applying for one is such a hassle. Changed my mind immediately after speaking to them for 2 months.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@EmiratesIslamic&lt;/a&gt; You claim an AED 22k theft is &amp;#34;secure&amp;#34; just because it’s Apple Wallet? Your system failed to see that a UAE &amp;#34;Darb&amp;#34; enrollment turned into a massive London spending spree. I reported it at the exact minute it happened. This is a failure of your fraud monitoring.</t>
+          <t>This is such a nightmare. The entire experience has been a nightmare and nothing more. Every time I call you guys, you say 48 working hours and then nothing! I can&amp;#39;t even cancel the credit card. It isn&amp;#39;t rocket science. Just call me back and cancel the card. Simple.</t>
         </is>
       </c>
       <c r="K26" t="b">
         <v>0</v>
       </c>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 3:59 AM UTC</t>
+          <t>May 2, 2026 · 3:23 PM UTC</t>
         </is>
       </c>
       <c r="P26" s="2" t="n">
-        <v>46144.16597222222</v>
+        <v>46144.64097222222</v>
       </c>
       <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>['https://x.com/emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="R26" t="inlineStr"/>
       <c r="S26" t="n">
         <v>1</v>
       </c>
@@ -4641,36 +4670,36 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>@EmiratesIslamic You claim an AED 22k theft is "secure" just because it’s Apple Wallet? Your system failed to see that a UAE "Darb" enrollment turned into a massive London spending spree. I reported it at the exact minute it happened. This is a failure of your fraud monitoring.</t>
+          <t>This is such a nightmare. The entire experience has been a nightmare and nothing more. Every time I call you guys, you say 48 working hours and then nothing! I can't even cancel the credit card. It isn't rocket science. Just call me back and cancel the card. Simple.</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>https://x.com/praksoni/status/2050424878524940571</t>
+          <t>https://x.com/chin2to/status/2050596951385944148</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>@EmiratesIslamic You claim an AED 22k theft is "secure" just because it’s Apple Wallet? Your system failed to see that a UAE "Darb" enrollment turned into a massive London spending spree. I reported it at the exact minute it happened. This is a failure of your fraud monitoring.</t>
+          <t>Finally thought I'll get an @EmiratesNBD_AE Skywards Credit Card, but applying for one is such a hassle. Changed my mind immediately after speaking to them for 2 months.</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>@EmiratesIslamic You claim an AED 22k theft is "secure" just because it’s Apple Wallet? Your system failed to see that a UAE "Darb" enrollment turned into a massive London spending spree. I reported it at the exact minute it happened. This is a failure of your fraud monitoring.</t>
+          <t>Finally thought I'll get an @EmiratesNBD_AE Skywards Credit Card, but applying for one is such a hassle. Changed my mind immediately after speaking to them for 2 months.</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>You claim an AED 22k theft is "secure" just because it’s Apple Wallet? Your system failed to see that a UAE "Darb" enrollment turned into a massive London spending spree. I reported it at the exact minute it happened. This is a failure of your fraud monitoring.</t>
+          <t>Finally thought I'd get an Emirates NBD Skywards Credit Card, but applying for one is such a hassle. I changed my mind immediately after speaking to them for 2 months.</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4684,35 +4713,183 @@
         </is>
       </c>
       <c r="AE26" s="2" t="n">
-        <v>46144.33263888889</v>
+        <v>46144.80763888889</v>
       </c>
       <c r="AF26" s="2" t="n">
         <v>46144</v>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
+          <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>You claim an AED 22k theft is "secure" just because it’s Apple Wallet? • Your system failed to see that a UAE "Darb" enrollment turned into a massive London spending spree. • I reported it at the exact minute it happened.</t>
+          <t>Finally thought I'd get an Emirates NBD Skywards Credit Card, but applying for one is such a hassle. • I changed my mind immediately after speaking to them for 2 months.</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>Emirates Islamic Bank (EIB)</t>
+          <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
       <c r="AK26" t="n">
         <v>2026</v>
       </c>
       <c r="AL26" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2050424878524940571</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://x.com/praksoni/status/2050424878524940571</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://x.com/praksoni</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>praksoni</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>prakash soni</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>@EmiratesIslamic You claim an AED 22k theft is "secure" just because it’s Apple Wallet? Your system failed to see that a UAE "Darb" enrollment turned into a massive London spending spree. I reported it at the exact minute it happened. This is a failure of your fraud monitoring.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@EmiratesIslamic&lt;/a&gt; You claim an AED 22k theft is &amp;#34;secure&amp;#34; just because it’s Apple Wallet? Your system failed to see that a UAE &amp;#34;Darb&amp;#34; enrollment turned into a massive London spending spree. I reported it at the exact minute it happened. This is a failure of your fraud monitoring.</t>
+        </is>
+      </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>May 2, 2026 · 3:59 AM UTC</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="n">
+        <v>46144.16597222222</v>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>14</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>@EmiratesIslamic You claim an AED 22k theft is "secure" just because it’s Apple Wallet? Your system failed to see that a UAE "Darb" enrollment turned into a massive London spending spree. I reported it at the exact minute it happened. This is a failure of your fraud monitoring.</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>@EmiratesIslamic You claim an AED 22k theft is "secure" just because it’s Apple Wallet? Your system failed to see that a UAE "Darb" enrollment turned into a massive London spending spree. I reported it at the exact minute it happened. This is a failure of your fraud monitoring.</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>You claim an AED 22k theft is "secure" just because it’s Apple Wallet? Your system failed to see that a UAE "Darb" enrollment turned into a massive London spending spree. I reported it at the exact minute it happened. This is a failure of your fraud monitoring.</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AE27" s="2" t="n">
+        <v>46144.33263888889</v>
+      </c>
+      <c r="AF27" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>2. Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>You claim an AED 22k theft is "secure" just because it’s Apple Wallet? • Your system failed to see that a UAE "Darb" enrollment turned into a massive London spending spree. • I reported it at the exact minute it happened.</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AK27" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL27" t="inlineStr">
         <is>
           <t>None</t>
         </is>

--- a/check2.xlsx
+++ b/check2.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL27"/>
+  <dimension ref="A1:AL19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,53 +625,43 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2050640575183962333</t>
+          <t>2051149273409143066</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/Waleedels_/status/2050640575183962333</t>
+          <t>https://x.com/patilabhijeet45/status/2051149273409143066</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/Waleedels_</t>
+          <t>https://x.com/patilabhijeet45</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Waleedels_</t>
+          <t>patilabhijeet45</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>وليد</t>
+          <t>abhijeet patil</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1912827800140013568/5UJC1UkQ_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1383992370509668355/lHQxfCEH_bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>عندك بطاقه ائتمانيه من مصرف الإنماء ؟
-اليوم تم إصدار كشف الحساب للبطاقات الائتمانيه .. 
-أهم نصيحتين :
-* سدد أجمالي المبلغ المستحق . ( احذر من سداد الحد الأدنى فقط )
-** سدد قبل تاريخ الاستحقاق 25 مايو 2026 . https://t.co/TtUyMKxK21</t>
+          <t>@EmiratesNBD_AE hello team need your assistance please dm.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>🤔
-عندي بطاقات الراجحي (المرابحة والكاش باك)
-بطاقة مزيد — ENBD
-بطاقة انفينت المسافر — Bsf 
-بطاقة سيجنتشر تمكين بلس — البلاد 
-فماذا يميز بطاقات مصرف الانماء لو سمحت من تجربتك حيث استنفذت الحد بالكامل 
-⚠️ لا انصح طبعا بتعدد البطاقات لانها سلاح ذو حدين</t>
+          <t>I have sent an email.</t>
         </is>
       </c>
       <c r="K2" t="b">
@@ -680,21 +670,21 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>['Jaw_02']</t>
+          <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>8h</t>
+          <t>5m</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 6:16 PM UTC</t>
+          <t>May 4, 2026 · 3:57 AM UTC</t>
         </is>
       </c>
       <c r="P2" s="2" t="n">
-        <v>46144.76111111111</v>
+        <v>46146.16458333333</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
@@ -705,10 +695,10 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>808</v>
+        <v>2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -717,45 +707,27 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>🤔
-عندي بطاقات الراجحي (المرابحة والكاش باك)
-بطاقة مزيد — ENBD
-بطاقة انفينت المسافر — Bsf 
-بطاقة سيجنتشر تمكين بلس — البلاد 
-فماذا يميز بطاقات مصرف الانماء لو سمحت من تجربتك حيث استنفذت الحد بالكامل 
-⚠️ لا انصح طبعا بتعدد البطاقات لانها سلاح ذو حدين</t>
+          <t>I have sent an email.</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>https://x.com/Waleedels_/status/2050640575183962333</t>
+          <t>https://x.com/patilabhijeet45/status/2051149273409143066</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>عندك بطاقه ائتمانيه من مصرف الإنماء ؟
-اليوم تم إصدار كشف الحساب للبطاقات الائتمانيه .. 
-أهم نصيحتين :
-* سدد أجمالي المبلغ المستحق . ( احذر من سداد الحد الأدنى فقط )
-** سدد قبل تاريخ الاستحقاق 25 مايو 2026 . https://t.co/TtUyMKxK21</t>
+          <t>@EmiratesNBD_AE hello team need your assistance please dm.</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>عندك بطاقه ائتمانيه من مصرف الإنماء ؟
-اليوم تم إصدار كشف الحساب للبطاقات الائتمانيه .. 
-أهم نصيحتين :
-* سدد أجمالي المبلغ المستحق . ( احذر من سداد الحد الأدنى فقط )
-** سدد قبل تاريخ الاستحقاق 25 مايو 2026 . https://t.co/TtUyMKxK21</t>
+          <t>@EmiratesNBD_AE hello team need your assistance please dm.</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Do you have a credit card from Alinma Bank? 
-Today, the statement for credit cards has been issued. 
-Two important tips: 
-* Pay the total amount due. (Beware of paying only the minimum amount) 
-** Pay before the due date of May 25, 2026.</t>
+          <t>Hello team, I need your assistance, please direct message me.</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -769,10 +741,10 @@
         </is>
       </c>
       <c r="AE2" s="2" t="n">
-        <v>46144.92777777778</v>
+        <v>46146.33125</v>
       </c>
       <c r="AF2" s="2" t="n">
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
@@ -786,7 +758,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>(Beware of paying only the minimum amount) ** Pay before the due date of May 25, 2026. • Two important tips: * Pay the total amount due. • Today, the statement for credit cards has been issued.</t>
+          <t>Hello team, I need your assistance, please direct message me.</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -799,7 +771,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>Jaw_02</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
@@ -809,43 +781,46 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2050638510642569502</t>
+          <t>2051134720344535096</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/homehustlerduba/status/2050638510642569502</t>
+          <t>https://x.com/ClapPakistan/status/2051134720344535096</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/homehustlerduba</t>
+          <t>https://x.com/ClapPakistan</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>homehustlerduba</t>
+          <t>ClapPakistan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>H&amp;H Real Estate</t>
+          <t>Clap</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1760746331201585152/TKyLTFah_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1813702655031562240/RuM4t2kR_bigger.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>UAE hotels are expected to resume hiring after ongoing refurbishments, but with a clear shift toward leaner, more efficient workforce models focused on multi-skilled and adaptable talent. Industry leaders say rehiring will prioritise quality over quantity, with teams designed to https://t.co/GK7z6Brnli</t>
+          <t>Peshawar Zalmi Defeats Hyderabad Kingsmen to Win PSL 11 Final
+The image is AI-generated and is just for reference.
+#PSL11 #PSLFinal #PeshawarZalmi #HyderabadKingsmen https://t.co/2zhkzsurQv</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Visa has appointed Emirates NBD as its UAE settlement agent, enabling domestic card transactions to be processed locally in dirhams instead of through international systems. This shift is expected to deliver faster payment confirmations, more reliable everyday transactions and</t>
+          <t>Syed Saad Shafi is Director – Signature Banking at Emirates NBD in Dubai, specializing in wealth management and global investment strategies for high-net-worth clients, overseeing multi-billion dirham portfolios.
+&lt;a href="/search?f=tweets&amp;amp;q=%23ClapPakistan"&gt;#ClapPakistan&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K3" t="b">
@@ -855,19 +830,23 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>8h</t>
+          <t>1h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 6:08 PM UTC</t>
+          <t>May 4, 2026 · 3:00 AM UTC</t>
         </is>
       </c>
       <c r="P3" s="2" t="n">
-        <v>46144.75555555556</v>
+        <v>46146.125</v>
       </c>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23ClapPakistan']</t>
+        </is>
+      </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
@@ -878,7 +857,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -887,27 +866,32 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Visa has appointed Emirates NBD as its UAE settlement agent, enabling domestic card transactions to be processed locally in dirhams instead of through international systems. This shift is expected to deliver faster payment confirmations, more reliable everyday transactions and</t>
+          <t>Syed Saad Shafi is Director – Signature Banking at Emirates NBD in Dubai, specializing in wealth management and global investment strategies for high-net-worth clients, overseeing multi-billion dirham portfolios.
+#ClapPakistan</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>https://x.com/homehustlerduba/status/2050638510642569502</t>
+          <t>https://x.com/ClapPakistan/status/2051134720344535096</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>UAE hotels are expected to resume hiring after ongoing refurbishments, but with a clear shift toward leaner, more efficient workforce models focused on multi-skilled and adaptable talent. Industry leaders say rehiring will prioritise quality over quantity, with teams designed to https://t.co/GK7z6Brnli</t>
+          <t>Peshawar Zalmi Defeats Hyderabad Kingsmen to Win PSL 11 Final
+The image is AI-generated and is just for reference.
+#PSL11 #PSLFinal #PeshawarZalmi #HyderabadKingsmen https://t.co/2zhkzsurQv</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>UAE hotels are expected to resume hiring after ongoing refurbishments, but with a clear shift toward leaner, more efficient workforce models focused on multi-skilled and adaptable talent. Industry leaders say rehiring will prioritise quality over quantity, with teams designed to https://t.co/GK7z6Brnli</t>
+          <t>Peshawar Zalmi Defeats Hyderabad Kingsmen to Win PSL 11 Final
+The image is AI-generated and is just for reference.
+#PSL11 #PSLFinal #PeshawarZalmi #HyderabadKingsmen https://t.co/2zhkzsurQv</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>UAE hotels are expected to resume hiring after ongoing refurbishments, but with a clear shift toward leaner, more efficient workforce models focused on multi-skilled and adaptable talent. Industry leaders say rehiring will prioritize quality over quantity, with teams designed to be more versatile.</t>
+          <t>Peshawar Zalmi defeats Hyderabad Kingsmen to win the PSL 11 final.</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -921,10 +905,10 @@
         </is>
       </c>
       <c r="AE3" s="2" t="n">
-        <v>46144.92222222222</v>
+        <v>46146.29166666666</v>
       </c>
       <c r="AF3" s="2" t="n">
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
@@ -938,7 +922,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>UAE hotels are expected to resume hiring after ongoing refurbishments, but with a clear shift toward leaner, more efficient workforce models focused on multi-skilled and adaptable talent. • Industry leaders say rehiring will prioritize quality over quantity, with teams designed to be more versatile.</t>
+          <t>Peshawar Zalmi defeats Hyderabad Kingsmen to win the PSL 11 final.</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -961,57 +945,43 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2050634843697152368</t>
+          <t>2050981352871264409</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/VedantKabra19/status/2050634843697152368</t>
+          <t>https://x.com/TrioMsPaname/status/2050981352871264409</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/VedantKabra19</t>
+          <t>https://x.com/TrioMsPaname</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>VedantKabra19</t>
+          <t>TrioMsPaname</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedant Kabra</t>
+          <t>yiahhhh</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2042611377949544449/zCad3iJc_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2043404881177006080/8Iry1NlJ_bigger.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>A great shortcut tool to analyse your mutual fund portfolio:- 
-The test takes 30 seconds: 
-Open your fund’s factsheet. If 60-70%+ of the portfolio is concentrated in the top 15-20 stocks by market cap (HDFC Bank, Reliance, TCS, ICICI, Infosys, SBI etc.) 
-Then you’re actively paying fees for what is effectively a Nifty 50 ETF. 
-Even despite such holdings, 76% of large cap funds have failed to beat the index over a 10 year period. 
-84% over five years. 
-The solution is also fairly simple:- 
-You can consider switching these to a low cost Nifty 50 ETF and pocket the TER expense. 
-Incase you need help with your portfolio, feel free to reach out to me.</t>
+          <t>Dubai prouve que ni la religion ni les étrangers sont le problème d’un état. Dubai tient avec 90% d étrangers. Tout le monde se tien à carreau, j’ai vécu une expérience incroyable de service, de sécurité et de kif. Merci @EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>In the last 6-12 months:
-1. Emirates NBD Bank has acquired a controlling stake (54%) in RBL Bank
-2. IHC (International Holding Company, Abu Dhabi) has acquired a 41.5% stake in Sammaan Capital, with a mandatory open offer for an additional 26%, which could take IHC&amp;#39;s total stake to ~63-67% on a fully diluted basis.
-3. Sumitomo Mitsui Banking Corporation (SMBC) bought a 24.2% stake in Yes Bank
-4. Mitsubishi UFJ Financial Group (MUFG) Bank acquired a 20% stake in Shriram Finance
-FIIs must be net sellers but select foreign institutions are clearly positioning to capitalise on India&amp;#39;s long term credit growth thesis.
-&lt;a href="/search?f=tweets&amp;amp;q=%23Banking"&gt;#Banking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23NBFC"&gt;#NBFC&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23NSE"&gt;#NSE&lt;/a&gt;</t>
+          <t>Dubai prouve que ni la religion ni les étrangers sont le problème d’un état. Dubai tient avec 90% d étrangers. Tout le monde se tien à carreau, j’ai vécu une expérience incroyable de service, de sécurité et de kif. Merci &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K4" t="b">
@@ -1021,34 +991,34 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 5:53 PM UTC</t>
+          <t>May 3, 2026 · 4:50 PM UTC</t>
         </is>
       </c>
       <c r="P4" s="2" t="n">
-        <v>46144.74513888889</v>
+        <v>46145.70138888889</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23Banking', 'https://x.com/search?f=tweets&amp;q=%23NBFC', 'https://x.com/search?f=tweets&amp;q=%23NSE']</t>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -1057,57 +1027,27 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>In the last 6-12 months:
-1. Emirates NBD Bank has acquired a controlling stake (54%) in RBL Bank
-2. IHC (International Holding Company, Abu Dhabi) has acquired a 41.5% stake in Sammaan Capital, with a mandatory open offer for an additional 26%, which could take IHC's total stake to ~63-67% on a fully diluted basis.
-3. Sumitomo Mitsui Banking Corporation (SMBC) bought a 24.2% stake in Yes Bank
-4. Mitsubishi UFJ Financial Group (MUFG) Bank acquired a 20% stake in Shriram Finance
-FIIs must be net sellers but select foreign institutions are clearly positioning to capitalise on India's long term credit growth thesis.
-#Banking #NBFC #NSE</t>
+          <t>Dubai prouve que ni la religion ni les étrangers sont le problème d’un état. Dubai tient avec 90% d étrangers. Tout le monde se tien à carreau, j’ai vécu une expérience incroyable de service, de sécurité et de kif. Merci @EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>https://x.com/VedantKabra19/status/2050634843697152368</t>
+          <t>https://x.com/TrioMsPaname/status/2050981352871264409</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>A great shortcut tool to analyse your mutual fund portfolio:- 
-The test takes 30 seconds: 
-Open your fund’s factsheet. If 60-70%+ of the portfolio is concentrated in the top 15-20 stocks by market cap (HDFC Bank, Reliance, TCS, ICICI, Infosys, SBI etc.) 
-Then you’re actively paying fees for what is effectively a Nifty 50 ETF. 
-Even despite such holdings, 76% of large cap funds have failed to beat the index over a 10 year period. 
-84% over five years. 
-The solution is also fairly simple:- 
-You can consider switching these to a low cost Nifty 50 ETF and pocket the TER expense. 
-Incase you need help with your portfolio, feel free to reach out to me.</t>
+          <t>Dubai prouve que ni la religion ni les étrangers sont le problème d’un état. Dubai tient avec 90% d étrangers. Tout le monde se tien à carreau, j’ai vécu une expérience incroyable de service, de sécurité et de kif. Merci @EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>A great shortcut tool to analyse your mutual fund portfolio:- 
-The test takes 30 seconds: 
-Open your fund’s factsheet. If 60-70%+ of the portfolio is concentrated in the top 15-20 stocks by market cap (HDFC Bank, Reliance, TCS, ICICI, Infosys, SBI etc.) 
-Then you’re actively paying fees for what is effectively a Nifty 50 ETF. 
-Even despite such holdings, 76% of large cap funds have failed to beat the index over a 10 year period. 
-84% over five years. 
-The solution is also fairly simple:- 
-You can consider switching these to a low cost Nifty 50 ETF and pocket the TER expense. 
-Incase you need help with your portfolio, feel free to reach out to me.</t>
+          <t>Dubai prouve que ni la religion ni les étrangers sont le problème d’un état. Dubai tient avec 90% d étrangers. Tout le monde se tien à carreau, j’ai vécu une expérience incroyable de service, de sécurité et de kif. Merci @EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>A great shortcut tool to analyze your mutual fund portfolio: 
-The test takes 30 seconds: 
-Open your fund’s factsheet. If 60-70%+ of the portfolio is concentrated in the top 15-20 stocks by market cap (HDFC Bank, Reliance, TCS, ICICI, Infosys, SBI, etc.) 
-Then you’re actively paying fees for what is effectively a Nifty 50 ETF. 
-Even despite such holdings, 76% of large cap funds have failed to beat the index over a 10-year period. 
-84% over five years. 
-The solution is also fairly simple: 
-You can consider switching these to a low-cost Nifty 50 ETF and pocket the TER expense. 
-In case you need help with your portfolio, feel free to reach out to me.</t>
+          <t>Dubai proves that neither religion nor foreigners are the problem of a state. Dubai has 90% foreigners. Everyone behaves well; I had an incredible experience of service, security, and enjoyment. Thank you @EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1117,14 +1057,14 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE4" s="2" t="n">
-        <v>46144.91180555556</v>
+        <v>46145.86805555555</v>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
@@ -1138,7 +1078,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Even despite such holdings, 76% of large cap funds have failed to beat the index over a 10-year period. • A great shortcut tool to analyze your mutual fund portfolio: The test takes 30 seconds: Open your fund’s factsheet. • The solution is also fairly simple: You can consider switching these to a low-cost Nifty 50 ETF and pocket the TER expense.</t>
+          <t>Dubai proves that neither religion nor foreigners are the problem of a state. • Dubai has 90% foreigners. • Everyone behaves well; I had an incredible experience of service, security, and enjoyment.</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1161,68 +1101,66 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2050606238627496289</t>
+          <t>2050948913431990505</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_EGY/status/2050606238627496289</t>
+          <t>https://x.com/ConmanNickJ/status/2050948913431990505</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_EGY</t>
+          <t>https://x.com/ConmanNickJ</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>EmiratesNBD_EGY</t>
+          <t>ConmanNickJ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>conman Nick</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427526482108416/qjFPlJ1n_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1945509816476094464/YIU-DVu4_bigger.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>يفخر بنك الإمارات دبي الوطني بالمشاركة في سباق النيروفيرس في سيليا، العاصمة الإدارية الجديدة.
-نركض معًا لنشر الوعي حول التنوع العصبي بما يشمل التوحد، وفرط الحركة وتشتت الانتباه (ADHD)، وعسر القراءة (الديسلكسيا)، وغيرها من الاختلافات الذهنية لأن كل خطوة تقرّبنا من مجتمع أكثر شمولًا وتفهمًا وتمكينًا.
-رقم التسجيل الضريبي: 319-897-204</t>
+          <t>Yet the IRGC have been laundering billions through both the central bank and ENBD among other financial institutions in the UAE</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Are you still paying for everything upfront?
-Enjoy 0% installments over 6 months or get 5% cashback with no limits when you pay your TMG Club fees whether renewing your membership, adding a new member or remove one with Emirates NBD Mastercard credit card x TMG.
-Together .. it pays off
-Terms and Conditions Apply.
-Tax registration number: 204-897-319</t>
+          <t>Yet the IRGC have been laundering billions through both the central bank and ENBD among other financial institutions in the UAE</t>
         </is>
       </c>
       <c r="K5" t="b">
         <v>0</v>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>['NarcisW63452', 'amjadt25']</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 4:00 PM UTC</t>
+          <t>May 3, 2026 · 2:41 PM UTC</t>
         </is>
       </c>
       <c r="P5" s="2" t="n">
-        <v>46144.66666666666</v>
+        <v>46145.61180555556</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
@@ -1236,7 +1174,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1245,54 +1183,36 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Are you still paying for everything upfront?
-Enjoy 0% installments over 6 months or get 5% cashback with no limits when you pay your TMG Club fees whether renewing your membership, adding a new member or remove one with Emirates NBD Mastercard credit card x TMG.
-Together .. it pays off
-Terms and Conditions Apply.
-Tax registration number: 204-897-319</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_EGY/status/2050606238627496289</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>يفخر بنك الإمارات دبي الوطني بالمشاركة في سباق النيروفيرس في سيليا، العاصمة الإدارية الجديدة.
-نركض معًا لنشر الوعي حول التنوع العصبي بما يشمل التوحد، وفرط الحركة وتشتت الانتباه (ADHD)، وعسر القراءة (الديسلكسيا)، وغيرها من الاختلافات الذهنية لأن كل خطوة تقرّبنا من مجتمع أكثر شمولًا وتفهمًا وتمكينًا.
-رقم التسجيل الضريبي: 319-897-204</t>
-        </is>
-      </c>
+          <t>Yet the IRGC have been laundering billions through both the central bank and ENBD among other financial institutions in the UAE</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>يفخر بنك الإمارات دبي الوطني بالمشاركة في سباق النيروفيرس في سيليا، العاصمة الإدارية الجديدة.
-نركض معًا لنشر الوعي حول التنوع العصبي بما يشمل التوحد، وفرط الحركة وتشتت الانتباه (ADHD)، وعسر القراءة (الديسلكسيا)، وغيرها من الاختلافات الذهنية لأن كل خطوة تقرّبنا من مجتمع أكثر شمولًا وتفهمًا وتمكينًا.
-رقم التسجيل الضريبي: 319-897-204</t>
+          <t>Yet the IRGC have been laundering billions through both the central bank and ENBD among other financial institutions in the UAE</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Emirates NBD is proud to participate in the Neurovirus Race in Celia, the New Administrative Capital. 
-We run together to raise awareness about neurodiversity, including autism, attention deficit hyperactivity disorder (ADHD), dyslexia, and other mental differences, as every step brings us closer to a more inclusive, understanding, and empowering community. 
-Tax registration number: 319-897-204</t>
+          <t>Yet the IRGC has been laundering billions through both the central bank and ENBD among other financial institutions in the UAE.</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Cust</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE5" s="2" t="n">
-        <v>46144.83333333334</v>
+        <v>46145.77847222222</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
@@ -1306,7 +1226,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Tax registration number: 319-897-204 • Emirates NBD is proud to participate in the Neurovirus Race in Celia, the New Administrative Capital.</t>
+          <t>Yet the IRGC has been laundering billions through both the central bank and ENBD among other financial institutions in the UAE.</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1319,7 +1239,7 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>NarcisW63452, amjadt25</t>
         </is>
       </c>
     </row>
@@ -1329,86 +1249,80 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2050591142492651968</t>
+          <t>2050919285036360149</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/VOX_Cinemas_KSA/status/2050591142492651968</t>
+          <t>https://x.com/Professor502/status/2050919285036360149</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/VOX_Cinemas_KSA</t>
+          <t>https://x.com/Professor502</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>VOX_Cinemas_KSA</t>
+          <t>Professor502</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>VOX Cinemas KSA ڤوكس سينما السعودية</t>
+          <t>Saad</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2049106132195815424/7BCTotN4_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1908889888478425088/ezst5JDu_bigger.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>عندك بطاقات بنك الإمارات دبي الوطني ؟ العرض من نصيبك 😎
-تذكرة عليك والثانية مجانًا في #ڤوكس_سينما 
-للحجز ولتفاصيل اكثر,  اضغط على الرابط 👇
-tps://ksa.voxcinemas.com/ar/ticket-offer/emirates-nbd</t>
+          <t>ردو على الخاص لو سمحت</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>عندك بطاقات بنك الإمارات دبي الوطني ؟ العرض من نصيبك 😎
-تذكرة عليك والثانية مجانًا في &lt;a href="/search?f=tweets&amp;amp;q=%23ڤوكس_سينما"&gt;#ڤوكس_سينما&lt;/a&gt; 
-للحجز ولتفاصيل اكثر,  اضغط على الرابط 👇
-tps://ksa.voxcinemas.com/ar/ticket-offer/emirates-nbd</t>
+          <t>ردو على الخاص لو سمحت</t>
         </is>
       </c>
       <c r="K6" t="b">
         <v>0</v>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_KSA']</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 3:00 PM UTC</t>
+          <t>May 3, 2026 · 12:43 PM UTC</t>
         </is>
       </c>
       <c r="P6" s="2" t="n">
-        <v>46144.625</v>
+        <v>46145.52986111111</v>
       </c>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23ڤوكس_سينما']</t>
-        </is>
-      </c>
+      <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1944</v>
+        <v>14</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1417,27 +1331,19 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>عندك بطاقات بنك الإمارات دبي الوطني ؟ العرض من نصيبك 😎
-تذكرة عليك والثانية مجانًا في #ڤوكس_سينما 
-للحجز ولتفاصيل اكثر,  اضغط على الرابط 👇
-tps://ksa.voxcinemas.com/ar/ticket-offer/emirates-nbd</t>
+          <t>ردو على الخاص لو سمحت</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>عندك بطاقات بنك الإمارات دبي الوطني ؟ العرض من نصيبك 😎
-تذكرة عليك والثانية مجانًا في #ڤوكس_سينما 
-للحجز ولتفاصيل اكثر,  اضغط على الرابط 👇
-tps://ksa.voxcinemas.com/ar/ticket-offer/emirates-nbd</t>
+          <t>ردو على الخاص لو سمحت</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Do you have Emirates NBD bank cards? The offer is for you 😎 One ticket is on you and the second is free at #Vox_Cinemas 
-For booking and more details, click on the link 👇
-tps://ksa.voxcinemas.com/ar/ticket-offer/emirates-nbd</t>
+          <t>Please reply in private, if you don't mind.</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1447,14 +1353,14 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE6" s="2" t="n">
-        <v>46144.79166666666</v>
+        <v>46145.69652777778</v>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
@@ -1468,7 +1374,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>The offer is for you 😎 One ticket is on you and the second is free at #Vox_Cinemas For booking and more details, click on the link 👇 tps://ksa.voxcinemas.com/ar/ticket-offer/emirates-nbd • Do you have Emirates NBD bank cards?</t>
+          <t>Please reply in private, if you don't mind.</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1481,7 +1387,7 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>EmiratesNBD_KSA</t>
         </is>
       </c>
     </row>
@@ -1491,43 +1397,43 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2050582653036888115</t>
+          <t>2050908749720703120</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/moha60062/status/2050582653036888115</t>
+          <t>https://x.com/abotameem430/status/2050908749720703120</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://x.com/moha60062</t>
+          <t>https://x.com/abotameem430</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>moha60062</t>
+          <t>abotameem430</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>🇸🇦MBS🇸🇦الجنرال</t>
+          <t>Fahad</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1791484692413177856/gROHdxzJ_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1780850701616242688/Ikq26ySl_bigger.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>هل ممكن تضيف معها بطاقات انكان و النايفات خصوصاً انها تعطي بعض الفئات اعلى لايف ستايل</t>
+          <t>ارغب بالاتصال</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>هل ممكن تضيف معها بطاقات انكان و النايفات خصوصاً انها تعطي بعض الفئات اعلى لايف ستايل</t>
+          <t>ارغب بالاتصال</t>
         </is>
       </c>
       <c r="K7" t="b">
@@ -1536,21 +1442,21 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>['Mohakhu', 'snbalahli', 'alrajhibank', 'EmiratesNBD_KSA', 'BSF_sa']</t>
+          <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>12h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 2:26 PM UTC</t>
+          <t>May 3, 2026 · 12:02 PM UTC</t>
         </is>
       </c>
       <c r="P7" s="2" t="n">
-        <v>46144.60138888889</v>
+        <v>46145.50138888889</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
@@ -1564,7 +1470,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1573,19 +1479,19 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>هل ممكن تضيف معها بطاقات انكان و النايفات خصوصاً انها تعطي بعض الفئات اعلى لايف ستايل</t>
+          <t>ارغب بالاتصال</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>هل ممكن تضيف معها بطاقات انكان و النايفات خصوصاً انها تعطي بعض الفئات اعلى لايف ستايل</t>
+          <t>ارغب بالاتصال</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Could you please add Inkan and Naif cards with it, especially since they offer some categories a higher lifestyle?</t>
+          <t>I would like to make a call.</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1599,10 +1505,10 @@
         </is>
       </c>
       <c r="AE7" s="2" t="n">
-        <v>46144.76805555556</v>
+        <v>46145.66805555556</v>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
@@ -1616,7 +1522,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Could you please add Inkan and Naif cards with it, especially since they offer some categories a higher lifestyle?</t>
+          <t>I would like to make a call.</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1629,7 +1535,7 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>Mohakhu, snbalahli, alrajhibank, EmiratesNBD_KSA, BSF_sa</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
@@ -1639,43 +1545,43 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2050546053124923502</t>
+          <t>2050881500527415748</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/NovoCinemas/status/2050546053124923502</t>
+          <t>https://x.com/MahtabAbbasi11/status/2050881500527415748</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://x.com/NovoCinemas</t>
+          <t>https://x.com/MahtabAbbasi11</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>NovoCinemas</t>
+          <t>MahtabAbbasi11</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Novo Cinemas</t>
+          <t>Mahtab Abbasi</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2008888282768429056/a3q3GqDa_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2042928635620081664/TSR-bQI9_bigger.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Sometimes, all you need is a quiet escape into a great story. 🎞️🤍 Use your Emirates NBD card at Novo Cinemas to enjoy 15% off tickets any day of the week. A simple way to reward yourself with a moment of peace. Book your tickets now by visiting NovoCinemas.com or the App</t>
+          <t>Emirates NBD to settle Visa payments in UAE dirhams, a major shift for daily transactions</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Sometimes, all you need is a quiet escape into a great story. 🎞️🤍 Use your Emirates NBD card at Novo Cinemas to enjoy 15% off tickets any day of the week. A simple way to reward yourself with a moment of peace. Book your tickets now by visiting &lt;a href="http://www.NovoCinemas.com"&gt;NovoCinemas.com&lt;/a&gt; or the App</t>
+          <t>Emirates NBD to settle Visa payments in UAE dirhams, a major shift for daily transactions</t>
         </is>
       </c>
       <c r="K8" t="b">
@@ -1685,23 +1591,19 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 12:00 PM UTC</t>
+          <t>May 3, 2026 · 10:13 AM UTC</t>
         </is>
       </c>
       <c r="P8" s="2" t="n">
-        <v>46144.5</v>
+        <v>46145.42569444444</v>
       </c>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>['http://www.NovoCinemas.com']</t>
-        </is>
-      </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
         <v>0</v>
       </c>
@@ -1712,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1721,19 +1623,19 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Sometimes, all you need is a quiet escape into a great story. 🎞️🤍 Use your Emirates NBD card at Novo Cinemas to enjoy 15% off tickets any day of the week. A simple way to reward yourself with a moment of peace. Book your tickets now by visiting NovoCinemas.com or the App</t>
+          <t>Emirates NBD to settle Visa payments in UAE dirhams, a major shift for daily transactions</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Sometimes, all you need is a quiet escape into a great story. 🎞️🤍 Use your Emirates NBD card at Novo Cinemas to enjoy 15% off tickets any day of the week. A simple way to reward yourself with a moment of peace. Book your tickets now by visiting NovoCinemas.com or the App</t>
+          <t>Emirates NBD to settle Visa payments in UAE dirhams, a major shift for daily transactions</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Sometimes, all you need is a quiet escape into a great story. Use your Emirates NBD card at Novo Cinemas to enjoy 15% off tickets any day of the week. A simple way to reward yourself with a moment of peace. Book your tickets now by visiting NovoCinemas.com or the App.</t>
+          <t>Emirates NBD to settle Visa payments in UAE dirhams, a major shift for daily transactions.</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1743,14 +1645,14 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE8" s="2" t="n">
-        <v>46144.66666666666</v>
+        <v>46145.59236111111</v>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
@@ -1764,7 +1666,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Use your Emirates NBD card at Novo Cinemas to enjoy 15% off tickets any day of the week. • Book your tickets now by visiting NovoCinemas.com or the App. • Sometimes, all you need is a quiet escape into a great story.</t>
+          <t>Emirates NBD to settle Visa payments in UAE dirhams, a major shift for daily transactions.</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1787,71 +1689,73 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2050530525820109288</t>
+          <t>2050877343745388916</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://x.com/adrianD36740715/status/2050530525820109288</t>
+          <t>https://x.com/t_Abdulraahman/status/2050877343745388916</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://x.com/adrianD36740715</t>
+          <t>https://x.com/t_Abdulraahman</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>adrianD36740715</t>
+          <t>t_Abdulraahman</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>adrian Dias</t>
+          <t>T.Abdulrahman</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1653777797888843776/NhAjroqA_bigger.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Please update the promotions on the mobile banking app also.</t>
+          <t>@EmiratesNBD_AE طلبت بطاقة مزيد بحد مالي محدد 
+و وصلتني البطاقه بحد مالي عالي جداً ! كيف ممكن اقلل الحد اقدر او لا لاني مافعلت الى الان</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Please update the promotions on the mobile banking app also.</t>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; طلبت بطاقة مزيد بحد مالي محدد 
+و وصلتني البطاقه بحد مالي عالي جداً ! كيف ممكن اقلل الحد اقدر او لا لاني مافعلت الى الان</t>
         </is>
       </c>
       <c r="K9" t="b">
         <v>0</v>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 10:59 AM UTC</t>
+          <t>May 3, 2026 · 9:57 AM UTC</t>
         </is>
       </c>
       <c r="P9" s="2" t="n">
-        <v>46144.45763888889</v>
+        <v>46145.41458333333</v>
       </c>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1860,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1869,19 +1773,21 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Please update the promotions on the mobile banking app also.</t>
+          <t>@EmiratesNBD_AE طلبت بطاقة مزيد بحد مالي محدد 
+و وصلتني البطاقه بحد مالي عالي جداً ! كيف ممكن اقلل الحد اقدر او لا لاني مافعلت الى الان</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Please update the promotions on the mobile banking app also.</t>
+          <t>@EmiratesNBD_AE طلبت بطاقة مزيد بحد مالي محدد 
+و وصلتني البطاقه بحد مالي عالي جداً ! كيف ممكن اقلل الحد اقدر او لا لاني مافعلت الى الان</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Please update the promotions on the mobile banking app as well.</t>
+          <t>I requested a Mazid card with a specific credit limit, and I received the card with a very high limit! How can I reduce the limit? Can I do that since I haven't activated it yet?</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1895,10 +1801,10 @@
         </is>
       </c>
       <c r="AE9" s="2" t="n">
-        <v>46144.62430555555</v>
+        <v>46145.58125</v>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
@@ -1912,7 +1818,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Please update the promotions on the mobile banking app as well.</t>
+          <t>I requested a Mazid card with a specific credit limit, and I received the card with a very high limit! • How can I reduce the limit? • Can I do that since I haven't activated it yet?</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1925,7 +1831,7 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1935,73 +1841,45 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2050526894626427022</t>
+          <t>2050855805600092255</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://x.com/Kashif111144/status/2050526894626427022</t>
+          <t>https://x.com/gulf_news/status/2050855805600092255</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://x.com/Kashif111144</t>
+          <t>https://x.com/gulf_news</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kashif111144</t>
+          <t>gulf_news</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kashif</t>
+          <t>Gulf News</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2035721972361928704/W-51tE0S_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2044041782519050242/muvl0wJC_bigger.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>UAE controls banking sector of PK after bribing leaders 
-BANKS owned by UAE in PK(not complete list)
-1. Alfalah 
-2. Dubai Islamic  
-3. Mashreq   
-4. Emirates NBD  
-5. Emirates Global 
-6. FirstWomen
-7. Al Baraka
-8. Ubank
-9. EasyPaisa
-10. Jazzcash
-11. BML
-#Islamabad
-#Pakistan 
-#UAE https://t.co/hEotNuuvdl</t>
+          <t>Whether you're paying your bills, transferring money within the UAE, sending it abroad or exchanging currencies, Emirates NBD makes it simple and secure through the ENBD X app.
+#transfers #payments #DirectRemit #Aani #currencies #travel #GlobalCash
+https://t.co/JhadMTFApo https://t.co/WHukK5bQyz</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>UAE controls banking sector of PK after bribing leaders 
-BANKS owned by UAE in PK(not complete list)
-1. Alfalah 
-2. Dubai Islamic  
-3. Mashreq   
-4. Emirates NBD  
-5. Emirates Global 
-6. FirstWomen
-7. Al Baraka
-8. Ubank
-9. EasyPaisa
-10. Jazzcash
-11. BML
-&lt;a href="/search?f=tweets&amp;amp;q=%23Islamabad"&gt;#Islamabad&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23Pakistan"&gt;#Pakistan&lt;/a&gt; 
-&lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt;</t>
+          <t>Emirates NBD to settle Visa payments in UAE dirhams, a major shift for daily transactions &lt;a href="https://mrf.lu/FJY3"&gt;mrf.lu/FJY3&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K10" t="b">
@@ -2011,34 +1889,34 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 10:44 AM UTC</t>
+          <t>May 3, 2026 · 8:31 AM UTC</t>
         </is>
       </c>
       <c r="P10" s="2" t="n">
-        <v>46144.44722222222</v>
+        <v>46145.35486111111</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23Islamabad', 'https://x.com/search?f=tweets&amp;q=%23Pakistan', 'https://x.com/search?f=tweets&amp;q=%23UAE']</t>
+          <t>['https://mrf.lu/FJY3']</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="V10" t="n">
-        <v>110</v>
+        <v>3733</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -2047,72 +1925,31 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>UAE controls banking sector of PK after bribing leaders 
-BANKS owned by UAE in PK(not complete list)
-1. Alfalah 
-2. Dubai Islamic  
-3. Mashreq   
-4. Emirates NBD  
-5. Emirates Global 
-6. FirstWomen
-7. Al Baraka
-8. Ubank
-9. EasyPaisa
-10. Jazzcash
-11. BML
-#Islamabad
-#Pakistan 
-#UAE</t>
+          <t>Emirates NBD to settle Visa payments in UAE dirhams, a major shift for daily transactions mrf.lu/FJY3</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>https://x.com/Kashif111144/status/2050526894626427022</t>
+          <t>https://x.com/gulf_news/status/2050855805600092255</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>UAE controls banking sector of PK after bribing leaders 
-BANKS owned by UAE in PK(not complete list)
-1. Alfalah 
-2. Dubai Islamic  
-3. Mashreq   
-4. Emirates NBD  
-5. Emirates Global 
-6. FirstWomen
-7. Al Baraka
-8. Ubank
-9. EasyPaisa
-10. Jazzcash
-11. BML
-#Islamabad
-#Pakistan 
-#UAE https://t.co/hEotNuuvdl</t>
+          <t>Whether you're paying your bills, transferring money within the UAE, sending it abroad or exchanging currencies, Emirates NBD makes it simple and secure through the ENBD X app.
+#transfers #payments #DirectRemit #Aani #currencies #travel #GlobalCash
+https://t.co/JhadMTFApo https://t.co/WHukK5bQyz</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>UAE controls banking sector of PK after bribing leaders 
-BANKS owned by UAE in PK(not complete list)
-1. Alfalah 
-2. Dubai Islamic  
-3. Mashreq   
-4. Emirates NBD  
-5. Emirates Global 
-6. FirstWomen
-7. Al Baraka
-8. Ubank
-9. EasyPaisa
-10. Jazzcash
-11. BML
-#Islamabad
-#Pakistan 
-#UAE https://t.co/hEotNuuvdl</t>
+          <t>Whether you're paying your bills, transferring money within the UAE, sending it abroad or exchanging currencies, Emirates NBD makes it simple and secure through the ENBD X app.
+#transfers #payments #DirectRemit #Aani #currencies #travel #GlobalCash
+https://t.co/JhadMTFApo https://t.co/WHukK5bQyz</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>UAE controls the banking sector of Pakistan after bribing leaders. Banks owned by UAE in Pakistan (not a complete list): 1. Alfalah 2. Dubai Islamic 3. Mashreq 4. Emirates NBD 5. Emirates Global 6. First Women 7. Al Baraka 8. Ubank 9. EasyPaisa 10. Jazzcash 11. BML.</t>
+          <t>Whether you're paying your bills, transferring money within the UAE, sending it abroad, or exchanging currencies, Emirates NBD makes it simple and secure through the ENBD X app.</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -2122,14 +1959,14 @@
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE10" s="2" t="n">
-        <v>46144.61388888889</v>
+        <v>46145.52152777778</v>
       </c>
       <c r="AF10" s="2" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
@@ -2143,7 +1980,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>UAE controls the banking sector of Pakistan after bribing leaders. • Banks owned by UAE in Pakistan (not a complete list): 1.</t>
+          <t>Whether you're paying your bills, transferring money within the UAE, sending it abroad, or exchanging currencies, Emirates NBD makes it simple and secure through the ENBD X app.</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -2166,43 +2003,43 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2050510080127455613</t>
+          <t>2050845248088055847</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/SavannahP57037/status/2050510080127455613</t>
+          <t>https://x.com/z6894890/status/2050845248088055847</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://x.com/SavannahP57037</t>
+          <t>https://x.com/z6894890</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SavannahP57037</t>
+          <t>z6894890</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mohamed Farag</t>
+          <t>Femal</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2050690957138595840/LXMOA3Q7_bigger.jpg</t>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Style, comfort, and cashback… that's how we do it at TMG with Emirates NBD✨ https://t.co/bt4VAtCnZL</t>
+          <t>@EmiratesNBD_AE ابي وظيفه باي فرع من اللي بالرياض</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Style, comfort, and cashback… that&amp;#39;s how we do it at TMG with Emirates NBD✨</t>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; ابي وظيفه باي فرع من اللي بالرياض</t>
         </is>
       </c>
       <c r="K11" t="b">
@@ -2212,21 +2049,25 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 9:37 AM UTC</t>
+          <t>May 3, 2026 · 7:49 AM UTC</t>
         </is>
       </c>
       <c r="P11" s="2" t="n">
-        <v>46144.40069444444</v>
+        <v>46145.32569444444</v>
       </c>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -2235,7 +2076,7 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -2244,27 +2085,27 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Style, comfort, and cashback… that's how we do it at TMG with Emirates NBD✨</t>
+          <t>@EmiratesNBD_AE ابي وظيفه باي فرع من اللي بالرياض</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>https://x.com/SavannahP57037/status/2050510080127455613</t>
+          <t>https://x.com/z6894890/status/2050845248088055847</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>Style, comfort, and cashback… that's how we do it at TMG with Emirates NBD✨ https://t.co/bt4VAtCnZL</t>
+          <t>@EmiratesNBD_AE ابي وظيفه باي فرع من اللي بالرياض</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Style, comfort, and cashback… that's how we do it at TMG with Emirates NBD✨ https://t.co/bt4VAtCnZL</t>
+          <t>@EmiratesNBD_AE ابي وظيفه باي فرع من اللي بالرياض</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Style, comfort, and cashback… that's how we do it at TMG with Emirates NBD.</t>
+          <t>I want a job at any branch in Riyadh.</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2274,14 +2115,14 @@
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE11" s="2" t="n">
-        <v>46144.56736111111</v>
+        <v>46145.49236111111</v>
       </c>
       <c r="AF11" s="2" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
@@ -2295,7 +2136,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Style, comfort, and cashback… that's how we do it at TMG with Emirates NBD.</t>
+          <t>I want a job at any branch in Riyadh.</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -2318,49 +2159,49 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2050500266760478726</t>
+          <t>2050841752987136094</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://x.com/uaefintechvibes/status/2050500266760478726</t>
+          <t>https://x.com/FintechGate1/status/2050841752987136094</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://x.com/uaefintechvibes</t>
+          <t>https://x.com/FintechGate1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>uaefintechvibes</t>
+          <t>FintechGate1</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>UAE Fintechvibes</t>
+          <t>FinTech Gate-بوابة التكنولوجيا المالية</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2003525276207333376/SpeiZyat_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1630704388531470336/_2WZb_12_bigger.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>@Visa  has officially appointed @EmiratesNBD_AE  as its National Net Settlement Service (NNSS) agent.
-Read more: https://t.co/zL56RMfxRn
-Follow @uaefintechvibes for daily fintech updates. 
-#uaefintech #visapayments #enbd https://t.co/8gN1xEE7BN</t>
+          <t>Emirates NBD Egypt Releases Its Third Sustainability Report, Reporting Strong Profit Growth and a Strategic Shift Toward Renewable Energy
+ https://t.co/zMJRGwIJEz  | details 
+#fintech_gate
+#Emirates_NBD_Egypt_Releases https://t.co/JnNoI8ViAd</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>&lt;a href="/Visa" title="Visa"&gt;@Visa&lt;/a&gt;  has officially appointed &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;  as its National Net Settlement Service (NNSS) agent.
-Read more: &lt;a href="https://uaefintechvibes.com/local-uae-dirham-settlements-visa-and-enbd/"&gt;uaefintechvibes.com/local-ua…&lt;/a&gt;
-Follow &lt;a href="/uaefintechvibes" title="UAE Fintechvibes"&gt;@uaefintechvibes&lt;/a&gt; for daily fintech updates. 
-&lt;a href="/search?f=tweets&amp;amp;q=%23uaefintech"&gt;#uaefintech&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23visapayments"&gt;#visapayments&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23enbd"&gt;#enbd&lt;/a&gt;</t>
+          <t>Emirates NBD Egypt Releases Its Third Sustainability Report, Reporting Strong Profit Growth and a Strategic Shift Toward Renewable Energy
+ &lt;a href="https://fintechgate.net/rhb4"&gt;fintechgate.net/rhb4&lt;/a&gt;  | details 
+&lt;a href="/search?f=tweets&amp;amp;q=%23fintech_gate"&gt;#fintech_gate&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23Emirates_NBD_Egypt_Releases"&gt;#Emirates_NBD_Egypt_Releases&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K12" t="b">
@@ -2370,21 +2211,21 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 8:58 AM UTC</t>
+          <t>May 3, 2026 · 7:35 AM UTC</t>
         </is>
       </c>
       <c r="P12" s="2" t="n">
-        <v>46144.37361111111</v>
+        <v>46145.31597222222</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>['https://x.com/Visa', 'https://x.com/EmiratesNBD_AE', 'https://uaefintechvibes.com/local-uae-dirham-settlements-visa-and-enbd/', 'https://x.com/uaefintechvibes', 'https://x.com/search?f=tweets&amp;q=%23uaefintech', 'https://x.com/search?f=tweets&amp;q=%23visapayments', 'https://x.com/search?f=tweets&amp;q=%23enbd']</t>
+          <t>['https://fintechgate.net/rhb4', 'https://x.com/search?f=tweets&amp;q=%23fintech_gate', 'https://x.com/search?f=tweets&amp;q=%23Emirates_NBD_Egypt_Releases']</t>
         </is>
       </c>
       <c r="S12" t="n">
@@ -2394,10 +2235,10 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -2406,39 +2247,36 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>@Visa  has officially appointed @EmiratesNBD_AE  as its National Net Settlement Service (NNSS) agent.
-Read more: uaefintechvibes.com/local-ua…
-Follow @uaefintechvibes for daily fintech updates. 
-#uaefintech #visapayments #enbd</t>
+          <t>Emirates NBD Egypt Releases Its Third Sustainability Report, Reporting Strong Profit Growth and a Strategic Shift Toward Renewable Energy
+ fintechgate.net/rhb4  | details 
+#fintech_gate
+#Emirates_NBD_Egypt_Releases</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>https://x.com/uaefintechvibes/status/2050500266760478726</t>
+          <t>https://x.com/FintechGate1/status/2050841752987136094</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>@Visa  has officially appointed @EmiratesNBD_AE  as its National Net Settlement Service (NNSS) agent.
-Read more: https://t.co/zL56RMfxRn
-Follow @uaefintechvibes for daily fintech updates. 
-#uaefintech #visapayments #enbd https://t.co/8gN1xEE7BN</t>
+          <t>Emirates NBD Egypt Releases Its Third Sustainability Report, Reporting Strong Profit Growth and a Strategic Shift Toward Renewable Energy
+ https://t.co/zMJRGwIJEz  | details 
+#fintech_gate
+#Emirates_NBD_Egypt_Releases https://t.co/JnNoI8ViAd</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>@Visa  has officially appointed @EmiratesNBD_AE  as its National Net Settlement Service (NNSS) agent.
-Read more: https://t.co/zL56RMfxRn
-Follow @uaefintechvibes for daily fintech updates. 
-#uaefintech #visapayments #enbd https://t.co/8gN1xEE7BN</t>
+          <t>Emirates NBD Egypt Releases Its Third Sustainability Report, Reporting Strong Profit Growth and a Strategic Shift Toward Renewable Energy
+ https://t.co/zMJRGwIJEz  | details 
+#fintech_gate
+#Emirates_NBD_Egypt_Releases https://t.co/JnNoI8ViAd</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Visa has officially appointed Emirates NBD as its National Net Settlement Service (NNSS) agent. 
-Read more: https://t.co/zL56RMfxRn
-Follow uaefintechvibes for daily fintech updates. 
-#uaefintech #visapayments #enbd https://t.co/8gN1xEE7BN</t>
+          <t>Emirates NBD Egypt Releases Its Third Sustainability Report, Reporting Strong Profit Growth and a Strategic Shift Toward Renewable Energy</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2452,10 +2290,10 @@
         </is>
       </c>
       <c r="AE12" s="2" t="n">
-        <v>46144.54027777778</v>
+        <v>46145.48263888889</v>
       </c>
       <c r="AF12" s="2" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
@@ -2469,7 +2307,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Visa has officially appointed Emirates NBD as its National Net Settlement Service (NNSS) agent. • Read more: https://t.co/zL56RMfxRn Follow uaefintechvibes for daily fintech updates. • #uaefintech #visapayments #enbd https://t.co/8gN1xEE7BN</t>
+          <t>Emirates NBD Egypt Releases Its Third Sustainability Report, Reporting Strong Profit Growth and a Strategic Shift Toward Renewable Energy</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2492,84 +2330,83 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2050470345820565788</t>
+          <t>2050809333848342901</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://x.com/ABCinGCC/status/2050470345820565788</t>
+          <t>https://x.com/abotameem430/status/2050809333848342901</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://x.com/ABCinGCC</t>
+          <t>https://x.com/abotameem430</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ABCinGCC</t>
+          <t>abotameem430</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Arabian Business Community (ABC GCC)</t>
+          <t>Fahad</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1782384725962653696/jF3qtc02_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1780850701616242688/Ikq26ySl_bigger.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Visa has appointed Emirates NBD, a leading banking group in the Middle East, North Africa and Türkiye (MENAT) region, as its official National Net Settlement Service (NNSS) Agent in the UAE.
-Read more on https://t.co/RPTuv9uD9h
-#ABCnews #Digital #Payment #Services https://t.co/Fs9eVfVeuP</t>
+          <t>Apply smarter, faster, and hassle-free.
+With our Straight Through Processing (STP) journey, complete your application in minutes—no delays.
+Watch how easy it is to get started.
+Apply Now: https://t.co/aeh8nbj5gC https://t.co/y7g1WeVQ6R</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Visa has appointed Emirates NBD, a leading banking group in the Middle East, North Africa and Türkiye (MENAT) region, as its official National Net Settlement Service (NNSS) Agent in the UAE.
-Read more on &lt;a href="https://abc-gcc.net/News/1/395250"&gt;abc-gcc.net/News/1/395250&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23ABCnews"&gt;#ABCnews&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Digital"&gt;#Digital&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Payment"&gt;#Payment&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Services"&gt;#Services&lt;/a&gt;</t>
+          <t>اريد تمويل وارغب بالاتصال</t>
         </is>
       </c>
       <c r="K13" t="b">
         <v>0</v>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 7:00 AM UTC</t>
+          <t>May 3, 2026 · 5:27 AM UTC</t>
         </is>
       </c>
       <c r="P13" s="2" t="n">
-        <v>46144.29166666666</v>
+        <v>46145.22708333333</v>
       </c>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>['https://abc-gcc.net/News/1/395250', 'https://x.com/search?f=tweets&amp;q=%23ABCnews', 'https://x.com/search?f=tweets&amp;q=%23Digital', 'https://x.com/search?f=tweets&amp;q=%23Payment', 'https://x.com/search?f=tweets&amp;q=%23Services']</t>
-        </is>
-      </c>
+      <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -2578,33 +2415,33 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Visa has appointed Emirates NBD, a leading banking group in the Middle East, North Africa and Türkiye (MENAT) region, as its official National Net Settlement Service (NNSS) Agent in the UAE.
-Read more on abc-gcc.net/News/1/395250
-#ABCnews #Digital #Payment #Services</t>
+          <t>اريد تمويل وارغب بالاتصال</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>https://x.com/ABCinGCC/status/2050470345820565788</t>
+          <t>https://x.com/abotameem430/status/2050809333848342901</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>Visa has appointed Emirates NBD, a leading banking group in the Middle East, North Africa and Türkiye (MENAT) region, as its official National Net Settlement Service (NNSS) Agent in the UAE.
-Read more on https://t.co/RPTuv9uD9h
-#ABCnews #Digital #Payment #Services https://t.co/Fs9eVfVeuP</t>
+          <t>Apply smarter, faster, and hassle-free.
+With our Straight Through Processing (STP) journey, complete your application in minutes—no delays.
+Watch how easy it is to get started.
+Apply Now: https://t.co/aeh8nbj5gC https://t.co/y7g1WeVQ6R</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Visa has appointed Emirates NBD, a leading banking group in the Middle East, North Africa and Türkiye (MENAT) region, as its official National Net Settlement Service (NNSS) Agent in the UAE.
-Read more on https://t.co/RPTuv9uD9h
-#ABCnews #Digital #Payment #Services https://t.co/Fs9eVfVeuP</t>
+          <t>Apply smarter, faster, and hassle-free.
+With our Straight Through Processing (STP) journey, complete your application in minutes—no delays.
+Watch how easy it is to get started.
+Apply Now: https://t.co/aeh8nbj5gC https://t.co/y7g1WeVQ6R</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Visa has appointed Emirates NBD, a leading banking group in the Middle East, North Africa, and Türkiye (MENAT) region, as its official National Net Settlement Service (NNSS) Agent in the UAE.</t>
+          <t>Apply smarter, faster, and hassle-free. With our Straight Through Processing (STP) journey, complete your application in minutes—no delays. Watch how easy it is to get started. Apply Now: https://t.co/aeh8nbj5gC https://t.co/y7g1WeVQ6R</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2618,10 +2455,10 @@
         </is>
       </c>
       <c r="AE13" s="2" t="n">
-        <v>46144.45833333334</v>
+        <v>46145.39375</v>
       </c>
       <c r="AF13" s="2" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
@@ -2635,7 +2472,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Visa has appointed Emirates NBD, a leading banking group in the Middle East, North Africa, and Türkiye (MENAT) region, as its official National Net Settlement Service (NNSS) Agent in the UAE.</t>
+          <t>Apply Now: https://t.co/aeh8nbj5gC https://t.co/y7g1WeVQ6R • With our Straight Through Processing (STP) journey, complete your application in minutes—no delays. • Apply smarter, faster, and hassle-free.</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2648,7 +2485,7 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
@@ -2658,53 +2495,47 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2050456364728680817</t>
+          <t>2050807726507516194</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2050456364728680817</t>
+          <t>https://x.com/uaefintechvibes/status/2050807726507516194</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/uaefintechvibes</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>uaefintechvibes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>UAE Fintechvibes</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2042294543308242946/ScvMjarh_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2003525276207333376/SpeiZyat_bigger.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Shop, save, and earn with the Emirates NBD noon One Visa Credit Card
-🛍️ Get up to 20% back on noon, noon Food, noon minutes, Namshi &amp; more
-🌟 Enjoy a FREE 1-year noon One membership
-🎁 Earn AED 500 welcome bonus
-Apply now in just a few clicks and start enjoying exclusive benefits! T&amp;C Apply!
-Apply Now: https://t.co/9cutEjf788</t>
+          <t>Ziina and @shamssmc have partnered to integrate advanced digital financial solutions directly into Sharjah’s creative business ecosystem.
+Read more: https://t.co/VrIYgQm2sy
+#digitalfinancialsolutions #uaepayments https://t.co/4m9BNOOUxb</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Shop, save, and earn with the Emirates NBD noon One Visa Credit Card
-🛍️ Get up to 20% back on noon, noon Food, noon minutes, Namshi &amp;amp; more
-🌟 Enjoy a FREE 1-year noon One membership
-🎁 Earn AED 500 welcome bonus
-Apply now in just a few clicks and start enjoying exclusive benefits! T&amp;amp;C Apply!
-Apply Now: &lt;a href="https://www.emiratesnbd.com/en/campaigns/noon-one-credit-card"&gt;emiratesnbd.com/en/campaigns…&lt;/a&gt;</t>
+          <t>UAE Fintech News this week
+&lt;a href="/takeem_ai" title="Takeem.ai"&gt;@takeem_ai&lt;/a&gt; &lt;a href="/CashewPayments" title="Cashew"&gt;@CashewPayments&lt;/a&gt; &lt;a href="/shamssmc" title="Sharjah Media City"&gt;@shamssmc&lt;/a&gt; &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; &lt;a href="/MashreqTweets" title="Mashreq"&gt;@MashreqTweets&lt;/a&gt; &lt;a href="/OfficialADCB" title="ADCB بنك أبوظبي التجاري"&gt;@OfficialADCB&lt;/a&gt; &lt;a href="/comfi_ai" title="Comfi"&gt;@comfi_ai&lt;/a&gt; 
+&lt;a href="/search?f=tweets&amp;amp;q=%23digitalpayments"&gt;#digitalpayments&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23uaefintech"&gt;#uaefintech&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23proptech"&gt;#proptech&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K14" t="b">
@@ -2714,34 +2545,34 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 6:04 AM UTC</t>
+          <t>May 3, 2026 · 5:20 AM UTC</t>
         </is>
       </c>
       <c r="P14" s="2" t="n">
-        <v>46144.25277777778</v>
+        <v>46145.22222222222</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
-          <t>['https://www.emiratesnbd.com/en/campaigns/noon-one-credit-card']</t>
+          <t>['https://x.com/takeem_ai', 'https://x.com/CashewPayments', 'https://x.com/shamssmc', 'https://x.com/EmiratesNBD_AE', 'https://x.com/MashreqTweets', 'https://x.com/OfficialADCB', 'https://x.com/comfi_ai', 'https://x.com/search?f=tweets&amp;q=%23digitalpayments', 'https://x.com/search?f=tweets&amp;q=%23uaefintech', 'https://x.com/search?f=tweets&amp;q=%23proptech']</t>
         </is>
       </c>
       <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
       <c r="U14" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="V14" t="n">
-        <v>1216</v>
+        <v>17</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -2750,64 +2581,50 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Shop, save, and earn with the Emirates NBD noon One Visa Credit Card
-🛍️ Get up to 20% back on noon, noon Food, noon minutes, Namshi &amp; more
-🌟 Enjoy a FREE 1-year noon One membership
-🎁 Earn AED 500 welcome bonus
-Apply now in just a few clicks and start enjoying exclusive benefits! T&amp;C Apply!
-Apply Now: emiratesnbd.com/en/campaigns…</t>
+          <t>UAE Fintech News this week
+@takeem_ai @CashewPayments @shamssmc @EmiratesNBD_AE @MashreqTweets @OfficialADCB @comfi_ai 
+#digitalpayments #uaefintech #proptech</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2050456364728680817</t>
+          <t>https://x.com/uaefintechvibes/status/2050807726507516194</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>Shop, save, and earn with the Emirates NBD noon One Visa Credit Card
-🛍️ Get up to 20% back on noon, noon Food, noon minutes, Namshi &amp; more
-🌟 Enjoy a FREE 1-year noon One membership
-🎁 Earn AED 500 welcome bonus
-Apply now in just a few clicks and start enjoying exclusive benefits! T&amp;C Apply!
-Apply Now: https://t.co/9cutEjf788</t>
+          <t>Ziina and @shamssmc have partnered to integrate advanced digital financial solutions directly into Sharjah’s creative business ecosystem.
+Read more: https://t.co/VrIYgQm2sy
+#digitalfinancialsolutions #uaepayments https://t.co/4m9BNOOUxb</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Shop, save, and earn with the Emirates NBD noon One Visa Credit Card
-🛍️ Get up to 20% back on noon, noon Food, noon minutes, Namshi &amp; more
-🌟 Enjoy a FREE 1-year noon One membership
-🎁 Earn AED 500 welcome bonus
-Apply now in just a few clicks and start enjoying exclusive benefits! T&amp;C Apply!
-Apply Now: https://t.co/9cutEjf788</t>
+          <t>Ziina and @shamssmc have partnered to integrate advanced digital financial solutions directly into Sharjah’s creative business ecosystem.
+Read more: https://t.co/VrIYgQm2sy
+#digitalfinancialsolutions #uaepayments https://t.co/4m9BNOOUxb</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Shop, save, and earn with the Emirates NBD noon One Visa Credit Card
-Get up to 20% back on noon, noon Food, noon minutes, Namshi, and more
-Enjoy a FREE 1-year noon One membership
-Earn AED 500 welcome bonus
-Apply now in just a few clicks and start enjoying exclusive benefits! Terms and Conditions apply!
-Apply Now: https://t.co/9cutEjf788</t>
+          <t>Ziina and @shamssmc have partnered to integrate advanced digital financial solutions directly into Sharjah’s creative business ecosystem.</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Cust</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE14" s="2" t="n">
-        <v>46144.41944444444</v>
+        <v>46145.38888888889</v>
       </c>
       <c r="AF14" s="2" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
@@ -2821,7 +2638,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Apply Now: https://t.co/9cutEjf788 • Terms and Conditions apply!</t>
+          <t>Ziina and @shamssmc have partnered to integrate advanced digital financial solutions directly into Sharjah’s creative business ecosystem.</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2844,81 +2661,84 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2050399772591399146</t>
+          <t>2050785564182392905</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://x.com/Jami076152121/status/2050399772591399146</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2050785564182392905</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://x.com/Jami076152121</t>
+          <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jami076152121</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jami's Nest</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/2042294543308242946/ScvMjarh_bigger.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Bandhan Bank and RBL Bank 👇
-Both are crap stock - Avoid for Investing 🎯</t>
+          <t>Whether you're paying your bills, transferring money within the UAE, sending it abroad or exchanging currencies, Emirates NBD makes it simple and secure through the ENBD X app.
+#transfers #payments #DirectRemit #Aani #currencies #travel #GlobalCash
+emiratesnbd.com/en/foreign-e…</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>RBL takenover by ENBD(Largest bank in UAE) is a bad investment according to you?</t>
+          <t>Whether you&amp;#39;re paying your bills, transferring money within the UAE, sending it abroad or exchanging currencies, Emirates NBD makes it simple and secure through the ENBD X app.
+&lt;a href="/search?f=tweets&amp;amp;q=%23transfers"&gt;#transfers&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23payments"&gt;#payments&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23DirectRemit"&gt;#DirectRemit&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Aani"&gt;#Aani&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23currencies"&gt;#currencies&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23travel"&gt;#travel&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23GlobalCash"&gt;#GlobalCash&lt;/a&gt;
+&lt;a href="https://www.emiratesnbd.com/en/foreign-exchange"&gt;emiratesnbd.com/en/foreign-e…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K15" t="b">
         <v>0</v>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>['CaVivekkhatri']</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>May 2</t>
+          <t>May 3</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 2:19 AM UTC</t>
+          <t>May 3, 2026 · 3:52 AM UTC</t>
         </is>
       </c>
       <c r="P15" s="2" t="n">
-        <v>46144.09652777778</v>
+        <v>46145.16111111111</v>
       </c>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23transfers', 'https://x.com/search?f=tweets&amp;q=%23payments', 'https://x.com/search?f=tweets&amp;q=%23DirectRemit', 'https://x.com/search?f=tweets&amp;q=%23Aani', 'https://x.com/search?f=tweets&amp;q=%23currencies', 'https://x.com/search?f=tweets&amp;q=%23travel', 'https://x.com/search?f=tweets&amp;q=%23GlobalCash', 'https://www.emiratesnbd.com/en/foreign-exchange']</t>
+        </is>
+      </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="V15" t="n">
-        <v>21</v>
+        <v>1912</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -2927,47 +2747,40 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>RBL takenover by ENBD(Largest bank in UAE) is a bad investment according to you?</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>https://x.com/Jami076152121/status/2050399772591399146</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Bandhan Bank and RBL Bank 👇
-Both are crap stock - Avoid for Investing 🎯</t>
-        </is>
-      </c>
+          <t>Whether you're paying your bills, transferring money within the UAE, sending it abroad or exchanging currencies, Emirates NBD makes it simple and secure through the ENBD X app.
+#transfers #payments #DirectRemit #Aani #currencies #travel #GlobalCash
+emiratesnbd.com/en/foreign-e…</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Bandhan Bank and RBL Bank 👇
-Both are crap stock - Avoid for Investing 🎯</t>
+          <t>Whether you're paying your bills, transferring money within the UAE, sending it abroad or exchanging currencies, Emirates NBD makes it simple and secure through the ENBD X app.
+#transfers #payments #DirectRemit #Aani #currencies #travel #GlobalCash
+emiratesnbd.com/en/foreign-e…</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Bandhan Bank and RBL Bank
-Both are poor stocks - Avoid for investing.</t>
+          <t>Whether you're paying your bills, transferring money within the UAE, sending it abroad, or exchanging currencies, Emirates NBD makes it simple and secure through the ENBD X app.</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Cust</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE15" s="2" t="n">
-        <v>46144.26319444444</v>
+        <v>46145.32777777778</v>
       </c>
       <c r="AF15" s="2" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
@@ -2981,7 +2794,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Bandhan Bank and RBL Bank Both are poor stocks - Avoid for investing.</t>
+          <t>Whether you're paying your bills, transferring money within the UAE, sending it abroad, or exchanging currencies, Emirates NBD makes it simple and secure through the ENBD X app.</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -2994,7 +2807,7 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>CaVivekkhatri</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3004,73 +2817,64 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2050382263129620695</t>
+          <t>2050908234156744921</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://x.com/Bushrasabih2/status/2050382263129620695</t>
+          <t>https://x.com/emiratesislamic/status/2050908234156744921</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://x.com/Bushrasabih2</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bushrasabih2</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bu_shaikh🌸❤️</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2037057205510574080/OEGMy7R9_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Make Eid surprises even more valuable.
-From silver to gold, discover a smarter way to own or gift something truly precious.
-Watch this episode and tell us:
-How can you buy gold and silver from the bank?
-To participate:
-Follow Emirates NBD
-Tag 3 friends
-Drop your answer below for a chance to win AED 10,000</t>
+          <t>Open a Digital Wealth Account instantly to enjoy a complete suite of Shariah-compliant global investments. Get access to International &amp; UAE stocks as well as Global Mutual Funds.
+Download the EI + Mobile Banking App today.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>👍</t>
+          <t>Open a Digital Wealth Account instantly to enjoy a complete suite of Shariah-compliant global investments. Get access to International &amp;amp; UAE stocks as well as Global Mutual Funds.
+Download the EI + Mobile Banking App today.</t>
         </is>
       </c>
       <c r="K16" t="b">
         <v>0</v>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE', 'Bushrasabih1']</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>May 2</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 1:10 AM UTC</t>
+          <t>May 3, 2026 · 12:00 PM UTC</t>
         </is>
       </c>
       <c r="P16" s="2" t="n">
-        <v>46144.04861111111</v>
+        <v>46145.5</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
@@ -3081,58 +2885,39 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" t="n">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>👍</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>https://x.com/Bushrasabih2/status/2050382263129620695</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Make Eid surprises even more valuable.
-From silver to gold, discover a smarter way to own or gift something truly precious.
-Watch this episode and tell us:
-How can you buy gold and silver from the bank?
-To participate:
-Follow Emirates NBD
-Tag 3 friends
-Drop your answer below for a chance to win AED 10,000</t>
-        </is>
-      </c>
+          <t>Open a Digital Wealth Account instantly to enjoy a complete suite of Shariah-compliant global investments. Get access to International &amp; UAE stocks as well as Global Mutual Funds.
+Download the EI + Mobile Banking App today.</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Make Eid surprises even more valuable.
-From silver to gold, discover a smarter way to own or gift something truly precious.
-Watch this episode and tell us:
-How can you buy gold and silver from the bank?
-To participate:
-Follow Emirates NBD
-Tag 3 friends
-Drop your answer below for a chance to win AED 10,000</t>
+          <t>Open a Digital Wealth Account instantly to enjoy a complete suite of Shariah-compliant global investments. Get access to International &amp; UAE stocks as well as Global Mutual Funds.
+Download the EI + Mobile Banking App today.</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Make Eid surprises even more valuable. From silver to gold, discover a smarter way to own or gift something truly precious. Watch this episode and tell us: How can you buy gold and silver from the bank? To participate: Follow Emirates NBD Tag 3 friends Drop your answer below for a chance to win AED 10,000</t>
+          <t>Open a Digital Wealth Account instantly to enjoy a complete suite of Shariah-compliant global investments. Get access to international and UAE stocks as well as global mutual funds.
+Download the EI + Mobile Banking App today.</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Cust</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -3141,29 +2926,29 @@
         </is>
       </c>
       <c r="AE16" s="2" t="n">
-        <v>46144.21527777778</v>
+        <v>46145.66666666666</v>
       </c>
       <c r="AF16" s="2" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
+          <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>To participate: Follow Emirates NBD Tag 3 friends Drop your answer below for a chance to win AED 10,000 • From silver to gold, discover a smarter way to own or gift something truly precious. • Watch this episode and tell us: How can you buy gold and silver from the bank?</t>
+          <t>Open a Digital Wealth Account instantly to enjoy a complete suite of Shariah-compliant global investments. • Get access to international and UAE stocks as well as global mutual funds. • Download the EI + Mobile Banking App today.</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank (ENBD)</t>
+          <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AK16" t="n">
@@ -3171,7 +2956,7 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE, Bushrasabih1</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3181,130 +2966,107 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2050374137852670288</t>
+          <t>2050908231610863903</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis/status/2050374137852670288</t>
+          <t>https://x.com/emiratesislamic/status/2050908231610863903</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>STKgenghis</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>khana-b-dosh</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1243248207293026305/b_s7UBzl_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Open an Emirates NBD Millionaire Account to be the next winner, with over 1,400 cash prizes worth AED 50,000,000.
-- Monthly prizes up to AED 1,000,000
-- Grand prizes up to AED 5,000,000
-Dedicated prizes for Emiratis, expats, and businesses 🇦🇪</t>
+          <t>ابدأ بفتح حساب "الثروات الرقمية" على الفور للوصول إلى مجموعة كاملة من الاستثمارات العالمية المتوافقة مع أحكام الشريعة الإسلامية. احصل على إمكانية التداول في الأسهم الدولية والمحلية بالإضافة إلى صناديق الاستثمار العالمية.
+قم بتحميل تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Had i the energy I would report this to &lt;a href="/centralbankuae" title="Central Bank of the UAE"&gt;@centralbankuae&lt;/a&gt; but no energy or time. I will now be silent. I blocked the card 17 April. No service since.</t>
+          <t>ابدأ بفتح حساب &amp;#34;الثروات الرقمية&amp;#34; على الفور للوصول إلى مجموعة كاملة من الاستثمارات العالمية المتوافقة مع أحكام الشريعة الإسلامية. احصل على إمكانية التداول في الأسهم الدولية والمحلية بالإضافة إلى صناديق الاستثمار العالمية.
+قم بتحميل تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك.</t>
         </is>
       </c>
       <c r="K17" t="b">
         <v>0</v>
       </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>May 2</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 12:37 AM UTC</t>
+          <t>May 3, 2026 · 12:00 PM UTC</t>
         </is>
       </c>
       <c r="P17" s="2" t="n">
-        <v>46144.02569444444</v>
+        <v>46145.5</v>
       </c>
       <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>['https://x.com/centralbankuae']</t>
-        </is>
-      </c>
+      <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V17" t="n">
-        <v>17</v>
+        <v>136</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Had i the energy I would report this to @centralbankuae but no energy or time. I will now be silent. I blocked the card 17 April. No service since.</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>https://x.com/STKgenghis/status/2050374137852670288</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Open an Emirates NBD Millionaire Account to be the next winner, with over 1,400 cash prizes worth AED 50,000,000.
-- Monthly prizes up to AED 1,000,000
-- Grand prizes up to AED 5,000,000
-Dedicated prizes for Emiratis, expats, and businesses 🇦🇪</t>
-        </is>
-      </c>
+          <t>ابدأ بفتح حساب "الثروات الرقمية" على الفور للوصول إلى مجموعة كاملة من الاستثمارات العالمية المتوافقة مع أحكام الشريعة الإسلامية. احصل على إمكانية التداول في الأسهم الدولية والمحلية بالإضافة إلى صناديق الاستثمار العالمية.
+قم بتحميل تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك.</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Open an Emirates NBD Millionaire Account to be the next winner, with over 1,400 cash prizes worth AED 50,000,000.
-- Monthly prizes up to AED 1,000,000
-- Grand prizes up to AED 5,000,000
-Dedicated prizes for Emiratis, expats, and businesses 🇦🇪</t>
+          <t>ابدأ بفتح حساب "الثروات الرقمية" على الفور للوصول إلى مجموعة كاملة من الاستثمارات العالمية المتوافقة مع أحكام الشريعة الإسلامية. احصل على إمكانية التداول في الأسهم الدولية والمحلية بالإضافة إلى صناديق الاستثمار العالمية.
+قم بتحميل تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك.</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Open an Emirates NBD Millionaire Account to be the next winner, with over 1,400 cash prizes worth AED 50,000,000. 
-- Monthly prizes up to AED 1,000,000 
-- Grand prizes up to AED 5,000,000 
-Dedicated prizes for Emiratis, expats, and businesses.</t>
+          <t>Start by opening a "Digital Wealth" account immediately to access a full range of global investments compliant with Islamic law. Get the ability to trade in international and local stocks as well as global investment funds.
+Download the + EI mobile banking app.</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Cust</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -3313,29 +3075,29 @@
         </is>
       </c>
       <c r="AE17" s="2" t="n">
-        <v>46144.19236111111</v>
+        <v>46145.66666666666</v>
       </c>
       <c r="AF17" s="2" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
+          <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>- Monthly prizes up to AED 1,000,000 - Grand prizes up to AED 5,000,000 Dedicated prizes for Emiratis, expats, and businesses. • Open an Emirates NBD Millionaire Account to be the next winner, with over 1,400 cash prizes worth AED 50,000,000.</t>
+          <t>Start by opening a "Digital Wealth" account immediately to access a full range of global investments compliant with Islamic law. • Get the ability to trade in international and local stocks as well as global investment funds. • Download the + EI mobile banking app.</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank (ENBD)</t>
+          <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AK17" t="n">
@@ -3343,7 +3105,7 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3353,46 +3115,49 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2050364684251893892</t>
+          <t>2051003496439427421</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://x.com/yasmeenalja/status/2050364684251893892</t>
+          <t>https://x.com/KaharUmesh/status/2051003496439427421</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://x.com/yasmeenalja</t>
+          <t>https://x.com/KaharUmesh</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>yasmeenalja</t>
+          <t>KaharUmesh</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Yasmeen Aljadah</t>
+          <t>Umesh R Kahar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2042291734583877632/pJUn80Vi_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/962204603965214722/wZzbG0I__bigger.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Expats in KSA — your salary might qualify you for better financing options.
-#SaudiArabia #ExpatsInKSA #Financing #PersonalFinance #KSAJobs https://t.co/CJ5MydF5fu</t>
+          <t>@EmiratesNBD_AE Such unfair charges for doing transactions at Binance Crypto whereas no other bank charge for it. 
+After multiple followups these charges are reversed. Kindly look into it or will file a complaint with @centralbankuae
+Reference:
+https://t.co/BcgwdgmQQQ</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Personal financing in Saudi Arabia made easy for expats.💸🙏🏻
-Emirates NBD – Dammam Branch | Financial Consultant
-&lt;a href="/search?f=tweets&amp;amp;q=%23SaudiArabia"&gt;#SaudiArabia&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23ExpatsInKSA"&gt;#ExpatsInKSA&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Financing"&gt;#Financing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23PersonalFinance"&gt;#PersonalFinance&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23KSAJobs"&gt;#KSAJobs&lt;/a&gt;</t>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; Such unfair charges for doing transactions at Binance Crypto whereas no other bank charge for it. 
+After multiple followups these charges are reversed. Kindly look into it or will file a complaint with &lt;a href="/centralbankuae" title="Central Bank of the UAE"&gt;@centralbankuae&lt;/a&gt;
+Reference:
+&lt;a href="https://gulfnews.com/uae/reader-complaints/uae-unwanted-cash-advance-fee-of-dh99-for-purchasing-crypto-currency-online-1.1672390194506"&gt;gulfnews.com/uae/reader-comp…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K18" t="b">
@@ -3402,21 +3167,21 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>May 2</t>
+          <t>9h</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 12:00 AM UTC</t>
+          <t>May 3, 2026 · 6:18 PM UTC</t>
         </is>
       </c>
       <c r="P18" s="2" t="n">
-        <v>46144</v>
+        <v>46145.7625</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23SaudiArabia', 'https://x.com/search?f=tweets&amp;q=%23ExpatsInKSA', 'https://x.com/search?f=tweets&amp;q=%23Financing', 'https://x.com/search?f=tweets&amp;q=%23PersonalFinance', 'https://x.com/search?f=tweets&amp;q=%23KSAJobs']</t>
+          <t>['https://x.com/EmiratesNBD_AE', 'https://x.com/centralbankuae', 'https://gulfnews.com/uae/reader-complaints/uae-unwanted-cash-advance-fee-of-dh99-for-purchasing-crypto-currency-online-1.1672390194506']</t>
         </is>
       </c>
       <c r="S18" t="n">
@@ -3429,7 +3194,7 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>143</v>
+        <v>12</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -3438,31 +3203,36 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Personal financing in Saudi Arabia made easy for expats.💸🙏🏻
-Emirates NBD – Dammam Branch | Financial Consultant
-#SaudiArabia #ExpatsInKSA #Financing #PersonalFinance #KSAJobs</t>
+          <t>@EmiratesNBD_AE Such unfair charges for doing transactions at Binance Crypto whereas no other bank charge for it. 
+After multiple followups these charges are reversed. Kindly look into it or will file a complaint with @centralbankuae
+Reference:
+gulfnews.com/uae/reader-comp…</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>https://x.com/yasmeenalja/status/2050364684251893892</t>
+          <t>https://x.com/KaharUmesh/status/2051003496439427421</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>Expats in KSA — your salary might qualify you for better financing options.
-#SaudiArabia #ExpatsInKSA #Financing #PersonalFinance #KSAJobs https://t.co/CJ5MydF5fu</t>
+          <t>@EmiratesNBD_AE Such unfair charges for doing transactions at Binance Crypto whereas no other bank charge for it. 
+After multiple followups these charges are reversed. Kindly look into it or will file a complaint with @centralbankuae
+Reference:
+https://t.co/BcgwdgmQQQ</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Expats in KSA — your salary might qualify you for better financing options.
-#SaudiArabia #ExpatsInKSA #Financing #PersonalFinance #KSAJobs https://t.co/CJ5MydF5fu</t>
+          <t>@EmiratesNBD_AE Such unfair charges for doing transactions at Binance Crypto whereas no other bank charge for it. 
+After multiple followups these charges are reversed. Kindly look into it or will file a complaint with @centralbankuae
+Reference:
+https://t.co/BcgwdgmQQQ</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Expats in KSA — your salary might qualify you for better financing options.</t>
+          <t>Such unfair charges for doing transactions at Binance Crypto whereas no other bank charges for it. After multiple follow-ups, these charges are reversed. Kindly look into it or I will file a complaint with @centralbankuae.</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3472,14 +3242,14 @@
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="AE18" s="2" t="n">
-        <v>46144.16666666666</v>
+        <v>46145.92916666667</v>
       </c>
       <c r="AF18" s="2" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
@@ -3493,7 +3263,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Expats in KSA — your salary might qualify you for better financing options.</t>
+          <t>Such unfair charges for doing transactions at Binance Crypto whereas no other bank charges for it. • After multiple follow-ups, these charges are reversed. • Kindly look into it or I will file a complaint with @centralbankuae.</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -3516,69 +3286,72 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2050477438539297270</t>
+          <t>2050976036028919856</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://x.com/patelumarjiarif/status/2050477438539297270</t>
+          <t>https://x.com/Nidhinkn/status/2050976036028919856</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://x.com/patelumarjiarif</t>
+          <t>https://x.com/Nidhinkn</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>patelumarjiarif</t>
+          <t>Nidhinkn</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Arif Patel - Preston Trading in UK</t>
+          <t>Nidhin</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1650401956072943616/wfZaFWCV_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/862744582882308096/PYF7ziU7_bigger.jpg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Emirates Islamic, announce the launch of a Shari’ah-compliant digital investment solution in gold and silver, seamlessly integrated into the bank’s EI + Mobile Banking App. The new offering is a first-of-its-kind by an Islamic bank in the UAE.
-#dubai #emiratesislamic</t>
+          <t>I am using @EmiratesNBD_KSA InfiniteCard for 3years. On 01/02/2026 I made a Purchase of 100$ as per the rule of VisaAirportComp @VisaCEMEA to avail LoungeAccess. #ENBD never notified me about the monthly spend req of SAR 3000. They charged me 460 SAR @SAMA_GOV @EmiratesNBD_AE https://t.co/wlpy5fYt7z</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Emirates Islamic, announce the launch of a Shari’ah-compliant digital investment solution in gold and silver, seamlessly integrated into the bank’s EI + Mobile Banking App. The new offering is a first-of-its-kind by an Islamic bank in the UAE.
-&lt;a href="/search?f=tweets&amp;amp;q=%23dubai"&gt;#dubai&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23emiratesislamic"&gt;#emiratesislamic&lt;/a&gt;</t>
+          <t>No update from your team. No update from anyone from &lt;a href="/EmiratesNBD_KSA" title="Emirates NBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; 
+Now I will escalate it to &lt;a href="/SAMA_GOV" title="SAMA | البنك المركزي السعودي"&gt;@SAMA_GOV&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K19" t="b">
         <v>0</v>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_KSA']</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 7:28 AM UTC</t>
+          <t>May 3, 2026 · 4:29 PM UTC</t>
         </is>
       </c>
       <c r="P19" s="2" t="n">
-        <v>46144.31111111111</v>
+        <v>46145.68680555555</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23dubai', 'https://x.com/search?f=tweets&amp;q=%23emiratesislamic']</t>
+          <t>['https://x.com/EmiratesNBD_KSA', 'https://x.com/SAMA_GOV']</t>
         </is>
       </c>
       <c r="S19" t="n">
@@ -3591,30 +3364,37 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Emirates Islamic, announce the launch of a Shari’ah-compliant digital investment solution in gold and silver, seamlessly integrated into the bank’s EI + Mobile Banking App. The new offering is a first-of-its-kind by an Islamic bank in the UAE.
-#dubai #emiratesislamic</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
+          <t>No update from your team. No update from anyone from @EmiratesNBD_KSA 
+Now I will escalate it to @SAMA_GOV</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>https://x.com/Nidhinkn/status/2050976036028919856</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>I am using @EmiratesNBD_KSA InfiniteCard for 3years. On 01/02/2026 I made a Purchase of 100$ as per the rule of VisaAirportComp @VisaCEMEA to avail LoungeAccess. #ENBD never notified me about the monthly spend req of SAR 3000. They charged me 460 SAR @SAMA_GOV @EmiratesNBD_AE https://t.co/wlpy5fYt7z</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Emirates Islamic, announce the launch of a Shari’ah-compliant digital investment solution in gold and silver, seamlessly integrated into the bank’s EI + Mobile Banking App. The new offering is a first-of-its-kind by an Islamic bank in the UAE.
-#dubai #emiratesislamic</t>
+          <t>I am using @EmiratesNBD_KSA InfiniteCard for 3years. On 01/02/2026 I made a Purchase of 100$ as per the rule of VisaAirportComp @VisaCEMEA to avail LoungeAccess. #ENBD never notified me about the monthly spend req of SAR 3000. They charged me 460 SAR @SAMA_GOV @EmiratesNBD_AE https://t.co/wlpy5fYt7z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Emirates Islamic announces the launch of a Shari’ah-compliant digital investment solution in gold and silver, seamlessly integrated into the bank’s EI + Mobile Banking App. The new offering is a first-of-its-kind by an Islamic bank in the UAE.</t>
+          <t>I have been using the @EmiratesNBD_KSA InfiniteCard for 3 years. On 01/02/2026, I made a purchase of $100 according to the rule of VisaAirportComp @VisaCEMEA to avail Lounge Access. #ENBD never notified me about the monthly spending requirement of SAR 3000. They charged me 460 SAR @SAMA_GOV @EmiratesNBD_AE https://t.co/wlpy5fYt7z</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3624,33 +3404,33 @@
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="AE19" s="2" t="n">
-        <v>46144.47777777778</v>
+        <v>46145.85347222222</v>
       </c>
       <c r="AF19" s="2" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
+          <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Emirates Islamic announces the launch of a Shari’ah-compliant digital investment solution in gold and silver, seamlessly integrated into the bank’s EI + Mobile Banking App. • The new offering is a first-of-its-kind by an Islamic bank in the UAE.</t>
+          <t>On 01/02/2026, I made a purchase of $100 according to the rule of VisaAirportComp @VisaCEMEA to avail Lounge Access. • They charged me 460 SAR @SAMA_GOV @EmiratesNBD_AE https://t.co/wlpy5fYt7z • #ENBD never notified me about the monthly spending requirement of SAR 3000.</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>Emirates Islamic Bank (EIB)</t>
+          <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
       <c r="AK19" t="n">
@@ -3658,1240 +3438,7 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2050455246686527975</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2050455246686527975</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Did You Know Emirates Islamic offers fully Shariah-compliant Corporate Finance solutions?
-From Working Capital to Structured Finance, Emirates Islamic provides tailored Islamic finance offerings designed to help businesses grow sustainably.</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Did You Know Emirates Islamic offers fully Shariah-compliant Corporate Finance solutions?
-From Working Capital to Structured Finance, Emirates Islamic provides tailored Islamic finance offerings designed to help businesses grow sustainably.</t>
-        </is>
-      </c>
-      <c r="K20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>May 2, 2026 · 6:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="n">
-        <v>46144.25</v>
-      </c>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1</v>
-      </c>
-      <c r="V20" t="n">
-        <v>77</v>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>Did You Know Emirates Islamic offers fully Shariah-compliant Corporate Finance solutions?
-From Working Capital to Structured Finance, Emirates Islamic provides tailored Islamic finance offerings designed to help businesses grow sustainably.</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>Did You Know Emirates Islamic offers fully Shariah-compliant Corporate Finance solutions?
-From Working Capital to Structured Finance, Emirates Islamic provides tailored Islamic finance offerings designed to help businesses grow sustainably.</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>Did you know Emirates Islamic offers fully Shariah-compliant Corporate Finance solutions? From Working Capital to Structured Finance, Emirates Islamic provides tailored Islamic finance offerings designed to help businesses grow sustainably.</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="AE20" s="2" t="n">
-        <v>46144.41666666666</v>
-      </c>
-      <c r="AF20" s="2" t="n">
-        <v>46144</v>
-      </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>From Working Capital to Structured Finance, Emirates Islamic provides tailored Islamic finance offerings designed to help businesses grow sustainably. • Did you know Emirates Islamic offers fully Shariah-compliant Corporate Finance solutions?</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK20" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2050485448754004332</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2050485448754004332</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Tailor-made home financing solutions to ease the process of owning a home.
-Learn More
-emiratesislamic.ae/en/person…</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Tailor-made home financing solutions to ease the process of owning a home.
-Learn More
-&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=home_finance"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K21" t="b">
-        <v>0</v>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>18h</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>May 2, 2026 · 8:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="n">
-        <v>46144.33333333334</v>
-      </c>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/personal-banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=home_finance']</t>
-        </is>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>59</v>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>Tailor-made home financing solutions to ease the process of owning a home.
-Learn More
-emiratesislamic.ae/en/person…</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>Tailor-made home financing solutions to ease the process of owning a home.
-Learn More
-emiratesislamic.ae/en/person…</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>Tailor-made home financing solutions to ease the process of owning a home.</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="AE21" s="2" t="n">
-        <v>46144.5</v>
-      </c>
-      <c r="AF21" s="2" t="n">
-        <v>46144</v>
-      </c>
-      <c r="AG21" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Tailor-made home financing solutions to ease the process of owning a home.</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK21" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2050485444593246460</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2050485444593246460</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>حلول للتمويل السكني مصممة خصيصاً لتتيح لك امتلاك منزلك في منتهى الراحة.
-اطلع على المزيد
-emiratesislamic.ae/ar/person…</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>حلول للتمويل السكني مصممة خصيصاً لتتيح لك امتلاك منزلك في منتهى الراحة.
-اطلع على المزيد
-&lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=home_finance"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K22" t="b">
-        <v>0</v>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>18h</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>May 2, 2026 · 8:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="n">
-        <v>46144.33333333334</v>
-      </c>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/personal-banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=home_finance']</t>
-        </is>
-      </c>
-      <c r="S22" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1</v>
-      </c>
-      <c r="V22" t="n">
-        <v>70</v>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>حلول للتمويل السكني مصممة خصيصاً لتتيح لك امتلاك منزلك في منتهى الراحة.
-اطلع على المزيد
-emiratesislamic.ae/ar/person…</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>حلول للتمويل السكني مصممة خصيصاً لتتيح لك امتلاك منزلك في منتهى الراحة.
-اطلع على المزيد
-emiratesislamic.ae/ar/person…</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>Solutions for housing finance designed specifically to allow you to own your home with utmost comfort. 
-Learn more</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE22" s="2" t="n">
-        <v>46144.5</v>
-      </c>
-      <c r="AF22" s="2" t="n">
-        <v>46144</v>
-      </c>
-      <c r="AG22" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Solutions for housing finance designed specifically to allow you to own your home with utmost comfort.</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK22" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2050455250096541870</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2050455250096541870</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Financing that aligns with both values and vision.
-Learn more: emiratesislamic.ae/en/corpor…</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Financing that aligns with both values and vision.
-Learn more: &lt;a href="http://emiratesislamic.ae/en/corporate-and-institutional-banking"&gt;emiratesislamic.ae/en/corpor…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K23" t="b">
-        <v>0</v>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>May 2, 2026 · 6:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="n">
-        <v>46144.25</v>
-      </c>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>['http://emiratesislamic.ae/en/corporate-and-institutional-banking']</t>
-        </is>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>63</v>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>Financing that aligns with both values and vision.
-Learn more: emiratesislamic.ae/en/corpor…</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>Financing that aligns with both values and vision.
-Learn more: emiratesislamic.ae/en/corpor…</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>Financing that aligns with both values and vision.</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE23" s="2" t="n">
-        <v>46144.41666666666</v>
-      </c>
-      <c r="AF23" s="2" t="n">
-        <v>46144</v>
-      </c>
-      <c r="AG23" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Financing that aligns with both values and vision.</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK23" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2050448328266063924</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2050448328266063924</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
-        </is>
-      </c>
-      <c r="K24" t="b">
-        <v>0</v>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>['AnkitMittal1403']</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>May 2, 2026 · 5:32 AM UTC</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="n">
-        <v>46144.23055555556</v>
-      </c>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>2</v>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>Dear customer, we have tried to reach you through direct message, but unfortunately, we were not successful because you are not following our page. Please DM us back so we can assist you better.</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE24" s="2" t="n">
-        <v>46144.39722222222</v>
-      </c>
-      <c r="AF24" s="2" t="n">
-        <v>46144</v>
-      </c>
-      <c r="AG24" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Dear customer, we have tried to reach you through direct message, but unfortunately, we were not successful because you are not following our page. • Please DM us back so we can assist you better.</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK24" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL24" t="inlineStr">
-        <is>
-          <t>AnkitMittal1403</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2050373118900977885</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>https://x.com/STKgenghis/status/2050373118900977885</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>https://x.com/STKgenghis</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>STKgenghis</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>khana-b-dosh</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1243248207293026305/b_s7UBzl_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE I will not be able to use airport lounge access because my card is blocked. 
-No one from your 'team' has reached out. I have no dues. 
-Why should I continue an approx 40 year old relationship? You have denied me access without notification.</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>I will not be able to use airport lounge access because my card is blocked. 
-No one from your &amp;#39;team&amp;#39; has reached out. I have no dues. 
-Why should I continue an approx 40 year old relationship? You have denied me access without notification.</t>
-        </is>
-      </c>
-      <c r="K25" t="b">
-        <v>0</v>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>May 2</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>May 2, 2026 · 12:33 AM UTC</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="n">
-        <v>46144.02291666667</v>
-      </c>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>10</v>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>I will not be able to use airport lounge access because my card is blocked. 
-No one from your 'team' has reached out. I have no dues. 
-Why should I continue an approx 40 year old relationship? You have denied me access without notification.</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>https://x.com/STKgenghis/status/2050373118900977885</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE I will not be able to use airport lounge access because my card is blocked. 
-No one from your 'team' has reached out. I have no dues. 
-Why should I continue an approx 40 year old relationship? You have denied me access without notification.</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE I will not be able to use airport lounge access because my card is blocked. 
-No one from your 'team' has reached out. I have no dues. 
-Why should I continue an approx 40 year old relationship? You have denied me access without notification.</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>I will not be able to use airport lounge access because my card is blocked. 
-No one from your team has reached out. I have no dues. 
-Why should I continue a relationship of approximately 40 years? You have denied me access without notification.</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="AE25" s="2" t="n">
-        <v>46144.18958333333</v>
-      </c>
-      <c r="AF25" s="2" t="n">
-        <v>46144</v>
-      </c>
-      <c r="AG25" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>I will not be able to use airport lounge access because my card is blocked. • Why should I continue a relationship of approximately 40 years? • You have denied me access without notification.</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK25" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL25" t="inlineStr">
-        <is>
-          <t>EmiratesNBD_AE</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2050596951385944148</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>https://x.com/chin2to/status/2050596951385944148</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>https://x.com/chin2to</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>chin2to</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Chintn S. Padhya</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2006918638885060609/VLnYZV2k_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Finally thought I'll get an @EmiratesNBD_AE Skywards Credit Card, but applying for one is such a hassle. Changed my mind immediately after speaking to them for 2 months.</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>This is such a nightmare. The entire experience has been a nightmare and nothing more. Every time I call you guys, you say 48 working hours and then nothing! I can&amp;#39;t even cancel the credit card. It isn&amp;#39;t rocket science. Just call me back and cancel the card. Simple.</t>
-        </is>
-      </c>
-      <c r="K26" t="b">
-        <v>0</v>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>11h</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>May 2, 2026 · 3:23 PM UTC</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="n">
-        <v>46144.64097222222</v>
-      </c>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="n">
-        <v>1</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>4</v>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>This is such a nightmare. The entire experience has been a nightmare and nothing more. Every time I call you guys, you say 48 working hours and then nothing! I can't even cancel the credit card. It isn't rocket science. Just call me back and cancel the card. Simple.</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>https://x.com/chin2to/status/2050596951385944148</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>Finally thought I'll get an @EmiratesNBD_AE Skywards Credit Card, but applying for one is such a hassle. Changed my mind immediately after speaking to them for 2 months.</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>Finally thought I'll get an @EmiratesNBD_AE Skywards Credit Card, but applying for one is such a hassle. Changed my mind immediately after speaking to them for 2 months.</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>Finally thought I'd get an Emirates NBD Skywards Credit Card, but applying for one is such a hassle. I changed my mind immediately after speaking to them for 2 months.</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="AE26" s="2" t="n">
-        <v>46144.80763888889</v>
-      </c>
-      <c r="AF26" s="2" t="n">
-        <v>46144</v>
-      </c>
-      <c r="AG26" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Finally thought I'd get an Emirates NBD Skywards Credit Card, but applying for one is such a hassle. • I changed my mind immediately after speaking to them for 2 months.</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK26" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL26" t="inlineStr">
-        <is>
-          <t>EmiratesNBD_AE</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2050424878524940571</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>https://x.com/praksoni/status/2050424878524940571</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>https://x.com/praksoni</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>praksoni</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>prakash soni</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>@EmiratesIslamic You claim an AED 22k theft is "secure" just because it’s Apple Wallet? Your system failed to see that a UAE "Darb" enrollment turned into a massive London spending spree. I reported it at the exact minute it happened. This is a failure of your fraud monitoring.</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@EmiratesIslamic&lt;/a&gt; You claim an AED 22k theft is &amp;#34;secure&amp;#34; just because it’s Apple Wallet? Your system failed to see that a UAE &amp;#34;Darb&amp;#34; enrollment turned into a massive London spending spree. I reported it at the exact minute it happened. This is a failure of your fraud monitoring.</t>
-        </is>
-      </c>
-      <c r="K27" t="b">
-        <v>0</v>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>May 2, 2026 · 3:59 AM UTC</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="n">
-        <v>46144.16597222222</v>
-      </c>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>['https://x.com/emiratesislamic']</t>
-        </is>
-      </c>
-      <c r="S27" t="n">
-        <v>1</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>14</v>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>@EmiratesIslamic You claim an AED 22k theft is "secure" just because it’s Apple Wallet? Your system failed to see that a UAE "Darb" enrollment turned into a massive London spending spree. I reported it at the exact minute it happened. This is a failure of your fraud monitoring.</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>@EmiratesIslamic You claim an AED 22k theft is "secure" just because it’s Apple Wallet? Your system failed to see that a UAE "Darb" enrollment turned into a massive London spending spree. I reported it at the exact minute it happened. This is a failure of your fraud monitoring.</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>You claim an AED 22k theft is "secure" just because it’s Apple Wallet? Your system failed to see that a UAE "Darb" enrollment turned into a massive London spending spree. I reported it at the exact minute it happened. This is a failure of your fraud monitoring.</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="AE27" s="2" t="n">
-        <v>46144.33263888889</v>
-      </c>
-      <c r="AF27" s="2" t="n">
-        <v>46144</v>
-      </c>
-      <c r="AG27" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>You claim an AED 22k theft is "secure" just because it’s Apple Wallet? • Your system failed to see that a UAE "Darb" enrollment turned into a massive London spending spree. • I reported it at the exact minute it happened.</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK27" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL27" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>EmiratesNBD_KSA</t>
         </is>
       </c>
     </row>

--- a/check2.xlsx
+++ b/check2.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL19"/>
+  <dimension ref="A1:AL42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,43 +625,49 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2051149273409143066</t>
+          <t>2051475218783158326</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/patilabhijeet45/status/2051149273409143066</t>
+          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/patilabhijeet45</t>
+          <t>https://x.com/STKgenghis</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>patilabhijeet45</t>
+          <t>STKgenghis</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>abhijeet patil</t>
+          <t>khana-b-dosh</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1383992370509668355/lHQxfCEH_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1243248207293026305/b_s7UBzl_bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE hello team need your assistance please dm.</t>
+          <t>Open an Emirates NBD Millionaire Account to be the next winner, with over 1,400 cash prizes worth AED 50,000,000.
+- Monthly prizes up to AED 1,000,000
+- Grand prizes up to AED 5,000,000
+Dedicated prizes for Emiratis, expats, and businesses 🇦🇪</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>I have sent an email.</t>
+          <t>Update. 
+Received email from your social medium team saying &amp;#34;Dear,
+Kindly note that the account is not active.&amp;#34;
+No name. My account is active. Not sure what this cryptic email meant.</t>
         </is>
       </c>
       <c r="K2" t="b">
@@ -675,16 +681,16 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>5m</t>
+          <t>1h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>May 4, 2026 · 3:57 AM UTC</t>
+          <t>May 5, 2026 · 1:33 AM UTC</t>
         </is>
       </c>
       <c r="P2" s="2" t="n">
-        <v>46146.16458333333</v>
+        <v>46147.06458333333</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
@@ -698,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -707,27 +713,39 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>I have sent an email.</t>
+          <t>Update. 
+Received email from your social medium team saying "Dear,
+Kindly note that the account is not active."
+No name. My account is active. Not sure what this cryptic email meant.</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>https://x.com/patilabhijeet45/status/2051149273409143066</t>
+          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE hello team need your assistance please dm.</t>
+          <t>Open an Emirates NBD Millionaire Account to be the next winner, with over 1,400 cash prizes worth AED 50,000,000.
+- Monthly prizes up to AED 1,000,000
+- Grand prizes up to AED 5,000,000
+Dedicated prizes for Emiratis, expats, and businesses 🇦🇪</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE hello team need your assistance please dm.</t>
+          <t>Open an Emirates NBD Millionaire Account to be the next winner, with over 1,400 cash prizes worth AED 50,000,000.
+- Monthly prizes up to AED 1,000,000
+- Grand prizes up to AED 5,000,000
+Dedicated prizes for Emiratis, expats, and businesses 🇦🇪</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Hello team, I need your assistance, please direct message me.</t>
+          <t>Open an Emirates NBD Millionaire Account to be the next winner, with over 1,400 cash prizes worth AED 50,000,000. 
+- Monthly prizes up to AED 1,000,000 
+- Grand prizes up to AED 5,000,000 
+Dedicated prizes for Emiratis, expats, and businesses.</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -737,14 +755,14 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE2" s="2" t="n">
-        <v>46146.33125</v>
+        <v>46147.23125</v>
       </c>
       <c r="AF2" s="2" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
@@ -758,7 +776,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Hello team, I need your assistance, please direct message me.</t>
+          <t>- Monthly prizes up to AED 1,000,000 - Grand prizes up to AED 5,000,000 Dedicated prizes for Emiratis, expats, and businesses. • Open an Emirates NBD Millionaire Account to be the next winner, with over 1,400 cash prizes worth AED 50,000,000.</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -781,72 +799,70 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2051134720344535096</t>
+          <t>2051396418695578094</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/ClapPakistan/status/2051134720344535096</t>
+          <t>https://x.com/Muhamma38929354/status/2051396418695578094</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/ClapPakistan</t>
+          <t>https://x.com/Muhamma38929354</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ClapPakistan</t>
+          <t>Muhamma38929354</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Clap</t>
+          <t>Muhammad Usman</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1813702655031562240/RuM4t2kR_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1983485239554097152/bfvpy8sg_bigger.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Peshawar Zalmi Defeats Hyderabad Kingsmen to Win PSL 11 Final
-The image is AI-generated and is just for reference.
-#PSL11 #PSLFinal #PeshawarZalmi #HyderabadKingsmen https://t.co/2zhkzsurQv</t>
+          <t>Millionaire account limited-time offer
+Increase your balance and multiply your chances to win from AED 50,000,000 in cash prizes. Boost your balance today.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Syed Saad Shafi is Director – Signature Banking at Emirates NBD in Dubai, specializing in wealth management and global investment strategies for high-net-worth clients, overseeing multi-billion dirham portfolios.
-&lt;a href="/search?f=tweets&amp;amp;q=%23ClapPakistan"&gt;#ClapPakistan&lt;/a&gt;</t>
+          <t>On which date of the month is the draw held?</t>
         </is>
       </c>
       <c r="K3" t="b">
         <v>0</v>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1h</t>
+          <t>6h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>May 4, 2026 · 3:00 AM UTC</t>
+          <t>May 4, 2026 · 8:19 PM UTC</t>
         </is>
       </c>
       <c r="P3" s="2" t="n">
-        <v>46146.125</v>
+        <v>46146.84652777778</v>
       </c>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23ClapPakistan']</t>
-        </is>
-      </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
         <v>0</v>
       </c>
@@ -857,7 +873,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -866,32 +882,30 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Syed Saad Shafi is Director – Signature Banking at Emirates NBD in Dubai, specializing in wealth management and global investment strategies for high-net-worth clients, overseeing multi-billion dirham portfolios.
-#ClapPakistan</t>
+          <t>On which date of the month is the draw held?</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>https://x.com/ClapPakistan/status/2051134720344535096</t>
+          <t>https://x.com/Muhamma38929354/status/2051396418695578094</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Peshawar Zalmi Defeats Hyderabad Kingsmen to Win PSL 11 Final
-The image is AI-generated and is just for reference.
-#PSL11 #PSLFinal #PeshawarZalmi #HyderabadKingsmen https://t.co/2zhkzsurQv</t>
+          <t>Millionaire account limited-time offer
+Increase your balance and multiply your chances to win from AED 50,000,000 in cash prizes. Boost your balance today.</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Peshawar Zalmi Defeats Hyderabad Kingsmen to Win PSL 11 Final
-The image is AI-generated and is just for reference.
-#PSL11 #PSLFinal #PeshawarZalmi #HyderabadKingsmen https://t.co/2zhkzsurQv</t>
+          <t>Millionaire account limited-time offer
+Increase your balance and multiply your chances to win from AED 50,000,000 in cash prizes. Boost your balance today.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Peshawar Zalmi defeats Hyderabad Kingsmen to win the PSL 11 final.</t>
+          <t>Millionaire account limited-time offer
+Increase your balance and multiply your chances to win from AED 50,000,000 in cash prizes. Boost your balance today.</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -901,14 +915,14 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE3" s="2" t="n">
-        <v>46146.29166666666</v>
+        <v>46147.01319444444</v>
       </c>
       <c r="AF3" s="2" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
@@ -922,7 +936,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Peshawar Zalmi defeats Hyderabad Kingsmen to win the PSL 11 final.</t>
+          <t>Millionaire account limited-time offer Increase your balance and multiply your chances to win from AED 50,000,000 in cash prizes. • Boost your balance today.</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -935,7 +949,7 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
@@ -945,62 +959,66 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2050981352871264409</t>
+          <t>2051370896619974704</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/TrioMsPaname/status/2050981352871264409</t>
+          <t>https://x.com/patilabhijeet45/status/2051370896619974704</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/TrioMsPaname</t>
+          <t>https://x.com/patilabhijeet45</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>TrioMsPaname</t>
+          <t>patilabhijeet45</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>yiahhhh</t>
+          <t>abhijeet patil</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2043404881177006080/8Iry1NlJ_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1383992370509668355/lHQxfCEH_bigger.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Dubai prouve que ni la religion ni les étrangers sont le problème d’un état. Dubai tient avec 90% d étrangers. Tout le monde se tien à carreau, j’ai vécu une expérience incroyable de service, de sécurité et de kif. Merci @EmiratesNBD_AE</t>
+          <t>@EmiratesNBD_AE hello team need your assistance please dm.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Dubai prouve que ni la religion ni les étrangers sont le problème d’un état. Dubai tient avec 90% d étrangers. Tout le monde se tien à carreau, j’ai vécu une expérience incroyable de service, de sécurité et de kif. Merci &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;</t>
+          <t>Dear &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;  thank you very much for your assistance, really appreciate 🙏.</t>
         </is>
       </c>
       <c r="K4" t="b">
         <v>0</v>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>May 3, 2026 · 4:50 PM UTC</t>
+          <t>May 4, 2026 · 6:38 PM UTC</t>
         </is>
       </c>
       <c r="P4" s="2" t="n">
-        <v>46145.70138888889</v>
+        <v>46146.77638888889</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -1009,7 +1027,7 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -1027,27 +1045,27 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Dubai prouve que ni la religion ni les étrangers sont le problème d’un état. Dubai tient avec 90% d étrangers. Tout le monde se tien à carreau, j’ai vécu une expérience incroyable de service, de sécurité et de kif. Merci @EmiratesNBD_AE</t>
+          <t>Dear @EmiratesNBD_AE  thank you very much for your assistance, really appreciate 🙏.</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>https://x.com/TrioMsPaname/status/2050981352871264409</t>
+          <t>https://x.com/patilabhijeet45/status/2051370896619974704</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Dubai prouve que ni la religion ni les étrangers sont le problème d’un état. Dubai tient avec 90% d étrangers. Tout le monde se tien à carreau, j’ai vécu une expérience incroyable de service, de sécurité et de kif. Merci @EmiratesNBD_AE</t>
+          <t>@EmiratesNBD_AE hello team need your assistance please dm.</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Dubai prouve que ni la religion ni les étrangers sont le problème d’un état. Dubai tient avec 90% d étrangers. Tout le monde se tien à carreau, j’ai vécu une expérience incroyable de service, de sécurité et de kif. Merci @EmiratesNBD_AE</t>
+          <t>@EmiratesNBD_AE hello team need your assistance please dm.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Dubai proves that neither religion nor foreigners are the problem of a state. Dubai has 90% foreigners. Everyone behaves well; I had an incredible experience of service, security, and enjoyment. Thank you @EmiratesNBD_AE</t>
+          <t>Hello team, I need your assistance, please direct message me.</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1057,14 +1075,14 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE4" s="2" t="n">
-        <v>46145.86805555555</v>
+        <v>46146.94305555556</v>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
@@ -1078,7 +1096,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Dubai proves that neither religion nor foreigners are the problem of a state. • Dubai has 90% foreigners. • Everyone behaves well; I had an incredible experience of service, security, and enjoyment.</t>
+          <t>Hello team, I need your assistance, please direct message me.</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1091,7 +1109,7 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
@@ -1101,43 +1119,45 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2050948913431990505</t>
+          <t>2051364056217374823</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/ConmanNickJ/status/2050948913431990505</t>
+          <t>https://x.com/hisho25/status/2051364056217374823</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/ConmanNickJ</t>
+          <t>https://x.com/hisho25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ConmanNickJ</t>
+          <t>hisho25</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>conman Nick</t>
+          <t>H</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1945509816476094464/YIU-DVu4_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1609939487995346951/jwOMR5WV_bigger.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Yet the IRGC have been laundering billions through both the central bank and ENBD among other financial institutions in the UAE</t>
+          <t>لا تشيل هم الفاتورة 🤩
+مع 5% كاش باك على مقاضي السوبر ماركت مع بطاقة مزيد الائتمانية من #بنك_الإمارات_دبي_الوطني 👌🏼💙
+للتفاصيل:https://t.co/oJpg7cbDbn https://t.co/cWHpRlVIyY</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Yet the IRGC have been laundering billions through both the central bank and ENBD among other financial institutions in the UAE</t>
+          <t>ماجاني شي على الخاص</t>
         </is>
       </c>
       <c r="K5" t="b">
@@ -1146,26 +1166,26 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>['NarcisW63452', 'amjadt25']</t>
+          <t>['EmiratesNBD_KSA']</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>May 3, 2026 · 2:41 PM UTC</t>
+          <t>May 4, 2026 · 6:11 PM UTC</t>
         </is>
       </c>
       <c r="P5" s="2" t="n">
-        <v>46145.61180555556</v>
+        <v>46146.75763888889</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1174,7 +1194,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1183,19 +1203,31 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Yet the IRGC have been laundering billions through both the central bank and ENBD among other financial institutions in the UAE</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
+          <t>ماجاني شي على الخاص</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>https://x.com/hisho25/status/2051364056217374823</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>لا تشيل هم الفاتورة 🤩
+مع 5% كاش باك على مقاضي السوبر ماركت مع بطاقة مزيد الائتمانية من #بنك_الإمارات_دبي_الوطني 👌🏼💙
+للتفاصيل:https://t.co/oJpg7cbDbn https://t.co/cWHpRlVIyY</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Yet the IRGC have been laundering billions through both the central bank and ENBD among other financial institutions in the UAE</t>
+          <t>لا تشيل هم الفاتورة 🤩
+مع 5% كاش باك على مقاضي السوبر ماركت مع بطاقة مزيد الائتمانية من #بنك_الإمارات_دبي_الوطني 👌🏼💙
+للتفاصيل:https://t.co/oJpg7cbDbn https://t.co/cWHpRlVIyY</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Yet the IRGC has been laundering billions through both the central bank and ENBD among other financial institutions in the UAE.</t>
+          <t>Don't worry about the bill 🤩 With 5% cashback on supermarket purchases using the Mazid credit card from #Emirates_NBD Bank 👌🏼💙 For details: https://t.co/oJpg7cbDbn https://t.co/cWHpRlVIyY</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1205,14 +1237,14 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE5" s="2" t="n">
-        <v>46145.77847222222</v>
+        <v>46146.92430555556</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
@@ -1226,7 +1258,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Yet the IRGC has been laundering billions through both the central bank and ENBD among other financial institutions in the UAE.</t>
+          <t>Don't worry about the bill 🤩 With 5% cashback on supermarket purchases using the Mazid credit card from #Emirates_NBD Bank 👌🏼💙 For details: https://t.co/oJpg7cbDbn https://t.co/cWHpRlVIyY</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1239,7 +1271,7 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>NarcisW63452, amjadt25</t>
+          <t>EmiratesNBD_KSA</t>
         </is>
       </c>
     </row>
@@ -1249,43 +1281,43 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2050919285036360149</t>
+          <t>2051355715994878347</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/Professor502/status/2050919285036360149</t>
+          <t>https://x.com/hisho25/status/2051355715994878347</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/Professor502</t>
+          <t>https://x.com/hisho25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Professor502</t>
+          <t>hisho25</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saad</t>
+          <t>H</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1908889888478425088/ezst5JDu_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1609939487995346951/jwOMR5WV_bigger.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ردو على الخاص لو سمحت</t>
+          <t>متى بتدعمون سامسونج باي؟؟</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>ردو على الخاص لو سمحت</t>
+          <t>متى بتدعمون سامسونج باي؟؟</t>
         </is>
       </c>
       <c r="K6" t="b">
@@ -1299,21 +1331,21 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>9h</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>May 3, 2026 · 12:43 PM UTC</t>
+          <t>May 4, 2026 · 5:38 PM UTC</t>
         </is>
       </c>
       <c r="P6" s="2" t="n">
-        <v>46145.52986111111</v>
+        <v>46146.73472222222</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1322,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1331,19 +1363,19 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>ردو على الخاص لو سمحت</t>
+          <t>متى بتدعمون سامسونج باي؟؟</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>ردو على الخاص لو سمحت</t>
+          <t>متى بتدعمون سامسونج باي؟؟</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Please reply in private, if you don't mind.</t>
+          <t>When will you support Samsung Pay?</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1357,10 +1389,10 @@
         </is>
       </c>
       <c r="AE6" s="2" t="n">
-        <v>46145.69652777778</v>
+        <v>46146.90138888889</v>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
@@ -1374,7 +1406,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Please reply in private, if you don't mind.</t>
+          <t>When will you support Samsung Pay?</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1397,80 +1429,86 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2050908749720703120</t>
+          <t>2051335593389601255</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/abotameem430/status/2050908749720703120</t>
+          <t>https://x.com/InformistMedia/status/2051335593389601255</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://x.com/abotameem430</t>
+          <t>https://x.com/InformistMedia</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>abotameem430</t>
+          <t>InformistMedia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fahad</t>
+          <t>Informist Media</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1780850701616242688/Ikq26ySl_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1845064843897827333/CfVeov1j_bigger.png</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ارغب بالاتصال</t>
+          <t>The Securities and Exchange Board of India on Monday approved the change in control of RBL Bank with regard to the ongoing acquisition of "certain" shareholding by Emirates NBD Bank in the Indian lender, RBL Bank said in an exchange filing. The Dubai-based lender has proposed to buy up to 60% stake in the Indian private-sector bank, and the Competition Commission of India has already approved it on Jan. 20.
+#SEBI
+Details Here:
+informistmedia.com/MoneyWire…</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>ارغب بالاتصال</t>
+          <t>The Securities and Exchange Board of India on Monday approved the change in control of RBL Bank with regard to the ongoing acquisition of &amp;#34;certain&amp;#34; shareholding by Emirates NBD Bank in the Indian lender, RBL Bank said in an exchange filing. The Dubai-based lender has proposed to buy up to 60% stake in the Indian private-sector bank, and the Competition Commission of India has already approved it on Jan. 20.
+&lt;a href="/search?f=tweets&amp;amp;q=%23SEBI"&gt;#SEBI&lt;/a&gt;
+Details Here:
+&lt;a href="https://informistmedia.com/MoneyWire/49753/Ongoing-acquisition-SEBI-OKs-change-in-control-of-RBL-Bank-amid-Emirates-NBD-s-stake-acquisition"&gt;informistmedia.com/MoneyWire…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K7" t="b">
         <v>0</v>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>May 3, 2026 · 12:02 PM UTC</t>
+          <t>May 4, 2026 · 4:18 PM UTC</t>
         </is>
       </c>
       <c r="P7" s="2" t="n">
-        <v>46145.50138888889</v>
+        <v>46146.67916666667</v>
       </c>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23SEBI', 'https://informistmedia.com/MoneyWire/49753/Ongoing-acquisition-SEBI-OKs-change-in-control-of-RBL-Bank-amid-Emirates-NBD-s-stake-acquisition']</t>
+        </is>
+      </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
-        <v>3</v>
+        <v>448</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1479,19 +1517,25 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>ارغب بالاتصال</t>
+          <t>The Securities and Exchange Board of India on Monday approved the change in control of RBL Bank with regard to the ongoing acquisition of "certain" shareholding by Emirates NBD Bank in the Indian lender, RBL Bank said in an exchange filing. The Dubai-based lender has proposed to buy up to 60% stake in the Indian private-sector bank, and the Competition Commission of India has already approved it on Jan. 20.
+#SEBI
+Details Here:
+informistmedia.com/MoneyWire…</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>ارغب بالاتصال</t>
+          <t>The Securities and Exchange Board of India on Monday approved the change in control of RBL Bank with regard to the ongoing acquisition of "certain" shareholding by Emirates NBD Bank in the Indian lender, RBL Bank said in an exchange filing. The Dubai-based lender has proposed to buy up to 60% stake in the Indian private-sector bank, and the Competition Commission of India has already approved it on Jan. 20.
+#SEBI
+Details Here:
+informistmedia.com/MoneyWire…</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>I would like to make a call.</t>
+          <t>The Securities and Exchange Board of India on Monday approved the change in control of RBL Bank concerning the ongoing acquisition of "certain" shareholding by Emirates NBD Bank in the Indian lender, RBL Bank said in an exchange filing. The Dubai-based lender has proposed to buy up to a 60% stake in the Indian private-sector bank, and the Competition Commission of India has already approved it on January 20.</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1505,10 +1549,10 @@
         </is>
       </c>
       <c r="AE7" s="2" t="n">
-        <v>46145.66805555556</v>
+        <v>46146.84583333333</v>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
@@ -1522,7 +1566,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>I would like to make a call.</t>
+          <t>The Dubai-based lender has proposed to buy up to a 60% stake in the Indian private-sector bank, and the Competition Commission of India has already approved it on January 20.</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1535,7 +1579,7 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1545,43 +1589,43 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2050881500527415748</t>
+          <t>2051310789596754286</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/MahtabAbbasi11/status/2050881500527415748</t>
+          <t>https://x.com/RedHat/status/2051310789596754286</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://x.com/MahtabAbbasi11</t>
+          <t>https://x.com/RedHat</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MahtabAbbasi11</t>
+          <t>RedHat</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mahtab Abbasi</t>
+          <t>Red Hat</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2042928635620081664/TSR-bQI9_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1123557710191001600/oMQc_xqN_bigger.png</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Emirates NBD to settle Visa payments in UAE dirhams, a major shift for daily transactions</t>
+          <t>2026 Innovation Awards winner @EmiratesNBD_AE manages 9,000 VMs and modern containers on one unified platform -  a modern, stable platform for innovation. See how they did it: red.ht/4ukH5l4 #RHSummit</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Emirates NBD to settle Visa payments in UAE dirhams, a major shift for daily transactions</t>
+          <t>2026 Innovation Awards winner &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; manages 9,000 VMs and modern containers on one unified platform -  a modern, stable platform for innovation. See how they did it: &lt;a href="https://red.ht/4ukH5l4"&gt;red.ht/4ukH5l4&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23RHSummit"&gt;#RHSummit&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K8" t="b">
@@ -1591,19 +1635,23 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>12h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>May 3, 2026 · 10:13 AM UTC</t>
+          <t>May 4, 2026 · 2:39 PM UTC</t>
         </is>
       </c>
       <c r="P8" s="2" t="n">
-        <v>46145.42569444444</v>
+        <v>46146.61041666667</v>
       </c>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE', 'https://red.ht/4ukH5l4', 'https://x.com/search?f=tweets&amp;q=%23RHSummit']</t>
+        </is>
+      </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
@@ -1614,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>23</v>
+        <v>191</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1623,19 +1671,19 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Emirates NBD to settle Visa payments in UAE dirhams, a major shift for daily transactions</t>
+          <t>2026 Innovation Awards winner @EmiratesNBD_AE manages 9,000 VMs and modern containers on one unified platform -  a modern, stable platform for innovation. See how they did it: red.ht/4ukH5l4 #RHSummit</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Emirates NBD to settle Visa payments in UAE dirhams, a major shift for daily transactions</t>
+          <t>2026 Innovation Awards winner @EmiratesNBD_AE manages 9,000 VMs and modern containers on one unified platform -  a modern, stable platform for innovation. See how they did it: red.ht/4ukH5l4 #RHSummit</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Emirates NBD to settle Visa payments in UAE dirhams, a major shift for daily transactions.</t>
+          <t>2026 Innovation Awards winner Emirates NBD manages 9,000 VMs and modern containers on one unified platform - a modern, stable platform for innovation. See how they did it: red.ht/4ukH5l4 #RHSummit</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1645,14 +1693,14 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE8" s="2" t="n">
-        <v>46145.59236111111</v>
+        <v>46146.77708333333</v>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
@@ -1666,7 +1714,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Emirates NBD to settle Visa payments in UAE dirhams, a major shift for daily transactions.</t>
+          <t>2026 Innovation Awards winner Emirates NBD manages 9,000 VMs and modern containers on one unified platform - a modern, stable platform for innovation. • See how they did it: red.ht/4ukH5l4 #RHSummit</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1689,45 +1737,47 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2050877343745388916</t>
+          <t>2051298992416272612</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://x.com/t_Abdulraahman/status/2050877343745388916</t>
+          <t>https://x.com/FreshGulfJob/status/2051298992416272612</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://x.com/t_Abdulraahman</t>
+          <t>https://x.com/FreshGulfJob</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>t_Abdulraahman</t>
+          <t>FreshGulfJob</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>T.Abdulrahman</t>
+          <t>Fresh Gulf Job</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1653777797888843776/NhAjroqA_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1487393053300064256/dEfLlKtr_bigger.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE طلبت بطاقة مزيد بحد مالي محدد 
-و وصلتني البطاقه بحد مالي عالي جداً ! كيف ممكن اقلل الحد اقدر او لا لاني مافعلت الى الان</t>
+          <t>Emirates NBD Job Vacancies Dubai | Latest Careers UAE (2026)
+Apply Link&gt;&gt; buff.ly/7izZwL2
+#jobs #careers #jobvacancy #jobs2026 #hiring #freshgulfjob #recruitment #jobvacancy2026 #UAEJobs #dubaijobs</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; طلبت بطاقة مزيد بحد مالي محدد 
-و وصلتني البطاقه بحد مالي عالي جداً ! كيف ممكن اقلل الحد اقدر او لا لاني مافعلت الى الان</t>
+          <t>Emirates NBD Job Vacancies Dubai | Latest Careers UAE (2026)
+Apply Link&amp;gt;&amp;gt; &lt;a href="https://buff.ly/7izZwL2"&gt;buff.ly/7izZwL2&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23jobs"&gt;#jobs&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23careers"&gt;#careers&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23jobvacancy"&gt;#jobvacancy&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23jobs2026"&gt;#jobs2026&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23hiring"&gt;#hiring&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23freshgulfjob"&gt;#freshgulfjob&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23recruitment"&gt;#recruitment&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23jobvacancy2026"&gt;#jobvacancy2026&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23UAEJobs"&gt;#UAEJobs&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23dubaijobs"&gt;#dubaijobs&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K9" t="b">
@@ -1737,34 +1787,34 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>12h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>May 3, 2026 · 9:57 AM UTC</t>
+          <t>May 4, 2026 · 1:52 PM UTC</t>
         </is>
       </c>
       <c r="P9" s="2" t="n">
-        <v>46145.41458333333</v>
+        <v>46146.57777777778</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>['https://x.com/EmiratesNBD_AE']</t>
+          <t>['https://buff.ly/7izZwL2', 'https://x.com/search?f=tweets&amp;q=%23jobs', 'https://x.com/search?f=tweets&amp;q=%23careers', 'https://x.com/search?f=tweets&amp;q=%23jobvacancy', 'https://x.com/search?f=tweets&amp;q=%23jobs2026', 'https://x.com/search?f=tweets&amp;q=%23hiring', 'https://x.com/search?f=tweets&amp;q=%23freshgulfjob', 'https://x.com/search?f=tweets&amp;q=%23recruitment', 'https://x.com/search?f=tweets&amp;q=%23jobvacancy2026', 'https://x.com/search?f=tweets&amp;q=%23UAEJobs', 'https://x.com/search?f=tweets&amp;q=%23dubaijobs']</t>
         </is>
       </c>
       <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
         <v>1</v>
       </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
       <c r="V9" t="n">
-        <v>12</v>
+        <v>187</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1773,21 +1823,23 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE طلبت بطاقة مزيد بحد مالي محدد 
-و وصلتني البطاقه بحد مالي عالي جداً ! كيف ممكن اقلل الحد اقدر او لا لاني مافعلت الى الان</t>
+          <t>Emirates NBD Job Vacancies Dubai | Latest Careers UAE (2026)
+Apply Link&gt;&gt; buff.ly/7izZwL2
+#jobs #careers #jobvacancy #jobs2026 #hiring #freshgulfjob #recruitment #jobvacancy2026 #UAEJobs #dubaijobs</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE طلبت بطاقة مزيد بحد مالي محدد 
-و وصلتني البطاقه بحد مالي عالي جداً ! كيف ممكن اقلل الحد اقدر او لا لاني مافعلت الى الان</t>
+          <t>Emirates NBD Job Vacancies Dubai | Latest Careers UAE (2026)
+Apply Link&gt;&gt; buff.ly/7izZwL2
+#jobs #careers #jobvacancy #jobs2026 #hiring #freshgulfjob #recruitment #jobvacancy2026 #UAEJobs #dubaijobs</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>I requested a Mazid card with a specific credit limit, and I received the card with a very high limit! How can I reduce the limit? Can I do that since I haven't activated it yet?</t>
+          <t>Emirates NBD Job Vacancies Dubai | Latest Careers UAE (2026) Apply Link&gt;&gt; buff.ly/7izZwL2</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1801,10 +1853,10 @@
         </is>
       </c>
       <c r="AE9" s="2" t="n">
-        <v>46145.58125</v>
+        <v>46146.74444444444</v>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
@@ -1818,7 +1870,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>I requested a Mazid card with a specific credit limit, and I received the card with a very high limit! • How can I reduce the limit? • Can I do that since I haven't activated it yet?</t>
+          <t>Emirates NBD Job Vacancies Dubai | Latest Careers UAE (2026) Apply Link&gt;&gt; buff.ly/7izZwL2</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1841,45 +1893,43 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2050855805600092255</t>
+          <t>2051294193515917659</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://x.com/gulf_news/status/2050855805600092255</t>
+          <t>https://x.com/deegrose/status/2051294193515917659</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://x.com/gulf_news</t>
+          <t>https://x.com/deegrose</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>gulf_news</t>
+          <t>deegrose</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gulf News</t>
+          <t>DeeG (Maria)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2044041782519050242/muvl0wJC_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2049879312543657984/hKTDD9K__bigger.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Whether you're paying your bills, transferring money within the UAE, sending it abroad or exchanging currencies, Emirates NBD makes it simple and secure through the ENBD X app.
-#transfers #payments #DirectRemit #Aani #currencies #travel #GlobalCash
-https://t.co/JhadMTFApo https://t.co/WHukK5bQyz</t>
+          <t>ADIB, Emirates NBD close $164mln loan for London property zawya.com/en/capital-markets…</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Emirates NBD to settle Visa payments in UAE dirhams, a major shift for daily transactions &lt;a href="https://mrf.lu/FJY3"&gt;mrf.lu/FJY3&lt;/a&gt;</t>
+          <t>ADIB, Emirates NBD close $164mln loan for London property &lt;a href="https://www.zawya.com/en/capital-markets/loans/adib-emirates-nbd-close-164mln-loan-for-london-property-n8gjsfqa"&gt;zawya.com/en/capital-markets…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K10" t="b">
@@ -1889,34 +1939,34 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>May 3, 2026 · 8:31 AM UTC</t>
+          <t>May 4, 2026 · 1:33 PM UTC</t>
         </is>
       </c>
       <c r="P10" s="2" t="n">
-        <v>46145.35486111111</v>
+        <v>46146.56458333333</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>['https://mrf.lu/FJY3']</t>
+          <t>['https://www.zawya.com/en/capital-markets/loans/adib-emirates-nbd-close-164mln-loan-for-london-property-n8gjsfqa']</t>
         </is>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>3733</v>
+        <v>12</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1925,31 +1975,19 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Emirates NBD to settle Visa payments in UAE dirhams, a major shift for daily transactions mrf.lu/FJY3</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>https://x.com/gulf_news/status/2050855805600092255</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Whether you're paying your bills, transferring money within the UAE, sending it abroad or exchanging currencies, Emirates NBD makes it simple and secure through the ENBD X app.
-#transfers #payments #DirectRemit #Aani #currencies #travel #GlobalCash
-https://t.co/JhadMTFApo https://t.co/WHukK5bQyz</t>
-        </is>
-      </c>
+          <t>ADIB, Emirates NBD close $164mln loan for London property zawya.com/en/capital-markets…</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Whether you're paying your bills, transferring money within the UAE, sending it abroad or exchanging currencies, Emirates NBD makes it simple and secure through the ENBD X app.
-#transfers #payments #DirectRemit #Aani #currencies #travel #GlobalCash
-https://t.co/JhadMTFApo https://t.co/WHukK5bQyz</t>
+          <t>ADIB, Emirates NBD close $164mln loan for London property zawya.com/en/capital-markets…</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Whether you're paying your bills, transferring money within the UAE, sending it abroad, or exchanging currencies, Emirates NBD makes it simple and secure through the ENBD X app.</t>
+          <t>ADIB and Emirates NBD have finalized a $164 million loan for a property in London.</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1959,14 +1997,14 @@
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE10" s="2" t="n">
-        <v>46145.52152777778</v>
+        <v>46146.73125</v>
       </c>
       <c r="AF10" s="2" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
@@ -1980,7 +2018,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Whether you're paying your bills, transferring money within the UAE, sending it abroad, or exchanging currencies, Emirates NBD makes it simple and secure through the ENBD X app.</t>
+          <t>ADIB and Emirates NBD have finalized a $164 million loan for a property in London.</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -2003,80 +2041,94 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2050845248088055847</t>
+          <t>2051288211184332916</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/z6894890/status/2050845248088055847</t>
+          <t>https://x.com/hisho25/status/2051288211184332916</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://x.com/z6894890</t>
+          <t>https://x.com/hisho25</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>z6894890</t>
+          <t>hisho25</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Femal</t>
+          <t>H</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1609939487995346951/jwOMR5WV_bigger.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE ابي وظيفه باي فرع من اللي بالرياض</t>
+          <t>انا قلت تقريبا مب 100% و الاكثر شعبية تفعلوا الان 
+يعني باقي هذولي للاسف
+@MobilyPay 
+@visionbank_sa
+@EmiratesNBD_KSA 
+@FABConnects</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; ابي وظيفه باي فرع من اللي بالرياض</t>
+          <t>انا قلت تقريبا مب 100% و الاكثر شعبية تفعلوا الان 
+يعني باقي هذولي للاسف
+&lt;a href="/MobilyPay" title="Mobily Pay"&gt;@MobilyPay&lt;/a&gt; 
+&lt;a href="/visionbank_sa" title="بنك فيجن"&gt;@visionbank_sa&lt;/a&gt;
+&lt;a href="/EmiratesNBD_KSA" title="Emirates NBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; 
+&lt;a href="/FABConnects" title="FAB Connects"&gt;@FABConnects&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K11" t="b">
         <v>0</v>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>['karimmohnaguib1', 'FinTech_KSA']</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>May 3, 2026 · 7:49 AM UTC</t>
+          <t>May 4, 2026 · 1:09 PM UTC</t>
         </is>
       </c>
       <c r="P11" s="2" t="n">
-        <v>46145.32569444444</v>
+        <v>46146.54791666667</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>['https://x.com/EmiratesNBD_AE']</t>
+          <t>['https://x.com/MobilyPay', 'https://x.com/visionbank_sa', 'https://x.com/EmiratesNBD_KSA', 'https://x.com/FABConnects']</t>
         </is>
       </c>
       <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
         <v>1</v>
       </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
       <c r="V11" t="n">
-        <v>14</v>
+        <v>848</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -2085,27 +2137,29 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE ابي وظيفه باي فرع من اللي بالرياض</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>https://x.com/z6894890/status/2050845248088055847</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE ابي وظيفه باي فرع من اللي بالرياض</t>
-        </is>
-      </c>
+          <t>انا قلت تقريبا مب 100% و الاكثر شعبية تفعلوا الان 
+يعني باقي هذولي للاسف
+@MobilyPay 
+@visionbank_sa
+@EmiratesNBD_KSA 
+@FABConnects</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE ابي وظيفه باي فرع من اللي بالرياض</t>
+          <t>انا قلت تقريبا مب 100% و الاكثر شعبية تفعلوا الان 
+يعني باقي هذولي للاسف
+@MobilyPay 
+@visionbank_sa
+@EmiratesNBD_KSA 
+@FABConnects</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>I want a job at any branch in Riyadh.</t>
+          <t>I said almost not 100% and the most popular ones are active now. Unfortunately, these are the remaining ones.</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2119,10 +2173,10 @@
         </is>
       </c>
       <c r="AE11" s="2" t="n">
-        <v>46145.49236111111</v>
+        <v>46146.71458333333</v>
       </c>
       <c r="AF11" s="2" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
@@ -2136,7 +2190,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>I want a job at any branch in Riyadh.</t>
+          <t>I said almost not 100% and the most popular ones are active now. • Unfortunately, these are the remaining ones.</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -2149,7 +2203,7 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>karimmohnaguib1, FinTech_KSA</t>
         </is>
       </c>
     </row>
@@ -2159,86 +2213,85 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2050841752987136094</t>
+          <t>2051287062402540010</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://x.com/FintechGate1/status/2050841752987136094</t>
+          <t>https://x.com/BabyIamInJail/status/2051287062402540010</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://x.com/FintechGate1</t>
+          <t>https://x.com/BabyIamInJail</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FintechGate1</t>
+          <t>BabyIamInJail</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FinTech Gate-بوابة التكنولوجيا المالية</t>
+          <t>حوا🍎</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1630704388531470336/_2WZb_12_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1931562837521911809/dqyeDv4z_bigger.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Emirates NBD Egypt Releases Its Third Sustainability Report, Reporting Strong Profit Growth and a Strategic Shift Toward Renewable Energy
- https://t.co/zMJRGwIJEz  | details 
-#fintech_gate
-#Emirates_NBD_Egypt_Releases https://t.co/JnNoI8ViAd</t>
+          <t>@BabyIamInJail پشمام دنبال قبض آب هم افتادن؟
+متاسفانه اطلاعی ندارم. یه سال و نیمه هی فرم جهت شناسایی شهروندای آمریکا میفرستن، ولی این مدلیشو ندیده بودم</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Emirates NBD Egypt Releases Its Third Sustainability Report, Reporting Strong Profit Growth and a Strategic Shift Toward Renewable Energy
- &lt;a href="https://fintechgate.net/rhb4"&gt;fintechgate.net/rhb4&lt;/a&gt;  | details 
-&lt;a href="/search?f=tweets&amp;amp;q=%23fintech_gate"&gt;#fintech_gate&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23Emirates_NBD_Egypt_Releases"&gt;#Emirates_NBD_Egypt_Releases&lt;/a&gt;</t>
+          <t>عه چی؟
+امروز دقیقا ENBD بودم
+ازم قبض آب از تورنتو می خواست!
+راهی داره اطلاعات مالیاتی ازم نگیرند؟
+تو کانادا ممکنه audit بخورم اگه با هم حرف بزنند. تا ثابت کنی بابا دوهزار بوده، کلی خرج audit شده.</t>
         </is>
       </c>
       <c r="K12" t="b">
         <v>0</v>
       </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>['bokonndarro']</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>May 3, 2026 · 7:35 AM UTC</t>
+          <t>May 4, 2026 · 1:05 PM UTC</t>
         </is>
       </c>
       <c r="P12" s="2" t="n">
-        <v>46145.31597222222</v>
+        <v>46146.54513888889</v>
       </c>
       <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>['https://fintechgate.net/rhb4', 'https://x.com/search?f=tweets&amp;q=%23fintech_gate', 'https://x.com/search?f=tweets&amp;q=%23Emirates_NBD_Egypt_Releases']</t>
-        </is>
-      </c>
+      <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" t="n">
-        <v>9</v>
+        <v>75</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -2247,36 +2300,33 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Emirates NBD Egypt Releases Its Third Sustainability Report, Reporting Strong Profit Growth and a Strategic Shift Toward Renewable Energy
- fintechgate.net/rhb4  | details 
-#fintech_gate
-#Emirates_NBD_Egypt_Releases</t>
+          <t>عه چی؟
+امروز دقیقا ENBD بودم
+ازم قبض آب از تورنتو می خواست!
+راهی داره اطلاعات مالیاتی ازم نگیرند؟
+تو کانادا ممکنه audit بخورم اگه با هم حرف بزنند. تا ثابت کنی بابا دوهزار بوده، کلی خرج audit شده.</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>https://x.com/FintechGate1/status/2050841752987136094</t>
+          <t>https://x.com/BabyIamInJail/status/2051287062402540010</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>Emirates NBD Egypt Releases Its Third Sustainability Report, Reporting Strong Profit Growth and a Strategic Shift Toward Renewable Energy
- https://t.co/zMJRGwIJEz  | details 
-#fintech_gate
-#Emirates_NBD_Egypt_Releases https://t.co/JnNoI8ViAd</t>
+          <t>@BabyIamInJail پشمام دنبال قبض آب هم افتادن؟
+متاسفانه اطلاعی ندارم. یه سال و نیمه هی فرم جهت شناسایی شهروندای آمریکا میفرستن، ولی این مدلیشو ندیده بودم</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Emirates NBD Egypt Releases Its Third Sustainability Report, Reporting Strong Profit Growth and a Strategic Shift Toward Renewable Energy
- https://t.co/zMJRGwIJEz  | details 
-#fintech_gate
-#Emirates_NBD_Egypt_Releases https://t.co/JnNoI8ViAd</t>
+          <t>@BabyIamInJail پشمام دنبال قبض آب هم افتادن؟
+متاسفانه اطلاعی ندارم. یه سال و نیمه هی فرم جهت شناسایی شهروندای آمریکا میفرستن، ولی این مدلیشو ندیده بودم</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Emirates NBD Egypt Releases Its Third Sustainability Report, Reporting Strong Profit Growth and a Strategic Shift Toward Renewable Energy</t>
+          <t>Are they after my water bill too? Unfortunately, I have no information. For a year and a half, they have been sending forms to identify American citizens, but I haven't seen one like this.</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2286,14 +2336,14 @@
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE12" s="2" t="n">
-        <v>46145.48263888889</v>
+        <v>46146.71180555555</v>
       </c>
       <c r="AF12" s="2" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
@@ -2307,7 +2357,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Emirates NBD Egypt Releases Its Third Sustainability Report, Reporting Strong Profit Growth and a Strategic Shift Toward Renewable Energy</t>
+          <t>For a year and a half, they have been sending forms to identify American citizens, but I haven't seen one like this. • Are they after my water bill too? • Unfortunately, I have no information.</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2320,7 +2370,7 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>bokonndarro</t>
         </is>
       </c>
     </row>
@@ -2330,46 +2380,44 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2050809333848342901</t>
+          <t>2051283691821834411</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://x.com/abotameem430/status/2050809333848342901</t>
+          <t>https://x.com/bokonndarro/status/2051283691821834411</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://x.com/abotameem430</t>
+          <t>https://x.com/bokonndarro</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>abotameem430</t>
+          <t>bokonndarro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fahad</t>
+          <t>Foroogh 🇮🇷</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1780850701616242688/Ikq26ySl_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2035505557650702336/C0i2amSB_bigger.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Apply smarter, faster, and hassle-free.
-With our Straight Through Processing (STP) journey, complete your application in minutes—no delays.
-Watch how easy it is to get started.
-Apply Now: https://t.co/aeh8nbj5gC https://t.co/y7g1WeVQ6R</t>
+          <t>ادمین دبی اینترنشنال چرا انقدر حیوونه :)))))))) https://t.co/juEIzEYwCT</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>اريد تمويل وارغب بالاتصال</t>
+          <t>توریست که چیزی نیست من با صد سال اقامت چند سال پیش با زور آشنا تو Emirates NBD برام حساب باز کردن :))) 
+ولی الان واسه جذب توریست و سرمایه‌گذار چندین طرح جدید ارائه کردن</t>
         </is>
       </c>
       <c r="K13" t="b">
@@ -2378,21 +2426,21 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_AE']</t>
+          <t>['BabyIamInJail']</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>May 3, 2026 · 5:27 AM UTC</t>
+          <t>May 4, 2026 · 12:51 PM UTC</t>
         </is>
       </c>
       <c r="P13" s="2" t="n">
-        <v>46145.22708333333</v>
+        <v>46146.53541666667</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
@@ -2403,10 +2451,10 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V13" t="n">
-        <v>19</v>
+        <v>672</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -2415,33 +2463,28 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>اريد تمويل وارغب بالاتصال</t>
+          <t>توریست که چیزی نیست من با صد سال اقامت چند سال پیش با زور آشنا تو Emirates NBD برام حساب باز کردن :))) 
+ولی الان واسه جذب توریست و سرمایه‌گذار چندین طرح جدید ارائه کردن</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>https://x.com/abotameem430/status/2050809333848342901</t>
+          <t>https://x.com/bokonndarro/status/2051283691821834411</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>Apply smarter, faster, and hassle-free.
-With our Straight Through Processing (STP) journey, complete your application in minutes—no delays.
-Watch how easy it is to get started.
-Apply Now: https://t.co/aeh8nbj5gC https://t.co/y7g1WeVQ6R</t>
+          <t>ادمین دبی اینترنشنال چرا انقدر حیوونه :)))))))) https://t.co/juEIzEYwCT</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Apply smarter, faster, and hassle-free.
-With our Straight Through Processing (STP) journey, complete your application in minutes—no delays.
-Watch how easy it is to get started.
-Apply Now: https://t.co/aeh8nbj5gC https://t.co/y7g1WeVQ6R</t>
+          <t>ادمین دبی اینترنشنال چرا انقدر حیوونه :)))))))) https://t.co/juEIzEYwCT</t>
   